--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K735"/>
+  <dimension ref="A1:K771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21766,6 +21766,1050 @@
       </c>
       <c r="K735" t="inlineStr"/>
     </row>
+    <row r="736">
+      <c r="A736" s="1" t="n">
+        <v>734</v>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0001.png</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr"/>
+      <c r="D736" t="inlineStr"/>
+      <c r="E736" t="inlineStr"/>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>CCCCCC/C=C/C=C/CCCCCCCC(=O)OCC(C)C(=O)CCCCCCC/C=C/C=C/CCCCCC.CCCCCC/C=C/C=C/CCCCCCCC(=O)OCCOC(=O)CCCCCCC/C=C/C=C/CCCCCC</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr"/>
+      <c r="H736" t="inlineStr"/>
+      <c r="I736" t="n">
+        <v>0.8242984419714765</v>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr"/>
+    </row>
+    <row r="737">
+      <c r="A737" s="1" t="n">
+        <v>735</v>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0002.png</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr"/>
+      <c r="D737" t="inlineStr"/>
+      <c r="E737" t="inlineStr"/>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>c1ccc2cc3c(cc2c1)-c1nc-3nc2[nH]c(nc3nc(nc4[nH]c(n1)c1cc5ccccc5cc41)-c1cc4ccccc4cc1-3)c1cc3ccccc3cc21</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr"/>
+      <c r="H737" t="inlineStr"/>
+      <c r="I737" t="n">
+        <v>0.6823870792080131</v>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr"/>
+    </row>
+    <row r="738">
+      <c r="A738" s="1" t="n">
+        <v>736</v>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0003.png</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr"/>
+      <c r="D738" t="inlineStr"/>
+      <c r="E738" t="inlineStr"/>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>CC1(C)CC23(CC(C)(C)C4=C2C3=C(C2=CC=C(C3=NC5=C(C=C3)C=CC3=C5N=CC=C3)C=C2)C=C4)C2=CC(C3=CC=C(C4=NC5=C(C=C4)C=CC4=C5N=CC=C4)C=C3)=CC=C21</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr"/>
+      <c r="H738" t="inlineStr"/>
+      <c r="I738" t="n">
+        <v>0.7612379923929188</v>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr"/>
+    </row>
+    <row r="739">
+      <c r="A739" s="1" t="n">
+        <v>737</v>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0004.png</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr"/>
+      <c r="D739" t="inlineStr"/>
+      <c r="E739" t="inlineStr"/>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>CC1=CCCCCC(=O)NCCNC(=O)CCCNC(=O)[CH]234(CCC(=O)O)NC567(=O)C(=CCC(=O)NCC(=O)NCCNC(=O)CCCC=CC(C)=C1S(N)(=O)=O)C18=O=C9%10(=O)C(NC(=O)CCCCCN)=CC%11C%12%13%14=O=C%11(=O=%12)(N%13)C%14C=C195N862[CH]3(CCC(=O)O)(N%107)C4(=O)NC(=O)NCCNC(=O)CCCOC1=CC(C)=C(S2(=O)(=O)NC(C(=O)O)N2)C(C)=C1</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr"/>
+      <c r="H739" t="inlineStr"/>
+      <c r="I739" t="n">
+        <v>0.0003807563396844947</v>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr"/>
+    </row>
+    <row r="740">
+      <c r="A740" s="1" t="n">
+        <v>738</v>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0005.png</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr"/>
+      <c r="D740" t="inlineStr"/>
+      <c r="E740" t="inlineStr"/>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>CC(C)c1cc2c(c(C(=O)NC/C=C/[C@H]3O[C@@H](n4cnc5c(N)ncnc54)[C@@H]4OC(C)(C)OC43)c1)OC(c1ccccc1)(c1ccccc1)O2</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr"/>
+      <c r="H740" t="inlineStr"/>
+      <c r="I740" t="n">
+        <v>0.6020299591264834</v>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="n">
+        <v>739</v>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0007.png</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr"/>
+      <c r="D741" t="inlineStr"/>
+      <c r="E741" t="inlineStr"/>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>COC(=O)[C@H](CNC(=O)c1ccc2c(cnn2CCCNC2=NCCCN2)c1)NS(=O)(=O)c1ccc(-c2ccc(S(=O)(=O)NCCNC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)CN3CCN(CC(=O)CC(C)(C)C)CCN(CC(=O)OC(C)(C)C)CCN(CC(=O)OC(C)(C)C)CC3)cc2)cc1</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr"/>
+      <c r="H741" t="inlineStr"/>
+      <c r="I741" t="n">
+        <v>0.780234126314532</v>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr"/>
+    </row>
+    <row r="742">
+      <c r="A742" s="1" t="n">
+        <v>740</v>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0010.png</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr"/>
+      <c r="D742" t="inlineStr"/>
+      <c r="E742" t="inlineStr"/>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>CCN1(CC)C2=CC(C(C)=CC=CC3=CC=C(N4C5=CC=CC=C5C5=C4C=CC=C5)C=C3)=CC=C2C(C)(=CC=CC2=CC=C(N3C4=CC=CC=C4C4=C3C=CC=C4)C=C2)C1C</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr"/>
+      <c r="H742" t="inlineStr"/>
+      <c r="I742" t="n">
+        <v>0.3313450299656993</v>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr"/>
+    </row>
+    <row r="743">
+      <c r="A743" s="1" t="n">
+        <v>741</v>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0012.png</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr"/>
+      <c r="D743" t="inlineStr"/>
+      <c r="E743" t="inlineStr"/>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>CCN(CC)c1cccc(N(c2cccc(N(CC)CC)c2)c2cc(N(c3cccc(N(CC)CC)c3)c3cccc(N(CC)CC)c3)cc(N(c3cccc(N(CC)CC)c3)c3cccc(N(CC)CC)c3)c2)c1</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr"/>
+      <c r="H743" t="inlineStr"/>
+      <c r="I743" t="n">
+        <v>0.7763734279931856</v>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr"/>
+    </row>
+    <row r="744">
+      <c r="A744" s="1" t="n">
+        <v>742</v>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0017.png</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr"/>
+      <c r="D744" t="inlineStr"/>
+      <c r="E744" t="inlineStr"/>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>CC1(C)O[C@@H]2[C@H](O1)[C@@H](/C=C/CNC(=O)c1cc(-c3ccc(F)cc3)cc3c1OC(c1ccccc1)(c1ccccc1)O3)O[C@H]2n1cnc2c(N)ncnc21</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr"/>
+      <c r="H744" t="inlineStr"/>
+      <c r="I744" t="n">
+        <v>0.4472940293868243</v>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr"/>
+    </row>
+    <row r="745">
+      <c r="A745" s="1" t="n">
+        <v>743</v>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0018.png</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr"/>
+      <c r="D745" t="inlineStr"/>
+      <c r="E745" t="inlineStr"/>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>CCN(CC)c1ccc(C(=Cc2ccc(N(c3ccc(C=C(c4ccccc4)c4ccc(N(CC)CC)cc4)cc3)c3ccc(/C=C(\c4ccccc4)c4ccc(N(CC)CC)cc4)cc3)cc2)c2ccccc2)cc1</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr"/>
+      <c r="H745" t="inlineStr"/>
+      <c r="I745" t="n">
+        <v>0.8016561308890439</v>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr"/>
+    </row>
+    <row r="746">
+      <c r="A746" s="1" t="n">
+        <v>744</v>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0027.png</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr"/>
+      <c r="D746" t="inlineStr"/>
+      <c r="E746" t="inlineStr"/>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>COc1ccc(C2(c3ccc(OC)cc3)Oc3cc(S(=O)(=O)c4ccc(C)cc4)cc(C(=O)NC/C=C/[C@H]4O[C@@H](n5cnc6c(N)ncnc65)[C@@H]5OC(C)(C)OC54)c3O2)cc1</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr"/>
+      <c r="H746" t="inlineStr"/>
+      <c r="I746" t="n">
+        <v>0.747584525638782</v>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr"/>
+    </row>
+    <row r="747">
+      <c r="A747" s="1" t="n">
+        <v>745</v>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0028.png</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr"/>
+      <c r="D747" t="inlineStr"/>
+      <c r="E747" t="inlineStr"/>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>CN(C)C(=O)/C=C/c1cc2c(c(C(=O)NC/C=C/[C@H]3O[C@@H](n4cnc5c(N)ncnc54)[C@@H]4OC(C)(C)OC43)c1)OC(c1ccccc1)(c1ccccc1)O2</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr"/>
+      <c r="H747" t="inlineStr"/>
+      <c r="I747" t="n">
+        <v>0.4107402777652157</v>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="1" t="n">
+        <v>746</v>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0029.png</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr"/>
+      <c r="D748" t="inlineStr"/>
+      <c r="E748" t="inlineStr"/>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>[H]C(=C)C=CCOCC(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C1(F)(F)FC1(F)C(F)(F)C1(F)(F)C(F)(F)C1(F)(F)C(F)(F)C(F)(F)C1(F)(F)FC1(F)C12(F)(F)FC1(F)C2134(F)FC12(F)(F)F3C24135(F)FC12(F)FC2314FC1523FC2(F)(F)F34</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr"/>
+      <c r="H748" t="inlineStr"/>
+      <c r="I748" t="n">
+        <v>1.338456729561256e-07</v>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr"/>
+    </row>
+    <row r="749">
+      <c r="A749" s="1" t="n">
+        <v>747</v>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0034.png</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr"/>
+      <c r="D749" t="inlineStr"/>
+      <c r="E749" t="inlineStr"/>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>COC(=O)[C@H](CNC(=O)c1ccc2c(CNc3nccn3C(c3ccccc3)(c3ccccc3)c3ccccc3)nn(C)c2c1)NS(=O)(=O)c1ccc(-c2ccc(S(=O)(=O)NCCNC(=O)CN3CCN(CC(=O)OC(C)(C)C)CCN(CC(=O)OC(C)(C)C)CCN(CC(=O)OC(C)(C)C)CC3)cc2)cc1</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr"/>
+      <c r="H749" t="inlineStr"/>
+      <c r="I749" t="n">
+        <v>0.4683825986467651</v>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr"/>
+    </row>
+    <row r="750">
+      <c r="A750" s="1" t="n">
+        <v>748</v>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0039.png</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr"/>
+      <c r="D750" t="inlineStr"/>
+      <c r="E750" t="inlineStr"/>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>[H]C(=C)C=CCOCC(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C1(F)(F)C(F)(F)C12(F)(F)FC2(F)C1(F)(F)C2(F)(F)C1345(F)(F)FC316(F)FC13789FC3(F)(F)(F7)C841(F)FC26195(F)F</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr"/>
+      <c r="H750" t="inlineStr"/>
+      <c r="I750" t="n">
+        <v>5.627333234204324e-07</v>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr"/>
+    </row>
+    <row r="751">
+      <c r="A751" s="1" t="n">
+        <v>749</v>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0040.png</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr"/>
+      <c r="D751" t="inlineStr"/>
+      <c r="E751" t="inlineStr"/>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>CC1=CC(OCCCC(=O)NCCNC(=O)CN2CCN(CC(=O)OC(C)(C)C)CCN3(CC(=O)OC(C)(C)C)CC3N(CC(=O)OC(C)(C)C)CC2)=CC(C)=C1S(=O)(=O)NC(CNC(=O)C1=CC2=CN(CCNC3=NCCCC3)N=C2C=C1)C(=O)O</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr"/>
+      <c r="H751" t="inlineStr"/>
+      <c r="I751" t="n">
+        <v>0.8161950891743478</v>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr"/>
+    </row>
+    <row r="752">
+      <c r="A752" s="1" t="n">
+        <v>750</v>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0043.png</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr"/>
+      <c r="D752" t="inlineStr"/>
+      <c r="E752" t="inlineStr"/>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>CNC1=CC=C(C(=O)NC([CH]C(=O)OC)[CH](CNC(=O)C2=CC3=C(C=C2)N(CCCNC2=NCCCN2)N=C3)(NS(=O)(=O)C2=C(C)C=C(OCCCC(=O)NCCNC(=O)C(CCC(=O)OC(C)(C)C)NC(=O)C(CCC(=O)OC(C)(C)C)NC(=O)CN(C)CCN(CCN(C)CC(=O)OC(C)(C)C)CC(=O)C(C)(C)C)C=C2C)C(=O)OC)C=C1</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr"/>
+      <c r="H752" t="inlineStr"/>
+      <c r="I752" t="n">
+        <v>0.2548355367704553</v>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="n">
+        <v>751</v>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0044.png</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr"/>
+      <c r="D753" t="inlineStr"/>
+      <c r="E753" t="inlineStr"/>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>CCN(CC)c1ccc(C(c2ccc(-n3c4ccccc4c4ccccc43)cc2)(c2ccc(-n3c4ccccc4c4ccccc43)cc2)c2ccc(-n3c4ccccc4c4ccccc43)cc2)cc1N(CC)CC</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr"/>
+      <c r="H753" t="inlineStr"/>
+      <c r="I753" t="n">
+        <v>0.7632183424371447</v>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="1" t="n">
+        <v>752</v>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0045.png</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr"/>
+      <c r="D754" t="inlineStr"/>
+      <c r="E754" t="inlineStr"/>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>CNC(=O)[CH](CCC(=O)OC(C)(C)C)(NC(=O)OCC1=CC=CC=C1)C(=O)(NCCNS(=O)(=O)C1=CC=C(C2=CC=C(S(=O)(=O)NC(CNC(=O)C3=CC4=C(C=C3)N(CCNC3=NCCCC3)N=C4)C(=O)OC)C=C2)C=C1)C(CCC(=O)OC(C)(C)C)NC(=O)OCC1=CC=CC=C1</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr"/>
+      <c r="H754" t="inlineStr"/>
+      <c r="I754" t="n">
+        <v>0.4471582169335309</v>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr"/>
+    </row>
+    <row r="755">
+      <c r="A755" s="1" t="n">
+        <v>753</v>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0051.png</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr"/>
+      <c r="D755" t="inlineStr"/>
+      <c r="E755" t="inlineStr"/>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>CCN(CC)c1ccc(CCc2ccc(N(c3ccc(CCc4ccc(N(CC)CC)cc4)cc3)c3ccc(CCc4ccc(N(CC)CC)cc4)cc3)cc2)cc1</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr"/>
+      <c r="H755" t="inlineStr"/>
+      <c r="I755" t="n">
+        <v>0.7458900281137122</v>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr"/>
+    </row>
+    <row r="756">
+      <c r="A756" s="1" t="n">
+        <v>754</v>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0055.png</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr"/>
+      <c r="D756" t="inlineStr"/>
+      <c r="E756" t="inlineStr"/>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>CNCCCNC1(=O)C23NC4(=O)C(CCC(=O)O)NC5(=O)C(CCC(=O)O)NC(=O)C(CCCCNC(=O)OC(C)(C)C)C(=O)(CCCCCNC(=O)OC(C)(C)C)NC6(=O)CC6C[CH]5(CCC(=O)O)C(=O)N[CH]4(CCC(=O)O)C(=O)NC1456CCC(=O)(COC(=O)CC=CNC(=O)CCCCCNC(=O)OC(C)(C)C)C17C2C2(CC34N5C6=O)C134=O=C27(=O=3)N4</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr"/>
+      <c r="H756" t="inlineStr"/>
+      <c r="I756" t="n">
+        <v>1.245656761894872e-06</v>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr"/>
+    </row>
+    <row r="757">
+      <c r="A757" s="1" t="n">
+        <v>755</v>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0059.png</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr"/>
+      <c r="D757" t="inlineStr"/>
+      <c r="E757" t="inlineStr"/>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>CC(C)(C)OC(=O)NCCCC(=O)NCCN.Cc1cc(OCCCC(=O)NCCNC(=O)C(=O)CCC(=O)NCCNC(=O)CCCOc2cc(C)c(S(=O)(=O)N[C@H](CNC(=O)c3ccc4c(cnn4CCCNc4ncc[nH]4)c3)C(=O)O)c(C)c2)cc(C)c1S(=O)(=O)N[C@@H](CNC(=O)c1ccc2c(cnn2CCCNc2ncc[nH]2)c1)C(=O)O</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr"/>
+      <c r="H757" t="inlineStr"/>
+      <c r="I757" t="n">
+        <v>0.6942820314109083</v>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr"/>
+    </row>
+    <row r="758">
+      <c r="A758" s="1" t="n">
+        <v>756</v>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0061.png</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr"/>
+      <c r="D758" t="inlineStr"/>
+      <c r="E758" t="inlineStr"/>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>COC(=O)C(CNC(=O)C1=CC2=C(C=C1)N(CCCNC1=NC=CN1C1(C3=CC=CC=C3)C3=CC=CC(=C3)=C3=CC=CC=C31)N=C2)NS(=O)(=O)C1=C(C)C=C(OCCCC(=O)NCCNC(=O)OCC2=CC=CC=C2)C=C1C</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr"/>
+      <c r="H758" t="inlineStr"/>
+      <c r="I758" t="n">
+        <v>0.2040754231779074</v>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="1" t="n">
+        <v>757</v>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0063.png</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr"/>
+      <c r="D759" t="inlineStr"/>
+      <c r="E759" t="inlineStr"/>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>CCN(CC)c1ccc(C=Cc2ccc(N(c3ccc(C=Cc4ccc(N(CC)CC)cc4)cc3)c3ccc(C=Cc4ccc(N(CC)CC)cc4)cc3)cc2)cc1</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr"/>
+      <c r="H759" t="inlineStr"/>
+      <c r="I759" t="n">
+        <v>0.7878815817573794</v>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K759" t="inlineStr"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="1" t="n">
+        <v>758</v>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0064.png</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr"/>
+      <c r="D760" t="inlineStr"/>
+      <c r="E760" t="inlineStr"/>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>COC(=O)C(CNC(=O)C1=CC2=C(C=C1)N(CCCNC1=NC=CC=C1)N=C2)NS(=O)(=O)C1=C(C)C=C(OCCCC(=O)NCCNC(=O)C(CCC(=O)OC(C)(C)C)NC(=O)C(CCC(=O)OC(C)(C)C)NC(=O)CN2CCN(CC(=O)OC(C)(C)C)CCN(CC(=O)OC(C)(C)C)C3CN34(CC(=O)OC(C)(C)C)CC24)C=C1C</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr"/>
+      <c r="H760" t="inlineStr"/>
+      <c r="I760" t="n">
+        <v>0.2734466876411635</v>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K760" t="inlineStr"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="1" t="n">
+        <v>759</v>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0066.png</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr"/>
+      <c r="D761" t="inlineStr"/>
+      <c r="E761" t="inlineStr"/>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>Cc1ccc(-c2c3c(c(-c4cccc(-c5ccccc5)c4)c4ccccc24)-c2ccc4cc5c6c(ccc5c5ccc-3c2c45)-c2c(c(-c3ccc4ccccc4c3)c3ccccc3c2-c2ccccc2-c2ccccc2)C=6)cc1</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr"/>
+      <c r="H761" t="inlineStr"/>
+      <c r="I761" t="n">
+        <v>0.8105327035358654</v>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr"/>
+    </row>
+    <row r="762">
+      <c r="A762" s="1" t="n">
+        <v>760</v>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0079.png</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr"/>
+      <c r="D762" t="inlineStr"/>
+      <c r="E762" t="inlineStr"/>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>COC(=O)[C@H](CNC(=O)c1ccc2c(cnn2CCNC2=NCCCC2)c1)NS(=O)(=O)c1c(C)cc(OCCCC(=O)NCCNC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)[C@H](CCC(=O)OC(C)C)NC(=O)CN2CCN(CC(=O)OC(C)(C)C)CCN(CC(=O)OC(C)(C)C)CCN(CC(=O)OC(C)(C)C)CC2)cc1C</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr"/>
+      <c r="H762" t="inlineStr"/>
+      <c r="I762" t="n">
+        <v>0.6433758687359159</v>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K762" t="inlineStr"/>
+    </row>
+    <row r="763">
+      <c r="A763" s="1" t="n">
+        <v>761</v>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0081.png</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr"/>
+      <c r="D763" t="inlineStr"/>
+      <c r="E763" t="inlineStr"/>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>[H][C@]1([C@@H](O)COP(=O)([O-])OC2CC(C)(C)C(/C=C/C=C/C=C/C(C)=C/C=C/C=C/C=C/C=C(C)/C=C/C3=C(C)C(=O)C(OP(=O)([O-])OC[C@H](O)[C@@]4([H])OC(=O)C(O)=C4O)CC3(C)C)=C(C)C2=O)OC(=O)C(O)=C1O</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr"/>
+      <c r="H763" t="inlineStr"/>
+      <c r="I763" t="n">
+        <v>0.7849186614137909</v>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K763" t="inlineStr"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="1" t="n">
+        <v>762</v>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0085.png</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr"/>
+      <c r="D764" t="inlineStr"/>
+      <c r="E764" t="inlineStr"/>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>CCc1cc(OCCCC(=O)NCCNC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)CN2CCN(CC(=O)OC(C)(C)C)CCN(CC(=O)OC(C)(C)C)CCN(CC(=O)OC(C)(C)C)CC2)cc(C)c1S(=O)(=O)N[C@@H](CNC(=O)c1ccc2c(CCCNC3=CCCCC3)nn(C)c2c1)C(=O)OC</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr"/>
+      <c r="H764" t="inlineStr"/>
+      <c r="I764" t="n">
+        <v>0.7580170314740595</v>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K764" t="inlineStr"/>
+    </row>
+    <row r="765">
+      <c r="A765" s="1" t="n">
+        <v>763</v>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0086.png</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr"/>
+      <c r="D765" t="inlineStr"/>
+      <c r="E765" t="inlineStr"/>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>CC(=O)NC[CH]NS(=O)(=O)c1c(C)cc(OCCCC(=O)NCCNC(=O)C(CCC(=O)NCCCC(=O)CCCOc2ccc(S(=O)(=O)N[C@@H](CCC(=O)c3ccc4c(cnn4CCCN/C=N/C=C/N)c3)C(=O)O)c(C)c2)NC(=O)[C@H](CCC(=O)OC(C)(C)C)NC(=O)[C@@H](CCC(=O)OC(C)(C)C)NC(=O)Oc2ccccc2)nc1C |^1:5|</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr"/>
+      <c r="H765" t="inlineStr"/>
+      <c r="I765" t="n">
+        <v>0.2104855494471531</v>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K765" t="inlineStr"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="1" t="n">
+        <v>764</v>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0088.png</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr"/>
+      <c r="D766" t="inlineStr"/>
+      <c r="E766" t="inlineStr"/>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>C=CN(CCCOCC)CCCC12=C3=C14C1=C5C(=CC=CC=CN(C67=CC=CC89=C6C=CC=CC=C8C=CC=C79)C=C3)C13(=C24)C12=CC5(C=CC=CCl)=C1C3(CCC1=CC=C(N(CCCOCC)CCOCCC)C=C1)=C2.CCCOCCCO</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr"/>
+      <c r="H766" t="inlineStr"/>
+      <c r="I766" t="n">
+        <v>2.215136946314792e-05</v>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K766" t="inlineStr"/>
+    </row>
+    <row r="767">
+      <c r="A767" s="1" t="n">
+        <v>765</v>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0089.png</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr"/>
+      <c r="D767" t="inlineStr"/>
+      <c r="E767" t="inlineStr"/>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Cc1ccc(-c2cc3c(c(C(=O)NC/C=C/[C@H]4O[C@@H](n5cnc6c(N)ncnc65)[C@@H]5OC(C)(C)O[C@@H]54)c2)OC(c2ccccc2)(c2ccccc2)O3)cc1</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr"/>
+      <c r="H767" t="inlineStr"/>
+      <c r="I767" t="n">
+        <v>0.4329134982301264</v>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K767" t="inlineStr"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="1" t="n">
+        <v>766</v>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0092.png</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr"/>
+      <c r="D768" t="inlineStr"/>
+      <c r="E768" t="inlineStr"/>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>CC1=CC=CC=C1.CCCC1=CC=C23C=C1=C1=CC2(=CC=C1CCCC1=CC=C(N(CC)CC)C=C1)N3C1=CC=C(CCCCC2=CC=C(N(CC)CC)C=C2)C=C1</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr"/>
+      <c r="H768" t="inlineStr"/>
+      <c r="I768" t="n">
+        <v>0.135889127799027</v>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K768" t="inlineStr"/>
+    </row>
+    <row r="769">
+      <c r="A769" s="1" t="n">
+        <v>767</v>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0093.png</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr"/>
+      <c r="D769" t="inlineStr"/>
+      <c r="E769" t="inlineStr"/>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>CC1=CC(OCCCC(=O)NCCNC(=O)C(CCC(=O)OC(C)(C)C)NC(=O)C(CCCOC(C)C)NC(=O)CN23CCN(CC(=O)OC(C)(C)C)CCN(CC(=O)OC(C)(C)C)CCN(CCOC45678CC(C4)(C5)(C6)(O7)O8)C2C3)=CC(C)=C1S(=O)(=O)NC(CNC(=O)C1=CC2=C(C=C1)N(CCCNC1=NC=CN1)N=C2)C(=O)O.O.O</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr"/>
+      <c r="H769" t="inlineStr"/>
+      <c r="I769" t="n">
+        <v>0.154990714087338</v>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K769" t="inlineStr"/>
+    </row>
+    <row r="770">
+      <c r="A770" s="1" t="n">
+        <v>768</v>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0095.png</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr"/>
+      <c r="D770" t="inlineStr"/>
+      <c r="E770" t="inlineStr"/>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>C/C=C1\NC(=O)[C@H](Cc2ccccc2)NC(=O)[C@@H](C(C)C)NC(=O)[C@@H]([C@H](C)CC)NC(=O)[C@H](NC(=O)[C@H](NC(=O)[C@@H](CCCN)NC(=O)[C@H]2CCCN2C(=O)[C@H](NC(=O)[C@@H](NC(=O)[C@@H](NC(=O)[C@H](NC(=O)CCCC(C)C)C(C)C)[C@H](C)O)C(C)C)C(C)C)[C@H](C)CC)COC(=O)[C@H](C(C)C)NC1=O.[2H][2H]</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr"/>
+      <c r="H770" t="inlineStr"/>
+      <c r="I770" t="n">
+        <v>0.6249745684951875</v>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K770" t="inlineStr"/>
+    </row>
+    <row r="771">
+      <c r="A771" s="1" t="n">
+        <v>769</v>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T061928/rb_0096.png</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr"/>
+      <c r="D771" t="inlineStr"/>
+      <c r="E771" t="inlineStr"/>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>CCOC(=O)CN1CCC(=O)OCCNC(=O)O[CH]2(CCC3(C)C(=CC=C4C3CCC3(C)C4CCC3C(C)CCCC(C)C)C2)OC(=O)NCCCCCC1=O</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr"/>
+      <c r="H771" t="inlineStr"/>
+      <c r="I771" t="n">
+        <v>0.7983616237423538</v>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K771" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K771"/>
+  <dimension ref="A1:K866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22810,6 +22810,2761 @@
       </c>
       <c r="K771" t="inlineStr"/>
     </row>
+    <row r="772">
+      <c r="A772" s="1" t="n">
+        <v>770</v>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0103.png</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr"/>
+      <c r="D772" t="inlineStr"/>
+      <c r="E772" t="inlineStr"/>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>CN1CC[C@H]2CC[C@@H](C(=O)N[C@@H](CCC(N)=O)C(=O)NC(CCCN3CCC(C#Cc4cccc5c4CN(C4CCC(=O)NC4=O)C5=O)CC3)c3ccccc3)N2C(=O)[C@@H](NC(=O)c2cc3cc(C(F)(F)P(=O)(O)O)ccc3s2)C1</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr"/>
+      <c r="H772" t="inlineStr"/>
+      <c r="I772" t="n">
+        <v>0.8333775914314193</v>
+      </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K772" t="inlineStr"/>
+    </row>
+    <row r="773">
+      <c r="A773" s="1" t="n">
+        <v>771</v>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0104.png</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr"/>
+      <c r="D773" t="inlineStr"/>
+      <c r="E773" t="inlineStr"/>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>NC(=O)c1c(-c2ccc(Oc3ccccc3)cc2)nn2c1Nc1cc(C(=O)N3CCC(CN4CCN(c5cc6c(cc5F)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)CC3)ccc1CC2</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr"/>
+      <c r="H773" t="inlineStr"/>
+      <c r="I773" t="n">
+        <v>0.842637364033899</v>
+      </c>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K773" t="inlineStr"/>
+    </row>
+    <row r="774">
+      <c r="A774" s="1" t="n">
+        <v>772</v>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0113.png</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr"/>
+      <c r="D774" t="inlineStr"/>
+      <c r="E774" t="inlineStr"/>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>CC=C1C23=C4=C1(=CCOCCOCCN(C)C[CH]1(CCC(NCC56=CC78=C9(C(C)(C)O)C%10=C5C=C=%10(C(C)(C)O)C9(=C6)N7C5(=O)C67=CC=CC(C(F)(F)F)=N69=C6(C(F)(F)F)=NC59(=CC=C6)C7(=O)N8)CC1)CN(C)CCOCCOC4=C(CNC(=O)[CH]14CC(O)C5N16C(=O)N54C6(=O)[CH]NC(=O)COCCOCCNCC)C=C2)C31=C(C)N=CS1</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr"/>
+      <c r="H774" t="inlineStr"/>
+      <c r="I774" t="n">
+        <v>4.320766166254583e-05</v>
+      </c>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K774" t="inlineStr"/>
+    </row>
+    <row r="775">
+      <c r="A775" s="1" t="n">
+        <v>773</v>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0115.png</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr"/>
+      <c r="D775" t="inlineStr"/>
+      <c r="E775" t="inlineStr"/>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>CCCC1NC1(=O)C(CCCN)NCC1=CC=CN=C1SC=CCNC(=O)C(CC1=CNC2=C1C=CC=C2)N1(C)C2(=O)[CH]3(CCCCN)NC(=O)[CH]4(CCCN)NCC56=CC=CN=C5SC5=C(CNC(=O)C(CC7=CNC8=C7C=CC=C8)N(C)C31(=O)[CH]2(CCCCN)NC4(=O)C(CCCN)NC6)C(C1=CC(=O)N(CC(=O)O)C=C1)=CC=C5Cl</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr"/>
+      <c r="H775" t="inlineStr"/>
+      <c r="I775" t="n">
+        <v>0.05337610514270492</v>
+      </c>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K775" t="inlineStr"/>
+    </row>
+    <row r="776">
+      <c r="A776" s="1" t="n">
+        <v>774</v>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0120.png</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr"/>
+      <c r="D776" t="inlineStr"/>
+      <c r="E776" t="inlineStr"/>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>*CCN(C(=O)NC(CCCN)C(=O)NC(C*)C(=O)NC(CSCC=CC(=O)NC1=C(OC2=CC=CC(O)=C2)C=C([H])C=C1)C(=O)O)N1C23=O=C12(NC(=O)CC(NC(=O)CC(=O)NC124=CC=CC15=C21C=CC12=C54C2(=O)CCC(=O)N1CCC([H])([H])C1)C(=O)O)=O=3.CNC(=O)CNC(=O)C1=CC=CC2=C1C=CC=C2NCCC=O |$CO2H;;;;;;;;;;;;;;;;;CO2H;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr"/>
+      <c r="H776" t="inlineStr"/>
+      <c r="I776" t="n">
+        <v>0.03858990791012543</v>
+      </c>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K776" t="inlineStr"/>
+    </row>
+    <row r="777">
+      <c r="A777" s="1" t="n">
+        <v>775</v>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0124.png</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr"/>
+      <c r="D777" t="inlineStr"/>
+      <c r="E777" t="inlineStr"/>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>COc1ccc(-c2ccc3c(c2)CCCOc2cc(ccc2Cc2nc4ccc(C(=O)O)cc4n2CC2CCO2)-c2cccc(n2)OC3)cn1</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr"/>
+      <c r="H777" t="inlineStr"/>
+      <c r="I777" t="n">
+        <v>0.5406033601862988</v>
+      </c>
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K777" t="inlineStr"/>
+    </row>
+    <row r="778">
+      <c r="A778" s="1" t="n">
+        <v>776</v>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0125.png</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr"/>
+      <c r="D778" t="inlineStr"/>
+      <c r="E778" t="inlineStr"/>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OC7CCN(C(=O)OC(C)(C)C)CC7)ccc6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr"/>
+      <c r="H778" t="inlineStr"/>
+      <c r="I778" t="n">
+        <v>0.7510675906763875</v>
+      </c>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K778" t="inlineStr"/>
+    </row>
+    <row r="779">
+      <c r="A779" s="1" t="n">
+        <v>777</v>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0128.png</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr"/>
+      <c r="D779" t="inlineStr"/>
+      <c r="E779" t="inlineStr"/>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>CO[C@H]1/C=C/O[C@@]2(C)Oc3c(C)c(O)c4c(=O)c(c5oc6cc(OCC7CCN(C)CC7)cc(O)c6nc-5c4c3C2=O)NC(=O)/C(C)=C\C=C\[C@H](C)[C@H](O)[C@@H](C)[C@@H](O)[C@@H](C)[C@H](OC(C)=O)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr"/>
+      <c r="H779" t="inlineStr"/>
+      <c r="I779" t="n">
+        <v>0.7771990074532436</v>
+      </c>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K779" t="inlineStr"/>
+    </row>
+    <row r="780">
+      <c r="A780" s="1" t="n">
+        <v>778</v>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0130.png</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr"/>
+      <c r="D780" t="inlineStr"/>
+      <c r="E780" t="inlineStr"/>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>CC(C)(O)C1=CC2=NN(C3CCC(CN45CC6(CC(CCNC7=C(N8CC(N9CCC(C%10=CC=C(NC%11=NC(N%12CCCCC%12)=CN=C%11C(N)=O)C=C%10)CC9)C8)C=CC8=C7C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)(C4)C5)CC3)C=C2C=C1NC(=O)C1=CC=CC(C(F)(F)F)=N1</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr"/>
+      <c r="H780" t="inlineStr"/>
+      <c r="I780" t="n">
+        <v>0.661833723903084</v>
+      </c>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K780" t="inlineStr"/>
+    </row>
+    <row r="781">
+      <c r="A781" s="1" t="n">
+        <v>779</v>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0132.png</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr"/>
+      <c r="D781" t="inlineStr"/>
+      <c r="E781" t="inlineStr"/>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>CCN(CC)CCOC1=CC2=C(C=C1)N=C13C(=C45NC(=O)C(C)=CC=CC(C)C(O)C(C)C(O)C(C)C(OC(C)=O)C(C)C(OC)C=COC67(C)OC89%10%11%12=C%13(C)C%14%15(O)=C%16%17%18(C4=O)C5(=O)C%1445=C%16(O)C%158(C)=C%1398(O6%10)C%1169%10=C14%17C86%12(=C35%189)C7%10=O)O2</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr"/>
+      <c r="H781" t="inlineStr"/>
+      <c r="I781" t="n">
+        <v>0.009600303191145146</v>
+      </c>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K781" t="inlineStr"/>
+    </row>
+    <row r="782">
+      <c r="A782" s="1" t="n">
+        <v>780</v>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0134.png</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr"/>
+      <c r="D782" t="inlineStr"/>
+      <c r="E782" t="inlineStr"/>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>[C-]OC(=O)C1=CC2=C(N=C(CC3=CC(F)=C45C=C3COCC3C6=C7C=C8C([N+]#[C-])=C6C36=C3(C=CC8([N+]#[C-])=C6)COC689=CC=C%10(F)C4(=N6)C4(F)=CC=C(N8=C4%105)O9C73)N2C(C2CCO2)[CH]23[C-]4C2CO43)C(OCCOC)=C1</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr"/>
+      <c r="H782" t="inlineStr"/>
+      <c r="I782" t="n">
+        <v>0.03638157741990497</v>
+      </c>
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K782" t="inlineStr"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="1" t="n">
+        <v>781</v>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0136.png</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr"/>
+      <c r="D783" t="inlineStr"/>
+      <c r="E783" t="inlineStr"/>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>*C[CH]NC(=O)C(CCCCN)NC(=O)C(C*)NC(=O)C(C)NC(=O)CC(C=O)NC(=O)C(O)NC1=CC=CC=C1C(=CC=N)NCC1(=O)N2C3CC321(C)F.CC12(F)CNC(=O)CNC3(=O)C45=C67=C89%10=C%11(C=CC=CC=8%12=C%119N%12CCC(=O)N8C9N(C%11C%12CC%119%13CC%12%13)C8(=O)CCNC=CC=C6)C347(=CC=N%10)C5(=O)NCC(=O)N(C1)C(O)C2 |$CO2H;;;;;;;;;;;;;;;;;HO2C;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr"/>
+      <c r="H783" t="inlineStr"/>
+      <c r="I783" t="n">
+        <v>1.321694514041938e-05</v>
+      </c>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K783" t="inlineStr"/>
+    </row>
+    <row r="784">
+      <c r="A784" s="1" t="n">
+        <v>782</v>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0137.png</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr"/>
+      <c r="D784" t="inlineStr"/>
+      <c r="E784" t="inlineStr"/>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>Cc1cccc(NC(=O)c2ccc(-c3nn4c(c3C(N)=O)Nc3ccc(N5CCN(CC6CCN(c7cc8c(cc7F)CN(C7CCC(=O)NC7=O)C8=O)CC6)CC5)cc3CC4)c(F)c2C)n1</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr"/>
+      <c r="H784" t="inlineStr"/>
+      <c r="I784" t="n">
+        <v>0.8289214604928052</v>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K784" t="inlineStr"/>
+    </row>
+    <row r="785">
+      <c r="A785" s="1" t="n">
+        <v>783</v>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0139.png</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr"/>
+      <c r="D785" t="inlineStr"/>
+      <c r="E785" t="inlineStr"/>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>CC1NC(C(=O)C(CCC(=O)NC=CN=CC=CC(=O)NCC(=O)N2CC(F)(F)CC2C#N)CC(=O)O)CCCC23NC(N2)C3CCC1[CH](=O)NC(CC(=O)O)C(=O)NC(C=O)CNC1CC(=O)N(CCCCCNC(=O)C2=CC3=C(C=C2)C24(OC3=O)C3=CC(N)=C5C(=C32)OC2=C4C=CC(N)=C2S(=O)(=O)OS5(=O)(=O)O)C1=O</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr"/>
+      <c r="H785" t="inlineStr"/>
+      <c r="I785" t="n">
+        <v>0.02188847705303438</v>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K785" t="inlineStr"/>
+    </row>
+    <row r="786">
+      <c r="A786" s="1" t="n">
+        <v>784</v>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0140.png</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr"/>
+      <c r="D786" t="inlineStr"/>
+      <c r="E786" t="inlineStr"/>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>COC1(c2ccc(/C=C/C(=O)OC(C)(C)C)c(OCc3ccc(NC(=O)[C@H](CC(C)C)NC(=O)[C@H](CCCCN)NC(=O)[C@H](Cc4ccc(Cl)cc4)NC(=O)[C@@H](NC(C)=O)C4Cc5ccccc5C4)cc3)c2Cl)OOC12C1CC3CC4(C1)CC2C34</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr"/>
+      <c r="H786" t="inlineStr"/>
+      <c r="I786" t="n">
+        <v>0.3406695227080012</v>
+      </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K786" t="inlineStr"/>
+    </row>
+    <row r="787">
+      <c r="A787" s="1" t="n">
+        <v>785</v>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0143.png</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr"/>
+      <c r="D787" t="inlineStr"/>
+      <c r="E787" t="inlineStr"/>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>CSC123SC4N5(C)C(=O)C(C)NC(=O)C(NC(=O)C6=NC7=CC=CC=C7N=C6)COC(=O)C(C(C)C)N(C)C(=O)C1N(C)C(=O)C(C)NC(=O)C16(NC(=O)C7=NC8=CC=CC=C8N=C7)COC(=O)C7(C(C)C)N8(C)C(=O)C5(S2)C48(=O)N7(C)C(C(C)C)C(=O)OC1C(NC(=O)C1=NC2=CC=CC=C2N=C1)C6(=O)NC(C)C(=O)N(C)C3C(=O)N(C)C</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr"/>
+      <c r="H787" t="inlineStr"/>
+      <c r="I787" t="n">
+        <v>0.02127053283218708</v>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K787" t="inlineStr"/>
+    </row>
+    <row r="788">
+      <c r="A788" s="1" t="n">
+        <v>786</v>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0147.png</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr"/>
+      <c r="D788" t="inlineStr"/>
+      <c r="E788" t="inlineStr"/>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>*Cc1nc(CBr)cc(C(=O)NCC(CNC(=O)c2cc(CS)nc(CBr)c2)C(=O)NC(=O)C(C(=O)NC(CCCNC(N)=O)C(=O)Nc2ccc(COC(=O)N(C)C(C(=O)NC(C(=O)NC(CCN3CCCC3C(CC)OC)(C(C)CC)C(CN3CCCC3C(OC)C(C)C(=O)NC(C)C(O)c3ccccc3)OC)C(C)C)C(C)C)cc2)C(C)C)n1 |$Ph;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr"/>
+      <c r="H788" t="inlineStr"/>
+      <c r="I788" t="n">
+        <v>0.1211969585502089</v>
+      </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K788" t="inlineStr"/>
+    </row>
+    <row r="789">
+      <c r="A789" s="1" t="n">
+        <v>787</v>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0148.png</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr"/>
+      <c r="D789" t="inlineStr"/>
+      <c r="E789" t="inlineStr"/>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>CCCC(CN1CCCC1C(N)=O)C(CC1=CNC2=C1C=C(F)C=C2)NC(=O)CNC(C)[CH]1(NC(=O)C(C)NC(=O)C(C)(NC2=CNC3=C2C=CC=C3)C(=O)N2[CH]345C(=O)[CH]26(C3C(N)=O=C(N)(=O)C46)N5C(=O)C(CC2=CC=CC=C2)NC(=O)CN2CCC(NC(=O)CN34CC(=O)CN(CCCC(N)=O)C3C4)CC2)CC(C)C1C</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr"/>
+      <c r="H789" t="inlineStr"/>
+      <c r="I789" t="n">
+        <v>0.09071834882651317</v>
+      </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K789" t="inlineStr"/>
+    </row>
+    <row r="790">
+      <c r="A790" s="1" t="n">
+        <v>788</v>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0153.png</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr"/>
+      <c r="D790" t="inlineStr"/>
+      <c r="E790" t="inlineStr"/>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>N#CC1CC(F)(F)CN1C(=O)CNC(=O)C1=CC=NC2=C(NC(=O)CCC(=O)NC(=O)NC(CCCCN)C(=O)NC3C4C567=O=C4(O)(=O=5)(O6)C37)C=CC=C12.O=C(O)CNCCN1(CC(=O)O)CCCN2(CCN(CC(=O)O)C3CN34CC3567=O=C(=O=3)(O5)(O6)C147)C1CCC(=O)NC3C4N567C(C8C(CC2C1(=O)O)C(=O)N38)N4512C3CC61(=O)=O=C72CCN124C5NC1C2[SH]3C54</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr"/>
+      <c r="H790" t="inlineStr"/>
+      <c r="I790" t="n">
+        <v>6.711886161924105e-05</v>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K790" t="inlineStr"/>
+    </row>
+    <row r="791">
+      <c r="A791" s="1" t="n">
+        <v>789</v>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0154.png</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr"/>
+      <c r="D791" t="inlineStr"/>
+      <c r="E791" t="inlineStr"/>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>NC(=O)CN1CCN2(CC(N)=O)C3C2N32(CC(N)=O)C34C5(CC6=CC=C7(NC(=S)NCCCC(NC(=O)CCOCCOCCOCCNC(=O)COC8=CC=C(C(=O)NCC(=O)N9C(=O)CCCC9Cl)C=C8)C(=O)NC8CC8CC(CCCCNC(=O)C8=CC=C9CC9=C8)C(=O)O)C8=CC7C=86)C32N5423CC(=O)NC2C13</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr"/>
+      <c r="H791" t="inlineStr"/>
+      <c r="I791" t="n">
+        <v>0.002708304098526183</v>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K791" t="inlineStr"/>
+    </row>
+    <row r="792">
+      <c r="A792" s="1" t="n">
+        <v>790</v>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0155.png</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr"/>
+      <c r="D792" t="inlineStr"/>
+      <c r="E792" t="inlineStr"/>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)c4cccc(C(=O)N[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)N[C@@H](C)c5ccc(-c6scnc6C)cc5)C(C)(C)C)c4)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr"/>
+      <c r="H792" t="inlineStr"/>
+      <c r="I792" t="n">
+        <v>0.8084408205408588</v>
+      </c>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K792" t="inlineStr"/>
+    </row>
+    <row r="793">
+      <c r="A793" s="1" t="n">
+        <v>791</v>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0156.png</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr"/>
+      <c r="D793" t="inlineStr"/>
+      <c r="E793" t="inlineStr"/>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>[H]C(F)(C1=CC=C(NC2=CC(CN(C)CC[CH]CC[CH]C(=O)N[CH]3(CCC(N)=O)C4(=O)N[CH]5(COCCCCCCCCCC#CC6=CC=CC7=C6CN(C6CCC(=O)NC6=O)C7=O)C436=C3=C547=CC=C58=C3=C(C5=C4)C8=C67)NC2=O)C=N1)P(=O)(O)O</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr"/>
+      <c r="H793" t="inlineStr"/>
+      <c r="I793" t="n">
+        <v>0.0326459538077921</v>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K793" t="inlineStr"/>
+    </row>
+    <row r="794">
+      <c r="A794" s="1" t="n">
+        <v>792</v>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0158.png</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr"/>
+      <c r="D794" t="inlineStr"/>
+      <c r="E794" t="inlineStr"/>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)CCC(=O)NC(CCCNC(=N)N)C(=O)NC(CCCNC(=N)N)C(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr"/>
+      <c r="H794" t="inlineStr"/>
+      <c r="I794" t="n">
+        <v>0.8330526882096466</v>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K794" t="inlineStr"/>
+    </row>
+    <row r="795">
+      <c r="A795" s="1" t="n">
+        <v>793</v>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0160.png</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr"/>
+      <c r="D795" t="inlineStr"/>
+      <c r="E795" t="inlineStr"/>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccc(N2C(=O)C(C)(C)N(c3ccc(-c4ccc(OCCCCOCC(=O)N[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)NCc5ccc(-c6scnc6C)cc5)C(C)(C)C)cc4)nc3)C2=S)c(F)c1C(F)(F)F</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr"/>
+      <c r="H795" t="inlineStr"/>
+      <c r="I795" t="n">
+        <v>0.6689416222143241</v>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K795" t="inlineStr"/>
+    </row>
+    <row r="796">
+      <c r="A796" s="1" t="n">
+        <v>794</v>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0161.png</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr"/>
+      <c r="D796" t="inlineStr"/>
+      <c r="E796" t="inlineStr"/>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>COC1(c2ccc(/C=C/C#N)c(OCc3ccc(NC(=O)[C@H](CC(C)C)NC(=O)[C@H](CCCCN)NC(=O)[C@H](Cc4ccc(Cl)cc4)NC(=O)[C@@H](NC(C)=O)C4Cc5ccccc5C4)cc3)c2Cl)OOC12C1CC3CC(C1)CC2C3</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr"/>
+      <c r="H796" t="inlineStr"/>
+      <c r="I796" t="n">
+        <v>0.5805204427955061</v>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K796" t="inlineStr"/>
+    </row>
+    <row r="797">
+      <c r="A797" s="1" t="n">
+        <v>795</v>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0162.png</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr"/>
+      <c r="D797" t="inlineStr"/>
+      <c r="E797" t="inlineStr"/>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>CCC(C)C1(N(C)C(=O)C(NC(=O)C(C(C)C)N(C)C(=O)OCC=CCNC(=O)C(CCCNC(N)=O)(CCCNC(N)=O)NC(=O)NC(=O)CCOCCOCCOCCOCCNC(=O)OC2CC=CC=CC2)C(C)C)C(OC)C(OC2O3(C)C456C7OC234(C7(C)C(=O)NC(C)C(O)C2=CC=CC=C2)N52(C(=O)OC)CCC62)C1(C)C</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr"/>
+      <c r="H797" t="inlineStr"/>
+      <c r="I797" t="n">
+        <v>0.02972276338768782</v>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K797" t="inlineStr"/>
+    </row>
+    <row r="798">
+      <c r="A798" s="1" t="n">
+        <v>796</v>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0163.png</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr"/>
+      <c r="D798" t="inlineStr"/>
+      <c r="E798" t="inlineStr"/>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>C=CN=CCNC.CCN1C(=O)C(C(C)C)NC(=O)[CH]2(C(C)C)(N(C)C)C(C)(C)C(N(C)C)C2(=O)NC(C(C)C)C(=O)C(O)CC2=O=C2(=O)N23CCC[CH]24[CH]2(OC)C(C)C(=O)N5C(CN=[N+]=[N-])C67C8=C9C=C%10NC%11=CC9=C6(C[CH]57(CN=[N+]=[N-])NC(=O)[CH]2(C)[CH]4(OC)[CH]32CCCN2C(O)C1=O)C1=C%11=C%10=C=18</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr"/>
+      <c r="H798" t="inlineStr"/>
+      <c r="I798" t="n">
+        <v>3.108380059250906e-05</v>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K798" t="inlineStr"/>
+    </row>
+    <row r="799">
+      <c r="A799" s="1" t="n">
+        <v>797</v>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0164.png</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr"/>
+      <c r="D799" t="inlineStr"/>
+      <c r="E799" t="inlineStr"/>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>[H]C(F)(C1=CC2=C(C=C1)NC(C(=O)N[CH]CN(C)CC[CH]CC[CH]C(=O)N[CH]1(CCC(N)=O)C3(=O)N[CH]4(COCCCCCCCCCC#CC5=CC=CC6=C5CN(C5CCC(=O)NC5=O)C6=O)C56=CC=C7C(=C)C8=CC=5=C314C6=C78)=C2F)P(=O)(O)OC</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr"/>
+      <c r="H799" t="inlineStr"/>
+      <c r="I799" t="n">
+        <v>0.06506338584730657</v>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K799" t="inlineStr"/>
+    </row>
+    <row r="800">
+      <c r="A800" s="1" t="n">
+        <v>798</v>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0171.png</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr"/>
+      <c r="D800" t="inlineStr"/>
+      <c r="E800" t="inlineStr"/>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>CN1CC[C@H]2CC[C@@H](C(=O)N[C@@H](CCC(N)=O)C(=O)NCCCCCCCCCC#Cc3cccc4c3CN(C3CCC(=O)NC3=O)C4=O)N2C(=O)[C@@H](NC(=O)c2cc3cc(C(F)(F)P(=O)(O)O)ncc3[nH]2)C1</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr"/>
+      <c r="H800" t="inlineStr"/>
+      <c r="I800" t="n">
+        <v>0.8081106414967414</v>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K800" t="inlineStr"/>
+    </row>
+    <row r="801">
+      <c r="A801" s="1" t="n">
+        <v>799</v>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0178.png</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr"/>
+      <c r="D801" t="inlineStr"/>
+      <c r="E801" t="inlineStr"/>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>C=CC(=CCNC(=O)C1CC(O)CN1C(=O)[CH]NC(=O)COCCOCCNCCNC(=O)C=CC=CNCC(=O)N(C)C=CC=CC)OCCOCCN(C)C[CH]123CC[CH]456C(C1)C217C4C3C15C1234=C589C%10(C(C)(C)O)=C1%11%12C51%13=N5%14N76%15C=C126(C12=C%10NC7(=O)C%10%16%17=N%18%19=C7%20%21%22%23=NC7%24=C%25=C%18%26%27%28=C%18=C%19%29(=C%19C%30=C1%10%20=C%19%18=C=%302%16%211=C%25=C1%22)(C%2612FC%29%27%10%16%18%19FC7(F)(F)(F)(F%10)(F%16)(F1%18)F2%19)N=%17=%23%24%28)C5%1183N=%13%15=C%14%12964</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr"/>
+      <c r="H801" t="inlineStr"/>
+      <c r="I801" t="n">
+        <v>1.48991209049083e-06</v>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K801" t="inlineStr"/>
+    </row>
+    <row r="802">
+      <c r="A802" s="1" t="n">
+        <v>800</v>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0179.png</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr"/>
+      <c r="D802" t="inlineStr"/>
+      <c r="E802" t="inlineStr"/>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>N#CC1CC(F)(F)CN1C(=O)CNC(=O)C1=CC=NC2=C(NC(=O)CCC(=O)NC(CC(=O)O)C(=O)NC(CCCCN)C(=O)NC(CC(=O)O)C(=O)NC(CSC3CC(=O)N(CCNC(=O)CCC4(C(=O)OC56N(CCC7C[PH]8(=O)(=O)C79C7N5C798)C65OC5=O)NCCCCNC5(OC5=O)OC4=O)C3=O)C(=O)O)C=CC=C12</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr"/>
+      <c r="H802" t="inlineStr"/>
+      <c r="I802" t="n">
+        <v>0.0004702380890784763</v>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K802" t="inlineStr"/>
+    </row>
+    <row r="803">
+      <c r="A803" s="1" t="n">
+        <v>801</v>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0180.png</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr"/>
+      <c r="D803" t="inlineStr"/>
+      <c r="E803" t="inlineStr"/>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2[C@@H](O)CCN2C(=O)[C@@H]2CCCCN2C(=O)c2ccc(/C=C/CCCCNC(=O)[C@@H](NC(=O)[C@H](CCC(N)=O)NC(=O)[C@@H]3CC[C@@H]4CCN(C)C[C@H](NC(=O)c5cc6cc(C(F)(F)P(=O)(O)O)ccc6[nH]5)C(=O)N43)c3ccccc3)cc2)cc1</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr"/>
+      <c r="H803" t="inlineStr"/>
+      <c r="I803" t="n">
+        <v>0.3503878463947419</v>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K803" t="inlineStr"/>
+    </row>
+    <row r="804">
+      <c r="A804" s="1" t="n">
+        <v>802</v>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0182.png</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr"/>
+      <c r="D804" t="inlineStr"/>
+      <c r="E804" t="inlineStr"/>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>Cc1cccc(NC(=O)c2ccc(-c3nn4c(c3C(N)=O)Nc3ccc(N5CCN(CC6CCN(c7cc8c(cc7F)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)cc3CC4)c(F)c2C)n1</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr"/>
+      <c r="H804" t="inlineStr"/>
+      <c r="I804" t="n">
+        <v>0.8332585022075375</v>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K804" t="inlineStr"/>
+    </row>
+    <row r="805">
+      <c r="A805" s="1" t="n">
+        <v>803</v>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0188.png</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr"/>
+      <c r="D805" t="inlineStr"/>
+      <c r="E805" t="inlineStr"/>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>CSC1=C(F)C=C2N=C34C(=C(CNC(=O)COCNC(=O)C(C)NC(=O)C(C)NC(=O)C(C)NC(=O)C(CCC(=O)NCC(O)C(O)C(O)C(O)CO)NC(=O)CCCCCN5C(=O)C=CC5=O)C2=C1)CN1C325=C36=C14278=C3512CC3(O)(CC17)C(=O)OCC=C6328</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr"/>
+      <c r="H805" t="inlineStr"/>
+      <c r="I805" t="n">
+        <v>0.1181277383162576</v>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K805" t="inlineStr"/>
+    </row>
+    <row r="806">
+      <c r="A806" s="1" t="n">
+        <v>804</v>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0193.png</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr"/>
+      <c r="D806" t="inlineStr"/>
+      <c r="E806" t="inlineStr"/>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>CCCCCC(=O)N[C@H]1CSCc2cc(cc(CN3CCN(C(=O)C4NC4CN4CCN(CCO)CC(=O)C4)CC3)c2)CSC[C@@H](C(=O)N[C@@H](CC(=O)O)C(N)=O)NC(=O)[C@H](Cc2ccccc2)NC(=O)[C@H](CCC(N)=O)NC(=O)[C@H]([C@@H](C)O)NC(=O)[C@@H]2CCCN2C(=O)[C@@H]2CCCN2C1=O.O=C1CNCCN(CC(=O)[O][Lu][OH])CO1</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr"/>
+      <c r="H806" t="inlineStr"/>
+      <c r="I806" t="n">
+        <v>0.1987824034163255</v>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K806" t="inlineStr"/>
+    </row>
+    <row r="807">
+      <c r="A807" s="1" t="n">
+        <v>805</v>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0194.png</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr"/>
+      <c r="D807" t="inlineStr"/>
+      <c r="E807" t="inlineStr"/>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>COC1(c2ccc(/C=C/C(=O)O)c(OCc3ccc(NC(=O)[C@H](CC(C)C)NC(=O)[C@H](CCCCN)NC(=O)[C@H](Cc4ccc(Cl)cc4)NC(=O)[C@@H](NC(C)=O)C4Cc5ccccc5C4)cc3)c2Cl)OOC12C1CC3CC(C1)CC2C3</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr"/>
+      <c r="H807" t="inlineStr"/>
+      <c r="I807" t="n">
+        <v>0.5376181078900542</v>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K807" t="inlineStr"/>
+    </row>
+    <row r="808">
+      <c r="A808" s="1" t="n">
+        <v>806</v>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0195.png</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr"/>
+      <c r="D808" t="inlineStr"/>
+      <c r="E808" t="inlineStr"/>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>CC(C)(O)c1cc2nc(C3CCC(CN4CC5(CC(CCNc6c(N7CC(N8CCC(c9ccc(Nc%10nc(N%11CCCCC%11)cnc%10C(N)=O)cc9)CC8)C7)ccc7c6C(=O)N(C6CCC(=O)NC6=O)C7=O)C5)C4)CC3)sc2cc1NC(=O)c1cccc(C(F)(F)F)n1</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr"/>
+      <c r="H808" t="inlineStr"/>
+      <c r="I808" t="n">
+        <v>0.8384177722224319</v>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K808" t="inlineStr"/>
+    </row>
+    <row r="809">
+      <c r="A809" s="1" t="n">
+        <v>807</v>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0198.png</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr"/>
+      <c r="D809" t="inlineStr"/>
+      <c r="E809" t="inlineStr"/>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>CC(NC=O)C(=O)NC(CCCNC(=N)N)C(=O)N1CCC1C1(=O)N[CH]2(C)C3(=O)N4C2(=O)(N2[CH]456CCC4NC7(=N)(N)NC89%10(=N)=N=C%11(N8)N9C8CC[CH]29%12C5(=O)[CH]92NC6%12(=O)C2CCN48%117%10)[CH]3(C)NC(=O)[CH]12CCN2C(=O)C(CCCNC(=N)N)NC(=O)C(C)NC(=O)C(CCCCN)NC1=CC=C([N+](=O)[O-])C2=NON=C12</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr"/>
+      <c r="H809" t="inlineStr"/>
+      <c r="I809" t="n">
+        <v>0.0001015575068036459</v>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K809" t="inlineStr"/>
+    </row>
+    <row r="810">
+      <c r="A810" s="1" t="n">
+        <v>808</v>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0202.png</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr"/>
+      <c r="D810" t="inlineStr"/>
+      <c r="E810" t="inlineStr"/>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>CC1=C2C=CC(=C1F)C1=NN3CCC=C(C=CC4(C)=CC=CC(=N4)NC2=O)NC3=C1C(N)=O.O=C1CCC(N23C(=O)C=C4(C=CC5=C6=N789%10%11CN56%12C5N(CC57N56C8C9(C5%10)C6%11)C%125=CC=C(C=C5)C42=O)C3=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr"/>
+      <c r="H810" t="inlineStr"/>
+      <c r="I810" t="n">
+        <v>0.01803078589840543</v>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K810" t="inlineStr"/>
+    </row>
+    <row r="811">
+      <c r="A811" s="1" t="n">
+        <v>809</v>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0204.png</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr"/>
+      <c r="D811" t="inlineStr"/>
+      <c r="E811" t="inlineStr"/>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(C(C)NC(=O)C3CC(N=N)CN3C(=O)C(NC(=O)CCOCCOCCOCCNC3=CC45=CC67(=C4)=NC4(=C5C=C3)=N6=C35C689%10=CC=CC=C6%11%12%13%14%15%16%17=C6=C%18(CN%19C=N%20C%21(=NC%22=C(C(C)C)C=NN%22%23C%22=N%21C%19%20%23%21N%19C%11%20%23N%22%21C%19%12%11C%208%13%12%19%21=C=%148%13=C%23%119%15%14%20=C=%12=%169C8%11=C8=C%139=C%119C%11=C3%10%19%14=C89=C=%11%185%21%20%17)OC3CNCC7C3)C4=CC=C6)C(C)(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr"/>
+      <c r="H811" t="inlineStr"/>
+      <c r="I811" t="n">
+        <v>0.0001280078379809475</v>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K811" t="inlineStr"/>
+    </row>
+    <row r="812">
+      <c r="A812" s="1" t="n">
+        <v>810</v>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0210.png</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr"/>
+      <c r="D812" t="inlineStr"/>
+      <c r="E812" t="inlineStr"/>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C([CH]CC(=O)N3CCC(C#CC45=CC=C6(CCNC7(=O)[CH]8(C=CC=CC(N)=O)NC9(=O)[CH]%10(CCC(N)=O)C(=O)(N[CH]7%11C=CC=C7%12(C(=O)N7C8%11=O)C7=CC%12=C7)[CH]9%10(CCC(N)=O)NC(=O)C7C(C)C8CCN(C)CC(NC(=O)C9=CC%10=C(C=CC(C(F)(F)C(N)=O)=C%10)N9)C(=O)N87)C7=C4=C6=C=75)CC3)C=C2)NC=N1</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr"/>
+      <c r="H812" t="inlineStr"/>
+      <c r="I812" t="n">
+        <v>0.0004651031306135211</v>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K812" t="inlineStr"/>
+    </row>
+    <row r="813">
+      <c r="A813" s="1" t="n">
+        <v>811</v>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0212.png</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr"/>
+      <c r="D813" t="inlineStr"/>
+      <c r="E813" t="inlineStr"/>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>[H]C(=O)NCCN(CCNCCCCC(=O)N1CCNC(=O)[CH]CCCC(N)N2(C=C(CNC(=O)CCC(=O)NC3=CC=CC4=C3N=CC=C4C(=O)NCC(=O)C3CC(F)(F)CC3O)N=N2)CCCCC(C(=O)CCC(=O)NC2=CC=CC3=C2N=CC=C3C(=O)NCC(=O)N2CC([H])(F)CC2O)C(=O)NCCNC1(=O)CCCCNCC(=O)O)CC(=O)O</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr"/>
+      <c r="H813" t="inlineStr"/>
+      <c r="I813" t="n">
+        <v>0.06890869612865451</v>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K813" t="inlineStr"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="1" t="n">
+        <v>812</v>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0214.png</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr"/>
+      <c r="D814" t="inlineStr"/>
+      <c r="E814" t="inlineStr"/>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr"/>
+      <c r="H814" t="inlineStr"/>
+      <c r="I814" t="n">
+        <v>0.05643655190943659</v>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K814" t="inlineStr"/>
+    </row>
+    <row r="815">
+      <c r="A815" s="1" t="n">
+        <v>813</v>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0215.png</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr"/>
+      <c r="D815" t="inlineStr"/>
+      <c r="E815" t="inlineStr"/>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>CCCCCCCC(=O)OCOP(=O)(OCOC(=O)CCCCCCC)OC[CH]123O[CH]4567[CH]8(F)C1OP19(=O)OC[CH]%10%11%12CO1P(=O)(OCOC(=O)CCCCCCC)(OC[CH]%101OC%11[CH]1(N1C=NC%10=C1N=CN=C%10N)CO%12)O9[CH]21C(F)O34[CH]852(C1F)N61C=NC3=C1N=CN=C3(N)C13=C(N=CN=C1N)N72C=N3</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr"/>
+      <c r="H815" t="inlineStr"/>
+      <c r="I815" t="n">
+        <v>0.002806480121505803</v>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K815" t="inlineStr"/>
+    </row>
+    <row r="816">
+      <c r="A816" s="1" t="n">
+        <v>814</v>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0217.png</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr"/>
+      <c r="D816" t="inlineStr"/>
+      <c r="E816" t="inlineStr"/>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>CCC(C)C1(=O)N(C)(C(=O)NC(=O)C(C(C)C)N(C)C(=O)OCC23=CC=C(NC(=O)C4NC(=O)C5(C(C)C)(C(C)C)NCCNC6(N)(=O)=O=C(N)N6CCC45CCCOCCOCCOCCOCCOC4=CC=C(C5=NN=C(C)N=N5)C=C4)C=2=C3)C12(C)(C(COC(C(C)C(=O)NC(C)C(O)C1=CC=CC=C1)C1CCCN1C(=O)OC)OC)C(=O)N2(C)C(C)C</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr"/>
+      <c r="H816" t="inlineStr"/>
+      <c r="I816" t="n">
+        <v>0.00723488188939999</v>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K816" t="inlineStr"/>
+    </row>
+    <row r="817">
+      <c r="A817" s="1" t="n">
+        <v>815</v>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0220.png</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr"/>
+      <c r="D817" t="inlineStr"/>
+      <c r="E817" t="inlineStr"/>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>*N1C(C(=O)N[CH]CN(C)CC[CH]CC[CH]C(=O)N[CH]2(CCC(N)=O)C3(=O)N[CH]4(COCCCCCCCCCC#CC5=CC=CC6=C5CN(C5CCC(=O)NC5=O)C6=O)C56=CC7=C8=C9=C=7C=C5C324(=C=69)C=C8)=CC2=C1C=NC(C([H])(F)P(=O)(O)O)=C2 |$Bn;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr"/>
+      <c r="H817" t="inlineStr"/>
+      <c r="I817" t="n">
+        <v>0.02904609943208719</v>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K817" t="inlineStr"/>
+    </row>
+    <row r="818">
+      <c r="A818" s="1" t="n">
+        <v>816</v>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0222.png</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr"/>
+      <c r="D818" t="inlineStr"/>
+      <c r="E818" t="inlineStr"/>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>N#CC1CC(F)(F)CN1C(=O)CNC(=O)C1=CC=CC2=CC=C(OCCCN3CCN(C(=O)CCC(=O)NC(CC(=O)O)C(=O)NC(CCCCN)C(=O)NC(CC(=O)O)C(=O)NC(CSC4CC(=O)N(C5=CC6=C(C=C5)C5(C=C7OC8(=C5C=CC(O)=C8)O7)OC6=O)C4=O)C(=O)O)CC3)C=C21.NCCCC[CH]NC(=O)[CH]CC=O</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr"/>
+      <c r="H818" t="inlineStr"/>
+      <c r="I818" t="n">
+        <v>0.4440273010368334</v>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K818" t="inlineStr"/>
+    </row>
+    <row r="819">
+      <c r="A819" s="1" t="n">
+        <v>817</v>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0223.png</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr"/>
+      <c r="D819" t="inlineStr"/>
+      <c r="E819" t="inlineStr"/>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>[H]C(F)C1CCN23C=C(C(=O)NC4CN(C)CC[CH]CCC(C(=O)N[CH]5(CCC(N)=O)C(=O)N[CH]6(COCCCCCCCCCC#CC7=CC=CC8=C7CN(C7CCC(=O)NC7=O)C8=O)C789=C%10=C56%11%12=C=7C5=C6C(=C8%11)C=5(=C%10)C6=C9%12)C4=O)C24=NC3=C=41</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr"/>
+      <c r="H819" t="inlineStr"/>
+      <c r="I819" t="n">
+        <v>0.0595164092970339</v>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K819" t="inlineStr"/>
+    </row>
+    <row r="820">
+      <c r="A820" s="1" t="n">
+        <v>818</v>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0224.png</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr"/>
+      <c r="D820" t="inlineStr"/>
+      <c r="E820" t="inlineStr"/>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2(F)CC2)C(C)(C)C)c(NCCN2CCC(N3CCC(CNc4ccc5c(-c6ccccc6CNc6nc(N[C@@H]7CCCNC7)nc7c(C(C)C)cnn67)nccc5c4)CC3)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr"/>
+      <c r="H820" t="inlineStr"/>
+      <c r="I820" t="n">
+        <v>0.8331168077578922</v>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K820" t="inlineStr"/>
+    </row>
+    <row r="821">
+      <c r="A821" s="1" t="n">
+        <v>819</v>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0225.png</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr"/>
+      <c r="D821" t="inlineStr"/>
+      <c r="E821" t="inlineStr"/>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>CC1=NOC(C(C(=O)N2CC(O)CC2C(=O)NCC2=CC=C(C3=C(C)N=CS3)C=C2OCCOCCOCCNC23=CC45=CC6=NC7(=C4C=C2)=C5(=C2N=CC64CNCC(C4)OC45=NC6=C(C(C)C)C=NN6C(=N4)(NCC4=CC=CC=C42)N5=CNCC2=CC=CC=C27)C=C3)C(C)C)=C1</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr"/>
+      <c r="H821" t="inlineStr"/>
+      <c r="I821" t="n">
+        <v>0.195282811972987</v>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K821" t="inlineStr"/>
+    </row>
+    <row r="822">
+      <c r="A822" s="1" t="n">
+        <v>820</v>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0226.png</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr"/>
+      <c r="D822" t="inlineStr"/>
+      <c r="E822" t="inlineStr"/>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>CCCC(=CC1=CN2[CH]CC[CH]CNC(CCCCNC3=CC=CC=C3C(=O)NCCCC=O)N34(CCC5(CCNCCCCNCCCC6=CC=C(NC7=NC(N8CCCCC8)=CN=C7C(N)=O)C=C6)CC3C5C4)CC3CC[CH]2(CC3)N2C=C3C=C(NC(=O)C4=NC(C(F)(F)F)=CC=C4)C(C(C)(C)O)=CC13=N2)NC(=O)C1=NC(C(F)(F)F)=CC=C1</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr"/>
+      <c r="H822" t="inlineStr"/>
+      <c r="I822" t="n">
+        <v>0.0850443763574466</v>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K822" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="A823" s="1" t="n">
+        <v>821</v>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0230.png</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr"/>
+      <c r="D823" t="inlineStr"/>
+      <c r="E823" t="inlineStr"/>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>NC(=O)c1ncc(N2CCCCC2)nc1Nc1ccc(C2CCN(CC(CNc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)C3CC4(C3)CN(CC3CCC(n5cc(NC(=O)c6cnn7ccc(N8CCOCC8)nc67)c(C(F)F)n5)CC3)C4)CC2)cc1</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr"/>
+      <c r="H823" t="inlineStr"/>
+      <c r="I823" t="n">
+        <v>0.642468848496626</v>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" s="1" t="n">
+        <v>822</v>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0231.png</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr"/>
+      <c r="D824" t="inlineStr"/>
+      <c r="E824" t="inlineStr"/>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>CC=C(F)C=CN=C123C45=CCN(C(=O)COCNC(=O)CNC(=O)C(CC6=CC=CC=C6)NC(=O)CNC(=O)CNC(=O)CCCCCN6C(=O)C=CC6=O)C=C4N46C51=C1C57=CC48(=O)C49%10%11=C%12%13%14%15%16C%17%18%19=C4%20%21C4%22%23N%20%24%25C4%179(=O)C8%21%1249=C8%12%17C%13%20%21%26%27=C%222%24%13C58%14%202%22%24=C=%2116%233%25%13C%2621CC%12%15235(O)C1(C%22)C7%17%1621(O)(CC%27%24)C3(=O)OC%18%104O(C%19%119)C51=O</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr"/>
+      <c r="H824" t="inlineStr"/>
+      <c r="I824" t="n">
+        <v>6.695456399573421e-07</v>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K824" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" s="1" t="n">
+        <v>823</v>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0233.png</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr"/>
+      <c r="D825" t="inlineStr"/>
+      <c r="E825" t="inlineStr"/>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>CC1=NOC(C(C(=O)N2CC(O)CC2C(=O)NCC2=CC=C(C3=C(C)N=CS3)C=C2OCCOCCOCCNC2=CC34=CC56=NC7(=C3C=C2)=N=52=C3C5=CC=CC8=C59%10%11C5%12N%13C9(N5C59%14=N%15=C%13%16=N=5C%15(=NC5=C(C(C)C)C=NN5%169)(OC5CNCC6(C5)C2=C4)N%14=CNCC2=CC=CC=C27)C=8%12%102=CC=CC=C3%112)C(C)C)=C1</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr"/>
+      <c r="H825" t="inlineStr"/>
+      <c r="I825" t="n">
+        <v>0.003000604103452299</v>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K825" t="inlineStr"/>
+    </row>
+    <row r="826">
+      <c r="A826" s="1" t="n">
+        <v>824</v>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0236.png</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr"/>
+      <c r="D826" t="inlineStr"/>
+      <c r="E826" t="inlineStr"/>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NC(=O)C3(F)CC3)C(C)(C)C)C(OCCOCCOCCNC34=CC5=C6789C%10(C3)CC3%11=C%10%12C%10=N3%13C63%14=N%10%11C%137(=C538C%129=C4)C%143=CC=CC=C3CNC3=NC(OC4CC5CO6C5OC46)=NC4=C(C(C)C)C=NN34)=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr"/>
+      <c r="H826" t="inlineStr"/>
+      <c r="I826" t="n">
+        <v>0.03627468271176342</v>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K826" t="inlineStr"/>
+    </row>
+    <row r="827">
+      <c r="A827" s="1" t="n">
+        <v>825</v>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0237.png</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr"/>
+      <c r="D827" t="inlineStr"/>
+      <c r="E827" t="inlineStr"/>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>CN1CC[C@H]2CC[C@@H](C(=O)N[C@@H](CCC(N)=O)C(=O)N[C@H](CC(=O)N3CCC(C#Cc4cccc5c4CN(C4CCC(=O)NC4=O)C5=O)CC3)Cc3ccccc3)N2C(=O)[C@@H](NC(=O)c2cc3cc(C(F)(F)P(=O)(O)O)ccc3s2)C1</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr"/>
+      <c r="H827" t="inlineStr"/>
+      <c r="I827" t="n">
+        <v>0.4610584255482637</v>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K827" t="inlineStr"/>
+    </row>
+    <row r="828">
+      <c r="A828" s="1" t="n">
+        <v>826</v>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0244.png</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr"/>
+      <c r="D828" t="inlineStr"/>
+      <c r="E828" t="inlineStr"/>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(C(C)NC(=O)C3CC(O)CN3C(=O)[CH]NC(=O)CCCCCCCNC(=O)[CH](CCC(N)=O)(NC(=O)C(CCC(N)=O)N3C(=O)[CH]34CCC3CCN(C)CC(NC(=O)C5=CC6=C(C=CC(C(F)(F)C(=O)O)=C6)N5)C(=O)C34)C3=CC=CC=C3)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr"/>
+      <c r="H828" t="inlineStr"/>
+      <c r="I828" t="n">
+        <v>0.06786082072067851</v>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K828" t="inlineStr"/>
+    </row>
+    <row r="829">
+      <c r="A829" s="1" t="n">
+        <v>827</v>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0248.png</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr"/>
+      <c r="D829" t="inlineStr"/>
+      <c r="E829" t="inlineStr"/>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN34C(=O)C(NC(=O)C3(F)CC3)C4(C)(C)C)C(OCCCCNC(=O)CCC(=O)N3CCC(C4=CC(NC5=CC(C#N)=CC=N5)=NC(N5CCC(F)(F)C5)=C4)CC3)=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr"/>
+      <c r="H829" t="inlineStr"/>
+      <c r="I829" t="n">
+        <v>0.4634788685135305</v>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K829" t="inlineStr"/>
+    </row>
+    <row r="830">
+      <c r="A830" s="1" t="n">
+        <v>828</v>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0249.png</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr"/>
+      <c r="D830" t="inlineStr"/>
+      <c r="E830" t="inlineStr"/>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>Cc1c(NC(=O)c2ccc(C(C)(C)C)cc2)cccc1-c1cn(C)c(=O)c(Nc2ccc(C(=O)N3CCN(CCCCCCNC(=O)CN(CCCCNC[C@@H]4CC[C@@H](n5cc6cc(NC(=O)c7cccc(C(F)(F)F)n7)c(C(C)(C)O)cc6n5)CC4)c4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)cc2)n1</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr"/>
+      <c r="H830" t="inlineStr"/>
+      <c r="I830" t="n">
+        <v>0.3140749054018298</v>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr"/>
+    </row>
+    <row r="831">
+      <c r="A831" s="1" t="n">
+        <v>829</v>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0251.png</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr"/>
+      <c r="D831" t="inlineStr"/>
+      <c r="E831" t="inlineStr"/>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>COCCOC1=CC(C(=O)OC)=CC23=C1N=C14(CC56789=CC=C%10%11C%12%13=NC(=CC=C%12)OCC%12=C(C=C(C(F)(F)F)N=C%12)CCOC%12C5%14%15=C%105C%13%10=CC=6=C%147(C18C=N)C%1259=C%11%10%15)N2C12C5C6CO5[CH]615(CCO5)CN234</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr"/>
+      <c r="H831" t="inlineStr"/>
+      <c r="I831" t="n">
+        <v>0.02417258156485566</v>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr"/>
+    </row>
+    <row r="832">
+      <c r="A832" s="1" t="n">
+        <v>830</v>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0253.png</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr"/>
+      <c r="D832" t="inlineStr"/>
+      <c r="E832" t="inlineStr"/>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CN(C)C(=O)C(NC3=CC=C(C(=O)N45(C(C)(=O)NCCNCCCCCCNC(=O)CNCC6=CC(=O)N(CCCC=O)C6=O)CCN(CCCCCCNCCCCNCC6CCC(N7C=C8C=C(NC(=O)C9=NC(C(F)(F)F)=CC=C9)C(O(C)(C)O)=CC8=N7)CC6)(CC4)CC5)C=C3)=N2)C=CC=C1NC(=O)C1=CC=C(C(C)(C)C)C=C1</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr"/>
+      <c r="H832" t="inlineStr"/>
+      <c r="I832" t="n">
+        <v>0.09321639910382741</v>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr"/>
+    </row>
+    <row r="833">
+      <c r="A833" s="1" t="n">
+        <v>831</v>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0257.png</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr"/>
+      <c r="D833" t="inlineStr"/>
+      <c r="E833" t="inlineStr"/>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>*C(CCCCNC(=O)CC1=CC=C(C)CC1)C(=O)[CH]1234CCCCNC(=O)NC567=CC=C(C=C5)CCN58CC(=O)NC5C(CCN(CC)CC(N)=O)(CC(N)=O)C5C8N(CCC8=CC=C6(NC(=O)NCCCC1C(C2(=O)OC)N31C(=O)(CC2CC21=O)N4)C7=C8)C1CN1(C(N)=O)CCN5CC(N)=O.CC(C)N1CCCN1C(=O)CNC(=O)C=CC=NC=CCO |$CO2R;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr"/>
+      <c r="H833" t="inlineStr"/>
+      <c r="I833" t="n">
+        <v>8.251917091968792e-05</v>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K833" t="inlineStr"/>
+    </row>
+    <row r="834">
+      <c r="A834" s="1" t="n">
+        <v>832</v>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0258.png</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr"/>
+      <c r="D834" t="inlineStr"/>
+      <c r="E834" t="inlineStr"/>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>C=CC1=CCCN23N=C4(C5=C(F)C(C)=C(C(=O)NCC=CC=CC)C=C5)C5(C(N)=O)=C26(=C4(C(N)=O)=C53N6C2=CC=C(N3CCN(C4CN(C5CN(C6=CC7=C(C=C6)C(=O)N(C6CCC(=O)N(S(C)=O)C6=O)C7=O)C5)C4)CC3)C=C2)N1</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr"/>
+      <c r="H834" t="inlineStr"/>
+      <c r="I834" t="n">
+        <v>0.02480420998354858</v>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K834" t="inlineStr"/>
+    </row>
+    <row r="835">
+      <c r="A835" s="1" t="n">
+        <v>833</v>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0261.png</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr"/>
+      <c r="D835" t="inlineStr"/>
+      <c r="E835" t="inlineStr"/>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>CC1(I)CC(C#N)C(C(=O)CNC(=O)C234=CC5=N6C789=C2%10%11=C67(=C38%102C=CC=C%112)N9C=C54)C1.CCCC(NC(=O)CCCC1=CC=C(F)C=C1)C(=O)NC[CH]NC(=O)C(CC(=O)O)NC1(=O)C(CC(=O)O)N1[CH]1234CCCCNC(N)CCC[CH]56789C%10%11%12(=O)[CH]5%13%14%15%16C5C(=O)OC(=O)(O)C[CH]%10%136%17%18%19C1(=O)[CH]2(N3)C47%171(=O)[CH]%11%148%1823C(C(=O)O)[CH]5%121%1592%19C%163C(=O)O</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr"/>
+      <c r="H835" t="inlineStr"/>
+      <c r="I835" t="n">
+        <v>6.09538910490743e-09</v>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K835" t="inlineStr"/>
+    </row>
+    <row r="836">
+      <c r="A836" s="1" t="n">
+        <v>834</v>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0265.png</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr"/>
+      <c r="D836" t="inlineStr"/>
+      <c r="E836" t="inlineStr"/>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>CN1CC[C@H]2CC[C@@H](C(=O)N[C@@H](CCC(N)=O)CN[C@H](C(=O)NCCCCCCCCCC#Cc3cccc4c3CN(C3CCC(=O)NC3=O)C4=O)c3ccccc3)N2C(=O)[C@@H](NC(=O)[C@H](Cc2cccc(C(F)(F)P(=O)(O)O)c2)N(C)C)C1</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr"/>
+      <c r="H836" t="inlineStr"/>
+      <c r="I836" t="n">
+        <v>0.8057029954498592</v>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr"/>
+    </row>
+    <row r="837">
+      <c r="A837" s="1" t="n">
+        <v>835</v>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0266.png</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr"/>
+      <c r="D837" t="inlineStr"/>
+      <c r="E837" t="inlineStr"/>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>CC(C)(O)C1=CC2=C(C=C1NC(=O)C1=CC=CC(C(F)(F)F)=N1)SC(C1CCC(CN3CC45(CC(C(CNC6=CC=CC7=C6C(=O)N(C6CCC(=O)NC6=O)C7=O)CN6CCC(C7=CC=C(NC8=NC(N9CCCCC9)=CN=C8C(N)=O)C=C7)CC6)C4C5)C3)CC1)=N2</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr"/>
+      <c r="H837" t="inlineStr"/>
+      <c r="I837" t="n">
+        <v>0.4386243198579738</v>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K837" t="inlineStr"/>
+    </row>
+    <row r="838">
+      <c r="A838" s="1" t="n">
+        <v>836</v>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0267.png</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr"/>
+      <c r="D838" t="inlineStr"/>
+      <c r="E838" t="inlineStr"/>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>C[CH]C(C=COC1(C)OC2=C(C1=O)C1=C(C(=O)C(NC(=O)C(C)=CC=CC(C)C(O)C(C)C(O)C(C)[CH]OC(C)=O)=CC1=O)C(O)=C2C)OC.NC1=C(O)C=C(Br)C(Cl)=C1.NC1=C(O)C=C(Br)C(Cl)=C1.O=[N+]([O-])C12=C(O)C=C(Br)C3(Cl)=C1C1(=C(O)C=C3(Br)C(Cl)=C1)[N+]2(=O)[O-]</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr"/>
+      <c r="H838" t="inlineStr"/>
+      <c r="I838" t="n">
+        <v>0.1439262785836069</v>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr"/>
+    </row>
+    <row r="839">
+      <c r="A839" s="1" t="n">
+        <v>837</v>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0273.png</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr"/>
+      <c r="D839" t="inlineStr"/>
+      <c r="E839" t="inlineStr"/>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>CNCCCCCCCNC1(=O)[CH]23C[CH]14(C)(NC15(=O)=O=C([CH]1(CCC(N)=O)NC(=O)[CH]CC[CH]CCN(C)C[CH]NC(=O)CNC1=CC=C(C(C(C)=O)C(C)C)C=C1)N254)C3(=O)NCCCCCCCNC1234=O=C56(=O=1)C2[CH]1(C2=CC=C(C7=C(C)N=CS7)C=C2)N53C(=O)(C2CC(O)CN2C(=O)C(NC(=O)C2(F)CC2)C(C)(C)C)N164</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr"/>
+      <c r="H839" t="inlineStr"/>
+      <c r="I839" t="n">
+        <v>0.004255709196618176</v>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr"/>
+    </row>
+    <row r="840">
+      <c r="A840" s="1" t="n">
+        <v>838</v>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0275.png</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr"/>
+      <c r="D840" t="inlineStr"/>
+      <c r="E840" t="inlineStr"/>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>NC(=O)C1=NC=C(N2CCCCC2)N=C1NC1=CC=C(C2CCN(C3CN(C4=C(NCCC5CC67(C5)CN(CC5CCC(N8C=C(NC(=O)C9=C%10N=C(N%11CCOCC%11)C=CN%10N=C9)C(C(F)F)=N8)CC5)(C6)C7)C5=C(C=C4)C(=O)N(C4CCC(=O)NC4=O)C5=O)C3)CC2)C=C1</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr"/>
+      <c r="H840" t="inlineStr"/>
+      <c r="I840" t="n">
+        <v>0.7615028646665155</v>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K840" t="inlineStr"/>
+    </row>
+    <row r="841">
+      <c r="A841" s="1" t="n">
+        <v>839</v>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0276.png</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr"/>
+      <c r="D841" t="inlineStr"/>
+      <c r="E841" t="inlineStr"/>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>N#CC1CC(F)(F)CN1C(=O)CNC(=O)C1=CC=NC2=C(NC(=O)CCC(=O)NC(CC(=O)O)C(=O)N[CH](CCCCN)(C(=O)NC(CC(=O)O)C(=O)NC(CNC3CC(=O)N(C4=CC5=C(C=C4)C46(OC5=O)O5C47OC54=C76C=CC(O)=C4)C3=O)C(=O)O)N([CH]CCCCN)C(=O)C(CC(=O)O)NC(=O)CCC(N)=O)C=CC=C12</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr"/>
+      <c r="H841" t="inlineStr"/>
+      <c r="I841" t="n">
+        <v>0.1762843499876355</v>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K841" t="inlineStr"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="1" t="n">
+        <v>840</v>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0280.png</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr"/>
+      <c r="D842" t="inlineStr"/>
+      <c r="E842" t="inlineStr"/>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>COc1ccccc1N1CCOCCOCCN(c2cc3c(cc2OC)C2(OC3=O)c3ccc(OC(C)=O)cc3C(c3ccccc3)(c3ccccc3)c3cc(OC(C)=O)ccc32)CCOCC1</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr"/>
+      <c r="H842" t="inlineStr"/>
+      <c r="I842" t="n">
+        <v>0.5773646358040566</v>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K842" t="inlineStr"/>
+    </row>
+    <row r="843">
+      <c r="A843" s="1" t="n">
+        <v>841</v>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0286.png</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr"/>
+      <c r="D843" t="inlineStr"/>
+      <c r="E843" t="inlineStr"/>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>N#C[C@@H]1CC(F)(F)CN1C(=O)CNC(=O)c1ccnc2c(NC(=O)CCC(=O)NCc3cn(CCCC[C@H](NC(=O)C[C@H](NC(=O)[C@H](CCC(=O)O)NC(=O)CCCc4ccc(I)cc4)C(=O)O)C(=O)N[C@H](CC(=O)O)C(=O)N[C@@H](CCCCN)C(=O)N[C@@H](CC(=O)O)C(=O)N[C@@H](CN)C(=O)O)nn3)cccc12</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr"/>
+      <c r="H843" t="inlineStr"/>
+      <c r="I843" t="n">
+        <v>0.7999160547248103</v>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="1" t="n">
+        <v>842</v>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0288.png</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr"/>
+      <c r="D844" t="inlineStr"/>
+      <c r="E844" t="inlineStr"/>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>CC1(C(=O)OCOP2(=O)OC[CH]3(CO2)OC(N2C=NC4=C2N=CN=C4N)C(F)C3OP2(=O)OCOC3(=O)C4(C)CCCCC4C34(C)(CCCCC4)C(=O)OCOP(=O)(OCOC(=O)C3(C)CCCCC3)OC3C(CO2)OCC3N2C=NC3=C2N=CN=C3N)CCCCC1</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr"/>
+      <c r="H844" t="inlineStr"/>
+      <c r="I844" t="n">
+        <v>0.2011840769052143</v>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K844" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="1" t="n">
+        <v>843</v>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0294.png</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr"/>
+      <c r="D845" t="inlineStr"/>
+      <c r="E845" t="inlineStr"/>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)C4C=C(C(=O)N[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)N[C@@H](C)c5ccc(-c6scnc6C)cc5)C(C)(C)C)C4)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr"/>
+      <c r="H845" t="inlineStr"/>
+      <c r="I845" t="n">
+        <v>0.4412454393192689</v>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K845" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="1" t="n">
+        <v>844</v>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0295.png</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr"/>
+      <c r="D846" t="inlineStr"/>
+      <c r="E846" t="inlineStr"/>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>CNC(CC(=O)O)C(=O)N[CH]CCCCN.N#CC1CC(F)(F)CN1C(=O)CNC(=O)C123=C45N=CC=C1C=CC=C4NC(=O)CCC(=O)NCC(=NNCCCCC(NC(=O)CC(NC(=O)CCC(=O)NC1=CC=CC4=C1N=CC=C4C(=O)NCC(=O)N1CC(F)(F)C1N)C(=O)O)C(=O)O)CNC(=O)CCC(=O)NC1=CC=CC54=C12N=CC=C43</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr"/>
+      <c r="H846" t="inlineStr"/>
+      <c r="I846" t="n">
+        <v>0.03863334092844055</v>
+      </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K846" t="inlineStr"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="1" t="n">
+        <v>845</v>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0299.png</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr"/>
+      <c r="D847" t="inlineStr"/>
+      <c r="E847" t="inlineStr"/>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>CC=C(F)C=CN=C1C(=CCNC(=O)COCNC(=O)CNC(=O)C(CC2=CC=CC=C2)NC(=O)CNC(=O)CNC(=O)CCCCCN2C(=O)C=CC2=O)CN2C(=O)C3=C4567C8=C129%10=C12C9C=%10149%11CCC514%10(O)C29=C625C6O9C2%12O6C12(=O=C94=O)O%12(C(=O)C27%10(O)CC8%11)C35</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr"/>
+      <c r="H847" t="inlineStr"/>
+      <c r="I847" t="n">
+        <v>0.0003279549609718775</v>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K847" t="inlineStr"/>
+    </row>
+    <row r="848">
+      <c r="A848" s="1" t="n">
+        <v>846</v>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0301.png</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr"/>
+      <c r="D848" t="inlineStr"/>
+      <c r="E848" t="inlineStr"/>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)c2cncc(C(=O)N3CCC(C4C=C(N5CCC(F)(F)C5)N=CC4)CC3)n2)C(C)(C)C)cc1.[C-]#[N+]/C=C/C=N\CN/C=C/CCCCNC(=O)/C=C/N=C\CC(=O)N[CH]C(=O)N1C[C@H](O)C[C@H]1C(=O)N[C@@H](C)/C=C/C=C(\C)c1scnc1C |^1:85|</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr"/>
+      <c r="H848" t="inlineStr"/>
+      <c r="I848" t="n">
+        <v>0.2958968486759245</v>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K848" t="inlineStr"/>
+    </row>
+    <row r="849">
+      <c r="A849" s="1" t="n">
+        <v>847</v>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0304.png</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr"/>
+      <c r="D849" t="inlineStr"/>
+      <c r="E849" t="inlineStr"/>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>CCOC1CC(C(=O)NC(C)C2=CC=C(C3=C(C)N=CS3)C=C2)N(C(=O)C(NC(=O)CCOCCOCCNC2=CC34=C5C6789=C3C53%10%11=N6C(=C4C=C2)C2=CC=CC=C24CNC=NC2=N5C6%12=C(C(C)C)C=NN6C6=N(=CN%13CC%14%15%16%17=C%18=C%14%19%20(=CC=CC=C%15%19%14C(=N73)(=N=%108)C4%14%16%20=CC=C%18)C%13%17N6)C53(=N%12)O[CH]4(CNCC9%11C4)C4NCCCC4O23)C(C)(C)C)C1</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr"/>
+      <c r="H849" t="inlineStr"/>
+      <c r="I849" t="n">
+        <v>2.18328209592547e-05</v>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K849" t="inlineStr"/>
+    </row>
+    <row r="850">
+      <c r="A850" s="1" t="n">
+        <v>848</v>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0305.png</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr"/>
+      <c r="D850" t="inlineStr"/>
+      <c r="E850" t="inlineStr"/>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>*[CH]12(NC(=O)CCCCCCCC(=O)N3CCC4CCC(C(=O)NC(CCC(N)=O)C(=O)NC(C5=CC=CC=C5)C5=CC=CC=C5)N4C(=O)C(NC(=O)C4=CC5=C(C=CC(C(F)(F)P(=O)(O)O)=C5)N4)C3)C34[CH]5(O)C[CH]6789%10C(=O)NC(C)C%11=CC=C(C=CC)CC=CC=C[CH]%11(C)NC6(=O)[CH]76%11C8C(CN3697C13=O=C27(=O)N43%11%10)O5 |$BuBu;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr"/>
+      <c r="H850" t="inlineStr"/>
+      <c r="I850" t="n">
+        <v>0.003126473966410291</v>
+      </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K850" t="inlineStr"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="1" t="n">
+        <v>849</v>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0306.png</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr"/>
+      <c r="D851" t="inlineStr"/>
+      <c r="E851" t="inlineStr"/>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>CC(C)c1cnn2c(NCc3ccccc3-c3nccc4cc(NCC5CCN(C6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)ccc34)nc(O[C@@H]3CCCNC3)nc12</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr"/>
+      <c r="H851" t="inlineStr"/>
+      <c r="I851" t="n">
+        <v>0.8126853888948732</v>
+      </c>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K851" t="inlineStr"/>
+    </row>
+    <row r="852">
+      <c r="A852" s="1" t="n">
+        <v>850</v>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0307.png</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr"/>
+      <c r="D852" t="inlineStr"/>
+      <c r="E852" t="inlineStr"/>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)[C@H]4C[C@@H]4C(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr"/>
+      <c r="H852" t="inlineStr"/>
+      <c r="I852" t="n">
+        <v>0.4994110179342131</v>
+      </c>
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K852" t="inlineStr"/>
+    </row>
+    <row r="853">
+      <c r="A853" s="1" t="n">
+        <v>851</v>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0308.png</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr"/>
+      <c r="D853" t="inlineStr"/>
+      <c r="E853" t="inlineStr"/>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>CC1=NOC(C(C(=O)N2CC(O)CC2C(=O)NCC2=CC=C(C3=C(C)N=CS3)C=C2OCCOCCOCCNC23=CC45=CC6=NC7(=C4C=C2)=C5(=C2C45=CC=CC8=C49%10%11C4%12N%13C9(N4C49%14=N%15=C%13%16=N=4C%15(=NC4=C(C(C)C)C=NN4%169)(OC4CNCC6C4)N%14=CNCC4=CC=CC=C47)C=8%12%104=CC=CC=C25%114)C=C3)C(C)C)=C1</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr"/>
+      <c r="H853" t="inlineStr"/>
+      <c r="I853" t="n">
+        <v>0.007311658628816336</v>
+      </c>
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K853" t="inlineStr"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="1" t="n">
+        <v>852</v>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0309.png</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr"/>
+      <c r="D854" t="inlineStr"/>
+      <c r="E854" t="inlineStr"/>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@@H](C)NC(=O)[C@H]2C[C@H](O)CN2C(=O)[C@H](NC(=O)C2CC(C(=O)NC34CC(n5cc(-c6cnc(N)c(OC(F)(F)F)c6)nc5C(O)C(C)C)(C3)C4)C2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr"/>
+      <c r="H854" t="inlineStr"/>
+      <c r="I854" t="n">
+        <v>0.693253464382275</v>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K854" t="inlineStr"/>
+    </row>
+    <row r="855">
+      <c r="A855" s="1" t="n">
+        <v>853</v>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0310.png</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr"/>
+      <c r="D855" t="inlineStr"/>
+      <c r="E855" t="inlineStr"/>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>C#CCCCOCC1NC(=O)C(CCC(N)=O)NC(=O)[CH]23CC[CH]4(CCN(C)CC(NC(=O)C5=CNC6=C5C=C(C(F)(F)OC(=O)O)C=C6)C(=O)N42)N32(C=O)C(CCNC)CCC2C(=O)NC(CCC(N)=O)C(=O)N[CH](COCCCC#CC2=CC=CC3=C2CN(C2CCC(=O)NC2=O)C3=O)(C2=CC=CC=C2)C12=CC=CC=C2</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr"/>
+      <c r="H855" t="inlineStr"/>
+      <c r="I855" t="n">
+        <v>0.1225453071938461</v>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K855" t="inlineStr"/>
+    </row>
+    <row r="856">
+      <c r="A856" s="1" t="n">
+        <v>854</v>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0313.png</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr"/>
+      <c r="D856" t="inlineStr"/>
+      <c r="E856" t="inlineStr"/>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>CC1=C(F)C=C2N=C3(C4=C(CN(C(=O)COCNC(=O)CNC(=O)C(CC5=CC=CC=C5)NC(=O)CNC(=O)CNC(=O)CCCCCN5C(=O)C=CC5=O)CC4)C2=C1)C124=C5678=C319%10=C2513%11%12CCC25%13%14%15%16%17(O)C%18%19%20C691C%1821(C%195269%18C73%135=C37%13=C8%11%14%19=C(C3OC2%15=O)(C7OC6%16(=O)C%2015%199%17(O)O%18)C%13(=O)N4%10)C%12</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr"/>
+      <c r="H856" t="inlineStr"/>
+      <c r="I856" t="n">
+        <v>4.747402335318509e-06</v>
+      </c>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K856" t="inlineStr"/>
+    </row>
+    <row r="857">
+      <c r="A857" s="1" t="n">
+        <v>855</v>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0314.png</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr"/>
+      <c r="D857" t="inlineStr"/>
+      <c r="E857" t="inlineStr"/>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>CN1CC[C@H]2CC[C@@H](C(=O)N[C@@H](CCC(N)=O)C(=O)N[C@@H](COCCCCCCCCCC#Cc3cccc4c3CN(C3CCC(=O)NC3=O)C4=O)c3ccccc3)N2C(=O)[C@@H](NC(=O)c2cn3cc(C(F)(F)N(C)C)ccc3n2)C1</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr"/>
+      <c r="H857" t="inlineStr"/>
+      <c r="I857" t="n">
+        <v>0.7119545421622195</v>
+      </c>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K857" t="inlineStr"/>
+    </row>
+    <row r="858">
+      <c r="A858" s="1" t="n">
+        <v>856</v>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0319.png</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr"/>
+      <c r="D858" t="inlineStr"/>
+      <c r="E858" t="inlineStr"/>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccnc(Nc2cc(C3CCN(C(=O)CC[C@H](NC(=O)C(N)CCCNC(=N)N)C(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc(N3CCC(F)(F)C3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr"/>
+      <c r="H858" t="inlineStr"/>
+      <c r="I858" t="n">
+        <v>0.8032838842509437</v>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K858" t="inlineStr"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="1" t="n">
+        <v>857</v>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0320.png</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr"/>
+      <c r="D859" t="inlineStr"/>
+      <c r="E859" t="inlineStr"/>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>CCCCCC(=O)NC1CSCC2=CC345=C6C(=C=3C6(=C2)C4N23(CCN(CC2)C(=O)C2C4CN3CC(=O)OC3CN3C3CN36CC(=O)C(C6)N42)C5)CSCC(C(=O)NC(CC(=O)O)C(N)=O)NC(=O)C(CC2=CC=CC=C2)NC(=O)C(CCC(N)=O)NC(=O)C(C(C)O)NC(=O)C2CCCN2C(=O)C2CCCN2C1=O</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr"/>
+      <c r="H859" t="inlineStr"/>
+      <c r="I859" t="n">
+        <v>0.06374556879327387</v>
+      </c>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K859" t="inlineStr"/>
+    </row>
+    <row r="860">
+      <c r="A860" s="1" t="n">
+        <v>858</v>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0325.png</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr"/>
+      <c r="D860" t="inlineStr"/>
+      <c r="E860" t="inlineStr"/>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Cc1cccc(NC(=O)c2ccc(-c3nn4c(c3C(N)=O)Nc3ccc(N5CCN(CC6CCN(c7ccc8c(c7)CN(C7CCC(=O)NC7=O)C8=O)CC6)CC5)cc3CC4)c(F)c2C)n1</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr"/>
+      <c r="H860" t="inlineStr"/>
+      <c r="I860" t="n">
+        <v>0.6804088584714424</v>
+      </c>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K860" t="inlineStr"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="1" t="n">
+        <v>859</v>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0327.png</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr"/>
+      <c r="D861" t="inlineStr"/>
+      <c r="E861" t="inlineStr"/>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>*C[CH]N[CH]1(CCCN)O[CH]12C(CCCN)N2C([CH]CCCN1NCCC(=O)CCC(=O)NC23456=CC=CC789=C2%10N=CC=CCNC2%11%12%13=OC%14(=O=2)(N%11C2%11%15%16%17=O%18=C%19%20%21(=O)N%22C%23%24%25%26=O=C%22%27%28%29%30=O=%23=C%242%27%22%23=C72C7=CC=3%24%27%31C843%32C=7=%245(N%27C(=O)C4C5=O=C4C54C57=NN45C17CC1CN1CC1=O=C(CCCCC=CC=C4CC4)N1)C=9=3%102%3161C23=C4=C256(=C4%19%11%282C=5%20%15%224N%25%29C=%18=6=%23%26%1624%30N%21%17)C=N3%321)C%121[CH]2(N)CC(F)CN12%14%13)C* |$CO2H;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;CO2H$|</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr"/>
+      <c r="H861" t="inlineStr"/>
+      <c r="I861" t="n">
+        <v>1.549881896146571e-18</v>
+      </c>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K861" t="inlineStr"/>
+    </row>
+    <row r="862">
+      <c r="A862" s="1" t="n">
+        <v>860</v>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0329.png</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr"/>
+      <c r="D862" t="inlineStr"/>
+      <c r="E862" t="inlineStr"/>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>COC1(c2ccc(/C=C/C(=O)O)c(OCc3ccc(NC(=O)[C@H](CC(C)C)NC(=O)[C@H](CCCCN)NC(=O)[C@H](Cc4ccc(Cl)cc4)NC(=O)[C@@H](NC(C)=O)C4Cc5ccccc5C4)cc3)c2Cl)OOC12C1CC3CC4(C1)CC2C34</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr"/>
+      <c r="H862" t="inlineStr"/>
+      <c r="I862" t="n">
+        <v>0.5871271841133691</v>
+      </c>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K862" t="inlineStr"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="1" t="n">
+        <v>861</v>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0331.png</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr"/>
+      <c r="D863" t="inlineStr"/>
+      <c r="E863" t="inlineStr"/>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>CC(C)C1=C2N=C34N=C5(NCC6=CC=CC=C6C=C6=C7(=C8C=CC(N9CCN(CC%10CCN(C%11=CC%12=C(C=C%11F)C(=O)N(C%11CCC(=O)NC%11=O)C%12=O)CC%10)CC9)=CC86=CC(=N7)C6CNCC(C6)O3)C3=CC=CC=C3CNC=N45)N2N=C1</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr"/>
+      <c r="H863" t="inlineStr"/>
+      <c r="I863" t="n">
+        <v>0.3518585811824636</v>
+      </c>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K863" t="inlineStr"/>
+    </row>
+    <row r="864">
+      <c r="A864" s="1" t="n">
+        <v>862</v>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0332.png</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr"/>
+      <c r="D864" t="inlineStr"/>
+      <c r="E864" t="inlineStr"/>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCOCCOCCOCCNc2ccc3c(-c4ccccc4CNc4nc(O[C@@H]5CCCNC5)nc5c(C(C)C)ccn45)nccc3c2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr"/>
+      <c r="H864" t="inlineStr"/>
+      <c r="I864" t="n">
+        <v>0.841570900948982</v>
+      </c>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K864" t="inlineStr"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="1" t="n">
+        <v>863</v>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0340.png</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr"/>
+      <c r="D865" t="inlineStr"/>
+      <c r="E865" t="inlineStr"/>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>CC(C)C12=C345N=C6N=C(NCC7=CC=CC=C7C=C7C=CC(NCC8CCN(CC9CCN(C%10=CC%11=C(C=C%10)C(=O)N(C%10CCC(=O)NC%10=O)C%11=O)CC9)CC8)=CC7=CC7(C)=NCC8=CC=CC=C8CN8C9%10=N%11=C89=N=%103(=C%11(=N4)O3C4CCCNC4[CH]34(CNCC7C4)O6)N=C1)N5N=C2</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr"/>
+      <c r="H865" t="inlineStr"/>
+      <c r="I865" t="n">
+        <v>0.03868369147545255</v>
+      </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K865" t="inlineStr"/>
+    </row>
+    <row r="866">
+      <c r="A866" s="1" t="n">
+        <v>864</v>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T070712/rb_0342.png</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr"/>
+      <c r="D866" t="inlineStr"/>
+      <c r="E866" t="inlineStr"/>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>CC=CC=CC=CCNC(=O)C1CC(O)CN1C(=O)[CH]12C[CH]N1C1=O=C(=O)(N2)N1(CCCCCCN1CCN(C(=O)C2=CC=C(NC3=NC(C4=C(C)C(NC(=O)C56=CC=C(C(C)(C)C)C=5=C6)=CC=C4)=CN=C3O)C=C2)CC1)CCCCNCC1CCC(N2C=C3C=C(NC(=O)C4=NC(C(F)(F)F)=CC=C4)C(C(C)(C)O)=CC3=N2)CC1</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr"/>
+      <c r="H866" t="inlineStr"/>
+      <c r="I866" t="n">
+        <v>0.2098848087602761</v>
+      </c>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K866" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K866"/>
+  <dimension ref="A1:K892"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25565,6 +25565,760 @@
       </c>
       <c r="K866" t="inlineStr"/>
     </row>
+    <row r="867">
+      <c r="A867" s="1" t="n">
+        <v>865</v>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0003.png</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr"/>
+      <c r="D867" t="inlineStr"/>
+      <c r="E867" t="inlineStr"/>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>*.CC(C)(C)c1cc(Cl)ccc1F |$,;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr"/>
+      <c r="H867" t="inlineStr"/>
+      <c r="I867" t="n">
+        <v>0.817614308903156</v>
+      </c>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K867" t="inlineStr"/>
+    </row>
+    <row r="868">
+      <c r="A868" s="1" t="n">
+        <v>866</v>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0008.png</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr"/>
+      <c r="D868" t="inlineStr"/>
+      <c r="E868" t="inlineStr"/>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>CC(C)(C)c1nccs1</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr"/>
+      <c r="H868" t="inlineStr"/>
+      <c r="I868" t="n">
+        <v>0.8068766752070159</v>
+      </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K868" t="inlineStr"/>
+    </row>
+    <row r="869">
+      <c r="A869" s="1" t="n">
+        <v>867</v>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0013.png</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr"/>
+      <c r="D869" t="inlineStr"/>
+      <c r="E869" t="inlineStr"/>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>CC(C)(C)C1CCC(C(C)(C)C)CC1</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr"/>
+      <c r="H869" t="inlineStr"/>
+      <c r="I869" t="n">
+        <v>0.8194374830910158</v>
+      </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K869" t="inlineStr"/>
+    </row>
+    <row r="870">
+      <c r="A870" s="1" t="n">
+        <v>868</v>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0019.png</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr"/>
+      <c r="D870" t="inlineStr"/>
+      <c r="E870" t="inlineStr"/>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>CC(C)OC1CC1</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr"/>
+      <c r="H870" t="inlineStr"/>
+      <c r="I870" t="n">
+        <v>0.813242186473459</v>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K870" t="inlineStr"/>
+    </row>
+    <row r="871">
+      <c r="A871" s="1" t="n">
+        <v>869</v>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0025.png</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr"/>
+      <c r="D871" t="inlineStr"/>
+      <c r="E871" t="inlineStr"/>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>CC(C)(C)n1ccnc1</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr"/>
+      <c r="H871" t="inlineStr"/>
+      <c r="I871" t="n">
+        <v>0.810428369672867</v>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K871" t="inlineStr"/>
+    </row>
+    <row r="872">
+      <c r="A872" s="1" t="n">
+        <v>870</v>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0028.png</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr"/>
+      <c r="D872" t="inlineStr"/>
+      <c r="E872" t="inlineStr"/>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>*.CC(C)CS(=O)(=O)c1cccnc1 |$.;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr"/>
+      <c r="H872" t="inlineStr"/>
+      <c r="I872" t="n">
+        <v>0.7880310062756188</v>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K872" t="inlineStr"/>
+    </row>
+    <row r="873">
+      <c r="A873" s="1" t="n">
+        <v>871</v>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0030.png</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr"/>
+      <c r="D873" t="inlineStr"/>
+      <c r="E873" t="inlineStr"/>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>CC(C)(C)n1cccn1</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr"/>
+      <c r="H873" t="inlineStr"/>
+      <c r="I873" t="n">
+        <v>0.8188771036510377</v>
+      </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K873" t="inlineStr"/>
+    </row>
+    <row r="874">
+      <c r="A874" s="1" t="n">
+        <v>872</v>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0031.png</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr"/>
+      <c r="D874" t="inlineStr"/>
+      <c r="E874" t="inlineStr"/>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>CC(C)c1cnn2c1CCC2</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr"/>
+      <c r="H874" t="inlineStr"/>
+      <c r="I874" t="n">
+        <v>0.8322174893307935</v>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K874" t="inlineStr"/>
+    </row>
+    <row r="875">
+      <c r="A875" s="1" t="n">
+        <v>873</v>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0039.png</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr"/>
+      <c r="D875" t="inlineStr"/>
+      <c r="E875" t="inlineStr"/>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>CC(C)(C)OCC1CC1</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr"/>
+      <c r="H875" t="inlineStr"/>
+      <c r="I875" t="n">
+        <v>0.8343369318405243</v>
+      </c>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K875" t="inlineStr"/>
+    </row>
+    <row r="876">
+      <c r="A876" s="1" t="n">
+        <v>874</v>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0040.png</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr"/>
+      <c r="D876" t="inlineStr"/>
+      <c r="E876" t="inlineStr"/>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>CC(C)Cn1ncc2ccccc21</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr"/>
+      <c r="H876" t="inlineStr"/>
+      <c r="I876" t="n">
+        <v>0.8246530631903097</v>
+      </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K876" t="inlineStr"/>
+    </row>
+    <row r="877">
+      <c r="A877" s="1" t="n">
+        <v>875</v>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0042.png</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr"/>
+      <c r="D877" t="inlineStr"/>
+      <c r="E877" t="inlineStr"/>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>CC(C)(C)C12CCCN1CCC2</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr"/>
+      <c r="H877" t="inlineStr"/>
+      <c r="I877" t="n">
+        <v>0.8078668050331296</v>
+      </c>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K877" t="inlineStr"/>
+    </row>
+    <row r="878">
+      <c r="A878" s="1" t="n">
+        <v>876</v>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0043.png</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr"/>
+      <c r="D878" t="inlineStr"/>
+      <c r="E878" t="inlineStr"/>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>CC(C)(C)C1(C)COC1</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr"/>
+      <c r="H878" t="inlineStr"/>
+      <c r="I878" t="n">
+        <v>0.7969790069028135</v>
+      </c>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K878" t="inlineStr"/>
+    </row>
+    <row r="879">
+      <c r="A879" s="1" t="n">
+        <v>877</v>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0044.png</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr"/>
+      <c r="D879" t="inlineStr"/>
+      <c r="E879" t="inlineStr"/>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>CC(C)c1ccc(OC(F)(F)F)cc1</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr"/>
+      <c r="H879" t="inlineStr"/>
+      <c r="I879" t="n">
+        <v>0.7009653923769675</v>
+      </c>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K879" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="A880" s="1" t="n">
+        <v>878</v>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0045.png</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr"/>
+      <c r="D880" t="inlineStr"/>
+      <c r="E880" t="inlineStr"/>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>CC(C)/C=C/c1ccncc1</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr"/>
+      <c r="H880" t="inlineStr"/>
+      <c r="I880" t="n">
+        <v>0.83636269995944</v>
+      </c>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K880" t="inlineStr"/>
+    </row>
+    <row r="881">
+      <c r="A881" s="1" t="n">
+        <v>879</v>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0050.png</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr"/>
+      <c r="D881" t="inlineStr"/>
+      <c r="E881" t="inlineStr"/>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>CC(C)C1=NCN(C(C)C)C(C(C)C)=C1C(C)C</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr"/>
+      <c r="H881" t="inlineStr"/>
+      <c r="I881" t="n">
+        <v>0.8275178781098258</v>
+      </c>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K881" t="inlineStr"/>
+    </row>
+    <row r="882">
+      <c r="A882" s="1" t="n">
+        <v>880</v>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0055.png</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr"/>
+      <c r="D882" t="inlineStr"/>
+      <c r="E882" t="inlineStr"/>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>CC(C)(C)C1(C(C)(C)C)OC1(C(C)(C)C)C(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr"/>
+      <c r="H882" t="inlineStr"/>
+      <c r="I882" t="n">
+        <v>0.8302648986745174</v>
+      </c>
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K882" t="inlineStr"/>
+    </row>
+    <row r="883">
+      <c r="A883" s="1" t="n">
+        <v>881</v>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0060.png</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr"/>
+      <c r="D883" t="inlineStr"/>
+      <c r="E883" t="inlineStr"/>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>CC(C)C1CN(C(C)C)C(C(C)C)C1C(C)C</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr"/>
+      <c r="H883" t="inlineStr"/>
+      <c r="I883" t="n">
+        <v>0.8210061548506171</v>
+      </c>
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K883" t="inlineStr"/>
+    </row>
+    <row r="884">
+      <c r="A884" s="1" t="n">
+        <v>882</v>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0067.png</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr"/>
+      <c r="D884" t="inlineStr"/>
+      <c r="E884" t="inlineStr"/>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>*.Cc1noc(C)c1C(C)(C)C |$.;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr"/>
+      <c r="H884" t="inlineStr"/>
+      <c r="I884" t="n">
+        <v>0.778852729396465</v>
+      </c>
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K884" t="inlineStr"/>
+    </row>
+    <row r="885">
+      <c r="A885" s="1" t="n">
+        <v>883</v>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0068.png</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr"/>
+      <c r="D885" t="inlineStr"/>
+      <c r="E885" t="inlineStr"/>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>CC(C)(C)C1COC1</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr"/>
+      <c r="H885" t="inlineStr"/>
+      <c r="I885" t="n">
+        <v>0.8299219186375342</v>
+      </c>
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K885" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" s="1" t="n">
+        <v>884</v>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0069.png</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr"/>
+      <c r="D886" t="inlineStr"/>
+      <c r="E886" t="inlineStr"/>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>CC(C)CCC12CC3CC(CC(C3)C1)C2</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr"/>
+      <c r="H886" t="inlineStr"/>
+      <c r="I886" t="n">
+        <v>0.8400428201921993</v>
+      </c>
+      <c r="J886" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K886" t="inlineStr"/>
+    </row>
+    <row r="887">
+      <c r="A887" s="1" t="n">
+        <v>885</v>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0070.png</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr"/>
+      <c r="D887" t="inlineStr"/>
+      <c r="E887" t="inlineStr"/>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>CC1COC2(CCC(C)(C)C2)CN1C(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr"/>
+      <c r="H887" t="inlineStr"/>
+      <c r="I887" t="n">
+        <v>0.824290721951648</v>
+      </c>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K887" t="inlineStr"/>
+    </row>
+    <row r="888">
+      <c r="A888" s="1" t="n">
+        <v>886</v>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0073.png</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr"/>
+      <c r="D888" t="inlineStr"/>
+      <c r="E888" t="inlineStr"/>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>CC(C)S(N)(=O)=O</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr"/>
+      <c r="H888" t="inlineStr"/>
+      <c r="I888" t="n">
+        <v>0.8345107510675754</v>
+      </c>
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K888" t="inlineStr"/>
+    </row>
+    <row r="889">
+      <c r="A889" s="1" t="n">
+        <v>887</v>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0074.png</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr"/>
+      <c r="D889" t="inlineStr"/>
+      <c r="E889" t="inlineStr"/>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>CC(C)c1csc(C(C)C)n1</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr"/>
+      <c r="H889" t="inlineStr"/>
+      <c r="I889" t="n">
+        <v>0.8004497972802574</v>
+      </c>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K889" t="inlineStr"/>
+    </row>
+    <row r="890">
+      <c r="A890" s="1" t="n">
+        <v>888</v>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0075.png</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr"/>
+      <c r="D890" t="inlineStr"/>
+      <c r="E890" t="inlineStr"/>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>CC(C)C(=O)OCCC#N</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr"/>
+      <c r="H890" t="inlineStr"/>
+      <c r="I890" t="n">
+        <v>0.8074205975055919</v>
+      </c>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K890" t="inlineStr"/>
+    </row>
+    <row r="891">
+      <c r="A891" s="1" t="n">
+        <v>889</v>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0080.png</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr"/>
+      <c r="D891" t="inlineStr"/>
+      <c r="E891" t="inlineStr"/>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>CC(C)CN1CCC(C(C)C)CC1</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr"/>
+      <c r="H891" t="inlineStr"/>
+      <c r="I891" t="n">
+        <v>0.8396083279938001</v>
+      </c>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K891" t="inlineStr"/>
+    </row>
+    <row r="892">
+      <c r="A892" s="1" t="n">
+        <v>890</v>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/wavy/cx_in/wv_0081.png</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr"/>
+      <c r="D892" t="inlineStr"/>
+      <c r="E892" t="inlineStr"/>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>CC(C)/C=C(/CC(C)C)C(C)C</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr"/>
+      <c r="H892" t="inlineStr"/>
+      <c r="I892" t="n">
+        <v>0.7984320129418967</v>
+      </c>
+      <c r="J892" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K892" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K892"/>
+  <dimension ref="A1:K968"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26319,6 +26319,2210 @@
       </c>
       <c r="K892" t="inlineStr"/>
     </row>
+    <row r="893">
+      <c r="A893" s="1" t="n">
+        <v>891</v>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0362.png</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr"/>
+      <c r="D893" t="inlineStr"/>
+      <c r="E893" t="inlineStr"/>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>[H]C1(C(=O)NC(C(=O)N2CC(O)CC2C(=O)NC(CC(=O)NCCOCCOCCOCCNC(=O)CN2CCN(C(=O)C3=CC(F)=C(NC4=NC(C5CC5)=CN56C7C89=CNN=C8C78(=CNN=C8)C95=CN5=C46N=C5)C=C3)CC2)C2=CC=C(C3=C(C)N=CS3)C=C2)C(C)(C)C)CC1</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr"/>
+      <c r="H893" t="inlineStr"/>
+      <c r="I893" t="n">
+        <v>0.1252789507773663</v>
+      </c>
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K893" t="inlineStr"/>
+    </row>
+    <row r="894">
+      <c r="A894" s="1" t="n">
+        <v>892</v>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0364.png</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr"/>
+      <c r="D894" t="inlineStr"/>
+      <c r="E894" t="inlineStr"/>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>CCn1nc(C)cc1C(=O)Nc1nc2cc(C(N)=O)cc3c2n1C/C=C/Cn1c(NC(=O)c2cc(C)nn2CC)nc2cc(C(N)=O)cc(c21)OCC(N1CC2CCC(C1)O2)CO3</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr"/>
+      <c r="H894" t="inlineStr"/>
+      <c r="I894" t="n">
+        <v>0.8167903231438567</v>
+      </c>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K894" t="inlineStr"/>
+    </row>
+    <row r="895">
+      <c r="A895" s="1" t="n">
+        <v>893</v>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0366.png</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr"/>
+      <c r="D895" t="inlineStr"/>
+      <c r="E895" t="inlineStr"/>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>CC(C)(C)C(=O)OCOP1(=O)OCOC2(=O)C(C)(C)(C)C(=O)(OCOP3(=O)(OCOC(=O)C(C)(C)C)CO3CC3OC(N4C=NC5=C4N=CN=C5N)C(F)C3OP3(=O)OC[CH]45C(O3)[CH]36OCC7N89C=NC%10%11=C8N=CN=C%10(N)=N8=C%11(N)C%10=C(N=C8)N(C=N%10)[CH]9(CO43)[CH]756O1)C2(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr"/>
+      <c r="H895" t="inlineStr"/>
+      <c r="I895" t="n">
+        <v>0.001817076448464142</v>
+      </c>
+      <c r="J895" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K895" t="inlineStr"/>
+    </row>
+    <row r="896">
+      <c r="A896" s="1" t="n">
+        <v>894</v>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0367.png</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr"/>
+      <c r="D896" t="inlineStr"/>
+      <c r="E896" t="inlineStr"/>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>CC1=NOC(C(C(=O)N2CC(O)CC2C(=O)NC(CC(=O)NCCCCCCCNC(=O)CN2CCN(C(=O)C3=CC(F)=C(NC45=NC(C6CC6)=C6N789C%10%11%12=C%13=C7%14%15(=C7N%16=C48%17=N7%13=C=%1659N6%10%17%14)C%114=C5=C%12%1567=C8NN9=C6=N(=C=947)N85)C=C3)CC2)C2=CC=C(C3=C(C)N=CS3)C=C2)C(C)(C)C)=C1</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr"/>
+      <c r="H896" t="inlineStr"/>
+      <c r="I896" t="n">
+        <v>0.01698433611194213</v>
+      </c>
+      <c r="J896" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K896" t="inlineStr"/>
+    </row>
+    <row r="897">
+      <c r="A897" s="1" t="n">
+        <v>895</v>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0379.png</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr"/>
+      <c r="D897" t="inlineStr"/>
+      <c r="E897" t="inlineStr"/>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC1=NC23=C4C(=CC(C(N)=O)=C2)OCC(N2CCC(C#N)CC2)COC2=CC(C(N)=O)=CC56=C27N(CC=CCN1)C(NC(=O)C1=CC(C)=NN1CC)(=N5)N7(CC=CCN4C(NC(=O)C1=CC(C)=NN1CC)=N3)C(NC(=O)C1=CC(C)=NN1CC)=N6</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr"/>
+      <c r="H897" t="inlineStr"/>
+      <c r="I897" t="n">
+        <v>0.3970236958179507</v>
+      </c>
+      <c r="J897" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K897" t="inlineStr"/>
+    </row>
+    <row r="898">
+      <c r="A898" s="1" t="n">
+        <v>896</v>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0386.png</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr"/>
+      <c r="D898" t="inlineStr"/>
+      <c r="E898" t="inlineStr"/>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>Cn1cc(-c2cccc(C(F)(F)F)c2)c2sc(C(=O)NC3CC4(CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6)CC4)C3)cc2c1=O</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr"/>
+      <c r="H898" t="inlineStr"/>
+      <c r="I898" t="n">
+        <v>0.8178532882779922</v>
+      </c>
+      <c r="J898" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K898" t="inlineStr"/>
+    </row>
+    <row r="899">
+      <c r="A899" s="1" t="n">
+        <v>897</v>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0388.png</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr"/>
+      <c r="D899" t="inlineStr"/>
+      <c r="E899" t="inlineStr"/>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC12=NC3=C45C(=CC(C(N)=O)=C3)OCC(N3CCC(OP(=O)(OC(C)(C)C)OC(C)(C)C)C3)COC3=CC(C(N)=O)=CC67=C38N39CC=CCN14CC=CCN81C348%10=N6=C913(=N=47)N(CC=CCN25)CNC(=O)C1=CC(C)=NN1(CC)C1(=CC2=NN1(CC)C1(=CC(C)(=NN1CC)C2)C(=O)N8)C(=O)N%103</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr"/>
+      <c r="H899" t="inlineStr"/>
+      <c r="I899" t="n">
+        <v>0.01271708829738312</v>
+      </c>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K899" t="inlineStr"/>
+    </row>
+    <row r="900">
+      <c r="A900" s="1" t="n">
+        <v>898</v>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0399.png</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr"/>
+      <c r="D900" t="inlineStr"/>
+      <c r="E900" t="inlineStr"/>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>CC(C)C(NC(=O)CCOCCOCCOCCC(=O)NCCN1CCN(C(=O)C2=CC(F)=C(NC34=NC(C5CC5)=C5N678C9%10=C%11=C6%12%13(=CN6=C37N59%12C=648=N%11)C3(=CNN=C3)C3=NNC=C3%10%13)C=C2)CC1)C(=O)N1CC(O)CC1C(=O)NCC1=CC=C(C2=CN=CS2)C=C1</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr"/>
+      <c r="H900" t="inlineStr"/>
+      <c r="I900" t="n">
+        <v>0.03670332202610745</v>
+      </c>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K900" t="inlineStr"/>
+    </row>
+    <row r="901">
+      <c r="A901" s="1" t="n">
+        <v>899</v>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0402.png</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr"/>
+      <c r="D901" t="inlineStr"/>
+      <c r="E901" t="inlineStr"/>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>CCC(C)(C)C(=O)OCOP12(=O)OCOC(=O)C(C)(C)(CC)C(=O)(C(C)(C)CC)OCCOCC3O[CH]456C(F)[CH]3789%10OP3(=O)OC[CH]C(O1)O2P1(=O)(OCOC(=O)C(C)(C)CC)C2C1O2C[CH]71O4C([CH]8(F)[CH]19O3%10)N51C=NC2=C1N=CN=C2(N)C12=C(N=CN=C1N)N6C=N2</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr"/>
+      <c r="H901" t="inlineStr"/>
+      <c r="I901" t="n">
+        <v>0.01257274257374918</v>
+      </c>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K901" t="inlineStr"/>
+    </row>
+    <row r="902">
+      <c r="A902" s="1" t="n">
+        <v>900</v>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0403.png</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr"/>
+      <c r="D902" t="inlineStr"/>
+      <c r="E902" t="inlineStr"/>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(C(CC(=O)NCCCCCNC(=O)CN3CCN(C(=O)C4=CC(F)=C(NC56=NC(C7CC7)=C7N89%10C%11%12%13=C%14=C8%15%16(=C8N%14=C59%14%17=N8=C6%10%14N7%11%15%17)C%125=C6=C%13%1678=C9NN%10=C7=N(=C=%1058)N96)C=C4)CC3)NC(=O)C3CC(O)CN3C(=O)C(NC(=O)C3(F)CC3)C(C)(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr"/>
+      <c r="H902" t="inlineStr"/>
+      <c r="I902" t="n">
+        <v>0.01105399300597473</v>
+      </c>
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K902" t="inlineStr"/>
+    </row>
+    <row r="903">
+      <c r="A903" s="1" t="n">
+        <v>901</v>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0405.png</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr"/>
+      <c r="D903" t="inlineStr"/>
+      <c r="E903" t="inlineStr"/>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)COCC(=O)NCCN2CCN(C(=O)c3ccc(Nc4nc(C5CC5)cn5c(-c6cn[nH]c6)cnc45)c(F)c3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr"/>
+      <c r="H903" t="inlineStr"/>
+      <c r="I903" t="n">
+        <v>0.8232431779310004</v>
+      </c>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K903" t="inlineStr"/>
+    </row>
+    <row r="904">
+      <c r="A904" s="1" t="n">
+        <v>902</v>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0408.png</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr"/>
+      <c r="D904" t="inlineStr"/>
+      <c r="E904" t="inlineStr"/>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>Cc1cc(-c2nc(-c3ccc(N4CCC(CN5CCC6(CC5)COc5cc7c(cc56)C(=O)N(C5CCC(=O)NC5=O)C7=O)CC4)nc3)cn3nccc23)ccc1[C@@H](C)NC(=O)c1nnn(C(C)(C)C)n1</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr"/>
+      <c r="H904" t="inlineStr"/>
+      <c r="I904" t="n">
+        <v>0.7983359986010865</v>
+      </c>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K904" t="inlineStr"/>
+    </row>
+    <row r="905">
+      <c r="A905" s="1" t="n">
+        <v>903</v>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0416.png</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr"/>
+      <c r="D905" t="inlineStr"/>
+      <c r="E905" t="inlineStr"/>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC1=NC2=C3N1CC=CCN145C6=C7C8=C(C(N)=O)C=C69OCC(N6CCC(O)C6)N6(CCC(O)C6)C6%10COC3(=CC(C(N)=O)=C2)OCC(N2CCC(O)C2)C6O2CC913=C81(C=C(C(N)=O)C=C23OC%10)N=C42(NC(=O)C3=CC(C)=NN3CC)=N71=C25NC(=O)C1=CC(C)=NN1CC</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr"/>
+      <c r="H905" t="inlineStr"/>
+      <c r="I905" t="n">
+        <v>0.004514561475377862</v>
+      </c>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K905" t="inlineStr"/>
+    </row>
+    <row r="906">
+      <c r="A906" s="1" t="n">
+        <v>904</v>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0417.png</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr"/>
+      <c r="D906" t="inlineStr"/>
+      <c r="E906" t="inlineStr"/>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC1=NC2=C3C(=CC(C(N)=O)=C2)OCC(N2CCC(OP(=O)(O)O)C2)COC24=CC(C(N)=O)=CC567=C2(C=C=4C(C(N)=O)=C5)N(CC=CCN13)(C(NC(=O)C1=CC(C)=NN1CC)=N6)C(NC(=O)C1=CC(C)=NN1CC)=N7.S</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr"/>
+      <c r="H906" t="inlineStr"/>
+      <c r="I906" t="n">
+        <v>0.5106671102894167</v>
+      </c>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K906" t="inlineStr"/>
+    </row>
+    <row r="907">
+      <c r="A907" s="1" t="n">
+        <v>905</v>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0422.png</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr"/>
+      <c r="D907" t="inlineStr"/>
+      <c r="E907" t="inlineStr"/>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>[H]C12CC(C)(C)C(C(=O)NC3C4=CC=CCC4=CC3OCC#CC#CCO[CH]3=CC4=C(C=CC=C4)C3NC(=O)C3N4C(=O)C(NC(=O)C(C)NC)CCOC4([H])CC3(C)C)N1C(=O)C(NC(=O)C(C)NC)CCO2</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr"/>
+      <c r="H907" t="inlineStr"/>
+      <c r="I907" t="n">
+        <v>0.5820154437331464</v>
+      </c>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K907" t="inlineStr"/>
+    </row>
+    <row r="908">
+      <c r="A908" s="1" t="n">
+        <v>906</v>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0423.png</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr"/>
+      <c r="D908" t="inlineStr"/>
+      <c r="E908" t="inlineStr"/>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>COC(=O)c1cccc(CN2CCOCCOCCN(Cc3cc(OCCc4ccc(NC(=O)OC(C)(C)C)cc4)cc(C(=O)OC)n3)CCOCCOCC2)n1</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr"/>
+      <c r="H908" t="inlineStr"/>
+      <c r="I908" t="n">
+        <v>0.7498794691086894</v>
+      </c>
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K908" t="inlineStr"/>
+    </row>
+    <row r="909">
+      <c r="A909" s="1" t="n">
+        <v>907</v>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0428.png</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr"/>
+      <c r="D909" t="inlineStr"/>
+      <c r="E909" t="inlineStr"/>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>CC(C)(C)Cc1cc(CSC[C@H](N)C(=O)O)cc(CN2CCN(C(=O)CN3CCN(CC(=O)O)CCN(CC(=O)O)CCN(CC(=O)O)CC3)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr"/>
+      <c r="H909" t="inlineStr"/>
+      <c r="I909" t="n">
+        <v>0.6288647608549713</v>
+      </c>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K909" t="inlineStr"/>
+    </row>
+    <row r="910">
+      <c r="A910" s="1" t="n">
+        <v>908</v>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0436.png</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr"/>
+      <c r="D910" t="inlineStr"/>
+      <c r="E910" t="inlineStr"/>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>CCn1c(-c2cc(N3CCN4CCOCC4C3)cnc2C(C)OC)c2c3cc(ccc31)-c1csc(n1)CC(NC(=O)C1C(C)C1C)C(=O)N1NC(C(=O)OCC(C)(C)C2)C2CC1C2</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr"/>
+      <c r="H910" t="inlineStr"/>
+      <c r="I910" t="n">
+        <v>0.7090422626759315</v>
+      </c>
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K910" t="inlineStr"/>
+    </row>
+    <row r="911">
+      <c r="A911" s="1" t="n">
+        <v>909</v>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0439.png</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr"/>
+      <c r="D911" t="inlineStr"/>
+      <c r="E911" t="inlineStr"/>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>CC(C)NC(=O)C1CC(O)CN1C(=O)C(NC(=O)COCCOCCOCCNC(=O)CN12CCN3C4(=O)N(CC1)(CC2)C31(=O)C2=C3=C4156=CC(F)=C14C=C5=C157=C=62=CC5(=C3F)NC123=C56=C89%10%11=C%12%13C5%14=C=85%15N%128%16%17C%12%18%19=C%20=C8%21%22%23(C8=CNN=C8)=CN=C1%168%24%25C=71%16=N7=C%26C21%27%28=N1=C%263%16%17(=N%20)(C6%278(=N9)N4)(N%13%125%24%21)N%18%15%28%25%22(C=C7C2CC2C%14%102CC2C%112CC2)C2(=C1)C1=CN3N=C1C2%19%231=C3NN=C1)C(C)C</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr"/>
+      <c r="H911" t="inlineStr"/>
+      <c r="I911" t="n">
+        <v>4.983511845494615e-07</v>
+      </c>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K911" t="inlineStr"/>
+    </row>
+    <row r="912">
+      <c r="A912" s="1" t="n">
+        <v>910</v>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0449.png</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr"/>
+      <c r="D912" t="inlineStr"/>
+      <c r="E912" t="inlineStr"/>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>[H]C12CC(C)(C)C(C(=O)NC3C4=C(C=CC=C4)CC3OCC3=CC=C(C#CCO[CH]4=CC5=C(C=CC=C5)C4NC(=O)C4N5C(=O)C(NC(=O)C(C)N(C)C(=O)OC(C)(C)C)CCSC5([H])CC4(C)C)C=C3)N1C(=O)C(NC(=O)C(C)N(C)C(=O)OC(C)(C)C)CCS2</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr"/>
+      <c r="H912" t="inlineStr"/>
+      <c r="I912" t="n">
+        <v>0.5264108564159679</v>
+      </c>
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K912" t="inlineStr"/>
+    </row>
+    <row r="913">
+      <c r="A913" s="1" t="n">
+        <v>911</v>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0452.png</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr"/>
+      <c r="D913" t="inlineStr"/>
+      <c r="E913" t="inlineStr"/>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NC(=O)C3(F)CC3)C(C)(C)C)C(OCCCCNC(=O)CN3CCN(C(=O)C4=CC(F)=C(NC5N=C(C6CC6)C=N6C(C7=CNN=C7)=CN=C56)C=C4)CC3)=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr"/>
+      <c r="H913" t="inlineStr"/>
+      <c r="I913" t="n">
+        <v>0.7613854620640638</v>
+      </c>
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K913" t="inlineStr"/>
+    </row>
+    <row r="914">
+      <c r="A914" s="1" t="n">
+        <v>912</v>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0456.png</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr"/>
+      <c r="D914" t="inlineStr"/>
+      <c r="E914" t="inlineStr"/>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>O=C(O)CCC(NC(=O)NC(CCCCN(Cc1ccc(Br)cc1)C(=O)CCCCCNC(=O)CN1CCN(CC(=O)O)CCN(CC(=O)O)CCN(CC(=O)O)CC1)C(=O)O)C(=O)O</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr"/>
+      <c r="H914" t="inlineStr"/>
+      <c r="I914" t="n">
+        <v>0.8137497071408518</v>
+      </c>
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K914" t="inlineStr"/>
+    </row>
+    <row r="915">
+      <c r="A915" s="1" t="n">
+        <v>913</v>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0457.png</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr"/>
+      <c r="D915" t="inlineStr"/>
+      <c r="E915" t="inlineStr"/>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC=NC1=C23C4=CC(C(N)=O)=C1C1=C5N2CC=CCN26C7=CC8=C(C(N)=O)C=C7(OCC(N7CCC(O)CC7)CO4)C24=C8(C=C(C(N)=O)C=C4OCC(N2CCC(O)CC2)COC53=CC(C(N)=O)=C1)N=C6NC(=O)C1=CC(C)=NN1CC</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr"/>
+      <c r="H915" t="inlineStr"/>
+      <c r="I915" t="n">
+        <v>0.1951681135951842</v>
+      </c>
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K915" t="inlineStr"/>
+    </row>
+    <row r="916">
+      <c r="A916" s="1" t="n">
+        <v>914</v>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0458.png</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr"/>
+      <c r="D916" t="inlineStr"/>
+      <c r="E916" t="inlineStr"/>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC1=NC23=C4N1CC=CCN15C(NC(=O)C6=CC(C)=NN6CC)=NC67(=C18C1=C(=C8(=CC(C(N)=O)=C6)OCC68COC4(=CC(C(N)=O)=C2)O(C=CC(C(N)=O)=C3)CC(C6O1)N1CCC(C1)O([Si]1(C)(C)CC1(C)C)[CH]1(O[Si](C)(C)C(C)(C)C)CCN8C1)C(C(N)=O)=C7)N=C5NC(=O)C1=CC(C)=NN1CC</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr"/>
+      <c r="H916" t="inlineStr"/>
+      <c r="I916" t="n">
+        <v>0.008252304500852051</v>
+      </c>
+      <c r="J916" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K916" t="inlineStr"/>
+    </row>
+    <row r="917">
+      <c r="A917" s="1" t="n">
+        <v>915</v>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0459.png</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr"/>
+      <c r="D917" t="inlineStr"/>
+      <c r="E917" t="inlineStr"/>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC1=NC2=C3N1CC=CCN145C6=C78C9=C(C(N)=O)C=C%10OCC(CCN%11CCOCC%11)COC3(=CC(C(N)=O)=C2)OCC(CCN2CCOCC2)COC62=CC(C(N)=O)=C7C93=C%1021NC41(NC(=O)C2=CC(C)=NN2CC)(=N3)=N8=C51NC(=O)C1=CC(C)=NN1CC</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr"/>
+      <c r="H917" t="inlineStr"/>
+      <c r="I917" t="n">
+        <v>0.004148247425585713</v>
+      </c>
+      <c r="J917" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K917" t="inlineStr"/>
+    </row>
+    <row r="918">
+      <c r="A918" s="1" t="n">
+        <v>916</v>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0464.png</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr"/>
+      <c r="D918" t="inlineStr"/>
+      <c r="E918" t="inlineStr"/>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC=NC1=C23C4=CC(C(N)=O)=C1C1=C5N2CC=CCN26C7=CC8=C(C(N)=O)C=C7(OCC(C7CCNCC7)CO4)C24=C8(C=C(C(N)=O)C=C4OCC(C2CCNCC2)COC53=CC(C(N)=O)=C1)N=C6NC(=O)C1=CC(C)=NN1CC</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr"/>
+      <c r="H918" t="inlineStr"/>
+      <c r="I918" t="n">
+        <v>0.1301031810989756</v>
+      </c>
+      <c r="J918" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K918" t="inlineStr"/>
+    </row>
+    <row r="919">
+      <c r="A919" s="1" t="n">
+        <v>917</v>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0465.png</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr"/>
+      <c r="D919" t="inlineStr"/>
+      <c r="E919" t="inlineStr"/>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCCC(O)NCCCCn2cnc(-c3cnc(O[C@@H]4CCN(C(=O)Cc5ccc(OC(F)(F)F)cc5)C[C@H]4F)c(C(N)=O)c3)c2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr"/>
+      <c r="H919" t="inlineStr"/>
+      <c r="I919" t="n">
+        <v>0.8430239027149971</v>
+      </c>
+      <c r="J919" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K919" t="inlineStr"/>
+    </row>
+    <row r="920">
+      <c r="A920" s="1" t="n">
+        <v>918</v>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0466.png</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr"/>
+      <c r="D920" t="inlineStr"/>
+      <c r="E920" t="inlineStr"/>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC1=NC2=C3C(=CC(C(N)=O)=C2)OCC(N2CCC(N)CC2)COC24=CC(C(N)=O)=CC567=C2(C(OCC(CO)N2CCC(N)CC2)=C=4C(C(N)=O)=C5)N2(CC=CCN13)C(NC(=O)C1=CC(C)=NN1CC)=N6C2(NC(=O)C1=CC(C)=NN1CC)=N7</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr"/>
+      <c r="H920" t="inlineStr"/>
+      <c r="I920" t="n">
+        <v>0.1766539403401964</v>
+      </c>
+      <c r="J920" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K920" t="inlineStr"/>
+    </row>
+    <row r="921">
+      <c r="A921" s="1" t="n">
+        <v>919</v>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0470.png</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr"/>
+      <c r="D921" t="inlineStr"/>
+      <c r="E921" t="inlineStr"/>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>[H]C12CC(C)(C)C(C(=O)NC3C4=C(C=CC=C4)CC3OCC#CC3=CC=CC(C#CCO[CH]CC4=CC=CC=C4)=C3)N1C(=O)C(NC(=O)C(C)N(C)C(=O)OC(C)(C)C)CCS2.[H]C12CC3(C)(C)C4[CH]3(C(=O)NC3C5=C(C=CC=C5)CC3O)N41C(=O)C(NC(=O)C(C)N(C)C(=O)OC(C)(C)C)CCS2</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr"/>
+      <c r="H921" t="inlineStr"/>
+      <c r="I921" t="n">
+        <v>0.2912964728985484</v>
+      </c>
+      <c r="J921" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K921" t="inlineStr"/>
+    </row>
+    <row r="922">
+      <c r="A922" s="1" t="n">
+        <v>920</v>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0471.png</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr"/>
+      <c r="D922" t="inlineStr"/>
+      <c r="E922" t="inlineStr"/>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>C=C1OC2C(CC3CCN(C)CC3)COC345=CC(C(N)=O)=CC6=C3N(CC=CCN378C9%10=C%11%12C%13=C(C(N)=O)C=C9%14OCC29%15(CO4)CC2(CCN(C)CC2)C9C(CO5)C%15OC%102=CC(C(N)=O)=C%11C%134(=C1%1423)N=C71(NC(=O)C2=CC(C)=NN2CC)=N%124=C18NC(=O)C1=CC(C)=NN1CC)C(NC(=O)C1=CC(C)=NN1CC)=N6</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr"/>
+      <c r="H922" t="inlineStr"/>
+      <c r="I922" t="n">
+        <v>0.0008862207562917128</v>
+      </c>
+      <c r="J922" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K922" t="inlineStr"/>
+    </row>
+    <row r="923">
+      <c r="A923" s="1" t="n">
+        <v>921</v>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0473.png</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr"/>
+      <c r="D923" t="inlineStr"/>
+      <c r="E923" t="inlineStr"/>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>COC=C1CN2CC3CN4CCC56CC4N4(CCC789(CC4)CN(C7)C4=CC=C7%10(CN(C%11CCC(=O)NC%11=O)C(=O)C7=C4)C4C7=CC=C(C=C7%10C(=O)N4C4CCC(=O)NC4=O)N(C58)C69)CC4CN(CC5=C(OC)C=CC=C5(OC)C=C1OC)(C4)C32</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr"/>
+      <c r="H923" t="inlineStr"/>
+      <c r="I923" t="n">
+        <v>0.01268095452392003</v>
+      </c>
+      <c r="J923" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K923" t="inlineStr"/>
+    </row>
+    <row r="924">
+      <c r="A924" s="1" t="n">
+        <v>922</v>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0476.png</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr"/>
+      <c r="D924" t="inlineStr"/>
+      <c r="E924" t="inlineStr"/>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>COP(=O)(S)O[CH]123O4[CH]56[CH]17(N1C=NC8=C1N=CN(CCNC(=O)CO)C8=O)O[CH]189%10COP(=O)(S)O[CH]%11(OP(=O)(S)OC1[CH]1(O78)[CH]529O[CH]163%10O)C(COP4(=O)S)OC(N1C=C2CCCSC3=NC=NC1=C23)C%11F</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr"/>
+      <c r="H924" t="inlineStr"/>
+      <c r="I924" t="n">
+        <v>0.1059968933483516</v>
+      </c>
+      <c r="J924" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K924" t="inlineStr"/>
+    </row>
+    <row r="925">
+      <c r="A925" s="1" t="n">
+        <v>923</v>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0480.png</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr"/>
+      <c r="D925" t="inlineStr"/>
+      <c r="E925" t="inlineStr"/>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>[H]C12CC(C)(C)C(C(=O)NC3C4=CC=CCC4=CC3OCC#CC#CCO[CH]3=CC4=C(C=CC=C4)C3NC(=O)C3N4C(=O)C(NC(=O)C(CC)NC)CCSC4([H])CC3(C)C)N1C(=O)C(NC(=O)C(CC)NC)CCS2</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr"/>
+      <c r="H925" t="inlineStr"/>
+      <c r="I925" t="n">
+        <v>0.5564464817718697</v>
+      </c>
+      <c r="J925" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K925" t="inlineStr"/>
+    </row>
+    <row r="926">
+      <c r="A926" s="1" t="n">
+        <v>924</v>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0487.png</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr"/>
+      <c r="D926" t="inlineStr"/>
+      <c r="E926" t="inlineStr"/>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>[H][C@]12CC(C)(C)[C@@H](C(=O)N[C@H]3c4ccccc4C[C@H]3OCCS(=O)(=O)CCO[C@@H]3Cc4ccccc4[C@@H]3NC(=O)[C@H]3N4C(=O)[C@@H](NC(=O)[C@H](C)N(C)C(=O)OC(C)(C)C)CCS[C@@]4(Cl)CC3(C)C)N1C(=O)[C@@H](NC(=O)[C@H](C)N(C)C(=O)OC(C)(C)C)CCS2</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr"/>
+      <c r="H926" t="inlineStr"/>
+      <c r="I926" t="n">
+        <v>0.794726161022269</v>
+      </c>
+      <c r="J926" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K926" t="inlineStr"/>
+    </row>
+    <row r="927">
+      <c r="A927" s="1" t="n">
+        <v>925</v>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0494.png</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr"/>
+      <c r="D927" t="inlineStr"/>
+      <c r="E927" t="inlineStr"/>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>COC(=O)c1cc2c(c([N+](=O)[O-])c1)NC/C=C/CNc1c(cc(C(=O)OC)cc1[N+](=O)[O-])OCC(N1CC[C@H](O[Si](C)(C)C(C)(C)C)C1)CO2.S</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr"/>
+      <c r="H927" t="inlineStr"/>
+      <c r="I927" t="n">
+        <v>0.7596514244874697</v>
+      </c>
+      <c r="J927" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K927" t="inlineStr"/>
+    </row>
+    <row r="928">
+      <c r="A928" s="1" t="n">
+        <v>926</v>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0496.png</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr"/>
+      <c r="D928" t="inlineStr"/>
+      <c r="E928" t="inlineStr"/>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>COC1=CC=CC(OC)=C1CN12CC3(CN45CCC678(CC4)CN(C6)C4=CC=C69%10C(=O)N(C%11CCC(=O)NC%11=O)(CC6=C4)C4C(C6CCC(=O)NC6=O)C9(=O)C6=CC=C(C=C64%10)N4C7C6(CCN(CC7CN(CC9=C(OC)C=C9)C731)C5C6)C48)C2</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr"/>
+      <c r="H928" t="inlineStr"/>
+      <c r="I928" t="n">
+        <v>0.01062268003809441</v>
+      </c>
+      <c r="J928" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K928" t="inlineStr"/>
+    </row>
+    <row r="929">
+      <c r="A929" s="1" t="n">
+        <v>927</v>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0498.png</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr"/>
+      <c r="D929" t="inlineStr"/>
+      <c r="E929" t="inlineStr"/>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NC(=O)CCOCCOCCOCCOCCNC(=O)CN3CCN(C(=O)C4=CC(F)=C(NC=NC(=CN5C678=CN=C569C756=CNN=C5C895=CNN=C65)C5CC5)C=C4)CC3)C(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr"/>
+      <c r="H929" t="inlineStr"/>
+      <c r="I929" t="n">
+        <v>0.2771900526634529</v>
+      </c>
+      <c r="J929" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K929" t="inlineStr"/>
+    </row>
+    <row r="930">
+      <c r="A930" s="1" t="n">
+        <v>928</v>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0500.png</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr"/>
+      <c r="D930" t="inlineStr"/>
+      <c r="E930" t="inlineStr"/>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC1=NC2=C3N1CC=CCN14C(NC(=O)C5=CC(C)=NN5CC)=NC56(=C17C1=C(=C7(=CC(C(N)=O)=C5)OCC5(N7CCC(OP(=O)(O)O)CC7)COC3(=CC(C(N)=O)=C2)OCC(N2CCC(OP(=O)(O)O)CC2)C5O1)C(C(N)=O)=C6)N=C4NC(=O)C1=CC(C)=NN1CC</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr"/>
+      <c r="H930" t="inlineStr"/>
+      <c r="I930" t="n">
+        <v>0.1039793297318868</v>
+      </c>
+      <c r="J930" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K930" t="inlineStr"/>
+    </row>
+    <row r="931">
+      <c r="A931" s="1" t="n">
+        <v>929</v>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0501.png</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr"/>
+      <c r="D931" t="inlineStr"/>
+      <c r="E931" t="inlineStr"/>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>COc1ccc(CC(=O)N2CC[C@@H](Oc3ccc(-c4cn(CCCC(=O)NCCCCCCCNc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)cn4)cc3C(N)=O)[C@H](F)C2)cc1</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr"/>
+      <c r="H931" t="inlineStr"/>
+      <c r="I931" t="n">
+        <v>0.8179582863868883</v>
+      </c>
+      <c r="J931" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K931" t="inlineStr"/>
+    </row>
+    <row r="932">
+      <c r="A932" s="1" t="n">
+        <v>930</v>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0509.png</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr"/>
+      <c r="D932" t="inlineStr"/>
+      <c r="E932" t="inlineStr"/>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>[H]c1c2cc(C(=O)N(C(C)C)C(C)C)cc1-n1nnc(c1[H])-c1cc(C(=O)N(C(C)C)C(C)C)cc(c1[H])-n1nnc(c1[H])-c1cc(C(=O)N(C(C)C)C(C)C)cc(c1[H])-n1nnc(c1[H])-c1cc(C(=O)N(C(C)C)C(C)C)cc(c1[H])-n1nnc-2c1[H]</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr"/>
+      <c r="H932" t="inlineStr"/>
+      <c r="I932" t="n">
+        <v>0.5856722169946543</v>
+      </c>
+      <c r="J932" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K932" t="inlineStr"/>
+    </row>
+    <row r="933">
+      <c r="A933" s="1" t="n">
+        <v>931</v>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0510.png</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr"/>
+      <c r="D933" t="inlineStr"/>
+      <c r="E933" t="inlineStr"/>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>O=C(O)C1=CC234=C(C=C1)N=C1(CC5678=CC=C9%10C%11=CC9%12%13=NC(=CC=C%12)OCC9=C(C=C(C%12=CN(C%14CC%14)N=C%12)C=C9)CCCCOC59=C%10C%11%13=CC=6=C97C8C5=N1C=2=CN53CC1CCO1)N4CC1CCO1</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr"/>
+      <c r="H933" t="inlineStr"/>
+      <c r="I933" t="n">
+        <v>0.008656474772805357</v>
+      </c>
+      <c r="J933" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K933" t="inlineStr"/>
+    </row>
+    <row r="934">
+      <c r="A934" s="1" t="n">
+        <v>932</v>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0517.png</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr"/>
+      <c r="D934" t="inlineStr"/>
+      <c r="E934" t="inlineStr"/>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>CC(C)C(NC(=O)CCOCCOCCOCCOCCC(=O)N1CCN(C(=O)C2=CC(F)=C(NC34=NC(C5CC5)=C5N678C9%10=C%11=C6%12%13(=CN6=C37N59%12C=648=N%11)C3(=CNN=C3)C3=NNC=C3%10%13)C=C2)CC1)C(=O)N1CC(O)CC1C(=O)NCC1=CC=C(C2=CN=CS2)C=C1</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr"/>
+      <c r="H934" t="inlineStr"/>
+      <c r="I934" t="n">
+        <v>0.02367715968557669</v>
+      </c>
+      <c r="J934" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K934" t="inlineStr"/>
+    </row>
+    <row r="935">
+      <c r="A935" s="1" t="n">
+        <v>933</v>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0520.png</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr"/>
+      <c r="D935" t="inlineStr"/>
+      <c r="E935" t="inlineStr"/>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>CCN12C(C3=C(C(C)OC)N=CC(N4CCN(C)CC4)=C3)=C34=C1(C1=C(C(C)OC)N=CC(N5CCN(C)CC5)=C1)=C1CC(C)(C)COC(=O)[CH]NN5(CC6(C)C(C(N5)C(=O)OCC(C)(C)C3)C6(F)F)C(=O)C(NC(=O)C3CC3C)CC3=NC(=CS3)C35=CC=C2(C1=C3)C4=C5</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr"/>
+      <c r="H935" t="inlineStr"/>
+      <c r="I935" t="n">
+        <v>0.3934247189193844</v>
+      </c>
+      <c r="J935" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K935" t="inlineStr"/>
+    </row>
+    <row r="936">
+      <c r="A936" s="1" t="n">
+        <v>934</v>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0522.png</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr"/>
+      <c r="D936" t="inlineStr"/>
+      <c r="E936" t="inlineStr"/>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>[H][C@]12CC(C)(C)[C@@H](C(=O)N[C@H](CCC(=O)NCCNC(=O)CC[C@@H](NC(=O)[C@H]3N4C(=O)[C@@H](NC(=O)[C@H](C)N(C)C(=O)OC(C)(C)C)CCS[C@@]4([H])CC3(C)C)c3ccccc3)c3ccccc3)N1C(=O)[C@@H](NC(=O)[C@H](C)N(C)C(=O)OC(C)(C)C)CCS2</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr"/>
+      <c r="H936" t="inlineStr"/>
+      <c r="I936" t="n">
+        <v>0.7626757112394875</v>
+      </c>
+      <c r="J936" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K936" t="inlineStr"/>
+    </row>
+    <row r="937">
+      <c r="A937" s="1" t="n">
+        <v>935</v>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0524.png</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr"/>
+      <c r="D937" t="inlineStr"/>
+      <c r="E937" t="inlineStr"/>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>COC(=O)COC1=C(N2CCOCCOCCN(C3=CC4=C(C=C3O3CC3(=O)OC)C3(OC4=O)C4=C(C=C(OC(C)=O)C(C5=CC=NC=C5)=C4)OC4=C3C=C(C3=CC=NC=C3)C(OC(C)=O)=C4)CCOCC2)C=CC=C1</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr"/>
+      <c r="H937" t="inlineStr"/>
+      <c r="I937" t="n">
+        <v>0.3529091629746254</v>
+      </c>
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K937" t="inlineStr"/>
+    </row>
+    <row r="938">
+      <c r="A938" s="1" t="n">
+        <v>936</v>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0526.png</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr"/>
+      <c r="D938" t="inlineStr"/>
+      <c r="E938" t="inlineStr"/>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>C=C1=C2(C(=O)N3CCN(CC(=O)NCCOCCOCCOCC(=O)NC(C(=O)N4CC(O)CC4C(=O)NCC4=CC=C(C5=C(C)N=CS5)C=C4)C(C)(C)C)CC3)=CC(F)=C34NC56789=NC%10=CN%11%12C%13%14%15%16=CN=C%115%17%18C65(=N=7C6(=C7N%13%17%11%19C%13%17(=CN=C%125%118N7%13%14%18%19)C%155=CNN=C5C%17%165=CNN=C5)C5CC5C%1065CC5)N39C(=C1F)C4=C2</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr"/>
+      <c r="H938" t="inlineStr"/>
+      <c r="I938" t="n">
+        <v>0.003147282892074059</v>
+      </c>
+      <c r="J938" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K938" t="inlineStr"/>
+    </row>
+    <row r="939">
+      <c r="A939" s="1" t="n">
+        <v>937</v>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0529.png</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr"/>
+      <c r="D939" t="inlineStr"/>
+      <c r="E939" t="inlineStr"/>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC1=NC2=C3N1CC=CCN145C67=C89C%10=C(C(N)=O)C=C6%11OCC6%12%13COC3(=CC(C(N)=O)=C2)OCC(C6OC72=CC(C(N)=O)=C8C%1036=C%1121NC41(NC(=O)C2=CC(C)=NN2CC)(=N3)=N96=C51NC(=O)C1=CC(C)=NN1CC)C%12C1(CN(C)C1)C%13</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr"/>
+      <c r="H939" t="inlineStr"/>
+      <c r="I939" t="n">
+        <v>0.01641490567281529</v>
+      </c>
+      <c r="J939" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K939" t="inlineStr"/>
+    </row>
+    <row r="940">
+      <c r="A940" s="1" t="n">
+        <v>938</v>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0530.png</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr"/>
+      <c r="D940" t="inlineStr"/>
+      <c r="E940" t="inlineStr"/>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC1=NC2=C3C(=CC(C(N)=O)=C2)OCC(N2CCC(C(=O)O)CC2)COC24=CC(C(N)=O)=CC567=C2(C(OCC(CO)N2CCC(C(=O)O)CC2)=C=4C(C(N)=O)=C5)N2(CC=CCN13)C(NC(=O)C1=CC(C)=NN1CC)=N6C2(NC(=O)C1=CC(C)=NN1CC)=N7</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr"/>
+      <c r="H940" t="inlineStr"/>
+      <c r="I940" t="n">
+        <v>0.1373248101091842</v>
+      </c>
+      <c r="J940" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K940" t="inlineStr"/>
+    </row>
+    <row r="941">
+      <c r="A941" s="1" t="n">
+        <v>939</v>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0532.png</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr"/>
+      <c r="D941" t="inlineStr"/>
+      <c r="E941" t="inlineStr"/>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC1=N2C3(NC(=O)C4=CC(C)=NN4CC)=NC245=C2(C=CC(C(N)=O)=C4)C(=CC(C(N)=O)=C5)OCC(N4CCC(C(=O)O)C4)COC4=CC(C(N)=O)=CC=C4NCC=CCN132</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr"/>
+      <c r="H941" t="inlineStr"/>
+      <c r="I941" t="n">
+        <v>0.49137262394176</v>
+      </c>
+      <c r="J941" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K941" t="inlineStr"/>
+    </row>
+    <row r="942">
+      <c r="A942" s="1" t="n">
+        <v>940</v>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0533.png</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr"/>
+      <c r="D942" t="inlineStr"/>
+      <c r="E942" t="inlineStr"/>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>COC1C=COC(C)OC2=C3(C)C(O)=CC45(=O)C67=C(O)C(C)=C238OC2(C)OC=CC(OC)[CH]1(C)C(OC(C)=O)C(C)C(O)C(C)C(O)C(C)C=CC=C(C)C(=O)N1C43=C49O%10C%11%12=C(N=C4(C6=C8C2=O)C%103(=C195C7=O)O%11)C(O)=CC(OCCNC(C)=O)=C%12</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr"/>
+      <c r="H942" t="inlineStr"/>
+      <c r="I942" t="n">
+        <v>0.01162381732013528</v>
+      </c>
+      <c r="J942" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K942" t="inlineStr"/>
+    </row>
+    <row r="943">
+      <c r="A943" s="1" t="n">
+        <v>941</v>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0535.png</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr"/>
+      <c r="D943" t="inlineStr"/>
+      <c r="E943" t="inlineStr"/>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC12=NC34=C56=C7C=C(C(N)=O)C=C58OCC5CO9C%10OC9%11=CC(C(N)=O)=CC9%12=C%11%13N%11CC=CCN1C=38(C(=CC(C(N)=O)=C74)OCC%10(C1=CC=CC=N1)C51=CC=CC=N1)N26CC=CCN%13C1(=N9)=N%12=C%11NC(=O)C2=CC(C)=NN2(CC)C2(=CC(C)=NN2CC)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr"/>
+      <c r="H943" t="inlineStr"/>
+      <c r="I943" t="n">
+        <v>0.002630635169755023</v>
+      </c>
+      <c r="J943" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K943" t="inlineStr"/>
+    </row>
+    <row r="944">
+      <c r="A944" s="1" t="n">
+        <v>942</v>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0536.png</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr"/>
+      <c r="D944" t="inlineStr"/>
+      <c r="E944" t="inlineStr"/>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NC(=O)COCCOCCOCCNC(=O)CN3CCN(C(=O)C4=CC(F)=C(NC56=NC(C7CC7)=C7N89%10C%11%12=C%13=C8%14%15(=CN8=C59%16N7%11%14C=86%16%10=N%13)C%125=C6=C%157(=CNN=C7)C5=NN6)C=C4)CC3)C(C)(C)C)C=C2)C=CN1</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr"/>
+      <c r="H944" t="inlineStr"/>
+      <c r="I944" t="n">
+        <v>0.01114003974878576</v>
+      </c>
+      <c r="J944" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K944" t="inlineStr"/>
+    </row>
+    <row r="945">
+      <c r="A945" s="1" t="n">
+        <v>943</v>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0538.png</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr"/>
+      <c r="D945" t="inlineStr"/>
+      <c r="E945" t="inlineStr"/>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCOCCC(=O)NCCCCn2cnc(-c3cnc(O[C@@H]4CCN(C(=O)Cc5ccc(OC(F)(F)F)cc5)C[C@H]4F)c(C(N)=O)c3)c2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr"/>
+      <c r="H945" t="inlineStr"/>
+      <c r="I945" t="n">
+        <v>0.8399942643559993</v>
+      </c>
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K945" t="inlineStr"/>
+    </row>
+    <row r="946">
+      <c r="A946" s="1" t="n">
+        <v>944</v>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0539.png</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr"/>
+      <c r="D946" t="inlineStr"/>
+      <c r="E946" t="inlineStr"/>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC1=NC2=C3C(=CC(C(=O)O)=C2)OCC2(N4CCC(O[Si](C)(C)C(C)(C)C)C4)COC45=CC(C(=O)O)=CC678=C4(C(=C=5C(C(=O)O)=C6)OC2CN2CCC(O[Si](C)(C)C(C)(C)C)C2)N(CC=CCN13)(C(NC(=O)C1=CC(C)=NN1CC)=N7)C(NC(=O)C1=CC(C)=NN1CC)=N8</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr"/>
+      <c r="H946" t="inlineStr"/>
+      <c r="I946" t="n">
+        <v>0.09876894263902443</v>
+      </c>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K946" t="inlineStr"/>
+    </row>
+    <row r="947">
+      <c r="A947" s="1" t="n">
+        <v>945</v>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0540.png</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr"/>
+      <c r="D947" t="inlineStr"/>
+      <c r="E947" t="inlineStr"/>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>NC(=O)c1cc(-c2cn(CCCCNC(=O)CCOCCOCCNc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)cn2)cnc1O[C@@H]1CCN(C(=O)Cc2ccc(OC(F)(F)F)cc2)C[C@H]1F</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr"/>
+      <c r="H947" t="inlineStr"/>
+      <c r="I947" t="n">
+        <v>0.8400529315157256</v>
+      </c>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K947" t="inlineStr"/>
+    </row>
+    <row r="948">
+      <c r="A948" s="1" t="n">
+        <v>946</v>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0541.png</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr"/>
+      <c r="D948" t="inlineStr"/>
+      <c r="E948" t="inlineStr"/>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>[H]C12CC3(CC=CC3)C(C(=O)NC3C4=C(C=CC=C4)CC3OCC#CC#CCO[CH]3=CC4=C(C=CC=C4)C3NC(=O)C3N4C(=O)C(NC(=O)C(C)NC)CCSC4([H])CC34CC=CC4)N1C(=O)C(NC(=O)C(C)NC)CCS2</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr"/>
+      <c r="H948" t="inlineStr"/>
+      <c r="I948" t="n">
+        <v>0.6619135757376027</v>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K948" t="inlineStr"/>
+    </row>
+    <row r="949">
+      <c r="A949" s="1" t="n">
+        <v>947</v>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0546.png</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr"/>
+      <c r="D949" t="inlineStr"/>
+      <c r="E949" t="inlineStr"/>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>C1C2[C-]3C2O13.[C-]#[N+]C1=C2C3=C4C=C1C1([N+]#[C-])=CC25=C2(C=C1)COC167=CC=C8(F)C9(=N1)C1(F)=CC=C(N6=C18C9(=CC=CCC1=NC6=C(C=C([C-]=O)C=C6OCCOC)N1CC1CCO1)C=CCOCC35)O7C42</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr"/>
+      <c r="H949" t="inlineStr"/>
+      <c r="I949" t="n">
+        <v>0.01955401887429398</v>
+      </c>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K949" t="inlineStr"/>
+    </row>
+    <row r="950">
+      <c r="A950" s="1" t="n">
+        <v>948</v>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0556.png</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr"/>
+      <c r="D950" t="inlineStr"/>
+      <c r="E950" t="inlineStr"/>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NCC4CC5(CCN(CCN6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)CO4)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr"/>
+      <c r="H950" t="inlineStr"/>
+      <c r="I950" t="n">
+        <v>0.8246892665782795</v>
+      </c>
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K950" t="inlineStr"/>
+    </row>
+    <row r="951">
+      <c r="A951" s="1" t="n">
+        <v>949</v>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0557.png</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr"/>
+      <c r="D951" t="inlineStr"/>
+      <c r="E951" t="inlineStr"/>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC1=NC2=C3C(=CC(C(N)=O)=C2)OCC2(CCC4CCOCN4)COC456=CC(C(N)=O)=CC789=C4(C(=C=5C(C(N)=O)=C7)O6C2)N2(CC=CCN13)C(NC(=O)C1=CC(C)=NN1CC)=N8C2(NC(=O)C1=CC(C)=NN1CC)=N9</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr"/>
+      <c r="H951" t="inlineStr"/>
+      <c r="I951" t="n">
+        <v>0.2430776260328035</v>
+      </c>
+      <c r="J951" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K951" t="inlineStr"/>
+    </row>
+    <row r="952">
+      <c r="A952" s="1" t="n">
+        <v>950</v>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0564.png</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr"/>
+      <c r="D952" t="inlineStr"/>
+      <c r="E952" t="inlineStr"/>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>C=C(C=CC=CC=CC1=CC=CC=C1)C1=C2(C=CC=C1)[C]13(=CC456=[C]789C%10%11%12=C1C%1071%13=[C]%117%10C%11=CC=CC7%14=[C]%111[Pt]38%1017%11%15%16%17[N]3=C(C=CC=C3)C3=[C]1(C=CC(=C)=C1=CC=C[C]47(=C1C1=C[C]%114=C(C=C1)C1=[N]4%15C=CC=C1)=[C]59%16=[C]%126%13%17)C=C%14C=C3)C213=N2C=CC=CC2=C1C=CC=C3</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr"/>
+      <c r="H952" t="inlineStr"/>
+      <c r="I952" t="n">
+        <v>0.0006956235549215273</v>
+      </c>
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K952" t="inlineStr"/>
+    </row>
+    <row r="953">
+      <c r="A953" s="1" t="n">
+        <v>951</v>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0566.png</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr"/>
+      <c r="D953" t="inlineStr"/>
+      <c r="E953" t="inlineStr"/>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>[C-]1CCO1.[C-]C(F)(F)CNCCOC1=CC(C(=O)O)=CC2=C1N=C(CC=CC=C13C4=C5C6(=CC=C4)O47C8C9=CC=C([N+]#[C-])C%10(=C9)C9([N+]#[C-])=C%11C=C8%12C=C9C%108([N+]#[C-])=CC%11=C9(C=C8)COC48%10%11=CC=C4C1%13%14=N8C431=N6%13%10C57(=CC=C%141)O%11C%129)N2CC1CCO1</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr"/>
+      <c r="H953" t="inlineStr"/>
+      <c r="I953" t="n">
+        <v>0.002256801484788682</v>
+      </c>
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K953" t="inlineStr"/>
+    </row>
+    <row r="954">
+      <c r="A954" s="1" t="n">
+        <v>952</v>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0570.png</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr"/>
+      <c r="D954" t="inlineStr"/>
+      <c r="E954" t="inlineStr"/>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>[H]C12CC(C)(C)C(C(=O)NC3C4=CC=CCC4=CC3OCC#CC#CCO[CH]3=CC4=C(C=CC=C4)C3NC(=O)C3N4C(=O)C(NC(=O)C(C)(C)NC)CCSC4([H])CC3(C)C)N1C(=O)C(NC(=O)C(C)(C)NC)CCS2</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr"/>
+      <c r="H954" t="inlineStr"/>
+      <c r="I954" t="n">
+        <v>0.5544399125273991</v>
+      </c>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K954" t="inlineStr"/>
+    </row>
+    <row r="955">
+      <c r="A955" s="1" t="n">
+        <v>953</v>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0573.png</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr"/>
+      <c r="D955" t="inlineStr"/>
+      <c r="E955" t="inlineStr"/>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>[H]C12CC(C)(CC=C)C(C(=O)NC3C4=C(C=CC=C4)C=[CH]3OCC#CC#CCOC3C=C4CC=C=C=C4C3NC(=O)C3N4C(=O)C(NC(=O)C(C)NC)CCSC4([H])CC3(CC=C)CC=C)N1C(=O)C(NC(=O)C(C)NC)CCS2</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr"/>
+      <c r="H955" t="inlineStr"/>
+      <c r="I955" t="n">
+        <v>0.251807944391749</v>
+      </c>
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K955" t="inlineStr"/>
+    </row>
+    <row r="956">
+      <c r="A956" s="1" t="n">
+        <v>954</v>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0577.png</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr"/>
+      <c r="D956" t="inlineStr"/>
+      <c r="E956" t="inlineStr"/>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>Cl.[H]C12CCC(C(=O)NC3C4=C(C=CC=C4)C=[CH]3OCC#CC#CCOC3C=C4CC=CC=C4C3NC(=O)C3C(O)CC4([H])SCCC(NC(=O)C(C)NC)C(=O)N34)N1C(=O)C(NC(=O)C(C)NC)CCS2</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr"/>
+      <c r="H956" t="inlineStr"/>
+      <c r="I956" t="n">
+        <v>0.4977714984601495</v>
+      </c>
+      <c r="J956" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K956" t="inlineStr"/>
+    </row>
+    <row r="957">
+      <c r="A957" s="1" t="n">
+        <v>955</v>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0579.png</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr"/>
+      <c r="D957" t="inlineStr"/>
+      <c r="E957" t="inlineStr"/>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>COc1cc(-c2cn(C)c(=O)c3cc(C(=O)NC4CCN(C5CCN(c6ccc7c(c6)CN(C6CCC(=O)NC6=O)C7=O)CC5(F)F)CC4)sc23)cc(OC)c1CN(C)C</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr"/>
+      <c r="H957" t="inlineStr"/>
+      <c r="I957" t="n">
+        <v>0.7189004129747113</v>
+      </c>
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K957" t="inlineStr"/>
+    </row>
+    <row r="958">
+      <c r="A958" s="1" t="n">
+        <v>956</v>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0580.png</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr"/>
+      <c r="D958" t="inlineStr"/>
+      <c r="E958" t="inlineStr"/>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>[H]C1([N+]#[C-])CC(F)(F)CN12C(=O)CNC(C)(=O)C1(=CC=NC3=CC=C(OCCCN4CCN(C(=O)C(CCCCNC(=O)CN5CCN(CC(=O)O)CCN(CC(=O)O)CCN(CC(=O)O)CC5)NC(=O)CCCC(=O)NC(CCCCNC(=O)CCCC5=CC=C(I)C=C5)C(=O)O)CC4)C=C31)C(=O)NCC(=O)N1CC(F)(F)CC12([H])[N+]#[C-]</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr"/>
+      <c r="H958" t="inlineStr"/>
+      <c r="I958" t="n">
+        <v>0.509621557110935</v>
+      </c>
+      <c r="J958" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K958" t="inlineStr"/>
+    </row>
+    <row r="959">
+      <c r="A959" s="1" t="n">
+        <v>957</v>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0581.png</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr"/>
+      <c r="D959" t="inlineStr"/>
+      <c r="E959" t="inlineStr"/>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC=NC1=C23C4=CC(C(N)=O)=C1C1=C5N2CC=CCN26C7=CC8=C(C(N)=O)C=C7(OCC(C7CNC7)CO4)C24=C8(C=C(C(N)=O)C=C4OCC(C2CNC2)COC53=CC(C(N)=O)=C1)N=C6NC(=O)C1=CC(C)=NN1CC</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr"/>
+      <c r="H959" t="inlineStr"/>
+      <c r="I959" t="n">
+        <v>0.1603132355197553</v>
+      </c>
+      <c r="J959" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K959" t="inlineStr"/>
+    </row>
+    <row r="960">
+      <c r="A960" s="1" t="n">
+        <v>958</v>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0582.png</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr"/>
+      <c r="D960" t="inlineStr"/>
+      <c r="E960" t="inlineStr"/>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>CC1=NOC(C(C(=O)N2CC(O)CC2C(=O)NC(CC(=O)NCCOCCOCCOCCNC(=O)CN23CCN4C5(=O)N(CC2)(CC3)C42(=O)C3=C4=C5267=CC(F)=C(C=C6)NC2568=NC9%10(C%11CC%11)=C%11N%12%13C%14=C(C9%15CC%15)N=%102=C2(N5C(=C4F)C=C=73)C634=NC2%1285=N=3C=C%13(C2=CNN=C2)N%14%1145)C2=CC=C(C3=C(C)N=CS3)C=C2)C(C)C)=C1</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr"/>
+      <c r="H960" t="inlineStr"/>
+      <c r="I960" t="n">
+        <v>0.001474417749027076</v>
+      </c>
+      <c r="J960" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K960" t="inlineStr"/>
+    </row>
+    <row r="961">
+      <c r="A961" s="1" t="n">
+        <v>959</v>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0585.png</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr"/>
+      <c r="D961" t="inlineStr"/>
+      <c r="E961" t="inlineStr"/>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>O.[H][C@]1(C)C/C(C)=C/[C@@]([H])(CC=C)C(=O)C[C@]([H])(O)[C@@]([H])(C)[C@@]([H])(C(C)=C[C@]2([H])CC[C@@]([H])(O)[C@]([H])(OC)C2)OC(=O)[C@]2([H])CCCCN2C(=O)C(=O)[C@]2(O)O[C@]([H])([C@@]([H])(OC)C1)[C@@]([H])(OC)C[C@@]2([H])C</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr"/>
+      <c r="H961" t="inlineStr"/>
+      <c r="I961" t="n">
+        <v>0.5265892542131855</v>
+      </c>
+      <c r="J961" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K961" t="inlineStr"/>
+    </row>
+    <row r="962">
+      <c r="A962" s="1" t="n">
+        <v>960</v>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0586.png</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr"/>
+      <c r="D962" t="inlineStr"/>
+      <c r="E962" t="inlineStr"/>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC12=NC34=C56=C7C=C(C(N)=O)C=C58OCC5N9(CCNCC9)C9(COC%10=CC(C(N)=O)=CC%11%12=C%10%13N%10CC=CCN16C=38(C(=CC(C(N)=O)=C74)OC9)N2CC=CCN%131C2=N%11=C%101(=N%12)NC(=O)C1(=CC(C)=NN1CC)N1(CC)N=C(C)C=C1C(=O)N2)N51CCNCC1</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr"/>
+      <c r="H962" t="inlineStr"/>
+      <c r="I962" t="n">
+        <v>0.02162091186534806</v>
+      </c>
+      <c r="J962" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K962" t="inlineStr"/>
+    </row>
+    <row r="963">
+      <c r="A963" s="1" t="n">
+        <v>961</v>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0588.png</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr"/>
+      <c r="D963" t="inlineStr"/>
+      <c r="E963" t="inlineStr"/>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>C1C2[C-]3C2O13.[C-]OC(=O)C1=CC2=C(N=C(CC=CC=C34C56=N789C%10%11=CC=C5%12C375=N%103C87%10(=CC=C65(F)C4%1239=N7)OCC34=C5C=C([N+]#[C-])(C=C3)C3=CC(=CC5=C3[N+]#[C-])C4O%11%10)N2CC2CCO2)C(OCCOC)=C1</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr"/>
+      <c r="H963" t="inlineStr"/>
+      <c r="I963" t="n">
+        <v>0.03307572973154837</v>
+      </c>
+      <c r="J963" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K963" t="inlineStr"/>
+    </row>
+    <row r="964">
+      <c r="A964" s="1" t="n">
+        <v>962</v>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0591.png</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr"/>
+      <c r="D964" t="inlineStr"/>
+      <c r="E964" t="inlineStr"/>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC1=NC2=C3C(=CC(C(=O)OC)=C2)OCC24(N5CCC(O[Si](C)(C)C(C)(C)C)C5)COC56=CC(C(=O)OC)=CC789=C5(C(=C=6C(C(=O)OC)=C7)OC2C(N2CCC(O[Si](C)(C)C(C)(C)C)C2)C4O)N(CC=CCN13)(C(NC(=O)C1=CC(C)=NN1CC)=N8)C(NC(=O)C1=CC(C)=NN1CC)=N9</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr"/>
+      <c r="H964" t="inlineStr"/>
+      <c r="I964" t="n">
+        <v>0.00662854049889302</v>
+      </c>
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K964" t="inlineStr"/>
+    </row>
+    <row r="965">
+      <c r="A965" s="1" t="n">
+        <v>963</v>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0593.png</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr"/>
+      <c r="D965" t="inlineStr"/>
+      <c r="E965" t="inlineStr"/>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NC(=O)CCCC(=O)NCCN3CCN(C(=O)C456=CC(F)=C78C(=C4)C(=C(F)C=5=C6)N74C567=N9=C45%10(=NC4=C5N%11C%12(C%13=CNN=C%13)=CN=C%116%10N5%12C=C9C5CC5C45CC5)N87)CC3)C(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr"/>
+      <c r="H965" t="inlineStr"/>
+      <c r="I965" t="n">
+        <v>0.05170676424581289</v>
+      </c>
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K965" t="inlineStr"/>
+    </row>
+    <row r="966">
+      <c r="A966" s="1" t="n">
+        <v>964</v>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0594.png</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr"/>
+      <c r="D966" t="inlineStr"/>
+      <c r="E966" t="inlineStr"/>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>[H][C@]12CC3(CCCC3)[C@@H](C(=O)N[C@H]3c4ccccc4C[C@H]3OCC#CC#CCO[C@@H]3Cc4ccccc4[C@@H]3NC(=O)[C@H]3N4C(=O)[C@@H](NC(=O)[C@H](C)NC)CCO[C@@]4([H])CC34CCCC4)N1C(=O)[C@@H](NC(=O)[C@H](C)NC)CCO2</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr"/>
+      <c r="H966" t="inlineStr"/>
+      <c r="I966" t="n">
+        <v>0.8249204783561979</v>
+      </c>
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K966" t="inlineStr"/>
+    </row>
+    <row r="967">
+      <c r="A967" s="1" t="n">
+        <v>965</v>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0598.png</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr"/>
+      <c r="D967" t="inlineStr"/>
+      <c r="E967" t="inlineStr"/>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>COC1=CC(OCCN(C)C)=CC=C1N=C1C=C23NC(=O)C(C)=CC=CC(C)[CH]45(O)[CH](C)(C=CC=C(C)C(=O)N2)[CH]2(O)[CH]4(C)[CH]4(O)[CH]6(C)[CH](O)([CH]4(C)[CH]4(OC(C)=O)[CH]7(C)[CH]8(OC)C=CO9%10C(=CC(OC)[CH]84(C)[CH]67OC(C)=O)OC9467(C)OC89%11=C(C)C(O)=C(C3=O)C1=C8C4(=O)C%1096O%117)[CH]25C</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr"/>
+      <c r="H967" t="inlineStr"/>
+      <c r="I967" t="n">
+        <v>0.002893464234439642</v>
+      </c>
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K967" t="inlineStr"/>
+    </row>
+    <row r="968">
+      <c r="A968" s="1" t="n">
+        <v>966</v>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T124239/rb_0599.png</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr"/>
+      <c r="D968" t="inlineStr"/>
+      <c r="E968" t="inlineStr"/>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NC(=O)CCCCCCCCNC(=O)CN34CCN5C6(=O)N(CC3)(CC4)C53(=O)C4=C5=C6378=CC(F)=C(C=C7)NC3679=NC%10%11%12=CN%13%14%15%16C%17=CN=C3%13%18C3(=N=%106C(=C%14N%17%186C%15(C%10=CNN=C%10)=CN=C367%16)C%113CC3C%123CC3)N9C(=C5F)C=C=84)C(C)(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr"/>
+      <c r="H968" t="inlineStr"/>
+      <c r="I968" t="n">
+        <v>0.001199295675504335</v>
+      </c>
+      <c r="J968" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K968" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K968"/>
+  <dimension ref="A1:K1050"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28523,6 +28523,2384 @@
       </c>
       <c r="K968" t="inlineStr"/>
     </row>
+    <row r="969">
+      <c r="A969" s="1" t="n">
+        <v>967</v>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0601.png</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr"/>
+      <c r="D969" t="inlineStr"/>
+      <c r="E969" t="inlineStr"/>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>COc1cnc(C(=O)NCc2cccc(CC(=O)N(C)CCCCCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)c2)cc1C=C[C@H]1CC[C@@H](C(F)(F)F)CC1</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr"/>
+      <c r="H969" t="inlineStr"/>
+      <c r="I969" t="n">
+        <v>0.4912208934435648</v>
+      </c>
+      <c r="J969" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K969" t="inlineStr"/>
+    </row>
+    <row r="970">
+      <c r="A970" s="1" t="n">
+        <v>968</v>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0609.png</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr"/>
+      <c r="D970" t="inlineStr"/>
+      <c r="E970" t="inlineStr"/>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr"/>
+      <c r="H970" t="inlineStr"/>
+      <c r="I970" t="n">
+        <v>0.858677920594599</v>
+      </c>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K970" t="inlineStr"/>
+    </row>
+    <row r="971">
+      <c r="A971" s="1" t="n">
+        <v>969</v>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0633.png</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr"/>
+      <c r="D971" t="inlineStr"/>
+      <c r="E971" t="inlineStr"/>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>CCN1C(C(=O)NC23CCC(C(=O)NCCOCCOCCOCC4NC45=CC=CC4=C5CN(C5CCC(=O)NC5=O)C4=O)(CC2)CC3)C(C2=CC=CC(Cl)=C2F)C2(C(=O)NC3=CC(Cl)=CC=C32)C12CCCCC2</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr"/>
+      <c r="H971" t="inlineStr"/>
+      <c r="I971" t="n">
+        <v>0.3278696182360725</v>
+      </c>
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K971" t="inlineStr"/>
+    </row>
+    <row r="972">
+      <c r="A972" s="1" t="n">
+        <v>970</v>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0645.png</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr"/>
+      <c r="D972" t="inlineStr"/>
+      <c r="E972" t="inlineStr"/>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>CCC=C(Cl)C(=O)N1CCN(C2=NC=NC34=C25F2C3(=F)C3(C6=C(F)C=CC=C6OCCCCCCCN6CCC(C7=C8CN(C9CCC(=O)NC9=O)C(=O)C8=CC(F)=C7)CC6)=C(Cl)C=C2354)CC1</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr"/>
+      <c r="H972" t="inlineStr"/>
+      <c r="I972" t="n">
+        <v>0.07914582071648514</v>
+      </c>
+      <c r="J972" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K972" t="inlineStr"/>
+    </row>
+    <row r="973">
+      <c r="A973" s="1" t="n">
+        <v>971</v>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0657.png</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr"/>
+      <c r="D973" t="inlineStr"/>
+      <c r="E973" t="inlineStr"/>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CCN(C23=NC(OCC4CCCN4C)=NC456=C789%10=C%11=C4%12(F7)(F8)C9(C4=C(F)C=CC=C4OCCCCCCCN4CCC(C7=C8CN(C9CCC(=O)NC9=O)C(=O)C8=CC(F)=C7)CC4)=C(Cl)C=C%1125C%12%10=C36Cl)CC1</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr"/>
+      <c r="H973" t="inlineStr"/>
+      <c r="I973" t="n">
+        <v>0.06385916462819353</v>
+      </c>
+      <c r="J973" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K973" t="inlineStr"/>
+    </row>
+    <row r="974">
+      <c r="A974" s="1" t="n">
+        <v>972</v>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0665.png</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr"/>
+      <c r="D974" t="inlineStr"/>
+      <c r="E974" t="inlineStr"/>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>O=C1NCCCC#CC2=C3CN4C5CCC6(=O)N7C(=O)C8(CCC7(=O)N6C58=O)N56CC78=C(C#CCCCNC(=O)C9%10=CC(=CC=C9)NC(=O)[CH]9%11NC%12%13(CCCCC%12)C9C9(=CC=CC(Cl)=C9F)[CH]%11(C9=CC=CC(Cl)=C9F)C(NC%139CCCCC9)C(=O)NC9=CC=C%10C1=C9)(C=CC=C7C5=O)C2=CC=C38C46=O</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr"/>
+      <c r="H974" t="inlineStr"/>
+      <c r="I974" t="n">
+        <v>0.01463260118201493</v>
+      </c>
+      <c r="J974" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K974" t="inlineStr"/>
+    </row>
+    <row r="975">
+      <c r="A975" s="1" t="n">
+        <v>973</v>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0677.png</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr"/>
+      <c r="D975" t="inlineStr"/>
+      <c r="E975" t="inlineStr"/>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3cccc(NCCCNC(=O)c4ccc(NC(=O)[C@@H]5NC6(CCCCC6)[C](C(=O)Nc6cccc(Cl)c6)[C@H]5c5cccc(Cl)c5F)cc4)c3C2=O)C(=O)N1 |^1:35|</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr"/>
+      <c r="H975" t="inlineStr"/>
+      <c r="I975" t="n">
+        <v>0.495200825275305</v>
+      </c>
+      <c r="J975" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K975" t="inlineStr"/>
+    </row>
+    <row r="976">
+      <c r="A976" s="1" t="n">
+        <v>974</v>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0685.png</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr"/>
+      <c r="D976" t="inlineStr"/>
+      <c r="E976" t="inlineStr"/>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr"/>
+      <c r="H976" t="inlineStr"/>
+      <c r="I976" t="n">
+        <v>0.8852381577782763</v>
+      </c>
+      <c r="J976" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K976" t="inlineStr"/>
+    </row>
+    <row r="977">
+      <c r="A977" s="1" t="n">
+        <v>975</v>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0701.png</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr"/>
+      <c r="D977" t="inlineStr"/>
+      <c r="E977" t="inlineStr"/>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>C=CC=C[CH]12C3NC4(CCCCC4)C14(C(=O)NC1=CC(Cl)=CC=C14)C14(CCCCC1)N[CH]2(C(=O)NC1CC[CH]2(CC1)C(=O)NCCOCCOCCOCCNC1=CC=CC5=C1CN(C5=O)C1CCC(=O)N5C(=O)CCC(NCC6=CC=CC=C6NCCOCCOCCOCCNC2(=O)[CH]CC[CH]NC3=O)C15=O)C4C1=CC=CC(Cl)=C1</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr"/>
+      <c r="H977" t="inlineStr"/>
+      <c r="I977" t="n">
+        <v>0.09757041519302079</v>
+      </c>
+      <c r="J977" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K977" t="inlineStr"/>
+    </row>
+    <row r="978">
+      <c r="A978" s="1" t="n">
+        <v>976</v>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0705.png</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr"/>
+      <c r="D978" t="inlineStr"/>
+      <c r="E978" t="inlineStr"/>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>COc1cc2nn(C3CC4(CCN(C(=O)C5(F)CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)CC4)C3)cc2cc1NC(=O)c1cccc(N2CCOCC2)n1.[I-39]</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr"/>
+      <c r="H978" t="inlineStr"/>
+      <c r="I978" t="n">
+        <v>0.8180840888568922</v>
+      </c>
+      <c r="J978" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K978" t="inlineStr"/>
+    </row>
+    <row r="979">
+      <c r="A979" s="1" t="n">
+        <v>977</v>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0721.png</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr"/>
+      <c r="D979" t="inlineStr"/>
+      <c r="E979" t="inlineStr"/>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>COc1cc2nn(C3CC4(CCN(C(=O)C5CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)CC4)C3)cc2cc1NC(=O)c1cccc(N2C[C@H]3C[C@@H]2CO3)n1</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr"/>
+      <c r="H979" t="inlineStr"/>
+      <c r="I979" t="n">
+        <v>0.8297926051539406</v>
+      </c>
+      <c r="J979" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K979" t="inlineStr"/>
+    </row>
+    <row r="980">
+      <c r="A980" s="1" t="n">
+        <v>978</v>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0733.png</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr"/>
+      <c r="D980" t="inlineStr"/>
+      <c r="E980" t="inlineStr"/>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(CCOc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)CC2)c(C)cc1Nc1ncc(Br)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr"/>
+      <c r="H980" t="inlineStr"/>
+      <c r="I980" t="n">
+        <v>0.7357674470872281</v>
+      </c>
+      <c r="J980" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K980" t="inlineStr"/>
+    </row>
+    <row r="981">
+      <c r="A981" s="1" t="n">
+        <v>979</v>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0741.png</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr"/>
+      <c r="D981" t="inlineStr"/>
+      <c r="E981" t="inlineStr"/>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr"/>
+      <c r="H981" t="inlineStr"/>
+      <c r="I981" t="n">
+        <v>0.8934688545023076</v>
+      </c>
+      <c r="J981" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K981" t="inlineStr"/>
+    </row>
+    <row r="982">
+      <c r="A982" s="1" t="n">
+        <v>980</v>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0749.png</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr"/>
+      <c r="D982" t="inlineStr"/>
+      <c r="E982" t="inlineStr"/>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr"/>
+      <c r="H982" t="inlineStr"/>
+      <c r="I982" t="n">
+        <v>0.8531395009049217</v>
+      </c>
+      <c r="J982" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K982" t="inlineStr"/>
+    </row>
+    <row r="983">
+      <c r="A983" s="1" t="n">
+        <v>981</v>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0757.png</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr"/>
+      <c r="D983" t="inlineStr"/>
+      <c r="E983" t="inlineStr"/>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>O=C1NCCCCCC2=C3=C4(=CC=CC56=C47C(=O)N4(C5=O)C58CCC(=O)N(C(=O)CCC(C5)N5C(=O)C(=C2C574=O)C6=C3)C8=O)CCCCCNC(=O)C2=CC=C(C=C2)NC(=O)[CH]2(NC3(CCCCC3)C2C2=CC=CC(Cl)=C2F)[CH]2(C3=CC=CC(Cl)=C3F)C(NC3(CCCCC3)C23C(=O)NC2=CC(Cl)=CC=C23)C(=O)NC2=CC=C1C=C2</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr"/>
+      <c r="H983" t="inlineStr"/>
+      <c r="I983" t="n">
+        <v>0.07981551710790846</v>
+      </c>
+      <c r="J983" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K983" t="inlineStr"/>
+    </row>
+    <row r="984">
+      <c r="A984" s="1" t="n">
+        <v>982</v>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0765.png</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr"/>
+      <c r="D984" t="inlineStr"/>
+      <c r="E984" t="inlineStr"/>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)N1CCc2cccc(Nc3nc(Nc4ccc(N5CCC(N6CCN(C(=O)CC7CN(c8ccc9c(c8)C(=O)N(C8CCC(=O)NC8=O)C9=O)C7)CC6)CC5)c(F)c4)nc4[nH]ccc34)c21</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr"/>
+      <c r="H984" t="inlineStr"/>
+      <c r="I984" t="n">
+        <v>0.7871255895387682</v>
+      </c>
+      <c r="J984" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K984" t="inlineStr"/>
+    </row>
+    <row r="985">
+      <c r="A985" s="1" t="n">
+        <v>983</v>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0769.png</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr"/>
+      <c r="D985" t="inlineStr"/>
+      <c r="E985" t="inlineStr"/>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>CCC(=O)N1CC(N2CC34=C5C6=C7C89%10=C%11%12C=CC(COCCOCCNC%13=CC=CC%14=C%13C(=O)N(C%13CCC(=O)NC%13=O)C%14=O)OCCN5(C=36C=C8(C=C4)C7%1193=CC(O)=CC%124=C%103C=CC=C4)C2(=O)=O)C1</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr"/>
+      <c r="H985" t="inlineStr"/>
+      <c r="I985" t="n">
+        <v>0.07879531184031321</v>
+      </c>
+      <c r="J985" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K985" t="inlineStr"/>
+    </row>
+    <row r="986">
+      <c r="A986" s="1" t="n">
+        <v>984</v>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0781.png</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr"/>
+      <c r="D986" t="inlineStr"/>
+      <c r="E986" t="inlineStr"/>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr"/>
+      <c r="H986" t="inlineStr"/>
+      <c r="I986" t="n">
+        <v>0.8524732282301815</v>
+      </c>
+      <c r="J986" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K986" t="inlineStr"/>
+    </row>
+    <row r="987">
+      <c r="A987" s="1" t="n">
+        <v>985</v>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0801.png</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr"/>
+      <c r="D987" t="inlineStr"/>
+      <c r="E987" t="inlineStr"/>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>O=C1[CH]NC234CCCCC2C32(CCCCC2)NC(C(=O)NC2=CC=C(C=C2)C(=O)NCCCCNC23=C5C(=O)N67C(=O)C5(=CC=C2)C=325=C(C=CC=C2C(=O)N(C2CCC3(=O)N8C(=O)C69CCC8(=O)N3C29=O)C75=O)NCCCCNC(=O)C2=CC=C(C=C2)N1)C(C1=CC=CC(Cl)=C1F)[CH]41C(=O)NC2=CC(Cl)=CC=C21</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr"/>
+      <c r="H987" t="inlineStr"/>
+      <c r="I987" t="n">
+        <v>0.005990953972428866</v>
+      </c>
+      <c r="J987" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K987" t="inlineStr"/>
+    </row>
+    <row r="988">
+      <c r="A988" s="1" t="n">
+        <v>986</v>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0817.png</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr"/>
+      <c r="D988" t="inlineStr"/>
+      <c r="E988" t="inlineStr"/>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cc3cn(C4CC5(CCN(C(=O)C6(C)CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)nc3cc2OC)n1.[I-37] |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr"/>
+      <c r="H988" t="inlineStr"/>
+      <c r="I988" t="n">
+        <v>0.7887588467909072</v>
+      </c>
+      <c r="J988" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K988" t="inlineStr"/>
+    </row>
+    <row r="989">
+      <c r="A989" s="1" t="n">
+        <v>987</v>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0821.png</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr"/>
+      <c r="D989" t="inlineStr"/>
+      <c r="E989" t="inlineStr"/>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>COc1cc2nn(C3CC4(CCN(C(=O)C5CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)CC4)C3)cc2cc1NC(=O)c1cnn2ccc(NCC3CO3)nc12</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr"/>
+      <c r="H989" t="inlineStr"/>
+      <c r="I989" t="n">
+        <v>0.7682720613065266</v>
+      </c>
+      <c r="J989" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K989" t="inlineStr"/>
+    </row>
+    <row r="990">
+      <c r="A990" s="1" t="n">
+        <v>988</v>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0825.png</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr"/>
+      <c r="D990" t="inlineStr"/>
+      <c r="E990" t="inlineStr"/>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr"/>
+      <c r="H990" t="inlineStr"/>
+      <c r="I990" t="n">
+        <v>0.8323601608930322</v>
+      </c>
+      <c r="J990" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K990" t="inlineStr"/>
+    </row>
+    <row r="991">
+      <c r="A991" s="1" t="n">
+        <v>989</v>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0829.png</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr"/>
+      <c r="D991" t="inlineStr"/>
+      <c r="E991" t="inlineStr"/>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>NC(C(=O)NC1CCC(C2(=O)=O=S(=O)(CCC#CC3=C4CN(C5CCC(=O)NC5=O)C(=O)(N5(C6CCC(=O)NC6=O)CC6=C(C#CCCS(=O)(=O)NC(=O)C7CCC(NC(=O)C8NC9(CCCCC9)C8C8=CC=CC(Cl)=C8F)CC7)C=CC=C6C5=O)C4=CC=C3)N2)CC1)C(C1C(=O)NC2=CC(Cl)=CC=C12)C1=CC=CC(Cl)=C1F</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr"/>
+      <c r="H991" t="inlineStr"/>
+      <c r="I991" t="n">
+        <v>0.378584422772024</v>
+      </c>
+      <c r="J991" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K991" t="inlineStr"/>
+    </row>
+    <row r="992">
+      <c r="A992" s="1" t="n">
+        <v>990</v>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0833.png</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr"/>
+      <c r="D992" t="inlineStr"/>
+      <c r="E992" t="inlineStr"/>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)NCC(=O)Nc2nc(-c3cccc(-c4ccnc(C5(C(=O)N6CCC(C7CCN(C(=O)COc8cccc9c8C(=O)N(C8CCC(=O)NC8=O)C9=O)CC7)CC6)CC5)c4)c3)co2)c1</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr"/>
+      <c r="H992" t="inlineStr"/>
+      <c r="I992" t="n">
+        <v>0.83145171661569</v>
+      </c>
+      <c r="J992" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K992" t="inlineStr"/>
+    </row>
+    <row r="993">
+      <c r="A993" s="1" t="n">
+        <v>991</v>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_0/rb_0837.png</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr"/>
+      <c r="D993" t="inlineStr"/>
+      <c r="E993" t="inlineStr"/>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>O=C(C1CCCC1)N1CCN2(CC1)C134=NC=NC56=C(F)C78=C(Cl)C=C519C15=C7(F)C7(=C(Cl)C=C613C29(=NC=N5)N41CCN(C(=O)C2CCCC2)CC1)C1=C(F)C=CC=C1OCCCCCCCN1CCC23C4=C5CN6C9%10CCC%11(=O)N%12C%13(=O)CCC(N%14CC(=C2C2%15(CCN%16(CCCCCCCOC%17=CC=CC(F)=C%1778)C7C2C%16C7%15)C3C1)C5(=CC(F)=C4)C6%14=O)(C%129=O)C%10(=O)N%11%13</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr"/>
+      <c r="H993" t="inlineStr"/>
+      <c r="I993" t="n">
+        <v>0.002066349661684765</v>
+      </c>
+      <c r="J993" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K993" t="inlineStr"/>
+    </row>
+    <row r="994">
+      <c r="A994" s="1" t="n">
+        <v>992</v>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0602.png</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr"/>
+      <c r="D994" t="inlineStr"/>
+      <c r="E994" t="inlineStr"/>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)NC(COCc2ccc(C(=O)N34CC56(CCN(CCCNc7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC5)C3C46)cc2)C(=O)Nn2ncc(-c3ccccc3)n2)c1</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr"/>
+      <c r="H994" t="inlineStr"/>
+      <c r="I994" t="n">
+        <v>0.8328216021266067</v>
+      </c>
+      <c r="J994" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K994" t="inlineStr"/>
+    </row>
+    <row r="995">
+      <c r="A995" s="1" t="n">
+        <v>993</v>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0610.png</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr"/>
+      <c r="D995" t="inlineStr"/>
+      <c r="E995" t="inlineStr"/>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>COc1cc2nn(C3CC4(CCN(C(=O)C5CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)CC4)C3)cc2cc1NC(=O)c1cnn2ccc(N3C[C@H]4C[C@@H]3CO4)nc12</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr"/>
+      <c r="H995" t="inlineStr"/>
+      <c r="I995" t="n">
+        <v>0.8120581362047716</v>
+      </c>
+      <c r="J995" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K995" t="inlineStr"/>
+    </row>
+    <row r="996">
+      <c r="A996" s="1" t="n">
+        <v>994</v>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0614.png</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr"/>
+      <c r="D996" t="inlineStr"/>
+      <c r="E996" t="inlineStr"/>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr"/>
+      <c r="H996" t="inlineStr"/>
+      <c r="I996" t="n">
+        <v>0.9028836966822654</v>
+      </c>
+      <c r="J996" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K996" t="inlineStr"/>
+    </row>
+    <row r="997">
+      <c r="A997" s="1" t="n">
+        <v>995</v>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0622.png</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr"/>
+      <c r="D997" t="inlineStr"/>
+      <c r="E997" t="inlineStr"/>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>CC1(C)CCC2(CC1)N[C@@H](C(=O)Nc1ccc(C(=O)NCCOCCOCCNc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)cc1)[C@H](c1cccc(Cl)c1F)[C@]21C(=O)Nc2cc(Cl)ccc21</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr"/>
+      <c r="H997" t="inlineStr"/>
+      <c r="I997" t="n">
+        <v>0.7355669911516756</v>
+      </c>
+      <c r="J997" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K997" t="inlineStr"/>
+    </row>
+    <row r="998">
+      <c r="A998" s="1" t="n">
+        <v>996</v>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0638.png</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr"/>
+      <c r="D998" t="inlineStr"/>
+      <c r="E998" t="inlineStr"/>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr"/>
+      <c r="H998" t="inlineStr"/>
+      <c r="I998" t="n">
+        <v>0.8530306172357077</v>
+      </c>
+      <c r="J998" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K998" t="inlineStr"/>
+    </row>
+    <row r="999">
+      <c r="A999" s="1" t="n">
+        <v>997</v>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0694.png</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr"/>
+      <c r="D999" t="inlineStr"/>
+      <c r="E999" t="inlineStr"/>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)NCC(=O)Nc2nc(-c3cccc(-c4ccnc(N5CCN(C(=O)CCOCCOCCNc6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)c4)c3)co2)c1</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr"/>
+      <c r="H999" t="inlineStr"/>
+      <c r="I999" t="n">
+        <v>0.786679615045047</v>
+      </c>
+      <c r="J999" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K999" t="inlineStr"/>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="1" t="n">
+        <v>998</v>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0706.png</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr"/>
+      <c r="D1000" t="inlineStr"/>
+      <c r="E1000" t="inlineStr"/>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>C=C(Cl)C(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCCCCCCN4CCC(c5cc(F)cc6c5CN(C5CCC(=O)NC5=O)C6=O)C4)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr"/>
+      <c r="H1000" t="inlineStr"/>
+      <c r="I1000" t="n">
+        <v>0.7494563998975018</v>
+      </c>
+      <c r="J1000" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1000" t="inlineStr"/>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0734.png</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr"/>
+      <c r="D1001" t="inlineStr"/>
+      <c r="E1001" t="inlineStr"/>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>*c1cccc(C(=O)Nc2cn(C3CC4(CCN(c5cnn(C6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=S)NC7=O)C8=O)CC6)c5)CC4)C3)nc2/C=C/OC)n1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr"/>
+      <c r="H1001" t="inlineStr"/>
+      <c r="I1001" t="n">
+        <v>0.8234628517415399</v>
+      </c>
+      <c r="J1001" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1001" t="inlineStr"/>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0758.png</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr"/>
+      <c r="D1002" t="inlineStr"/>
+      <c r="E1002" t="inlineStr"/>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>O=C1[CH]NC23(CCCCC2)C2(C(=O)NC4=CC(Cl)=CC=C42)C324(CCCCC2)NC(C(=O)NC2=CC=C(N=C2)C(=O)NCCCC#CC2=C35CN6(C(=O)C3=CC=C2)C23CCC7(=O)N(C2=O)C2(=O)CCC(N8CC9=C(C#CCCCNC(=O)C%10=CC=C(C=N%10)N1)C=CC=C95C86=O)C3(=O)N27)C4C1=CC=CC(Cl)=C1F</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr"/>
+      <c r="H1002" t="inlineStr"/>
+      <c r="I1002" t="n">
+        <v>0.03900469498840138</v>
+      </c>
+      <c r="J1002" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1002" t="inlineStr"/>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="1" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0774.png</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr"/>
+      <c r="D1003" t="inlineStr"/>
+      <c r="E1003" t="inlineStr"/>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>CCC(=O)N1CCN(c2ncnc3c(Cl)c(-c4c(F)cccc4OCCCCCCCCN4CCC(c5cc(F)cc6c5CN(C5CCC(=O)NC5=O)C6=O)CC4)c(F)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr"/>
+      <c r="H1003" t="inlineStr"/>
+      <c r="I1003" t="n">
+        <v>0.5676500385505983</v>
+      </c>
+      <c r="J1003" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1003" t="inlineStr"/>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="1" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0782.png</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr"/>
+      <c r="D1004" t="inlineStr"/>
+      <c r="E1004" t="inlineStr"/>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)N1CCc2cccc(Nc3nc(Nc4ccc(N5CCC(N6CCN(CCC7CCN(c8ccc9c(c8)C(=O)N(C8CCC(=O)NC8=O)C9=O)CC7)CC6)CC5)c(F)c4)nc4[nH]ccc34)c21</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr"/>
+      <c r="H1004" t="inlineStr"/>
+      <c r="I1004" t="n">
+        <v>0.841321794995898</v>
+      </c>
+      <c r="J1004" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1004" t="inlineStr"/>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="1" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0802.png</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr"/>
+      <c r="D1005" t="inlineStr"/>
+      <c r="E1005" t="inlineStr"/>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>O=C(COc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O)NCCCN1CCN(c2ccc(C(=O)N3CCC[C@@H](Nc4ncc(Cl)c(-c5c[nH]c6ccccc56)n4)C3)cc2)CC1</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr"/>
+      <c r="H1005" t="inlineStr"/>
+      <c r="I1005" t="n">
+        <v>0.5595300768024545</v>
+      </c>
+      <c r="J1005" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1005" t="inlineStr"/>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="1" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0806.png</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr"/>
+      <c r="D1006" t="inlineStr"/>
+      <c r="E1006" t="inlineStr"/>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)N1CCc2cccc(Nc3nc(Nc4ccc(N5CCC(N6CCN(C(=O)CCN7CCN(c8ccc9c(c8)C(=O)N(C8CCC(=O)NC8=O)C9=O)CC7)CC6)CC5)c(F)c4)nc4[nH]ccc34)c21</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr"/>
+      <c r="H1006" t="inlineStr"/>
+      <c r="I1006" t="n">
+        <v>0.6684700189600594</v>
+      </c>
+      <c r="J1006" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1006" t="inlineStr"/>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="1" t="n">
+        <v>1005</v>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0814.png</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr"/>
+      <c r="D1007" t="inlineStr"/>
+      <c r="E1007" t="inlineStr"/>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>C=C12C3(C4=C(F)C=CC=C4OCCCCCCCN4CCC(C5=CC(F)=CC6=C5CN(C5CCC(=O)NC5=O)C6=O)CC4)=C(Cl)C=C456C7=N8=C4(=NC=N4C159=C3(F)=C4269N=C8)N71CCN(C(=O)C2COC2)CC1</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr"/>
+      <c r="H1007" t="inlineStr"/>
+      <c r="I1007" t="n">
+        <v>0.3226807894598234</v>
+      </c>
+      <c r="J1007" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1007" t="inlineStr"/>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="1" t="n">
+        <v>1006</v>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0818.png</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr"/>
+      <c r="D1008" t="inlineStr"/>
+      <c r="E1008" t="inlineStr"/>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr"/>
+      <c r="H1008" t="inlineStr"/>
+      <c r="I1008" t="n">
+        <v>0.8812746277516728</v>
+      </c>
+      <c r="J1008" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1008" t="inlineStr"/>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="1" t="n">
+        <v>1007</v>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0846.png</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr"/>
+      <c r="D1009" t="inlineStr"/>
+      <c r="E1009" t="inlineStr"/>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)n1ccc(C(=O)N[C@@H](CCOCCCC(=O)N2CCC3(CC2)CC(Oc2ccc4c(c2)C(=O)N(C2CCC(=O)NC2=O)C4=O)C3)C(=O)Nc2nc(-c3ccccc3)cs2)c1</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr"/>
+      <c r="H1009" t="inlineStr"/>
+      <c r="I1009" t="n">
+        <v>0.7429811127317307</v>
+      </c>
+      <c r="J1009" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1009" t="inlineStr"/>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="1" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_1/rb_0850.png</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr"/>
+      <c r="D1010" t="inlineStr"/>
+      <c r="E1010" t="inlineStr"/>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr"/>
+      <c r="H1010" t="inlineStr"/>
+      <c r="I1010" t="n">
+        <v>0.8794586520865699</v>
+      </c>
+      <c r="J1010" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1010" t="inlineStr"/>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="1" t="n">
+        <v>1009</v>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0615.png</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr"/>
+      <c r="D1011" t="inlineStr"/>
+      <c r="E1011" t="inlineStr"/>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>O=C(NC1CC[CH]2(C=CC3=CC=CC45=C36CN3(C4=O)C47CCC8(=O)N(C4=O)C4(=O)CCC(N9CC%10=C(C=CC=C%106C=C2)C953=O)C7(=O)N48)CC1)C1=CC=C(NC(=O)C([CH]C2=CC=CC(Cl)=C2F)NC2CCCCC2)C=C1</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr"/>
+      <c r="H1011" t="inlineStr"/>
+      <c r="I1011" t="n">
+        <v>0.2527255278901379</v>
+      </c>
+      <c r="J1011" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1011" t="inlineStr"/>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="1" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0635.png</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr"/>
+      <c r="D1012" t="inlineStr"/>
+      <c r="E1012" t="inlineStr"/>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>O=C1NCCOCCOCCOCCCC2=C3CN4C5CCC6(=O)N7C(=O)C8(CCC7(=O)N6C58=O)N56CC7(=C(C=CC=C7C5=O)CCCOCCOCCOCCNC(=O)C57=CC=C(C=C5)NC(=O)[CH]58NC9(CCCCC9)(C9CCCCC9%10NC(C(=O)NC9=CC=C1C7=C9)[CH]%105C1=CC=CC(Cl)=C1F)C8C1=CC=CC(Cl)=C1F)C3(=CC=C2)C46=O</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr"/>
+      <c r="H1012" t="inlineStr"/>
+      <c r="I1012" t="n">
+        <v>0.01467610075527621</v>
+      </c>
+      <c r="J1012" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1012" t="inlineStr"/>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="1" t="n">
+        <v>1011</v>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0643.png</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr"/>
+      <c r="D1013" t="inlineStr"/>
+      <c r="E1013" t="inlineStr"/>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr"/>
+      <c r="H1013" t="inlineStr"/>
+      <c r="I1013" t="n">
+        <v>0.8806932544269596</v>
+      </c>
+      <c r="J1013" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1013" t="inlineStr"/>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="1" t="n">
+        <v>1012</v>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0651.png</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr"/>
+      <c r="D1014" t="inlineStr"/>
+      <c r="E1014" t="inlineStr"/>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3c(NCCOCCNC(=O)c4ccc(NC(=O)[C@@H]5NC6(CCCCC6)[C@@]6(C(=O)Nc7cc(Cl)ccc76)[C@H]5c5cccc(Cl)c5F)cc4)cccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr"/>
+      <c r="H1014" t="inlineStr"/>
+      <c r="I1014" t="n">
+        <v>0.7884547530805567</v>
+      </c>
+      <c r="J1014" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1014" t="inlineStr"/>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="1" t="n">
+        <v>1013</v>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0667.png</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr"/>
+      <c r="D1015" t="inlineStr"/>
+      <c r="E1015" t="inlineStr"/>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr"/>
+      <c r="H1015" t="inlineStr"/>
+      <c r="I1015" t="n">
+        <v>0.8194684027905188</v>
+      </c>
+      <c r="J1015" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1015" t="inlineStr"/>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="1" t="n">
+        <v>1014</v>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0687.png</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr"/>
+      <c r="D1016" t="inlineStr"/>
+      <c r="E1016" t="inlineStr"/>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)C3=C(C2=O)C(CCCOCCOCCOCCNC(=O)C2=CC=C(NC(=O)[CH]45NC67(CCCCC6)C68(C(=O)NC9=CC(Cl)=CC=C96)[CH]469C4%10=CC=CC(Cl)=C4%11(F)=C4(Cl)=C(F)C%116(=CC=C4)[CH]%105789)C=C2)=CC=C3)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr"/>
+      <c r="H1016" t="inlineStr"/>
+      <c r="I1016" t="n">
+        <v>0.3222829749730065</v>
+      </c>
+      <c r="J1016" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1016" t="inlineStr"/>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="1" t="n">
+        <v>1015</v>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0699.png</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr"/>
+      <c r="D1017" t="inlineStr"/>
+      <c r="E1017" t="inlineStr"/>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>C=C(Cl)C(=O)N1CCN(c2ncnc3c(F)c(-c4c(F)cccc4OCCc4ccc(CCN5CCC(c6cc(F)cc7c6CN(C6CCC(=O)NC6=O)C7=O)CC5)cc4)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr"/>
+      <c r="H1017" t="inlineStr"/>
+      <c r="I1017" t="n">
+        <v>0.5624541874021034</v>
+      </c>
+      <c r="J1017" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1017" t="inlineStr"/>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="1" t="n">
+        <v>1016</v>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0707.png</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr"/>
+      <c r="D1018" t="inlineStr"/>
+      <c r="E1018" t="inlineStr"/>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>O=C1NCCCOCCCCOCCCNC2=C3=C45=CC=C6=C7=CC(=CC=C7NC(=O)[CH]7(NC8(CCCCC8)C7C7=CC=CC(Cl)=C7F)[CH]7(C8=CC=CC(Cl)=C8F)C(NC78CCCCC8)C(=O)NC7=CC=C1C=C7=C1(=C3)C3=C2C27(=O)N8C9%10CCC(=O)N%11C(=O)CCC(C9)(C%11%10=O)N29C(=O)C47=C61(C9=O)C38=O)C(=O)NCCCOCCCCOCCCN5</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr"/>
+      <c r="H1018" t="inlineStr"/>
+      <c r="I1018" t="n">
+        <v>0.01418593010142592</v>
+      </c>
+      <c r="J1018" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1018" t="inlineStr"/>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="1" t="n">
+        <v>1017</v>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0739.png</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr"/>
+      <c r="D1019" t="inlineStr"/>
+      <c r="E1019" t="inlineStr"/>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>COc1cc2nn(C3CC4(CCN(C(=O)C5CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)CC4)C3)cc2cc1NC(=O)c1cnn2ccc(N3CCN(C)CC3)nc12</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr"/>
+      <c r="H1019" t="inlineStr"/>
+      <c r="I1019" t="n">
+        <v>0.8231395689731064</v>
+      </c>
+      <c r="J1019" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1019" t="inlineStr"/>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="1" t="n">
+        <v>1018</v>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0743.png</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr"/>
+      <c r="D1020" t="inlineStr"/>
+      <c r="E1020" t="inlineStr"/>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>CCN1[C@@H](C(=O)NC23CCC(C(=O)NCCCCCc4cccc5c4CN(C4CCC(=O)NC4=O)C5=O)(CC2)CC3)[C@H](c2cccc(Cl)c2F)[C@]2(C(=O)Nc3cc(Cl)ccc32)C12CCCCC2</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr"/>
+      <c r="H1020" t="inlineStr"/>
+      <c r="I1020" t="n">
+        <v>0.7782155847020633</v>
+      </c>
+      <c r="J1020" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1020" t="inlineStr"/>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="1" t="n">
+        <v>1019</v>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0747.png</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr"/>
+      <c r="D1021" t="inlineStr"/>
+      <c r="E1021" t="inlineStr"/>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>O=C1NCCCC#CC2=C3CN4C5CCC6(=O)N7C(=O)C8(CCC7(=O)N6C58=O)N56CC78=C(C#CCCCNC(=O)C9=CC=C(C=C9)NC(=O)[CH]9%10NC%11(CCCCC%11)(C9C9=CC=NC(Cl)=C9F)C9%11(CCCCC9)NC(C(=O)NC9=CC=C1C=C9)[CH]%10%11C1=CC=NC(Cl)=C1F)(C=CC=C7C5=O)C2=CC=C38C46=O</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr"/>
+      <c r="H1021" t="inlineStr"/>
+      <c r="I1021" t="n">
+        <v>0.01802621974193853</v>
+      </c>
+      <c r="J1021" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1021" t="inlineStr"/>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="1" t="n">
+        <v>1020</v>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0767.png</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr"/>
+      <c r="D1022" t="inlineStr"/>
+      <c r="E1022" t="inlineStr"/>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr"/>
+      <c r="H1022" t="inlineStr"/>
+      <c r="I1022" t="n">
+        <v>0.8781762530893351</v>
+      </c>
+      <c r="J1022" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1022" t="inlineStr"/>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="1" t="n">
+        <v>1021</v>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0775.png</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr"/>
+      <c r="D1023" t="inlineStr"/>
+      <c r="E1023" t="inlineStr"/>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>O=C(NCCOCCOCCOCC12C3C4O15C1C(=CC=C6C78=C9C%10=CC=C7C67%11%12=C%106(C=CC=C7)C(=O)N7(C%11=O)C%10%11CCC%13(=O)N%14%15C%16(=O)CCC%17(N(C8%12=O)C976=O)C%10%14(=O)N%16%13C%17%11%15=O)O142C35)C1=CC=C(NC(=O)C2NC34(CCCCC3)C3567C(=O)NC8=CC(Cl)=CC=C83C453(C4CCCCC4)(C4=CC=C(Cl)C=C4NC63=O)[CH]27C2=CC=CC(Cl)=C2F)C=C1</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr"/>
+      <c r="H1023" t="inlineStr"/>
+      <c r="I1023" t="n">
+        <v>0.001682871493257713</v>
+      </c>
+      <c r="J1023" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1023" t="inlineStr"/>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="1" t="n">
+        <v>1022</v>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0779.png</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr"/>
+      <c r="D1024" t="inlineStr"/>
+      <c r="E1024" t="inlineStr"/>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr"/>
+      <c r="H1024" t="inlineStr"/>
+      <c r="I1024" t="n">
+        <v>0.7949348056530242</v>
+      </c>
+      <c r="J1024" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1024" t="inlineStr"/>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="1" t="n">
+        <v>1023</v>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0803.png</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr"/>
+      <c r="D1025" t="inlineStr"/>
+      <c r="E1025" t="inlineStr"/>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>O=C1NC2CCC3(CCC4=C56CN7(C(=O)C5=CC=C4)C4CCC(=O)N(C(=O)CCCN5CC8=C(C=CC=C86C57)CCC5CCC(CC53)NC(=O)C3=CC=C(C=C3)NC(=O)C3NC56(CCCCC5)C57(CCCCC5)N[CH]5(C(=O)NC8=CC=C1C=C8)C(C1=CC=CC(Cl)=C1F)C1(=CC=CC(Cl)=C1F)[CH]35C671C(=O)NC3=CC(Cl)=CC=C31)C4=O)CC2</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr"/>
+      <c r="H1025" t="inlineStr"/>
+      <c r="I1025" t="n">
+        <v>0.02280567542778026</v>
+      </c>
+      <c r="J1025" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1025" t="inlineStr"/>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="1" t="n">
+        <v>1024</v>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0807.png</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr"/>
+      <c r="D1026" t="inlineStr"/>
+      <c r="E1026" t="inlineStr"/>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>C=C(Cl)C(=O)N1CCN(C2=NC=NC(C(F)=C3C4=C(F)C=CC=C45O4CCCCCCCN6(CCCCCCC4OC4=CC=CC(F)=C435)CCCC(C3=C4CN(C5CCC(=O)NC5=O)C(=O)C4=CC(F)=C3)C6)=C2)CC1</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr"/>
+      <c r="H1026" t="inlineStr"/>
+      <c r="I1026" t="n">
+        <v>0.03461780085019259</v>
+      </c>
+      <c r="J1026" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1026" t="inlineStr"/>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="1" t="n">
+        <v>1025</v>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_2/rb_0835.png</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr"/>
+      <c r="D1027" t="inlineStr"/>
+      <c r="E1027" t="inlineStr"/>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>[H]C([H])(F)[C@@H]1CCC(*Cc2cc(C(=O)NCc3cccc(CC(=O)NCCOCCOCCOCCOCC(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)NCc4ccc(-c5scnc5C)cc4)C(C)(C)C)c3)ncc2OC)CC1 |$;;;;;;;;10;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr"/>
+      <c r="H1027" t="inlineStr"/>
+      <c r="I1027" t="n">
+        <v>0.6151626213309682</v>
+      </c>
+      <c r="J1027" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1027" t="inlineStr"/>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="1" t="n">
+        <v>1026</v>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0620.png</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr"/>
+      <c r="D1028" t="inlineStr"/>
+      <c r="E1028" t="inlineStr"/>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3c(C#CCOCCOCCNC(=O)c4ccc(NC(=O)[C@@H]5NC6(CCCCC6)[C@@]6(C(=O)Nc7cc(Cl)ccc76)[C@H]5c5cccc(Cl)c5F)cc4)cccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr"/>
+      <c r="H1028" t="inlineStr"/>
+      <c r="I1028" t="n">
+        <v>0.7994476611793708</v>
+      </c>
+      <c r="J1028" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1028" t="inlineStr"/>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="1" t="n">
+        <v>1027</v>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0632.png</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr"/>
+      <c r="D1029" t="inlineStr"/>
+      <c r="E1029" t="inlineStr"/>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>O=C1CCC(NCC=CC23CCN4(CCCCCCCOC5=CC=CC(F)=C5C5=C(Cl)C=C6C(N7CCN(C(=O)C8CCOCC8)CC7)=NC=NC6=C5F)C5C2C4C53)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr"/>
+      <c r="H1029" t="inlineStr"/>
+      <c r="I1029" t="n">
+        <v>0.5798944448344608</v>
+      </c>
+      <c r="J1029" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1029" t="inlineStr"/>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="1" t="n">
+        <v>1028</v>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0636.png</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr"/>
+      <c r="D1030" t="inlineStr"/>
+      <c r="E1030" t="inlineStr"/>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)N1CCc2cccc(Nc3nc(Nc4ccc(N5CCC(N6CCN(CCC7CCN(c8ccc9c(c8)CN(C8CCC(=O)NC8=O)C9=O)CC7)CC6)CC5)c(F)c4)nc4[nH]ccc34)c21</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr"/>
+      <c r="H1030" t="inlineStr"/>
+      <c r="I1030" t="n">
+        <v>0.7984117524183872</v>
+      </c>
+      <c r="J1030" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1030" t="inlineStr"/>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="1" t="n">
+        <v>1029</v>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0644.png</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr"/>
+      <c r="D1031" t="inlineStr"/>
+      <c r="E1031" t="inlineStr"/>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3c(cc(F)cc3C3=CCN(CCCCCCCOc4cccc(F)c4-c4c(Cl)cc5c(N6CCN(C(=O)C7CCOC7)CC6)ncnc5c4F)CC3)C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr"/>
+      <c r="H1031" t="inlineStr"/>
+      <c r="I1031" t="n">
+        <v>0.5519905807838874</v>
+      </c>
+      <c r="J1031" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1031" t="inlineStr"/>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="1" t="n">
+        <v>1030</v>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0656.png</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr"/>
+      <c r="D1032" t="inlineStr"/>
+      <c r="E1032" t="inlineStr"/>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>CN1C(=O)C2=C(C=C(N3CC(CCCN4CCN(C5CCN(C6=C(F)C=C(NC=NC7=CC=CN7)C=C6)CC5)CC4)C3C34(CCCN5CCN(C6CCN(C7=C(F)C=C(NCN=CNC8=C9C(=CC=C8)CCN9S(C)(=O)=O)C=C7)CC6)CC5)CN(C5=CC6=C(C=C5)C(=O)N(C5CCC(=O)NC5=O)C6=O)(C3)C4)C=C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr"/>
+      <c r="H1032" t="inlineStr"/>
+      <c r="I1032" t="n">
+        <v>0.06422457521756057</v>
+      </c>
+      <c r="J1032" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1032" t="inlineStr"/>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="1" t="n">
+        <v>1031</v>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0660.png</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr"/>
+      <c r="D1033" t="inlineStr"/>
+      <c r="E1033" t="inlineStr"/>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>[H]C12CC34(C)CCC1(C)CCC15(C)C6CC27(C)CC3C(C)(CC7([H])C12(C)CCC1(C)C3=CC(=O)C(O)=C(C)C37(=CC=C15C62C)C=CC(=O)C(O)=C7C)C(=O)NCCOCCNC1=C2C(=O)N(C3CCC(=O)NC3=O)C(=O)C2(=CC=C1)C12=C(C=CC=C1C(=O)N(C1CCC(=O)NC1=O)C2=O)NCCOCCNC4=O</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr"/>
+      <c r="H1033" t="inlineStr"/>
+      <c r="I1033" t="n">
+        <v>0.01302467291585344</v>
+      </c>
+      <c r="J1033" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1033" t="inlineStr"/>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="1" t="n">
+        <v>1032</v>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0668.png</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr"/>
+      <c r="D1034" t="inlineStr"/>
+      <c r="E1034" t="inlineStr"/>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>COC1=CC(C(=O)NCCCOCCOCCOCCCNC2=CC=CC3=C2C(=O)N(C2CCC(=O)NC2=O)C3=O)=CC=C1C123=O=C(=O=1)(N2)[CH]31NC(CC(C)(C)C)C(C#N)(C2=CC=C(Cl)C=C2F)C1C1=CC=CC(Cl)=C1F</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr"/>
+      <c r="H1034" t="inlineStr"/>
+      <c r="I1034" t="n">
+        <v>0.6363292833406201</v>
+      </c>
+      <c r="J1034" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1034" t="inlineStr"/>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="1" t="n">
+        <v>1033</v>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0672.png</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr"/>
+      <c r="D1035" t="inlineStr"/>
+      <c r="E1035" t="inlineStr"/>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr"/>
+      <c r="H1035" t="inlineStr"/>
+      <c r="I1035" t="n">
+        <v>0.8691732288074623</v>
+      </c>
+      <c r="J1035" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1035" t="inlineStr"/>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="1" t="n">
+        <v>1034</v>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0680.png</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr"/>
+      <c r="D1036" t="inlineStr"/>
+      <c r="E1036" t="inlineStr"/>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>C=C(Cl)C(=O)N1C[C@H](C(=O)N(CCCCCCCN2CCC(c3cc(F)cc4c3CN(C3CCC(=O)NC3=O)C4=O)CC2)c2cnc3c(F)c(-c4c(O)cccc4F)c(Cl)cc3c2)NC[C@H]1C</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr"/>
+      <c r="H1036" t="inlineStr"/>
+      <c r="I1036" t="n">
+        <v>0.7367263661583464</v>
+      </c>
+      <c r="J1036" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1036" t="inlineStr"/>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="1" t="n">
+        <v>1035</v>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0700.png</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr"/>
+      <c r="D1037" t="inlineStr"/>
+      <c r="E1037" t="inlineStr"/>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)C3=C(C2=O)C2=CC=C3NCCCOCCOCCOCCCNC(=O)C3=CC=C(NC(=O)[CH]45N6C789%10%11C%12CCCC7C%12687%13%14(CCCCC7)C967(C(=O)NC8=CC(Cl)=CC=C86)[CH]4%10%136C4(=CC=CC(Cl)=C4F)[CH]57%11%14C64=CC=CC(Cl)=C4F)N=2=C3)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr"/>
+      <c r="H1037" t="inlineStr"/>
+      <c r="I1037" t="n">
+        <v>0.02085019847168814</v>
+      </c>
+      <c r="J1037" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1037" t="inlineStr"/>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="1" t="n">
+        <v>1036</v>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0716.png</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr"/>
+      <c r="D1038" t="inlineStr"/>
+      <c r="E1038" t="inlineStr"/>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)N1CCc2cccc(Nc3nc(Nc4ccc(N5CCC(N6CCN(CCC7CCN(c8ccc9c(c8)C(=O)N(C8CCC(=O)NC8=O)C9=O)CC7)CC6)CC5)c(F)c4)ncc3Cl)c21</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr"/>
+      <c r="H1038" t="inlineStr"/>
+      <c r="I1038" t="n">
+        <v>0.8292670431032181</v>
+      </c>
+      <c r="J1038" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1038" t="inlineStr"/>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="1" t="n">
+        <v>1037</v>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0724.png</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr"/>
+      <c r="D1039" t="inlineStr"/>
+      <c r="E1039" t="inlineStr"/>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr"/>
+      <c r="H1039" t="inlineStr"/>
+      <c r="I1039" t="n">
+        <v>0.721161816320262</v>
+      </c>
+      <c r="J1039" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1039" t="inlineStr"/>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="1" t="n">
+        <v>1038</v>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0740.png</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr"/>
+      <c r="D1040" t="inlineStr"/>
+      <c r="E1040" t="inlineStr"/>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>O=C1CCC(NCC=CC23CCN4(CCCCCCCOC5=CC=CC(F)=C5C5=C(Cl)C=C6C(N7CCN(C(=O)CC8CC8)CC7)=NC=NC6=C5F)C5C2C4C53)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr"/>
+      <c r="H1040" t="inlineStr"/>
+      <c r="I1040" t="n">
+        <v>0.564156320475762</v>
+      </c>
+      <c r="J1040" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1040" t="inlineStr"/>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="1" t="n">
+        <v>1039</v>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0744.png</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr"/>
+      <c r="D1041" t="inlineStr"/>
+      <c r="E1041" t="inlineStr"/>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>*C1=NC(C(=O)O=C2NC3=CN(C4CC5(CCC(C(=O)N6CCN(C7=CC=C8C(=O)N(C9CCC(=O)NC9=O)C(=O)C8=C7)CC6)CC5)C4)N=C3C=C2OC)=CC=C1 |$CF3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr"/>
+      <c r="H1041" t="inlineStr"/>
+      <c r="I1041" t="n">
+        <v>0.6245877031717919</v>
+      </c>
+      <c r="J1041" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1041" t="inlineStr"/>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="1" t="n">
+        <v>1040</v>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0752.png</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr"/>
+      <c r="D1042" t="inlineStr"/>
+      <c r="E1042" t="inlineStr"/>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]CC1CN(C2=C3C=C(Cl)C(C4=C(F)C=CC=C4OCCC4CCC(CCN5CCC(C6=CC(F)=CC7=C6C=N(C6CCC(=O)NC6=O)C7=O)CC5)CC4)=C(F)C3=NC=N2)CCN1C(=O)C(=C)Cl</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr"/>
+      <c r="H1042" t="inlineStr"/>
+      <c r="I1042" t="n">
+        <v>0.8081692353983084</v>
+      </c>
+      <c r="J1042" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1042" t="inlineStr"/>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="1" t="n">
+        <v>1041</v>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0760.png</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr"/>
+      <c r="D1043" t="inlineStr"/>
+      <c r="E1043" t="inlineStr"/>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr"/>
+      <c r="H1043" t="inlineStr"/>
+      <c r="I1043" t="n">
+        <v>0.9004938391981899</v>
+      </c>
+      <c r="J1043" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1043" t="inlineStr"/>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="1" t="n">
+        <v>1042</v>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0764.png</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr"/>
+      <c r="D1044" t="inlineStr"/>
+      <c r="E1044" t="inlineStr"/>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>O=C1NCCOCCNC2=C3=C45=CC=CC67=C48C(=O)N4(C6=O)C6CCC(=O)N(C(=O)CCCN9C(=O)C(=C2C984=O)C7(=C3)=C2=CC1=CC=C2NC(=O)C1NC2(CCCCC2)C2(C(=O)NC3=CC(Cl)=CC=C32)[CH]1(C1=CC=CC(Cl)=C1F)[CH]1(NC2(CCCCC2)C1C1=CC=CC(Cl)=C1F)C(=O)NC1=CC=C(C=C1)C(=O)NCCOCCN5)C6=O</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr"/>
+      <c r="H1044" t="inlineStr"/>
+      <c r="I1044" t="n">
+        <v>0.03925627915029682</v>
+      </c>
+      <c r="J1044" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1044" t="inlineStr"/>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="1" t="n">
+        <v>1043</v>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0768.png</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr"/>
+      <c r="D1045" t="inlineStr"/>
+      <c r="E1045" t="inlineStr"/>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr"/>
+      <c r="H1045" t="inlineStr"/>
+      <c r="I1045" t="n">
+        <v>0.8385258629935995</v>
+      </c>
+      <c r="J1045" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1045" t="inlineStr"/>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="1" t="n">
+        <v>1044</v>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0784.png</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr"/>
+      <c r="D1046" t="inlineStr"/>
+      <c r="E1046" t="inlineStr"/>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)C3=C(C2=O)C(NCCCOCCOCCOCCCNCCCNC(=O)C24=CC=C5(NC(=O)C6NC789(CCCCC7)C7C8%10%11%12C6(C6=CC=CC(Cl)=C6F)C79%1068C7(=O)NC9%10%13%14%15%16=C%17C(Cl)=CC=C69%18%19=C6=C%118%109%20=CC=C(Cl)C=%138=C%189%14%10%11=C%15(C(Cl)=C6)C=8%17%19%20%106C%12(=O)N7%116%16)C6=C2=C5=C=64)=CC=C3)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr"/>
+      <c r="H1046" t="inlineStr"/>
+      <c r="I1046" t="n">
+        <v>0.0002059176871838343</v>
+      </c>
+      <c r="J1046" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1046" t="inlineStr"/>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="1" t="n">
+        <v>1045</v>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0788.png</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr"/>
+      <c r="D1047" t="inlineStr"/>
+      <c r="E1047" t="inlineStr"/>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr"/>
+      <c r="H1047" t="inlineStr"/>
+      <c r="I1047" t="n">
+        <v>0.8627293950043126</v>
+      </c>
+      <c r="J1047" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1047" t="inlineStr"/>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="1" t="n">
+        <v>1046</v>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0796.png</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr"/>
+      <c r="D1048" t="inlineStr"/>
+      <c r="E1048" t="inlineStr"/>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>COc1cc(N2CCC(N3CCN(CCC4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)CC3)CC2)c(C)cc1Nc1ncc(Br)c(Nc2cccc3c2N(S(C)(=O)=O)CC3)n1</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr"/>
+      <c r="H1048" t="inlineStr"/>
+      <c r="I1048" t="n">
+        <v>0.7211214174839992</v>
+      </c>
+      <c r="J1048" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1048" t="inlineStr"/>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="1" t="n">
+        <v>1047</v>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0832.png</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr"/>
+      <c r="D1049" t="inlineStr"/>
+      <c r="E1049" t="inlineStr"/>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>CS(=O)(=O)N1CCC2=CC=CC(NC3=NC(NC4=C5OCCC5=C(NCCCN5CCN(CCCC67CN(C8=CC9=C(C=C8)C(=O)N(C8CCC(=O)NC8=O)C9=O)(C6)C7)CC5)C=C4)=NC=C3Cl)=C21</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr"/>
+      <c r="H1049" t="inlineStr"/>
+      <c r="I1049" t="n">
+        <v>0.7991494141802596</v>
+      </c>
+      <c r="J1049" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1049" t="inlineStr"/>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="1" t="n">
+        <v>1048</v>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T163050_3/rb_0836.png</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr"/>
+      <c r="D1050" t="inlineStr"/>
+      <c r="E1050" t="inlineStr"/>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>CC1(C(=O)NCCCOCCOCCOCCCNC(=O)COC2=CC=CC3C(=O)N(C4CCC(=O)NC4=O)C(=O)C23)CCC2(C)(NC(=O)C3N4CCCCCCC45(C)C4(C(=O)NC6=CC(Cl)=CC=C64)[CH]35C3=CC=CC(Cl)=C3F)CC12</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr"/>
+      <c r="H1050" t="inlineStr"/>
+      <c r="I1050" t="n">
+        <v>0.2173893225133658</v>
+      </c>
+      <c r="J1050" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1050" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1050"/>
+  <dimension ref="A1:K1128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30901,6 +30901,2268 @@
       </c>
       <c r="K1050" t="inlineStr"/>
     </row>
+    <row r="1051">
+      <c r="A1051" s="1" t="n">
+        <v>1049</v>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0855.png</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr"/>
+      <c r="D1051" t="inlineStr"/>
+      <c r="E1051" t="inlineStr"/>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>CCC(=O)N[C@H](C(=O)N1C[C@H](O)C[C@H]1C(=O)NCc1ccc(-c2scnc2C)cc1)C(C)(C)C.CN1C2CCC1CN([C@H]1CC[C@H](c3cnc(N4C5CCC4CN(c4cc(-c6ccccc6O)nnc4N)C5)nc3)CC1)C2</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr"/>
+      <c r="H1051" t="inlineStr"/>
+      <c r="I1051" t="n">
+        <v>0.8168239538982957</v>
+      </c>
+      <c r="J1051" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1051" t="inlineStr"/>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="1" t="n">
+        <v>1050</v>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0899.png</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr"/>
+      <c r="D1052" t="inlineStr"/>
+      <c r="E1052" t="inlineStr"/>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>CN(C)c1ccc(-c2nc3ccc(O[C@@H]4C[C@@H](OC5CCN(CCCCCOc6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)C4)cc3s2)cc1</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr"/>
+      <c r="H1052" t="inlineStr"/>
+      <c r="I1052" t="n">
+        <v>0.76627460162594</v>
+      </c>
+      <c r="J1052" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1052" t="inlineStr"/>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="1" t="n">
+        <v>1051</v>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0907.png</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr"/>
+      <c r="D1053" t="inlineStr"/>
+      <c r="E1053" t="inlineStr"/>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CCN(CCCNc6cccc7c6C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr"/>
+      <c r="H1053" t="inlineStr"/>
+      <c r="I1053" t="n">
+        <v>0.8391898020767578</v>
+      </c>
+      <c r="J1053" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1053" t="inlineStr"/>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="1" t="n">
+        <v>1052</v>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0923.png</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr"/>
+      <c r="D1054" t="inlineStr"/>
+      <c r="E1054" t="inlineStr"/>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>CCS(=O)(=O)N1CC23(CC#N)(C=N2N32C=C3C(=N2)C24=CC5=C36C3=C78NC59(=C7=CC(=C3)(=N=968)C(=O)N3CCCN5CCN6CC5N5(CCCNC32=O)CCN(CC5)C2=CC3(=C(C=C2)C(=O)N(C2CCC(=O)NC2=O)C3=O)C2(=O)C3=C(C=CC6=C3)C(=O)N2C2CCC(=O)NC2=O)C=C4)C1</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr"/>
+      <c r="H1054" t="inlineStr"/>
+      <c r="I1054" t="n">
+        <v>2.948421274880749e-05</v>
+      </c>
+      <c r="J1054" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1054" t="inlineStr"/>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="1" t="n">
+        <v>1053</v>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0931.png</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr"/>
+      <c r="D1055" t="inlineStr"/>
+      <c r="E1055" t="inlineStr"/>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(C3=CC(OCCN4CCC(OC5CC(OC67=CC89=C%10C%11%12=N6=C%106=N=%117C(=C%126)N867C8%10CN(C%11=C(N)N=NC(C%12=CC=CC=C%12O)=C%11)CC6%11C7(C8)N%10%119)C5)CC4)=NO3)C(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr"/>
+      <c r="H1055" t="inlineStr"/>
+      <c r="I1055" t="n">
+        <v>0.01453556676922829</v>
+      </c>
+      <c r="J1055" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1055" t="inlineStr"/>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="1" t="n">
+        <v>1054</v>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0951.png</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr"/>
+      <c r="D1056" t="inlineStr"/>
+      <c r="E1056" t="inlineStr"/>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3C=[CH](O)CN3C(=O)C(NC(=O)C3CC4(C3)CC(N3CCC(OC56=NC=C789CCC%10CN(C%11=C(N)N=NC(C%12=CC=CC=C%12O)=C%11)CCC7C%10C87=C5=C9=C=76)CC3)C4)C(C)(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr"/>
+      <c r="H1056" t="inlineStr"/>
+      <c r="I1056" t="n">
+        <v>0.1775872552332483</v>
+      </c>
+      <c r="J1056" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1056" t="inlineStr"/>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="1" t="n">
+        <v>1055</v>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0955.png</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr"/>
+      <c r="D1057" t="inlineStr"/>
+      <c r="E1057" t="inlineStr"/>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NC(=O)N3CCC(N4CCC(C5=CN=C67N8C9%10CCC8(CN(C8=C(N)N=NC(C%11=CC=CC=C%11O)=C8)C9)(N6=C5)N%107C)CC4)CC3)C(C)(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr"/>
+      <c r="H1057" t="inlineStr"/>
+      <c r="I1057" t="n">
+        <v>0.6299941033496184</v>
+      </c>
+      <c r="J1057" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1057" t="inlineStr"/>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="1" t="n">
+        <v>1056</v>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0959.png</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr"/>
+      <c r="D1058" t="inlineStr"/>
+      <c r="E1058" t="inlineStr"/>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CCN(C6CN(Cc7ccc8c(c7)CN(C7CCC(=O)NC7=O)C8=O)C6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr"/>
+      <c r="H1058" t="inlineStr"/>
+      <c r="I1058" t="n">
+        <v>0.8379016918894014</v>
+      </c>
+      <c r="J1058" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1058" t="inlineStr"/>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="1" t="n">
+        <v>1057</v>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0963.png</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr"/>
+      <c r="D1059" t="inlineStr"/>
+      <c r="E1059" t="inlineStr"/>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>CCN(CC1CCN(C(=O)CCOCCCc2cccc3c2CN(C2CCC(=O)NC2=O)C3=O)CC1)c1ccc(Nc2nc(N3CCC[C@@H](N4CCN(C)C4=O)C3)cnc2C(N)=O)cc1</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr"/>
+      <c r="H1059" t="inlineStr"/>
+      <c r="I1059" t="n">
+        <v>0.5352415410999674</v>
+      </c>
+      <c r="J1059" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1059" t="inlineStr"/>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="1" t="n">
+        <v>1058</v>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0971.png</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr"/>
+      <c r="D1060" t="inlineStr"/>
+      <c r="E1060" t="inlineStr"/>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)[CH]34CC(O)CN3C(=O)C(C(C)(C)C)NC(=O)COCCOCCOCCOCCN4C(=O)CCCCCCCCOC3=CC(N4CCN(C=CC(=O)C5=C(O)C=CC=C5)CC4)=NC=C3)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1060" t="inlineStr"/>
+      <c r="H1060" t="inlineStr"/>
+      <c r="I1060" t="n">
+        <v>0.431321861336966</v>
+      </c>
+      <c r="J1060" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1060" t="inlineStr"/>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="1" t="n">
+        <v>1059</v>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_0995.png</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr"/>
+      <c r="D1061" t="inlineStr"/>
+      <c r="E1061" t="inlineStr"/>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>C#CC12=C(F)C=C3C45=C167C31=C243C62=C468N=C9N4%10=C2(C6(F)=C24N=C6%11%12N=C%13%14%15%16C2%17=C%10C94%13=C=%17(N%142CCCC4(C)OC9(C)(O)CCCN%15(C9)C42)N6%16=CO%11C2CCNCCCCNCCNC4=CC=C6C(=O)N(C9CCC(=O)NC9=O)C(=O)C6(=C4)C46=CC=C(C=C4C(=O)N(C4CCC(=O)NC4=O)C6=O)N4CCN(CC4)CC4CCN(CC4)CC24(CC4)CO%12)C738=CC=C51</t>
+        </is>
+      </c>
+      <c r="G1061" t="inlineStr"/>
+      <c r="H1061" t="inlineStr"/>
+      <c r="I1061" t="n">
+        <v>0.0003560045577562223</v>
+      </c>
+      <c r="J1061" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1061" t="inlineStr"/>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="1" t="n">
+        <v>1060</v>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1015.png</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr"/>
+      <c r="D1062" t="inlineStr"/>
+      <c r="E1062" t="inlineStr"/>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>COc1cc2nn(C3CC4(CCN(C(=O)C5CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5(F)F)CC4)C3)cc2cc1NC(=O)c1cccc(N2CCOCC2)n1.[I-56]</t>
+        </is>
+      </c>
+      <c r="G1062" t="inlineStr"/>
+      <c r="H1062" t="inlineStr"/>
+      <c r="I1062" t="n">
+        <v>0.7702902282237259</v>
+      </c>
+      <c r="J1062" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1062" t="inlineStr"/>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="1" t="n">
+        <v>1061</v>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1023.png</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr"/>
+      <c r="D1063" t="inlineStr"/>
+      <c r="E1063" t="inlineStr"/>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>*C1=CC=C(C=CC=C2C(=O)N(CC3=CC=C(OC4CC(OC5CCN(CCN67CCN89(C%10=CC=C%11%12C(=O)N(CCCC=O)(C(=O)C%11=C%10)C%12(=O)(N(C=O)C%10CCC%11=O=C%10(=O)N%11)C=CC=C8NCCNCCNCCCOCC[CH]OC=CC=CCNC(=O)C=CC=CC=CC=C[N+](=O)[O-])C8C6C9C87)CC5)C4)C=C3)C3=C2C=CC=C3)C=C1 |$O2N;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr"/>
+      <c r="H1063" t="inlineStr"/>
+      <c r="I1063" t="n">
+        <v>0.02773732895303984</v>
+      </c>
+      <c r="J1063" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1063" t="inlineStr"/>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="1" t="n">
+        <v>1062</v>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1051.png</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr"/>
+      <c r="D1064" t="inlineStr"/>
+      <c r="E1064" t="inlineStr"/>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>COC1=CN=C(C(=O)NCC2=CC(CC(=O)N(C)CCCCCCCOC3=CC=C4C(=O)N(C5CCC(=O)NC5=O)C(=O)C4=C3)=CC=C2)C=C1C12=C3C4=C567=C(=C1)C41(=C=53)(C6=C2)C2(CC2)C2CC271</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr"/>
+      <c r="H1064" t="inlineStr"/>
+      <c r="I1064" t="n">
+        <v>0.2803633502742973</v>
+      </c>
+      <c r="J1064" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1064" t="inlineStr"/>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="1" t="n">
+        <v>1063</v>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1055.png</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr"/>
+      <c r="D1065" t="inlineStr"/>
+      <c r="E1065" t="inlineStr"/>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(C3=CC(N4CCC(N5CCC(C6=CN=C(C7N8C9%10CCC78(CC9)CN(C7=C(N)N=NC(C8=CC=CC=C8O)=C7)C%10)N=C6)CC5)CC4)=NO3)C(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr"/>
+      <c r="H1065" t="inlineStr"/>
+      <c r="I1065" t="n">
+        <v>0.37958467030987</v>
+      </c>
+      <c r="J1065" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1065" t="inlineStr"/>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="1" t="n">
+        <v>1064</v>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1087.png</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr"/>
+      <c r="D1066" t="inlineStr"/>
+      <c r="E1066" t="inlineStr"/>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>CCS(=O)(=O)N1CC(CC#N)(n2cc(-c3nc(Nc4ccc(C(=O)NCCCN/C=C/C=C/CCC(=O)NC=O)cc4)nc4[nH]ccc34)cn2)C1</t>
+        </is>
+      </c>
+      <c r="G1066" t="inlineStr"/>
+      <c r="H1066" t="inlineStr"/>
+      <c r="I1066" t="n">
+        <v>0.2217930678080703</v>
+      </c>
+      <c r="J1066" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1066" t="inlineStr"/>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="1" t="n">
+        <v>1065</v>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1091.png</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr"/>
+      <c r="D1067" t="inlineStr"/>
+      <c r="E1067" t="inlineStr"/>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1067" t="inlineStr"/>
+      <c r="H1067" t="inlineStr"/>
+      <c r="I1067" t="n">
+        <v>0.02942782433461805</v>
+      </c>
+      <c r="J1067" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1067" t="inlineStr"/>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="1" t="n">
+        <v>1066</v>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_0/rb_1099.png</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr"/>
+      <c r="D1068" t="inlineStr"/>
+      <c r="E1068" t="inlineStr"/>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>C#CC1=C(F)C=CC2=C1C(C1=C(F)C34=NC567=NC89(N%10CCCC(C)(O)C%10)=C3%10(C#C)C(=N1)C48=C%10(N5=CO6CCCNCCCCN1CCN3CC1N1(CCN(CC1)C14=CC=C5(C(=O)N(C6CCC(=O)NC6=O)C(=O)C5=C1)C15=C4C3=CC=C1C(=O)N(C1CCC(=O)NC1=O)C5=O)CC1CCN(CC1)CC1(CC1)CO7)N91CCCC(C)(O)C1)=CC(O)=C2</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr"/>
+      <c r="H1068" t="inlineStr"/>
+      <c r="I1068" t="n">
+        <v>0.002971131761046809</v>
+      </c>
+      <c r="J1068" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1068" t="inlineStr"/>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="1" t="n">
+        <v>1067</v>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0868.png</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr"/>
+      <c r="D1069" t="inlineStr"/>
+      <c r="E1069" t="inlineStr"/>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>*#[N+]c1ccc(N2C(=O)C(C)(C)N(c3cnc(-c4ccc(OCCNC(=O)COc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)c(F)c4)c(F)c3)C2=S)c(F)c1OC |$Y;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr"/>
+      <c r="H1069" t="inlineStr"/>
+      <c r="I1069" t="n">
+        <v>0.8138048490392431</v>
+      </c>
+      <c r="J1069" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1069" t="inlineStr"/>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="1" t="n">
+        <v>1068</v>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0876.png</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr"/>
+      <c r="D1070" t="inlineStr"/>
+      <c r="E1070" t="inlineStr"/>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(C3=CC(OCCCN4CCC(C5=CN=C(C67=CC8CN(C9=C(N)N=NC(C%10=CC=CC=C%10O)=C9)CC6CC87)N=C5)CC4)=NO3)C(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr"/>
+      <c r="H1070" t="inlineStr"/>
+      <c r="I1070" t="n">
+        <v>0.3707734114397584</v>
+      </c>
+      <c r="J1070" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1070" t="inlineStr"/>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="1" t="n">
+        <v>1069</v>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0884.png</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr"/>
+      <c r="D1071" t="inlineStr"/>
+      <c r="E1071" t="inlineStr"/>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>CNc1ccc(-c2nc3ccc(OCCOCCOCCOCCOCCOCC(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)cc3s2)cc1</t>
+        </is>
+      </c>
+      <c r="G1071" t="inlineStr"/>
+      <c r="H1071" t="inlineStr"/>
+      <c r="I1071" t="n">
+        <v>0.8356674060849554</v>
+      </c>
+      <c r="J1071" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1071" t="inlineStr"/>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="1" t="n">
+        <v>1070</v>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0916.png</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr"/>
+      <c r="D1072" t="inlineStr"/>
+      <c r="E1072" t="inlineStr"/>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NC(=O)C3CCC(N4CCC(C5=CN=C6(CN67C6CCC7CN(C7=C(N)N=NC(C8=CC=CC=C8O)=C7)C6)N=C5)CC4)CC3)C(C)(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1072" t="inlineStr"/>
+      <c r="H1072" t="inlineStr"/>
+      <c r="I1072" t="n">
+        <v>0.5675346830832738</v>
+      </c>
+      <c r="J1072" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1072" t="inlineStr"/>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="1" t="n">
+        <v>1071</v>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0928.png</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr"/>
+      <c r="D1073" t="inlineStr"/>
+      <c r="E1073" t="inlineStr"/>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>NC(=O)c1ncc(-n2ccc(C(F)(F)F)n2)nc1Nc1ccc(C2CCN(C[C@H]3CCN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)C3)CC2)cc1</t>
+        </is>
+      </c>
+      <c r="G1073" t="inlineStr"/>
+      <c r="H1073" t="inlineStr"/>
+      <c r="I1073" t="n">
+        <v>0.8278392413871453</v>
+      </c>
+      <c r="J1073" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1073" t="inlineStr"/>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="1" t="n">
+        <v>1072</v>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0932.png</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr"/>
+      <c r="D1074" t="inlineStr"/>
+      <c r="E1074" t="inlineStr"/>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>CN1C2CCC1CN(c1cc(-c3ccccc3O)nnc1N)C2.Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)[C@H]2CC[C@H](c3cnc(N4C5CCC4CN(c4cc(-c6ccccc6O)nnc4N)C5)nc3)CC2)C(C)(C)C)c(C(F)(F)F)c1</t>
+        </is>
+      </c>
+      <c r="G1074" t="inlineStr"/>
+      <c r="H1074" t="inlineStr"/>
+      <c r="I1074" t="n">
+        <v>0.7650545858817598</v>
+      </c>
+      <c r="J1074" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1074" t="inlineStr"/>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="1" t="n">
+        <v>1073</v>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0936.png</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr"/>
+      <c r="D1075" t="inlineStr"/>
+      <c r="E1075" t="inlineStr"/>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>CN1C2CCC1CN(c1cc(-c3ccccc3O)nnc1N)C2.Cc1cnc(C)nc1.Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2CCCCC2)C(C)(C)C)c(OC(F)(F)F)c1</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr"/>
+      <c r="H1075" t="inlineStr"/>
+      <c r="I1075" t="n">
+        <v>0.7807865404755123</v>
+      </c>
+      <c r="J1075" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1075" t="inlineStr"/>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="1" t="n">
+        <v>1074</v>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0944.png</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr"/>
+      <c r="D1076" t="inlineStr"/>
+      <c r="E1076" t="inlineStr"/>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)N[C@@H]2CC[C@@H](c3cnc(N4C5CCC4CN(c4cc(-c6ccccc6O)nnc4N)C5)nc3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr"/>
+      <c r="H1076" t="inlineStr"/>
+      <c r="I1076" t="n">
+        <v>0.8312110705344209</v>
+      </c>
+      <c r="J1076" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1076" t="inlineStr"/>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="1" t="n">
+        <v>1075</v>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0952.png</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr"/>
+      <c r="D1077" t="inlineStr"/>
+      <c r="E1077" t="inlineStr"/>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>Cn1cc(Nc2nc(N3CCC[C@@H](NC(=O)C4CCN(CC5CN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)C5)CC4)C3)cnc2C(N)=O)cn1</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr"/>
+      <c r="H1077" t="inlineStr"/>
+      <c r="I1077" t="n">
+        <v>0.6101558554184495</v>
+      </c>
+      <c r="J1077" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1077" t="inlineStr"/>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="1" t="n">
+        <v>1076</v>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0960.png</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr"/>
+      <c r="D1078" t="inlineStr"/>
+      <c r="E1078" t="inlineStr"/>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(OCCOCCOCCOCCOc4ccc(CN5C(=O)/C(=C/C=C/c6ccc([N+](=O)[O-])cc6)c6ccccc65)cc4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1078" t="inlineStr"/>
+      <c r="H1078" t="inlineStr"/>
+      <c r="I1078" t="n">
+        <v>0.8346259040818108</v>
+      </c>
+      <c r="J1078" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1078" t="inlineStr"/>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="1" t="n">
+        <v>1077</v>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0968.png</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr"/>
+      <c r="D1079" t="inlineStr"/>
+      <c r="E1079" t="inlineStr"/>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CCN(C[C@H]6C[C@H](Nc7cccc8c7C(=O)N([C@@H]7CCC(=O)NC7=O)C8=O)C6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G1079" t="inlineStr"/>
+      <c r="H1079" t="inlineStr"/>
+      <c r="I1079" t="n">
+        <v>0.8121556157599831</v>
+      </c>
+      <c r="J1079" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1079" t="inlineStr"/>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="1" t="n">
+        <v>1078</v>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_0972.png</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr"/>
+      <c r="D1080" t="inlineStr"/>
+      <c r="E1080" t="inlineStr"/>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>CN1C2CCC1CN(c1cc(-c3ccccc3O)nnc1N)C2.Cc1ccnc(O[C@H]2C[C@H](OC3CCN(CCOc4cc(C(C(=O)N5C[C@H](O)C[C@H]5C(=O)NCc5ccc(-c6scnc6C)cc5)C(C)C)on4)CC3)C2)c1</t>
+        </is>
+      </c>
+      <c r="G1080" t="inlineStr"/>
+      <c r="H1080" t="inlineStr"/>
+      <c r="I1080" t="n">
+        <v>0.8236100180889458</v>
+      </c>
+      <c r="J1080" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1080" t="inlineStr"/>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="1" t="n">
+        <v>1079</v>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1020.png</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr"/>
+      <c r="D1081" t="inlineStr"/>
+      <c r="E1081" t="inlineStr"/>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NC(=O)C3CC4(C3)CC(N3CCC(OC5=CC(N67CC8CN(C9=C(N)N=NC(C%10=CC=CC=C%10O)=C9)CC6CC87)=CC=N5)CC3)C4)C(C)(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr"/>
+      <c r="H1081" t="inlineStr"/>
+      <c r="I1081" t="n">
+        <v>0.2280072162590101</v>
+      </c>
+      <c r="J1081" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1081" t="inlineStr"/>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="1" t="n">
+        <v>1080</v>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1032.png</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr"/>
+      <c r="D1082" t="inlineStr"/>
+      <c r="E1082" t="inlineStr"/>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(C3=CC(OCCCN4CCC(C5=CN=C(C67=CC8CN(C9=C(N)N=NC(C%10=CC=CC=C%10O)=C9)CC6CC87)N=C5)CC4)=NO3)C(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr"/>
+      <c r="H1082" t="inlineStr"/>
+      <c r="I1082" t="n">
+        <v>0.364327160936058</v>
+      </c>
+      <c r="J1082" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1082" t="inlineStr"/>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="1" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1044.png</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr"/>
+      <c r="D1083" t="inlineStr"/>
+      <c r="E1083" t="inlineStr"/>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>CC(C)(C)[C@H](NC(=O)C1CC2(C1)CN(C1CCN(c3cnc(N4CC56CC(CC45)CN(c4cc(-c5ccccc5O)nnc4N)C6)nc3)CC1)C2)C(=O)N1C[C@H](O)C[C@H]1C(=O)NCc1ccc(-c2cncs2)cc1</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr"/>
+      <c r="H1083" t="inlineStr"/>
+      <c r="I1083" t="n">
+        <v>0.344562278494658</v>
+      </c>
+      <c r="J1083" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1083" t="inlineStr"/>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="1" t="n">
+        <v>1082</v>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1052.png</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr"/>
+      <c r="D1084" t="inlineStr"/>
+      <c r="E1084" t="inlineStr"/>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)[CH]NC(=O)[CH]34CC5(CC(N6CCC(C7=CN=C(N8C9CCC8CN(C8=C(N)N=NC(C%10=CC=CC=C%10O)=C8)C9)N=C7)CC6)C5)(C3)C4)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1084" t="inlineStr"/>
+      <c r="H1084" t="inlineStr"/>
+      <c r="I1084" t="n">
+        <v>0.6287094525810472</v>
+      </c>
+      <c r="J1084" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1084" t="inlineStr"/>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="1" t="n">
+        <v>1083</v>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1068.png</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr"/>
+      <c r="D1085" t="inlineStr"/>
+      <c r="E1085" t="inlineStr"/>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)COCCCc2cnc(N3C4CCC3CN(c3cc(-c5ccccc5O)nnc3N)C4)nc2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1085" t="inlineStr"/>
+      <c r="H1085" t="inlineStr"/>
+      <c r="I1085" t="n">
+        <v>0.8138856505980657</v>
+      </c>
+      <c r="J1085" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1085" t="inlineStr"/>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="1" t="n">
+        <v>1084</v>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1072.png</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr"/>
+      <c r="D1086" t="inlineStr"/>
+      <c r="E1086" t="inlineStr"/>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCCCCN2CCC(c3cnc(N4C5CCC4CN(c4cc(-c6ccccc6O)nnc4N)C5)nc3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr"/>
+      <c r="H1086" t="inlineStr"/>
+      <c r="I1086" t="n">
+        <v>0.7596908592263146</v>
+      </c>
+      <c r="J1086" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1086" t="inlineStr"/>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="1" t="n">
+        <v>1085</v>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1080.png</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr"/>
+      <c r="D1087" t="inlineStr"/>
+      <c r="E1087" t="inlineStr"/>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>C/C(=N/C=C/C1CCC(C(=O)N[C@H](C(=O)N2C[C@H](O)C[C@H]2C(=O)NCc2ccc(-c3scnc3C)cc2)C(C)(C)C)CC1)N1C2CCC1CN(c1cc(-c3ccccc3O)nnc1N)C2.CN1C2CCC1CN(c1cc(-c3ccccc3O)nnc1N)C2</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr"/>
+      <c r="H1087" t="inlineStr"/>
+      <c r="I1087" t="n">
+        <v>0.5351078079495393</v>
+      </c>
+      <c r="J1087" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1087" t="inlineStr"/>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="1" t="n">
+        <v>1086</v>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_1/rb_1092.png</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr"/>
+      <c r="D1088" t="inlineStr"/>
+      <c r="E1088" t="inlineStr"/>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)CC(C)(C)C)c(O[C@H]2CC[C@H](N3CCC(c4cnc(CN5C6CCC5CN(c5cc(-c7ccccc7O)nnc5N)C6)nc4)CC3)CC2)c1.O=C(O)C1(F)CC1</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr"/>
+      <c r="H1088" t="inlineStr"/>
+      <c r="I1088" t="n">
+        <v>0.2516079303787021</v>
+      </c>
+      <c r="J1088" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1088" t="inlineStr"/>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="1" t="n">
+        <v>1087</v>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0857.png</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr"/>
+      <c r="D1089" t="inlineStr"/>
+      <c r="E1089" t="inlineStr"/>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)CC(C)(C)C)c(O[C@H]2CC[C@@H](N3CCC(c4cnc(C5N6C7CCC56CN(c5cc(-c6ccccc6O)nnc5N)C7)nc4)CC3)CC2)c1.O=C(O)C1(F)CC1</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr"/>
+      <c r="H1089" t="inlineStr"/>
+      <c r="I1089" t="n">
+        <v>0.2512666766440956</v>
+      </c>
+      <c r="J1089" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1089" t="inlineStr"/>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="1" t="n">
+        <v>1088</v>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0865.png</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr"/>
+      <c r="D1090" t="inlineStr"/>
+      <c r="E1090" t="inlineStr"/>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(C3=CC(N4CCC(N5CCC(C6=CN=C(C78C9CC7%10%11CCC9(CN(C7=C(N)N=NC(C9=CC=CC=C9O)=C7)C%10)N8%11)N=C6)CC5)CC4)=NO3)C(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr"/>
+      <c r="H1090" t="inlineStr"/>
+      <c r="I1090" t="n">
+        <v>0.2426181589609933</v>
+      </c>
+      <c r="J1090" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1090" t="inlineStr"/>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="1" t="n">
+        <v>1089</v>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0881.png</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr"/>
+      <c r="D1091" t="inlineStr"/>
+      <c r="E1091" t="inlineStr"/>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2CCN(Cc3cnc(CN4C5CCC4CN(c4cc(-c6ccccc6O)nnc4N)C5)nc3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr"/>
+      <c r="H1091" t="inlineStr"/>
+      <c r="I1091" t="n">
+        <v>0.7064359609763232</v>
+      </c>
+      <c r="J1091" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1091" t="inlineStr"/>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="1" t="n">
+        <v>1090</v>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0913.png</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr"/>
+      <c r="D1092" t="inlineStr"/>
+      <c r="E1092" t="inlineStr"/>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>CN1C2CCC1CN(c1cc(-c3ccccc3O)nnc1N)C2.Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2(F)CC2)C(C)(C)C)c(OCCN2CCC(c3cnc(N4C5CCC4CN(c4cc(-c6ccccc6O)nnc4N)C5)nc3)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr"/>
+      <c r="H1092" t="inlineStr"/>
+      <c r="I1092" t="n">
+        <v>0.8329465213191566</v>
+      </c>
+      <c r="J1092" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1092" t="inlineStr"/>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="1" t="n">
+        <v>1091</v>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0921.png</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr"/>
+      <c r="D1093" t="inlineStr"/>
+      <c r="E1093" t="inlineStr"/>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C23CCC(CN(C)Cc4cnc(N5C6CCC5CN(c5cc(-c7ccccc7O)nnc5N)C6)nc4)(CC2)CC3)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr"/>
+      <c r="H1093" t="inlineStr"/>
+      <c r="I1093" t="n">
+        <v>0.3820188956201154</v>
+      </c>
+      <c r="J1093" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1093" t="inlineStr"/>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="1" t="n">
+        <v>1092</v>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0933.png</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr"/>
+      <c r="D1094" t="inlineStr"/>
+      <c r="E1094" t="inlineStr"/>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>CC(NC(=O)C1CC(O)CN1C(=O)C(NC(=O)C1CC2(C1)CC(N1CCC(C3=CN=C45CCC6CN7(C8=C(N)N=NC(C9=CC=CC=C9O)=C8)CC8(C7N684)N5=C3)CC1)C2)C(C)(C)C)C1=CC=C(C2=C(I)N=CS2)C=C1</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr"/>
+      <c r="H1094" t="inlineStr"/>
+      <c r="I1094" t="n">
+        <v>0.6033365272113524</v>
+      </c>
+      <c r="J1094" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1094" t="inlineStr"/>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="1" t="n">
+        <v>1093</v>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0941.png</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr"/>
+      <c r="D1095" t="inlineStr"/>
+      <c r="E1095" t="inlineStr"/>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>O=C(CC1=CC=C2C3=CC=CC24=C13C(=O)N(C1CCC(=O)NC1=O)C4=O)NCCCCCCCN1CCN(C2=CC(C(=O)N3CCCC(NC4=NC=C(Cl)C(C5=CNC6=CC=CC=C65)=N4)C3)=CC=C2)CC1</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr"/>
+      <c r="H1095" t="inlineStr"/>
+      <c r="I1095" t="n">
+        <v>0.2667974320189003</v>
+      </c>
+      <c r="J1095" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1095" t="inlineStr"/>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="1" t="n">
+        <v>1094</v>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0945.png</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr"/>
+      <c r="D1096" t="inlineStr"/>
+      <c r="E1096" t="inlineStr"/>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>Cn1cc(Nc2nc(N3CCC[C@@H](N4CC5(CN(C6CCN(c7ccc8c(c7)C(=O)N([C@H]7CCC(=O)NC7=O)C8=O)CC6)C5)OC4=O)C3)cnc2C(N)=O)cn1</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr"/>
+      <c r="H1096" t="inlineStr"/>
+      <c r="I1096" t="n">
+        <v>0.4386826391452817</v>
+      </c>
+      <c r="J1096" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1096" t="inlineStr"/>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="1" t="n">
+        <v>1095</v>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0961.png</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr"/>
+      <c r="D1097" t="inlineStr"/>
+      <c r="E1097" t="inlineStr"/>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>CN(C)c1ccc(-c2nc3ccc(O[C@@H]4C[C@@H](OC5CCN(CCN6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)C4)cc3s2)cc1</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr"/>
+      <c r="H1097" t="inlineStr"/>
+      <c r="I1097" t="n">
+        <v>0.7531908241205766</v>
+      </c>
+      <c r="J1097" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1097" t="inlineStr"/>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="1" t="n">
+        <v>1096</v>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0965.png</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr"/>
+      <c r="D1098" t="inlineStr"/>
+      <c r="E1098" t="inlineStr"/>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>CN1CCN(C2=CN=C(C(N)=O)C3=N2C2(=CC=C(C4CCN(CC5CCN(C6=CC7=C(C=C6)C(=O)N(C6CCC(=O)NC6=O)C7=O)C5)CC4)C=C2)N3)CC1</t>
+        </is>
+      </c>
+      <c r="G1098" t="inlineStr"/>
+      <c r="H1098" t="inlineStr"/>
+      <c r="I1098" t="n">
+        <v>0.5115945213167523</v>
+      </c>
+      <c r="J1098" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1098" t="inlineStr"/>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="1" t="n">
+        <v>1097</v>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0973.png</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr"/>
+      <c r="D1099" t="inlineStr"/>
+      <c r="E1099" t="inlineStr"/>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)C(NC(=O)COCCOCCOCCNC(=O)CCCCCCCCOc2ccc(N3CCN(/C=C/C(=O)c4ccccc4O)CC3)nc2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr"/>
+      <c r="H1099" t="inlineStr"/>
+      <c r="I1099" t="n">
+        <v>0.7906156294824052</v>
+      </c>
+      <c r="J1099" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1099" t="inlineStr"/>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="1" t="n">
+        <v>1098</v>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0985.png</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr"/>
+      <c r="D1100" t="inlineStr"/>
+      <c r="E1100" t="inlineStr"/>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)N[C@H]2CC[C@@H](c3cnc(CN4C5CCC4CN(c4cc(-c6ccccc6O)nnc4N)C5)nc3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr"/>
+      <c r="H1100" t="inlineStr"/>
+      <c r="I1100" t="n">
+        <v>0.6696131422099123</v>
+      </c>
+      <c r="J1100" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1100" t="inlineStr"/>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="1" t="n">
+        <v>1099</v>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0989.png</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr"/>
+      <c r="D1101" t="inlineStr"/>
+      <c r="E1101" t="inlineStr"/>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>CNc1ccc(-c2nc3ccc(OCCOCCOCCOCCOCCOCCOCC(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)cc3s2)cc1</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr"/>
+      <c r="H1101" t="inlineStr"/>
+      <c r="I1101" t="n">
+        <v>0.5445889104173453</v>
+      </c>
+      <c r="J1101" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1101" t="inlineStr"/>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="1" t="n">
+        <v>1100</v>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_0997.png</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr"/>
+      <c r="D1102" t="inlineStr"/>
+      <c r="E1102" t="inlineStr"/>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NC(=O)COCCOCCOCCNC(=O)CCCCCCCCOC3=CC(N4CC5CCC4CO5CC=C(O)C4=C(O)C=CC=C4)=NC=C3)C(C)(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr"/>
+      <c r="H1102" t="inlineStr"/>
+      <c r="I1102" t="n">
+        <v>0.1811347600984777</v>
+      </c>
+      <c r="J1102" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1102" t="inlineStr"/>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="1" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1001.png</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr"/>
+      <c r="D1103" t="inlineStr"/>
+      <c r="E1103" t="inlineStr"/>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>CC(C)(C)C(NC(=O)C1CC2(C1)C[CH]1(C2)C2N13CC2145678CN29C1C41%10(C35)C6N3(C=CN=CC4=NC=C23C=N4)(C17)C9%108)C(=O)N1CC(O)CC1C(=O)NCC1=CC=C(C2=CN=CS2)C=C1.NC1=C(N2CC3CCC4(C2)CN34)C=C(C2=CC=CC=C2O)N=N1</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr"/>
+      <c r="H1103" t="inlineStr"/>
+      <c r="I1103" t="n">
+        <v>0.006584221977195752</v>
+      </c>
+      <c r="J1103" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1103" t="inlineStr"/>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="1" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1009.png</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr"/>
+      <c r="D1104" t="inlineStr"/>
+      <c r="E1104" t="inlineStr"/>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)C3CC(C)C(c4cc(N5CCC(N6CCC(c7cnc(N8CC9%10CC(CC89)CN(c8cc(-c9ccccc9O)nnc8N)C%10)nc7)CC6)CC5)no4)C(=O)N32)cc1.[I-46]</t>
+        </is>
+      </c>
+      <c r="G1104" t="inlineStr"/>
+      <c r="H1104" t="inlineStr"/>
+      <c r="I1104" t="n">
+        <v>0.1010996844132863</v>
+      </c>
+      <c r="J1104" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1104" t="inlineStr"/>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="1" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1037.png</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr"/>
+      <c r="D1105" t="inlineStr"/>
+      <c r="E1105" t="inlineStr"/>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(C3=CC(C4CCC(N5CCC(C6=CN=C(N78CCC7C8)N=C6)CC5)CC4)=NO3)C(C)C)C=C2)SC=N1.CCCN(CCC)C1=C(N)N=NC(C2=CC=CC=C2O)=C1</t>
+        </is>
+      </c>
+      <c r="G1105" t="inlineStr"/>
+      <c r="H1105" t="inlineStr"/>
+      <c r="I1105" t="n">
+        <v>0.6455328162761255</v>
+      </c>
+      <c r="J1105" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1105" t="inlineStr"/>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="1" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1053.png</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr"/>
+      <c r="D1106" t="inlineStr"/>
+      <c r="E1106" t="inlineStr"/>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(C3=CC(N4CCC(CCN5CCC(C6=CN=C(N78C9C%10C7%11CCC%1098CN(C7=C(N)N=NC(C8=CC=CC=C8O)=C7)C%11)N=C6)CC5)CC4)=NO3)C(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr"/>
+      <c r="H1106" t="inlineStr"/>
+      <c r="I1106" t="n">
+        <v>0.2184648005956619</v>
+      </c>
+      <c r="J1106" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1106" t="inlineStr"/>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="1" t="n">
+        <v>1105</v>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1057.png</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr"/>
+      <c r="D1107" t="inlineStr"/>
+      <c r="E1107" t="inlineStr"/>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CCN(C[C@@H]6[C@H]7CN(c8ccc9c(c8)C(=O)N(C8CCC(=O)NC8=O)C9=O)C[C@@H]67)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr"/>
+      <c r="H1107" t="inlineStr"/>
+      <c r="I1107" t="n">
+        <v>0.7345980688077915</v>
+      </c>
+      <c r="J1107" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1107" t="inlineStr"/>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="1" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1073.png</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr"/>
+      <c r="D1108" t="inlineStr"/>
+      <c r="E1108" t="inlineStr"/>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(C3=CC(N4CCC(CN5CCC(C6=CN=C(C78C9C%10C7%11%12CCC(CN(C7=C(N)N=NC(C%13=CC=CC=C%13O)=C7)C%11)N9%108%12)N=C6)CC5)CC4)=NO3)C(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr"/>
+      <c r="H1108" t="inlineStr"/>
+      <c r="I1108" t="n">
+        <v>0.1213477921282607</v>
+      </c>
+      <c r="J1108" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1108" t="inlineStr"/>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="1" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1077.png</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr"/>
+      <c r="D1109" t="inlineStr"/>
+      <c r="E1109" t="inlineStr"/>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>CN1CCN([C@@H]2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CCN(C[C@H]6C[C@@H](Nc7cccc8c7C(=O)N([C@@H]7CCC(=O)NC7=O)C8=O)C6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr"/>
+      <c r="H1109" t="inlineStr"/>
+      <c r="I1109" t="n">
+        <v>0.824200322643568</v>
+      </c>
+      <c r="J1109" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1109" t="inlineStr"/>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="1" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1081.png</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr"/>
+      <c r="D1110" t="inlineStr"/>
+      <c r="E1110" t="inlineStr"/>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>O=C(CCCCCCCCOc1ccc(N2C[C@H]3CC[C@@H]2CN3/C=C/C(=O)c2ccccc2O)nc1)NCCOCCOCCNc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr"/>
+      <c r="H1110" t="inlineStr"/>
+      <c r="I1110" t="n">
+        <v>0.2673531501505655</v>
+      </c>
+      <c r="J1110" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1110" t="inlineStr"/>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="1" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_2/rb_1089.png</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr"/>
+      <c r="D1111" t="inlineStr"/>
+      <c r="E1111" t="inlineStr"/>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NC(=O)C3CCC4(CC3)CC(N3CCC(C5=CN=C(N67CC6CN(C6=C(N)N=NC(C8=CC=CC=C8O)=C6)CC7C)N=C5)CC3)C4)C(C)(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr"/>
+      <c r="H1111" t="inlineStr"/>
+      <c r="I1111" t="n">
+        <v>0.4402147479993556</v>
+      </c>
+      <c r="J1111" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1111" t="inlineStr"/>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="1" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0870.png</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr"/>
+      <c r="D1112" t="inlineStr"/>
+      <c r="E1112" t="inlineStr"/>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NC(=O)CN3C4CCC3CN(C3CCC(C5=CN=C(N67C8CC6C7CN(C6=C(N)N=NC(C7=CC=CC=C7O)=C6)C8)N=C5)CC3)C4)C(C)(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr"/>
+      <c r="H1112" t="inlineStr"/>
+      <c r="I1112" t="n">
+        <v>0.4116853151778123</v>
+      </c>
+      <c r="J1112" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1112" t="inlineStr"/>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="1" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0898.png</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr"/>
+      <c r="D1113" t="inlineStr"/>
+      <c r="E1113" t="inlineStr"/>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1ccc(N2CCN(c3ccc(NC(=O)c4ccc(OCCOCCOCC(=O)N[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)N[C@@H](C)c5ccc(-c6scnc6C)cc5)C(C)C)cc4)cc3)CC2)nc1</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr"/>
+      <c r="H1113" t="inlineStr"/>
+      <c r="I1113" t="n">
+        <v>0.7994679121328179</v>
+      </c>
+      <c r="J1113" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1113" t="inlineStr"/>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="1" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0902.png</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr"/>
+      <c r="D1114" t="inlineStr"/>
+      <c r="E1114" t="inlineStr"/>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](c2cc(N3CCC(CCN4CCC(c5cnc(N6C7CCC6CN(c6cc(-c8ccccc8O)nnc6N)C7)nc5)CC4)CC3)no2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr"/>
+      <c r="H1114" t="inlineStr"/>
+      <c r="I1114" t="n">
+        <v>0.7016062245261593</v>
+      </c>
+      <c r="J1114" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1114" t="inlineStr"/>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="1" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0930.png</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr"/>
+      <c r="D1115" t="inlineStr"/>
+      <c r="E1115" t="inlineStr"/>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>CC(C)(C)C(NC(=O)C1CC2(C1)CC(N1CC3(CN(C4=CN=C(C56789CC%10C%11C%12%13C%14N%11%15(C%11=C(N)N=NC(C%16=CC=CC=C%16O)=C%11)C%11C5%16C%15C%1165(CC%10%127)C%1686CN%14%13659)N=C4)C3)C1)C2)C(=O)N1CC(O)CC1C(=O)NCC1=CC=C(C2=CN=CS2)C=C1</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr"/>
+      <c r="H1115" t="inlineStr"/>
+      <c r="I1115" t="n">
+        <v>0.003367279560048584</v>
+      </c>
+      <c r="J1115" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1115" t="inlineStr"/>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="1" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0934.png</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr"/>
+      <c r="D1116" t="inlineStr"/>
+      <c r="E1116" t="inlineStr"/>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2(F)CC2)C(C)(C)C)c(OCCCCCCN2CCC(c3cnc(N4C5CCC4CN(c4cc(-c6ccccc6O)nnc4N)C5)nc3)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr"/>
+      <c r="H1116" t="inlineStr"/>
+      <c r="I1116" t="n">
+        <v>0.817554511699392</v>
+      </c>
+      <c r="J1116" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1116" t="inlineStr"/>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="1" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0958.png</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr"/>
+      <c r="D1117" t="inlineStr"/>
+      <c r="E1117" t="inlineStr"/>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NC(=O)C3CC4(CCCCC4)C3)C(C)(C)C)C=C2)SC=N1.NC12=C3C45=C6C7=CC=CC=C7(O)C7(=CC=CC=C7O)C478=CC5(=C(N)(N1=N7)N2=N68)N124CC567CCC8(C1)(C21C2CCCCN31C284)N51C6CC17</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr"/>
+      <c r="H1117" t="inlineStr"/>
+      <c r="I1117" t="n">
+        <v>0.03834124552748674</v>
+      </c>
+      <c r="J1117" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1117" t="inlineStr"/>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="1" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0978.png</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr"/>
+      <c r="D1118" t="inlineStr"/>
+      <c r="E1118" t="inlineStr"/>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>CC1=C(C23=CC=C4(CNC(=O)C5CC(O)CN5C(=O)[CH]NC(=O)C5CC6(C5)CC(C5=CC=C(CN7CCC(CN8C=C(C9=CC(C%10=CC=CC=C%10O)=NN=C9N)C=N8)CC7)C=C5)C6)C5=C4=C=2=C=53)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr"/>
+      <c r="H1118" t="inlineStr"/>
+      <c r="I1118" t="n">
+        <v>0.1413812028672022</v>
+      </c>
+      <c r="J1118" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1118" t="inlineStr"/>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="1" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_0990.png</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr"/>
+      <c r="D1119" t="inlineStr"/>
+      <c r="E1119" t="inlineStr"/>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>C1=C234=C5=C(C6=NC(=N5)C(=N1)N=C=62)C3CCN1CCC4CC1.CC1=C(C2=CC=C(C(C)NC(=O)C3CC(O)CN3C(=O)C(NC(=O)C3CCC4(CCC4)CC3)C(C)(C)C)C=C2)SC=N1.NC1=C(N2CC3CCC4(C2)C2CN324)C=C(C2=CC=CC=C2O)N=N1</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr"/>
+      <c r="H1119" t="inlineStr"/>
+      <c r="I1119" t="n">
+        <v>0.1524682340510544</v>
+      </c>
+      <c r="J1119" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1119" t="inlineStr"/>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="1" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1002.png</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr"/>
+      <c r="D1120" t="inlineStr"/>
+      <c r="E1120" t="inlineStr"/>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>CCCn1cc(-c2nc(Nc3ccc(C(=O)NCCOCCOCCOCCOCCNc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)cc3)nc3[nH]ccc23)cn1</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr"/>
+      <c r="H1120" t="inlineStr"/>
+      <c r="I1120" t="n">
+        <v>0.8099272678768195</v>
+      </c>
+      <c r="J1120" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1120" t="inlineStr"/>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="1" t="n">
+        <v>1119</v>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1022.png</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr"/>
+      <c r="D1121" t="inlineStr"/>
+      <c r="E1121" t="inlineStr"/>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3c(SCCCCCCCCN4CCN(CCCCCCCCSc5cccc6c5CN(C5CCC(=O)NC5=O)C6=O)CC4)cccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr"/>
+      <c r="H1121" t="inlineStr"/>
+      <c r="I1121" t="n">
+        <v>0.5488822068399454</v>
+      </c>
+      <c r="J1121" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1121" t="inlineStr"/>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="1" t="n">
+        <v>1120</v>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1026.png</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr"/>
+      <c r="D1122" t="inlineStr"/>
+      <c r="E1122" t="inlineStr"/>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>CC1=C(C=CC=CC(C)NC(=O)[CH]23CC(O)CN24C(=O)C(C2=CC(OCCOCCOC5=CC=C(CN6C(=O)C(=CC=CC7=CC=C([N+](=O)[O-])C=C7)C7=CC=CC=C76)C=C5)=NO2)(C(C)C)C34)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr"/>
+      <c r="H1122" t="inlineStr"/>
+      <c r="I1122" t="n">
+        <v>0.2308758717495142</v>
+      </c>
+      <c r="J1122" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1122" t="inlineStr"/>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="1" t="n">
+        <v>1121</v>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1054.png</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr"/>
+      <c r="D1123" t="inlineStr"/>
+      <c r="E1123" t="inlineStr"/>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>CCS(=O)(=O)N1CC(CC#N)(N23C=C(C4=C5C=CNC5=NC(NC5=CC=C(C(=O)NCCCNC(=O)COC6=C7C(=O)N(C8CCC(=O)NC8=O)C(=O)C7=CC=C6)C=C5)=N4)C2=N3)C1</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr"/>
+      <c r="H1123" t="inlineStr"/>
+      <c r="I1123" t="n">
+        <v>0.3638579425050026</v>
+      </c>
+      <c r="J1123" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1123" t="inlineStr"/>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="1" t="n">
+        <v>1122</v>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1058.png</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr"/>
+      <c r="D1124" t="inlineStr"/>
+      <c r="E1124" t="inlineStr"/>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>CN(C)c1ccc(-c2nc3ccc(O[C@@H]4C[C@@H](OCCCN5CCN(c6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)C4)cc3s2)cc1</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr"/>
+      <c r="H1124" t="inlineStr"/>
+      <c r="I1124" t="n">
+        <v>0.572330103496409</v>
+      </c>
+      <c r="J1124" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1124" t="inlineStr"/>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="1" t="n">
+        <v>1123</v>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1062.png</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr"/>
+      <c r="D1125" t="inlineStr"/>
+      <c r="E1125" t="inlineStr"/>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>CN1CCN(C2CCCN(c3cnc(C(N)=O)c(Nc4ccc(C5CCN(C[C@@H]6CCN(c7ccc8c(c7)CN(C7CCC(=O)NC7=O)C8=O)C6)CC5)cc4)n3)C2)C1=O</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr"/>
+      <c r="H1125" t="inlineStr"/>
+      <c r="I1125" t="n">
+        <v>0.7920154867081765</v>
+      </c>
+      <c r="J1125" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1125" t="inlineStr"/>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="1" t="n">
+        <v>1124</v>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1070.png</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr"/>
+      <c r="D1126" t="inlineStr"/>
+      <c r="E1126" t="inlineStr"/>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>CNc1ccc(-c2nc3ccc(OCCOCCOCCOCC(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)N[C@@H](C)c4ccc(-c5scnc5C)cc4)C(C)(C)C)cc3s2)cc1</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr"/>
+      <c r="H1126" t="inlineStr"/>
+      <c r="I1126" t="n">
+        <v>0.8255959710842474</v>
+      </c>
+      <c r="J1126" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1126" t="inlineStr"/>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="1" t="n">
+        <v>1125</v>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1090.png</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr"/>
+      <c r="D1127" t="inlineStr"/>
+      <c r="E1127" t="inlineStr"/>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>[H][C@@]12C[C@](C)(C(=O)NCCOCCOCCOCCOCC(=O)N[C@H](C(=O)N3C[C@H](O)C[C@H]3C(=O)N[C@@H](C)c3ccc(-c4scnc4C)cc3)C(C)(C)C)CC[C@]1(C)CC[C@]1(C)C3=CC=C4C(=CC(=O)C(O)=C4C)[C@]3(C)CC[C@@]21C</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr"/>
+      <c r="H1127" t="inlineStr"/>
+      <c r="I1127" t="n">
+        <v>0.8231792128766132</v>
+      </c>
+      <c r="J1127" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1127" t="inlineStr"/>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="1" t="n">
+        <v>1126</v>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261009T212214_3/rb_1094.png</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr"/>
+      <c r="D1128" t="inlineStr"/>
+      <c r="E1128" t="inlineStr"/>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(C3(NC(=O)C4CC(O)CN4C(=O)C(NC(=O)C4CC5(C4)CC(N4CCC(C6=CN=C(N78CCC79CCC8CN(C7=C(N)N=NC(C8=CC=CC=C8O)=C7)C9)N=C6)CC4)C5)C(C)(C)C)CC3)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr"/>
+      <c r="H1128" t="inlineStr"/>
+      <c r="I1128" t="n">
+        <v>0.6110796011540417</v>
+      </c>
+      <c r="J1128" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1128" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1128"/>
+  <dimension ref="A1:K1200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33163,6 +33163,2094 @@
       </c>
       <c r="K1128" t="inlineStr"/>
     </row>
+    <row r="1129">
+      <c r="A1129" s="1" t="n">
+        <v>1127</v>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1101.png</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr"/>
+      <c r="D1129" t="inlineStr"/>
+      <c r="E1129" t="inlineStr"/>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>COc1c(N2CCC(O[C@@H]3CC[C@@H](CN4CCN(c5cc(-c6n[nH]c7cnc(OC8(C)CC8)cc67)ncn5)CC4)CC3)CC2)ccc2c1CN(C1CCC(=O)NC1=O)C2=O</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr"/>
+      <c r="H1129" t="inlineStr"/>
+      <c r="I1129" t="n">
+        <v>0.8011236544333296</v>
+      </c>
+      <c r="J1129" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1129" t="inlineStr"/>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="1" t="n">
+        <v>1128</v>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1125.png</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr"/>
+      <c r="D1130" t="inlineStr"/>
+      <c r="E1130" t="inlineStr"/>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>CCCn1cc(-c2nc(Nc3ccc(NC(=O)CCOCCOCCOCCOCCOCCNc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)cc3)nc3[nH]ccc23)cn1</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr"/>
+      <c r="H1130" t="inlineStr"/>
+      <c r="I1130" t="n">
+        <v>0.8005233003346057</v>
+      </c>
+      <c r="J1130" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1130" t="inlineStr"/>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="1" t="n">
+        <v>1129</v>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1137.png</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr"/>
+      <c r="D1131" t="inlineStr"/>
+      <c r="E1131" t="inlineStr"/>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3cc(N4CCN(CCC5CCN(c6ncc(-c7ccc8c(c7)[nH]c7ccncc78)cc6C(F)(F)F)CC5)CC4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr"/>
+      <c r="H1131" t="inlineStr"/>
+      <c r="I1131" t="n">
+        <v>0.8271073564946256</v>
+      </c>
+      <c r="J1131" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1131" t="inlineStr"/>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="1" t="n">
+        <v>1130</v>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1145.png</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr"/>
+      <c r="D1132" t="inlineStr"/>
+      <c r="E1132" t="inlineStr"/>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2CC3C=C(OCC#Cc4ccc(O[C@@H]5C[C@H](Oc6ccc(-c7ccc8c(c7)[nH]c7ccncc78)cn6)C5)cn4)C=CC3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr"/>
+      <c r="H1132" t="inlineStr"/>
+      <c r="I1132" t="n">
+        <v>0.8123908240027398</v>
+      </c>
+      <c r="J1132" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1132" t="inlineStr"/>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="1" t="n">
+        <v>1131</v>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1149.png</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr"/>
+      <c r="D1133" t="inlineStr"/>
+      <c r="E1133" t="inlineStr"/>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(N4CCN(CCC5CCN(c6ncc(-c7ccc8c(c7)[nH]c7ccncc78)cc6C(F)(F)F)CC5)CC4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr"/>
+      <c r="H1133" t="inlineStr"/>
+      <c r="I1133" t="n">
+        <v>0.7928982837857186</v>
+      </c>
+      <c r="J1133" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1133" t="inlineStr"/>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="1" t="n">
+        <v>1132</v>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1153.png</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr"/>
+      <c r="D1134" t="inlineStr"/>
+      <c r="E1134" t="inlineStr"/>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(OCCCN4CC5(CCCN(c6ncc(-c7ccc8c9cnccc9n(C(F)F)c8c7)cc6F)C5)C4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr"/>
+      <c r="H1134" t="inlineStr"/>
+      <c r="I1134" t="n">
+        <v>0.8154509005333735</v>
+      </c>
+      <c r="J1134" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1134" t="inlineStr"/>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="1" t="n">
+        <v>1133</v>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1173.png</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr"/>
+      <c r="D1135" t="inlineStr"/>
+      <c r="E1135" t="inlineStr"/>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)C3=C(C=C(N4CCN(CC5CC5678CC5N9%10%11C(C6)N56(C95C7C%106C58)C%115=NC=C(C6=CC7=C(C=C6)C6=C(C=CN=C6)N7C(F)F)C=C5F)CC4)C=C3)C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr"/>
+      <c r="H1135" t="inlineStr"/>
+      <c r="I1135" t="n">
+        <v>0.6478105281724953</v>
+      </c>
+      <c r="J1135" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1135" t="inlineStr"/>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="1" t="n">
+        <v>1134</v>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1181.png</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr"/>
+      <c r="D1136" t="inlineStr"/>
+      <c r="E1136" t="inlineStr"/>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](c2cc(OCCN3CCC(OC4CN(c5ccc(-c6ccn7c(n6)nc6ccccc67)cn5)C4)CC3)no2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr"/>
+      <c r="H1136" t="inlineStr"/>
+      <c r="I1136" t="n">
+        <v>0.6749969286735001</v>
+      </c>
+      <c r="J1136" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1136" t="inlineStr"/>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="1" t="n">
+        <v>1135</v>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1185.png</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr"/>
+      <c r="D1137" t="inlineStr"/>
+      <c r="E1137" t="inlineStr"/>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>CC1(CCOc2cc(-c3ccccc3O)nnc2N)C=C(NC(=O)CCOCCOCCOc2ccc3c(c2)C(=O)N(C2CCC(=O)NC2=O)C3=O)CC1</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr"/>
+      <c r="H1137" t="inlineStr"/>
+      <c r="I1137" t="n">
+        <v>0.4186281672833621</v>
+      </c>
+      <c r="J1137" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1137" t="inlineStr"/>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="1" t="n">
+        <v>1136</v>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1209.png</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr"/>
+      <c r="D1138" t="inlineStr"/>
+      <c r="E1138" t="inlineStr"/>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>C[C@H]1CN(c2cc(-c3[nH]nc4ccc(OC5(C)CC5)cc34)ncn2)CCN1CC1CCN(CC2CCN(c3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)CC2)CC1</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr"/>
+      <c r="H1138" t="inlineStr"/>
+      <c r="I1138" t="n">
+        <v>0.766504520896391</v>
+      </c>
+      <c r="J1138" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1138" t="inlineStr"/>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="1" t="n">
+        <v>1137</v>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1225.png</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr"/>
+      <c r="D1139" t="inlineStr"/>
+      <c r="E1139" t="inlineStr"/>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>NC1=NN=C(C2=CC=CC=C2O)C=C1OCCC12(CC1)CC(NC(=O)CCCCCCCCNC1=CC3=C(C=C1)C(=O)N(C1CCC(=O)NC1=O)C3=O)C2</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr"/>
+      <c r="H1139" t="inlineStr"/>
+      <c r="I1139" t="n">
+        <v>0.4533259276552987</v>
+      </c>
+      <c r="J1139" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1139" t="inlineStr"/>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="1" t="n">
+        <v>1138</v>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1229.png</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr"/>
+      <c r="D1140" t="inlineStr"/>
+      <c r="E1140" t="inlineStr"/>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>Nc1nnc(-c2ccccc2O)cc1OCC12CCC(C(=O)N3CCC(CN4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)CC3)(C1)C2</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr"/>
+      <c r="H1140" t="inlineStr"/>
+      <c r="I1140" t="n">
+        <v>0.2518343191358382</v>
+      </c>
+      <c r="J1140" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1140" t="inlineStr"/>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="1" t="n">
+        <v>1139</v>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1237.png</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr"/>
+      <c r="D1141" t="inlineStr"/>
+      <c r="E1141" t="inlineStr"/>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>Nc1nnc(-c2ccccc2O)cc1OCCC12CCC(NC(=O)CCOCCOCCNc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)(C1)C2</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr"/>
+      <c r="H1141" t="inlineStr"/>
+      <c r="I1141" t="n">
+        <v>0.6828816199340613</v>
+      </c>
+      <c r="J1141" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1141" t="inlineStr"/>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="1" t="n">
+        <v>1140</v>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1241.png</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr"/>
+      <c r="D1142" t="inlineStr"/>
+      <c r="E1142" t="inlineStr"/>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NC(=O)COCCOCCOCCOCC(=O)NCC345CC3(COC3=CC(C6=CC=CC=C6O)=NN=C3N)(C4)O5)C(C)(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr"/>
+      <c r="H1142" t="inlineStr"/>
+      <c r="I1142" t="n">
+        <v>0.5598097284019102</v>
+      </c>
+      <c r="J1142" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1142" t="inlineStr"/>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="1" t="n">
+        <v>1141</v>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1249.png</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr"/>
+      <c r="D1143" t="inlineStr"/>
+      <c r="E1143" t="inlineStr"/>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>CN(C1CC(Oc2ncc(-c3ccc4c5cnccc5n(C)c4c3)cn2)C1)C1CC2(C1)CN(CCCCCOc1ccc3c(c1)C(=O)N(C1CCC(=O)NC1=O)C3=O)C2</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr"/>
+      <c r="H1143" t="inlineStr"/>
+      <c r="I1143" t="n">
+        <v>0.8237156531709705</v>
+      </c>
+      <c r="J1143" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1143" t="inlineStr"/>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="1" t="n">
+        <v>1142</v>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1253.png</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr"/>
+      <c r="D1144" t="inlineStr"/>
+      <c r="E1144" t="inlineStr"/>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>CC1(Oc2ccc3n[nH]c(-c4cc(N5CC(F)(CN6CCN(CC7CCN(c8ccc9c(c8)C(=O)N(C8CCC(=O)NC8=O)C9=O)CC7)CC6)C5)ncn4)c3c2)CC1</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr"/>
+      <c r="H1144" t="inlineStr"/>
+      <c r="I1144" t="n">
+        <v>0.4388556786068096</v>
+      </c>
+      <c r="J1144" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1144" t="inlineStr"/>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="1" t="n">
+        <v>1143</v>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1257.png</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr"/>
+      <c r="D1145" t="inlineStr"/>
+      <c r="E1145" t="inlineStr"/>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(C(CN(C)C)NC(=O)[C@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CN2CCN(c3ccc(-c4cnnc(-c5ccccc5O)c4)cc3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr"/>
+      <c r="H1145" t="inlineStr"/>
+      <c r="I1145" t="n">
+        <v>0.515568401618447</v>
+      </c>
+      <c r="J1145" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1145" t="inlineStr"/>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="1" t="n">
+        <v>1144</v>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1261.png</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr"/>
+      <c r="D1146" t="inlineStr"/>
+      <c r="E1146" t="inlineStr"/>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>NC1=NN=C(C2=CC=CC=C2O)C=C1OCC123C=C(CNC(=O)CCCCCCCCCCNC4=CC5=C(C=C4)C(=O)N(C4CCC(=O)NC4=O)C5=O)C1C2C3</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr"/>
+      <c r="H1146" t="inlineStr"/>
+      <c r="I1146" t="n">
+        <v>0.4366307651218524</v>
+      </c>
+      <c r="J1146" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1146" t="inlineStr"/>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="1" t="n">
+        <v>1145</v>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1265.png</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr"/>
+      <c r="D1147" t="inlineStr"/>
+      <c r="E1147" t="inlineStr"/>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>Cn1c2ccncc2c2ccc(-c3cnc(N4CC(OC5CCN(CC(F)(F)CO[C@@H]6C[C@H](Oc7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)CC5)C4)c(C(F)(F)F)c3)cc21</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr"/>
+      <c r="H1147" t="inlineStr"/>
+      <c r="I1147" t="n">
+        <v>0.3595175769413622</v>
+      </c>
+      <c r="J1147" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1147" t="inlineStr"/>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="1" t="n">
+        <v>1146</v>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1277.png</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr"/>
+      <c r="D1148" t="inlineStr"/>
+      <c r="E1148" t="inlineStr"/>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>CCOc1ccc2n[nH]c(-c3cc(N4CCC(Cc5cccc(CC6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)c5)CC4)ncn3)c2c1</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr"/>
+      <c r="H1148" t="inlineStr"/>
+      <c r="I1148" t="n">
+        <v>0.5775800261896662</v>
+      </c>
+      <c r="J1148" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1148" t="inlineStr"/>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="1" t="n">
+        <v>1147</v>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1285.png</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr"/>
+      <c r="D1149" t="inlineStr"/>
+      <c r="E1149" t="inlineStr"/>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>O=C(C=CCN1CCC(N23CCN4(CC=CC=CCSC5=CC=CC6=C5CN(C5CCC(=O)NC5=O)C6=O)C5C2C4C53)CC1)NC1=CC2=C(NC3=CC=C(F)C(Cl)=C3)N=CN=C2C=C1O</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr"/>
+      <c r="H1149" t="inlineStr"/>
+      <c r="I1149" t="n">
+        <v>0.7900473427188397</v>
+      </c>
+      <c r="J1149" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1149" t="inlineStr"/>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="1" t="n">
+        <v>1148</v>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1329.png</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr"/>
+      <c r="D1150" t="inlineStr"/>
+      <c r="E1150" t="inlineStr"/>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CCN(c2nc(NCCC(=O)N(C)CCOCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)nc3c(F)c(-c4c(O)cccc4F)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr"/>
+      <c r="H1150" t="inlineStr"/>
+      <c r="I1150" t="n">
+        <v>0.2149668827297465</v>
+      </c>
+      <c r="J1150" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1150" t="inlineStr"/>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="1" t="n">
+        <v>1149</v>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_0/rb_1345.png</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr"/>
+      <c r="D1151" t="inlineStr"/>
+      <c r="E1151" t="inlineStr"/>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>NC1=NN=C(C2=CC=CC=C2O)C=C1OCC12(CC1)CC(C(=O)NCCOC1=CC=CC(OCCNC3=CC4=C(C=C3)C(=O)N(C3CCC(=O)NC3=O)C4=O)=C1)C2</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr"/>
+      <c r="H1151" t="inlineStr"/>
+      <c r="I1151" t="n">
+        <v>0.8380602283461082</v>
+      </c>
+      <c r="J1151" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1151" t="inlineStr"/>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="1" t="n">
+        <v>1150</v>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_1/rb_1106.png</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr"/>
+      <c r="D1152" t="inlineStr"/>
+      <c r="E1152" t="inlineStr"/>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(OCCN4CC5(C4)CN(C[C@H]4C[C@H](OC6CCN(c7ccn8c(n7)nc7ccccc78)CC6)C4)C5)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr"/>
+      <c r="H1152" t="inlineStr"/>
+      <c r="I1152" t="n">
+        <v>0.8332869985722006</v>
+      </c>
+      <c r="J1152" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1152" t="inlineStr"/>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="1" t="n">
+        <v>1151</v>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_1/rb_1110.png</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr"/>
+      <c r="D1153" t="inlineStr"/>
+      <c r="E1153" t="inlineStr"/>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CCN(c2nc(NCCC(=O)N(C)CCOc3ccc4c(c3)CN(C3CCC(=O)NC3=O)C4=O)nc3c(F)c(-c4c(O)cccc4F)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr"/>
+      <c r="H1153" t="inlineStr"/>
+      <c r="I1153" t="n">
+        <v>0.4642555624425059</v>
+      </c>
+      <c r="J1153" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1153" t="inlineStr"/>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="1" t="n">
+        <v>1152</v>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_1/rb_1114.png</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr"/>
+      <c r="D1154" t="inlineStr"/>
+      <c r="E1154" t="inlineStr"/>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2CC(O)CN2C(=O)[C@@H](NC(=O)COCCOCCOCCOCCOCCN(C)C(=O)CCNc2nc(N3CCN(C(N)=O)CC3)c3cc(Cl)c(-c4c(F)ccnc4O)c(F)c3n2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr"/>
+      <c r="H1154" t="inlineStr"/>
+      <c r="I1154" t="n">
+        <v>0.8108600044738618</v>
+      </c>
+      <c r="J1154" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1154" t="inlineStr"/>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="1" t="n">
+        <v>1153</v>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_1/rb_1118.png</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr"/>
+      <c r="D1155" t="inlineStr"/>
+      <c r="E1155" t="inlineStr"/>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>NC1=NN=C(C2=CC=CC=C2O)C=C1OCC123CCC(CNC(=O)CCCCCCCCCCNC4=CC=CC5=C4C(=O)N(C4CCC(=O)NC4=O)C5=O)(C1)C2C3</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr"/>
+      <c r="H1155" t="inlineStr"/>
+      <c r="I1155" t="n">
+        <v>0.3355220224942992</v>
+      </c>
+      <c r="J1155" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1155" t="inlineStr"/>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="1" t="n">
+        <v>1154</v>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_1/rb_1126.png</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr"/>
+      <c r="D1156" t="inlineStr"/>
+      <c r="E1156" t="inlineStr"/>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>CC1(Oc2ccc3n[nH]c(-c4cc(N5CCC(CN6CC(F)(CN7CCN(c8ccc9c(c8F)CN(C8CCC(=O)NC8=O)C9=O)CC7)C6)CC5)ncn4)c3c2)CC1</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr"/>
+      <c r="H1156" t="inlineStr"/>
+      <c r="I1156" t="n">
+        <v>0.7964514097394578</v>
+      </c>
+      <c r="J1156" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1156" t="inlineStr"/>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="1" t="n">
+        <v>1155</v>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_1/rb_1174.png</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr"/>
+      <c r="D1157" t="inlineStr"/>
+      <c r="E1157" t="inlineStr"/>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>CN1C2=C(C=NC=C2)C2=C1C=C(C1=CN=C(OC3456CC789(CN(CCOCCCOC%10CN(C%11=CC=C%12C(=O)N(C%13CCC(=O)NC%13=O)C(=O)C%12=C%11)C%10)C7C83)CC43C5C396)C=C1)C=C2</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr"/>
+      <c r="H1157" t="inlineStr"/>
+      <c r="I1157" t="n">
+        <v>0.3107493982485345</v>
+      </c>
+      <c r="J1157" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1157" t="inlineStr"/>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="1" t="n">
+        <v>1156</v>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_1/rb_1190.png</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr"/>
+      <c r="D1158" t="inlineStr"/>
+      <c r="E1158" t="inlineStr"/>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>CC1(Oc2ccc3n[nH]c(-c4cc(N5CCC(CN6CCN(CC7(F)CN(c8ccc9c(c8)C(=O)N(C8CCC(=O)NC8=O)C9=O)C7)CC6)CC5)ncn4)c3c2)CC1</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr"/>
+      <c r="H1158" t="inlineStr"/>
+      <c r="I1158" t="n">
+        <v>0.5968703046268249</v>
+      </c>
+      <c r="J1158" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1158" t="inlineStr"/>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="1" t="n">
+        <v>1157</v>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_1/rb_1198.png</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr"/>
+      <c r="D1159" t="inlineStr"/>
+      <c r="E1159" t="inlineStr"/>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>CC1(C)C(OC2=CC(Cl)=C(C#N)C=C2)C2(C)(C)C3N4C(=O)C5=CC=C(C=C5)OCCCCCOCC(=O)NC5C(=O)N67C[CH](O)(CC6C(=O)NCC6=CC=C(C8=CN=CS8)C=C6)C768CC5(C)(C)C(NC(=O)COCCCCCOC5=CC=C(C=C5)C(=O)N[CH]3412)C(=O)N6C(C(=O)NCC1=CC=C(C2=CN=CS2)C=C1)CC8O</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr"/>
+      <c r="H1159" t="inlineStr"/>
+      <c r="I1159" t="n">
+        <v>0.03508336476422</v>
+      </c>
+      <c r="J1159" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1159" t="inlineStr"/>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="1" t="n">
+        <v>1158</v>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_1/rb_1226.png</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr"/>
+      <c r="D1160" t="inlineStr"/>
+      <c r="E1160" t="inlineStr"/>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>CN(CCOCCNc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O)C(=O)CCNc1nc(N2CCN(C(=O)C(O)O)CC2)c2cc(Cl)c(-c3c(O)cccc3F)c(F)c2n1</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr"/>
+      <c r="H1160" t="inlineStr"/>
+      <c r="I1160" t="n">
+        <v>0.7757000625431733</v>
+      </c>
+      <c r="J1160" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1160" t="inlineStr"/>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="1" t="n">
+        <v>1159</v>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_1/rb_1246.png</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr"/>
+      <c r="D1161" t="inlineStr"/>
+      <c r="E1161" t="inlineStr"/>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>COc1c(N2CCC(N3CC(F)(CC4CCN(c5cc(-c6[nH]nc7ccc(OC8(C)CC8)cc67)ncn5)CC4)C3)CC2)ccc2c1CN(C1CCC(=O)NC1=O)C2=O</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr"/>
+      <c r="H1161" t="inlineStr"/>
+      <c r="I1161" t="n">
+        <v>0.8354091674600096</v>
+      </c>
+      <c r="J1161" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1161" t="inlineStr"/>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="1" t="n">
+        <v>1160</v>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_1/rb_1274.png</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr"/>
+      <c r="D1162" t="inlineStr"/>
+      <c r="E1162" t="inlineStr"/>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>Nc1nnc(-c2ccccc2O)cc1OCC1CCC(C(=O)N2CC3(CCN(CCCNc4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)C2)C1</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr"/>
+      <c r="H1162" t="inlineStr"/>
+      <c r="I1162" t="n">
+        <v>0.63850765643184</v>
+      </c>
+      <c r="J1162" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1162" t="inlineStr"/>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="1" t="n">
+        <v>1161</v>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_1/rb_1294.png</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr"/>
+      <c r="D1163" t="inlineStr"/>
+      <c r="E1163" t="inlineStr"/>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>Nc1nnc(-c2ccccc2O)cc1OCC12CCC(C(=O)N3CCC(CCN4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)CC3)(C1)C2</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr"/>
+      <c r="H1163" t="inlineStr"/>
+      <c r="I1163" t="n">
+        <v>0.78357341966171</v>
+      </c>
+      <c r="J1163" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1163" t="inlineStr"/>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="1" t="n">
+        <v>1162</v>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_1/rb_1310.png</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr"/>
+      <c r="D1164" t="inlineStr"/>
+      <c r="E1164" t="inlineStr"/>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>[C-]#CC1=C(C2=CC(O)=CC3=C2C=CC=C3)C(F)=C2N=C(NCCC(=O)N(C)CCOCCOCCOCCOC3=NOC(C(C(=O)N4C[CH](O)=CC4C(=O)NC(C)C4=CC=C(C5=C(C)N=CS5)C=C4OC)C(C)C)=C3)N=C(N3CCN(C(C)=O)CC3)C2=C1</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr"/>
+      <c r="H1164" t="inlineStr"/>
+      <c r="I1164" t="n">
+        <v>0.8214977462325269</v>
+      </c>
+      <c r="J1164" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1164" t="inlineStr"/>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="1" t="n">
+        <v>1163</v>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_1/rb_1330.png</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr"/>
+      <c r="D1165" t="inlineStr"/>
+      <c r="E1165" t="inlineStr"/>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NC(=O)CCCCCNC(=O)[CH]34CC(COC5=CC(C6=CC=CC=C6O)=NN=C5N)(C3)C4)C(C)(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr"/>
+      <c r="H1165" t="inlineStr"/>
+      <c r="I1165" t="n">
+        <v>0.583692656076385</v>
+      </c>
+      <c r="J1165" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1165" t="inlineStr"/>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="1" t="n">
+        <v>1164</v>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_1/rb_1338.png</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr"/>
+      <c r="D1166" t="inlineStr"/>
+      <c r="E1166" t="inlineStr"/>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr"/>
+      <c r="H1166" t="inlineStr"/>
+      <c r="I1166" t="n">
+        <v>0.767130062290746</v>
+      </c>
+      <c r="J1166" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1166" t="inlineStr"/>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="1" t="n">
+        <v>1165</v>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_1/rb_1346.png</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr"/>
+      <c r="D1167" t="inlineStr"/>
+      <c r="E1167" t="inlineStr"/>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>Nc1nnc(-c2ccccc2O)cc1OCCC1CC(NC(=O)C2CCN(CCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)CC2)C1</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr"/>
+      <c r="H1167" t="inlineStr"/>
+      <c r="I1167" t="n">
+        <v>0.7583957880694752</v>
+      </c>
+      <c r="J1167" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1167" t="inlineStr"/>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="1" t="n">
+        <v>1166</v>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1115.png</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr"/>
+      <c r="D1168" t="inlineStr"/>
+      <c r="E1168" t="inlineStr"/>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCCC(=O)NCC23CC(COc4cc(-c5ccccc5O)nnc4N)(C2)C3)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr"/>
+      <c r="H1168" t="inlineStr"/>
+      <c r="I1168" t="n">
+        <v>0.5139175507740065</v>
+      </c>
+      <c r="J1168" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1168" t="inlineStr"/>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="1" t="n">
+        <v>1167</v>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1119.png</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr"/>
+      <c r="D1169" t="inlineStr"/>
+      <c r="E1169" t="inlineStr"/>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>COc1cc2ncnc(Nc3ccc(F)c(Cl)c3)c2cc1NC(=O)/C=C/CN1CCC(N2CCN(C(=O)COCCOCCOCCOCCOCCSc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)CC2)CC1</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr"/>
+      <c r="H1169" t="inlineStr"/>
+      <c r="I1169" t="n">
+        <v>0.8326251387147536</v>
+      </c>
+      <c r="J1169" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1169" t="inlineStr"/>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="1" t="n">
+        <v>1168</v>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1123.png</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr"/>
+      <c r="D1170" t="inlineStr"/>
+      <c r="E1170" t="inlineStr"/>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>CC1(CCOc2cc(-c3ccccc3O)nnc2N)C=C(NC(=O)CCOCCOCCNc2ccc3c(c2)C(=O)N(C2CCC(=O)NC2=O)C3=O)C1</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr"/>
+      <c r="H1170" t="inlineStr"/>
+      <c r="I1170" t="n">
+        <v>0.55652878671976</v>
+      </c>
+      <c r="J1170" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1170" t="inlineStr"/>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="1" t="n">
+        <v>1169</v>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1139.png</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr"/>
+      <c r="D1171" t="inlineStr"/>
+      <c r="E1171" t="inlineStr"/>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>Nc1nnc(-c2ccccc2O)cc1OCC1CC(C(=O)N2CC(CN3CCN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)C2)C1</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr"/>
+      <c r="H1171" t="inlineStr"/>
+      <c r="I1171" t="n">
+        <v>0.8267025062992579</v>
+      </c>
+      <c r="J1171" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1171" t="inlineStr"/>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="1" t="n">
+        <v>1170</v>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1147.png</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr"/>
+      <c r="D1172" t="inlineStr"/>
+      <c r="E1172" t="inlineStr"/>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>CCN(CCOCCOCCOCCOCCc1cc(Cl)cc(NC(=O)NCc2ccc3c(c2)CN(C2CCC(=O)NC2=O)C3=O)c1)CCOc1ccc(C(=O)c2c(-c3ccc(O)cc3)sc3cc(O)ccc23)cc1</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr"/>
+      <c r="H1172" t="inlineStr"/>
+      <c r="I1172" t="n">
+        <v>0.8415552659277385</v>
+      </c>
+      <c r="J1172" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1172" t="inlineStr"/>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="1" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1195.png</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr"/>
+      <c r="D1173" t="inlineStr"/>
+      <c r="E1173" t="inlineStr"/>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>Nc1nnc(-c2ccccc2O)cc1OCC1CC(C(=O)NCCOC2CN(c3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)C2)C1</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr"/>
+      <c r="H1173" t="inlineStr"/>
+      <c r="I1173" t="n">
+        <v>0.8423842940680013</v>
+      </c>
+      <c r="J1173" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1173" t="inlineStr"/>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="1" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1203.png</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr"/>
+      <c r="D1174" t="inlineStr"/>
+      <c r="E1174" t="inlineStr"/>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)COCCOCCOCCOCCOCCN(C)C(=O)CCNc2nc(N3CCN(C(=O)C(=O)O)CC3)c3cc(Cl)c(-c4c(F)ccnc4O)c(F)c3n2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr"/>
+      <c r="H1174" t="inlineStr"/>
+      <c r="I1174" t="n">
+        <v>0.5421717652754852</v>
+      </c>
+      <c r="J1174" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1174" t="inlineStr"/>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="1" t="n">
+        <v>1173</v>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1207.png</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr"/>
+      <c r="D1175" t="inlineStr"/>
+      <c r="E1175" t="inlineStr"/>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>CC1=C2C34=C5C=C=36=C3=CC(CNC(=O)C7CC(O)CN7C(=O)C(NC(=O)CCCCCCCCCCCCC(=O)NCC78CC(COC9=CC(C%10=CC=CC=C%10O)=NN=C9N)(C7)C8)C(C)(C)C)=CC7=C4C=72536=C1C</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr"/>
+      <c r="H1175" t="inlineStr"/>
+      <c r="I1175" t="n">
+        <v>0.09343093585864932</v>
+      </c>
+      <c r="J1175" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1175" t="inlineStr"/>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="1" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1219.png</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr"/>
+      <c r="D1176" t="inlineStr"/>
+      <c r="E1176" t="inlineStr"/>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CCN(c2nc(NCCC(=O)NCCOCCOCCOCCOCCOc3cc(-c4scnc4C)ccc3CNC(=O)[C@@H]3C[C@@H](O)CN3C(=O)C(=C(C)C)c3cc(C)no3)nc3c(F)c(-c4cc(O)cc5ccccc45)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr"/>
+      <c r="H1176" t="inlineStr"/>
+      <c r="I1176" t="n">
+        <v>0.6045878158673594</v>
+      </c>
+      <c r="J1176" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1176" t="inlineStr"/>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="1" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1235.png</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr"/>
+      <c r="D1177" t="inlineStr"/>
+      <c r="E1177" t="inlineStr"/>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>Nc1nnc(-c2ccccc2O)cc1OCC12COC1(C(=O)N1CCC(CCCCN3CCN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)CC1)C2</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr"/>
+      <c r="H1177" t="inlineStr"/>
+      <c r="I1177" t="n">
+        <v>0.4609376159566883</v>
+      </c>
+      <c r="J1177" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1177" t="inlineStr"/>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="1" t="n">
+        <v>1176</v>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1255.png</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr"/>
+      <c r="D1178" t="inlineStr"/>
+      <c r="E1178" t="inlineStr"/>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>C#CC1=C(F)C=CC2=C1C(C1=C(F)C34=NC567=NC89(N%10CCCC(C)(O)C%10)=C3%10(C#C)C(=N1)C48=C%10(N5=CO6CCCNCCNCC1CCN3CC1C1(CCN(CC1)C14=CC=C5(C(=O)N(C6CCC(=O)NC6=O)C(=O)C5=C1)C15=C4C3=CC=C1C(=O)N(C1CCC(=O)NC1=O)C5=O)CN1CCN(CC1)CC1(CC1)CO7)N91CCCC(C)(O)C1)=CC(O)=C2</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr"/>
+      <c r="H1178" t="inlineStr"/>
+      <c r="I1178" t="n">
+        <v>0.001973469890866523</v>
+      </c>
+      <c r="J1178" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1178" t="inlineStr"/>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="1" t="n">
+        <v>1177</v>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1263.png</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr"/>
+      <c r="D1179" t="inlineStr"/>
+      <c r="E1179" t="inlineStr"/>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)COCCOCCOCCOCCOCCOC2CCN(C[C@@H](C)Oc3nc(N4CCN(C(=O)C(O)O)CC4)c4cc(Cl)c(-c5cc(O)cc6ccccc56)c(F)c4n3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr"/>
+      <c r="H1179" t="inlineStr"/>
+      <c r="I1179" t="n">
+        <v>0.8429034506593704</v>
+      </c>
+      <c r="J1179" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1179" t="inlineStr"/>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="1" t="n">
+        <v>1178</v>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1271.png</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr"/>
+      <c r="D1180" t="inlineStr"/>
+      <c r="E1180" t="inlineStr"/>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CCN(c2nc(NCCC(=O)N(C)CCOCCOCCOCCOc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)nc3c(F)c(-c4c(O)cccc4F)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr"/>
+      <c r="H1180" t="inlineStr"/>
+      <c r="I1180" t="n">
+        <v>0.7835142484167238</v>
+      </c>
+      <c r="J1180" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1180" t="inlineStr"/>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="1" t="n">
+        <v>1179</v>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1295.png</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr"/>
+      <c r="D1181" t="inlineStr"/>
+      <c r="E1181" t="inlineStr"/>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>CN(C(=O)C12(COCCCCOC3=CC4=C(C=C3)C(=O)N(C3CCC(=O)NC3=O)C4=O)CC1(C)C2)C1CC(OC2=NC=C(C3=CC=C(C4=CC=CN=C4)C=C3)C=C2)C1.CN1C2=C(C=NC=C2)C2=C1C=C(C1=CN=C(OC3CC(N(C)C(=O)C4(C)CC4)C3)C=C1)C=C2</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr"/>
+      <c r="H1181" t="inlineStr"/>
+      <c r="I1181" t="n">
+        <v>0.1275535148455663</v>
+      </c>
+      <c r="J1181" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1181" t="inlineStr"/>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="1" t="n">
+        <v>1180</v>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1299.png</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr"/>
+      <c r="D1182" t="inlineStr"/>
+      <c r="E1182" t="inlineStr"/>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CCN(c2nc(NCCC(=O)N(C)CCOCCOCCOCCOc3ccc4c(c3)CN(C3CCC(=O)NC3=O)C4=O)nc3c(F)c(-c4c(O)cccc4F)c(Cl)cc23)CC1</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr"/>
+      <c r="H1182" t="inlineStr"/>
+      <c r="I1182" t="n">
+        <v>0.8021975153419155</v>
+      </c>
+      <c r="J1182" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1182" t="inlineStr"/>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="1" t="n">
+        <v>1181</v>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1303.png</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr"/>
+      <c r="D1183" t="inlineStr"/>
+      <c r="E1183" t="inlineStr"/>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>CCN(CCCC(=O)N[C@@H]1CCCN(c2cnc(C(N)=O)c(Nc3cc(C)ns3)n2)C1)CC1CN(c2ccc3c(c2)C(=O)N(C2CCC(=O)NC2=O)C3=O)C1</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr"/>
+      <c r="H1183" t="inlineStr"/>
+      <c r="I1183" t="n">
+        <v>0.5161525267593754</v>
+      </c>
+      <c r="J1183" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1183" t="inlineStr"/>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="1" t="n">
+        <v>1182</v>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1307.png</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr"/>
+      <c r="D1184" t="inlineStr"/>
+      <c r="E1184" t="inlineStr"/>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>Cn1c2ccncc2c2ccc(-c3cnc(O[C@@H]4C[C@@H](Oc5ccc(C#CCOCCOc6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)nc5)C4)c(C#N)c3)cc21</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr"/>
+      <c r="H1184" t="inlineStr"/>
+      <c r="I1184" t="n">
+        <v>0.7653313152600512</v>
+      </c>
+      <c r="J1184" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1184" t="inlineStr"/>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="1" t="n">
+        <v>1183</v>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1319.png</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr"/>
+      <c r="D1185" t="inlineStr"/>
+      <c r="E1185" t="inlineStr"/>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>CC1(Oc2ccc3n[nH]c(-c4cc(N5CCC(O[C@@H]6C[C@@H](N7CC[C@@H](c8ccc9c(c8)CN(C8CCC(=O)NC8=O)C9=O)[C@@H](F)C7)C6)CC5)ncn4)c3c2)CC1</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr"/>
+      <c r="H1185" t="inlineStr"/>
+      <c r="I1185" t="n">
+        <v>0.3969351934101498</v>
+      </c>
+      <c r="J1185" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1185" t="inlineStr"/>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="1" t="n">
+        <v>1184</v>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_2/rb_1339.png</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr"/>
+      <c r="D1186" t="inlineStr"/>
+      <c r="E1186" t="inlineStr"/>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>Nc1nnc(-c2ccccc2O)cc1OCC12CC(C(=O)NC3CCN(CCOc4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)(C1)C2</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr"/>
+      <c r="H1186" t="inlineStr"/>
+      <c r="I1186" t="n">
+        <v>0.8427881632260776</v>
+      </c>
+      <c r="J1186" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1186" t="inlineStr"/>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="1" t="n">
+        <v>1185</v>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_3/rb_1120.png</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr"/>
+      <c r="D1187" t="inlineStr"/>
+      <c r="E1187" t="inlineStr"/>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>Nc1nnc(-c2ccccc2O)cc1OCC12CC(C(=O)N3CCN(CCCOCC#Cc4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)C1C2</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr"/>
+      <c r="H1187" t="inlineStr"/>
+      <c r="I1187" t="n">
+        <v>0.3531065119276005</v>
+      </c>
+      <c r="J1187" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1187" t="inlineStr"/>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="1" t="n">
+        <v>1186</v>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_3/rb_1124.png</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr"/>
+      <c r="D1188" t="inlineStr"/>
+      <c r="E1188" t="inlineStr"/>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>COc1c(N2CCC(CN3CCN(CC4CCN(c5cc(-c6n[nH]c7cnc(OC8(C)CC8)cc67)ncn5)CC4)CC3)CC2)ccc2c1CN(C1CCC(=O)NC1=O)C2=O</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr"/>
+      <c r="H1188" t="inlineStr"/>
+      <c r="I1188" t="n">
+        <v>0.8284054325929522</v>
+      </c>
+      <c r="J1188" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1188" t="inlineStr"/>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="1" t="n">
+        <v>1187</v>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_3/rb_1128.png</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr"/>
+      <c r="D1189" t="inlineStr"/>
+      <c r="E1189" t="inlineStr"/>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCCCCCCCCCCCCCC(=O)NC2C=C(CCOc3cc(-c4ccccc4O)nnc3N)OC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr"/>
+      <c r="H1189" t="inlineStr"/>
+      <c r="I1189" t="n">
+        <v>0.7360525925297805</v>
+      </c>
+      <c r="J1189" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1189" t="inlineStr"/>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="1" t="n">
+        <v>1188</v>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_3/rb_1148.png</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr"/>
+      <c r="D1190" t="inlineStr"/>
+      <c r="E1190" t="inlineStr"/>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>Nc1nnc(-c2ccccc2O)cc1OCC1C[C](C(=O)N2CCN(CC3CN(c4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)C3)CC2)C1 |^1:18|</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr"/>
+      <c r="H1190" t="inlineStr"/>
+      <c r="I1190" t="n">
+        <v>0.7818513234898459</v>
+      </c>
+      <c r="J1190" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1190" t="inlineStr"/>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="1" t="n">
+        <v>1189</v>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_3/rb_1152.png</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr"/>
+      <c r="D1191" t="inlineStr"/>
+      <c r="E1191" t="inlineStr"/>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>Nc1nnc(-c2ccccc2O)cc1OCC12CC(CNC(=O)C3CCN(CCOc4ccc5c(c4)C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)(C1)C2</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr"/>
+      <c r="H1191" t="inlineStr"/>
+      <c r="I1191" t="n">
+        <v>0.8053787394468883</v>
+      </c>
+      <c r="J1191" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1191" t="inlineStr"/>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="1" t="n">
+        <v>1190</v>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_3/rb_1156.png</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr"/>
+      <c r="D1192" t="inlineStr"/>
+      <c r="E1192" t="inlineStr"/>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NC(=O)COCCOCCNC(=O)C3456CC7(COC8=CC(C9=CC=CC=C9O)=NN=C8N)C38O4C75O86)C(C)(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr"/>
+      <c r="H1192" t="inlineStr"/>
+      <c r="I1192" t="n">
+        <v>0.2595352995093928</v>
+      </c>
+      <c r="J1192" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1192" t="inlineStr"/>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="1" t="n">
+        <v>1191</v>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_3/rb_1180.png</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr"/>
+      <c r="D1193" t="inlineStr"/>
+      <c r="E1193" t="inlineStr"/>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>Cn1c2ccncc2c2ccc(-c3cnc(N4CC(OC5CCN(CCCCCOc6ccc7c(c6)C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)C4)c(C#N)c3)cc21</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr"/>
+      <c r="H1193" t="inlineStr"/>
+      <c r="I1193" t="n">
+        <v>0.8321778228393703</v>
+      </c>
+      <c r="J1193" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1193" t="inlineStr"/>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="1" t="n">
+        <v>1192</v>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_3/rb_1220.png</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr"/>
+      <c r="D1194" t="inlineStr"/>
+      <c r="E1194" t="inlineStr"/>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>COC1=C(C(C)NC(=O)C2CC(O)CN2C(=O)C(C(C)C)C2(C=COCCOCCN(C)C(=O)CCNC3=NC4=C(F)C(C5=C6CCC=CC6=CC(O)=C5)=C(Cl)C=C4C(N4CCN(C(C)=O)CC4)=N3)=NO2)C=CC(C2=C(C)N=CS2)=C1</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr"/>
+      <c r="H1194" t="inlineStr"/>
+      <c r="I1194" t="n">
+        <v>0.254958962381198</v>
+      </c>
+      <c r="J1194" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1194" t="inlineStr"/>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="1" t="n">
+        <v>1193</v>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_3/rb_1248.png</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr"/>
+      <c r="D1195" t="inlineStr"/>
+      <c r="E1195" t="inlineStr"/>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>CCCC[C@H](NC(=O)c1cc2cc(C(F)(F)P(=O)(O)O)ccc2[nH]1)C(=O)N1C[C@H](C(=O)N2CCC(CCCCC#Cc3cccc4c3CN(C3CCC(=O)NC3=O)C4=O)CC2)C[C@H]1C(=O)N[C@H](CCC(N)=O)C(=O)NC(c1ccccc1)c1ccccc1</t>
+        </is>
+      </c>
+      <c r="G1195" t="inlineStr"/>
+      <c r="H1195" t="inlineStr"/>
+      <c r="I1195" t="n">
+        <v>0.7902916388875627</v>
+      </c>
+      <c r="J1195" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1195" t="inlineStr"/>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="1" t="n">
+        <v>1194</v>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_3/rb_1252.png</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr"/>
+      <c r="D1196" t="inlineStr"/>
+      <c r="E1196" t="inlineStr"/>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>NC1=NN=C(C2=CC=CC=C2O)C=C1OCC123(CC1)CC(CNC(=O)C1CC1CNC(=O)COC1=CC4C(=O)N(C5CCC(=O)NC5=O)C(=O)C4C=C1)C2C3</t>
+        </is>
+      </c>
+      <c r="G1196" t="inlineStr"/>
+      <c r="H1196" t="inlineStr"/>
+      <c r="I1196" t="n">
+        <v>0.4683906550424789</v>
+      </c>
+      <c r="J1196" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1196" t="inlineStr"/>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="1" t="n">
+        <v>1195</v>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_3/rb_1268.png</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr"/>
+      <c r="D1197" t="inlineStr"/>
+      <c r="E1197" t="inlineStr"/>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>C#CC12=C(F)C=C3C45=C167C31=C243C62=C468N=C9N4%10=C2(C6(F)=C24N=C6%11%12N=C%13%14%15%16C2%17=C%10C94%13=C=%17(N%142CCCC4(C)OC9(C)(O)CCCN%15(C9)C42)N6%16=CO%11CCCNCCNCCCCNC2=CC=C4C(=O)N(C6CCC(=O)NC6=O)C(=O)C4(=C2)C24=CC=C(C=C2C(=O)N(C2CCC(=O)NC2=O)C4=O)N2CCC(CC2)CN2CCN(CC2)CC2(CC2)CO%12)C738=CC=C51</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr"/>
+      <c r="H1197" t="inlineStr"/>
+      <c r="I1197" t="n">
+        <v>0.0003106025543079181</v>
+      </c>
+      <c r="J1197" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1197" t="inlineStr"/>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="1" t="n">
+        <v>1196</v>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_3/rb_1316.png</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr"/>
+      <c r="D1198" t="inlineStr"/>
+      <c r="E1198" t="inlineStr"/>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>CC1=NN=C2C(CC(=O)NCCOCCCOCC(=O)NC(C(=O)N3CC(O)C4C[CH]43C(=O)NC(C)C3=CC=C(C4=C(C)N=CS4)C=C3)C(C)(C)C)N=C(C3=CC=C(Cl)C=C3)C3=C(SC(C)=C3C)N12.[HH]</t>
+        </is>
+      </c>
+      <c r="G1198" t="inlineStr"/>
+      <c r="H1198" t="inlineStr"/>
+      <c r="I1198" t="n">
+        <v>0.2220490955619864</v>
+      </c>
+      <c r="J1198" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1198" t="inlineStr"/>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="1" t="n">
+        <v>1197</v>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_3/rb_1328.png</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr"/>
+      <c r="D1199" t="inlineStr"/>
+      <c r="E1199" t="inlineStr"/>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>CN(CCOCCOCCOCCNc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O)C(=O)CCNc1nc(N2CCN(C(=O)C(O)O)CC2)c2cc(Cl)c(-c3c(O)cccc3F)c(F)c2n1</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr"/>
+      <c r="H1199" t="inlineStr"/>
+      <c r="I1199" t="n">
+        <v>0.3951853978948844</v>
+      </c>
+      <c r="J1199" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1199" t="inlineStr"/>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="1" t="n">
+        <v>1198</v>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T021432_3/rb_1340.png</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr"/>
+      <c r="D1200" t="inlineStr"/>
+      <c r="E1200" t="inlineStr"/>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>COc1c(N2CCN(CC3(F)CCN(CC4CCN(c5cc(-c6n[nH]c7cnc(OC8(C)CC8)cc67)ncn5)CC4)CC3)CC2)ccc2c1CN(C1CCC(=O)NC1=O)C2=O</t>
+        </is>
+      </c>
+      <c r="G1200" t="inlineStr"/>
+      <c r="H1200" t="inlineStr"/>
+      <c r="I1200" t="n">
+        <v>0.8031569666629649</v>
+      </c>
+      <c r="J1200" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1200" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1200"/>
+  <dimension ref="A1:K1299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35251,6 +35251,2877 @@
       </c>
       <c r="K1200" t="inlineStr"/>
     </row>
+    <row r="1201">
+      <c r="A1201" s="1" t="n">
+        <v>1199</v>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1351.png</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr"/>
+      <c r="D1201" t="inlineStr"/>
+      <c r="E1201" t="inlineStr"/>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>CC(C)(O)c1cc2nc(C3CCC(CN4CC5(CC(CCNc6cccc7c6C(=O)N(C6CCC(=O)NC6=O)C7=O)C5)C4)CC3)sc2cc1NC(=O)c1cccc(C(F)F)n1</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr"/>
+      <c r="H1201" t="inlineStr"/>
+      <c r="I1201" t="n">
+        <v>0.839830421213857</v>
+      </c>
+      <c r="J1201" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1201" t="inlineStr"/>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1383.png</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr"/>
+      <c r="D1202" t="inlineStr"/>
+      <c r="E1202" t="inlineStr"/>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1cnn2c(-c3cc(NC)c(-c4nnc(N5CCN(C(=O)CN6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)s4)cn3)ccc2c1</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr"/>
+      <c r="H1202" t="inlineStr"/>
+      <c r="I1202" t="n">
+        <v>0.738029522529674</v>
+      </c>
+      <c r="J1202" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1202" t="inlineStr"/>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="1" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1395.png</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr"/>
+      <c r="D1203" t="inlineStr"/>
+      <c r="E1203" t="inlineStr"/>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>CC(=O)CC[C@H](NC(=O)[C@@H]1CC[C@@H]2CCN(C(=O)CCCCCC#Cc3cccc4c3CN(C3CCC(=O)NC3=O)C4=O)C[C@H](NC(=O)c3cc4cc(C(F)(F)P(=O)(O)O)ccc4s3)C(=O)N21)c1ncc(-c2ccc(C(C)(C)C)cc2)s1</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr"/>
+      <c r="H1203" t="inlineStr"/>
+      <c r="I1203" t="n">
+        <v>0.8403955524333437</v>
+      </c>
+      <c r="J1203" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1203" t="inlineStr"/>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="1" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1399.png</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr"/>
+      <c r="D1204" t="inlineStr"/>
+      <c r="E1204" t="inlineStr"/>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>COC1=CC2=C(C=C1NC(=O)C1=CC=CC(C(C)(F)F)=N1)SC(C1CCC(CN3CCC4(CC3)CC(CCNC35=C6C=CC=C3=C(=C5)C=CC(=O)N(C3CCC(=O)NC3=O)C6=O)C4)CC1)=N2</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr"/>
+      <c r="H1204" t="inlineStr"/>
+      <c r="I1204" t="n">
+        <v>0.3916276550914051</v>
+      </c>
+      <c r="J1204" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1204" t="inlineStr"/>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="1" t="n">
+        <v>1203</v>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1403.png</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr"/>
+      <c r="D1205" t="inlineStr"/>
+      <c r="E1205" t="inlineStr"/>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>CN(C[C@H]1CC[C@@H](N2Cc3cc(C(C)(C)O)c(NC(=O)c4cccc(C(F)(F)F)n4)cc3C2=O)CC1)C1CCC2(CC1)CC(Nc1cccc3c1C(=O)N(C1CCC(=O)NC1=O)C3=O)C2</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr"/>
+      <c r="H1205" t="inlineStr"/>
+      <c r="I1205" t="n">
+        <v>0.386899685471886</v>
+      </c>
+      <c r="J1205" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1205" t="inlineStr"/>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="1" t="n">
+        <v>1204</v>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1407.png</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr"/>
+      <c r="D1206" t="inlineStr"/>
+      <c r="E1206" t="inlineStr"/>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>CC1=NC(C(=O)NC2=C3=C24(NC(=O)C2=CC(F)=CC(C)=N2)=CC25=C(C=C4C(C)(C)O)N=C4(S2)[CH]2(CCC(CNCC(C)(C)C)CC2)C2(C6CCC(CN(C)CC(C)(C)C)CC6)=NC=C3S425)=CC(F)=C1</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr"/>
+      <c r="H1206" t="inlineStr"/>
+      <c r="I1206" t="n">
+        <v>0.04439771811404271</v>
+      </c>
+      <c r="J1206" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1206" t="inlineStr"/>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="1" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1423.png</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr"/>
+      <c r="D1207" t="inlineStr"/>
+      <c r="E1207" t="inlineStr"/>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>C=CC(=CC=CC1=C(C)N=CS1)C(C)NC(=O)C1CC(O)CN1C(=O)C(C1=CC(OCCN2CCC(OC3CC(OC45=CC6(N78CCCC7CN(C7=C(N)N=NC(C9=C(O)C=CC=C9)=C7)CC8)=N4C=C56)C3)CC2C)=NO1)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr"/>
+      <c r="H1207" t="inlineStr"/>
+      <c r="I1207" t="n">
+        <v>0.1405970037209854</v>
+      </c>
+      <c r="J1207" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1207" t="inlineStr"/>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="1" t="n">
+        <v>1206</v>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1431.png</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr"/>
+      <c r="D1208" t="inlineStr"/>
+      <c r="E1208" t="inlineStr"/>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1cnn2c(-c3cc(NC)c(-c4nnc(N5CCN(C6CCN(C(=O)Cc7ccc8c(c7)CN(C7CCC(=O)NC7=O)C8=O)CC6)CC5)s4)cn3)ccc2c1</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr"/>
+      <c r="H1208" t="inlineStr"/>
+      <c r="I1208" t="n">
+        <v>0.808557876964864</v>
+      </c>
+      <c r="J1208" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1208" t="inlineStr"/>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="1" t="n">
+        <v>1207</v>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1435.png</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr"/>
+      <c r="D1209" t="inlineStr"/>
+      <c r="E1209" t="inlineStr"/>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@H](c2cc(N3CCN(C[C@H]4C[C@H](Oc5cc(N6C(C)CN(c7cc(-c8ccccc8O)nnc7N)CC6C)ccn5)C4)CC3)no2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr"/>
+      <c r="H1209" t="inlineStr"/>
+      <c r="I1209" t="n">
+        <v>0.8195640262217769</v>
+      </c>
+      <c r="J1209" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1209" t="inlineStr"/>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="1" t="n">
+        <v>1208</v>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1451.png</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr"/>
+      <c r="D1210" t="inlineStr"/>
+      <c r="E1210" t="inlineStr"/>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C([CH]NC(=O)C3CC(O)CN3C(=O)C(C3=CC(OCCN4CCC(OC5CC(OC678=N9C%10=C6C6(N%11C%12CCC%11CN(C%11=CC(C%13=C(O)C=CC=C%13)=NN=C%11N)C%12)(=C7)=N=8%10=C9=C6)C5)CC4)=NO3)C(C)C)C=C2)SC=N1.FCF</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr"/>
+      <c r="H1210" t="inlineStr"/>
+      <c r="I1210" t="n">
+        <v>0.02266591588256573</v>
+      </c>
+      <c r="J1210" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1210" t="inlineStr"/>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="1" t="n">
+        <v>1209</v>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1459.png</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr"/>
+      <c r="D1211" t="inlineStr"/>
+      <c r="E1211" t="inlineStr"/>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1cnn2c(-c3cc(NC)c(-c4nnc(N5CCN(C(=O)C6CCN(Cc7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)s4)cn3)ccc2c1</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr"/>
+      <c r="H1211" t="inlineStr"/>
+      <c r="I1211" t="n">
+        <v>0.8092358573406258</v>
+      </c>
+      <c r="J1211" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1211" t="inlineStr"/>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="1" t="n">
+        <v>1210</v>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1463.png</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr"/>
+      <c r="D1212" t="inlineStr"/>
+      <c r="E1212" t="inlineStr"/>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>*c1ccc(C[C@H](NC(=O)[C@H](CCC(N)=O)NC(=O)[C@@H]2CC[C@@H]3CCN(CC(F)F)C[C@H](NC(=O)c4cc5cc(C(F)(F)P(=O)(O)O)ccc5s4)C(=O)N32)C(=O)N2CCN(CCCNc3cccc4c3CN(C3CCC(=O)NC3=O)C4=O)CC2)cc1 |$tBu;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr"/>
+      <c r="H1212" t="inlineStr"/>
+      <c r="I1212" t="n">
+        <v>0.8206320412797321</v>
+      </c>
+      <c r="J1212" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1212" t="inlineStr"/>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="1" t="n">
+        <v>1211</v>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1487.png</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr"/>
+      <c r="D1213" t="inlineStr"/>
+      <c r="E1213" t="inlineStr"/>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>*C1=CC=C(CC(NC(=O)C(CCC(N)=O)NC(=O)C2CCC(CCN3CC456FC(F)(F4)(F5)C36)N2C(=O)C(C)NC(=O)C2=CC3=C(C=CC(C(*)(F)F)=C3)S2)C(=O)N2CCC(CCNC3=CC4=C(C=C3)C(=O)N(C3CCC(=O)NC3=O)C4)CC2)C=C1 |$Ali;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;AO3N;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr"/>
+      <c r="H1213" t="inlineStr"/>
+      <c r="I1213" t="n">
+        <v>0.2042048291506326</v>
+      </c>
+      <c r="J1213" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1213" t="inlineStr"/>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="1" t="n">
+        <v>1212</v>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1495.png</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr"/>
+      <c r="D1214" t="inlineStr"/>
+      <c r="E1214" t="inlineStr"/>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>C=C/C(=C\C=C\[C@H](CCCC(N)=O)NC(=O)[C@@H]1C[C@@H](O)CN1C(=O)[C@H](c1cc(OCCN2CCC(OC3C[C@@H](Oc4cc(N5C6CCC5CN(c5cc(-c7ccccc7O)nnc5N)C6)ccn4)C3)CC2)no1)C(C)C)c1scnc1C</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr"/>
+      <c r="H1214" t="inlineStr"/>
+      <c r="I1214" t="n">
+        <v>0.1139596982573711</v>
+      </c>
+      <c r="J1214" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1214" t="inlineStr"/>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="1" t="n">
+        <v>1213</v>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1499.png</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr"/>
+      <c r="D1215" t="inlineStr"/>
+      <c r="E1215" t="inlineStr"/>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>CC=CC=CC=CC(C)NC(=O)C1CC(O)CN1C(=O)C(CC)C1=CC(N2CCC(CN34CC56C3C3N578C5C49(COC9)C7N3564O3C56C7C9C5%10C5%11(CC73%10(C5)O684)OC345=C6C7(=NC=CC8%10%12=C73C637(=NC=C483)N%10346C8%10CCC3%13%14C3N%15%16%17C%18C4%19CCC6(C%13%15N%1834(C8)C%163=C(N)N=N6C8%13%15=C%16=C6%18(=C=83C%16%174=C(N)N=N%13%18)C3(=C(O)C=CC=C3)C3=CC=CC(O)=C3%15)N%10%19%14%127)O9%115)CC2)=NO1</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr"/>
+      <c r="H1215" t="inlineStr"/>
+      <c r="I1215" t="n">
+        <v>1.217746528977456e-06</v>
+      </c>
+      <c r="J1215" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1215" t="inlineStr"/>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="1" t="n">
+        <v>1214</v>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1515.png</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr"/>
+      <c r="D1216" t="inlineStr"/>
+      <c r="E1216" t="inlineStr"/>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>CC1(CNCC2CCC(C3=NC4=C(C=C(NC(=O)C5=CC=NC(C(F)(F)F)=N5)C(C(C)(C)O)=C4)S3)CC2)CC(CCN2C3=C4C(=O)N(C5CCC(=O)NC5=O)C(=O)C4(=CC=C3)C34=C2(NCCC25CC6(C)C7C2C76C5)C=CC=C3C(=O)N(C2CCC(=O)NC2=O)C4=O)C1</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr"/>
+      <c r="H1216" t="inlineStr"/>
+      <c r="I1216" t="n">
+        <v>0.004439164346014058</v>
+      </c>
+      <c r="J1216" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1216" t="inlineStr"/>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="1" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1519.png</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr"/>
+      <c r="D1217" t="inlineStr"/>
+      <c r="E1217" t="inlineStr"/>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@H](c2cc(N3CCCC(CN4CCC(O[C@@H]5C[C@@H](Oc6cc(N7C8CCC7CN(c7cc(-c9ccccc9O)nnc7N)C8)ccn6)C5)CC4)C3)no2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr"/>
+      <c r="H1217" t="inlineStr"/>
+      <c r="I1217" t="n">
+        <v>0.5399521084193895</v>
+      </c>
+      <c r="J1217" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1217" t="inlineStr"/>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="1" t="n">
+        <v>1216</v>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1523.png</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr"/>
+      <c r="D1218" t="inlineStr"/>
+      <c r="E1218" t="inlineStr"/>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>COc1cc2nc([C@@H]3CC[C@@H](CN(C)CC4(C)CC(CCNc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)CC3)sc2cc1NC(=O)c1cccc(C(C)(F)F)n1</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr"/>
+      <c r="H1218" t="inlineStr"/>
+      <c r="I1218" t="n">
+        <v>0.7339563960605864</v>
+      </c>
+      <c r="J1218" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1218" t="inlineStr"/>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="1" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1531.png</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr"/>
+      <c r="D1219" t="inlineStr"/>
+      <c r="E1219" t="inlineStr"/>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>CC(=O)N1CC(NC(=O)C2CC(O)CN2C(=O)C(C2=CC(OCCNCCNCCOC345=NC6=C7C89%10=C3=C73(=C84)(=N=5C=C=693)N%103C4CCC3CN(C3=C(N)N=NC(C5=CC=CC=C5O)=C3)C4)=NO2)C(C)C)(C2=CC=C(C3=C(C)N=CS3)C=C2)C1</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr"/>
+      <c r="H1219" t="inlineStr"/>
+      <c r="I1219" t="n">
+        <v>0.0606426750907137</v>
+      </c>
+      <c r="J1219" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1219" t="inlineStr"/>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="1" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_0/rb_1563.png</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr"/>
+      <c r="D1220" t="inlineStr"/>
+      <c r="E1220" t="inlineStr"/>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>CN1CC2(CC(CCNc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)C2)C1.COc1c(NC(=O)c2cccc(C(C)(C)F)n2)cc2cn(C3CCCCC3)nc2c1C</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr"/>
+      <c r="H1220" t="inlineStr"/>
+      <c r="I1220" t="n">
+        <v>0.7934618621681816</v>
+      </c>
+      <c r="J1220" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1220" t="inlineStr"/>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="1" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1360.png</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr"/>
+      <c r="D1221" t="inlineStr"/>
+      <c r="E1221" t="inlineStr"/>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>CNc1cc(-c2ccc3cc(C#N)cnn23)ncc1-c1nnc(N2CC3CCC(C2)N3C(=O)C[C@H](NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2(F)CC2)C(C)(C)C)c2ccc(-c3scnc3C)cc2)s1</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr"/>
+      <c r="H1221" t="inlineStr"/>
+      <c r="I1221" t="n">
+        <v>0.8395194883356348</v>
+      </c>
+      <c r="J1221" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1221" t="inlineStr"/>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="1" t="n">
+        <v>1220</v>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1364.png</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr"/>
+      <c r="D1222" t="inlineStr"/>
+      <c r="E1222" t="inlineStr"/>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](c2cc(CCCOCCOCCOCCOCCn3cc(-c4cc(-c5ccccc5O)nnc4N)cn3)no2)C(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr"/>
+      <c r="H1222" t="inlineStr"/>
+      <c r="I1222" t="n">
+        <v>0.8174784058985507</v>
+      </c>
+      <c r="J1222" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1222" t="inlineStr"/>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="1" t="n">
+        <v>1221</v>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1372.png</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr"/>
+      <c r="D1223" t="inlineStr"/>
+      <c r="E1223" t="inlineStr"/>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>CC(C)Nc1cc(-c2ccc3cc(C#N)cnn23)ncc1-c1nnc(N2CCN(C(=O)C3CCN(C[C@H]4CCN(c5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)CC3)CC2)s1</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr"/>
+      <c r="H1223" t="inlineStr"/>
+      <c r="I1223" t="n">
+        <v>0.82801471683048</v>
+      </c>
+      <c r="J1223" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1223" t="inlineStr"/>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="1" t="n">
+        <v>1222</v>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1376.png</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr"/>
+      <c r="D1224" t="inlineStr"/>
+      <c r="E1224" t="inlineStr"/>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>CC(C)(O)C1=CC2=C(C=C1NC(=O)C1=CC=CC(C(F)(F)F)=N1)SC(C1CCC(CN3CC34(C)CC4)CC1)=N2.CC(CNC1=C2C(=O)N(C3CCC(=O)NC3=O)C(=O)C2=CC=C1)C1CC2(C)(C)C1C2(C)CC12(C)(C)CC(C)C1C2</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr"/>
+      <c r="H1224" t="inlineStr"/>
+      <c r="I1224" t="n">
+        <v>0.04310311175891839</v>
+      </c>
+      <c r="J1224" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1224" t="inlineStr"/>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="1" t="n">
+        <v>1223</v>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1384.png</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr"/>
+      <c r="D1225" t="inlineStr"/>
+      <c r="E1225" t="inlineStr"/>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>C=CN1=C(N2C3CCC2CN(C2=C(N)N=NC(C4=C(O)C=CC=C4)=C2)C3)C=C=1OCCOCC1CN(C2=NOC(C(C(=O)N3CC(O)CC3C(=O)NC(C)C3=CC=C(C4=C(C)N=CS4)C=C3)C(C)C)=C2)C1</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr"/>
+      <c r="H1225" t="inlineStr"/>
+      <c r="I1225" t="n">
+        <v>0.4045634861529245</v>
+      </c>
+      <c r="J1225" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1225" t="inlineStr"/>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="1" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1392.png</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr"/>
+      <c r="D1226" t="inlineStr"/>
+      <c r="E1226" t="inlineStr"/>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>CC(C)(O)C1=NC2=C(C=C1NC(=O)C1=CC=CC(C(F)(F)F)=N1)SC(C1CCC(CN34CC567CC(CCNC8=C9C(=O)N(C%10CCC(=O)NC%10=O)C(=O)C9=CC=C8)C5C36C47)CC1)=N2</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr"/>
+      <c r="H1226" t="inlineStr"/>
+      <c r="I1226" t="n">
+        <v>0.2290310363930549</v>
+      </c>
+      <c r="J1226" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1226" t="inlineStr"/>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="1" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1400.png</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr"/>
+      <c r="D1227" t="inlineStr"/>
+      <c r="E1227" t="inlineStr"/>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>CN(C[C@@H]1CC[C@@H](n2cc3cc(C(=O)Nc4cccc(C(F)(F)F)n4)c(C(C)(C)O)cc3c2)CC1)C1CCC2(CC1)CC(Nc1cccc3c1C(=O)N(C1CCC(=O)NC1=O)C3=O)C2</t>
+        </is>
+      </c>
+      <c r="G1227" t="inlineStr"/>
+      <c r="H1227" t="inlineStr"/>
+      <c r="I1227" t="n">
+        <v>0.462787686652557</v>
+      </c>
+      <c r="J1227" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1227" t="inlineStr"/>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="1" t="n">
+        <v>1226</v>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1416.png</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr"/>
+      <c r="D1228" t="inlineStr"/>
+      <c r="E1228" t="inlineStr"/>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>*c1ccc(C[C@H](NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H]2CC[C@@H]3CCN(CCN(C)C)C[C@H](NC(=O)c4cc5cc(C(F)(F)S(=O)(=O)O)ccc5s4)C(=O)N32)C(=O)N2CCN(CCCNc3cccc4c3CN(C3CCC(=O)NC3=O)C4=O)CC2)cc1 |$tBu;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1228" t="inlineStr"/>
+      <c r="H1228" t="inlineStr"/>
+      <c r="I1228" t="n">
+        <v>0.8248419726663134</v>
+      </c>
+      <c r="J1228" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1228" t="inlineStr"/>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="1" t="n">
+        <v>1227</v>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1432.png</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr"/>
+      <c r="D1229" t="inlineStr"/>
+      <c r="E1229" t="inlineStr"/>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](c2cc(N3CCC(CN4CCC(O[C@@H]5C[C@@H](Oc6cc(N7C8CCC7CN(c7cc(-c9ccccc9O)nnc7N)C8)ccn6)C5)CC4)CC3)no2)C(C)C)cc1N</t>
+        </is>
+      </c>
+      <c r="G1229" t="inlineStr"/>
+      <c r="H1229" t="inlineStr"/>
+      <c r="I1229" t="n">
+        <v>0.7996082587746314</v>
+      </c>
+      <c r="J1229" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1229" t="inlineStr"/>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="1" t="n">
+        <v>1228</v>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1452.png</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr"/>
+      <c r="D1230" t="inlineStr"/>
+      <c r="E1230" t="inlineStr"/>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCC(=O)N2CCN(c3nnc(-c4cnc(-c5ccc6cc(C#N)cnn56)cc4NC(C)C)s3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr"/>
+      <c r="H1230" t="inlineStr"/>
+      <c r="I1230" t="n">
+        <v>0.7497363403413357</v>
+      </c>
+      <c r="J1230" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1230" t="inlineStr"/>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="1" t="n">
+        <v>1229</v>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1456.png</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr"/>
+      <c r="D1231" t="inlineStr"/>
+      <c r="E1231" t="inlineStr"/>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>COC1=CC2=C(C=C1NC(=O)C1=CC=CC(C)=N1)SC(C1CCC(CNCCC34(C)CC(NC5=C6C(=O)N(C7CCC(=O)NC7=O)C(=O)C6=CC=C5)C3C4)CC1)=N2</t>
+        </is>
+      </c>
+      <c r="G1231" t="inlineStr"/>
+      <c r="H1231" t="inlineStr"/>
+      <c r="I1231" t="n">
+        <v>0.6980218815449994</v>
+      </c>
+      <c r="J1231" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1231" t="inlineStr"/>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="1" t="n">
+        <v>1230</v>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1460.png</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr"/>
+      <c r="D1232" t="inlineStr"/>
+      <c r="E1232" t="inlineStr"/>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2(F)CC2)C(C)(C)C)c(OCC(=O)N2CCC(C(=O)N3CCN(c4nnc(-c5cnc(-c6ccc7cc(C#N)cnn67)cc5NC(C)C)s4)CC3)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G1232" t="inlineStr"/>
+      <c r="H1232" t="inlineStr"/>
+      <c r="I1232" t="n">
+        <v>0.8089191944839697</v>
+      </c>
+      <c r="J1232" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1232" t="inlineStr"/>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="1" t="n">
+        <v>1231</v>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1464.png</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr"/>
+      <c r="D1233" t="inlineStr"/>
+      <c r="E1233" t="inlineStr"/>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>CNc1cc(-c2ccc3cc(C#N)cnn23)ncc1-c1nnc([C@@H]2CC[C@@H](NC(=O)CN3CCC4(CC3)CN(c3ccc5c(c3)C(=O)N(C3CCC(=O)NC3=O)C5=O)C4)CC2)s1</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr"/>
+      <c r="H1233" t="inlineStr"/>
+      <c r="I1233" t="n">
+        <v>0.5943883423203384</v>
+      </c>
+      <c r="J1233" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1233" t="inlineStr"/>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="1" t="n">
+        <v>1232</v>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1476.png</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr"/>
+      <c r="D1234" t="inlineStr"/>
+      <c r="E1234" t="inlineStr"/>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>CN(C[C@@H]1CC[C@@H](n2cc3cc(NC(=S)c4cccc(C(F)(F)F)n4)c(C(C)(C)O)cc3n2)CC1)C1CCC2(CC1)CC(Nc1cccc3c1C(=O)N(C1CCC(=O)NC1=O)C3=O)C2</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr"/>
+      <c r="H1234" t="inlineStr"/>
+      <c r="I1234" t="n">
+        <v>0.4436877014789172</v>
+      </c>
+      <c r="J1234" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1234" t="inlineStr"/>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="1" t="n">
+        <v>1233</v>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1484.png</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr"/>
+      <c r="D1235" t="inlineStr"/>
+      <c r="E1235" t="inlineStr"/>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>C=CCN=NC(N)=CNCC1CCCN1CC=CO[CH]C[CH]CNCCCCNCCCCCN(CCC)C12=CC3=N=14=C1(N5CCC6CC65)=N(OC(=C1)[CH]15(C(C)C)C(=O)N6CC(O)C[CH]678(C(=O)NC(C)C6=CC=C(C9=C(C)N=CS9)C=C6)C6C(O)CN7(C6C8(=O)NC(C)C6=CC=C(C7=C(C)N=CS7)C=C6)C1(=O)C3C5(C)C)O24</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr"/>
+      <c r="H1235" t="inlineStr"/>
+      <c r="I1235" t="n">
+        <v>0.001827254355761244</v>
+      </c>
+      <c r="J1235" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1235" t="inlineStr"/>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="1" t="n">
+        <v>1234</v>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1492.png</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr"/>
+      <c r="D1236" t="inlineStr"/>
+      <c r="E1236" t="inlineStr"/>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>CCCCCC.CNC(=O)C(NC(=O)C1CC(O)CN1C(=O)[CH]C12=CC(OCCN3CCC(OC4CC(OC5=CC(N67C8C(NC9=CC(C%10=C(O)C=CC=C%10)=NN=C9N)C69CC6C89C8CC867)=CC=N5)C4)CC3)(=C1)=NO2)C1=CC=C(C2=C(C)N=CS2)C=C1</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr"/>
+      <c r="H1236" t="inlineStr"/>
+      <c r="I1236" t="n">
+        <v>0.0854084345680841</v>
+      </c>
+      <c r="J1236" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1236" t="inlineStr"/>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="1" t="n">
+        <v>1235</v>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1496.png</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr"/>
+      <c r="D1237" t="inlineStr"/>
+      <c r="E1237" t="inlineStr"/>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>CN(C[C@H]1CC[C@@H](c2cc3cc(NC(=O)c4cccc(C(F)(F)F)n4)c(C(C)(C)O)cn3n2)CC1)C1CCC2(CC1)CC(Nc1cccc3c1C(=O)N(C1CCC(=O)NC1=O)C3=O)C2</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr"/>
+      <c r="H1237" t="inlineStr"/>
+      <c r="I1237" t="n">
+        <v>0.4626958694771887</v>
+      </c>
+      <c r="J1237" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1237" t="inlineStr"/>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="1" t="n">
+        <v>1236</v>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1528.png</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr"/>
+      <c r="D1238" t="inlineStr"/>
+      <c r="E1238" t="inlineStr"/>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(C(C)NC(=O)C3CC(O)CN3C(=O)C(C3=CC(N4CCC(CN56CCN7(CC8CC(OC9=CC(N%10C%11CCC%10CN(C%10=C(N)N=NC(C%12=C(O)C=CC=C%12)=C%10)C%11)=CC=N9)C8)C89%10CC7(C8)(C59)C6%10)CC4)=NO3)C(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr"/>
+      <c r="H1238" t="inlineStr"/>
+      <c r="I1238" t="n">
+        <v>0.4945556087031145</v>
+      </c>
+      <c r="J1238" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1238" t="inlineStr"/>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="1" t="n">
+        <v>1237</v>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1548.png</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr"/>
+      <c r="D1239" t="inlineStr"/>
+      <c r="E1239" t="inlineStr"/>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>CN(C[C@@H]1CC[C@@H](c2cc3cc(NC(=O)c4cccc(C(F)(F)F)n4)c(C(C)(C)O)cn3n2)CC1)C1CCC2(CC1)CC(Nc1cccc3c1C(=O)N(C1CCC(=O)NC1=O)C3=O)C2</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr"/>
+      <c r="H1239" t="inlineStr"/>
+      <c r="I1239" t="n">
+        <v>0.5340844553857738</v>
+      </c>
+      <c r="J1239" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1239" t="inlineStr"/>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="1" t="n">
+        <v>1238</v>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1552.png</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr"/>
+      <c r="D1240" t="inlineStr"/>
+      <c r="E1240" t="inlineStr"/>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>CC(C)(O)c1cc2nc([C@@H]3CC[C@@H](CN4CC56C7C8(CCNc9cccc%10c9C(=O)N(C9CCC(=O)NC9=O)C%10=O)C5C7(C4)C86)CC3)sc2cc1NC(=O)c1ccccn1</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr"/>
+      <c r="H1240" t="inlineStr"/>
+      <c r="I1240" t="n">
+        <v>0.2148354306324823</v>
+      </c>
+      <c r="J1240" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1240" t="inlineStr"/>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="1" t="n">
+        <v>1239</v>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1568.png</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr"/>
+      <c r="D1241" t="inlineStr"/>
+      <c r="E1241" t="inlineStr"/>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2(F)CC2)C(C)(C)C)c(OCCN2CCC(c3c[nH]c4nnc(-c5ccccc5O)cc34)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr"/>
+      <c r="H1241" t="inlineStr"/>
+      <c r="I1241" t="n">
+        <v>0.6063029674817704</v>
+      </c>
+      <c r="J1241" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1241" t="inlineStr"/>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="1" t="n">
+        <v>1240</v>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1572.png</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr"/>
+      <c r="D1242" t="inlineStr"/>
+      <c r="E1242" t="inlineStr"/>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>CC(C)S(=O)(=O)CC1CCCC(=O)N12C(=O)C(C)(CC(=O)NC1=CC=C(C(=O)NCCCC#CC3=CC=CC4=C3CN(C3CCC(=O)NC3=O)C4=O)C=C1)CC(C1=CC=CC(Cl)=C1)C2C1=CC=C(Cl)C=C1</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr"/>
+      <c r="H1242" t="inlineStr"/>
+      <c r="I1242" t="n">
+        <v>0.6114126886301268</v>
+      </c>
+      <c r="J1242" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1242" t="inlineStr"/>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="1" t="n">
+        <v>1241</v>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1580.png</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr"/>
+      <c r="D1243" t="inlineStr"/>
+      <c r="E1243" t="inlineStr"/>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2(F)CC2)C(C)(C)C)c(OCCCCCCN2CCC(c3c[nH]c4nnc(-c5ccccc5O)cc34)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr"/>
+      <c r="H1243" t="inlineStr"/>
+      <c r="I1243" t="n">
+        <v>0.7956423874539017</v>
+      </c>
+      <c r="J1243" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1243" t="inlineStr"/>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="1" t="n">
+        <v>1242</v>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_1/rb_1596.png</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr"/>
+      <c r="D1244" t="inlineStr"/>
+      <c r="E1244" t="inlineStr"/>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>CCCCCCNc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O.CCN(C)C[C@H]1CC[C@H](c2nc3cc(C(C)(C)O)c(NC(=O)c4cccc(C(C)(F)F)c4)cc3s2)CC1</t>
+        </is>
+      </c>
+      <c r="G1244" t="inlineStr"/>
+      <c r="H1244" t="inlineStr"/>
+      <c r="I1244" t="n">
+        <v>0.8031310343401168</v>
+      </c>
+      <c r="J1244" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1244" t="inlineStr"/>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="1" t="n">
+        <v>1243</v>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1353.png</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr"/>
+      <c r="D1245" t="inlineStr"/>
+      <c r="E1245" t="inlineStr"/>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>CNc1cc(-c2ccc3cc(C#N)cnn23)ncc1C1N=NC(C23CCC(NC(=O)[C@H]4C[C@@H](OCCNc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)(CC2)C3)S1</t>
+        </is>
+      </c>
+      <c r="G1245" t="inlineStr"/>
+      <c r="H1245" t="inlineStr"/>
+      <c r="I1245" t="n">
+        <v>0.7941596411265978</v>
+      </c>
+      <c r="J1245" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1245" t="inlineStr"/>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="1" t="n">
+        <v>1244</v>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1357.png</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr"/>
+      <c r="D1246" t="inlineStr"/>
+      <c r="E1246" t="inlineStr"/>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>CC(C)(O)c1cc2nc([C@@H]3CC[C@@H](CN4CC(CCNc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)CC3)sc2cc1NC(=O)c1cccc(C(F)(F)F)n1</t>
+        </is>
+      </c>
+      <c r="G1246" t="inlineStr"/>
+      <c r="H1246" t="inlineStr"/>
+      <c r="I1246" t="n">
+        <v>0.8210121584744666</v>
+      </c>
+      <c r="J1246" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1246" t="inlineStr"/>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="1" t="n">
+        <v>1245</v>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1373.png</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr"/>
+      <c r="D1247" t="inlineStr"/>
+      <c r="E1247" t="inlineStr"/>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>COc1cc2nn([C@@H]3CC[C@@H](CN(C)CCCO[C@@H]4C[C@@H](Nc5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)CC3)cc2cc1NC(=O)c1cccc(C(F)(F)F)n1</t>
+        </is>
+      </c>
+      <c r="G1247" t="inlineStr"/>
+      <c r="H1247" t="inlineStr"/>
+      <c r="I1247" t="n">
+        <v>0.8395813433863213</v>
+      </c>
+      <c r="J1247" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1247" t="inlineStr"/>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="1" t="n">
+        <v>1246</v>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1381.png</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr"/>
+      <c r="D1248" t="inlineStr"/>
+      <c r="E1248" t="inlineStr"/>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>C=C12N34CC356789CCC3(CN(C%10=CC(C%11=CC=CC=C%11O)=NN=C%10N)C5)N165C1C7C3248C159.CC1=C(C2=CC=C(C(CCC#N)NC(=O)C3CC(O)CN3C(=O)C(C3=CC(OCCN4CCC(OC5CC(OC6=NC=CC(N78C9CCC7C98)=C6)C5)CC4)=NO3)C(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1248" t="inlineStr"/>
+      <c r="H1248" t="inlineStr"/>
+      <c r="I1248" t="n">
+        <v>0.004749101733031994</v>
+      </c>
+      <c r="J1248" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1248" t="inlineStr"/>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="1" t="n">
+        <v>1247</v>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1385.png</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr"/>
+      <c r="D1249" t="inlineStr"/>
+      <c r="E1249" t="inlineStr"/>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>NC(=O)CC[C@H](NC(=O)[C@@H]1CC[C@@H]2CCN(CC(F)F)C[C@H](NC(=O)c3cc4cc(C(F)(F)C(F)(F)F)ccc4s3)C(=O)N21)C(=O)N[C@@H](Cc1ccc(O)cc1)C(=O)N1CCC(CCNc2cccc3c2CN(C2CCC(=O)NC2=O)C3=O)CC1</t>
+        </is>
+      </c>
+      <c r="G1249" t="inlineStr"/>
+      <c r="H1249" t="inlineStr"/>
+      <c r="I1249" t="n">
+        <v>0.7679343753736594</v>
+      </c>
+      <c r="J1249" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1249" t="inlineStr"/>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="1" t="n">
+        <v>1248</v>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1389.png</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr"/>
+      <c r="D1250" t="inlineStr"/>
+      <c r="E1250" t="inlineStr"/>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>CC(C)(O)C1=CC2=C(C=C1NC(=O)C1=CC=CC(C(F)(F)F)=N1)SC([CH]CC[CH]CN1CC3(C)(CC(CCNC4=C5C(=O)N(C6CCC(=O)NC6=O)C(=O)C5=CC=C4)C3)C1)=N2</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr"/>
+      <c r="H1250" t="inlineStr"/>
+      <c r="I1250" t="n">
+        <v>0.831273043265143</v>
+      </c>
+      <c r="J1250" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1250" t="inlineStr"/>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="1" t="n">
+        <v>1249</v>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1401.png</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr"/>
+      <c r="D1251" t="inlineStr"/>
+      <c r="E1251" t="inlineStr"/>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1cnn2c(-c3cc(NC)c(-c4nnc([C@@H]5CC[C@@H](NC(=O)CCC(=O)N[C@H](C(=O)N6C[C@@H](O)C[C@H]6C(=O)NCc6ccc(-c7scnc7C)cc6)C(C)C)CC5)s4)cn3)ccc2c1</t>
+        </is>
+      </c>
+      <c r="G1251" t="inlineStr"/>
+      <c r="H1251" t="inlineStr"/>
+      <c r="I1251" t="n">
+        <v>0.825849871448332</v>
+      </c>
+      <c r="J1251" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1251" t="inlineStr"/>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="1" t="n">
+        <v>1250</v>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1405.png</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr"/>
+      <c r="D1252" t="inlineStr"/>
+      <c r="E1252" t="inlineStr"/>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>COC12=CC=C(C(CC(=O)O)NC3=C(Cl)C=NC=C3Cl)C=C1OC(COCCOCCOCCCNC1=CC=CC3=C1CN(C1CCC(=O)NC1=O)C3=O)CO2</t>
+        </is>
+      </c>
+      <c r="G1252" t="inlineStr"/>
+      <c r="H1252" t="inlineStr"/>
+      <c r="I1252" t="n">
+        <v>0.7739608795592253</v>
+      </c>
+      <c r="J1252" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1252" t="inlineStr"/>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="1" t="n">
+        <v>1251</v>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1409.png</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr"/>
+      <c r="D1253" t="inlineStr"/>
+      <c r="E1253" t="inlineStr"/>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>NC(=O)CC[C@H](NC(=O)[C@@H]1CC[C@@H]2CCN(C(=O)CCCCCC#Cc3cccc4c3CN(C3CCC(=O)NC3=O)C4=O)C[C@H](NC(=O)c3cc4cc(C(F)(F)P(=O)(O)O)ccc4s3)C(=O)N21)c1ncc(-c2ccccc2)s1</t>
+        </is>
+      </c>
+      <c r="G1253" t="inlineStr"/>
+      <c r="H1253" t="inlineStr"/>
+      <c r="I1253" t="n">
+        <v>0.7896137952611227</v>
+      </c>
+      <c r="J1253" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1253" t="inlineStr"/>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="1" t="n">
+        <v>1252</v>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1417.png</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr"/>
+      <c r="D1254" t="inlineStr"/>
+      <c r="E1254" t="inlineStr"/>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>CC(CCNC12=C(C=CC=C1)C(=O)N(C1CCC(=O)NC1=O)C(=O)C=CC=C2)CC1CCN(CC2CCC(N3C=C4C=C(NC(=O)C5=CC=CC(C(C)(F)F)=N5)C(OCC(C)(C)O)=CC4=N3)CC2)CC1</t>
+        </is>
+      </c>
+      <c r="G1254" t="inlineStr"/>
+      <c r="H1254" t="inlineStr"/>
+      <c r="I1254" t="n">
+        <v>0.4692929188468646</v>
+      </c>
+      <c r="J1254" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1254" t="inlineStr"/>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="1" t="n">
+        <v>1253</v>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1425.png</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr"/>
+      <c r="D1255" t="inlineStr"/>
+      <c r="E1255" t="inlineStr"/>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>CCC1C(C)(C)[CH]1(C(=O)N1CC(O)CC1C(=O)NCC1=CC=C(C2=C(C)N=CS2)C=C1)C1=CC(N2CC(CN3CCC(OC4CC(OC5=CC(N6C7CCC6CN(C6=CC(C8=C(O)C=CC=C8)=NN=C6N)C7)=CC=N5)C4)CC3)C2)=NO1</t>
+        </is>
+      </c>
+      <c r="G1255" t="inlineStr"/>
+      <c r="H1255" t="inlineStr"/>
+      <c r="I1255" t="n">
+        <v>0.5746106361903819</v>
+      </c>
+      <c r="J1255" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1255" t="inlineStr"/>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="1" t="n">
+        <v>1254</v>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1441.png</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr"/>
+      <c r="D1256" t="inlineStr"/>
+      <c r="E1256" t="inlineStr"/>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(C(C)NC(=O)C3CC(O)CN3C(=O)C(C3=CC(N4CCC(C(C)(C)N5CCC(OC6CC(OC7=CC(N89CC%10C8CCC9CN%10C8=C(N)N=NC(C9=C(O)C=CC=C9)=C8)=CC=N7)C6)CC5)CC4)=NO3)C(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1256" t="inlineStr"/>
+      <c r="H1256" t="inlineStr"/>
+      <c r="I1256" t="n">
+        <v>0.6805971894439008</v>
+      </c>
+      <c r="J1256" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1256" t="inlineStr"/>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="1" t="n">
+        <v>1255</v>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1445.png</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr"/>
+      <c r="D1257" t="inlineStr"/>
+      <c r="E1257" t="inlineStr"/>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>CC(C)(O)c1cc2nc(C3CCC(N4CC5(CC(CCNc6cccc7c6C(=O)N(C6CCC(=O)NC6=O)C7=O)C5)C4)CC3)sc2cc1NC(=O)c1cccc(C(F)(F)F)n1</t>
+        </is>
+      </c>
+      <c r="G1257" t="inlineStr"/>
+      <c r="H1257" t="inlineStr"/>
+      <c r="I1257" t="n">
+        <v>0.7909899741039269</v>
+      </c>
+      <c r="J1257" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1257" t="inlineStr"/>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="1" t="n">
+        <v>1256</v>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1457.png</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr"/>
+      <c r="D1258" t="inlineStr"/>
+      <c r="E1258" t="inlineStr"/>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>CN(C[C@H]1CC[C@@H](c2cc3cc(C(C)(C)O)c(NC(=O)c4cccc(C(F)(F)F)n4)cn3n2)CC1)C1CCC2(CC1)CC(Nc1cccc3c1C(=O)N(C1CCC(=O)NC1=O)C3=O)C2</t>
+        </is>
+      </c>
+      <c r="G1258" t="inlineStr"/>
+      <c r="H1258" t="inlineStr"/>
+      <c r="I1258" t="n">
+        <v>0.4049472237161348</v>
+      </c>
+      <c r="J1258" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1258" t="inlineStr"/>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="1" t="n">
+        <v>1257</v>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1461.png</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr"/>
+      <c r="D1259" t="inlineStr"/>
+      <c r="E1259" t="inlineStr"/>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>CN(C[C@H]1CC[C@@H](n2cc3cc(NC(=O)c4cccc(C(F)(F)F)n4)c4c(c3n2)CCC4(C)O)CC1)C1CCC2(CC1)CC(Nc1cccc3c1C(=O)N(C1CCC(=O)NC1=O)C3=O)C2</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr"/>
+      <c r="H1259" t="inlineStr"/>
+      <c r="I1259" t="n">
+        <v>0.4776665387389025</v>
+      </c>
+      <c r="J1259" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1259" t="inlineStr"/>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="1" t="n">
+        <v>1258</v>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1465.png</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr"/>
+      <c r="D1260" t="inlineStr"/>
+      <c r="E1260" t="inlineStr"/>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>CN(O)c1cc2nn([C@@H]3CC[C@@H](CN(C)C4CCC5(CC4)CC(Nc4cccc6c4C(=O)N(C4CCC(=O)NC4=O)C6=O)C5)CC3)cc2cc1NC(=O)c1cccc(C(F)(F)F)n1</t>
+        </is>
+      </c>
+      <c r="G1260" t="inlineStr"/>
+      <c r="H1260" t="inlineStr"/>
+      <c r="I1260" t="n">
+        <v>0.6089271954586239</v>
+      </c>
+      <c r="J1260" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1260" t="inlineStr"/>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="1" t="n">
+        <v>1259</v>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1469.png</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr"/>
+      <c r="D1261" t="inlineStr"/>
+      <c r="E1261" t="inlineStr"/>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2(F)CC2)C(C)(C)C)c(OCCCCCCCCN2CCC(c3c[nH]c4nnc(-c5ccccc5O)cc34)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G1261" t="inlineStr"/>
+      <c r="H1261" t="inlineStr"/>
+      <c r="I1261" t="n">
+        <v>0.8360560996826283</v>
+      </c>
+      <c r="J1261" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1261" t="inlineStr"/>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="1" t="n">
+        <v>1260</v>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1481.png</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr"/>
+      <c r="D1262" t="inlineStr"/>
+      <c r="E1262" t="inlineStr"/>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>COc1cc2nc([C@@H]3CC[C@@H](CN(C)CC4(C)CCC(CCNc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)CC3)oc2cc1NC(=O)c1cccc(C(C)(F)F)n1</t>
+        </is>
+      </c>
+      <c r="G1262" t="inlineStr"/>
+      <c r="H1262" t="inlineStr"/>
+      <c r="I1262" t="n">
+        <v>0.8404457060160504</v>
+      </c>
+      <c r="J1262" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1262" t="inlineStr"/>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="1" t="n">
+        <v>1261</v>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1485.png</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr"/>
+      <c r="D1263" t="inlineStr"/>
+      <c r="E1263" t="inlineStr"/>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>NC(=O)CC[C@H](NC(=O)[C@@H]1CC[C@@H]2CCN(CC(F)F)C[C@H](NC(=O)c3cc4cc(C(F)(F)P(=O)(O)O)ccc4s3)C(=O)N21)C(=O)N[C@@H](Cc1ccc(O)cc1)C(=O)N1CCC(CNc2cccc3c2CN(C2CCC(=O)NC2=O)C3=O)CC1</t>
+        </is>
+      </c>
+      <c r="G1263" t="inlineStr"/>
+      <c r="H1263" t="inlineStr"/>
+      <c r="I1263" t="n">
+        <v>0.7825796493058281</v>
+      </c>
+      <c r="J1263" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1263" t="inlineStr"/>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="1" t="n">
+        <v>1262</v>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1489.png</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr"/>
+      <c r="D1264" t="inlineStr"/>
+      <c r="E1264" t="inlineStr"/>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>CC(=O)N12C3(=O)N4(C(=O)C5=CC=C6C7=C538=C63(=C(C4=O)C8(C)=CC=C3)NCCC345CC689(CN(CC%10CCC(C%11=NC%12=C(C=C(NC(=O)C%13=CC=CC(C(F)(F)F)=N%13)C(C(C)(C)O)=C%12)S%11)CC%10)C6)(CC86C3C(C4CN7)C69)C5)C1345C1CC67=O=C89(=O)CC3C123C41=O=C35(=O)(N68)N719</t>
+        </is>
+      </c>
+      <c r="G1264" t="inlineStr"/>
+      <c r="H1264" t="inlineStr"/>
+      <c r="I1264" t="n">
+        <v>0.0006813590144905352</v>
+      </c>
+      <c r="J1264" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1264" t="inlineStr"/>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="1" t="n">
+        <v>1263</v>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1497.png</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr"/>
+      <c r="D1265" t="inlineStr"/>
+      <c r="E1265" t="inlineStr"/>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>CC(CC(C)(C)C1N(C[C@@H]2CC[C@@H](c3nc4cc(C(C)(C)O)c(NC(=O)c5cccc(C(F)(F)F)n5)cc4s3)CC2)CC1(C)C)[C@@H](C)CNc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O</t>
+        </is>
+      </c>
+      <c r="G1265" t="inlineStr"/>
+      <c r="H1265" t="inlineStr"/>
+      <c r="I1265" t="n">
+        <v>0.3721901926007144</v>
+      </c>
+      <c r="J1265" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1265" t="inlineStr"/>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="1" t="n">
+        <v>1264</v>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1517.png</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr"/>
+      <c r="D1266" t="inlineStr"/>
+      <c r="E1266" t="inlineStr"/>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>COc1c(NC(=O)c2cccc(C(C)(F)F)n2)cc2cn(C3CCC(CN4CC5(CC(CCNc6cccc7c6C(=O)N(C6CCC(=O)NC6=O)C7=O)C5)C4)CC3)nc2c1C</t>
+        </is>
+      </c>
+      <c r="G1266" t="inlineStr"/>
+      <c r="H1266" t="inlineStr"/>
+      <c r="I1266" t="n">
+        <v>0.8367751395199656</v>
+      </c>
+      <c r="J1266" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1266" t="inlineStr"/>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="1" t="n">
+        <v>1265</v>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1521.png</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr"/>
+      <c r="D1267" t="inlineStr"/>
+      <c r="E1267" t="inlineStr"/>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1cnn2c(-c3cc(NC)c(-c4nnc([C@@H]5CC[C@@H](NC(=O)CCCOc6cc(-c7scnc7C)ccc6CNC(=O)[C@@H]6C[C@@H](O)CN6C(=O)[C@@H](NC(=O)C6(F)CC6)C(C)(C)C)CC5)s4)cn3)ccc2c1</t>
+        </is>
+      </c>
+      <c r="G1267" t="inlineStr"/>
+      <c r="H1267" t="inlineStr"/>
+      <c r="I1267" t="n">
+        <v>0.8200591475051859</v>
+      </c>
+      <c r="J1267" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1267" t="inlineStr"/>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="1" t="n">
+        <v>1266</v>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1525.png</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr"/>
+      <c r="D1268" t="inlineStr"/>
+      <c r="E1268" t="inlineStr"/>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>NC(=O)CC[C@H](NC(=O)[C@@H]1CC[C@@H]2CCN(C(=O)CCCCCC#Cc3cccc4c3CN(C3CCC(=O)NC3=O)C4=O)C[C@H](NC(=O)c3cc4cc(C(F)(F)[PH](O)(F)F)ccc4s3)C(=O)N21)c1ncc(-c2ccccc2F)s1</t>
+        </is>
+      </c>
+      <c r="G1268" t="inlineStr"/>
+      <c r="H1268" t="inlineStr"/>
+      <c r="I1268" t="n">
+        <v>0.8316916738993041</v>
+      </c>
+      <c r="J1268" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1268" t="inlineStr"/>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="1" t="n">
+        <v>1267</v>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1529.png</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr"/>
+      <c r="D1269" t="inlineStr"/>
+      <c r="E1269" t="inlineStr"/>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>CC(C)(O)C1=CC2=C(C=C1NC(=O)C1=CC=CC(C(F)(F)F)=N1)SC(C1CCC(CN3CCC456(CC3)CC3(C)(C)C4(C4(C)(C)CC(CCNC7=C8C(=O)N(C9CCC(=O)NC9=O)C(=O)C8=CC=C7)C4)C35(C)C6)CC1)=N2</t>
+        </is>
+      </c>
+      <c r="G1269" t="inlineStr"/>
+      <c r="H1269" t="inlineStr"/>
+      <c r="I1269" t="n">
+        <v>0.09447318856587768</v>
+      </c>
+      <c r="J1269" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1269" t="inlineStr"/>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="1" t="n">
+        <v>1268</v>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1541.png</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr"/>
+      <c r="D1270" t="inlineStr"/>
+      <c r="E1270" t="inlineStr"/>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1cnn2c(-c3cc(NC)c(-c4nnc([C@@H]5CC[C@@H](N(C)C(=O)CCN6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)CC5)s4)cn3)ccc2c1</t>
+        </is>
+      </c>
+      <c r="G1270" t="inlineStr"/>
+      <c r="H1270" t="inlineStr"/>
+      <c r="I1270" t="n">
+        <v>0.7880374593249252</v>
+      </c>
+      <c r="J1270" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1270" t="inlineStr"/>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="1" t="n">
+        <v>1269</v>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1549.png</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr"/>
+      <c r="D1271" t="inlineStr"/>
+      <c r="E1271" t="inlineStr"/>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>CCCCC1C23C45=CC6=C(SCC(=O)N[CH]78C(=O)NC(CCCNC(=N)N)C(=O)N[CH]9%10(CC%11=CC=C(O)C=C%11)C(=O)N%11(CCN(CCCNC%12=CC=CC%13=C%12CN(C%12CCC(=O)NC%12=O)C%13=O)CC%11)C9(=O)(NCCNCCCN)C(CC9=CC=C(O)C=C9)N%10C(=O)C(CCCNC(=N)N)NC(=O)[CH]79%10CCC(CC(F)F)N9C8%10=O)C=CC24=C6135</t>
+        </is>
+      </c>
+      <c r="G1271" t="inlineStr"/>
+      <c r="H1271" t="inlineStr"/>
+      <c r="I1271" t="n">
+        <v>0.001196941287788776</v>
+      </c>
+      <c r="J1271" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1271" t="inlineStr"/>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="1" t="n">
+        <v>1270</v>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1557.png</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr"/>
+      <c r="D1272" t="inlineStr"/>
+      <c r="E1272" t="inlineStr"/>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>CC(C)(O)C1=CC2=C(C=C1NC(=O)C1=CC=C(C(F)(F)F)N=N1)SC(C1CCC(CN3CC45(CCC46C(CCNC4=C7C(=O)N(C8CCC(=O)NC8=O)C(=O)C7=CC=C4)C65)C3)CC1)=N2</t>
+        </is>
+      </c>
+      <c r="G1272" t="inlineStr"/>
+      <c r="H1272" t="inlineStr"/>
+      <c r="I1272" t="n">
+        <v>0.2695803350098004</v>
+      </c>
+      <c r="J1272" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1272" t="inlineStr"/>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="1" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1561.png</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr"/>
+      <c r="D1273" t="inlineStr"/>
+      <c r="E1273" t="inlineStr"/>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(C(C)NC(=O)C3CC(O)CN3C(=O)C(C3=CC(N4CC(OCCN5CCN(CCOC67=CC8(N9C%10CCC9CN(C9CC(C%11=C(O)C=CC=C%11)=NN=C9N)C%10)=N=6C=C87)CC5)C4)=NO3)C(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1273" t="inlineStr"/>
+      <c r="H1273" t="inlineStr"/>
+      <c r="I1273" t="n">
+        <v>0.3537679683541843</v>
+      </c>
+      <c r="J1273" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1273" t="inlineStr"/>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="1" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1573.png</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr"/>
+      <c r="D1274" t="inlineStr"/>
+      <c r="E1274" t="inlineStr"/>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>COC1=CC2=C(C=C1NC(=O)C1=CC=NC(C)=N1)SC(C1CCC(CN(C)CC3(C)(C)CC(CCNC4=C5C(=O)N(C6CCC(=O)NC6=O)C(=O)C5=CC=C4)C3)CC1)=N2</t>
+        </is>
+      </c>
+      <c r="G1274" t="inlineStr"/>
+      <c r="H1274" t="inlineStr"/>
+      <c r="I1274" t="n">
+        <v>0.5978187177584416</v>
+      </c>
+      <c r="J1274" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1274" t="inlineStr"/>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="1" t="n">
+        <v>1273</v>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_2/rb_1593.png</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr"/>
+      <c r="D1275" t="inlineStr"/>
+      <c r="E1275" t="inlineStr"/>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(C(C)NC(=O)C3CC(O)CN3C(=O)C(C3=CC(OCCC4CCC(OC5CC(OC6=NC=CC(N78C9CC7C8CN(C7=CC(C8=CC=CC=C8O)=NN=C7N)C9)=C6)C5)CC4)=NO3)C(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1275" t="inlineStr"/>
+      <c r="H1275" t="inlineStr"/>
+      <c r="I1275" t="n">
+        <v>0.3909968144807513</v>
+      </c>
+      <c r="J1275" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1275" t="inlineStr"/>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="1" t="n">
+        <v>1274</v>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1354.png</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr"/>
+      <c r="D1276" t="inlineStr"/>
+      <c r="E1276" t="inlineStr"/>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>CN(C[C@@H]1CC[C@@H](n2cc3cc(C(C)(C)O)c(NC(=O)c4cccc(C(F)(F)F)n4)cc3n2)CC1)C1CCC2(CC1)CC(Nc1cccc3c1C(=O)N(C1CCC(=O)NC1=O)C3=O)C2</t>
+        </is>
+      </c>
+      <c r="G1276" t="inlineStr"/>
+      <c r="H1276" t="inlineStr"/>
+      <c r="I1276" t="n">
+        <v>0.4482218907461398</v>
+      </c>
+      <c r="J1276" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1276" t="inlineStr"/>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="1" t="n">
+        <v>1275</v>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1358.png</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr"/>
+      <c r="D1277" t="inlineStr"/>
+      <c r="E1277" t="inlineStr"/>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)C3=CC=CC(NCCC45CC6(CCN(CCCCCC7=NC8=C(C=C(NC(=O)C9=CC=CC(C(F)(F)F)=N9)C(N9CCOCC9)=C8)O7)CC6)(C4)C5)=C3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1277" t="inlineStr"/>
+      <c r="H1277" t="inlineStr"/>
+      <c r="I1277" t="n">
+        <v>0.8011596638968984</v>
+      </c>
+      <c r="J1277" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1277" t="inlineStr"/>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="1" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1374.png</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr"/>
+      <c r="D1278" t="inlineStr"/>
+      <c r="E1278" t="inlineStr"/>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>CCOCCCC1=CC(C(=O)NC2CN(CC(F)F)CCC3CCC(C(=O)NC(CCC(N)=O)C(=O)N[CH]4(CC5=CC=C(OCC)C=C5)C5(=O)N67C8CC9CCCN%10C%11=CC=C%12%13C%14=C%15C%12%16=C%11%12%17CN%11%18C%19CCC(=O)NC%19(=O)C%11%19(CCC(=O)NC%19=O)N%11%19CC(=C%15%13%12(C%11=O)C%16%19%18=O)C%10%17(=C%14)NCCCCN85(C6C9)C47=O)N3C2=O)=C1</t>
+        </is>
+      </c>
+      <c r="G1278" t="inlineStr"/>
+      <c r="H1278" t="inlineStr"/>
+      <c r="I1278" t="n">
+        <v>0.005633116675811284</v>
+      </c>
+      <c r="J1278" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1278" t="inlineStr"/>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="1" t="n">
+        <v>1277</v>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1382.png</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr"/>
+      <c r="D1279" t="inlineStr"/>
+      <c r="E1279" t="inlineStr"/>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>Cc1cccc(C(=O)Nc2cc3sc([C@@H]4CC[C@@H](CN(C)[C@@H]5CC[C@@H](Nc6cccc7c6C(=O)N(C6CCC(=O)NC6=O)C7=O)CC5)CC4)nc3cc2C(C)(C)O)n1</t>
+        </is>
+      </c>
+      <c r="G1279" t="inlineStr"/>
+      <c r="H1279" t="inlineStr"/>
+      <c r="I1279" t="n">
+        <v>0.8401272217203848</v>
+      </c>
+      <c r="J1279" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1279" t="inlineStr"/>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="1" t="n">
+        <v>1278</v>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1390.png</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr"/>
+      <c r="D1280" t="inlineStr"/>
+      <c r="E1280" t="inlineStr"/>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)C2(F)CC2)C(C)(C)C)c(OCCOCCC(=O)N2CCN(c3nnc(-c4cnc(-c5ccc6cc(C#N)cnn56)cc4NC(C)C)s3)CC2)c1</t>
+        </is>
+      </c>
+      <c r="G1280" t="inlineStr"/>
+      <c r="H1280" t="inlineStr"/>
+      <c r="I1280" t="n">
+        <v>0.6135539743022232</v>
+      </c>
+      <c r="J1280" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1280" t="inlineStr"/>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="1" t="n">
+        <v>1279</v>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1406.png</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr"/>
+      <c r="D1281" t="inlineStr"/>
+      <c r="E1281" t="inlineStr"/>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>COc1cc2nc([C@@H]3CC[C@@H](CN(C)[C@@H]4CC[C@]5(CC4)C[C@H](CNc4cccc6c4C(=O)N(C4CCC(=O)NC4=O)C6=O)C5)CC3)sc2cc1NC(=O)c1cccc(C(C)(F)F)n1</t>
+        </is>
+      </c>
+      <c r="G1281" t="inlineStr"/>
+      <c r="H1281" t="inlineStr"/>
+      <c r="I1281" t="n">
+        <v>0.7973923802513972</v>
+      </c>
+      <c r="J1281" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1281" t="inlineStr"/>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="1" t="n">
+        <v>1280</v>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1410.png</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr"/>
+      <c r="D1282" t="inlineStr"/>
+      <c r="E1282" t="inlineStr"/>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>CC(C)(O)C1=CC2=C(C=C1NC(=O)C1=CC=CC(C(F)(F)F)=N1)SC(N1CCC(CN3CC3(C)(C)C)CC1)=N2.CC12(C)CC(CCNC3=C4C(=O)N(C5CCC(=O)NC5=O)C(=O)C4=CC=C3)C1C2</t>
+        </is>
+      </c>
+      <c r="G1282" t="inlineStr"/>
+      <c r="H1282" t="inlineStr"/>
+      <c r="I1282" t="n">
+        <v>0.2134599146244884</v>
+      </c>
+      <c r="J1282" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1282" t="inlineStr"/>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="1" t="n">
+        <v>1281</v>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1418.png</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr"/>
+      <c r="D1283" t="inlineStr"/>
+      <c r="E1283" t="inlineStr"/>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>CC(C)(O)c1cc2nc(C3CCC(N4CC5(CC(CCNc6cccc7c6C(=O)N(C6CCC(=O)NC6=O)C7=O)C5)C4)CC3)sc2cc1NC(=O)c1cccc(C(F)(F)F)n1</t>
+        </is>
+      </c>
+      <c r="G1283" t="inlineStr"/>
+      <c r="H1283" t="inlineStr"/>
+      <c r="I1283" t="n">
+        <v>0.8046659272370875</v>
+      </c>
+      <c r="J1283" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1283" t="inlineStr"/>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="1" t="n">
+        <v>1282</v>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1422.png</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr"/>
+      <c r="D1284" t="inlineStr"/>
+      <c r="E1284" t="inlineStr"/>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCCCCCCC2Oc3cc(C(=O)Nc4c(Cl)cncc4Cl)ccc3OC2C2CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1284" t="inlineStr"/>
+      <c r="H1284" t="inlineStr"/>
+      <c r="I1284" t="n">
+        <v>0.5834107527525708</v>
+      </c>
+      <c r="J1284" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1284" t="inlineStr"/>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="1" t="n">
+        <v>1283</v>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1434.png</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr"/>
+      <c r="D1285" t="inlineStr"/>
+      <c r="E1285" t="inlineStr"/>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(C(C)NC(=O)C3CC(O)CN3C(=O)[CH]3(C4=CC(OCCC5CCN(C(=O)C6CC(CN7CCC(N8C=C(C9=CC(C%10=CC=CC=C%10O)=NN=C9N)C=N8)CC7)C6)CC5)=NO4)C456CC3(C4)(C5)C6)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1285" t="inlineStr"/>
+      <c r="H1285" t="inlineStr"/>
+      <c r="I1285" t="n">
+        <v>0.7371665403565393</v>
+      </c>
+      <c r="J1285" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1285" t="inlineStr"/>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="1" t="n">
+        <v>1284</v>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1458.png</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr"/>
+      <c r="D1286" t="inlineStr"/>
+      <c r="E1286" t="inlineStr"/>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(C(C)NC(=O)C3CC(O)CN3C(=O)[CH]34NC(=O)C567(CCCCC(=O)N8CCN(C9=NN=C(C%10=CN=C(C%11=CC=C%12C=C(C#N)C=NN%12%11)C=C%10NC(C)C)S9)CC8)CC389%10%11%12CC4(C8)(C9)(C5%10)(C6%11)C7%12)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1286" t="inlineStr"/>
+      <c r="H1286" t="inlineStr"/>
+      <c r="I1286" t="n">
+        <v>0.197262757500397</v>
+      </c>
+      <c r="J1286" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1286" t="inlineStr"/>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="1" t="n">
+        <v>1285</v>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1474.png</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr"/>
+      <c r="D1287" t="inlineStr"/>
+      <c r="E1287" t="inlineStr"/>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]c1cnn2c(-c3cc(NC(C)C)c(-c4nnc(N5CCN(C6CCN(C(=O)Cc7cccc8c7CN(C7CCC(=O)NC7=O)C8=O)CC6)CC5)s4)cn3)ccc2c1</t>
+        </is>
+      </c>
+      <c r="G1287" t="inlineStr"/>
+      <c r="H1287" t="inlineStr"/>
+      <c r="I1287" t="n">
+        <v>0.8204352136817052</v>
+      </c>
+      <c r="J1287" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1287" t="inlineStr"/>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="1" t="n">
+        <v>1286</v>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1478.png</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr"/>
+      <c r="D1288" t="inlineStr"/>
+      <c r="E1288" t="inlineStr"/>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3cccc(NCCC4CC5(CCN(CC6CCC(c7nc8cc(N9CCC(CO)CC9)c(NC(=O)c9cccc(C(F)(F)F)n9)cc8o7)CC6)CC5)C4)c3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1288" t="inlineStr"/>
+      <c r="H1288" t="inlineStr"/>
+      <c r="I1288" t="n">
+        <v>0.82788194720053</v>
+      </c>
+      <c r="J1288" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1288" t="inlineStr"/>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="1" t="n">
+        <v>1287</v>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1490.png</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr"/>
+      <c r="D1289" t="inlineStr"/>
+      <c r="E1289" t="inlineStr"/>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>COc1cc2nn(C3CCCCC3)cc2cc1NC(=O)c1cccc(C(F)(F)F)n1.C[C@H](CNc1cccc2c1C(=O)N(C1CCC(=O)NC1=O)C2=O)C1CC2(C1)CN(C)C2</t>
+        </is>
+      </c>
+      <c r="G1289" t="inlineStr"/>
+      <c r="H1289" t="inlineStr"/>
+      <c r="I1289" t="n">
+        <v>0.8072061808901365</v>
+      </c>
+      <c r="J1289" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1289" t="inlineStr"/>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="1" t="n">
+        <v>1288</v>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1498.png</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr"/>
+      <c r="D1290" t="inlineStr"/>
+      <c r="E1290" t="inlineStr"/>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3c(cc(F)cc3C3CCN(CCCCCCCN(C(=O)c4ccc(OC(F)F)c(OCC5CC5)c4)c4c(Cl)cncc4Cl)CC3)C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1290" t="inlineStr"/>
+      <c r="H1290" t="inlineStr"/>
+      <c r="I1290" t="n">
+        <v>0.8329147737190961</v>
+      </c>
+      <c r="J1290" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1290" t="inlineStr"/>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="1" t="n">
+        <v>1289</v>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1510.png</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr"/>
+      <c r="D1291" t="inlineStr"/>
+      <c r="E1291" t="inlineStr"/>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>CC1=C(C(=CC=CC(C)NC(=O)C2CC(O)CN2C(=O)C(C2=CC(OCCC3CCN(CC4CC(OC56=CC7(N89CCCC8CN(C8=C(N)N=NC(C%10=C(O)C=CC=C%10)=C8)CC9)=N5C=C67)C4)CC3)=NO2)C(C)C)CF)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1291" t="inlineStr"/>
+      <c r="H1291" t="inlineStr"/>
+      <c r="I1291" t="n">
+        <v>0.3041889108054539</v>
+      </c>
+      <c r="J1291" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1291" t="inlineStr"/>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="1" t="n">
+        <v>1290</v>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1518.png</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr"/>
+      <c r="D1292" t="inlineStr"/>
+      <c r="E1292" t="inlineStr"/>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>CN(C[C@@H]1CC[C@@H](n2cc3cc4c(cc3n2)C(C)(O)C[SH]=C4Nc2cccc(C(F)(F)F)n2)CC1)C1CCC2(CC1)CC(Nc1cccc3c1C(=O)N(C1CCC(=O)NC1=O)C3=O)C2</t>
+        </is>
+      </c>
+      <c r="G1292" t="inlineStr"/>
+      <c r="H1292" t="inlineStr"/>
+      <c r="I1292" t="n">
+        <v>0.3324987209962189</v>
+      </c>
+      <c r="J1292" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1292" t="inlineStr"/>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="1" t="n">
+        <v>1291</v>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1538.png</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr"/>
+      <c r="D1293" t="inlineStr"/>
+      <c r="E1293" t="inlineStr"/>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>NC(=O)CC[C@H](NC(=O)[C@@H]1CC[C@@H]2CCN(C(=O)CCCCCC#Cc3cccc4c3CN(C3CCC(=O)NC3=O)C4=O)C[C@H](NC(=O)c3cc4cc(C(F)(F)[SH3])ccc4s3)C(=O)N21)c1nc2c(s1)C=C1CC=CC=C12</t>
+        </is>
+      </c>
+      <c r="G1293" t="inlineStr"/>
+      <c r="H1293" t="inlineStr"/>
+      <c r="I1293" t="n">
+        <v>0.578794321840673</v>
+      </c>
+      <c r="J1293" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1293" t="inlineStr"/>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="1" t="n">
+        <v>1292</v>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1542.png</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr"/>
+      <c r="D1294" t="inlineStr"/>
+      <c r="E1294" t="inlineStr"/>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>NC(=O)CC[C@H](NC(=O)[C@@H]1CC[C@@H]2CCN(C(=O)CCCCCC#Cc3cccc4c3CN(C3CCC(=O)NC3=O)C4=O)C[C@H](NC(=O)c3cc4cc(C(F)(F)P(=O)(O)O)ccc4s3)C(=O)N21)c1nc(-c2ccccc2)cs1</t>
+        </is>
+      </c>
+      <c r="G1294" t="inlineStr"/>
+      <c r="H1294" t="inlineStr"/>
+      <c r="I1294" t="n">
+        <v>0.8047492347645062</v>
+      </c>
+      <c r="J1294" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1294" t="inlineStr"/>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="1" t="n">
+        <v>1293</v>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1554.png</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr"/>
+      <c r="D1295" t="inlineStr"/>
+      <c r="E1295" t="inlineStr"/>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>[H]C(F)CN1CC[C@H]2CC[C@@H](C(=O)N[C@@H](CCCNC(=N)N)C(=O)N[C@@H](Cc3ccc(O)cc3)C(=O)N3CCN(CCNc4cccc5c4CN(C4CCC(=O)NC4=O)C5=O)CC3)N2C(=O)[C@@H](NC(=O)c2cc3cc(C(F)(F)P(=O)(O)O)ccc3s2)C1</t>
+        </is>
+      </c>
+      <c r="G1295" t="inlineStr"/>
+      <c r="H1295" t="inlineStr"/>
+      <c r="I1295" t="n">
+        <v>0.7830406939910324</v>
+      </c>
+      <c r="J1295" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1295" t="inlineStr"/>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="1" t="n">
+        <v>1294</v>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1566.png</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr"/>
+      <c r="D1296" t="inlineStr"/>
+      <c r="E1296" t="inlineStr"/>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>CC(C)Nc1cc(-c2ccc3cc(C#N)cnn23)ncc1-c1nnc(N2CCN(C(=O)CCCCCNc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)CC2)s1</t>
+        </is>
+      </c>
+      <c r="G1296" t="inlineStr"/>
+      <c r="H1296" t="inlineStr"/>
+      <c r="I1296" t="n">
+        <v>0.8207695339118048</v>
+      </c>
+      <c r="J1296" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1296" t="inlineStr"/>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="1" t="n">
+        <v>1295</v>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1574.png</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr"/>
+      <c r="D1297" t="inlineStr"/>
+      <c r="E1297" t="inlineStr"/>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>O=C(C1=CC=C(OC(F)F)C(OCC2CC2)=C1)N(CCCCCCCN1CCC(C2=CC=CC=C2CNC23CCC4(=O)N5C267=O=C53(=O=6)N47)CC1)C1=C(Cl)C=NC=C1Cl</t>
+        </is>
+      </c>
+      <c r="G1297" t="inlineStr"/>
+      <c r="H1297" t="inlineStr"/>
+      <c r="I1297" t="n">
+        <v>0.7582999548389051</v>
+      </c>
+      <c r="J1297" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1297" t="inlineStr"/>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="1" t="n">
+        <v>1296</v>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1578.png</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr"/>
+      <c r="D1298" t="inlineStr"/>
+      <c r="E1298" t="inlineStr"/>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(C(C)NC(=O)C3CC(O)CN3C(=O)C(C3=CC(N4CCC(N5CCC(OC6CC(OC7=CC(N89%10CCC%11C8%12C8C9%13C9C%10%14C%10C%12%13C%119%14N8%10C8=CC(C9=C(O)C=CC=C9)=NN=C8N)=CC=N7)C6)CC5)CC4)=NO3)C(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1298" t="inlineStr"/>
+      <c r="H1298" t="inlineStr"/>
+      <c r="I1298" t="n">
+        <v>0.02055938261914675</v>
+      </c>
+      <c r="J1298" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1298" t="inlineStr"/>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="1" t="n">
+        <v>1297</v>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T071416_3/rb_1586.png</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr"/>
+      <c r="D1299" t="inlineStr"/>
+      <c r="E1299" t="inlineStr"/>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1cc(F)c([C@H](C)NC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@H](c2cc(N3CCC(CN4CCC(O[C@@H]5C[C@@H](Oc6cc(N7C8CCC7CN(c7cc(-c9ccccc9O)nnc7N)C8)ccn6)C5)CC4)CC3)no2)C(C)C)cc1F</t>
+        </is>
+      </c>
+      <c r="G1299" t="inlineStr"/>
+      <c r="H1299" t="inlineStr"/>
+      <c r="I1299" t="n">
+        <v>0.7123150301062497</v>
+      </c>
+      <c r="J1299" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1299" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1299"/>
+  <dimension ref="A1:K1382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38122,6 +38122,2413 @@
       </c>
       <c r="K1299" t="inlineStr"/>
     </row>
+    <row r="1300">
+      <c r="A1300" s="1" t="n">
+        <v>1298</v>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1601.png</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr"/>
+      <c r="D1300" t="inlineStr"/>
+      <c r="E1300" t="inlineStr"/>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>C#CC1=C(F)C=CC2=C1C(C1=NC=C3C(N456CCN(C(=O)OC(C)(C)C)C7(C4)C5C76)=NC(OCC45CCCN4C(CN4CCN(CC6CCN(C7=CC=C8C(=O)N(C9CCC(=O)NC9=O)CC8=C7)CC6)CC4)CC5)=NC3=C1F)=CC(OCOC)=C2</t>
+        </is>
+      </c>
+      <c r="G1300" t="inlineStr"/>
+      <c r="H1300" t="inlineStr"/>
+      <c r="I1300" t="n">
+        <v>0.3968877280575184</v>
+      </c>
+      <c r="J1300" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1300" t="inlineStr"/>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="1" t="n">
+        <v>1299</v>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1609.png</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr"/>
+      <c r="D1301" t="inlineStr"/>
+      <c r="E1301" t="inlineStr"/>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>CC1=C2C=C(C3=CC=C(CN4CCOCC4)C=C3)C=C13CCCCC1(=C(COC2=O)C(=O)NC=C1)CC1C2C(C)C1N23C1CC2C34C(C1)O21C3(=O)C2C3O5CC6O(CC5O3C241=O)C1CO23CCO45C7CO8CCOCCOCCOCCO9C%10=O=C%11CO%12CCC%12=C%12C(C(=O)N(C)CCCC=O)=CC=CC%12OCCNC(=O)(CC9OCCOCCOCCOCCOC8C4O7C5C2OC3CO61)C%11%10</t>
+        </is>
+      </c>
+      <c r="G1301" t="inlineStr"/>
+      <c r="H1301" t="inlineStr"/>
+      <c r="I1301" t="n">
+        <v>2.451378697280502e-07</v>
+      </c>
+      <c r="J1301" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1301" t="inlineStr"/>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1621.png</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr"/>
+      <c r="D1302" t="inlineStr"/>
+      <c r="E1302" t="inlineStr"/>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>CCOc1cc(O[C@@H]2CC[C@@H](NC(=O)c3cnc(N4CC5CN([C@@H]6C[C@@H](Oc7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)C6)C(C)CC54)nc3)CC2)ccc1C#N</t>
+        </is>
+      </c>
+      <c r="G1302" t="inlineStr"/>
+      <c r="H1302" t="inlineStr"/>
+      <c r="I1302" t="n">
+        <v>0.8168983492821332</v>
+      </c>
+      <c r="J1302" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1302" t="inlineStr"/>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="1" t="n">
+        <v>1301</v>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1629.png</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr"/>
+      <c r="D1303" t="inlineStr"/>
+      <c r="E1303" t="inlineStr"/>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>[H][C@@]1(CC[C@]2([H])[C@]3([H])C(=C[C@]([H])(C)C[C@]3([H])OC(=O)NCc3cncc(CNC(=O)COc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)c3)C=C[C@]2([H])C)C[C@@]([H])(O[Si](C)(C)C(C)(C)C)CC(=O)O1</t>
+        </is>
+      </c>
+      <c r="G1303" t="inlineStr"/>
+      <c r="H1303" t="inlineStr"/>
+      <c r="I1303" t="n">
+        <v>0.793701636138281</v>
+      </c>
+      <c r="J1303" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1303" t="inlineStr"/>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="1" t="n">
+        <v>1302</v>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1633.png</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr"/>
+      <c r="D1304" t="inlineStr"/>
+      <c r="E1304" t="inlineStr"/>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>CC1CC2C(CN2c2ccc(C(=O)NC3C(C)(C)C(Oc4ccc(C#N)c(Cl)c4)C3(C)C)cc2)CN1C1CC(Oc2ccc3c(c2)C(=O)N(C2CCC(=O)NC2=O)C3=O)C1</t>
+        </is>
+      </c>
+      <c r="G1304" t="inlineStr"/>
+      <c r="H1304" t="inlineStr"/>
+      <c r="I1304" t="n">
+        <v>0.7292159532431526</v>
+      </c>
+      <c r="J1304" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1304" t="inlineStr"/>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="1" t="n">
+        <v>1303</v>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1653.png</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr"/>
+      <c r="D1305" t="inlineStr"/>
+      <c r="E1305" t="inlineStr"/>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>COC1=C(C2=NC=C3NN=C4C3=N2C42=CC=C(N3CCN(CC(=O)NCCCCCCCCNC4=CC=C5C(=O)N(C6CCC(=O)NC6=O)C(=O)C5=C4)CC3)C=C2)C(F)=CC=C1</t>
+        </is>
+      </c>
+      <c r="G1305" t="inlineStr"/>
+      <c r="H1305" t="inlineStr"/>
+      <c r="I1305" t="n">
+        <v>0.4433569765372888</v>
+      </c>
+      <c r="J1305" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1305" t="inlineStr"/>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="1" t="n">
+        <v>1304</v>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1665.png</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr"/>
+      <c r="D1306" t="inlineStr"/>
+      <c r="E1306" t="inlineStr"/>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>COC1=C(C2=NC=C3NN=C(C4=CC=C(N5CCN(C(=O)CCCCCCC6=O=C6NC(C(=O)N6CC(O)CC6C(=O)NCC6=CC=C(C7=C(C)N=CS7)C=C6)C(C)(C)C)CC5)C=C4)C3=N2)C(F)=CC=C1</t>
+        </is>
+      </c>
+      <c r="G1306" t="inlineStr"/>
+      <c r="H1306" t="inlineStr"/>
+      <c r="I1306" t="n">
+        <v>0.2738687776740026</v>
+      </c>
+      <c r="J1306" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1306" t="inlineStr"/>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="1" t="n">
+        <v>1305</v>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1669.png</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr"/>
+      <c r="D1307" t="inlineStr"/>
+      <c r="E1307" t="inlineStr"/>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>[H][C@]1(OC(C)=O)CC(=O)O[C@]([H])(CC[C@]2([H])[C@]3([H])C(=C[C@]([H])(C)C[C@]3([H])OC(=O)NCCOCCOCCNc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)C=C[C@]2([H])C)C1</t>
+        </is>
+      </c>
+      <c r="G1307" t="inlineStr"/>
+      <c r="H1307" t="inlineStr"/>
+      <c r="I1307" t="n">
+        <v>0.8412181540705297</v>
+      </c>
+      <c r="J1307" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1307" t="inlineStr"/>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="1" t="n">
+        <v>1306</v>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1681.png</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr"/>
+      <c r="D1308" t="inlineStr"/>
+      <c r="E1308" t="inlineStr"/>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>[H]N1CCC12CCN(c1nc(OCCN3CCC(CN4CCN(CC5CCN(c6ccc7c(c6F)CN(C6CCC(=O)NC6=O)C7=O)CC5)CC4(C)C)CC3)nc3c(F)c(-c4cc(O)cc5ccc(F)c(C#C)c45)ncc13)C2</t>
+        </is>
+      </c>
+      <c r="G1308" t="inlineStr"/>
+      <c r="H1308" t="inlineStr"/>
+      <c r="I1308" t="n">
+        <v>0.5026938965868412</v>
+      </c>
+      <c r="J1308" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1308" t="inlineStr"/>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="1" t="n">
+        <v>1307</v>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1685.png</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr"/>
+      <c r="D1309" t="inlineStr"/>
+      <c r="E1309" t="inlineStr"/>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>[H][C@]1(OC)CC(=O)O[C@]([H])(CC[C@]2([H])[C@]3([H])C(=C[C@]([H])(C)C[C@]3([H])OC(=O)NCCOCCOCCNc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)C=C[C@]2([H])C)C1</t>
+        </is>
+      </c>
+      <c r="G1309" t="inlineStr"/>
+      <c r="H1309" t="inlineStr"/>
+      <c r="I1309" t="n">
+        <v>0.8408385654966298</v>
+      </c>
+      <c r="J1309" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1309" t="inlineStr"/>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="1" t="n">
+        <v>1308</v>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1693.png</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr"/>
+      <c r="D1310" t="inlineStr"/>
+      <c r="E1310" t="inlineStr"/>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>CC1=C(CC=CCCNC(=O)C2CC(O)CN2C(=O)C(NC(=O)CCOCCOCCOCCOCCOCCC(=O)(=O)NCCC(=O)NC2=CC3=CC(C4=C(C)C(N)=CN=C4)=C(F)C(N)=C3CN2)C(C)(C)C)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1310" t="inlineStr"/>
+      <c r="H1310" t="inlineStr"/>
+      <c r="I1310" t="n">
+        <v>0.4374830072046371</v>
+      </c>
+      <c r="J1310" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1310" t="inlineStr"/>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="1" t="n">
+        <v>1309</v>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1709.png</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr"/>
+      <c r="D1311" t="inlineStr"/>
+      <c r="E1311" t="inlineStr"/>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>C#Cc1c(F)ccc2cc(OCOC)cc(-c3ncc4c(N5CC6CCC(C5)N6C(=O)OC(C)(C)C)nc(OCCN5CCC(CN6CCC(CC7CCN(c8ccc9c(c8)CN(C8CCC(=O)NC8=O)C9=O)CC7)CC6)CC5)nc4c3F)c12</t>
+        </is>
+      </c>
+      <c r="G1311" t="inlineStr"/>
+      <c r="H1311" t="inlineStr"/>
+      <c r="I1311" t="n">
+        <v>0.7984320099081911</v>
+      </c>
+      <c r="J1311" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1311" t="inlineStr"/>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="1" t="n">
+        <v>1310</v>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1729.png</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr"/>
+      <c r="D1312" t="inlineStr"/>
+      <c r="E1312" t="inlineStr"/>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>COC1(CN2CCN3C4=CC(C5=CC=CC=C5O)=NN=C4NC[CH]3(C)C2)CCN(CC2CCN(C3=CC4=C(C=C3)C(=O)N(C3CCC(=O)NC3=O)C4)CC2)CC1</t>
+        </is>
+      </c>
+      <c r="G1312" t="inlineStr"/>
+      <c r="H1312" t="inlineStr"/>
+      <c r="I1312" t="n">
+        <v>0.6902726395495059</v>
+      </c>
+      <c r="J1312" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1312" t="inlineStr"/>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="1" t="n">
+        <v>1311</v>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1741.png</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr"/>
+      <c r="D1313" t="inlineStr"/>
+      <c r="E1313" t="inlineStr"/>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>COC1=C2C(=O)N(C3CCC(=O)NC3=O)C(=O)C2=CC(OC2CC(N3(C4CCN(C5=CC=C(C(=O)N[CH]67CC6(C)C(OC6=CC(C)=C(C#N)C=C6)C7(C)C)C=C5)CC4)CCOCC3)C2)=C1</t>
+        </is>
+      </c>
+      <c r="G1313" t="inlineStr"/>
+      <c r="H1313" t="inlineStr"/>
+      <c r="I1313" t="n">
+        <v>0.1705949455187626</v>
+      </c>
+      <c r="J1313" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1313" t="inlineStr"/>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="1" t="n">
+        <v>1312</v>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1745.png</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr"/>
+      <c r="D1314" t="inlineStr"/>
+      <c r="E1314" t="inlineStr"/>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>COc1cccc(F)c1-c1ncc2[nH]nc(-c3ccc(N4CCN(CC(=O)NCCOCCOCCNc5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)cc3)c2n1</t>
+        </is>
+      </c>
+      <c r="G1314" t="inlineStr"/>
+      <c r="H1314" t="inlineStr"/>
+      <c r="I1314" t="n">
+        <v>0.7719582980837228</v>
+      </c>
+      <c r="J1314" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1314" t="inlineStr"/>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="1" t="n">
+        <v>1313</v>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1753.png</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr"/>
+      <c r="D1315" t="inlineStr"/>
+      <c r="E1315" t="inlineStr"/>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>[H]N123CCC45C67C(C48C614CCC2C7843)C51=NC(OCC23CCCN2C(COC(=O)N2CCN(C4=C5C(=O)N(C6CCC(=O)NC6=O)C(=O)C5=CC=C4)CC2)CC3)=NC2=C(F)C(C3=C4C(=CC(O)=C3)C=CC=C4C(C)C)=NC=C21</t>
+        </is>
+      </c>
+      <c r="G1315" t="inlineStr"/>
+      <c r="H1315" t="inlineStr"/>
+      <c r="I1315" t="n">
+        <v>0.4054899128144829</v>
+      </c>
+      <c r="J1315" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1315" t="inlineStr"/>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="1" t="n">
+        <v>1314</v>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1757.png</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr"/>
+      <c r="D1316" t="inlineStr"/>
+      <c r="E1316" t="inlineStr"/>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>COc1cccc(F)c1-c1ncc2[nH]nc(-c3ccc(N4CCN(C(=O)CCCCCCCC(=O)N[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)NCc5ccc(-c6scnc6C)cc5)C(C)(C)C)CC4)cc3)c2n1</t>
+        </is>
+      </c>
+      <c r="G1316" t="inlineStr"/>
+      <c r="H1316" t="inlineStr"/>
+      <c r="I1316" t="n">
+        <v>0.5828475163027366</v>
+      </c>
+      <c r="J1316" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1316" t="inlineStr"/>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="1" t="n">
+        <v>1315</v>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1765.png</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr"/>
+      <c r="D1317" t="inlineStr"/>
+      <c r="E1317" t="inlineStr"/>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>[H]C1(C)C=C2C=CC([H])(C)C([H])(CCC3([H])CC([H])(O[SH]=[2H])CC(=O)O3)C2([H])C([H])(OC(=O)NCCOCCCCCOCCNC2=C3C(=O)N(C4CCC(=O)NC4=O)C(=O)C3=CC=C2)C1</t>
+        </is>
+      </c>
+      <c r="G1317" t="inlineStr"/>
+      <c r="H1317" t="inlineStr"/>
+      <c r="I1317" t="n">
+        <v>0.7545165517099425</v>
+      </c>
+      <c r="J1317" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1317" t="inlineStr"/>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="1" t="n">
+        <v>1316</v>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1769.png</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr"/>
+      <c r="D1318" t="inlineStr"/>
+      <c r="E1318" t="inlineStr"/>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>CC1=C(C(=O)Nc2ccc3[nH]nc(-c4ccnc(N5CCN(CC6CN(C7CCN(c8ccc9c(c8)C(=O)N(C8CCC(=O)NC8=O)C9=O)CC7)C6)CC5)c4)c3c2)[C@@H](C)n2nnnc2N1C</t>
+        </is>
+      </c>
+      <c r="G1318" t="inlineStr"/>
+      <c r="H1318" t="inlineStr"/>
+      <c r="I1318" t="n">
+        <v>0.8427224279155722</v>
+      </c>
+      <c r="J1318" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1318" t="inlineStr"/>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="1" t="n">
+        <v>1317</v>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1801.png</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr"/>
+      <c r="D1319" t="inlineStr"/>
+      <c r="E1319" t="inlineStr"/>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>CCN(c1cc(C(=O)NCc2c(C)cc(C)[nH]c2=O)cc(-c2ccc(CN3CCN(CC(=O)NCCCCCOCCCOCC(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)NCc4ccc(-c5scnc5C)cc4)C(C)C)CC3)cc2)c1)C1CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1319" t="inlineStr"/>
+      <c r="H1319" t="inlineStr"/>
+      <c r="I1319" t="n">
+        <v>0.8362200729321148</v>
+      </c>
+      <c r="J1319" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1319" t="inlineStr"/>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="1" t="n">
+        <v>1318</v>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1813.png</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr"/>
+      <c r="D1320" t="inlineStr"/>
+      <c r="E1320" t="inlineStr"/>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>CC1CC2C(CN2c2ncc(C(=O)N[C@@H]3CC[C@@H](Oc4ccc(C#N)c(Cl)c4)CC3)cn2)CN1[C@@H]1C[C@@H](Oc2ccc3c(c2)C(=O)N(C2CCC(=O)NC2=O)C3=O)C1</t>
+        </is>
+      </c>
+      <c r="G1320" t="inlineStr"/>
+      <c r="H1320" t="inlineStr"/>
+      <c r="I1320" t="n">
+        <v>0.7601612421915017</v>
+      </c>
+      <c r="J1320" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1320" t="inlineStr"/>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="1" t="n">
+        <v>1319</v>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1821.png</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr"/>
+      <c r="D1321" t="inlineStr"/>
+      <c r="E1321" t="inlineStr"/>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>CCN(c1cc(-c2ccc(CN3CCN(CCCCCCCCCCCC(=O)N[C@H](C(=O)N4C[C@@H](C)C[C@H]4C(=O)NCc4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc2)cc(C(=O)NCc2c(C)cc(C)[nH]c2=O)c1C)C1CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1321" t="inlineStr"/>
+      <c r="H1321" t="inlineStr"/>
+      <c r="I1321" t="n">
+        <v>0.7978480116900178</v>
+      </c>
+      <c r="J1321" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1321" t="inlineStr"/>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="1" t="n">
+        <v>1320</v>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_0/rb_1845.png</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr"/>
+      <c r="D1322" t="inlineStr"/>
+      <c r="E1322" t="inlineStr"/>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>C#Cc1c(F)ccc2cc(O)cc(-c3ncc4c(N5CC6NC7(CC67)C5)nc(OCCN5CCC(C(F)(F)C6CCN(CC7CCN(c8ccc9c(c8F)CN(C8CCC(=O)NC8=O)C9=O)CC7)CC6)CC5)nc4c3F)c12</t>
+        </is>
+      </c>
+      <c r="G1322" t="inlineStr"/>
+      <c r="H1322" t="inlineStr"/>
+      <c r="I1322" t="n">
+        <v>0.5731391052815046</v>
+      </c>
+      <c r="J1322" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1322" t="inlineStr"/>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="1" t="n">
+        <v>1321</v>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1614.png</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr"/>
+      <c r="D1323" t="inlineStr"/>
+      <c r="E1323" t="inlineStr"/>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)COCCOCCOCC(=O)N2CCN(CCCNC(=O)c3c(C)[nH]c(/C=C4\C(=O)Nc5ccc(F)cc54)c3C)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1323" t="inlineStr"/>
+      <c r="H1323" t="inlineStr"/>
+      <c r="I1323" t="n">
+        <v>0.8149673844138653</v>
+      </c>
+      <c r="J1323" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1323" t="inlineStr"/>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="1" t="n">
+        <v>1322</v>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1618.png</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr"/>
+      <c r="D1324" t="inlineStr"/>
+      <c r="E1324" t="inlineStr"/>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>COC1=C(C2=NC=C3NN=C(C4=CC=C(N56CCNCC(=O)NCCCCCCCCCC7(=O)=O=C8(N7)[CH]79%10C%11%12%13=O=C7%14(=O)(N%117C%11C(O)CN%117%12%14)[CH]8%137(NC(=O)CCCCCCCCCNC(=O)CN(CC5)CC6)C9568%11%12CC%107(C5)(C6)(C8)(C%11)C%12)C=C4)C3=N2)C(F)=CC=C1</t>
+        </is>
+      </c>
+      <c r="G1324" t="inlineStr"/>
+      <c r="H1324" t="inlineStr"/>
+      <c r="I1324" t="n">
+        <v>0.00447952789025804</v>
+      </c>
+      <c r="J1324" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1324" t="inlineStr"/>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="1" t="n">
+        <v>1323</v>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1622.png</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr"/>
+      <c r="D1325" t="inlineStr"/>
+      <c r="E1325" t="inlineStr"/>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(N4CCN(C(=O)OCCN5CCC(N6CCN7c8cc(-c9ccccc9O)nnc8NC[C@H]7C6)CC5)CC4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1325" t="inlineStr"/>
+      <c r="H1325" t="inlineStr"/>
+      <c r="I1325" t="n">
+        <v>0.7638958276634141</v>
+      </c>
+      <c r="J1325" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1325" t="inlineStr"/>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="1" t="n">
+        <v>1324</v>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1626.png</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr"/>
+      <c r="D1326" t="inlineStr"/>
+      <c r="E1326" t="inlineStr"/>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>[H]N123CCCC1CN14567C8C2CC2C19C1CC3C4N893(C215)C612=C45C=NC6=C89(F)=C%10%11(=C%12(F)C8%13%14=NC8%15=NC437%16=C%131(C=N%10)C5%129=N8%14C(=N2%16)OCCN1(CCCCC1)CCO%15)C61=C2C3(C#C)=C(F)C=CC24=C2=C56=CC=CC%11(=C345C(C#C)=C(F)C=C6)C1=C2</t>
+        </is>
+      </c>
+      <c r="G1326" t="inlineStr"/>
+      <c r="H1326" t="inlineStr"/>
+      <c r="I1326" t="n">
+        <v>7.151557464412992e-06</v>
+      </c>
+      <c r="J1326" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1326" t="inlineStr"/>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="1" t="n">
+        <v>1325</v>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1634.png</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr"/>
+      <c r="D1327" t="inlineStr"/>
+      <c r="E1327" t="inlineStr"/>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>Cc1noc(C)c1-c1ccn2c(NC3CCCCC3)c(CCc3ccc(NC(=O)CCOCCOCCOCCNc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)cc3)nc2c1</t>
+        </is>
+      </c>
+      <c r="G1327" t="inlineStr"/>
+      <c r="H1327" t="inlineStr"/>
+      <c r="I1327" t="n">
+        <v>0.6594430396096541</v>
+      </c>
+      <c r="J1327" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1327" t="inlineStr"/>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="1" t="n">
+        <v>1326</v>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1642.png</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr"/>
+      <c r="D1328" t="inlineStr"/>
+      <c r="E1328" t="inlineStr"/>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>CCN(c1cc(-c2ccc(CN3CCN(CC(=O)NCCCCCCN[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)NCc4ccc(-c5scnc5C)cc4)C(C)(C)C)CC3)cc2)cc(C(=O)NCc2c(C)cc(C)[nH]c2=O)c1C)C1CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1328" t="inlineStr"/>
+      <c r="H1328" t="inlineStr"/>
+      <c r="I1328" t="n">
+        <v>0.6419639491325835</v>
+      </c>
+      <c r="J1328" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1328" t="inlineStr"/>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="1" t="n">
+        <v>1327</v>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1658.png</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr"/>
+      <c r="D1329" t="inlineStr"/>
+      <c r="E1329" t="inlineStr"/>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>CC1(CN2CCN34C56=CC(C7=CC=CC=C7O)=N7=C8(C9=CC=CC=C9O)=NN=C59NC[CH]3(CNC6(=N7)C94=C8)C2)CCN(CC2CCN(C3=CC4=C(C=C3)C(=O)N(C3CCC(=O)NC3=O)C4)CC2)CC1</t>
+        </is>
+      </c>
+      <c r="G1329" t="inlineStr"/>
+      <c r="H1329" t="inlineStr"/>
+      <c r="I1329" t="n">
+        <v>0.2401465746376237</v>
+      </c>
+      <c r="J1329" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1329" t="inlineStr"/>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="1" t="n">
+        <v>1328</v>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1682.png</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr"/>
+      <c r="D1330" t="inlineStr"/>
+      <c r="E1330" t="inlineStr"/>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>[H]N1CCCC1.[H]NCCN(C)c1nc(OCCN2CCC(CN3CCN(CC4CCN(c5ccc6c(c5F)CN(C5CCC(=O)NC5=O)C6=O)CC4)C(C)(C)C3)CC2)nc2c(F)c(-c3cc(O)cc4ccc(F)c(C#C)c34)ncc12</t>
+        </is>
+      </c>
+      <c r="G1330" t="inlineStr"/>
+      <c r="H1330" t="inlineStr"/>
+      <c r="I1330" t="n">
+        <v>0.3271966798904722</v>
+      </c>
+      <c r="J1330" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1330" t="inlineStr"/>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="1" t="n">
+        <v>1329</v>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1690.png</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr"/>
+      <c r="D1331" t="inlineStr"/>
+      <c r="E1331" t="inlineStr"/>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>C#Cc1c(F)ccc2cc(O)cc(-c3ncc4c(NCC5CCCN5)nc(OC[C@@H]5C[C@@H](OC6CCN(CC7CN(c8ccc9c(c8)CN(C8CCC(=O)NC8=O)C9=O)C7)CC6)CN5C)nc4c3F)c12</t>
+        </is>
+      </c>
+      <c r="G1331" t="inlineStr"/>
+      <c r="H1331" t="inlineStr"/>
+      <c r="I1331" t="n">
+        <v>0.7666224990103564</v>
+      </c>
+      <c r="J1331" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1331" t="inlineStr"/>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="1" t="n">
+        <v>1330</v>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1710.png</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr"/>
+      <c r="D1332" t="inlineStr"/>
+      <c r="E1332" t="inlineStr"/>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>[H]C1C2C3([H])(C)C=C4C=CC([H])(C)C5([H])(CCC([H])(O)CC([H])(O)CC(=O)O)C678([H])C9%10=CC2([H])(C)C3[CH]6([H])C41957([H])C8([H])(CCC([H])(O)CC([H])(O)CC(=O)O)C([H])(C)C=C%10</t>
+        </is>
+      </c>
+      <c r="G1332" t="inlineStr"/>
+      <c r="H1332" t="inlineStr"/>
+      <c r="I1332" t="n">
+        <v>0.08803924281471437</v>
+      </c>
+      <c r="J1332" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1332" t="inlineStr"/>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="1" t="n">
+        <v>1331</v>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1730.png</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr"/>
+      <c r="D1333" t="inlineStr"/>
+      <c r="E1333" t="inlineStr"/>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>COc1cccc(F)c1-c1ncc2[nH]nc(-c3ccc(N4CCN(C(=O)CCOCCOCCOCCOCCOCCNc5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)cc3)c2n1</t>
+        </is>
+      </c>
+      <c r="G1333" t="inlineStr"/>
+      <c r="H1333" t="inlineStr"/>
+      <c r="I1333" t="n">
+        <v>0.8351003902333418</v>
+      </c>
+      <c r="J1333" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1333" t="inlineStr"/>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="1" t="n">
+        <v>1332</v>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1742.png</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr"/>
+      <c r="D1334" t="inlineStr"/>
+      <c r="E1334" t="inlineStr"/>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>CC1(C)CC(C)(C)C1OC1=CC=C(C#N)C(Cl)=C1.O=C123=O=C4(N1)C21=CC=C25=C6=CC437=CC=C6(C2=C17)N1(CCNCC1)C1CNCCN15.O=C1CCC(N2C(=O)C3=C(C=C(OC4CCCC4)C=C3)C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1334" t="inlineStr"/>
+      <c r="H1334" t="inlineStr"/>
+      <c r="I1334" t="n">
+        <v>0.09432579010503853</v>
+      </c>
+      <c r="J1334" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1334" t="inlineStr"/>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="1" t="n">
+        <v>1333</v>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1750.png</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr"/>
+      <c r="D1335" t="inlineStr"/>
+      <c r="E1335" t="inlineStr"/>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>COc1cccc(F)c1-c1ncc2[nH]nc(-c3ccc(N4CCN(CC(=O)NCCCCC(=O)N[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)NCc5ccc(-c6scnc6C)cc5)C(C)(C)C)CC4)cc3)c2n1</t>
+        </is>
+      </c>
+      <c r="G1335" t="inlineStr"/>
+      <c r="H1335" t="inlineStr"/>
+      <c r="I1335" t="n">
+        <v>0.8280490218708512</v>
+      </c>
+      <c r="J1335" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1335" t="inlineStr"/>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="1" t="n">
+        <v>1334</v>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1754.png</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr"/>
+      <c r="D1336" t="inlineStr"/>
+      <c r="E1336" t="inlineStr"/>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>C#CC1=C(F)C=CC2=CC(O)=CC(C34=NC=C5(C(N=COCCN6CCC(CC7CCN(CCCCNCC=CCN8CCCC(=O)CC8)CC7)CC6)=CCC36=C3C7(=CC78=CC=8)C7=CC=73=CC(O)=C6)C(N36CCNC(C3)C6)=NC(OCCN3CCC(CC6CCN(CC7CCN(C8=CC=C9C(=O)N(C%10CCC(=O)NC%10=O)CC9=C8)CC7)CC6)CC3)=NC5=C4F)=C21</t>
+        </is>
+      </c>
+      <c r="G1336" t="inlineStr"/>
+      <c r="H1336" t="inlineStr"/>
+      <c r="I1336" t="n">
+        <v>0.0003824947112795073</v>
+      </c>
+      <c r="J1336" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1336" t="inlineStr"/>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="1" t="n">
+        <v>1335</v>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1774.png</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr"/>
+      <c r="D1337" t="inlineStr"/>
+      <c r="E1337" t="inlineStr"/>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>COc1cccc(F)c1-c1ncc2[nH]nc(-c3ccc(N4CCN(C(=O)CCCCC(=O)N[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)NCc5ccc(-c6scnc6C)cc5)C(C)(C)C)CC4)cc3)c2n1</t>
+        </is>
+      </c>
+      <c r="G1337" t="inlineStr"/>
+      <c r="H1337" t="inlineStr"/>
+      <c r="I1337" t="n">
+        <v>0.7191197337658054</v>
+      </c>
+      <c r="J1337" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1337" t="inlineStr"/>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="1" t="n">
+        <v>1336</v>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1790.png</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr"/>
+      <c r="D1338" t="inlineStr"/>
+      <c r="E1338" t="inlineStr"/>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>[H][C@]1(O)CC(=O)O[C@]([H])(CC[C@]2([H])[C@]3([H])C(=C[C@]([H])(C)C[C@]3([H])OC(=O)NCCCOCCCCNc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)C=C[C@]2([H])C)C1</t>
+        </is>
+      </c>
+      <c r="G1338" t="inlineStr"/>
+      <c r="H1338" t="inlineStr"/>
+      <c r="I1338" t="n">
+        <v>0.8030306156765605</v>
+      </c>
+      <c r="J1338" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1338" t="inlineStr"/>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="1" t="n">
+        <v>1337</v>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1810.png</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr"/>
+      <c r="D1339" t="inlineStr"/>
+      <c r="E1339" t="inlineStr"/>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>[H]N12CCCC134CN(C1=NC(OCC56CCCN5C(COC(=O)N5CCN(C7=CC8=C(C=C7)C(=O)N(C7CCC(=O)NC7=O)C8)CC5)CC6)=NC5=C(F)C(C6=C7C(=CC(O)=C6)C=CC=C7CC)=NC=C15)CCC3C24</t>
+        </is>
+      </c>
+      <c r="G1339" t="inlineStr"/>
+      <c r="H1339" t="inlineStr"/>
+      <c r="I1339" t="n">
+        <v>0.2050250207766999</v>
+      </c>
+      <c r="J1339" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1339" t="inlineStr"/>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="1" t="n">
+        <v>1338</v>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_1/rb_1834.png</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr"/>
+      <c r="D1340" t="inlineStr"/>
+      <c r="E1340" t="inlineStr"/>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>CC1CC(C(=O)N2CCN3c4cc(-c5ccccc5O)nnc4NC[C@H]3C2)CCN1CC1CCN(c2ccc3c(c2)C(=O)N(C2CCC(=O)NC2=O)C3)CC1</t>
+        </is>
+      </c>
+      <c r="G1340" t="inlineStr"/>
+      <c r="H1340" t="inlineStr"/>
+      <c r="I1340" t="n">
+        <v>0.8097787975278466</v>
+      </c>
+      <c r="J1340" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1340" t="inlineStr"/>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="1" t="n">
+        <v>1339</v>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1611.png</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr"/>
+      <c r="D1341" t="inlineStr"/>
+      <c r="E1341" t="inlineStr"/>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>[H]N1CCN(C2=C3C=CC4(C5=CC(O)=CC6=C5C(C#C)=C(F)C=C6)=C5C4C35=NC(OCCN3CCC(CC4CCN(CC5CCN(C6=C(F)C7=C(C=C6)C(=O)N(C6CCC(=O)NC6=O)C7)CC5)CC4)CC3)=N2)CC1</t>
+        </is>
+      </c>
+      <c r="G1341" t="inlineStr"/>
+      <c r="H1341" t="inlineStr"/>
+      <c r="I1341" t="n">
+        <v>0.5291233101982596</v>
+      </c>
+      <c r="J1341" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1341" t="inlineStr"/>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="1" t="n">
+        <v>1340</v>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1627.png</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr"/>
+      <c r="D1342" t="inlineStr"/>
+      <c r="E1342" t="inlineStr"/>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>CC1=CC=CC2=C1C(C1=C(F)C3=C(C=N1)C(N1CC4CCC(C1)N4)=NC(OCCN145CCCCNC(C6CCN(C7=CC8=C(C=C7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)N6CC7CN(CC1)C1C4C(CC76)C15)=N3)=CC(O)=C2</t>
+        </is>
+      </c>
+      <c r="G1342" t="inlineStr"/>
+      <c r="H1342" t="inlineStr"/>
+      <c r="I1342" t="n">
+        <v>0.1230118332739503</v>
+      </c>
+      <c r="J1342" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1342" t="inlineStr"/>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="1" t="n">
+        <v>1341</v>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1643.png</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr"/>
+      <c r="D1343" t="inlineStr"/>
+      <c r="E1343" t="inlineStr"/>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>C#Cc1c(F)ccc2cc(O)cc(-c3ncc4c(NCC5CCCN5)nc(OCCN5CCC(CN6CC7(CCN(c8cc(C)c9c(c8F)CN(C8CCC(=O)NC8=O)C9=O)CC7)C6)CC5)nc4c3F)c12</t>
+        </is>
+      </c>
+      <c r="G1343" t="inlineStr"/>
+      <c r="H1343" t="inlineStr"/>
+      <c r="I1343" t="n">
+        <v>0.7465804649564657</v>
+      </c>
+      <c r="J1343" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1343" t="inlineStr"/>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="1" t="n">
+        <v>1342</v>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1647.png</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr"/>
+      <c r="D1344" t="inlineStr"/>
+      <c r="E1344" t="inlineStr"/>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>COc1cccc(F)c1-c1ncc2[nH]nc(-c3ccc(N4CCN(CC(=O)NCCOCCNc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)cc3)c2n1</t>
+        </is>
+      </c>
+      <c r="G1344" t="inlineStr"/>
+      <c r="H1344" t="inlineStr"/>
+      <c r="I1344" t="n">
+        <v>0.7893006186562986</v>
+      </c>
+      <c r="J1344" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1344" t="inlineStr"/>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="1" t="n">
+        <v>1343</v>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1655.png</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr"/>
+      <c r="D1345" t="inlineStr"/>
+      <c r="E1345" t="inlineStr"/>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(N4CCC(NC56CC(CN7CCN8c9cc(-c%10ccccc%10O)nnc9NC[C@H]8C7)(C5)C6)CC4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1345" t="inlineStr"/>
+      <c r="H1345" t="inlineStr"/>
+      <c r="I1345" t="n">
+        <v>0.8422057208900023</v>
+      </c>
+      <c r="J1345" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1345" t="inlineStr"/>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="1" t="n">
+        <v>1344</v>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1659.png</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr"/>
+      <c r="D1346" t="inlineStr"/>
+      <c r="E1346" t="inlineStr"/>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>[H][C@@]1(CC[C@]2([H])[C@]3([H])C(=C[C@]([H])(C)C[C@]3([H])OC(=O)NCCOCCOCCNc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)C=C[C@]2([H])C)C[C@@]([H])(O[Si](C(C)C)(C(C)C)C(C)C)CC(=O)O1</t>
+        </is>
+      </c>
+      <c r="G1346" t="inlineStr"/>
+      <c r="H1346" t="inlineStr"/>
+      <c r="I1346" t="n">
+        <v>0.8373721221416833</v>
+      </c>
+      <c r="J1346" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1346" t="inlineStr"/>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="1" t="n">
+        <v>1345</v>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1663.png</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr"/>
+      <c r="D1347" t="inlineStr"/>
+      <c r="E1347" t="inlineStr"/>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>Cc1noc(C)c1-c1ccc2nc(-c3ccc(N4CCN(C(=O)CCCCCCCCCCCNc5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)cc3)c(NC3CCCCC3)n2c1</t>
+        </is>
+      </c>
+      <c r="G1347" t="inlineStr"/>
+      <c r="H1347" t="inlineStr"/>
+      <c r="I1347" t="n">
+        <v>0.5489583527155764</v>
+      </c>
+      <c r="J1347" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1347" t="inlineStr"/>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="1" t="n">
+        <v>1346</v>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1687.png</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr"/>
+      <c r="D1348" t="inlineStr"/>
+      <c r="E1348" t="inlineStr"/>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>CCC1=CC=CC2=CC(O)=CC(C3=NC=C4C(N56CCNC(CC5)C6)=NC(OCC56CCCN5C(COC(=O)N5CCN(C7=CC8=C(C=C7)C(=O)N(C7CCC(=O)NC7=O)C8)CC5)CC6)=NC4=C3F)=C21</t>
+        </is>
+      </c>
+      <c r="G1348" t="inlineStr"/>
+      <c r="H1348" t="inlineStr"/>
+      <c r="I1348" t="n">
+        <v>0.631723888116693</v>
+      </c>
+      <c r="J1348" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1348" t="inlineStr"/>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="1" t="n">
+        <v>1347</v>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1695.png</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr"/>
+      <c r="D1349" t="inlineStr"/>
+      <c r="E1349" t="inlineStr"/>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>[H][C@@]1(CC[C@]2([H])[C@]3([H])C(=C[C@]([H])(C)C[C@]3([H])OC(=O)NCCOCCOCC(=O)Nc3cccc4c3C(=O)N(C3CCC(=O)NC3=O)C4=O)C=C[C@]2([H])C)C[C@@]([H])(O[Si](C)(C)C(C)(C)C)CC(=O)O1</t>
+        </is>
+      </c>
+      <c r="G1349" t="inlineStr"/>
+      <c r="H1349" t="inlineStr"/>
+      <c r="I1349" t="n">
+        <v>0.821655499550235</v>
+      </c>
+      <c r="J1349" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1349" t="inlineStr"/>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="1" t="n">
+        <v>1348</v>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1707.png</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr"/>
+      <c r="D1350" t="inlineStr"/>
+      <c r="E1350" t="inlineStr"/>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(N4CCC(OCCN5CCC(N6CCN7c8cc(-c9ccccc9O)nnc8NC[C@H]7C6)C5)CC4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1350" t="inlineStr"/>
+      <c r="H1350" t="inlineStr"/>
+      <c r="I1350" t="n">
+        <v>0.8233561885879073</v>
+      </c>
+      <c r="J1350" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1350" t="inlineStr"/>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="1" t="n">
+        <v>1349</v>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1711.png</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr"/>
+      <c r="D1351" t="inlineStr"/>
+      <c r="E1351" t="inlineStr"/>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>CC1(CN2CCC(CN3CCN45C6=CC(C7=CC=CC=C7O)=NN=C6N6C7C48C3[CH]75C68)CC2)CCN(C2=CC3=C(C=C2)C(=O)N(C2CCC(=O)NC2=O)C3=O)CC1</t>
+        </is>
+      </c>
+      <c r="G1351" t="inlineStr"/>
+      <c r="H1351" t="inlineStr"/>
+      <c r="I1351" t="n">
+        <v>0.5441493816249375</v>
+      </c>
+      <c r="J1351" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1351" t="inlineStr"/>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="1" t="n">
+        <v>1350</v>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1751.png</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr"/>
+      <c r="D1352" t="inlineStr"/>
+      <c r="E1352" t="inlineStr"/>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>COC1=CC(OC2C(C)(C)C(NC(=O)C3=CN=C(N4CC5C6N78C5N65(C(C)C(C4)C75C)[CH]84CC(OC5=CC=C6C(=O)N(C7CCC(=O)NC7=O)C(=O)C6=C5)C4)C=N3)C2(C)C)=CC=C1C#N</t>
+        </is>
+      </c>
+      <c r="G1352" t="inlineStr"/>
+      <c r="H1352" t="inlineStr"/>
+      <c r="I1352" t="n">
+        <v>0.1358879674546468</v>
+      </c>
+      <c r="J1352" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1352" t="inlineStr"/>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="1" t="n">
+        <v>1351</v>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1767.png</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr"/>
+      <c r="D1353" t="inlineStr"/>
+      <c r="E1353" t="inlineStr"/>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>CCC12C(F)=CC=C34C=C(O)C=C(C5=NC=C6C(NCC78CCC(CC7)N8)=NC(OCCN7CCC(CC8CCN(CC9CCN(C%10=CC=CC%11=C%10CN(C%10CCC(=O)NC%10=O)C%11=O)CC9)CC8)CC7)=NC6=C5F)C13=C24</t>
+        </is>
+      </c>
+      <c r="G1353" t="inlineStr"/>
+      <c r="H1353" t="inlineStr"/>
+      <c r="I1353" t="n">
+        <v>0.2642196442071867</v>
+      </c>
+      <c r="J1353" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1353" t="inlineStr"/>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="1" t="n">
+        <v>1352</v>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1771.png</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr"/>
+      <c r="D1354" t="inlineStr"/>
+      <c r="E1354" t="inlineStr"/>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]C=CC=CC=C(CCN1C2CN(C3=CC(C4=C([N+]#[C-])C=CN=C4)=CC=C3NC(=O)C3=NC(OC)=NC=C3)CCN23C(=O)CCOCCOCCOCCOCCNC2=CC=C4(C(=O)N(C5CCC(=O)NC5=O)C(=O)C4=C2)C2(=O)(C=CC=CNCCOCCOCCOCCOCCC13=O)NC2CCC=O)NC(=O)C1=NC(C2=C(F)C=CC=C2)=NC=C1</t>
+        </is>
+      </c>
+      <c r="G1354" t="inlineStr"/>
+      <c r="H1354" t="inlineStr"/>
+      <c r="I1354" t="n">
+        <v>0.1238972633759907</v>
+      </c>
+      <c r="J1354" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1354" t="inlineStr"/>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="1" t="n">
+        <v>1353</v>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1779.png</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr"/>
+      <c r="D1355" t="inlineStr"/>
+      <c r="E1355" t="inlineStr"/>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3ccc(N4CC(CN5C[C@@H]6[C@H](C5)[C@H]6CN5CCN6c7cc(-c8ccccc8O)nnc7NC[C@H]6C5)C4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1355" t="inlineStr"/>
+      <c r="H1355" t="inlineStr"/>
+      <c r="I1355" t="n">
+        <v>0.8418774829076949</v>
+      </c>
+      <c r="J1355" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1355" t="inlineStr"/>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="1" t="n">
+        <v>1354</v>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1783.png</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr"/>
+      <c r="D1356" t="inlineStr"/>
+      <c r="E1356" t="inlineStr"/>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>CC[C@H](NC(=O)CCCCCNC(=O)CN1CCN(c2ccc(-c3n[nH]c4cnc(-c5c(F)cccc5OC)nc34)cc2)CC1)C(=O)N1C[C@H](O)C[C@H]1C(=O)NCc1ccc(-c2scnc2C)cc1</t>
+        </is>
+      </c>
+      <c r="G1356" t="inlineStr"/>
+      <c r="H1356" t="inlineStr"/>
+      <c r="I1356" t="n">
+        <v>0.8073779842629777</v>
+      </c>
+      <c r="J1356" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1356" t="inlineStr"/>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="1" t="n">
+        <v>1355</v>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1811.png</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr"/>
+      <c r="D1357" t="inlineStr"/>
+      <c r="E1357" t="inlineStr"/>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>*N1C2CN(c3nc(OC[C@@H]4CC[C@@H](COC(=O)N5CCN(c6ccc7c(c6)CN(C6CCC(=O)NC6=O)C7=O)CC5)N4C)nc4c(F)c(-c5cc(O*=O)cc6ccc(F)c(C#C)c56)ncc34)CC13CC23 |$Boc;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;Roc;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1357" t="inlineStr"/>
+      <c r="H1357" t="inlineStr"/>
+      <c r="I1357" t="n">
+        <v>0.3611447038992087</v>
+      </c>
+      <c r="J1357" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1357" t="inlineStr"/>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="1" t="n">
+        <v>1356</v>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1819.png</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr"/>
+      <c r="D1358" t="inlineStr"/>
+      <c r="E1358" t="inlineStr"/>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>[H]C1(C)CC2=CC=C([H])(C)C([H])(CCC3([H])CC([H])([SH]=[2H]#*=[3H])CC(=O)O3)C2([H])C([H])(OC(=O)NCCCCCN2CCC(NC3=C4C(=O)N(C5CCC(=O)NC5=O)C(=O)C4=CC=C3)CC2)C1 |$;;;;;;;;;;;;;;;;;;;;;*;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1358" t="inlineStr"/>
+      <c r="H1358" t="inlineStr"/>
+      <c r="I1358" t="n">
+        <v>0.2794576701576297</v>
+      </c>
+      <c r="J1358" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1358" t="inlineStr"/>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="1" t="n">
+        <v>1357</v>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1827.png</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr"/>
+      <c r="D1359" t="inlineStr"/>
+      <c r="E1359" t="inlineStr"/>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>CCCOCCOCCOCCOCCOCCC1(=O)N2C3C4C567C89CN31(C(=O)CCOCCOCCOCCOCCOCCC(=O)NCCOC1=C3C(=O)N(C%10CCC(=O)NC%10=O)C(=O)C3=CC=C1)C28CC4912N534C589=C%10%11(C)=C3%12%13%14%15=C3%16%17%18=C%104%19%20(=C=%125(C3)(C%16)C%11%17(=CC(C3=CC=C(CN4CCOCC4)C=C3)=C%19%13)C(=O)NC3N%18C4C5%10%11%12=C%13%16C=C%17=N%18%19C%21=CC5(=C34%13%105C%18%11(=O)N%21%17C%19%125=O)CC3CN681%20%14C3CC%16)N792%15CC</t>
+        </is>
+      </c>
+      <c r="G1359" t="inlineStr"/>
+      <c r="H1359" t="inlineStr"/>
+      <c r="I1359" t="n">
+        <v>6.378422507986482e-06</v>
+      </c>
+      <c r="J1359" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1359" t="inlineStr"/>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="1" t="n">
+        <v>1358</v>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_2/rb_1843.png</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr"/>
+      <c r="D1360" t="inlineStr"/>
+      <c r="E1360" t="inlineStr"/>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>COCOC1=CC(C2=C(F)C3=NC(OCCN4CCC(CN5CCC(CN6CCN(C7=C(F)C8=C(C=C7)C(=O)N(C7CCC(=O)NC7=O)C8)CC6)CC5)CC4)=NC(N45CCN(C(=O)OC(C)(C)C)CC4C5)=C3C=N2)=C2C(=C1)C=CC(F)=C2C#C[Si]</t>
+        </is>
+      </c>
+      <c r="G1360" t="inlineStr"/>
+      <c r="H1360" t="inlineStr"/>
+      <c r="I1360" t="n">
+        <v>0.4877665454424556</v>
+      </c>
+      <c r="J1360" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1360" t="inlineStr"/>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="1" t="n">
+        <v>1359</v>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1608.png</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr"/>
+      <c r="D1361" t="inlineStr"/>
+      <c r="E1361" t="inlineStr"/>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>C#CC1=C(F)C=CC2=CC(O)=CC(C3=NC=C4C(NC)=NC(OCC5CC(OC6CCN(CC7CCN(C8=C(F)C9=C(C(=O)N(C%10CCC(=O)NC%10=O)C9)C(C)=C8)CC7)CC6)CN5C)=NC4=C3F)=C21.C1CC23C4N25C1N435</t>
+        </is>
+      </c>
+      <c r="G1361" t="inlineStr"/>
+      <c r="H1361" t="inlineStr"/>
+      <c r="I1361" t="n">
+        <v>0.422247838869727</v>
+      </c>
+      <c r="J1361" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1361" t="inlineStr"/>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="1" t="n">
+        <v>1360</v>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1612.png</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr"/>
+      <c r="D1362" t="inlineStr"/>
+      <c r="E1362" t="inlineStr"/>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCCCCCCC(=O)CCC(=O)Nc2ccc3c(c2)CC[C@@]32OC(=O)N(CC(=O)N(Cc3ccc(F)cc3)[C@@H](C)C(F)(F)F)C2=O)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1362" t="inlineStr"/>
+      <c r="H1362" t="inlineStr"/>
+      <c r="I1362" t="n">
+        <v>0.7553653490429403</v>
+      </c>
+      <c r="J1362" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1362" t="inlineStr"/>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="1" t="n">
+        <v>1361</v>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1620.png</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr"/>
+      <c r="D1363" t="inlineStr"/>
+      <c r="E1363" t="inlineStr"/>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>CC1=NC(C)=C1C1=CN2C(=CC1)NC(c1ccc(N3CCN(C(=O)CCOCCOCCOCCOCCOCCOCCNc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)cc1)=C2NC1CCCCC1</t>
+        </is>
+      </c>
+      <c r="G1363" t="inlineStr"/>
+      <c r="H1363" t="inlineStr"/>
+      <c r="I1363" t="n">
+        <v>0.764069261005575</v>
+      </c>
+      <c r="J1363" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1363" t="inlineStr"/>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="1" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1624.png</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr"/>
+      <c r="D1364" t="inlineStr"/>
+      <c r="E1364" t="inlineStr"/>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>CCc1cccc2cc(OCOC)cc(-c3ncc4c(N(C)CC5CCCN5C(=O)OC(C)(C)C)nc(OC[C@]56CCCN5[C@@H](COC(=O)N5CCN(c7ccc8c(c7)CN(C7CCC(=O)N(C)C7=O)C8=O)CC5)CC6)nc4c3F)c12</t>
+        </is>
+      </c>
+      <c r="G1364" t="inlineStr"/>
+      <c r="H1364" t="inlineStr"/>
+      <c r="I1364" t="n">
+        <v>0.820081161670235</v>
+      </c>
+      <c r="J1364" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1364" t="inlineStr"/>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="1" t="n">
+        <v>1363</v>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1640.png</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr"/>
+      <c r="D1365" t="inlineStr"/>
+      <c r="E1365" t="inlineStr"/>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>COc1cccc(F)c1-c1ncc2[nH]nc(-c3ccc(N4CCN(CC(=O)NCCCCCCCCCCC(=O)N[C@H](C(=O)N5C[C@H](O)C[C@H]5C(=O)NCc5ccc(-c6scnc6C)cc5)C(C)(C)C)CC4)cc3)c2n1</t>
+        </is>
+      </c>
+      <c r="G1365" t="inlineStr"/>
+      <c r="H1365" t="inlineStr"/>
+      <c r="I1365" t="n">
+        <v>0.7717931924489244</v>
+      </c>
+      <c r="J1365" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1365" t="inlineStr"/>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="1" t="n">
+        <v>1364</v>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1648.png</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr"/>
+      <c r="D1366" t="inlineStr"/>
+      <c r="E1366" t="inlineStr"/>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>[H]C1=C2C=NC(C3=C4C(=CC(O)=C3)C=CC(F)=C4C#C)=C(F)C2=NC(OCC(C)N2CCC(CC3CCN(CC4CCN(C5=C(F)C6=C(C=C5)C(=O)N(C5CCC(=O)NC5=O)C6)CC4)CC3)CC2)=N1.[H]N12345([H]N6789%10[H]N%11%12%13%14([H]%15N%16%17%18%19[H]N%15%20%21%22%23C%16%15C%16(C%17)C%17%24C%15(C%16(C%186%11%201)C%17%197%12%212)C%13%22CCC%248%14%233)C9CCC%104)CCCC5</t>
+        </is>
+      </c>
+      <c r="G1366" t="inlineStr"/>
+      <c r="H1366" t="inlineStr"/>
+      <c r="I1366" t="n">
+        <v>2.735919866842903e-05</v>
+      </c>
+      <c r="J1366" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1366" t="inlineStr"/>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="1" t="n">
+        <v>1365</v>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1652.png</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr"/>
+      <c r="D1367" t="inlineStr"/>
+      <c r="E1367" t="inlineStr"/>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>CC1=C(C#N)C=CC(OC2C(C)C(NC(=O)C3=CC=C(N45CCC67C8(C4)C4N9%10C%11COC65C89N%1147[CH]%104CC(OC5=CC=C6C(=O)N(C7CCC(=O)NC7=O)C(=O)C6=C5)C4)C=C3)C2(C)C)=C1</t>
+        </is>
+      </c>
+      <c r="G1367" t="inlineStr"/>
+      <c r="H1367" t="inlineStr"/>
+      <c r="I1367" t="n">
+        <v>0.03118438688031717</v>
+      </c>
+      <c r="J1367" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1367" t="inlineStr"/>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="1" t="n">
+        <v>1366</v>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1656.png</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr"/>
+      <c r="D1368" t="inlineStr"/>
+      <c r="E1368" t="inlineStr"/>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3cc(N4CCC(CNC56CCC(C(=O)N7CCN8c9cc(-c%10ccccc%10O)nnc9NC[C@H]8C7)(CC5)C6)CC4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1368" t="inlineStr"/>
+      <c r="H1368" t="inlineStr"/>
+      <c r="I1368" t="n">
+        <v>0.7586242762274066</v>
+      </c>
+      <c r="J1368" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1368" t="inlineStr"/>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="1" t="n">
+        <v>1367</v>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1664.png</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr"/>
+      <c r="D1369" t="inlineStr"/>
+      <c r="E1369" t="inlineStr"/>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>[H][C@]1(O)CC(=O)O[C@]([H])(CC[C@]2([H])[C@]3([H])C(=C[C@]([H])(C)C[C@]3([H])OC(=O)NCCCCCN3CCC(Nc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)C=C[C@]2([H])C)C1</t>
+        </is>
+      </c>
+      <c r="G1369" t="inlineStr"/>
+      <c r="H1369" t="inlineStr"/>
+      <c r="I1369" t="n">
+        <v>0.8395241724542885</v>
+      </c>
+      <c r="J1369" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1369" t="inlineStr"/>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="1" t="n">
+        <v>1368</v>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1680.png</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr"/>
+      <c r="D1370" t="inlineStr"/>
+      <c r="E1370" t="inlineStr"/>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>[H][C@@]1(CC[C@]2([H])[C@]3([H])C(=C[C@]([H])(C)C[C@]3([H])OC(=O)NCCCCN3CCC(Nc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)C=C[C@]2([H])C)C[C@@]([H])(O[Si](C)(C)C(C)(C)C)CC(=O)O1</t>
+        </is>
+      </c>
+      <c r="G1370" t="inlineStr"/>
+      <c r="H1370" t="inlineStr"/>
+      <c r="I1370" t="n">
+        <v>0.8156031885816529</v>
+      </c>
+      <c r="J1370" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1370" t="inlineStr"/>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="1" t="n">
+        <v>1369</v>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1688.png</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr"/>
+      <c r="D1371" t="inlineStr"/>
+      <c r="E1371" t="inlineStr"/>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>C#CC1=C234C5=CC2(=C2N=CC6=C(N7CC8CCC(C7)N8)N=C(OCCN7CCC(CN8CC9(CCN(C%10=CC=CC%11=C%10CN(C%10CCC(=O)NC%10=O)C%11=O)CC9)C8)CC7)N=C6C2=CC=C(F)C=C5)C=C(O)C2=C3=C(=C=24)C=C1F</t>
+        </is>
+      </c>
+      <c r="G1371" t="inlineStr"/>
+      <c r="H1371" t="inlineStr"/>
+      <c r="I1371" t="n">
+        <v>0.4404423664492361</v>
+      </c>
+      <c r="J1371" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1371" t="inlineStr"/>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="1" t="n">
+        <v>1370</v>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1724.png</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr"/>
+      <c r="D1372" t="inlineStr"/>
+      <c r="E1372" t="inlineStr"/>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>[H]C1=NC(OCC23CCCN2C(CN2CCN(CC4CCN(C5=CC=C6C(=O)N(C7CCC(=O)NC7=O)CC6=C5)CC4)CC2)C3C)=NC2=C(F)C(C=CC(O)=CC34=C56C(=CC(O)=C3)C3(=C57C(C#C)=C([H])C(F)=C367)C=C4)=NC=C12.[H]N1CCCC123N145[H]N2678[H]N329([H])(CCCC2)C6CC2C1C(CC479)C258</t>
+        </is>
+      </c>
+      <c r="G1372" t="inlineStr"/>
+      <c r="H1372" t="inlineStr"/>
+      <c r="I1372" t="n">
+        <v>0.001474339969137522</v>
+      </c>
+      <c r="J1372" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1372" t="inlineStr"/>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="1" t="n">
+        <v>1371</v>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1728.png</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr"/>
+      <c r="D1373" t="inlineStr"/>
+      <c r="E1373" t="inlineStr"/>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>COc1cccc(F)c1-c1ncc2[nH]nc(N3CCN(C(=O)CCOCCOCCOCCOCCNc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)CC3)c2n1</t>
+        </is>
+      </c>
+      <c r="G1373" t="inlineStr"/>
+      <c r="H1373" t="inlineStr"/>
+      <c r="I1373" t="n">
+        <v>0.8155922949611882</v>
+      </c>
+      <c r="J1373" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1373" t="inlineStr"/>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="1" t="n">
+        <v>1372</v>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1736.png</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr"/>
+      <c r="D1374" t="inlineStr"/>
+      <c r="E1374" t="inlineStr"/>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>[H]N(C)CCCCN(C)c1nc(OC[C@]23CCCN2[C@@H](COC(=O)N2CCN(c4ccc5c(c4)CN(C4CCC(=O)N(C)C4=O)C5=O)CC2)CC3)nc2c(F)c(-c3cc(O)cc4cccc(CC)c34)ncc12.[H]N1CCCC1</t>
+        </is>
+      </c>
+      <c r="G1374" t="inlineStr"/>
+      <c r="H1374" t="inlineStr"/>
+      <c r="I1374" t="n">
+        <v>0.5776702721328838</v>
+      </c>
+      <c r="J1374" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1374" t="inlineStr"/>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="1" t="n">
+        <v>1373</v>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1740.png</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr"/>
+      <c r="D1375" t="inlineStr"/>
+      <c r="E1375" t="inlineStr"/>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>CC[N+]C=C1C2C=C13C1=CC=C456C=C1C23=CC=C(C4)C51N2CCN3C4C(=O)NCCCCCOCCCOCC(=O)N5C7C(C)(C)[CH]58(C(C)C)(NC(=O)COCCCOCCCCCNC(=O)CN459CCN1(CC5)(C6)C2C39)C(=O)N1(CC(O)CC1C(=O)NCC1=CC=C(C2=CN=CS2)C=C1)C1(C(=O)NCC2=CC=C(C3=CN=CS3)C=C2)CC(O)CN1C78=O</t>
+        </is>
+      </c>
+      <c r="G1375" t="inlineStr"/>
+      <c r="H1375" t="inlineStr"/>
+      <c r="I1375" t="n">
+        <v>6.21483055785192e-05</v>
+      </c>
+      <c r="J1375" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1375" t="inlineStr"/>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="1" t="n">
+        <v>1374</v>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1744.png</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr"/>
+      <c r="D1376" t="inlineStr"/>
+      <c r="E1376" t="inlineStr"/>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)C(NCCOCCOCCOCCOCCOCC(=O)(=O)NCCC(=O)NC3=CC4=CC(C5=C(C)C(N)=CN=C5)=C(F)C(N)=C4C=N3)C(C)(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1376" t="inlineStr"/>
+      <c r="H1376" t="inlineStr"/>
+      <c r="I1376" t="n">
+        <v>0.216664751852244</v>
+      </c>
+      <c r="J1376" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1376" t="inlineStr"/>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="1" t="n">
+        <v>1375</v>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1768.png</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr"/>
+      <c r="D1377" t="inlineStr"/>
+      <c r="E1377" t="inlineStr"/>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>[H]N1CCCC12C13NC=C4C=NC(C5=C6C(=CC=C5)C=CC(F)=C6C#C)=C(F)C4(=NCOCCNCCCCNCCCC4C56C7=C(C=C)=C5N746)C45=C(N=C(OCCN6CCC(CN7CC8(CCN(C9=CC=C%10C(=O)N(C%11CCC(=O)NC%11=O)CC%10=C9F)CC8)C7)CC6)N=C4C(F)=C(C4=C6C(=CC=C4)C=CC(F)=C6C#C)N=C5)N14CC1CCC3(C4)N12[H]</t>
+        </is>
+      </c>
+      <c r="G1377" t="inlineStr"/>
+      <c r="H1377" t="inlineStr"/>
+      <c r="I1377" t="n">
+        <v>0.005784526505558763</v>
+      </c>
+      <c r="J1377" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1377" t="inlineStr"/>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="1" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1776.png</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr"/>
+      <c r="D1378" t="inlineStr"/>
+      <c r="E1378" t="inlineStr"/>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>CCc1cccc2cc(O)cc(-c3ncc4c(N5CC6CCC(C5)N6)nc(OC[C@@H]5C[C@@H](OC6CCN(CC7CCN(c8cccc9c8CN(C8CCC(=O)NC8=O)C9=O)CC7)CC6)CN5C)nc4c3F)c12</t>
+        </is>
+      </c>
+      <c r="G1378" t="inlineStr"/>
+      <c r="H1378" t="inlineStr"/>
+      <c r="I1378" t="n">
+        <v>0.8430271553590936</v>
+      </c>
+      <c r="J1378" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1378" t="inlineStr"/>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="1" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1800.png</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr"/>
+      <c r="D1379" t="inlineStr"/>
+      <c r="E1379" t="inlineStr"/>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>[H]N1([H]NCC2CN2(C)C2=C3C=NC(C4=C5C(=CC(O)=C4)C=CC(F)=C5C#C)=C(F)C3=NC(OCCN3CCC(CN4CCC(CN5CCN(C6=C(F)C7=C(C=C6)C(=O)N(C6CCC(=O)NC6=O)C7)CC5)CC4)CC3)=N2)CCCC1</t>
+        </is>
+      </c>
+      <c r="G1379" t="inlineStr"/>
+      <c r="H1379" t="inlineStr"/>
+      <c r="I1379" t="n">
+        <v>0.1687828080761902</v>
+      </c>
+      <c r="J1379" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1379" t="inlineStr"/>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="1" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1808.png</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr"/>
+      <c r="D1380" t="inlineStr"/>
+      <c r="E1380" t="inlineStr"/>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>[H][C@]1(O)CC(=O)O[C@]([H])(CC[C@]2([H])[C@]3([H])C(=C[C@]([H])(C)C[C@]3([H])OC(=O)NCCCCn3cc(CCCC(=O)N[C@H](C(=O)N4C[C@H](O)C[C@H]4C(=O)NCc4ccc(-c5scnc5C)cc4)C(C)(C)C)nn3)C=C[C@]2([H])C)C1</t>
+        </is>
+      </c>
+      <c r="G1380" t="inlineStr"/>
+      <c r="H1380" t="inlineStr"/>
+      <c r="I1380" t="n">
+        <v>0.8210787155713253</v>
+      </c>
+      <c r="J1380" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1380" t="inlineStr"/>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="1" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1820.png</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr"/>
+      <c r="D1381" t="inlineStr"/>
+      <c r="E1381" t="inlineStr"/>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>[H]N1CCCC1CN(C)c1nc(NCCN2CCC(CC3CCN(CC4CN(c5ccc6c(c5)CN(C5CCC(=O)NC5=O)C6=O)C4)CC3)CC2)nc2c(F)c(-c3cc(O)cc4ccc(F)c(C#C)c34)ncc12</t>
+        </is>
+      </c>
+      <c r="G1381" t="inlineStr"/>
+      <c r="H1381" t="inlineStr"/>
+      <c r="I1381" t="n">
+        <v>0.8232604872855277</v>
+      </c>
+      <c r="J1381" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1381" t="inlineStr"/>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="1" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T124124_3/rb_1840.png</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr"/>
+      <c r="D1382" t="inlineStr"/>
+      <c r="E1382" t="inlineStr"/>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>COC1=C(C=NC=CNN=CC23=CC=C4(N5CCN(C(=O)CCOCCOCCOCCOCCC(=O)NC(C(=O)N6CC(O)CC6C(=O)NCC6=CC=C(C7=C(C)N=CS7)C=C6)C(C)(C)C)CC5)C5=C2=C4=C=53)C(F)=CC=C1</t>
+        </is>
+      </c>
+      <c r="G1382" t="inlineStr"/>
+      <c r="H1382" t="inlineStr"/>
+      <c r="I1382" t="n">
+        <v>0.8373267440868749</v>
+      </c>
+      <c r="J1382" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1382" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1382"/>
+  <dimension ref="A1:K1532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40529,6 +40529,4356 @@
       </c>
       <c r="K1382" t="inlineStr"/>
     </row>
+    <row r="1383">
+      <c r="A1383" s="1" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1851.png</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr"/>
+      <c r="D1383" t="inlineStr"/>
+      <c r="E1383" t="inlineStr"/>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>NCCCC[CH]12NC(=O)C(CCCCNC(=O)C3=CC=CN=C3)NC(=O)C(CC3=CC=C(O)C=C3)NC(=O)[CH]3(NC(=O)C(N)CC4=CC=C(Cl)C=C4)C4[CH]C3SSC[CH]356NC7(=O)[CH]89C(O)[CH]7%10(N7C1(=O=C72=O)N8%10)C9(=O)NC(C3SC4)C5(=O)N1C2C(C3=CC=C(O)C=C3)[CH]1(CC1=CC=C(O)C=C1)(C(N)=O)(NC6=O)C2(N)=O</t>
+        </is>
+      </c>
+      <c r="G1383" t="inlineStr"/>
+      <c r="H1383" t="inlineStr"/>
+      <c r="I1383" t="n">
+        <v>0.00875721151560423</v>
+      </c>
+      <c r="J1383" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1383" t="inlineStr"/>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="1" t="n">
+        <v>1382</v>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1855.png</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr"/>
+      <c r="D1384" t="inlineStr"/>
+      <c r="E1384" t="inlineStr"/>
+      <c r="F1384" t="inlineStr">
+        <is>
+          <t>CNCCCC[C@@H]1NC(=O)[C@H](CO)NC(=O)C[C@@H](C(=O)N2CCC[C@H]2C(N)=O)NC(=O)[C@@H](NC(=O)[C@@H]2CCCN2C(=O)CO)CCCCNC(=O)[C@H](CS)NC(=O)[C@H](Cc2c[nH]c3c2C(=O)C=CC3)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1384" t="inlineStr"/>
+      <c r="H1384" t="inlineStr"/>
+      <c r="I1384" t="n">
+        <v>0.7715770937083909</v>
+      </c>
+      <c r="J1384" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1384" t="inlineStr"/>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="1" t="n">
+        <v>1383</v>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1863.png</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr"/>
+      <c r="D1385" t="inlineStr"/>
+      <c r="E1385" t="inlineStr"/>
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>CC=CC=C(N)CC1=O=C(CCC(=O)NC2C3(NC=CC=CC=CCCCCCCC(C4CO4CCOCCNCCOCCOCCNCCC(=O)(=O)O)N4CC4CCCC4C5OC45[CH]C(C)(C)C)[CH]([CH]CNCCCCC=CC=CCCCCCN45C6C4N6C5C45C6C4N65CC)(CC(=O)NCCCC(=O)NC(=O)CO)[CH]23CCCCNC(C)=O)N1.O</t>
+        </is>
+      </c>
+      <c r="G1385" t="inlineStr"/>
+      <c r="H1385" t="inlineStr"/>
+      <c r="I1385" t="n">
+        <v>4.332802513136343e-10</v>
+      </c>
+      <c r="J1385" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1385" t="inlineStr"/>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="1" t="n">
+        <v>1384</v>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1871.png</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr"/>
+      <c r="D1386" t="inlineStr"/>
+      <c r="E1386" t="inlineStr"/>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>[H]C1CCCN1C(=O)[CH]NC(=O)C(C)N(C)C(=O)[CH]1(CC2=CC=C(O)C=C2)NC(=O)CSC[CH]2(C(=O)NCC(N)=O)C[CH]CSCC(=O)NC(CC3=CC=C(O)C=C3)C1(=O)[CH]CC[CH]C(=O)NC(CC1=CN(CC(=O)O)C3=C1C=CC=C3)C(=O)N(C)C(CCCC)C(=O)N(C)C(CCCC)C(=O)NC(CCC)C(=O)N2</t>
+        </is>
+      </c>
+      <c r="G1386" t="inlineStr"/>
+      <c r="H1386" t="inlineStr"/>
+      <c r="I1386" t="n">
+        <v>0.06172865318898627</v>
+      </c>
+      <c r="J1386" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1386" t="inlineStr"/>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="1" t="n">
+        <v>1385</v>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1875.png</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr"/>
+      <c r="D1387" t="inlineStr"/>
+      <c r="E1387" t="inlineStr"/>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>O=C1CCC(n2c(=O)c3ccc4c(c3c2=O)n4CCCN2CCN(c3cccc(-c4cnc5ccc(N6CCC[C@@H]6c6cccc(F)c6)nn45)n3)CC2)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1387" t="inlineStr"/>
+      <c r="H1387" t="inlineStr"/>
+      <c r="I1387" t="n">
+        <v>0.5519953781989043</v>
+      </c>
+      <c r="J1387" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1387" t="inlineStr"/>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="1" t="n">
+        <v>1386</v>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1879.png</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr"/>
+      <c r="D1388" t="inlineStr"/>
+      <c r="E1388" t="inlineStr"/>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>[H]C1C(=O)NC([H])(CC2=CC=CC=C2)C(=O)N(C)C([H])(CC(C)C)C(=O)N2(C)CC2C(=O)N(C)C(C(C)C)C(=O)NC([H])(C)C(=O)NC(C(=O)N2(C)C(C3=CC=CC=C3)C2([H])C(=O)N(C)C([H])(CC2=CC=CC=C2)C(=O)NC([H])(C)C)CC(=O)N(C)C(C)C(=O)N(C)CC(=O)NC([H])(C(C)O)C(=O)N1C</t>
+        </is>
+      </c>
+      <c r="G1388" t="inlineStr"/>
+      <c r="H1388" t="inlineStr"/>
+      <c r="I1388" t="n">
+        <v>0.1361937797721387</v>
+      </c>
+      <c r="J1388" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1388" t="inlineStr"/>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="1" t="n">
+        <v>1387</v>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1883.png</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr"/>
+      <c r="D1389" t="inlineStr"/>
+      <c r="E1389" t="inlineStr"/>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>CCCCCCCCCCC[CH]CCCCC(=O)NCCCC.CCCCCCCCCCC[CH]CCCNC(=O)CCCOCCOCC(=O)COCC1CO1C(=O)C1NC(=O)C(C(C)C)N[CH](CCCNC(=O)CCNC(C)=O)(C2(=O)CC2CC2NC2C)C(=O)NC(=O)NC(C)(C)NC(C)(C)NC(C)(C)NC(=O)C2=O=C1(C)N2.O=C(CO)COCCCOCC1CC1</t>
+        </is>
+      </c>
+      <c r="G1389" t="inlineStr"/>
+      <c r="H1389" t="inlineStr"/>
+      <c r="I1389" t="n">
+        <v>6.092616234790074e-06</v>
+      </c>
+      <c r="J1389" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1389" t="inlineStr"/>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="1" t="n">
+        <v>1388</v>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1891.png</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr"/>
+      <c r="D1390" t="inlineStr"/>
+      <c r="E1390" t="inlineStr"/>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>CCC(C)C(NC(=O)C(CC(C)C)N(C)C(=O)CC(C(=O)N1CCOCC1)N(C)C(=O)[CH]1(C2CCCC2)N234CN15(C2)C31=O=C45=O=1)C(=O)N(C)CC(=O)N(C)C1CCCCN(C(Cc2ccc(F)cc2)C(=O)N(C)CC(=O)NC(CCc2ccc(C(F)(F)F)c(Cl)c2)C(=O)N2CCCC2C(=O)NC2CCCC2)C1=O</t>
+        </is>
+      </c>
+      <c r="G1390" t="inlineStr"/>
+      <c r="H1390" t="inlineStr"/>
+      <c r="I1390" t="n">
+        <v>0.6334831466004236</v>
+      </c>
+      <c r="J1390" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1390" t="inlineStr"/>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="1" t="n">
+        <v>1389</v>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1895.png</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr"/>
+      <c r="D1391" t="inlineStr"/>
+      <c r="E1391" t="inlineStr"/>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>NCCCCC1NC(=O)C(CC2=CC=C(CNC(N)=O)C=C2)NC(=O)C(CC2=CC=C(O)C=C2)NC(=O)C(NC(=O)C(N)CC2=CC=C(Cl)C=C2)CSSC2[CH]345C67SC38[CH]639(O)[CH]6(O)[CH]3%10%11O3C1(=O)N[CH]3691C%10(=O)N43C%111(=O)N[CH]27831C(=O)N[CH]234(C(N)=O)CC6(=CC=C(O)C=C6)C6=CC(O)=CC=C6C2C(N3C51=O)C4(N)=O</t>
+        </is>
+      </c>
+      <c r="G1391" t="inlineStr"/>
+      <c r="H1391" t="inlineStr"/>
+      <c r="I1391" t="n">
+        <v>0.0003632345323552992</v>
+      </c>
+      <c r="J1391" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1391" t="inlineStr"/>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="1" t="n">
+        <v>1390</v>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1899.png</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr"/>
+      <c r="D1392" t="inlineStr"/>
+      <c r="E1392" t="inlineStr"/>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>CCO[C@@H]1C[C@H]2C(=O)NC3(CCC3)C(=O)N(C)[C@@H](C(CC)CC)C(=O)N(C)[C@H](C(=O)N(C)C)CC(=O)N(C)[C@@H](COC)C(=O)N[C@@H]([C@@H](C)CC)C(=O)N(C)CC(=O)N(C)[C@H]3C/C=C\CCN(C3=O)[C@@H](Cc3ccc(C(F)(F)F)cc3)C(=O)N(C)CC(=O)N[C@@H](CCc3ccc(Cl)c(Cl)c3)C(=O)N2C1</t>
+        </is>
+      </c>
+      <c r="G1392" t="inlineStr"/>
+      <c r="H1392" t="inlineStr"/>
+      <c r="I1392" t="n">
+        <v>0.8287026059600443</v>
+      </c>
+      <c r="J1392" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1392" t="inlineStr"/>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="1" t="n">
+        <v>1391</v>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1903.png</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr"/>
+      <c r="D1393" t="inlineStr"/>
+      <c r="E1393" t="inlineStr"/>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>COC(C(C)C(=O)NC(C)C(O)C1=CC=CC=C1)C1CCCN1C1(=O)C2C34(=O)C156CC[CH]17C[CH]89(C)CCC%10C5%11(=O)[CH]1385%12N13C(=O)N5(C1(=O)[CH]1(NC(=O)C(C(C)C)N(C)C(=O)OCC5=CC=C(NC(=O)C(C)NC(=O)C(NC(=O)CCCCCNC(=O)C=CC(=O)O)C(C)C)C=C5)C58%13CC1(C5)(C8)C%13)[CH]73%1149[CH]%1026%12OC</t>
+        </is>
+      </c>
+      <c r="G1393" t="inlineStr"/>
+      <c r="H1393" t="inlineStr"/>
+      <c r="I1393" t="n">
+        <v>0.01333609411541415</v>
+      </c>
+      <c r="J1393" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1393" t="inlineStr"/>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="1" t="n">
+        <v>1392</v>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1911.png</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr"/>
+      <c r="D1394" t="inlineStr"/>
+      <c r="E1394" t="inlineStr"/>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>CCNCCCNC123456=O789=C%10%11%12%13=N1%14%15%16%17%18%19=C%101%20%21%22%23=O%10%24%25%26%27=C%28%29%30%31(NC%32C%33NC%34%35(=O)=O=C%34%36%37=O=C(=O)(O)(O%36)C%37(=O)N%35C%33%32=O)=C=%10%111%14%32%33=C21%10%11%14%34%35%36=O2=C=7%15%37%38%39%40C7%15C%41%42C%43C%41(C%427C%15%37C=2=8=%20%38%167%15O=C=%12=%24=%21=%32%1728%16%20(=C=%25=1%12%17%21N1%24C%12%25%32%37%38=O%12%41=C%25%42C=%12%25(C%12C%44%45C(N%44C(C)=O)C%12%45%25)C=%41=9%421%32%12N%37321C=%28=%26=%10=8%24%172C%1138C%149%10N%3947%34C=5931%29%21%22%18%35%16[CH]%108%38%40%126%23%152%19%36%20)N%13%30%27%33C12[CH]34O(CC(N)=O)C(CCN5C6C5C65CC56C5(=O)C78C9%10C%11%12C%13%14C(C%15C%16C(C)C%16%15)C%13C%14%11C%1297C6%1085)O[CH]13%31[CH]24O1C2C3C(C4C5C46C54C65C67C89C(N8CCCC(N)=O)C96C457)C321)C%43(N)=O.O</t>
+        </is>
+      </c>
+      <c r="G1394" t="inlineStr"/>
+      <c r="H1394" t="inlineStr"/>
+      <c r="I1394" t="n">
+        <v>1.41524447389801e-44</v>
+      </c>
+      <c r="J1394" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1394" t="inlineStr"/>
+    </row>
+    <row r="1395">
+      <c r="A1395" s="1" t="n">
+        <v>1393</v>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1915.png</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr"/>
+      <c r="D1395" t="inlineStr"/>
+      <c r="E1395" t="inlineStr"/>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>O.[H][C](NC(=O)[CH]CCCCN/C=C/CC[C@H](NC(=O)[C@H](CC(=O)O)NC(C)(C)C)C(=O)N[C@@H](C)CN[C@@H](Cc1c[nH]c2ccccc12)C(=O)N[C@@H](Cc1c[nH]cn1)C(=O)N[C@@H](CC(C)C)C(=O)NCC(=O)N[C@@H](CCC(=O)O)C(=O)N[C@@H](CC(C)C)C(=O)N[C@H](C(=O)N[CH]Cc1c[nH]cc1C=C)C(C)C)C(N)=O |^1:2,6,94|</t>
+        </is>
+      </c>
+      <c r="G1395" t="inlineStr"/>
+      <c r="H1395" t="inlineStr"/>
+      <c r="I1395" t="n">
+        <v>0.239242448631134</v>
+      </c>
+      <c r="J1395" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1395" t="inlineStr"/>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="1" t="n">
+        <v>1394</v>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1931.png</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr"/>
+      <c r="D1396" t="inlineStr"/>
+      <c r="E1396" t="inlineStr"/>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>CCOC1CN2C(=O)C(CCc3ccc(C(F)(F)F)c(OC)c3)NC(=O)CN(C)C(=O)C(CC3CCC(F)(F)CC3)N3CCC=CCC(C3=O)N(C)C(=O)CN(C)C(=O)C(C(C)CC)NC(=O)C(C(C)C)N(C)C(=O)CC(C(=O)N(C)C)N(C)C(=O)C(C(CC)CC)N(C)C(=O)C3(CC(C)(C)C3)NC3(=O)=O=C[CH]23C1</t>
+        </is>
+      </c>
+      <c r="G1396" t="inlineStr"/>
+      <c r="H1396" t="inlineStr"/>
+      <c r="I1396" t="n">
+        <v>0.6222166123693196</v>
+      </c>
+      <c r="J1396" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1396" t="inlineStr"/>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="1" t="n">
+        <v>1395</v>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1935.png</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr"/>
+      <c r="D1397" t="inlineStr"/>
+      <c r="E1397" t="inlineStr"/>
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>CCC(CO)C(=O)N[CH]1(CO)C(=O)NC2CC3(=CC=C(O)C=C3)C(C3=CC=C(O)C=C3)C(NC(=O)C(CO)C1C(=O)NC(=O)[CH]CC(=O)OCC(=O)N[CH]C(=O)C1CC34(=CC=CC=C3)CC3C(=O34)N3C(=O)C(C)C3(=O)N1)C(=O)C[CH]C(=O)N1[CH]34C(CC(C)=O)[CH]15(CCC(=O)O)(NC2=O)C312=O=C453(=O)N14CC1C4N123</t>
+        </is>
+      </c>
+      <c r="G1397" t="inlineStr"/>
+      <c r="H1397" t="inlineStr"/>
+      <c r="I1397" t="n">
+        <v>2.211293063866447e-07</v>
+      </c>
+      <c r="J1397" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1397" t="inlineStr"/>
+    </row>
+    <row r="1398">
+      <c r="A1398" s="1" t="n">
+        <v>1396</v>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1939.png</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr"/>
+      <c r="D1398" t="inlineStr"/>
+      <c r="E1398" t="inlineStr"/>
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)C3=C(C2=O)C2=C(C=C3)N23CC(C(=O)N2CCN(C4=NC(C5=CN=C6C=CC(N7CCCC7C7=CC=CC(F)=C7)=NN56)=CC=C4)CC2)C3)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1398" t="inlineStr"/>
+      <c r="H1398" t="inlineStr"/>
+      <c r="I1398" t="n">
+        <v>0.5175472137355112</v>
+      </c>
+      <c r="J1398" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1398" t="inlineStr"/>
+    </row>
+    <row r="1399">
+      <c r="A1399" s="1" t="n">
+        <v>1397</v>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1943.png</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr"/>
+      <c r="D1399" t="inlineStr"/>
+      <c r="E1399" t="inlineStr"/>
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)C(NC(=O)CCCCCCNC(=O)CN2CCN(c3cccc(-c4cnc5ccc(N6CCC[C@@H]6c6cccc(F)c6)nn45)n3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1399" t="inlineStr"/>
+      <c r="H1399" t="inlineStr"/>
+      <c r="I1399" t="n">
+        <v>0.8237808377902702</v>
+      </c>
+      <c r="J1399" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1399" t="inlineStr"/>
+    </row>
+    <row r="1400">
+      <c r="A1400" s="1" t="n">
+        <v>1398</v>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1947.png</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr"/>
+      <c r="D1400" t="inlineStr"/>
+      <c r="E1400" t="inlineStr"/>
+      <c r="F1400" t="inlineStr">
+        <is>
+          <t>[H][C@]1(C(C)C)NC(=O)C[C@@]([H])(C(=O)N2CCCCC2)NC(=O)[C@]([H])([C@@H](C)O)NC(=O)[C@]([H])(C)N(C)C(=O)CN(C)C(=O)[C@]([H])(CC(C)C)N(C)C(=O)[C@]([H])(Cc2ccccc2)NC(=O)[C@]([H])(Cc2ccccc2)N(C)C(=O)[C@]2([H])CCC(=O)NCCC(C)C[C@@]([H])(C(=O)N2)N(C)C(=O)C(C)N(C)C1=O</t>
+        </is>
+      </c>
+      <c r="G1400" t="inlineStr"/>
+      <c r="H1400" t="inlineStr"/>
+      <c r="I1400" t="n">
+        <v>0.7570875902025254</v>
+      </c>
+      <c r="J1400" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1400" t="inlineStr"/>
+    </row>
+    <row r="1401">
+      <c r="A1401" s="1" t="n">
+        <v>1399</v>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1951.png</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr"/>
+      <c r="D1401" t="inlineStr"/>
+      <c r="E1401" t="inlineStr"/>
+      <c r="F1401" t="inlineStr">
+        <is>
+          <t>[H]C(C)NC(=O)C([H])(CC(C)C)N(C)C(=O)C(C)N(C)C(=O)C([H])(NC(=O)C([H])(CC1=CC=CC=C1)NC(=O)C(C)(C)N(C)C(=O)C([H])(C(C)C)N(C)C(=O)C([H])(C)N(C)C(=O)CC([H])(NC(C)=O)C(=O)N(C)C([H])(CC1=CC=CC=C1)C(=O)NC1([H])C(=O)N2345CC6C7C8C2N2(C3CC68C7C24)C15=O)C(C)O</t>
+        </is>
+      </c>
+      <c r="G1401" t="inlineStr"/>
+      <c r="H1401" t="inlineStr"/>
+      <c r="I1401" t="n">
+        <v>0.06655560470841387</v>
+      </c>
+      <c r="J1401" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1401" t="inlineStr"/>
+    </row>
+    <row r="1402">
+      <c r="A1402" s="1" t="n">
+        <v>1400</v>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1955.png</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr"/>
+      <c r="D1402" t="inlineStr"/>
+      <c r="E1402" t="inlineStr"/>
+      <c r="F1402" t="inlineStr">
+        <is>
+          <t>CCCCCC[C@H]1C(=O)N[C@@H]([C@@H](C)CC)C(=O)N(C)CC(=O)N(C)[C@H]2C/C=C\CCN(C2=O)[C@@H](Cc2ccc(C(F)(F)F)cc2)C(=O)N(C)CC(=O)N[C@@H](CCc2cc(F)c(C(F)(F)F)c(F)c2)C(=O)N2C[C@H](OCC)C[C@H]2C(=O)NC2(CCC2)C(=O)N(C)[C@@H](C(CC)CC)C(=O)N(C)[C@H](C(=O)N(C)C)CC(=O)N1C</t>
+        </is>
+      </c>
+      <c r="G1402" t="inlineStr"/>
+      <c r="H1402" t="inlineStr"/>
+      <c r="I1402" t="n">
+        <v>0.8357375045357066</v>
+      </c>
+      <c r="J1402" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1402" t="inlineStr"/>
+    </row>
+    <row r="1403">
+      <c r="A1403" s="1" t="n">
+        <v>1401</v>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1959.png</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr"/>
+      <c r="D1403" t="inlineStr"/>
+      <c r="E1403" t="inlineStr"/>
+      <c r="F1403" t="inlineStr">
+        <is>
+          <t>CC12=C3456C7=C8(C9=CC=C(CN%10CCOCC%10)C=C9)C=C73C14(=C85)N61(C3CCN(C(=O)CCOCCOCCOCCOCCOCCOCCOCCC(=O)NCCOC4=C5C(=O)N(C6CCC(=O)NC6=O)C(=O)C5=CC=C4)CC3)CCCC3(=C(CNC(=O)C2)C(=O)OC=C3)CCC1</t>
+        </is>
+      </c>
+      <c r="G1403" t="inlineStr"/>
+      <c r="H1403" t="inlineStr"/>
+      <c r="I1403" t="n">
+        <v>0.138197954883169</v>
+      </c>
+      <c r="J1403" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1403" t="inlineStr"/>
+    </row>
+    <row r="1404">
+      <c r="A1404" s="1" t="n">
+        <v>1402</v>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1967.png</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr"/>
+      <c r="D1404" t="inlineStr"/>
+      <c r="E1404" t="inlineStr"/>
+      <c r="F1404" t="inlineStr">
+        <is>
+          <t>[H]C1NC(=O)C([H])(C)N(C)C(=O)C(CC2=CC=CC=C2)NC23=O=C2(=O=3)N(C)C(=O)C([H])(C)NC(=O)C2(C)(C)CN2C(=O)C(CC(C)C)N(C)C(=O)C2(C)(C)CN2C(=O)CC([H])(C(=O)N(C)C([H])(CC2=CC=CC=C2)C(=O)NC2([H])C34=O=C25(=O=3)N236C7C8C9%10C%11C2N7452C3C9C8%11C%10C62)NC(=O)C2(C)CN2C(=O)C([H])N(C)C1=O</t>
+        </is>
+      </c>
+      <c r="G1404" t="inlineStr"/>
+      <c r="H1404" t="inlineStr"/>
+      <c r="I1404" t="n">
+        <v>0.009731891416421787</v>
+      </c>
+      <c r="J1404" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1404" t="inlineStr"/>
+    </row>
+    <row r="1405">
+      <c r="A1405" s="1" t="n">
+        <v>1403</v>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1975.png</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr"/>
+      <c r="D1405" t="inlineStr"/>
+      <c r="E1405" t="inlineStr"/>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>CCN(c1cc(-c2ccc(CN3CCN(CC(=O)NCC4C5CCN(CCCCNc6cccc7c6C(=O)N(C6CCC(=O)NC6=O)C7=O)CC54)CC3)cc2)cc(C(=O)NCc2c(C)cc(C)[nH]c2=O)c1C)C1CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1405" t="inlineStr"/>
+      <c r="H1405" t="inlineStr"/>
+      <c r="I1405" t="n">
+        <v>0.4737216899622648</v>
+      </c>
+      <c r="J1405" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1405" t="inlineStr"/>
+    </row>
+    <row r="1406">
+      <c r="A1406" s="1" t="n">
+        <v>1404</v>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1979.png</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr"/>
+      <c r="D1406" t="inlineStr"/>
+      <c r="E1406" t="inlineStr"/>
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1406" t="inlineStr"/>
+      <c r="H1406" t="inlineStr"/>
+      <c r="I1406" t="n">
+        <v>0.5715623974237456</v>
+      </c>
+      <c r="J1406" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1406" t="inlineStr"/>
+    </row>
+    <row r="1407">
+      <c r="A1407" s="1" t="n">
+        <v>1405</v>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_1995.png</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr"/>
+      <c r="D1407" t="inlineStr"/>
+      <c r="E1407" t="inlineStr"/>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCOCCOCCOCCC(=O)N2CCN(Cc3ccc(NC(=O)c4coc(N5CCOCC5)n4)c(N4CC=C(C(N)=O)CC4)c3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1407" t="inlineStr"/>
+      <c r="H1407" t="inlineStr"/>
+      <c r="I1407" t="n">
+        <v>0.8417886880957504</v>
+      </c>
+      <c r="J1407" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1407" t="inlineStr"/>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="1" t="n">
+        <v>1406</v>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_2011.png</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr"/>
+      <c r="D1408" t="inlineStr"/>
+      <c r="E1408" t="inlineStr"/>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>CCCOC[CH]12(C(=O)NC(C(=O)NC3CC3)C(C)CC)CC(C1(=O)OCCC)N2(C)C(=O)CC(C(=O)N(C)C)N(C)C(=O)C1N(C)C(=O)C2(N(C)C(=O)C3CC(C)CN3C(=O)C(CCc3ccc(C(F)(F)F)c(OC)c3)NC(=O)CNC(=O)C(Cc3ccc(C)cc3)NCCC=CC[CH]N(C)C(C)=O)CCC2C12CCCC2</t>
+        </is>
+      </c>
+      <c r="G1408" t="inlineStr"/>
+      <c r="H1408" t="inlineStr"/>
+      <c r="I1408" t="n">
+        <v>0.2044967184070558</v>
+      </c>
+      <c r="J1408" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1408" t="inlineStr"/>
+    </row>
+    <row r="1409">
+      <c r="A1409" s="1" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_2031.png</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr"/>
+      <c r="D1409" t="inlineStr"/>
+      <c r="E1409" t="inlineStr"/>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>C=C/C(=C\C=C(\N)NC(=O)c1ccc(N2CCN(CC(=O)NCCCCCCCCC(=O)N[C@H](C(=O)N3C[C@H](O)C[C@H]3C(=O)NCc3ccc(-c4scnc4C)cc3)C(C)(C)C)CC2)cc1NC1CCOCC1)Cc1cc(F)cc(F)c1</t>
+        </is>
+      </c>
+      <c r="G1409" t="inlineStr"/>
+      <c r="H1409" t="inlineStr"/>
+      <c r="I1409" t="n">
+        <v>0.4315807068620567</v>
+      </c>
+      <c r="J1409" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1409" t="inlineStr"/>
+    </row>
+    <row r="1410">
+      <c r="A1410" s="1" t="n">
+        <v>1408</v>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_2039.png</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr"/>
+      <c r="D1410" t="inlineStr"/>
+      <c r="E1410" t="inlineStr"/>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>NC(=O)CC[C@H](NC(=O)[C@@H]1CC[C@@H]2CCN(C(=O)CCCCCC#Cc3cccc4c3CN(C3CCC(=O)NC3=O)C4=O)C[C@H](NC(=O)c3cc4cc(C(F)(F)P(=O)(O)O)ccc4s3)C(=O)N21)c1ncc(Cc2ccccc2)s1</t>
+        </is>
+      </c>
+      <c r="G1410" t="inlineStr"/>
+      <c r="H1410" t="inlineStr"/>
+      <c r="I1410" t="n">
+        <v>0.6927561746627984</v>
+      </c>
+      <c r="J1410" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1410" t="inlineStr"/>
+    </row>
+    <row r="1411">
+      <c r="A1411" s="1" t="n">
+        <v>1409</v>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_2043.png</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr"/>
+      <c r="D1411" t="inlineStr"/>
+      <c r="E1411" t="inlineStr"/>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>[H][C@]1(C)NC(=O)[C@]([H])(CC(C)C)NC(=O)[C@]([H])(CC(C)C)N(C)C(=O)[C@]([H])(C(C)C)NC(=O)[C@]([H])(CC(C)C)N(C)C(=O)N(C)C(=O)[C@]([H])(C(C)C)NC(=O)[C@]([H])(CO)N(C)C(=O)[C@]([H])(CC(C)C)N(C)C(=O)[C@]([H])(C)NC(=O)[C@]([H])(CC(C)C)N(C)C1=O</t>
+        </is>
+      </c>
+      <c r="G1411" t="inlineStr"/>
+      <c r="H1411" t="inlineStr"/>
+      <c r="I1411" t="n">
+        <v>0.8235943948067018</v>
+      </c>
+      <c r="J1411" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1411" t="inlineStr"/>
+    </row>
+    <row r="1412">
+      <c r="A1412" s="1" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_2047.png</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr"/>
+      <c r="D1412" t="inlineStr"/>
+      <c r="E1412" t="inlineStr"/>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>CC.CC</t>
+        </is>
+      </c>
+      <c r="G1412" t="inlineStr"/>
+      <c r="H1412" t="inlineStr"/>
+      <c r="I1412" t="n">
+        <v>0.416951156240351</v>
+      </c>
+      <c r="J1412" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1412" t="inlineStr"/>
+    </row>
+    <row r="1413">
+      <c r="A1413" s="1" t="n">
+        <v>1411</v>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_2051.png</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr"/>
+      <c r="D1413" t="inlineStr"/>
+      <c r="E1413" t="inlineStr"/>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>CC(=O)NCCCC[CH]12NC134=O=C2(=O=3)N4[CH]C(=O)N[CH]C(=O)OC(CC1=CC2=C34C5=CC=CC23=C54C=1)C(=O)NCC(=O)NC(CCC(=O)O)C(=O)NC(CC(N)=O)C(N)=O.CCCCCC(=O)NC(CCCNC(=N)N)C1=O[CH]2(CN2C(CC(N)=O)C(=O)NC(C(=O)[CH]CC2=CNC3=C2C=CC=C3C)C(C)O)N1.O</t>
+        </is>
+      </c>
+      <c r="G1413" t="inlineStr"/>
+      <c r="H1413" t="inlineStr"/>
+      <c r="I1413" t="n">
+        <v>0.005960230552616611</v>
+      </c>
+      <c r="J1413" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1413" t="inlineStr"/>
+    </row>
+    <row r="1414">
+      <c r="A1414" s="1" t="n">
+        <v>1412</v>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_2055.png</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr"/>
+      <c r="D1414" t="inlineStr"/>
+      <c r="E1414" t="inlineStr"/>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>CCC.CCCN(C(=O)C1[CH]23C[CH]1(O2C)[CH]3(NCC(CNC(=O)CCC1=CC=C(NC(=O)C(CCCNC(N)=O)NC(=O)C(NC(=O)CCCCCN2C(=O)CC(OC(C)C)C2=O)C(C)C)C=C1)C(C)C)C(C)CC)C(C)C(OC)C(C)C(=O)NC(C)C(O)C1=CC=CC=C1</t>
+        </is>
+      </c>
+      <c r="G1414" t="inlineStr"/>
+      <c r="H1414" t="inlineStr"/>
+      <c r="I1414" t="n">
+        <v>0.4925018308785664</v>
+      </c>
+      <c r="J1414" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1414" t="inlineStr"/>
+    </row>
+    <row r="1415">
+      <c r="A1415" s="1" t="n">
+        <v>1413</v>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_2067.png</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr"/>
+      <c r="D1415" t="inlineStr"/>
+      <c r="E1415" t="inlineStr"/>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>COC1=CC=C(COC=CC=CCN2C3=NC=C45C6=C7=NN(CC(=O)NCCOCCOCCOCCOCCC(=O)NC(CN8CC(O)CC8C(=O)NCC8=CC=C(C9=C(C)N=CS9)C=C8)C(C)(C)C)C=C74C=6=C35=C2N)C=C1</t>
+        </is>
+      </c>
+      <c r="G1415" t="inlineStr"/>
+      <c r="H1415" t="inlineStr"/>
+      <c r="I1415" t="n">
+        <v>0.1910892092470251</v>
+      </c>
+      <c r="J1415" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1415" t="inlineStr"/>
+    </row>
+    <row r="1416">
+      <c r="A1416" s="1" t="n">
+        <v>1414</v>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_2075.png</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr"/>
+      <c r="D1416" t="inlineStr"/>
+      <c r="E1416" t="inlineStr"/>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>CC(O)O.CCC(O)O.O.O.[1*]C123OC4[H]C4C([H])([H])(C)OS4=O=C(CC5678N9C5%10C(CCCC(=O)(OC)=O=C(OCC)CCOC5%11C%12OC6%13N4(CCCCOCCCC)(COCCOCCCC4=O=C4OC)C5%1374(CC4NC([H])(O)(O)C(O)(O)O)C%12%11)C9%108)OC4([H])C56([H])[H]C45(O)(OCC45([1*])C789%10([1*])OC147%11%12%13OC258%11([1*])(O3)([1*]9%12)O%10%13)O6.[H]C(O)(O)C(O)(O)O |$;;;;;;;;;;;R1;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;R1;;R1;;;;;R1;;R1;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1416" t="inlineStr"/>
+      <c r="H1416" t="inlineStr"/>
+      <c r="I1416" t="n">
+        <v>5.830552921468916e-12</v>
+      </c>
+      <c r="J1416" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1416" t="inlineStr"/>
+    </row>
+    <row r="1417">
+      <c r="A1417" s="1" t="n">
+        <v>1415</v>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_2079.png</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr"/>
+      <c r="D1417" t="inlineStr"/>
+      <c r="E1417" t="inlineStr"/>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>CC[CH]1(C)C2N3C4(=O)[CH](N)(CC(C)C)C5(=O)N[CH]31C2(=O)N(C)CC(=O)N(C)C1CCCCCN(C1=O)C(Cc1ccc(F)cc1)C(=O)N(C)CC(=O)NC(CCc1ccc(C(F)(F)F)c(Cl)c1)C(=O)N1CCCC1C(=O)NCC(=O)N(C)C(C1CCCC1)C(=O)N(C)C(C(=O)N1CCOCC1)CC(=O)N(C)[CH]54CC(C)C</t>
+        </is>
+      </c>
+      <c r="G1417" t="inlineStr"/>
+      <c r="H1417" t="inlineStr"/>
+      <c r="I1417" t="n">
+        <v>0.08255849242172407</v>
+      </c>
+      <c r="J1417" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1417" t="inlineStr"/>
+    </row>
+    <row r="1418">
+      <c r="A1418" s="1" t="n">
+        <v>1416</v>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_2087.png</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr"/>
+      <c r="D1418" t="inlineStr"/>
+      <c r="E1418" t="inlineStr"/>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>C1=C2=C1C21=CC=1.CC12CC1(C)C2C1=O=C1.CCCCCNC[CH]123NCCNCCOCCCNCCN[CH]456CCCCNCCOC78CC7(C)(CC7C(O)C7C7=CCC9C%10CC9N7%10)C8(C)(C)COCCNCCCC4[CH]5(C)N6CCOC45C[CH]4(CO5C[CH]O)NC4=O=C45=O4=CC=416=O1=C478N9C=14([CH]97(CO1CC1)NC147=O=C19(=O=4)N7[CH]91CC1C)[CH]862N53.O</t>
+        </is>
+      </c>
+      <c r="G1418" t="inlineStr"/>
+      <c r="H1418" t="inlineStr"/>
+      <c r="I1418" t="n">
+        <v>2.337839264978895e-12</v>
+      </c>
+      <c r="J1418" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1418" t="inlineStr"/>
+    </row>
+    <row r="1419">
+      <c r="A1419" s="1" t="n">
+        <v>1417</v>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_2095.png</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr"/>
+      <c r="D1419" t="inlineStr"/>
+      <c r="E1419" t="inlineStr"/>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>CCC(CC)C1C(=O)N(C)[CH]2(C(=O)N(C)C)CC3(=O)N4(C)C(COC)C5N6C7C(=O)(N(C)CC(=O)N(C)[CH]CC=CCCNC(Cc8ccc(C(F)(F)F)cc8)C(=O)N(C)CC(=O)NC(CCc8cc(F)c(C(F)(F)F)c(F)c8)C(=O)N8CCOCC8C(=O)NCC(=O)N1C)[CH]6(NC[CH]5(COC)N3(C)C4(=O)C2)[CH]7(C)CC</t>
+        </is>
+      </c>
+      <c r="G1419" t="inlineStr"/>
+      <c r="H1419" t="inlineStr"/>
+      <c r="I1419" t="n">
+        <v>0.1171961835428328</v>
+      </c>
+      <c r="J1419" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1419" t="inlineStr"/>
+    </row>
+    <row r="1420">
+      <c r="A1420" s="1" t="n">
+        <v>1418</v>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_0/rb_2099.png</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr"/>
+      <c r="D1420" t="inlineStr"/>
+      <c r="E1420" t="inlineStr"/>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>CC(N)C1NC(=O)C(CCCCN)NC(=O)C(CC2=CC=C(NC(N)=O)C=C2)NC(=O)C(CC2=CC=C(O)C=C2)NC(=O)C(NC(=O)C(CC2=CC=C(Cl)C=C2)NC(=O)CCC(C(=O)O)[N]2345CC[O]6[CH]27[N]28(CC[N]79%10CC(=O)[O](C3C9)[Cu]62%104[O]C(=O)C8)CC5)CSSCC(C(=O)NC(CO)C(C)O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1420" t="inlineStr"/>
+      <c r="H1420" t="inlineStr"/>
+      <c r="I1420" t="n">
+        <v>0.001268312849778616</v>
+      </c>
+      <c r="J1420" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1420" t="inlineStr"/>
+    </row>
+    <row r="1421">
+      <c r="A1421" s="1" t="n">
+        <v>1419</v>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_1852.png</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr"/>
+      <c r="D1421" t="inlineStr"/>
+      <c r="E1421" t="inlineStr"/>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>COc1ccc(CCc2nc3cc(-c4c(C)noc4C)ccc3n2C[C@H](C)N2CCN(C(=O)CCOCCOCCOCCNc3ccc4c(c3)C(=O)N(C3CCC(=O)NC3=O)C4=O)CC2)cc1Cl</t>
+        </is>
+      </c>
+      <c r="G1421" t="inlineStr"/>
+      <c r="H1421" t="inlineStr"/>
+      <c r="I1421" t="n">
+        <v>0.8106351917029333</v>
+      </c>
+      <c r="J1421" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1421" t="inlineStr"/>
+    </row>
+    <row r="1422">
+      <c r="A1422" s="1" t="n">
+        <v>1420</v>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_1856.png</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr"/>
+      <c r="D1422" t="inlineStr"/>
+      <c r="E1422" t="inlineStr"/>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>CO[C@H]([C@@H](C)C(=O)N[C@H](C)[C@@H](O)c1ccccc1)[C@@H]1CCCN1C(=O)C1CC[C@H](C)[C@H](N(C)C(=O)[C@@H](NC(=O)[C@@H](NC(=O)OCc2ccc(NC(=O)[C@H](C)NC(=O)[C@@H](NC(=O)CCNC(=O)/C=C/[C@@H](O)OC)C(C)C)cc2)C(C)C)C(C)C)[C@@H]1OC</t>
+        </is>
+      </c>
+      <c r="G1422" t="inlineStr"/>
+      <c r="H1422" t="inlineStr"/>
+      <c r="I1422" t="n">
+        <v>0.7775168665529941</v>
+      </c>
+      <c r="J1422" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1422" t="inlineStr"/>
+    </row>
+    <row r="1423">
+      <c r="A1423" s="1" t="n">
+        <v>1421</v>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_1868.png</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr"/>
+      <c r="D1423" t="inlineStr"/>
+      <c r="E1423" t="inlineStr"/>
+      <c r="F1423" t="inlineStr">
+        <is>
+          <t>CC(C)C(NC(=O)CN1C(=O)C(NC(=O)CNC(=O)C(CC2=CC=CC=C2)NC(=O)C(C)N2C34=O=C25(=O)[CH]3(N)C2[CH]45(N)C3C45=C6=C3278=CC=CC(=C47)=C58=CC=C6)CC(C)(C)C1C(C)C)C(=O)NC(CC1=CC=CC=C1)C(=O)NC(CC(=O)O)C(=O)NCC(=O)NC(CO)C(=O)NCC(N)=O</t>
+        </is>
+      </c>
+      <c r="G1423" t="inlineStr"/>
+      <c r="H1423" t="inlineStr"/>
+      <c r="I1423" t="n">
+        <v>0.007026346582577591</v>
+      </c>
+      <c r="J1423" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1423" t="inlineStr"/>
+    </row>
+    <row r="1424">
+      <c r="A1424" s="1" t="n">
+        <v>1422</v>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_1876.png</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr"/>
+      <c r="D1424" t="inlineStr"/>
+      <c r="E1424" t="inlineStr"/>
+      <c r="F1424" t="inlineStr">
+        <is>
+          <t>CC[CH]C1(=O)N[CH]23C(C4=CC=C(OCCN5CCOCC5)C=C4)[CH]45(CC6=CC=C(OCCN7CCOCC7)C=C6)NC(=O)[CH]1(CC1=CC=C(O)C=C1)NC(=O)C(NC(=O)C(N)CC1=CC=C(Cl)C=C1)CSSCC(C(=O)NC(CC1=CC=C(O)C=C1)C(N)=O)NC(=O)[CH]NC(=O)(C(CCCCN)NC24=O)C(CCCCN)NC35=O</t>
+        </is>
+      </c>
+      <c r="G1424" t="inlineStr"/>
+      <c r="H1424" t="inlineStr"/>
+      <c r="I1424" t="n">
+        <v>0.2300639508811204</v>
+      </c>
+      <c r="J1424" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1424" t="inlineStr"/>
+    </row>
+    <row r="1425">
+      <c r="A1425" s="1" t="n">
+        <v>1423</v>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_1884.png</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr"/>
+      <c r="D1425" t="inlineStr"/>
+      <c r="E1425" t="inlineStr"/>
+      <c r="F1425" t="inlineStr">
+        <is>
+          <t>[H]C1NC(=O)[C@]2([H])CCCN2C(=O)[C@]([H])([C@@H](C)O)NC(=O)[C@]([H])(CC(C)C)N(C)C(=O)CNC(=O)[C@]([H])([C@@H](C)CC)N(C)C(=O)[C@]([H])(CC(C)C)NC(=O)[C@]([H])(CC(C)C)N(C)C(=O)C(Cc2ccccc2)NC(=O)[C@]2([H])CCCCN2C(=O)[C@H](C(=O)N2CCCCC2)NC1=O.[H][C]1CCCN1C=O |^1:97|</t>
+        </is>
+      </c>
+      <c r="G1425" t="inlineStr"/>
+      <c r="H1425" t="inlineStr"/>
+      <c r="I1425" t="n">
+        <v>0.4863592633611287</v>
+      </c>
+      <c r="J1425" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1425" t="inlineStr"/>
+    </row>
+    <row r="1426">
+      <c r="A1426" s="1" t="n">
+        <v>1424</v>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_1892.png</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr"/>
+      <c r="D1426" t="inlineStr"/>
+      <c r="E1426" t="inlineStr"/>
+      <c r="F1426" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)[C@@H](NC(=O)CCOCCOCCOCCC(=O)N2CCN(c3cccc(-c4cnc5ccc(N6CCC[C@@H]6c6cccc(F)c6)nn45)n3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1426" t="inlineStr"/>
+      <c r="H1426" t="inlineStr"/>
+      <c r="I1426" t="n">
+        <v>0.8418656819745934</v>
+      </c>
+      <c r="J1426" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1426" t="inlineStr"/>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="1" t="n">
+        <v>1425</v>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_1896.png</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr"/>
+      <c r="D1427" t="inlineStr"/>
+      <c r="E1427" t="inlineStr"/>
+      <c r="F1427" t="inlineStr">
+        <is>
+          <t>CCC(C)C1NC(=O)[CH]2(CCCCC=Cc3ccc(cc3)CC(C(=O)NC)N3CCC=CCC(C3=O)N(C)C(=O)CN(C)C1=O)N1CN2(C)C1=O.CCOC1CC(C(=O)NC2(C(=O)N(C)C(C(=O)N(C)C(C)C(=O)N(C)C)C3CCCC3)CC(C)(C)C2)N(C(=O)C(CCc2ccc(C(F)(F)F)c(OC)c2)NC(C)=O)C1</t>
+        </is>
+      </c>
+      <c r="G1427" t="inlineStr"/>
+      <c r="H1427" t="inlineStr"/>
+      <c r="I1427" t="n">
+        <v>0.4658013432719386</v>
+      </c>
+      <c r="J1427" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1427" t="inlineStr"/>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="1" t="n">
+        <v>1426</v>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_1924.png</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr"/>
+      <c r="D1428" t="inlineStr"/>
+      <c r="E1428" t="inlineStr"/>
+      <c r="F1428" t="inlineStr">
+        <is>
+          <t>[H][C]NC(=O)[CH]Cc1ccccc1NC(=O)CC(NC(=O)[C@H](CC(=O)O)NC(C)(C)C)C(=O)N[C@@H](C)C(=O)N[C@@H](Cc1c[nH]c2ccccc12)C(=O)N[C@@H](Cc1c[nH]cn1)C(=O)N[C@@H](CC(C)C)C(=O)NCC(=O)N[C@@H](CCC(=O)O)C(=O)N[C@@H](CC(C)C)C(=O)N[C@H](C(=O)N[CH]Cc1c[nH]cc1C=C)C(C)C |^1:5,96,^2:1|</t>
+        </is>
+      </c>
+      <c r="G1428" t="inlineStr"/>
+      <c r="H1428" t="inlineStr"/>
+      <c r="I1428" t="n">
+        <v>0.8261052939129311</v>
+      </c>
+      <c r="J1428" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1428" t="inlineStr"/>
+    </row>
+    <row r="1429">
+      <c r="A1429" s="1" t="n">
+        <v>1427</v>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_1944.png</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr"/>
+      <c r="D1429" t="inlineStr"/>
+      <c r="E1429" t="inlineStr"/>
+      <c r="F1429" t="inlineStr">
+        <is>
+          <t>[H][C@]1(C)CC(=O)N(C)[C@@]([H])(CC(C)C)C(=O)N(C)[C@@]([H])(CC(C)C)C(=O)N[C@@]([H])([C@@H](C)CC)C(=O)N[C@@]([H])(C)C(=O)N(C)[C@@]([H])(C)C(=O)N(C)[C@@]([H])(CC(C)C)C(=O)N(C)[C@@]([H])(CC(C)C)C(=O)N[C@@]([H])([C@@H](C)O)C(=O)N[C@@]([H])(Cc2ccccc2)C(=O)N(C)[C@@]([H])(CC(C)C)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1429" t="inlineStr"/>
+      <c r="H1429" t="inlineStr"/>
+      <c r="I1429" t="n">
+        <v>0.8418196174044986</v>
+      </c>
+      <c r="J1429" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1429" t="inlineStr"/>
+    </row>
+    <row r="1430">
+      <c r="A1430" s="1" t="n">
+        <v>1428</v>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_1948.png</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr"/>
+      <c r="D1430" t="inlineStr"/>
+      <c r="E1430" t="inlineStr"/>
+      <c r="F1430" t="inlineStr">
+        <is>
+          <t>[H][C@]1(C(=O)N2CCCCC2)NC(=O)[C@]([H])(CC(C)C)NC(=O)[C@]([H])(Cc2ccccc2)NC(=O)[C@]([H])(CC)N(C)C(=O)[C@]([H])(CC(C)C)NC(=O)[C@]([H])([C@@H](C)O)NC(=O)[C@]([H])(Cc2ccccc2)NC(=O)[C@]([H])([C@@H](C)CC)NC(=O)[C@]([H])(C(C)C)N(C)C(=O)[C@]([H])(C)N(C)C1=O</t>
+        </is>
+      </c>
+      <c r="G1430" t="inlineStr"/>
+      <c r="H1430" t="inlineStr"/>
+      <c r="I1430" t="n">
+        <v>0.8172559579019332</v>
+      </c>
+      <c r="J1430" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1430" t="inlineStr"/>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="1" t="n">
+        <v>1429</v>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_1952.png</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr"/>
+      <c r="D1431" t="inlineStr"/>
+      <c r="E1431" t="inlineStr"/>
+      <c r="F1431" t="inlineStr">
+        <is>
+          <t>COc1ccc(CC[C@H]2OC(=O)[C@@H]3CCCCN3C(=O)C(=O)C(C)(C)COC(=O)/C=C/CCN(C)C(=O)[C@@H](Cc3ccccc3)NC(=O)CN(C)C(=O)[C@@H](Cc3ccccc3)NC(=O)[C@H](Cc3ccc(OC(=O)N4CCOCC4)cc3)N(C)C(=O)CCC(=O)Nc3cccc2c3)cc1OC</t>
+        </is>
+      </c>
+      <c r="G1431" t="inlineStr"/>
+      <c r="H1431" t="inlineStr"/>
+      <c r="I1431" t="n">
+        <v>0.7808594861910306</v>
+      </c>
+      <c r="J1431" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1431" t="inlineStr"/>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="1" t="n">
+        <v>1430</v>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_1956.png</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr"/>
+      <c r="D1432" t="inlineStr"/>
+      <c r="E1432" t="inlineStr"/>
+      <c r="F1432" t="inlineStr">
+        <is>
+          <t>CCCOC[CH]12C3(=O)N[CH]45C(=O)N6(C)CC(=O)N(C)C7CC=CCCNC(Cc8ccc(C)cc8)C(=O)N(C)CC(=O)NC(CCc8cc(F)c(C(F)(F)F)c(F)c8)C(=O)N8CC(OCC)CC8C(=O)NCC(=O)N(C)C(CC(C)(C)C)C(=O)N[CH]CC(=O)N1(C)[CH]3(COCCC)C2(=O)N4[CH]C56(=O)N(C)CC(=O)N7C</t>
+        </is>
+      </c>
+      <c r="G1432" t="inlineStr"/>
+      <c r="H1432" t="inlineStr"/>
+      <c r="I1432" t="n">
+        <v>0.03569076630040318</v>
+      </c>
+      <c r="J1432" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1432" t="inlineStr"/>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="1" t="n">
+        <v>1431</v>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_1976.png</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr"/>
+      <c r="D1433" t="inlineStr"/>
+      <c r="E1433" t="inlineStr"/>
+      <c r="F1433" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1433" t="inlineStr"/>
+      <c r="H1433" t="inlineStr"/>
+      <c r="I1433" t="n">
+        <v>0.02723812910383523</v>
+      </c>
+      <c r="J1433" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1433" t="inlineStr"/>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="1" t="n">
+        <v>1432</v>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_1980.png</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr"/>
+      <c r="D1434" t="inlineStr"/>
+      <c r="E1434" t="inlineStr"/>
+      <c r="F1434" t="inlineStr">
+        <is>
+          <t>Cc1ncsc1-c1ccc(CNC(=O)[C@@H]2C[C@@H](O)CN2C(=O)C(NC(=O)CCCCCCCCNC(=O)CN2CCN(c3cccc(-c4cnc5ccc(N6CCCC6c6cccc(F)c6)nn45)n3)CC2)C(C)(C)C)cc1</t>
+        </is>
+      </c>
+      <c r="G1434" t="inlineStr"/>
+      <c r="H1434" t="inlineStr"/>
+      <c r="I1434" t="n">
+        <v>0.83690662805334</v>
+      </c>
+      <c r="J1434" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1434" t="inlineStr"/>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="1" t="n">
+        <v>1433</v>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_1992.png</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr"/>
+      <c r="D1435" t="inlineStr"/>
+      <c r="E1435" t="inlineStr"/>
+      <c r="F1435" t="inlineStr">
+        <is>
+          <t>[H]C(CC(=O)NC([H])(C(=O)NC1(C)C2(=O)N3(C)C4([H])(C)C5(=O)N67(C)C(=O)(N8(C)C69([H])CC6=CC=CC=C6C6(=CC=CC=C6)CC876([H])C(=O)N78CCCC7%10%11%12%13%14([H])[H]C8%107(C%11CCN7%12C96=O)C%13(=O)NC([H])(CC(C)C)NC%14=O)C53([H])(C)N4(C)C(=O)C2([H])(C)(C(C)O)[CH]1(C)O)C(C)C)NC(=O)C([H])CC</t>
+        </is>
+      </c>
+      <c r="G1435" t="inlineStr"/>
+      <c r="H1435" t="inlineStr"/>
+      <c r="I1435" t="n">
+        <v>0.02035518846716674</v>
+      </c>
+      <c r="J1435" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1435" t="inlineStr"/>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="1" t="n">
+        <v>1434</v>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2004.png</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr"/>
+      <c r="D1436" t="inlineStr"/>
+      <c r="E1436" t="inlineStr"/>
+      <c r="F1436" t="inlineStr">
+        <is>
+          <t>[H]CNC(=O)C([H])(CC1=CC=CC=C1)N(C)C(=O)C1([H])CC(=O)N(C)C([H])(C)C(=O)N(C)C([H])(CC(C)C)C(=O)NC([H])(C(C)O)C(=O)N(C)[CH]([H])(C)C(=O)N(C)C([H])(CC2=CC=CC=C2)C(=O)NC([H])(C(C)CC)C(=O)N(C)CC(=O)N(CC(C)C)C([H])C(=O)N(C)C([H])(C(C)C)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1436" t="inlineStr"/>
+      <c r="H1436" t="inlineStr"/>
+      <c r="I1436" t="n">
+        <v>0.1844041890158041</v>
+      </c>
+      <c r="J1436" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1436" t="inlineStr"/>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="1" t="n">
+        <v>1435</v>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2008.png</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr"/>
+      <c r="D1437" t="inlineStr"/>
+      <c r="E1437" t="inlineStr"/>
+      <c r="F1437" t="inlineStr">
+        <is>
+          <t>CCC[CH]NC(=O)C1CCCN1C(=O)C(CC(N)=O)N12C3(=O)[CH]45C6C7=CC=C(O)C=C7C7(=CC=C(O)C=C7)C[CH]637(NC(=O)[CH]3(CC(N)=O)NC6(=O)=O=C(N6)C(CC(N)=O)C3(=O)N47)C51(=O)N[CH]2(CC(N)=O)C(=O)N1CCCC1C(=O)NC(CCC(=O)O)C(=O)NC(CO)C(=O)N[CH]C(=O)NC(C)CCCCCCCCCCC</t>
+        </is>
+      </c>
+      <c r="G1437" t="inlineStr"/>
+      <c r="H1437" t="inlineStr"/>
+      <c r="I1437" t="n">
+        <v>0.003219262106283666</v>
+      </c>
+      <c r="J1437" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1437" t="inlineStr"/>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="1" t="n">
+        <v>1436</v>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2012.png</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr"/>
+      <c r="D1438" t="inlineStr"/>
+      <c r="E1438" t="inlineStr"/>
+      <c r="F1438" t="inlineStr">
+        <is>
+          <t>COCCC(CCOC)(CNC(=O)N[CH]12C(=O)C(C(=O)NCC34FC3F4)CC3=CC=CC4(=C3)N3C5678=O=C3(=O=54)(N6)(C17)C28)NC(=O)C1NC(C(=O)N2C3C2(NC(C)C=O)C3(=O)NC(CCCNC(C)=O)C23(=O)N4C5C267=C289%10C%11C62(=CN2C6=O=C(=O)(NC(=O)NCC(N)=O)(N6)N(C6(C)=O=C6C)C24=O)C8246=CC=C8(C)C(C)=CC2=C849[CH]5%11376%10)C1(=O)NC1NC1=O</t>
+        </is>
+      </c>
+      <c r="G1438" t="inlineStr"/>
+      <c r="H1438" t="inlineStr"/>
+      <c r="I1438" t="n">
+        <v>2.303440844341322e-09</v>
+      </c>
+      <c r="J1438" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1438" t="inlineStr"/>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="1" t="n">
+        <v>1437</v>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2016.png</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr"/>
+      <c r="D1439" t="inlineStr"/>
+      <c r="E1439" t="inlineStr"/>
+      <c r="F1439" t="inlineStr">
+        <is>
+          <t>CCCN1C(=O)CN(C)C(=O)CN(C)C(=O)[C@H]([C@@H](C)CC)NC(=O)[C@@H]2CCCCCN2C(=O)C[C@@H](C(=O)N2CCOCC2)N(C)C(=O)[C@H](C2CCCC2)N(C)C(=O)C2(CCCC2)NC(=O)[C@@H]2CCCN2C(=O)[C@H](CCc2ccc(C(F)(F)F)c(Cl)c2)NC(=O)CN(C)C(=O)[C@@H]1Cc1ccc(C(F)(F)F)cc1</t>
+        </is>
+      </c>
+      <c r="G1439" t="inlineStr"/>
+      <c r="H1439" t="inlineStr"/>
+      <c r="I1439" t="n">
+        <v>0.5217938569847</v>
+      </c>
+      <c r="J1439" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1439" t="inlineStr"/>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="1" t="n">
+        <v>1438</v>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2024.png</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr"/>
+      <c r="D1440" t="inlineStr"/>
+      <c r="E1440" t="inlineStr"/>
+      <c r="F1440" t="inlineStr">
+        <is>
+          <t>CC=CC=CC1=C2C3=CC2=C3(C[CH]2([CH]CC=CC=CC[CH]NC(=O)CCCCCNC(C)=O)C(=O)C2CNC(=O)CC)C=C1.[H]C(C1(=O)C23CCCCC2C31=O)C123(O)O4[CH]5678CC9[CH]1(C)C[CH]92CC5C1C62C(C)C(C)(=CC=C)[CH]42(C(C)=CC=CC=CN([H])CC(C)C(=O)C(OC)C(O)C2=CC4=C5C6=C2C=465C)(C7)O138</t>
+        </is>
+      </c>
+      <c r="G1440" t="inlineStr"/>
+      <c r="H1440" t="inlineStr"/>
+      <c r="I1440" t="n">
+        <v>8.542714552418565e-06</v>
+      </c>
+      <c r="J1440" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1440" t="inlineStr"/>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="1" t="n">
+        <v>1439</v>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2028.png</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr"/>
+      <c r="D1441" t="inlineStr"/>
+      <c r="E1441" t="inlineStr"/>
+      <c r="F1441" t="inlineStr">
+        <is>
+          <t>[H]C(N)(C(=O)N(C)C([H])(CC(C)C)C(=O)N(C)C1=O=C1(=O)NC([H])(C(=O)N(C)C(C)C(=O)NC1(C)CC(=O)N(C)CCC2(=O)N(C)C34(CC5=CC=CC=C5)C(=O)(C(CC5=CC=CC=C5)N23(C)C(=O)CCN2(C)CC2(=O)C1)N1(C(C)C)C4(=O)N(C)C23(CC(C)C)C(=O)N(C)C([H])(C)N4(C)C2567=O=C43528=O=6=C172[H]8)C(C)O)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1441" t="inlineStr"/>
+      <c r="H1441" t="inlineStr"/>
+      <c r="I1441" t="n">
+        <v>0.0001026149481028903</v>
+      </c>
+      <c r="J1441" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1441" t="inlineStr"/>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="1" t="n">
+        <v>1440</v>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2032.png</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr"/>
+      <c r="D1442" t="inlineStr"/>
+      <c r="E1442" t="inlineStr"/>
+      <c r="F1442" t="inlineStr">
+        <is>
+          <t>CC[C@H](C)[C@H](NC(=O)[C@@H](NC(=O)[C@@H](NC(=O)OCc1ccc(NC(=O)[C@H](C)NC(=O)[C@@H](NC(=O)CCCCCNC(=O)/C=C\C(=O)OC)C(C)C)cc1)C(C)C)C(C)C)[C@@H](CC(=O)N1CCC[C@H]1[C@H](OC)[C@@H](C)C(=O)N[C@H](C)[C@@H](O)c1ccccc1)OC</t>
+        </is>
+      </c>
+      <c r="G1442" t="inlineStr"/>
+      <c r="H1442" t="inlineStr"/>
+      <c r="I1442" t="n">
+        <v>0.7850691823021936</v>
+      </c>
+      <c r="J1442" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1442" t="inlineStr"/>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="1" t="n">
+        <v>1441</v>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2036.png</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr"/>
+      <c r="D1443" t="inlineStr"/>
+      <c r="E1443" t="inlineStr"/>
+      <c r="F1443" t="inlineStr">
+        <is>
+          <t>C=CC(=O)NC1=CC(NC(=O)C2=C(C)N(C3=CC=C(OCC(=O)N45CCN6(C(=O)CCCCC(O)[CH]C(=O)N[CH]78C(=O)C(CC(=O)N(C)C(CC(C)C)C(=O)NC9CCCN(C(CC(C)C)C(=O)NC(C)C(=O)NC(C)C%10NCC%10C(C)C)C9=O)C7CC8C)C7C4C6C75)C=C3)N=C2)=CC(Cl)=C1.CC</t>
+        </is>
+      </c>
+      <c r="G1443" t="inlineStr"/>
+      <c r="H1443" t="inlineStr"/>
+      <c r="I1443" t="n">
+        <v>0.02304110458741965</v>
+      </c>
+      <c r="J1443" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1443" t="inlineStr"/>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="1" t="n">
+        <v>1442</v>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2040.png</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr"/>
+      <c r="D1444" t="inlineStr"/>
+      <c r="E1444" t="inlineStr"/>
+      <c r="F1444" t="inlineStr">
+        <is>
+          <t>CCO[CH]12CN3C(=O)C(CCc4cc(F)c(C(F)(F)F)c(F)c4)NC(=O)CN(C)C(=O)C4Cc5ccc(cc5)C=CCCCCC(C(=O)NC(C(C)CC)C(=O)N(C)CC(=O)N(C)C5CC=CCCN4C5=O)N(C)C(=O)CC(C(=O)N(C)CC)N(C)C(=O)C(C4CCCC4)N(C)C(=O)C4(CCC4)NC(=O)[CH]3(C1)C2</t>
+        </is>
+      </c>
+      <c r="G1444" t="inlineStr"/>
+      <c r="H1444" t="inlineStr"/>
+      <c r="I1444" t="n">
+        <v>0.4644516885210819</v>
+      </c>
+      <c r="J1444" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1444" t="inlineStr"/>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="1" t="n">
+        <v>1443</v>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2044.png</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr"/>
+      <c r="D1445" t="inlineStr"/>
+      <c r="E1445" t="inlineStr"/>
+      <c r="F1445" t="inlineStr">
+        <is>
+          <t>CC(C)[C@@H](NC(=O)CCOCCC(=O)N1CCN(c2ccc(C(=O)Nc3n[nH]c4ccc(Cc5cc(F)cc(F)c5)cc34)c(NC3CCOCC3)c2)CC1)C(=O)N1C[C@H](O)C[C@H]1C(=O)NCc1ccc(-c2cncs2)cc1</t>
+        </is>
+      </c>
+      <c r="G1445" t="inlineStr"/>
+      <c r="H1445" t="inlineStr"/>
+      <c r="I1445" t="n">
+        <v>0.5628303352292217</v>
+      </c>
+      <c r="J1445" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1445" t="inlineStr"/>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="1" t="n">
+        <v>1444</v>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2048.png</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr"/>
+      <c r="D1446" t="inlineStr"/>
+      <c r="E1446" t="inlineStr"/>
+      <c r="F1446" t="inlineStr">
+        <is>
+          <t>[H][C@]1(C)C(=O)N[C@@]([H])(COC(C)(C)C)C(=O)N(C)[C@@]([H])(CC(C)C)C(=O)N(C)[C@@]([H])(CC(C)C)C(=O)N[C@]([H])(C(=O)N2CCCCC2)CC(=O)N(C)CCC(=O)N(C)[C@@]([H])(Cc2ccccc2)C(=O)N[C@@]([H])([C@@H](C)O)C(=O)N1C</t>
+        </is>
+      </c>
+      <c r="G1446" t="inlineStr"/>
+      <c r="H1446" t="inlineStr"/>
+      <c r="I1446" t="n">
+        <v>0.7322280780642483</v>
+      </c>
+      <c r="J1446" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1446" t="inlineStr"/>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="1" t="n">
+        <v>1445</v>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2052.png</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr"/>
+      <c r="D1447" t="inlineStr"/>
+      <c r="E1447" t="inlineStr"/>
+      <c r="F1447" t="inlineStr">
+        <is>
+          <t>[H]C1(C(=O)N2CCCCC2)CC(=O)N(C)CCCC(=O)N(C)C([H])(C)C(=O)N(C)C([H])(CC(C)C)N2C(=O)C2([H])(C(C)O)C(=O)N(C)C([H])(C)C(=O)N(C)C([H])(CC(C)C)C(=O)N(C)C([H])(CC2=CC=CC=C2)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1447" t="inlineStr"/>
+      <c r="H1447" t="inlineStr"/>
+      <c r="I1447" t="n">
+        <v>0.4004709510818837</v>
+      </c>
+      <c r="J1447" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1447" t="inlineStr"/>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="1" t="n">
+        <v>1446</v>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2060.png</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr"/>
+      <c r="D1448" t="inlineStr"/>
+      <c r="E1448" t="inlineStr"/>
+      <c r="F1448" t="inlineStr">
+        <is>
+          <t>[H]C(C)C([H])([H])OC1[H]C1O[CH]C1([H])([H])[H]C1([H])C([H])([H])C([H])([H])NCCCCN([H])CC1=C([N+]=[N+][N-]C=CCCCOCC2CO2CCCN2C34C256C327C45389C6245%10C7326%11C8437%12C95248%13C%1063259C%117436%10C%128247%11C%135328%12C96435%13C%1072469%14C%118327%10%15C%125438%11%16C%136245%12%17C97326%13%18C%14%1084379%19C%15%115248%10%14C%16%126325%11%15C%17%137436%12%16C%1898247%13%17C%19%1053289%18C%14%116435%10%19C%15%127246%11%14C%16%138327%12%15C%1795438%13%16C%18%1062459%17%20C%19%117326%10%18%21C%14%128437%11%19%22C%15%135248%12%14%23C%1696325%13%15%24C%17%1074369%16%25C%20%18%118247%10%17%26C%21%19%125328%11%18%20C%22%14%136435%12%19%21C%23%1597246%13%14%22C%24%16%1083279%15%23C%25%17%115438%10%16%24C%26%18%126245%11%17%25C%20%19%137326%12%18%26C%21%1498437%13%19%20C%22%15%1052489%14%21C%23%16%116325%10%15%22C%24%17%127436%11%16%23C%25%18%138247%12%17%24C%26%1995328%13%18%25C%20%14%1064359%19%26C%21%15%117246%10%14%20C27%11%15%21%27%28%29%30%31C%32%33%34%35%36%37%38%39%40%41C%42%43%44%45%46%47%48%49%50%51C%52%53%54%55%56%57%58C%59%60%61%62C%52%63%64%65%66C%59%53%52%67%68%69C%60%63%54%42%53%59%70%71C%61%64%52%55%43%42%54%60%63C%62%65%67%56%53%44%43%52%55%61C%66%68%57%59%42%45%44%53%56%62C%69%58%70%54%43%46%42%45%57%59C%71%60%52%44%47%32%43%46%54%58C%63%55%53%42%48%33%32%44%47%52C%61%56%45%49%43%34%33%42%48%53C%62%57%50%46%32%35%34%43%45%49C%59%51%54%44%33%36%32%35%46%50C%58%47%42%34%372%33%36%44%51C%52%48%43%32%3872%34%37%42C%53%45%35%39%33%117%32%38%43C%49%46%40%362%15%11%33%35%39C%50%41%44%347%212%15%36%40C%51%37%32%113%2747%21%34C%22%16%12825%28634C%42%38%33%13%159%29%1072C%23%17%35%18%36%19%30%14%213C%43%24%39%25%40%26%31%20%3442)=C1</t>
+        </is>
+      </c>
+      <c r="G1448" t="inlineStr"/>
+      <c r="H1448" t="inlineStr"/>
+      <c r="I1448" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1448" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1448" t="inlineStr"/>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="1" t="n">
+        <v>1447</v>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2064.png</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr"/>
+      <c r="D1449" t="inlineStr"/>
+      <c r="E1449" t="inlineStr"/>
+      <c r="F1449" t="inlineStr">
+        <is>
+          <t>CCCCC[C@H](C)C(NC(=O)C1=CCCCN1C)C(=O)N[C@H](C[CH]OC(=O)CNC(=O)N[C@@H](Cc1ccc(NCc2ccc(NC(=O)[C@H](CCCNC(N)=O)NC(=O)[C@@H](NC(=O)CCOCCOCCOCCOCCNC(=O)CCC(=O)N3Cc4ccccc4/C=C\c4ccccc43)C(C)C)cc2)cc1)CC(C)(C)C(=O)O)C(C)C.CCO |^1:23|</t>
+        </is>
+      </c>
+      <c r="G1449" t="inlineStr"/>
+      <c r="H1449" t="inlineStr"/>
+      <c r="I1449" t="n">
+        <v>0.100263287469374</v>
+      </c>
+      <c r="J1449" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1449" t="inlineStr"/>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="1" t="n">
+        <v>1448</v>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2068.png</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr"/>
+      <c r="D1450" t="inlineStr"/>
+      <c r="E1450" t="inlineStr"/>
+      <c r="F1450" t="inlineStr">
+        <is>
+          <t>CCCCCON12C(=O)C34NC5(=O)[CH]6(CCCCN6(C)[CH]356CCCCN6C)C(=O)C1(=O)N1(C(O)C(C)[CH]4(O)CC)C(C(C)C)CC345=C678[CH]9(O%10C%11(=O=C%10(C)(=O)C%11)O3)C43%10%11=C4[SH]6%12=C6%13=C(C(=O)NC(CC=CC=CNC(=O)OCC=CC=CNC(=O)C(CCCNC(N)=O)NC(=O)[CH]NC(=O)CC)CC(C)(C)C(=O)O)N3C3%14=C=6=59%12([CH]37%10CC21)S4%14%138%11</t>
+        </is>
+      </c>
+      <c r="G1450" t="inlineStr"/>
+      <c r="H1450" t="inlineStr"/>
+      <c r="I1450" t="n">
+        <v>7.856236714961795e-07</v>
+      </c>
+      <c r="J1450" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1450" t="inlineStr"/>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="1" t="n">
+        <v>1449</v>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2072.png</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr"/>
+      <c r="D1451" t="inlineStr"/>
+      <c r="E1451" t="inlineStr"/>
+      <c r="F1451" t="inlineStr">
+        <is>
+          <t>CCC[CH]12N(C)C(=O)CC(C(=O)N(C)C)N(C)C(=O)C3C(CC)C(C)C4(C)(C)CC(C4)(NC(=O)C4CC(OC5CCC5)CN4C(=O)C(CCc4ccc(Cl)c(Cl)c4)NC(=O)CN(C)C(=O)C(Cc4ccc(C)cc4)NCCC=CC[CH]N(C)C(=O)CN(C)C(=O)C4N5C(NC1(=O)C(CC)C52=O)[CH]4(C)CC)C(=O)N3C</t>
+        </is>
+      </c>
+      <c r="G1451" t="inlineStr"/>
+      <c r="H1451" t="inlineStr"/>
+      <c r="I1451" t="n">
+        <v>0.1008922753849505</v>
+      </c>
+      <c r="J1451" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1451" t="inlineStr"/>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="1" t="n">
+        <v>1450</v>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2080.png</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr"/>
+      <c r="D1452" t="inlineStr"/>
+      <c r="E1452" t="inlineStr"/>
+      <c r="F1452" t="inlineStr">
+        <is>
+          <t>CCO[CH]12CN3C(=O)C(CCc4ccc(C(F)(F)F)c(Cl)c4)NC(=O)CN(C)C(=O)C(Cc4ccc(C(F)(F)F)cc4)N4CCC=CCC(C4=O)N(C)C(=O)CN(C)C(=O)C(C(C)CC)NC(=O)C(COC)N(C)C(=O)CC(C(=O)N(C)C)N(C)C(=O)C(C4CCCC4)N(C)C(=O)C4(CC(C)(C)C4)NC(=O)[CH]3(C1)C2</t>
+        </is>
+      </c>
+      <c r="G1452" t="inlineStr"/>
+      <c r="H1452" t="inlineStr"/>
+      <c r="I1452" t="n">
+        <v>0.3477894845090306</v>
+      </c>
+      <c r="J1452" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1452" t="inlineStr"/>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="1" t="n">
+        <v>1451</v>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2088.png</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr"/>
+      <c r="D1453" t="inlineStr"/>
+      <c r="E1453" t="inlineStr"/>
+      <c r="F1453" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(N4CCOC(CN5CCN(c6ccc(C(=O)Nc7n[nH]c8ccc(Cc9cc(F)cc(F)c9)cc78)c(NC7CCOCC7)c6)CC5)C4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1453" t="inlineStr"/>
+      <c r="H1453" t="inlineStr"/>
+      <c r="I1453" t="n">
+        <v>0.8375769027379451</v>
+      </c>
+      <c r="J1453" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1453" t="inlineStr"/>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="1" t="n">
+        <v>1452</v>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2092.png</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr"/>
+      <c r="D1454" t="inlineStr"/>
+      <c r="E1454" t="inlineStr"/>
+      <c r="F1454" t="inlineStr">
+        <is>
+          <t>C[CH]NC(=O)C(CO1CC1[CH]NC1CC1NC[CH]C1OCC(=O)(O)=O=C(O)CO[CH]2345678O[CH]29%10%11%12%13C32%14O[CH]194C2%1051349%15C%1162C(O)C%142%1271[CH]%1383(OC1CC1C1C2CC21)[CH]123O5C(O)[CH]51467(O)C1(=O)(O)OC4=O=C4(OC4O5[CH]48C(=O)(O)C584=O=C4CNCCCCCCCC4=O=C(CCCCCNC(=O)CCCCCCCCCC)C4)O[CH]1269[CH]37%15OCC1CC1C)NCC.O</t>
+        </is>
+      </c>
+      <c r="G1454" t="inlineStr"/>
+      <c r="H1454" t="inlineStr"/>
+      <c r="I1454" t="n">
+        <v>5.147762232870881e-22</v>
+      </c>
+      <c r="J1454" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1454" t="inlineStr"/>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="1" t="n">
+        <v>1453</v>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_1/rb_2100.png</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr"/>
+      <c r="D1455" t="inlineStr"/>
+      <c r="E1455" t="inlineStr"/>
+      <c r="F1455" t="inlineStr">
+        <is>
+          <t>COC1=CC=C(CC[CH]23OC(=O)[CH]45CCCCN4C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)C(CC(C)C)N(C)C(=O)C4CCCN4C(=O)C(CC4=CC=C(C(=O)NCCO)C=C4)NC(=O)C(C4=CC=CC=C4)NC(=O)CCC(=O)NC46=CC278=C29=C3(=C=73C27=C4=C93=C=76)[CH]8(CCC2=CC=C(OC)C(OC)=C2)OC5=O)C=C1OC</t>
+        </is>
+      </c>
+      <c r="G1455" t="inlineStr"/>
+      <c r="H1455" t="inlineStr"/>
+      <c r="I1455" t="n">
+        <v>0.1755831867821512</v>
+      </c>
+      <c r="J1455" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1455" t="inlineStr"/>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="1" t="n">
+        <v>1454</v>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1861.png</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr"/>
+      <c r="D1456" t="inlineStr"/>
+      <c r="E1456" t="inlineStr"/>
+      <c r="F1456" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3cc(C4CN(C5CCN(c6ccc(C(=O)Nc7n[nH]c8ccc(Cc9cc(F)cc(F)c9)cc78)c(NC7CCOCC7)c6)CC5)C4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1456" t="inlineStr"/>
+      <c r="H1456" t="inlineStr"/>
+      <c r="I1456" t="n">
+        <v>0.7205370816450204</v>
+      </c>
+      <c r="J1456" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1456" t="inlineStr"/>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="1" t="n">
+        <v>1455</v>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1865.png</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr"/>
+      <c r="D1457" t="inlineStr"/>
+      <c r="E1457" t="inlineStr"/>
+      <c r="F1457" t="inlineStr">
+        <is>
+          <t>CC(C)CCC(=O)N1CC(=O)N[C@@H](Cc2ccccc2)CN(CC(N)=O)C(=O)CCSCc2ccc(cc2)C(=O)N[C@@H](Cc2ccccc2)CN(C(=O)CC2CC2)CC(=O)N[C@@H](Cc2ccccc2)CN(C(=O)CC2CC2)CC(=O)N[C@@H](CCCCN)C1</t>
+        </is>
+      </c>
+      <c r="G1457" t="inlineStr"/>
+      <c r="H1457" t="inlineStr"/>
+      <c r="I1457" t="n">
+        <v>0.6092229181810388</v>
+      </c>
+      <c r="J1457" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1457" t="inlineStr"/>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="1" t="n">
+        <v>1456</v>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1869.png</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr"/>
+      <c r="D1458" t="inlineStr"/>
+      <c r="E1458" t="inlineStr"/>
+      <c r="F1458" t="inlineStr">
+        <is>
+          <t>C=CC(=O)NCCNC=NCNCCC(=O)NCCNC(=O)CCCC(C)C(O)C1NCCC2(C)(C)CCC(C)(C)CC2C1(=O)NC(CC)C(=O)N(C)CC(=O)N(C)C(CCC)C(=O)N(C)C(=O)N(C)[CH]C(=O)NC(C)C(=O)NC(C)C(=O)N(CC)C(CCC)C(=O)N(C)C12=O=C34(=O)C15[CH]1(C67CC1(C6)C7)N531CN24C1</t>
+        </is>
+      </c>
+      <c r="G1458" t="inlineStr"/>
+      <c r="H1458" t="inlineStr"/>
+      <c r="I1458" t="n">
+        <v>0.0003761716770419136</v>
+      </c>
+      <c r="J1458" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1458" t="inlineStr"/>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="1" t="n">
+        <v>1457</v>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1873.png</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr"/>
+      <c r="D1459" t="inlineStr"/>
+      <c r="E1459" t="inlineStr"/>
+      <c r="F1459" t="inlineStr">
+        <is>
+          <t>C#CC1=C(F)C=CC2=C1C(C1=C34(F)C5678=C19(F)=C351%10=N63=C5(OCC6%11CCCN6C(COC(=O)NCCCNC6=C%12C(=O)N(C%13CCC(=O)NC%13=O)C(=O)C%12=CC=C6)CC%11)=NC(N6CC%11CCC(C6)N%11)=C71C3498%10=N5)=CC(O)=C2</t>
+        </is>
+      </c>
+      <c r="G1459" t="inlineStr"/>
+      <c r="H1459" t="inlineStr"/>
+      <c r="I1459" t="n">
+        <v>0.09432179947483145</v>
+      </c>
+      <c r="J1459" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1459" t="inlineStr"/>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="1" t="n">
+        <v>1458</v>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1877.png</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr"/>
+      <c r="D1460" t="inlineStr"/>
+      <c r="E1460" t="inlineStr"/>
+      <c r="F1460" t="inlineStr">
+        <is>
+          <t>CCO[C@@H]1C[C@H]2C(=O)NC3(CCC3)C(=O)N(C)[C@@H](C3CCCC3)C(=O)N(C)[C@H](C(=O)N3CCOCC3)CC(=O)N(C)[C@@H](CC(C)C)C(=O)N[C@@H]([C@@H](C)CC)C(=O)N(C)CC(=O)N(C)[C@H]3CCCCCN(C3=O)[C@@H](Cc3ccc(F)cc3Cl)C(=O)N(C)CC(=O)N[C@@H](CCc3cc(F)c(C(F)(F)F)c(F)c3)C(=O)N2C1</t>
+        </is>
+      </c>
+      <c r="G1460" t="inlineStr"/>
+      <c r="H1460" t="inlineStr"/>
+      <c r="I1460" t="n">
+        <v>0.7113367491456201</v>
+      </c>
+      <c r="J1460" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1460" t="inlineStr"/>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="1" t="n">
+        <v>1459</v>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1881.png</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr"/>
+      <c r="D1461" t="inlineStr"/>
+      <c r="E1461" t="inlineStr"/>
+      <c r="F1461" t="inlineStr">
+        <is>
+          <t>CCC(C)C1NC(=O)C2CCCCCC34(=O)=O=C(C3C(C(=O)N3CCOCC3)N(C)C(=O)C(C3CCCC3)N(C)C(=O)C3(CCCC3)NC(=O)C3CCCN3C(=O)C(CCc3cc(F)c(C(F)(F)F)c(F)c3)NC(=O)CN(C)C(=O)C(Cc3ccc(C(F)(F)F)cc3)N3CCCCCC3N(C)C(=O)CN(C)C1=O)N24</t>
+        </is>
+      </c>
+      <c r="G1461" t="inlineStr"/>
+      <c r="H1461" t="inlineStr"/>
+      <c r="I1461" t="n">
+        <v>0.1164800994962805</v>
+      </c>
+      <c r="J1461" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1461" t="inlineStr"/>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="1" t="n">
+        <v>1460</v>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1885.png</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr"/>
+      <c r="D1462" t="inlineStr"/>
+      <c r="E1462" t="inlineStr"/>
+      <c r="F1462" t="inlineStr">
+        <is>
+          <t>C[CH]NC(=O)N1CCC1C(CC(N)N)NC(=O)C(C)N(C)C1(=O)CNC[CH]C2(=O)N[CH]C(=O)N(C)C(CCCC)C(=O)N(C)C(CCC)C(=O)NC(CC(C)C)C(=O)NC(C(=O)NCC(N)=O)CSCC(=O)N[CH]1(CC1=CC=C(O)C=C1)C(=O)CNCC2C=O.[H]CCC=CC=CC=C(O)N12(C(=O)O)C3=C145C=CC4=C352</t>
+        </is>
+      </c>
+      <c r="G1462" t="inlineStr"/>
+      <c r="H1462" t="inlineStr"/>
+      <c r="I1462" t="n">
+        <v>0.06615250025585755</v>
+      </c>
+      <c r="J1462" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1462" t="inlineStr"/>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="1" t="n">
+        <v>1461</v>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1893.png</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr"/>
+      <c r="D1463" t="inlineStr"/>
+      <c r="E1463" t="inlineStr"/>
+      <c r="F1463" t="inlineStr">
+        <is>
+          <t>CCO[C@@H]1C[C@@H](C(=O)NC2(C(=O)N(C)[C@H](C(=O)N(C)[C@@H](CC(=O)N(C)[C@@H](CC3CC3)C(=O)N[C@H](C(=O)N(C)CC(=O)N(C)[C@H]3C/C=C\CCNC3=O)[C@@H](C)CC)C(=O)N(C)C)C3CCCC3)CCC2)N(C(=O)[C@H](CCc2cc(F)c(C(F)(F)F)c(F)c2)NC(=O)CN(C)C(=O)[CH]CC2CCC(F)(F)CC2)C1 |^1:95|</t>
+        </is>
+      </c>
+      <c r="G1463" t="inlineStr"/>
+      <c r="H1463" t="inlineStr"/>
+      <c r="I1463" t="n">
+        <v>0.5172615730882704</v>
+      </c>
+      <c r="J1463" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1463" t="inlineStr"/>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="1" t="n">
+        <v>1462</v>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1897.png</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr"/>
+      <c r="D1464" t="inlineStr"/>
+      <c r="E1464" t="inlineStr"/>
+      <c r="F1464" t="inlineStr">
+        <is>
+          <t>CC.CCNCC(NC(=O)CO)C1C2C13N(C1=O=C1OC)C145C23C12C413C254C125C16C2789C2%10C7%11%12C7%13%14C%15%16%17C2%117(C1%10%128C63459)C%13%1512C%14%1634C%17156C2317C4523C6145C7216C3427C5134C6215C7326C4137C5214C6325C71368C179%10%11C423%12%13C61234%14C58%1271C925678C29%12%15C%16%17C2%18%19C%16952%20C%17%18%12635C%19%152%1074C%20%131%1158%14.CNCCC[CH]12C(NCCCNCCO3C4C(OCCOC(=O)(=O)COC(=O)(=O)CO5CC5COCCOCCC5O6CC6[CH]67O[CH]6(O)[CH]57O)C43)C3C1N32.COC1(O)C(O)[CH]2(O)OC12.O</t>
+        </is>
+      </c>
+      <c r="G1464" t="inlineStr"/>
+      <c r="H1464" t="inlineStr"/>
+      <c r="I1464" t="n">
+        <v>7.088525726909075e-77</v>
+      </c>
+      <c r="J1464" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1464" t="inlineStr"/>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="1" t="n">
+        <v>1463</v>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1901.png</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr"/>
+      <c r="D1465" t="inlineStr"/>
+      <c r="E1465" t="inlineStr"/>
+      <c r="F1465" t="inlineStr">
+        <is>
+          <t>[H]C(CC(C)C)N(C)C(=O)CCN(C)C(=O)CC123([H])C(=O)N456(C)C(C78=CC=CC7=C8)C4789([H])[H]C54%10%11CN47(C)(C%1084=O=C%119=O=4)C164([H])(C)(=O)C2N34C(=O)C(NC(=O)C([H])(CC(C)C)N(C)C(=O)CN(C)C)C(C)C.[H]C1(CC2=CC=CC=C2)C(=O)N2C1(=O)NC1([H])(C)C3456=O=C17(=O=3)(C24([H])C)N5123C45C89C%10%11C4%12C84C%108C1%10C%114C82N5%1067C9%123</t>
+        </is>
+      </c>
+      <c r="G1465" t="inlineStr"/>
+      <c r="H1465" t="inlineStr"/>
+      <c r="I1465" t="n">
+        <v>0.0001031273748019923</v>
+      </c>
+      <c r="J1465" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1465" t="inlineStr"/>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="1" t="n">
+        <v>1464</v>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1905.png</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr"/>
+      <c r="D1466" t="inlineStr"/>
+      <c r="E1466" t="inlineStr"/>
+      <c r="F1466" t="inlineStr">
+        <is>
+          <t>CC[C@H](C)[C@@H]([C@@H](C[C@H](OC)N1CCC[C@H]1[C@H](OC)[C@@H](C)C(=O)N[C@H](C)[C@@H](O)c1ccccc1)OC)N(C)C(=O)C(NC(=O)[C@H](C(C)C)N(C)C(=O)OCc1ccc(NC(=O)[C@H](CCCNC(N)=O)NC(=O)[C@@H](NC(=O)CCCCCNC(=O)/C=C/C(=O)OC)C(C)C)cc1)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1466" t="inlineStr"/>
+      <c r="H1466" t="inlineStr"/>
+      <c r="I1466" t="n">
+        <v>0.4690260463673327</v>
+      </c>
+      <c r="J1466" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1466" t="inlineStr"/>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="1" t="n">
+        <v>1465</v>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1909.png</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr"/>
+      <c r="D1467" t="inlineStr"/>
+      <c r="E1467" t="inlineStr"/>
+      <c r="F1467" t="inlineStr">
+        <is>
+          <t>C=CC[CH]NC(=O)C(CC(N)=O)NC(=O)C(CCC(=O)O)NC1(=O)=O=C(C(CC2=CC=C3C=CC=CC3=C2)NC(=O)C(CC2=CC=C(OCCN)C=C2)NC(=O)[CH]C(C)(C)NC(C)(C)C(NC(C)=O)C(=O)NC(CC(N)=O)C(=O)N[CH]C(=O)NC(CC2=CNC3=C2C=CC=C3C)C(=O)N[CH]CCCCNC(C)=O)NC1</t>
+        </is>
+      </c>
+      <c r="G1467" t="inlineStr"/>
+      <c r="H1467" t="inlineStr"/>
+      <c r="I1467" t="n">
+        <v>0.4880341735284454</v>
+      </c>
+      <c r="J1467" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1467" t="inlineStr"/>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="1" t="n">
+        <v>1466</v>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1913.png</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr"/>
+      <c r="D1468" t="inlineStr"/>
+      <c r="E1468" t="inlineStr"/>
+      <c r="F1468" t="inlineStr">
+        <is>
+          <t>CCNC=O.CCSSC1=C(OC(C)=CN(C(=O)CC2=CC=CC=C2)C(=O)C(CC(C)=O)N23C(=O)[CH]45CC6(=CC=CC=C62C43)C5C(=O)C(C(C)C)N2C(=O)C(N(C)C(=O)CC(CC3=CC=CC=C3)NC(=O)[CH]3(C(C)O)N4567C8C9C4%10CC[CH]4%11%12C95N8%10359C4638=O=C%1175(=O=3)[CH]%1289(NC(=O)CC(=O)CC(=O)CC)C(C)C)C2C(C)C)C=CC=C1.Cl</t>
+        </is>
+      </c>
+      <c r="G1468" t="inlineStr"/>
+      <c r="H1468" t="inlineStr"/>
+      <c r="I1468" t="n">
+        <v>0.003704713369039543</v>
+      </c>
+      <c r="J1468" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1468" t="inlineStr"/>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="1" t="n">
+        <v>1467</v>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1921.png</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr"/>
+      <c r="D1469" t="inlineStr"/>
+      <c r="E1469" t="inlineStr"/>
+      <c r="F1469" t="inlineStr">
+        <is>
+          <t>C=CCN(CC(=O)N(C)C1CC=CCCN(C(Cc2ccc(C)cc2)C(=O)N(C)CC(=O)NC(CCc2cc(F)c(C(F)(F)F)c(F)c2)C(=O)N2CC(OCC)CC2C(=O)NC2CC(C)(C)C2)C1=O)C1(=O)[CH]23C45C67CC4(C)(C)(C6)C72[CH]512NC14(=O)=O=C(C1CCC)N342.CN(C)C=O.CNC(=O)[CH]1(C2CCCC2)N2CN1(C)C2=O</t>
+        </is>
+      </c>
+      <c r="G1469" t="inlineStr"/>
+      <c r="H1469" t="inlineStr"/>
+      <c r="I1469" t="n">
+        <v>0.03642751959598936</v>
+      </c>
+      <c r="J1469" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1469" t="inlineStr"/>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="1" t="n">
+        <v>1468</v>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1925.png</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr"/>
+      <c r="D1470" t="inlineStr"/>
+      <c r="E1470" t="inlineStr"/>
+      <c r="F1470" t="inlineStr">
+        <is>
+          <t>O=C1CC[C@H](N2C(=O)c3ccc(N4CC(N5CCN(c6ccc(C(=O)Nc7n[nH]c8ccc(Cc9cc(F)cc(F)c9)cc78)c(NC7CCOCC7)c6)CC5)C4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1470" t="inlineStr"/>
+      <c r="H1470" t="inlineStr"/>
+      <c r="I1470" t="n">
+        <v>0.6460896015537653</v>
+      </c>
+      <c r="J1470" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1470" t="inlineStr"/>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="1" t="n">
+        <v>1469</v>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1937.png</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr"/>
+      <c r="D1471" t="inlineStr"/>
+      <c r="E1471" t="inlineStr"/>
+      <c r="F1471" t="inlineStr">
+        <is>
+          <t>[H]C(C)NC(=O)C([H])(CC=C)N(C)C(=O)C([H])(CC1=CC=CC=C1)N(C)C(=O)C1CC(=O)N(C)C([H])(C)C(=O)N(C)C([H])C(=O)NC([H])(C(C)O)C(=O)N(C)C(C)C(=O)N(C)C2(C(=O)N(C)C3(C(=O)NC([H])(C(C)CC)C(=O)NC(C(C)C)C(=O)N1)C1C4567CC1(C4)(C5)(C6)C37)C1C345CC1(C)(C3)(C4)C25</t>
+        </is>
+      </c>
+      <c r="G1471" t="inlineStr"/>
+      <c r="H1471" t="inlineStr"/>
+      <c r="I1471" t="n">
+        <v>0.1000776714660507</v>
+      </c>
+      <c r="J1471" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1471" t="inlineStr"/>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="1" t="n">
+        <v>1470</v>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1941.png</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr"/>
+      <c r="D1472" t="inlineStr"/>
+      <c r="E1472" t="inlineStr"/>
+      <c r="F1472" t="inlineStr">
+        <is>
+          <t>[H]C1(=O)N(C(CNC2=C(NC3=C(=O)C=CC=C3Cl)C(=O)N2)C(=O)N[CH]C(=O)N2CC(O)CC2C[CH]NC(=O)C(C=O)CC2=CN(C3=O=C3)C3=C2C=CC=C3)C2345([H])=O=C67(N2)N132C1CC2N16423CCCN752C31=O=C1NC(=O)(=O)C(C)N(C)C(=O)C(CC1=CC=C(O)C=C1Cl)NC(=O)NC1=C(NC2=C(Cl)C=CC=C2Cl)C(=O)C1=O</t>
+        </is>
+      </c>
+      <c r="G1472" t="inlineStr"/>
+      <c r="H1472" t="inlineStr"/>
+      <c r="I1472" t="n">
+        <v>0.0004856438186418708</v>
+      </c>
+      <c r="J1472" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1472" t="inlineStr"/>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="1" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1953.png</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr"/>
+      <c r="D1473" t="inlineStr"/>
+      <c r="E1473" t="inlineStr"/>
+      <c r="F1473" t="inlineStr">
+        <is>
+          <t>[H]C(C)CC(=O)N(C)C([H])(C)CC(=O)N(C)C([H])(CC(C)C)C(=O)NC([H])(CC1=CC=CC=C1)C(=O)N1CC23(C)CC(C)(C2)C3C1([H])C(=O)NC([H])(C(=O)N(C)C([H])(C(=O)NCC(=O)NC([H])([H])(CC1=CC=CC(Cl)=C1)C(=O)NC([H])(C(=O)N1CC(C)(C)C(C)C1[H])C(C)O)C(C)CC)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1473" t="inlineStr"/>
+      <c r="H1473" t="inlineStr"/>
+      <c r="I1473" t="n">
+        <v>0.04955571111345996</v>
+      </c>
+      <c r="J1473" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1473" t="inlineStr"/>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="1" t="n">
+        <v>1472</v>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1957.png</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr"/>
+      <c r="D1474" t="inlineStr"/>
+      <c r="E1474" t="inlineStr"/>
+      <c r="F1474" t="inlineStr">
+        <is>
+          <t>CC1=C(C(=O)Nc2ccc3[nH]nc(-c4ccnc(N5C[C@@H](C)N(CCOCCOCCN6CCN(c7ccc8c(c7)C(=O)N(C7CCC(=O)NC7=O)C8=O)CC6)[C@@H](C)C5)c4)c3c2)Cn2nnnc2N1C</t>
+        </is>
+      </c>
+      <c r="G1474" t="inlineStr"/>
+      <c r="H1474" t="inlineStr"/>
+      <c r="I1474" t="n">
+        <v>0.6340094408718936</v>
+      </c>
+      <c r="J1474" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1474" t="inlineStr"/>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="1" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1961.png</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr"/>
+      <c r="D1475" t="inlineStr"/>
+      <c r="E1475" t="inlineStr"/>
+      <c r="F1475" t="inlineStr">
+        <is>
+          <t>C1C23[SH]4[SH]2C143</t>
+        </is>
+      </c>
+      <c r="G1475" t="inlineStr"/>
+      <c r="H1475" t="inlineStr"/>
+      <c r="I1475" t="n">
+        <v>0.2440106387895831</v>
+      </c>
+      <c r="J1475" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1475" t="inlineStr"/>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="1" t="n">
+        <v>1474</v>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1969.png</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr"/>
+      <c r="D1476" t="inlineStr"/>
+      <c r="E1476" t="inlineStr"/>
+      <c r="F1476" t="inlineStr">
+        <is>
+          <t>CC1CC12C1C3C(C4=O5=C(CCNC6C[CH]7(NCCCCCC(N)=O)CC7NC(C(C)(C)CNC78=C9%10NC(NC%11[CH]N%11C%11[CH]C%11NC%11CC%11C(N)=O)C=79[CH]%10([CH]7(O)C9C(CCCNCCO%10CC%10COCCNCCO)O97)N8)[CH]6(O)(C(C)O)C6(NC7(=O)=O=C7)=O7=C89%10=C%11%12%13=C=78%14(=C=6=97(CNC(C)(=O)=O)=C=%10%11%14N%127)N%13)C=54)C312.CCCCCCCCCCCCNCC[CH]NCCCC</t>
+        </is>
+      </c>
+      <c r="G1476" t="inlineStr"/>
+      <c r="H1476" t="inlineStr"/>
+      <c r="I1476" t="n">
+        <v>1.491401048862611e-14</v>
+      </c>
+      <c r="J1476" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1476" t="inlineStr"/>
+    </row>
+    <row r="1477">
+      <c r="A1477" s="1" t="n">
+        <v>1475</v>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1973.png</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr"/>
+      <c r="D1477" t="inlineStr"/>
+      <c r="E1477" t="inlineStr"/>
+      <c r="F1477" t="inlineStr">
+        <is>
+          <t>[H]C(C)NC(=O)C([H])(CC(C)C)N(C)C(=O)C([H])(C(C)C)N(C)C(=O)NC(=O)CCCC1=CC=CC(C([H])(NC(=O)C([H])(CC(C)C)NC(=O)C2([H])CCCN2C(=O)C([H])(NC(=O)C([H])(CC2=CC=CC=C2)N([H])C2([H])C3C2([H])(N)C2C4=C5=C2367=C2C5=C35=C2=C2C38=C6=C25=C=847)C(C)O)C(=O)N2CCCCC2)=C1</t>
+        </is>
+      </c>
+      <c r="G1477" t="inlineStr"/>
+      <c r="H1477" t="inlineStr"/>
+      <c r="I1477" t="n">
+        <v>0.02181734378864976</v>
+      </c>
+      <c r="J1477" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1477" t="inlineStr"/>
+    </row>
+    <row r="1478">
+      <c r="A1478" s="1" t="n">
+        <v>1476</v>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1981.png</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr"/>
+      <c r="D1478" t="inlineStr"/>
+      <c r="E1478" t="inlineStr"/>
+      <c r="F1478" t="inlineStr">
+        <is>
+          <t>[H][C](CN)NC(=O)[C@@H]1Cc2ccccc2CNC(=O)CC(NC(C)(C)C)C(=O)N[C@@H](C)C(=O)N[C@@H](Cc2n[nH]c3ccccc23)C(=O)N[C@@H](Cc2c[nH]cn2)C(=O)N[C@@H](CC(C)C)C(=O)NCC(=O)N[C@@H](CCC(=O)O)C(=O)N[C@@H](CC(C)C)C(=O)N[C@@H](C(C)C)C(=O)N[C@@H](Cc2c[nH]c3ccccc23)C(=O)N1 |^1:1|</t>
+        </is>
+      </c>
+      <c r="G1478" t="inlineStr"/>
+      <c r="H1478" t="inlineStr"/>
+      <c r="I1478" t="n">
+        <v>0.7154973090377661</v>
+      </c>
+      <c r="J1478" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1478" t="inlineStr"/>
+    </row>
+    <row r="1479">
+      <c r="A1479" s="1" t="n">
+        <v>1477</v>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1989.png</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr"/>
+      <c r="D1479" t="inlineStr"/>
+      <c r="E1479" t="inlineStr"/>
+      <c r="F1479" t="inlineStr">
+        <is>
+          <t>CC(=O)NC=CC=CC1C2C(=O)(NC(CCCCN)C(=O)N[CH]C(C)O)[CH]13(CC1=CC=C(NC(=O)C4=CC=CC=C4)C=C1)NC1(=O)N23C2(=O)C3C(C4=CC=C(O)C=C4)[CH]12(CC1=CC=C(O)C=C1)NC12(=O)N3C3(=O)[CH]145NC(=O)C(N)CC16(=CC=C(Cl)C=C1)C1=CC(Cl)=CC=C1C6C(N)C(=O)N[CH]321C4S23[SH]4C[CH]C4[SH]2SC351</t>
+        </is>
+      </c>
+      <c r="G1479" t="inlineStr"/>
+      <c r="H1479" t="inlineStr"/>
+      <c r="I1479" t="n">
+        <v>0.000205292172080807</v>
+      </c>
+      <c r="J1479" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1479" t="inlineStr"/>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="1" t="n">
+        <v>1478</v>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_1997.png</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr"/>
+      <c r="D1480" t="inlineStr"/>
+      <c r="E1480" t="inlineStr"/>
+      <c r="F1480" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2Cc3cc(N4CC(N5CCN(c6ccc(C(=O)Nc7n[nH]c8ccc(Cc9cc(F)cc(F)c9)cc78)c(NC7CCOCC7)c6)CC5)C4)ccc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1480" t="inlineStr"/>
+      <c r="H1480" t="inlineStr"/>
+      <c r="I1480" t="n">
+        <v>0.5710725933418278</v>
+      </c>
+      <c r="J1480" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1480" t="inlineStr"/>
+    </row>
+    <row r="1481">
+      <c r="A1481" s="1" t="n">
+        <v>1479</v>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_2001.png</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr"/>
+      <c r="D1481" t="inlineStr"/>
+      <c r="E1481" t="inlineStr"/>
+      <c r="F1481" t="inlineStr">
+        <is>
+          <t>[H][C@]1(CC(C)C)C(=O)N[C@@]([H])([C@@H](C)O)C(=O)N(C)CC(=O)N(C)[C@@]([H])(CC(C)C)C(=O)N(C)[C@@]([H])(Cc2ccccc2)C(=O)N[C@]([H])(C(=O)N2CCCCC2)CC(=O)N(C)CCCC(=O)N(C)C(C)(C)C(=O)N1C</t>
+        </is>
+      </c>
+      <c r="G1481" t="inlineStr"/>
+      <c r="H1481" t="inlineStr"/>
+      <c r="I1481" t="n">
+        <v>0.8364696113370187</v>
+      </c>
+      <c r="J1481" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1481" t="inlineStr"/>
+    </row>
+    <row r="1482">
+      <c r="A1482" s="1" t="n">
+        <v>1480</v>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_2005.png</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr"/>
+      <c r="D1482" t="inlineStr"/>
+      <c r="E1482" t="inlineStr"/>
+      <c r="F1482" t="inlineStr">
+        <is>
+          <t>CCC(C)[CH]12NC(=O)[CH]3(CC4CCC4)C(=O)N1[CH]C2(=O)N(C)CC(=O)N(C)C1CC=CCCN(C1=O)C(Cc1ccc(C(F)(F)F)cc1)C(=O)N(C)CC(=O)NC(CCc1cc(F)c(C(F)(F)F)c(F)c1)C(=O)N1CC(F)(F)CC1C(=O)NCC(=O)N(C)C(C1CCCC1)C(=O)N(C)C(C(=O)N(C)C)CC(=O)N3C</t>
+        </is>
+      </c>
+      <c r="G1482" t="inlineStr"/>
+      <c r="H1482" t="inlineStr"/>
+      <c r="I1482" t="n">
+        <v>0.5318567478216998</v>
+      </c>
+      <c r="J1482" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1482" t="inlineStr"/>
+    </row>
+    <row r="1483">
+      <c r="A1483" s="1" t="n">
+        <v>1481</v>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_2025.png</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr"/>
+      <c r="D1483" t="inlineStr"/>
+      <c r="E1483" t="inlineStr"/>
+      <c r="F1483" t="inlineStr">
+        <is>
+          <t>NCCCC[CH]NC1(=O)[CH]23C4C5=CC=C(C=C5)NC5(=O)[CH]6(CCCN6)C(=O)(NC6=CC=C(C=C6)C[CH]4167NC(=O)[CH]14(CC8=CC=C(O)C=C8)NC(=O)C(CSCC[CH]8(C(=O)NC(CC9=CC=C(O)C=C9)C(N)=O)[CH]C(NC(=O)C(CCCCN)NC26=O)C(=O)N8)C(=O)N[CH]1(CC1=CC=C(O)C=C1)C4(=O)N37)[CH]51CCCN1</t>
+        </is>
+      </c>
+      <c r="G1483" t="inlineStr"/>
+      <c r="H1483" t="inlineStr"/>
+      <c r="I1483" t="n">
+        <v>0.01783000699168745</v>
+      </c>
+      <c r="J1483" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1483" t="inlineStr"/>
+    </row>
+    <row r="1484">
+      <c r="A1484" s="1" t="n">
+        <v>1482</v>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_2029.png</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr"/>
+      <c r="D1484" t="inlineStr"/>
+      <c r="E1484" t="inlineStr"/>
+      <c r="F1484" t="inlineStr">
+        <is>
+          <t>C=C123C(=O)C4(=C)(C1(=O)NC(=O)C(C)=O)N21C25=O=C1(=O)(N234)C512=C[SH]3C4567=N89%10=C4%11%12%13=CCC4%14NC(=O)C(C)C(=O)C(C)NC(=O)NC(=O)C(C(C)CC)NCC=CC=C(C(C)O)C=CC(=O)OC(C)C(NC(=O)C%15=CSC(=C(C(C)(O)C(C)O)NC(=O)C%16CSC(=N%16)C(=CC)NC(=O)C(C(C)O)NC%16=CSC4=N%16)C%15=O)C4=NC(=CS4)C%148=N%11C95%1248=N16C=%103%134=N278</t>
+        </is>
+      </c>
+      <c r="G1484" t="inlineStr"/>
+      <c r="H1484" t="inlineStr"/>
+      <c r="I1484" t="n">
+        <v>0.001432791994003032</v>
+      </c>
+      <c r="J1484" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1484" t="inlineStr"/>
+    </row>
+    <row r="1485">
+      <c r="A1485" s="1" t="n">
+        <v>1483</v>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_2041.png</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr"/>
+      <c r="D1485" t="inlineStr"/>
+      <c r="E1485" t="inlineStr"/>
+      <c r="F1485" t="inlineStr">
+        <is>
+          <t>C=CC(=CC=CC=CC(N)=O)CCN[CH](CC12=CC3=C45C6(=C31C=C2)C41=C56=C1)(NC(=O)CC=CC=COCC)C(=O)N[CH]C(=O)NC12C3C4C(C431)C21NC2(=O)C34C(NCC(CC5=CN=CC=C5)C(=O)N5CC(N)=O=C(N)(=O)C5)[CH]3(NC(N)=O)C(=O)N[CH]142CCCC.C[CH]NC(=O)CCCCCCCCCCC.O=CCOC1CO1CC1OC1CCC1(=O)CCN1</t>
+        </is>
+      </c>
+      <c r="G1485" t="inlineStr"/>
+      <c r="H1485" t="inlineStr"/>
+      <c r="I1485" t="n">
+        <v>7.749401201205212e-07</v>
+      </c>
+      <c r="J1485" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1485" t="inlineStr"/>
+    </row>
+    <row r="1486">
+      <c r="A1486" s="1" t="n">
+        <v>1484</v>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_2049.png</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr"/>
+      <c r="D1486" t="inlineStr"/>
+      <c r="E1486" t="inlineStr"/>
+      <c r="F1486" t="inlineStr">
+        <is>
+          <t>C.CC[CH]1(C)C(=O)NC2C3C4CC56CCNC7(C)C8N(C)C9(=O)C(CC(C)C)NC(=O)[CH]%10%11CC(C)CCN%10C(=O)C(C)NC(=O)[CH]%10%12%13%14%15%16%17CC%18%19%20%21(=O)=O=C%22%23%24N%18%25%26[CH]%18%27%28%29%30%31%32C[CH]%33%34%35%36%37%38C%10%39%40%41%42%43N%33%18%10%44C%12%27%18%33%45%46%47%48%49=O%12=C%27%50=O=%18%51=C=%12%13%18%52%53N%34%14%28%12[CH]%27%25%10%18%39%33%13%14%28C%35%15%29%10%18%25=O=%45=C=%51%36%16%30%13%15%27(=O=%52=%10=%46)N%40%18%37%31%47%14%10C%41%13%14(=O)([CH]%22%19%16%18CC3C4253C(CCNC8(C)C7N9(C)C(=O)C(CC(C)C)NC%11=O)C[CH]%23%13%202N(C)C1(=O)N%162(C)[CH]%243%14%21C6%18)N%42%38%17%32%15%48%28[CH]%50%26%12%44%53%43%25%10%27%49CC</t>
+        </is>
+      </c>
+      <c r="G1486" t="inlineStr"/>
+      <c r="H1486" t="inlineStr"/>
+      <c r="I1486" t="n">
+        <v>4.451274506172336e-15</v>
+      </c>
+      <c r="J1486" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1486" t="inlineStr"/>
+    </row>
+    <row r="1487">
+      <c r="A1487" s="1" t="n">
+        <v>1485</v>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_2053.png</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr"/>
+      <c r="D1487" t="inlineStr"/>
+      <c r="E1487" t="inlineStr"/>
+      <c r="F1487" t="inlineStr">
+        <is>
+          <t>Cc1noc(C)c1-c1ccn2c(NC3CCCCC3)c(CCc3ccc(NC(=O)CCOCCOCCOCCOCCOCCOCCNc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)cc3)nc2c1</t>
+        </is>
+      </c>
+      <c r="G1487" t="inlineStr"/>
+      <c r="H1487" t="inlineStr"/>
+      <c r="I1487" t="n">
+        <v>0.7911960693912992</v>
+      </c>
+      <c r="J1487" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1487" t="inlineStr"/>
+    </row>
+    <row r="1488">
+      <c r="A1488" s="1" t="n">
+        <v>1486</v>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_2057.png</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr"/>
+      <c r="D1488" t="inlineStr"/>
+      <c r="E1488" t="inlineStr"/>
+      <c r="F1488" t="inlineStr">
+        <is>
+          <t>CC=CC=CC=CCNC=O.CCCCCCCCCCCCCCC(=O)N[CH]C(N)=O.CCN(C1=CC(C2=CC=C(CN3CCN(C(=O)CCCCCCCCCCCCCCC(=O)N[CH]4567C89=O=C4%10%11%12=O=C5(=O)(N%10CC(C)O)[CH]8%1145C68%10%11%13%14%15CC746%16%17%18%19%20%21CC5(C6)(C8%16)(C%10%17)(C%11%18)(C%13%19)(C%14%20)(C%15%21)N9%12CC(C)O)CC3)C=C2)=CC(C(=O)NCC2=C(C)C=C(C)NC2=O)=C1C)C1CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1488" t="inlineStr"/>
+      <c r="H1488" t="inlineStr"/>
+      <c r="I1488" t="n">
+        <v>0.006994020647019841</v>
+      </c>
+      <c r="J1488" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1488" t="inlineStr"/>
+    </row>
+    <row r="1489">
+      <c r="A1489" s="1" t="n">
+        <v>1487</v>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_2065.png</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr"/>
+      <c r="D1489" t="inlineStr"/>
+      <c r="E1489" t="inlineStr"/>
+      <c r="F1489" t="inlineStr">
+        <is>
+          <t>CCCC1C2C3C4CNC5C6(=O)N[CH]789%10%11%12%13C%14%15CCNC(N)(=O)N(C(=N)N)CCC[CH]%14%16%17%18%19%20%21[CH]7%14%22C%1687(=O)[CH]%15%14%1798(CC(C)C)[CH]%18%109%14C%10=O=C%19%11%15%16(=O)N[CH]%20%12(CCCCNC(=N)N)(C(=O)CNCC(C(C)CC)[CH]C(CCCNC(=N)N)NC(=O)CCC%11C(=O)C6%12[CH]%11(CCCNC(=N)N)C(=O)N5%12C4CC[CH]13N2CCN)N79%15[CH]%168%21%13(N%10)C(C(C)C)C1(C)(C)C%22C(C)(C)C1%14</t>
+        </is>
+      </c>
+      <c r="G1489" t="inlineStr"/>
+      <c r="H1489" t="inlineStr"/>
+      <c r="I1489" t="n">
+        <v>1.048023608053137e-15</v>
+      </c>
+      <c r="J1489" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1489" t="inlineStr"/>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="1" t="n">
+        <v>1488</v>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_2077.png</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr"/>
+      <c r="D1490" t="inlineStr"/>
+      <c r="E1490" t="inlineStr"/>
+      <c r="F1490" t="inlineStr">
+        <is>
+          <t>[H][C](CC(C)C)C(=O)N[C@]([H])(C(=O)N(C)[C@@]([H])(C)C(=O)N(C)[C@@]([H])(Cc1ccccc1)C(=O)N[C@]([H])(C(=O)N(C)[C@@]([H])(C)C(=O)N(C)[C@@]([H])(CC(C)C)C(=O)N[C@@]([H])(Cc1cccc(C(=C)CCC(=O)N(C)[C@@]([H])(Cc2ccccc2)C(=O)NC)c1)C(=O)N1CCCCC1)[C@@H](C)O)[C@@H](C)CC |^1:1|</t>
+        </is>
+      </c>
+      <c r="G1490" t="inlineStr"/>
+      <c r="H1490" t="inlineStr"/>
+      <c r="I1490" t="n">
+        <v>0.6557802225476529</v>
+      </c>
+      <c r="J1490" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1490" t="inlineStr"/>
+    </row>
+    <row r="1491">
+      <c r="A1491" s="1" t="n">
+        <v>1489</v>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_2081.png</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr"/>
+      <c r="D1491" t="inlineStr"/>
+      <c r="E1491" t="inlineStr"/>
+      <c r="F1491" t="inlineStr">
+        <is>
+          <t>[CH]N1C2(=O)[CH]345C6SC37[CH]3(O)[CH]89N%10C%11(=O)[CH]%12(CCCCN)N%13C(=O)[CH]%14(CC=CC=CNC(=O)C(N)C(C)C)NC(=O)C(CC%15=CC=C(O)C=C%15)NC(=O)C(NC(=O)C(N)CC%15=CC=C(Cl)C=C%15)CSCC(O)[CH]3%15(NC%10%12(=O)[CH]%13%11(CCCCN)NC%14=O)C83(=O)N48C9%15(=O)N35[CH]6728C(=O)N[CH]1(CC1=CC=C(O)C=C1)C(N)=O</t>
+        </is>
+      </c>
+      <c r="G1491" t="inlineStr"/>
+      <c r="H1491" t="inlineStr"/>
+      <c r="I1491" t="n">
+        <v>0.002631046481622815</v>
+      </c>
+      <c r="J1491" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1491" t="inlineStr"/>
+    </row>
+    <row r="1492">
+      <c r="A1492" s="1" t="n">
+        <v>1490</v>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_2085.png</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr"/>
+      <c r="D1492" t="inlineStr"/>
+      <c r="E1492" t="inlineStr"/>
+      <c r="F1492" t="inlineStr">
+        <is>
+          <t>CC1CCCC1.CCCOC[CH]C(=O)NC(C(=O)N(C)CC(=O)N(C)C1CC=CCCN(C(Cc2ccc(C(F)(F)F)cc2)C(=O)N(C)CC(=O)NC(CCc2cc(F)c(C(F)(F)F)c(F)c2)C(=O)N2CC(OCC)CC2C(=O)NC2(C3CCCC3NC3(=O)[CH]45C6[CH]7(OCC)C8C(CCC)C74[CH]63N85)CCCC2)C1=O)C(C)CC</t>
+        </is>
+      </c>
+      <c r="G1492" t="inlineStr"/>
+      <c r="H1492" t="inlineStr"/>
+      <c r="I1492" t="n">
+        <v>0.06958470663519857</v>
+      </c>
+      <c r="J1492" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1492" t="inlineStr"/>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="1" t="n">
+        <v>1491</v>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_2089.png</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr"/>
+      <c r="D1493" t="inlineStr"/>
+      <c r="E1493" t="inlineStr"/>
+      <c r="F1493" t="inlineStr">
+        <is>
+          <t>[H][C](Cc1ccccc1)C(=O)N(C)[C@@]([H])(CC(C)C)C(=O)N[C@]([H])(C(=O)N(C)[C@@]([H])(C)C(=O)N(C)[C@@]([H])(Cc1ccccc1)C(=O)N[C@]([H])(CC(=O)N(C)C[C@@]([H])(C)C(=O)N(C)[C@@]([H])(CC(C)C)C(=O)N[C@@]([H])(C)C(=O)N[C@@]([H])(C(=O)NC)C(C)C)[C@@H](C)O)[C@@H](C)CC |^1:1|</t>
+        </is>
+      </c>
+      <c r="G1493" t="inlineStr"/>
+      <c r="H1493" t="inlineStr"/>
+      <c r="I1493" t="n">
+        <v>0.5991268824295676</v>
+      </c>
+      <c r="J1493" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1493" t="inlineStr"/>
+    </row>
+    <row r="1494">
+      <c r="A1494" s="1" t="n">
+        <v>1492</v>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_2/rb_2097.png</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr"/>
+      <c r="D1494" t="inlineStr"/>
+      <c r="E1494" t="inlineStr"/>
+      <c r="F1494" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1494" t="inlineStr"/>
+      <c r="H1494" t="inlineStr"/>
+      <c r="I1494" t="n">
+        <v>0.1064713002620402</v>
+      </c>
+      <c r="J1494" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1494" t="inlineStr"/>
+    </row>
+    <row r="1495">
+      <c r="A1495" s="1" t="n">
+        <v>1493</v>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1858.png</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr"/>
+      <c r="D1495" t="inlineStr"/>
+      <c r="E1495" t="inlineStr"/>
+      <c r="F1495" t="inlineStr">
+        <is>
+          <t>Cc1noc(C)c1-c1ccn2c(NCc3ccccc3)c(-c3ccc(N4CCN(C(=O)CCOCCOCCOCCOCCOCCOCCNc5cccc6c5C(=O)N(C5CCC(=O)NC5=O)C6=O)CC4)cc3)nc2c1</t>
+        </is>
+      </c>
+      <c r="G1495" t="inlineStr"/>
+      <c r="H1495" t="inlineStr"/>
+      <c r="I1495" t="n">
+        <v>0.8155652713564273</v>
+      </c>
+      <c r="J1495" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1495" t="inlineStr"/>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="1" t="n">
+        <v>1494</v>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1862.png</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr"/>
+      <c r="D1496" t="inlineStr"/>
+      <c r="E1496" t="inlineStr"/>
+      <c r="F1496" t="inlineStr">
+        <is>
+          <t>[H].[H]C(CC(=O)N(C)CC(=O)N(C)C([H])(CC(C)C)C(=O)NC(CC(C)C)C1(=O)N(C)C2([H])(CC(C)C)C3(=O)=O=C45N3C4([H])(C(C)O)[CH](C)(O)C([H])(CC([H])(NC=O)C(=O)N(C)C(CC3=CC=CC=C3)C(=O)NC5([H])CC3=CC=CC=C3)C(=O)C3([H])(CC(C)C)C(=O)N132C)NC(=O)C([H])CC(C)C</t>
+        </is>
+      </c>
+      <c r="G1496" t="inlineStr"/>
+      <c r="H1496" t="inlineStr"/>
+      <c r="I1496" t="n">
+        <v>0.005265600276719892</v>
+      </c>
+      <c r="J1496" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1496" t="inlineStr"/>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="1" t="n">
+        <v>1495</v>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1866.png</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr"/>
+      <c r="D1497" t="inlineStr"/>
+      <c r="E1497" t="inlineStr"/>
+      <c r="F1497" t="inlineStr">
+        <is>
+          <t>Cc1noc(C)c1-c1ccn2c(NC3CCCCC3)c(CCc3ccc(NC(=O)CCCCCCCCCCCNc4cccc5c4C(=O)N(C4CCC(=O)NC4=O)C5=O)cc3)nc2c1</t>
+        </is>
+      </c>
+      <c r="G1497" t="inlineStr"/>
+      <c r="H1497" t="inlineStr"/>
+      <c r="I1497" t="n">
+        <v>0.6495089705669175</v>
+      </c>
+      <c r="J1497" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1497" t="inlineStr"/>
+    </row>
+    <row r="1498">
+      <c r="A1498" s="1" t="n">
+        <v>1496</v>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1882.png</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr"/>
+      <c r="D1498" t="inlineStr"/>
+      <c r="E1498" t="inlineStr"/>
+      <c r="F1498" t="inlineStr">
+        <is>
+          <t>[H]C(NC(=O)C(C)N(C)C(=O)C1(C)CN1C(=O)C([H])(NC(=O)C([H])(C)N(C)C(=O)C([H])(NC(=O)C([H])(CC(C)C)N(C)C(=O)C1C2C3C4=C2(C=CC=C4)C13)C(C)O)C(C)C)C(=O)N1CC23=CC=CC(=C2)=C32=CC=CC=C2CC1([H])C(=O)N(C)C([H])(CC1=CC=CC=C1)C(=O)NC([H])(C)C(=O)N1CCCCC1</t>
+        </is>
+      </c>
+      <c r="G1498" t="inlineStr"/>
+      <c r="H1498" t="inlineStr"/>
+      <c r="I1498" t="n">
+        <v>0.01901748951301483</v>
+      </c>
+      <c r="J1498" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1498" t="inlineStr"/>
+    </row>
+    <row r="1499">
+      <c r="A1499" s="1" t="n">
+        <v>1497</v>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1890.png</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr"/>
+      <c r="D1499" t="inlineStr"/>
+      <c r="E1499" t="inlineStr"/>
+      <c r="F1499" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N2C(=O)c3ccc(CN4CC(CN5CCN(c6ccc(C(=O)Nc7n[nH]c8ccc(Cc9cc(F)cc(F)c9)cc78)c(NC7CCOCC7)c6)CC5)C4)cc3C2=O)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1499" t="inlineStr"/>
+      <c r="H1499" t="inlineStr"/>
+      <c r="I1499" t="n">
+        <v>0.8220354878439107</v>
+      </c>
+      <c r="J1499" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1499" t="inlineStr"/>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="1" t="n">
+        <v>1498</v>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1894.png</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr"/>
+      <c r="D1500" t="inlineStr"/>
+      <c r="E1500" t="inlineStr"/>
+      <c r="F1500" t="inlineStr">
+        <is>
+          <t>CC1=C(C(=O)Nc2ccc3[nH]nc(-c4ccnc(N5C[C@@H](C)N(CC6CCN(CC7CCN(c8ccc9c(c8)C(=O)N(C8CCC(=O)NC8=O)C9=O)CC7)CC6)[C@@H](C)C5)c4)c3c2)Cn2nnnc2N1C</t>
+        </is>
+      </c>
+      <c r="G1500" t="inlineStr"/>
+      <c r="H1500" t="inlineStr"/>
+      <c r="I1500" t="n">
+        <v>0.8133923515942885</v>
+      </c>
+      <c r="J1500" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1500" t="inlineStr"/>
+    </row>
+    <row r="1501">
+      <c r="A1501" s="1" t="n">
+        <v>1499</v>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1898.png</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr"/>
+      <c r="D1501" t="inlineStr"/>
+      <c r="E1501" t="inlineStr"/>
+      <c r="F1501" t="inlineStr">
+        <is>
+          <t>[H]CCC1=C2C=NN21CCCC[CH]OCCCNC(=O)C1CCN1C(=O)C(CCC(=O)O)C(=O)NC12(=O)N3C456=O=C37(=O=4)[CH]153NC(=O)[CH]14(CO)NC5(=O)C8(C)(C)C(C1[CH]4(CO)C1(=O)N49C(=O)C4[CH]267N132C(CCCC1=CC=C(O)C=C1)[CH]92CO)C5(C)(C)(C(=O)NCCN1CN23C1C1C2C13=O)C8(=O)N1CC12=O=C1C([CH]C)N12</t>
+        </is>
+      </c>
+      <c r="G1501" t="inlineStr"/>
+      <c r="H1501" t="inlineStr"/>
+      <c r="I1501" t="n">
+        <v>5.992442301627389e-08</v>
+      </c>
+      <c r="J1501" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1501" t="inlineStr"/>
+    </row>
+    <row r="1502">
+      <c r="A1502" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1902.png</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr"/>
+      <c r="D1502" t="inlineStr"/>
+      <c r="E1502" t="inlineStr"/>
+      <c r="F1502" t="inlineStr">
+        <is>
+          <t>CC1=NC=NC12=C134C=CC(CNC(=O)C5CC(O)CN5C(=O)C(NC(=O)CCOCCOCCOCCNC(=O)CN5CCN(C6=CC=C(C(=O)NC7=ONC8=C7C=C(CC7=CC(F)=CC(F)=C7)C=C8)C(NC7CCOCC7)=C6)CC5)C(C)(C)C)=CC1=C23C41=C(C)N=CS1</t>
+        </is>
+      </c>
+      <c r="G1502" t="inlineStr"/>
+      <c r="H1502" t="inlineStr"/>
+      <c r="I1502" t="n">
+        <v>0.2057706655142636</v>
+      </c>
+      <c r="J1502" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1502" t="inlineStr"/>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="1" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1906.png</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr"/>
+      <c r="D1503" t="inlineStr"/>
+      <c r="E1503" t="inlineStr"/>
+      <c r="F1503" t="inlineStr">
+        <is>
+          <t>CCOC[C@H]1C(=O)N[C@@H]([C@@H](C)CC)C(=O)N(C)CC(=O)N(C)[C@H]2C/C=C\CCN(C2=O)[C@@H](Cc2ccc(C(F)(F)F)cc2)C(=O)N(C)CC(=O)N[C@@H](CCc2cc(F)c(C(F)(F)F)c(F)c2)C(=O)N2C[C@H](OCC)C[C@H]2C(=O)NC2(CCC2)C(=O)N(C)[C@@H](C2CCCC2)C(=O)N(C)[C@H](C(=O)N(C)C)CC(=O)N1C</t>
+        </is>
+      </c>
+      <c r="G1503" t="inlineStr"/>
+      <c r="H1503" t="inlineStr"/>
+      <c r="I1503" t="n">
+        <v>0.8013113539110185</v>
+      </c>
+      <c r="J1503" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1503" t="inlineStr"/>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="1" t="n">
+        <v>1502</v>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1910.png</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr"/>
+      <c r="D1504" t="inlineStr"/>
+      <c r="E1504" t="inlineStr"/>
+      <c r="F1504" t="inlineStr">
+        <is>
+          <t>CCCCCC1C2C(CC3CC3(=O)NCCCC(=O)NCCOCCOCC(=O)CC3C4C(CCC5=O=C5N[CH]567C[CH]5(C6)C7(=O)C(CCC(=O)O)NC=O)C34)C12.CCCCCCCCC(=O)CNC1CC12C13=O=C21N3CCOC1CO1CC12=O=C34C15C231C23(C)=O=C5416(=O)(=O)O1C2C136.O=CNC=O.[CH]CN[CH]123N(C4CC4CCC4NC(C)N4)[CH]456C17=O=C24(N)[CH]75N36CCC</t>
+        </is>
+      </c>
+      <c r="G1504" t="inlineStr"/>
+      <c r="H1504" t="inlineStr"/>
+      <c r="I1504" t="n">
+        <v>4.125982588013963e-13</v>
+      </c>
+      <c r="J1504" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1504" t="inlineStr"/>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="1" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1914.png</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr"/>
+      <c r="D1505" t="inlineStr"/>
+      <c r="E1505" t="inlineStr"/>
+      <c r="F1505" t="inlineStr">
+        <is>
+          <t>CC=CCOC=CCl.CCNC(=O)C(CC(C)C)N(C)C(=O)[CH]12345CC(C)CC6789(C)CCN1%10C2(=O)[CH]%1031C64C(C7)(C8)C195.CC[CH]1234C(=O)C(C1C)N21C2(=O)C(N(C=O)CCC(C)CC(C5=O[CH]6(N5)C5=O=C67(=O)N[CH]689(C)CC(C6%10=O=C8(=O)N%10CCC(C)C)N579)NCCC5C(C)C5(=O)NC(=O)C(CC(C)C)N5CN(C)(C5)C3=O)C1(=O)N24</t>
+        </is>
+      </c>
+      <c r="G1505" t="inlineStr"/>
+      <c r="H1505" t="inlineStr"/>
+      <c r="I1505" t="n">
+        <v>0.000304785294331455</v>
+      </c>
+      <c r="J1505" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1505" t="inlineStr"/>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="1" t="n">
+        <v>1504</v>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1922.png</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr"/>
+      <c r="D1506" t="inlineStr"/>
+      <c r="E1506" t="inlineStr"/>
+      <c r="F1506" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1506" t="inlineStr"/>
+      <c r="H1506" t="inlineStr"/>
+      <c r="I1506" t="n">
+        <v>0.567797011982671</v>
+      </c>
+      <c r="J1506" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1506" t="inlineStr"/>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="1" t="n">
+        <v>1505</v>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1926.png</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr"/>
+      <c r="D1507" t="inlineStr"/>
+      <c r="E1507" t="inlineStr"/>
+      <c r="F1507" t="inlineStr">
+        <is>
+          <t>CCN(CCOC)C1CC(Oc2ccc3c(c2)C(=O)N(C2CCC(=O)NC2=O)C3=O)C1.Cc1cc(O[C@@H]2C(C)[C@@H](NC(=O)c3cnc(N4CCC5C(C4)CN5C4CC(Oc5ccc6c(c5)C(=O)N(C5CCC(=O)NC5=O)C6=O)C4)cn3)C2(C)C)ccc1C#N</t>
+        </is>
+      </c>
+      <c r="G1507" t="inlineStr"/>
+      <c r="H1507" t="inlineStr"/>
+      <c r="I1507" t="n">
+        <v>0.5892197881329633</v>
+      </c>
+      <c r="J1507" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1507" t="inlineStr"/>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="1" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1938.png</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr"/>
+      <c r="D1508" t="inlineStr"/>
+      <c r="E1508" t="inlineStr"/>
+      <c r="F1508" t="inlineStr">
+        <is>
+          <t>CCO[C@@H]1C[C@H]2C(=O)NC3(CCC3)C(=O)N(C)[C@@H](C3CCCC3)C(=O)N(C)[C@H](C(=O)N3CCOCC3)CC(=O)N(C)[C@@H](CC(C)C)C(=O)N[C@@H]([C@@H](C)CC)C(=O)N(C)CC(=O)N(C)[C@H]3CCCCCN(C3=O)[C@@H](Cc3ccc(F)c(C)c3)C(=O)N(C)CC(=O)N[C@@H](CCc3cc(F)c(C(F)(F)F)c(F)c3)C(=O)N2C1</t>
+        </is>
+      </c>
+      <c r="G1508" t="inlineStr"/>
+      <c r="H1508" t="inlineStr"/>
+      <c r="I1508" t="n">
+        <v>0.8171349860111984</v>
+      </c>
+      <c r="J1508" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1508" t="inlineStr"/>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="1" t="n">
+        <v>1507</v>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1946.png</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr"/>
+      <c r="D1509" t="inlineStr"/>
+      <c r="E1509" t="inlineStr"/>
+      <c r="F1509" t="inlineStr">
+        <is>
+          <t>[H]C(C)(C=O)NC(=O)C([H])(CC1=CC=CC=C1)N(C)C(=O)C1([H])CC(=O)N(C)CCCC(=O)N(C)C(C(C)C)C(=O)N(C)C2([H])(CC3=CC=CC=C3)O=C2N(C)C(CC2=CC=CC=C2)C(=O)NC(C)C(=O)N(C)C([H])(C)C(=O)N(C)C([H])(CC(C)C)C(=O)NC([H])(C(C)O)C(=O)N(C)C([H])(C)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1509" t="inlineStr"/>
+      <c r="H1509" t="inlineStr"/>
+      <c r="I1509" t="n">
+        <v>0.04999354600320171</v>
+      </c>
+      <c r="J1509" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1509" t="inlineStr"/>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="1" t="n">
+        <v>1508</v>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1950.png</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr"/>
+      <c r="D1510" t="inlineStr"/>
+      <c r="E1510" t="inlineStr"/>
+      <c r="F1510" t="inlineStr">
+        <is>
+          <t>[H]C1(C(=O)N(C)C([H])(CC2=CC=CC=C2)C(N)=O)CC(=O)N(C)C(C)C(=O)N2CC2([H])(C)C(=O)NC([H])(C)N2C34C2([H])(C(=O)N(C)C([H])(C)C(=O)N(C)C(CC2=CC=CC=C2)C(=O)NC([H])(C(C)O)C(=O)N2CC2(C)C(=O)N(C)C([H])(CC(C)C)C(=O)N(C)CC(=O)N1)C1C3256=C37=C1489=C=21C32=C34=C71=C=21C32=C58=C41=C=269</t>
+        </is>
+      </c>
+      <c r="G1510" t="inlineStr"/>
+      <c r="H1510" t="inlineStr"/>
+      <c r="I1510" t="n">
+        <v>0.03250562345068909</v>
+      </c>
+      <c r="J1510" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1510" t="inlineStr"/>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="1" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1954.png</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr"/>
+      <c r="D1511" t="inlineStr"/>
+      <c r="E1511" t="inlineStr"/>
+      <c r="F1511" t="inlineStr">
+        <is>
+          <t>[H]C12NC(=O)NC13([H])CS[CH]21CCCCC(=O)NCCOCCOCCOCC(=O)N2C(=O)(COCCOCCOCCNC(=O)CCCCC4SCC5([H])NC(=O)NC4513[H])N[CH]21CC2=CN3CCCCC4N5C6(=O)C7CCNC8(=CC=CC=C8)NCCC6C7(=O)N[CH]5(C(N)=O)(CCCCN56C=C(C1)(N=N5)N2=N36)C4(N)=O</t>
+        </is>
+      </c>
+      <c r="G1511" t="inlineStr"/>
+      <c r="H1511" t="inlineStr"/>
+      <c r="I1511" t="n">
+        <v>0.02031284601505914</v>
+      </c>
+      <c r="J1511" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1511" t="inlineStr"/>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="1" t="n">
+        <v>1510</v>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1958.png</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr"/>
+      <c r="D1512" t="inlineStr"/>
+      <c r="E1512" t="inlineStr"/>
+      <c r="F1512" t="inlineStr">
+        <is>
+          <t>CC[CH]1(C)C2N3C4(=O)C(COC)N5(C)CN6(C)C5(=O)CC(C(=O)N(C)C)N(C)C(=O)C(C5CCCC5)N(C)C(=O)CNC(=O)C5CCCCN5C(=O)C(CCc5cc(F)c(C(F)(F)F)c(F)c5)NC(=O)CN(C)C(=O)C(Cc5ccc(C(F)(F)F)cc5)NCCC=CC[CH]N(C)C(=O)CN(C)C2(=O)[CH]31NC(=O)[CH]46COC</t>
+        </is>
+      </c>
+      <c r="G1512" t="inlineStr"/>
+      <c r="H1512" t="inlineStr"/>
+      <c r="I1512" t="n">
+        <v>0.1223039705811827</v>
+      </c>
+      <c r="J1512" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1512" t="inlineStr"/>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="1" t="n">
+        <v>1511</v>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1966.png</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr"/>
+      <c r="D1513" t="inlineStr"/>
+      <c r="E1513" t="inlineStr"/>
+      <c r="F1513" t="inlineStr">
+        <is>
+          <t>O=C1CCC(N234C(=O)C56(=C789C=C(NCCOCCOCCC(=O)N%10CCC(NC%11=CC=C%11)CC%10)C7=C5(C82=O)C963=O)C4(=O)C2=CC=C(NCCOCCOCCC(=O)N3CCC(NC4=NC(C(=O)NC5=C67N=C(N8CCCC8C8=CC(F)=CC=C8F)C=CN6N=C57)=CC=C4)CC3)C=C2)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1513" t="inlineStr"/>
+      <c r="H1513" t="inlineStr"/>
+      <c r="I1513" t="n">
+        <v>0.1622848190618911</v>
+      </c>
+      <c r="J1513" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1513" t="inlineStr"/>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="1" t="n">
+        <v>1512</v>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1970.png</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr"/>
+      <c r="D1514" t="inlineStr"/>
+      <c r="E1514" t="inlineStr"/>
+      <c r="F1514" t="inlineStr">
+        <is>
+          <t>O.[CH]NC[C@@H]1CNC(=O)NCCCCCCNC(=O)N[C@@H](Cc2ccc(O)cc2)NC(=O)CSC[C@@H](C(=O)NCC(N)=O)NC(=O)[C@H](CC(C)C)NC(=O)[C@H](CCCC)N(C)C(=O)[C@H](CCC)NC(=O)[CH]NC(=O)[CH]CCN[C@@H](Cc2ccc(O)cc2)C(=O)N(C)[C@@H](C)C(=O)N[C@@H](CC(N)=O)C(=O)N(CC)[C](F)C(=O)N1 |^1:70,74,106,^2:1|</t>
+        </is>
+      </c>
+      <c r="G1514" t="inlineStr"/>
+      <c r="H1514" t="inlineStr"/>
+      <c r="I1514" t="n">
+        <v>0.0174418953107638</v>
+      </c>
+      <c r="J1514" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1514" t="inlineStr"/>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="1" t="n">
+        <v>1513</v>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1974.png</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr"/>
+      <c r="D1515" t="inlineStr"/>
+      <c r="E1515" t="inlineStr"/>
+      <c r="F1515" t="inlineStr">
+        <is>
+          <t>CC1=C(C2=CC=C(CNC(=O)C3CC(O)CN3C(=O)[CH]3(NC(=O)CCCCCCCCC(=O)N4CCN(C5=CC=C(C(=O)NC6=NNC7=C6C=C(CC6=CC(F)=CC(F)=C6)C=C7)C(NC6CCOCC6)=C5)CC4)C456CC3(C)(C4)(C5)C6)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1515" t="inlineStr"/>
+      <c r="H1515" t="inlineStr"/>
+      <c r="I1515" t="n">
+        <v>0.4184902578572794</v>
+      </c>
+      <c r="J1515" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1515" t="inlineStr"/>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="1" t="n">
+        <v>1514</v>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1982.png</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr"/>
+      <c r="D1516" t="inlineStr"/>
+      <c r="E1516" t="inlineStr"/>
+      <c r="F1516" t="inlineStr">
+        <is>
+          <t>C=C12(N)=C=C3(N)N1C1CCC(NC(=O)C(C)[CH]CCCNC)C(=O)NC(NC(CCN)C(=O)NC(CC(C)C)C(CCCN)NC(=O)CC(C)C[CH]C(CCN)C(CCCNC(=N)N)C(CC(C)C)C(=O)NC(NN[Si](C)(CCC(C)C)C(CC(C)C)NC(=O)C(CC(C)C)NCC(C)C4NC4(N)=O)C(C)C(C)=O)CCCN132</t>
+        </is>
+      </c>
+      <c r="G1516" t="inlineStr"/>
+      <c r="H1516" t="inlineStr"/>
+      <c r="I1516" t="n">
+        <v>0.0001043920619104923</v>
+      </c>
+      <c r="J1516" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1516" t="inlineStr"/>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="1" t="n">
+        <v>1515</v>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1986.png</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr"/>
+      <c r="D1517" t="inlineStr"/>
+      <c r="E1517" t="inlineStr"/>
+      <c r="F1517" t="inlineStr">
+        <is>
+          <t>C=CC=C1C2=C1(NC=CCN1(C3(=O)=C45NC4(CC(=O)CCCCC(=O)CCC(=O)N4CC6=CC=CC=C6C#CC6=C4C=CC=C6)=CN53)C3C(NC(C(C)C)C4(=O)N5[CH]67C(CCNC(N)=O)[CH]589NC5(=O=C68(=O)=O=C579NCCC(N)=O)[CH]45(C(=O)NC(=O)C(C)C)C4C67CC6C475)C31)=CC=C2.CCNCCNCCCNC=CCN1C(=O)C=CC=C1C=NC</t>
+        </is>
+      </c>
+      <c r="G1517" t="inlineStr"/>
+      <c r="H1517" t="inlineStr"/>
+      <c r="I1517" t="n">
+        <v>6.052174549229362e-07</v>
+      </c>
+      <c r="J1517" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1517" t="inlineStr"/>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="1" t="n">
+        <v>1516</v>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_1990.png</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr"/>
+      <c r="D1518" t="inlineStr"/>
+      <c r="E1518" t="inlineStr"/>
+      <c r="F1518" t="inlineStr">
+        <is>
+          <t>CC(CCC1CC1CCC12C3C14C15C6(C3241)C512C634C156C2317C4523C6145C7216C3427C5134C6215C7326C4137C5214C6325C7136C4217C5324C6135C7216C4327C5134C6215C7326C4137C5214C6325C7136C4217C5324C6135C7216C4327C5134C6215C7326C4137C5214C6325C7136C4217C5324C6135C7216C4327C5134C6215C7326C4137C5214C6325C7136C4217C5324C6135C7216C4327C5134C6215C7326C4137C5214C6325C7136C4217C5324C6135C7216C4327C5134C6215C7326C4137C5214C6325C7136C4217C5324C6135C7216C4327C5134C6215C7326C4137C5214C6325C7136C4217C5324C6135C7216C4327C5134C6215C7326C4137C5214C6325C7136C4217C5324C6135C7216C4327C5134C6215C7326C4137C5214C6325C7136C4217C5324C6135C7216C4327C5134C6215C7326C4137C5214C6325C7136C4217C5324C6135C7216C4327C5134C6215C2689%10C%11%12%13C%14%15C%112%16%17C%14%1262%11C%15%13%1686C73129C%1745%116%10)C1CC1C</t>
+        </is>
+      </c>
+      <c r="G1518" t="inlineStr"/>
+      <c r="H1518" t="inlineStr"/>
+      <c r="I1518" t="n">
+        <v>8.447101855156244e-163</v>
+      </c>
+      <c r="J1518" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1518" t="inlineStr"/>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="1" t="n">
+        <v>1517</v>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_2006.png</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr"/>
+      <c r="D1519" t="inlineStr"/>
+      <c r="E1519" t="inlineStr"/>
+      <c r="F1519" t="inlineStr">
+        <is>
+          <t>CCOC[C@H]1C(=O)N[C@@H]([C@@H](C)CC)C(=O)N(C)CC(=O)N(C)[C@H]2C/C=C\CCN(C2=O)[C@@H](Cc2ccc(C(F)(F)F)cc2)C(=O)N(C)CC(=O)N[C@@H](CCc2cc(F)c(C(F)(F)F)c(F)c2)C(=O)N2C[C@H](OCC)C[C@H]2C(=O)NC2(CC(C)(C)C2)C(=O)N(C)[C@@H](CC(C)(C)C)C(=O)N(C)[C@H](C(=O)N(C)C)CC(=O)N1C</t>
+        </is>
+      </c>
+      <c r="G1519" t="inlineStr"/>
+      <c r="H1519" t="inlineStr"/>
+      <c r="I1519" t="n">
+        <v>0.8332941908629119</v>
+      </c>
+      <c r="J1519" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1519" t="inlineStr"/>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="1" t="n">
+        <v>1518</v>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_2018.png</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr"/>
+      <c r="D1520" t="inlineStr"/>
+      <c r="E1520" t="inlineStr"/>
+      <c r="F1520" t="inlineStr">
+        <is>
+          <t>CC(C)[CH]1234(NC5C6CCC[CH]NC789(=O)(=O)=O=[CH]%10(O)(C7%11C7C(C%12=O=C(=O)(C(CCCN)NC(=O)C%13C(CC(N)=O)[CH]%14%15(=O)CN%14C(N)(=O)(=O)N%13%15)N%12)N%11C7%108)C97NC[CH]7(CC(=O)O)C7=O=C6(=O)(N7)[CH]56CCC6)C(=O)(CCCCN)[CH]56N7C18=O=C2(=O)N[CH]78(C(=O)CCCCN)(C53(C)C)C64(C)C.[CH]N1C2=O=C(NC3=O=C3N)[CH]21NC(C)=O</t>
+        </is>
+      </c>
+      <c r="G1520" t="inlineStr"/>
+      <c r="H1520" t="inlineStr"/>
+      <c r="I1520" t="n">
+        <v>1.448904339609522e-08</v>
+      </c>
+      <c r="J1520" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1520" t="inlineStr"/>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="1" t="n">
+        <v>1519</v>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_2030.png</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr"/>
+      <c r="D1521" t="inlineStr"/>
+      <c r="E1521" t="inlineStr"/>
+      <c r="F1521" t="inlineStr">
+        <is>
+          <t>C.CC(C)[CH]NC(=O)C(CO)NC(=O)C(CC1=CC=CC=C1)N(C)C(=O)C(CCCNC(=N)N)NC(=O)C(CC1=CC=CC=C1)NCCSCC(C(=O)NCC(N)=O)C(=O)[CH]12C(C3=CC=CC=C3)C1C2(=O)C(CC(N)=O)NC(=O)C1CC2=C(C=CC=C2)N1C(=O)C(CC(=O)O)NC(=O)[CH]CC(=O)[CH]CCCCN.O</t>
+        </is>
+      </c>
+      <c r="G1521" t="inlineStr"/>
+      <c r="H1521" t="inlineStr"/>
+      <c r="I1521" t="n">
+        <v>0.177828766101118</v>
+      </c>
+      <c r="J1521" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1521" t="inlineStr"/>
+    </row>
+    <row r="1522">
+      <c r="A1522" s="1" t="n">
+        <v>1520</v>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_2038.png</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr"/>
+      <c r="D1522" t="inlineStr"/>
+      <c r="E1522" t="inlineStr"/>
+      <c r="F1522" t="inlineStr">
+        <is>
+          <t>CCCCC1C2(=O)N3C4C(C5=CC6=C(C=CC=C6)C=C5)[CH]356(CC3=CC7=C(C=CC=C7)C=C3)NC(=O)[CH]2(CCCC)N1(C)C(=O)COCC=CC(CCC1=CC(OC)=C(OC)C=C1O)OC(=O)C1CCCCN1C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)CNC(=O)[CH]12(COC(C)(C)C)C(OC)C3N17(C)C5(=O)N32(C)C476=O</t>
+        </is>
+      </c>
+      <c r="G1522" t="inlineStr"/>
+      <c r="H1522" t="inlineStr"/>
+      <c r="I1522" t="n">
+        <v>0.06915562858111719</v>
+      </c>
+      <c r="J1522" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1522" t="inlineStr"/>
+    </row>
+    <row r="1523">
+      <c r="A1523" s="1" t="n">
+        <v>1521</v>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_2042.png</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr"/>
+      <c r="D1523" t="inlineStr"/>
+      <c r="E1523" t="inlineStr"/>
+      <c r="F1523" t="inlineStr">
+        <is>
+          <t>[H][C@]1(C)CC(=O)N(C)[C@@]([H])(C)C(=O)N(C)[C@@]([H])(Cc2ccccc2)C(=O)N(C)CC(=O)N(C)[C@@]([H])(CC(C)C)C(=O)N[C@@]([H])([C@@H](C)O)C(=O)N(C)[C@@]([H])(C)C(=O)N(C)[C@@]([H])(CC(C)C)C(=O)N(C)[C@@]([H])([C@@H](C)CC)C(=O)N[C@@]([H])(COC(C)(C)C)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1523" t="inlineStr"/>
+      <c r="H1523" t="inlineStr"/>
+      <c r="I1523" t="n">
+        <v>0.780534012038993</v>
+      </c>
+      <c r="J1523" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1523" t="inlineStr"/>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="1" t="n">
+        <v>1522</v>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_2054.png</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr"/>
+      <c r="D1524" t="inlineStr"/>
+      <c r="E1524" t="inlineStr"/>
+      <c r="F1524" t="inlineStr">
+        <is>
+          <t>C=CC1C2C(C3=CC=CC=C3)[CH]12NC(=O)CSC[CH]NC(=O)C1CCCN1C(=O)C(C)NC(=O)C(CCC(=O)O)NC(C)N(C)C(=O)C1CC=CC=C(C2=CC=CC=C2)C(=O)N(C)C(CC)C(=O)NC(C(C)O)C(=O)NC(C(C)O)C(=O)NC(CC2=CC=C(C3=CC=CC=C3)C=C2)C(=O)N(C)[CH]C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1524" t="inlineStr"/>
+      <c r="H1524" t="inlineStr"/>
+      <c r="I1524" t="n">
+        <v>0.2695967517582538</v>
+      </c>
+      <c r="J1524" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1524" t="inlineStr"/>
+    </row>
+    <row r="1525">
+      <c r="A1525" s="1" t="n">
+        <v>1523</v>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_2062.png</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr"/>
+      <c r="D1525" t="inlineStr"/>
+      <c r="E1525" t="inlineStr"/>
+      <c r="F1525" t="inlineStr">
+        <is>
+          <t>[H]C1NC(=O)C(C)(C)N(C)C(=O)[C@@]([H])(C)N(C)C(=O)C[C@]([H])(C)NC(=O)[C@]([H])(CC(C)C)NC(=O)[C@]([H])(C)N(C)C(=O)[C@]([H])([C@@H](C)O)NC(=O)[C@]([H])(Cc2ccccc2)N(C)C(=O)CNC(=O)[C@]([H])([C@@H](C)CC)N(C)C(=O)[C@]([H])(C(C)C)NC(=O)[C@]([H])(CC(C)C)N(C)C1=O.[H][C](C)C |^1:96|</t>
+        </is>
+      </c>
+      <c r="G1525" t="inlineStr"/>
+      <c r="H1525" t="inlineStr"/>
+      <c r="I1525" t="n">
+        <v>0.6546039900469435</v>
+      </c>
+      <c r="J1525" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1525" t="inlineStr"/>
+    </row>
+    <row r="1526">
+      <c r="A1526" s="1" t="n">
+        <v>1524</v>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_2070.png</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr"/>
+      <c r="D1526" t="inlineStr"/>
+      <c r="E1526" t="inlineStr"/>
+      <c r="F1526" t="inlineStr">
+        <is>
+          <t>CC1=C(C2(=CC=CCNC(=O)C3CC(O)CN3C(=O)C(NC(=O)CCOCCOCCOCCOCCC(=O)N34CCN56CC3C(C4)N3C547=C5=C3648=CC=C3C4=O6=C9%10(=O)N%11C%12%13%14%15=C%16C=C(CC%17=CC(F)=CC(F)=C%17)C=CC%16%17=C%12N%17N%13N%12C5%13=C95(C(NC9CCOCC9)=C=%13%12758)C=63%11(=O)(N%14)N4%10%15)C(C)(C)C)C=C2)SC=N1</t>
+        </is>
+      </c>
+      <c r="G1526" t="inlineStr"/>
+      <c r="H1526" t="inlineStr"/>
+      <c r="I1526" t="n">
+        <v>5.583268972563762e-05</v>
+      </c>
+      <c r="J1526" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1526" t="inlineStr"/>
+    </row>
+    <row r="1527">
+      <c r="A1527" s="1" t="n">
+        <v>1525</v>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_2074.png</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr"/>
+      <c r="D1527" t="inlineStr"/>
+      <c r="E1527" t="inlineStr"/>
+      <c r="F1527" t="inlineStr">
+        <is>
+          <t>[H]C1C(=O)N(C)C2([H])(CC3=CC=CC=C3)C3(=O)CC2(=O)C([H])(N3)C(=O)N(C)C([H])(CC(C)C)C(=O)N(C)C([H])(C)C(=O)N2(C)CC2([H])C(=O)NC([H])(C(C)O)C(=O)NC([H])(C(=O)N2CCCCC2)CC(=O)NC([H])(C(C)C)C(=O)N(C)C([H])(C)C(=O)N(C)(C([H])CC(C)C)C(=O)C1C(C)C</t>
+        </is>
+      </c>
+      <c r="G1527" t="inlineStr"/>
+      <c r="H1527" t="inlineStr"/>
+      <c r="I1527" t="n">
+        <v>0.04915084326009767</v>
+      </c>
+      <c r="J1527" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1527" t="inlineStr"/>
+    </row>
+    <row r="1528">
+      <c r="A1528" s="1" t="n">
+        <v>1526</v>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_2078.png</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr"/>
+      <c r="D1528" t="inlineStr"/>
+      <c r="E1528" t="inlineStr"/>
+      <c r="F1528" t="inlineStr">
+        <is>
+          <t>CC(C)=O.NC(CCC(=O)O)C(=O)N1CCCC1C(=O)NC1CC2=CC34(=C2C=CC3=C4)NC1=O.[CH]NC1(=O)C2C(C3=CC=C(O)C=C3)[CH]13(C=O)(CC1=CC=C(O)C=C1)NC(=O)C(C)NC(=O)C145(CC)(C(=O)N1[CH]41CCCC15=O)C(=O)(C(CC)C(=O)NCC(=O)NC(=O)C[CH]C(=O)NC(=O)[CH]C)C(CO)C(=O)N23</t>
+        </is>
+      </c>
+      <c r="G1528" t="inlineStr"/>
+      <c r="H1528" t="inlineStr"/>
+      <c r="I1528" t="n">
+        <v>8.651149265988899e-06</v>
+      </c>
+      <c r="J1528" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1528" t="inlineStr"/>
+    </row>
+    <row r="1529">
+      <c r="A1529" s="1" t="n">
+        <v>1527</v>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_2086.png</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr"/>
+      <c r="D1529" t="inlineStr"/>
+      <c r="E1529" t="inlineStr"/>
+      <c r="F1529" t="inlineStr">
+        <is>
+          <t>CC[CH]NC1(=O)C2C3(=O)NC(CC)C4N567CN48(C5)C6CC84C5689=O=C4%10(=O=5)(C76)N84CN9%10(C4)C(CC(C)C)C(=O)NC(C(C)C)C(=O)N(C)C(CC(C)C)C(=O)NC(C)C(=O)NC(C)C(=O)N(C)C(CC(C)C)C(=O)N(C)C(CC(C)C)C(=O)N4C(=O)([CH]CCC)N5[CH]67C(C)[CH]458(CC)C64(=O)N25(C)CN426C4(=O=C47528=O)[CH]136</t>
+        </is>
+      </c>
+      <c r="G1529" t="inlineStr"/>
+      <c r="H1529" t="inlineStr"/>
+      <c r="I1529" t="n">
+        <v>3.102348748325114e-05</v>
+      </c>
+      <c r="J1529" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1529" t="inlineStr"/>
+    </row>
+    <row r="1530">
+      <c r="A1530" s="1" t="n">
+        <v>1528</v>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_2090.png</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr"/>
+      <c r="D1530" t="inlineStr"/>
+      <c r="E1530" t="inlineStr"/>
+      <c r="F1530" t="inlineStr">
+        <is>
+          <t>[H][C@]1(C(C)C)NC(=O)C[C@@]([H])(C(=O)N2CCCCC2)NC(=O)[C@]([H])(CC(C)C)N(C)C(=O)[C@]([H])(Cc2ccccc2)N(C)C(=O)C(C)(C)N(C)C(=O)[C@]([H])([C@@H](C)O)NC(=O)[C@]([H])(Cc2ccccc2)N(C)C(=O)[C@]([H])(CC(C)C)NC(=O)[C@]([H])(CC(C)C)N(C)C1=O</t>
+        </is>
+      </c>
+      <c r="G1530" t="inlineStr"/>
+      <c r="H1530" t="inlineStr"/>
+      <c r="I1530" t="n">
+        <v>0.8050313157315842</v>
+      </c>
+      <c r="J1530" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1530" t="inlineStr"/>
+    </row>
+    <row r="1531">
+      <c r="A1531" s="1" t="n">
+        <v>1529</v>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_2094.png</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr"/>
+      <c r="D1531" t="inlineStr"/>
+      <c r="E1531" t="inlineStr"/>
+      <c r="F1531" t="inlineStr">
+        <is>
+          <t>CCCC(NC(=O)CN1CCC(NC(=O)C(CCCN2N=NC(C[N+](C)(C)CO)=NN2)NC(=O)CNCCN(CCN(CC)CC(=O)O)CC(=O)O)CC1)C(=O)NC(CCCNC(=N)N)C(=O)N1CCCCN2C(=O)C3CC(=O)C[CH]32C(=O)NCC(=O)NC(CC2CCCCC2)C(=O)NC(CO)C(=O)N2CCCC2C(=O)NC(CC(C)C)C1</t>
+        </is>
+      </c>
+      <c r="G1531" t="inlineStr"/>
+      <c r="H1531" t="inlineStr"/>
+      <c r="I1531" t="n">
+        <v>0.10613582250386</v>
+      </c>
+      <c r="J1531" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1531" t="inlineStr"/>
+    </row>
+    <row r="1532">
+      <c r="A1532" s="1" t="n">
+        <v>1530</v>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T170847_3/rb_2098.png</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr"/>
+      <c r="D1532" t="inlineStr"/>
+      <c r="E1532" t="inlineStr"/>
+      <c r="F1532" t="inlineStr">
+        <is>
+          <t>C=CC1=C(COCC)C[CH]23C(CC(=O)[CH]COC(=O)C(N)NC4[CH][CH]4)C2(O)C3C23=O=C=12(C=CC1C=CC=C1C12=C=C45=C67(=C=14O26)=O12=C(C=CC=C4C=CC=CC4)NC=1468=O=C=219%10(=O=42%11=C4%12(C(=O)N4C4(=O)[CH]N4%13C4C%13C4(=O)(=O)O)N14C=21(N9)C=%11%12%10[CH]54176)C8NCC=CC=CC)N3.CC123=C(C1)C2=CC=CN3.C[CH]12C(O)C1C2(=O)NC(=O)CC[CH]NC=O</t>
+        </is>
+      </c>
+      <c r="G1532" t="inlineStr"/>
+      <c r="H1532" t="inlineStr"/>
+      <c r="I1532" t="n">
+        <v>1.669590595137312e-15</v>
+      </c>
+      <c r="J1532" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1532" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1532"/>
+  <dimension ref="A1:K1729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44879,6 +44879,5719 @@
       </c>
       <c r="K1532" t="inlineStr"/>
     </row>
+    <row r="1533">
+      <c r="A1533" s="1" t="n">
+        <v>1531</v>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2101.png</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr"/>
+      <c r="D1533" t="inlineStr"/>
+      <c r="E1533" t="inlineStr"/>
+      <c r="F1533" t="inlineStr">
+        <is>
+          <t>C[CH]12C3NC(=O)C(CCCCN)NC(=O)C(CC4=CC=C(CN)C=C4)NC(=O)C(CC4=CC=C(O)C=C4)NC(=O)C(NC(=O)C(N)CC4=CC=C(Cl)C=C4)CSCC1[CH]1(C(=O)NC(CC4=CC=C(O)C=C4)C(N)=O)(CSC21)NC3=O</t>
+        </is>
+      </c>
+      <c r="G1533" t="inlineStr"/>
+      <c r="H1533" t="inlineStr"/>
+      <c r="I1533" t="n">
+        <v>0.4442959055897008</v>
+      </c>
+      <c r="J1533" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1533" t="inlineStr"/>
+    </row>
+    <row r="1534">
+      <c r="A1534" s="1" t="n">
+        <v>1532</v>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2105.png</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr"/>
+      <c r="D1534" t="inlineStr"/>
+      <c r="E1534" t="inlineStr"/>
+      <c r="F1534" t="inlineStr">
+        <is>
+          <t>NCCCC[CH]NC1(=O)[CH]23CC4=CC=C(C=C4)NC4(=O)[CH](N)(CC(=O)O)C(=O)(NC5=CC=C(C=C5)C[CH]15NC1(=O)[CH]6(CC7=CC=C(O)C=C7)NC(=O)C(CSSC[CH]7(C(=O)N[CH]CC8=CC=C(O)C=C8)CC(O)C(NC(=O)C(CCCCN)NC25=O)C(=O)N7)C(=O)N[CH]1(CC1=CC=C(O)C=C1)C6(=O)N3)[CH]4(N)CC(=O)O</t>
+        </is>
+      </c>
+      <c r="G1534" t="inlineStr"/>
+      <c r="H1534" t="inlineStr"/>
+      <c r="I1534" t="n">
+        <v>0.008671474593817114</v>
+      </c>
+      <c r="J1534" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1534" t="inlineStr"/>
+    </row>
+    <row r="1535">
+      <c r="A1535" s="1" t="n">
+        <v>1533</v>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2109.png</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr"/>
+      <c r="D1535" t="inlineStr"/>
+      <c r="E1535" t="inlineStr"/>
+      <c r="F1535" t="inlineStr">
+        <is>
+          <t>CC[CH]NC(=O)C(C)NC(=O)[CH]C(=O)NC(=O)C(C)NCC1(C)C(CCCNC(C)=O)NC(=O)C2(=O)C3(=O)N[CH]24C(CCNC(=N)N)[CH]25(CNC(CCC)C2(=O)N[CH]34C(=O)N[CH]2(CC(C)C2)C(CC(C)=O)CC(=O)N5)C(=O)NC(=O)[CH]1(NC(=O)NC(C)CCCCNC(=O)C(C)NC(CC1=CC=CC=C1)C(N)=O)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1535" t="inlineStr"/>
+      <c r="H1535" t="inlineStr"/>
+      <c r="I1535" t="n">
+        <v>2.517149781251266e-06</v>
+      </c>
+      <c r="J1535" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1535" t="inlineStr"/>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="1" t="n">
+        <v>1534</v>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2117.png</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr"/>
+      <c r="D1536" t="inlineStr"/>
+      <c r="E1536" t="inlineStr"/>
+      <c r="F1536" t="inlineStr">
+        <is>
+          <t>CC=CCC12C345678OC139%10%11%12%13%14O1C493%15%16%17O49C3%10%18%19%20O5%11C14%186%15%123C%197%16%131(CNCC(NCCCCCNCCCCCCCCCCCCCCOCCC4C5C6C7C(CC)C7C465)C(=O)NCC4=C5=C4C=CC=C5)OC29%2081%173%14.CCCCCCCCCCCC1CC1(O)CCCC1C2C3C45C6C(CCCC7CC7C7CO78C79C8%10C78C7%11%12C%13%14C7%15%16C7C(CC%17%18%19(C)(C)C%20%21%22C%17%23%24C%20%18%17%25C%18%20%26%27C%28%29%30C%31%32C%33(C%34C%35C(C%36C%37%38C%36%39C%37%36C%38%39%37%40C%38%39%41%42=C%43%44%45=C%37%38%46%47C%43%39%37%38=C%39%43%48C%49%50C%51%52C%49%39%53C%50%51%43C=%44%52%53%48%37%41%46C=%45%36%40%38%42%47)C%35%34%33)C%31%28%33C%32%29%18%28C%33%30%20%18C%21%23%28%26%17C%22%24%18%27%25%19)C7%15C%13%16%11C9%108%14%12)C64C1235</t>
+        </is>
+      </c>
+      <c r="G1536" t="inlineStr"/>
+      <c r="H1536" t="inlineStr"/>
+      <c r="I1536" t="n">
+        <v>1.437742303876029e-34</v>
+      </c>
+      <c r="J1536" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1536" t="inlineStr"/>
+    </row>
+    <row r="1537">
+      <c r="A1537" s="1" t="n">
+        <v>1535</v>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2121.png</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr"/>
+      <c r="D1537" t="inlineStr"/>
+      <c r="E1537" t="inlineStr"/>
+      <c r="F1537" t="inlineStr">
+        <is>
+          <t>CC(=O)NCCCC(=O)NC(C)=O.CC=CC=C1C2(=O)NC34(=O)[CH]56(C(C)O)NC78(=O)N9C%10(=O)N%11C%12(=O)[CH]97(C(N)=O)[CH]%1285(C(C)O)N357C63(=O)[CH]45(C)[CH]12374NC1[CH]235C(=O)(NC(=O)C(C)(C)(SC(C)(C)N6C789=O=C6%12%13(=O=7)N6[CH]8%127%14C8CC%12NC(CC7[CH]869%13C%14(=O)C4C)N%12)C%114(=O)C(C)(C)C=N6[CH]7(C)CC67(C)SC%104(C)C)[CH]124C312CC54(C)(O1)O2.O</t>
+        </is>
+      </c>
+      <c r="G1537" t="inlineStr"/>
+      <c r="H1537" t="inlineStr"/>
+      <c r="I1537" t="n">
+        <v>2.040542088476646e-11</v>
+      </c>
+      <c r="J1537" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1537" t="inlineStr"/>
+    </row>
+    <row r="1538">
+      <c r="A1538" s="1" t="n">
+        <v>1536</v>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2125.png</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr"/>
+      <c r="D1538" t="inlineStr"/>
+      <c r="E1538" t="inlineStr"/>
+      <c r="F1538" t="inlineStr">
+        <is>
+          <t>CC[CH]NC[CH]NC1=C23C4N56C278N29%10C%11%12%13%14N%15%16C%11%17%18%19%20C5%152%11%21[CH]%12%1725%15N%18C%12(=O=C(C(N)=O)N[CH]%13%17%18%22%23%24%25N%13C%17%26C2%18%17%27(C2%18NC2%17(C(=O)C(=O)NCC(CCNC(N)=O)NCC(N)=O)C%18%27%22)C%13%23C%26%195%242[CH]4679%11([CH]13NC13N4C5(=O)C6(NC6=O)[CH]41567C3145=O=C39%11%13%17%18(=O=1)=O=C=4631%19%22=O=C346%23%24%26(=O=9)=O9=C3%27%28(N4C=9%2763C1469N%28%23[CH]437%19%111C%13(N65%17)N91%24%18)N%22%261CC1(C)=O)[CH]%168%10%14%20%212%15%25)=O=C(C)(=O)N%12.CNCCCNCNC1CC1.O.O.O.O.O</t>
+        </is>
+      </c>
+      <c r="G1538" t="inlineStr"/>
+      <c r="H1538" t="inlineStr"/>
+      <c r="I1538" t="n">
+        <v>2.281793418174335e-31</v>
+      </c>
+      <c r="J1538" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1538" t="inlineStr"/>
+    </row>
+    <row r="1539">
+      <c r="A1539" s="1" t="n">
+        <v>1537</v>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2129.png</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr"/>
+      <c r="D1539" t="inlineStr"/>
+      <c r="E1539" t="inlineStr"/>
+      <c r="F1539" t="inlineStr">
+        <is>
+          <t>C=C123456C=C1789C21%10=C2%11%12C=C%13%14%15%16%17C=C%18%19C%20%21%22%23=C%24%25%26%27%28%29[CH]%30%31%32C[CH]%24%33%34(C%30%24ClC%31%33Cl%24)C173%24=C8%134%251C2%1434(=CC2=C%18%20%2678(C(=O)C%13=CN%14C=C(NC(=O)C%18=CC=C(O)C=C%18)C=CC%14=N%13)C%21(=C2%153)C%19%227%27(=O)C%32%23%3418%28=C9%24%1645%29)C%11%17C%10C%126.CC(C)C(NC(=O)OCCOCCNC(=O)CNC(=O)CNC(=O)CN)C(=O)NCC(=O)NC=CC=CCOC(=O)C123CN4(C1)C2C1(C43)N23CN14(CCOC(CO)C(O)COCC24)C3(=O)O</t>
+        </is>
+      </c>
+      <c r="G1539" t="inlineStr"/>
+      <c r="H1539" t="inlineStr"/>
+      <c r="I1539" t="n">
+        <v>4.854604158161271e-06</v>
+      </c>
+      <c r="J1539" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1539" t="inlineStr"/>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="1" t="n">
+        <v>1538</v>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2133.png</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr"/>
+      <c r="D1540" t="inlineStr"/>
+      <c r="E1540" t="inlineStr"/>
+      <c r="F1540" t="inlineStr">
+        <is>
+          <t>CC(C)C[CH]NC(=O)C(CCC(=O)O)NC(=O)CNC(=O)C(CC(C)C)NC(=O)C(CC1=CNC=N1)NC(=O)C(CC1=CNC2=C1C=CC=C2)NC(=O)C(C)NC(=O)[CH]CSSC[CH]C(=O)NC(C(=O)NC(CSSCC(NC(C)(C)C)C1(=O)=O=C2[CH]345CC6(=O)(O)=O=C(O6)C3[CH]23(N14)C12=O=C53(=O=1)N2)C(=O)O)C(C)O</t>
+        </is>
+      </c>
+      <c r="G1540" t="inlineStr"/>
+      <c r="H1540" t="inlineStr"/>
+      <c r="I1540" t="n">
+        <v>0.06147665331526032</v>
+      </c>
+      <c r="J1540" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1540" t="inlineStr"/>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="1" t="n">
+        <v>1539</v>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2145.png</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr"/>
+      <c r="D1541" t="inlineStr"/>
+      <c r="E1541" t="inlineStr"/>
+      <c r="F1541" t="inlineStr">
+        <is>
+          <t>CC(C)[CH]NC(=O)[C@H](CCCCN)NC(=O)[C@@H](Cc1ccc(C(N)=O)cc1)NC(=O)[C@H](Cc1ccc(O)cc1)NC(=O)[C@@H](CNC(=O)C[CH]C(=O)N[C@H](Cc1ccc(O)cc1)C(N)=O)NC(=O)[C@@H](N)Cc1ccc(Cl)cc1 |^1:3,48|</t>
+        </is>
+      </c>
+      <c r="G1541" t="inlineStr"/>
+      <c r="H1541" t="inlineStr"/>
+      <c r="I1541" t="n">
+        <v>0.58763413833853</v>
+      </c>
+      <c r="J1541" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1541" t="inlineStr"/>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="1" t="n">
+        <v>1540</v>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2157.png</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr"/>
+      <c r="D1542" t="inlineStr"/>
+      <c r="E1542" t="inlineStr"/>
+      <c r="F1542" t="inlineStr">
+        <is>
+          <t>CC[C@@H](C)C(NC(=O)[C@H](C)NC(=O)OC(C)(C)C)C(=O)NC(CCCCNc1nc(OC)nc(OC)n1)C(=O)N[C@H](C(=O)N[C@@H](Cc1ccccc1)C(=O)OC)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1542" t="inlineStr"/>
+      <c r="H1542" t="inlineStr"/>
+      <c r="I1542" t="n">
+        <v>0.8332320761545409</v>
+      </c>
+      <c r="J1542" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1542" t="inlineStr"/>
+    </row>
+    <row r="1543">
+      <c r="A1543" s="1" t="n">
+        <v>1541</v>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2161.png</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr"/>
+      <c r="D1543" t="inlineStr"/>
+      <c r="E1543" t="inlineStr"/>
+      <c r="F1543" t="inlineStr">
+        <is>
+          <t>C1C234C1567C2189C352%10%11C46135%12C782146C9%103278C39%10%13%14%15C%16%17%18%19%20C%21%22%23%24C%16%25%26(C%21%17%16%27%28C%22%25%17%21%29C%23%16%22%25%30C%27%17%16%23%31C%28%21%22%17%27%32C%29%25%16%21%22%28C%30%23%17%16%25%29C%31%27%21%17%23%30C%32%22%16%21%27%31C%28%25%17%16%22%32C%29%23%21%17%25%28C%30%27%16%21%23%29C%31%22%17%16%27%30C%32%25%21%17%22%31C%28%23%16%21%25%32C%29%27%17%16%23%28C%30%22%21%17%27%29C%31%25%16%21%22%30C%32%23%17%16%25%31C%28%27%21%17%23%32C%29%22%16%21%27%28C%30%25%17%16%22%29C%31%23%21%17%25%30C%32%27%16%21%23%31C%28%22%17%16%27%32C%29%25%21%17%22%28C%30%23%16%21%25%29C%31%27%17%16%23%30C%32%22%21%17%27%31C%28%25%16%21%22%32C%29%23%17%16%25%28C%30%27%21%17%23%29C%31%22%16%21%27%30%33C%32%25%17%16%22%31%34C%28%23%21%17%25%32%35C%29%27%16%21%23%28%36C%30%22%17%16%27%29%37C%33%31%25%21%17%22%30%38C%34%32%23%16%21%25%31%33C%35%28%27%17%16%23%32%34C%36%29%22%21%17%27%28%35C%37%30%25%16%21%22%29%36C%38%31%23%17%16%25%30%37C%33%32%27%21%17%23%31%38C%34%28%22%16%21%27%32%33C%35%29%25%17%16%22%28%34C%36%30%23%21%17%25%29%35C%37%31%27%16%21%23%30%36C%38%32%22%17%16%27%31%37C%33%28%25%21%17%22%32%38C%34%29%23%16%21%25%28%33C%35%30%27%17%16%23%29%34C%36%31%22%21%17%27%30%35C%37%32%25%16%21%22%31%36C%38%28%23%17%16%25%32%37C%33%29%27%21%17%23%28%38C%34%30%22%16%21%27%29%33C%35%31%25%17%16%22%30%34C%36%32%23%21%17%25%31%35%39C%37%28%27%16%21%23%32%36%40C%38%29%22%17%16%27%28%37%41C%33%30%25%21%17%22%29%38%42C%34%31%23%16%21%25%30%33%43C%35%32%27%17%16%23%31%34%44C%17%27%32%35%45%46%47%48%49%50C%51%52%53%54C%17%55%56%57%58C%51%27%17%59%60%61C%52%55%32%27%51%62%63C%53%56%17%35%32%52%55%64C%54%57%59%27%45%17%35%53%56C%58%60%51%32%21%16%46%27%45%54C%61%62%52%22%25%17%23%47%16%21C%63%55%28%29%30%35%31%48%27%17C%64%36%37%38%33%53%34%49%45%16C%39%40%41%42%43%56%44%50%54%21%17)C%24%183%16%17%21C%1993%18%22C%26%20%16%109%19C3%1712%13%10C%11%185497%14C%22%21%126%198%15%10.O=C(NC1C2C13C214C325C367C89C(NC%10(=O)CCCCC%11%12%13C%14%15C%16%17C%18C%14%11%19C%16(C%11C%14C%11%16C%11C(C%14%11%16)C%11(=O)C(C(=O)O)N%10%11)C%18%15%12C%17%19%13)(C(=O)O)C83%10C126C94%1057)C1CC1CCC1CC1CCC1C2CC12</t>
+        </is>
+      </c>
+      <c r="G1543" t="inlineStr"/>
+      <c r="H1543" t="inlineStr"/>
+      <c r="I1543" t="n">
+        <v>8.979376630015718e-163</v>
+      </c>
+      <c r="J1543" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1543" t="inlineStr"/>
+    </row>
+    <row r="1544">
+      <c r="A1544" s="1" t="n">
+        <v>1542</v>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2165.png</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr"/>
+      <c r="D1544" t="inlineStr"/>
+      <c r="E1544" t="inlineStr"/>
+      <c r="F1544" t="inlineStr">
+        <is>
+          <t>CCC(C(=O)NC(CC(C)=O)C(N)(=O)[CH]C(C)(C)NCC(C)(C)C12=O=C345(=O=C3NCCC3=CC=CC=C3)=O=C1436(=O=C3C6)N25)C1(=O)=O=C(CC(CC2=CC(C)=CC=C2)NC(=O)CC[CH]C(=O)NCCCCC(C)N)N1.CCCCCCCCC1(=O)N2C345=O=C2367C2C(C(NC(=O)CCC3CC3CCCC)C1463C1N46CC489=O=C163(=O=8)N91C34C6C3(CCCCCCC)C641)C257</t>
+        </is>
+      </c>
+      <c r="G1544" t="inlineStr"/>
+      <c r="H1544" t="inlineStr"/>
+      <c r="I1544" t="n">
+        <v>9.651406382589794e-09</v>
+      </c>
+      <c r="J1544" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1544" t="inlineStr"/>
+    </row>
+    <row r="1545">
+      <c r="A1545" s="1" t="n">
+        <v>1543</v>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2169.png</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr"/>
+      <c r="D1545" t="inlineStr"/>
+      <c r="E1545" t="inlineStr"/>
+      <c r="F1545" t="inlineStr">
+        <is>
+          <t>C[C@@H](O)[C@@H]1NC(=O)[C@H](CCCCN)NC(=O)[C@@H](CCCNC(N)=O)NC(=O)[C@H](Cc2ccc(O)cc2)NC(=O)[C@H](NC(=O)[C@@H](N)Cc2ccc(Cl)cc2)CSSC[C@@H](C(=O)N[C@H](Cc2ccc(O)cc2)C(N)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1545" t="inlineStr"/>
+      <c r="H1545" t="inlineStr"/>
+      <c r="I1545" t="n">
+        <v>0.8412964269230462</v>
+      </c>
+      <c r="J1545" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1545" t="inlineStr"/>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="1" t="n">
+        <v>1544</v>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2173.png</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr"/>
+      <c r="D1546" t="inlineStr"/>
+      <c r="E1546" t="inlineStr"/>
+      <c r="F1546" t="inlineStr">
+        <is>
+          <t>C=CC=C(NCC1CC1(C)(C)C=O)C1CO1CCOCCOCCC(C)=O.O.O=C(O)CCC1CC1CCCCC1CCC1CCCC(=O)O[CH]CC(=O)NCCOCCCO.[H]C1(OCC)C23N(C[CH]C4=O=C4N)[CH]12C3(=O)N1C(CC(C2=CC=CC=C2)=C2CCC2=O)C12=O=C2CCC1C2C(CCCCCC3C4C3C4C3C4C3C43C4C5C(CCNCCC6=C7=C6C=CC=C7)C543)C12</t>
+        </is>
+      </c>
+      <c r="G1546" t="inlineStr"/>
+      <c r="H1546" t="inlineStr"/>
+      <c r="I1546" t="n">
+        <v>2.976618523071807e-16</v>
+      </c>
+      <c r="J1546" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1546" t="inlineStr"/>
+    </row>
+    <row r="1547">
+      <c r="A1547" s="1" t="n">
+        <v>1545</v>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2177.png</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr"/>
+      <c r="D1547" t="inlineStr"/>
+      <c r="E1547" t="inlineStr"/>
+      <c r="F1547" t="inlineStr">
+        <is>
+          <t>C=CC1=CC234=C5(C=C)C678=C9%10N2%11C2%12=C5%13(=C=6%11(N923)N%10%124)[CH]72O3C45=CC=CC6=C4NC=C6CC(N)C(=O)NC(CC(N)=O)C(=O)N[CH]2(C(=O)NC(CO)C(=O)NC(C(=O)NC(CO)C(=O)NC(CC2=CC=CC=C2)C(=O)O)C1CCCN)[CH]38%13O5</t>
+        </is>
+      </c>
+      <c r="G1547" t="inlineStr"/>
+      <c r="H1547" t="inlineStr"/>
+      <c r="I1547" t="n">
+        <v>0.06096135838653074</v>
+      </c>
+      <c r="J1547" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1547" t="inlineStr"/>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="1" t="n">
+        <v>1546</v>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2185.png</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr"/>
+      <c r="D1548" t="inlineStr"/>
+      <c r="E1548" t="inlineStr"/>
+      <c r="F1548" t="inlineStr">
+        <is>
+          <t>[CH]C(=O)N[CH]CSCC.[H][C]1CCCC[C@]1([H])N([CH]C(=O)O)C(=O)C1CCCN1C(=O)[C@H](CC(C)O)NC(=O)[C@H](COC(C)(C)C)NC(=O)[C@H](CCCNC(=N)NS(=O)(=O)/C1=C(\OC)CC(C)(C)O/C=C(\C)C1C)NC(=O)C(COC(C)(C)C)C(=O)N1[C@@H](N)[C@@H]1C(c1ccccc1)(c1ccccc1)c1ccccc1 |^1:4,10,18,^2:0|</t>
+        </is>
+      </c>
+      <c r="G1548" t="inlineStr"/>
+      <c r="H1548" t="inlineStr"/>
+      <c r="I1548" t="n">
+        <v>0.03145617458570971</v>
+      </c>
+      <c r="J1548" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1548" t="inlineStr"/>
+    </row>
+    <row r="1549">
+      <c r="A1549" s="1" t="n">
+        <v>1547</v>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2189.png</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr"/>
+      <c r="D1549" t="inlineStr"/>
+      <c r="E1549" t="inlineStr"/>
+      <c r="F1549" t="inlineStr">
+        <is>
+          <t>C[C@@H](O)[C@@H]1NC(=O)[C@H](CCCCN)NC(=O)[C@@H](Cc2ccc(C(N)=O)cc2)NC(=O)[C@H](Cc2ccc(O)cc2)NC(=O)[C@H](NC(=O)[C@@H](N)Cc2ccc(Cl)cc2)Cn2cc(nn2)C[C@@H](C(=O)N[C@H](Cc2ccc(O)cc2)C(N)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1549" t="inlineStr"/>
+      <c r="H1549" t="inlineStr"/>
+      <c r="I1549" t="n">
+        <v>0.522363451046985</v>
+      </c>
+      <c r="J1549" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1549" t="inlineStr"/>
+    </row>
+    <row r="1550">
+      <c r="A1550" s="1" t="n">
+        <v>1548</v>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2197.png</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr"/>
+      <c r="D1550" t="inlineStr"/>
+      <c r="E1550" t="inlineStr"/>
+      <c r="F1550" t="inlineStr">
+        <is>
+          <t>[H]C12CCCCC1([H])C134=O=C(=O=1)(N3C(C(=O)NC(C(=O)NC(CSC1=CC=CC=C1)C(C)NC(=O)C(C)CC)C(C)CC)C2)[CH]412CC1CN2C(=O)C(CC(C)O)NC(=O)C(COC(C)(C)C)NC(=O)[CH]NC(=O)N[CH]123C4[SH](CC5=CC=CC=C5)C1(SC15=CC=CC=1=C5)[CH]41C2(N[CH]CCCNC(=N)N[SH]=O)=O=C13=O</t>
+        </is>
+      </c>
+      <c r="G1550" t="inlineStr"/>
+      <c r="H1550" t="inlineStr"/>
+      <c r="I1550" t="n">
+        <v>0.005483029937226316</v>
+      </c>
+      <c r="J1550" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1550" t="inlineStr"/>
+    </row>
+    <row r="1551">
+      <c r="A1551" s="1" t="n">
+        <v>1549</v>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2201.png</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr"/>
+      <c r="D1551" t="inlineStr"/>
+      <c r="E1551" t="inlineStr"/>
+      <c r="F1551" t="inlineStr">
+        <is>
+          <t>CN(C)CCOC1=CC2=C(C=C1)NC(C(=O)N1CC(CCl)C3=C1C=C(OC(=O)N(C)CCN(C)C(=O)OCC1=CC=C(NC(=O)C(CCCNC(N)=O)NC(=O)[CH]45N6C7=O=C8(=O)(CNC(=O)CNC(=O)CN)N[CH]6(C78)(C4(C)C)C5(C)C)C=C1)C1=CC=CC=C13)=C2</t>
+        </is>
+      </c>
+      <c r="G1551" t="inlineStr"/>
+      <c r="H1551" t="inlineStr"/>
+      <c r="I1551" t="n">
+        <v>0.09374686170891999</v>
+      </c>
+      <c r="J1551" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1551" t="inlineStr"/>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="1" t="n">
+        <v>1550</v>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2205.png</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr"/>
+      <c r="D1552" t="inlineStr"/>
+      <c r="E1552" t="inlineStr"/>
+      <c r="F1552" t="inlineStr">
+        <is>
+          <t>CC[C@H](C)[C@@H](C(=O)N(C)[C@H](C(=O)N/C=C\c1c[nH]c2ccccc12)C(C)C)N(C)C(=O)[C@H](C)N(C)C(=O)[C@H](C(C)C)N(C)C(=O)[C@@H](Cc1ccccc1)N(C)C(C)=O</t>
+        </is>
+      </c>
+      <c r="G1552" t="inlineStr"/>
+      <c r="H1552" t="inlineStr"/>
+      <c r="I1552" t="n">
+        <v>0.7540882745675641</v>
+      </c>
+      <c r="J1552" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1552" t="inlineStr"/>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="1" t="n">
+        <v>1551</v>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2209.png</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr"/>
+      <c r="D1553" t="inlineStr"/>
+      <c r="E1553" t="inlineStr"/>
+      <c r="F1553" t="inlineStr">
+        <is>
+          <t>COC=CC=CCC[CH]12OC(=O)[CH]34CCCCN3C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)C(CC(C)C)N(C)C(=O)C3CCCN3C(=O)C(CC3=CC=C(CNC(=O)C5=CC=CC=C5)C=C3)NC(=O)C(C3=CC=CC=C3)NC(=O)CCC(=O)NC35=CC167=C18=C2(=C=62C16=C3=C82=C=65)[CH]7(CCC1=CC=C(OC)C(OC)=C1)OC4=O</t>
+        </is>
+      </c>
+      <c r="G1553" t="inlineStr"/>
+      <c r="H1553" t="inlineStr"/>
+      <c r="I1553" t="n">
+        <v>0.2649558761845113</v>
+      </c>
+      <c r="J1553" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1553" t="inlineStr"/>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="1" t="n">
+        <v>1552</v>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2213.png</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr"/>
+      <c r="D1554" t="inlineStr"/>
+      <c r="E1554" t="inlineStr"/>
+      <c r="F1554" t="inlineStr">
+        <is>
+          <t>C=CC=CCCNC(=O)C(CCCNC(=N)N)NC(=O)C(CO)NC(=O)C(CC1=CC=CC=C1)NC(=O)C(CC1CCCCC1)NC(=O)C(CC(=O)O)NC(=O)CN1CCN(CC(=O)O)CCN(CC(=O)O)CC1.CC(C)CC1C2=O=C1(=O)NC134CC56=CNC7(=C5C=CC=C7)C5=CC=CC67=C5NC=C7C1C(N2)C3(=O)NC(CO)C(=O)(O)C(CO)(C(=O)O)NC4=O</t>
+        </is>
+      </c>
+      <c r="G1554" t="inlineStr"/>
+      <c r="H1554" t="inlineStr"/>
+      <c r="I1554" t="n">
+        <v>0.05548279193900991</v>
+      </c>
+      <c r="J1554" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1554" t="inlineStr"/>
+    </row>
+    <row r="1555">
+      <c r="A1555" s="1" t="n">
+        <v>1553</v>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2217.png</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr"/>
+      <c r="D1555" t="inlineStr"/>
+      <c r="E1555" t="inlineStr"/>
+      <c r="F1555" t="inlineStr">
+        <is>
+          <t>[H].[H]C12CCCCC1([H])C(C(=O)NC1C(=O)NC(C(N)=O)C(SC3=CC=CC=C3)[CH](CSC3=CC=CC=C3)(C(=O)C3N[CH]456789%10(C(C)CC)N%11[CH]%12%13(C(=O)OC%14%15=CC=CC=%14=C%15)[CH]4(C)(CC)[CH]C5(=O)(OC)[CH]%1145%14([CH]%126(C)CC)C3%137(=O)OC483(=O)=O4=C5967=O=C=4%14%105O64CO375C4)NC(=O)[CH]3(C4CC35(C)C3CC45C3)[CH]1(C)CC)C2</t>
+        </is>
+      </c>
+      <c r="G1555" t="inlineStr"/>
+      <c r="H1555" t="inlineStr"/>
+      <c r="I1555" t="n">
+        <v>1.049334681089039e-05</v>
+      </c>
+      <c r="J1555" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1555" t="inlineStr"/>
+    </row>
+    <row r="1556">
+      <c r="A1556" s="1" t="n">
+        <v>1554</v>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2221.png</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr"/>
+      <c r="D1556" t="inlineStr"/>
+      <c r="E1556" t="inlineStr"/>
+      <c r="F1556" t="inlineStr">
+        <is>
+          <t>CNCCCCC1NC(=O)C(CC2=CC=C(C(N)=O)C=C2)NC(=O)C(CC2=CC=C(O)C=C2)NC(=O)C(NC(=O)C(N)CC2=CC=C(Cl)C=C2)CSCCC(C(=O)NC(CC2=CC=C(O)C=C2)C(N)=O)NC(=O)[CH]2(NC1=O)C(C)C1SC[CH]12(C)C</t>
+        </is>
+      </c>
+      <c r="G1556" t="inlineStr"/>
+      <c r="H1556" t="inlineStr"/>
+      <c r="I1556" t="n">
+        <v>0.05362049950752516</v>
+      </c>
+      <c r="J1556" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1556" t="inlineStr"/>
+    </row>
+    <row r="1557">
+      <c r="A1557" s="1" t="n">
+        <v>1555</v>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2225.png</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr"/>
+      <c r="D1557" t="inlineStr"/>
+      <c r="E1557" t="inlineStr"/>
+      <c r="F1557" t="inlineStr">
+        <is>
+          <t>C[C@@H](O)[C@@H]1NC(=O)[C@H](CCCCN)N(C)C(=O)[C@@H](Cc2ccc(C(N)=O)cc2)NC(=O)[C@H](Cc2ccc(O)cc2)NC(=O)[C@H](NC(=O)[C@@H](N)Cc2ccc(Cl)cc2)CSSC[C@@H](C(=O)N[C@H](Cc2ccc(O)cc2)C(N)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1557" t="inlineStr"/>
+      <c r="H1557" t="inlineStr"/>
+      <c r="I1557" t="n">
+        <v>0.6090310537539657</v>
+      </c>
+      <c r="J1557" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1557" t="inlineStr"/>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="1" t="n">
+        <v>1556</v>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2229.png</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr"/>
+      <c r="D1558" t="inlineStr"/>
+      <c r="E1558" t="inlineStr"/>
+      <c r="F1558" t="inlineStr">
+        <is>
+          <t>CCCCC1C2(=O)N3C4C(C5=CC6=C(C=CC=C6)C=C5)[CH]356(CC3=CC7=C(C=CC=C7)C=C3)NC(=O)[CH]2(CCCC)N1(C)C(=O)COCC=CC(CCC1=C(O)C(OC)=C(OC)C=C1)OC(=O)C1CCCCN1C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)CNC(=O)[CH]12(COC(C)(C)C)C(O)C3N17(C)C5(=O)N32(C)C476=O</t>
+        </is>
+      </c>
+      <c r="G1558" t="inlineStr"/>
+      <c r="H1558" t="inlineStr"/>
+      <c r="I1558" t="n">
+        <v>0.0637657607951434</v>
+      </c>
+      <c r="J1558" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1558" t="inlineStr"/>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="1" t="n">
+        <v>1557</v>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2233.png</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr"/>
+      <c r="D1559" t="inlineStr"/>
+      <c r="E1559" t="inlineStr"/>
+      <c r="F1559" t="inlineStr">
+        <is>
+          <t>NCCCCC1C2N(C(=O)CC3=CC=CC=C3)CC(=O)NC(CC3=CC=CC=C3)CN(CC(N)=O)C(=O)CCSCC3=CC=C(C=C3)C(=O)NC(CC3=CC=CC=C3)CN(C(=O)CC3CC3)CC(=O)NC(CC3=CNC4=C3C=CC=C4)C3N45C6C(=O)N1[CH]2(CCCCN)NC(=O)CN63(C4C(CC1=CNC2=C1C=CC=C2)NC=O)C5(=O)CC1CC1</t>
+        </is>
+      </c>
+      <c r="G1559" t="inlineStr"/>
+      <c r="H1559" t="inlineStr"/>
+      <c r="I1559" t="n">
+        <v>0.08339189565815365</v>
+      </c>
+      <c r="J1559" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1559" t="inlineStr"/>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="1" t="n">
+        <v>1558</v>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2237.png</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr"/>
+      <c r="D1560" t="inlineStr"/>
+      <c r="E1560" t="inlineStr"/>
+      <c r="F1560" t="inlineStr">
+        <is>
+          <t>NCCCCC1NC(=O)C(CC2=CC=C(NC(=O)C(N)CCC(=O)O)C=C2)NC(=O)C(CC2=CC=C(O)C=C2)NC(=O)C(NC(=O)C(N)CC2=CC=C(Cl)C=C2)CSSC[CH]23NC4(=O)C5C(O)[CH]4(NC1=O)C5(=O)NC(C(=O)N1C4CC5=CC=C(O)C=C5C5(=CC=C(O)C=C5)C[CH]1(C(N)=O)(NC2=O)C4(N)=O)C3SS</t>
+        </is>
+      </c>
+      <c r="G1560" t="inlineStr"/>
+      <c r="H1560" t="inlineStr"/>
+      <c r="I1560" t="n">
+        <v>0.05671667412777295</v>
+      </c>
+      <c r="J1560" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1560" t="inlineStr"/>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="1" t="n">
+        <v>1559</v>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2241.png</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr"/>
+      <c r="D1561" t="inlineStr"/>
+      <c r="E1561" t="inlineStr"/>
+      <c r="F1561" t="inlineStr">
+        <is>
+          <t>[H]N1C(=O)C(C(C)C)N(C)C(=O)C(C(C)CC)OC(=O)C(C(C)(C)O)N(C)C(=O)C(CC(C)C)N([H])C(=O)C(C(C)C)N2(C)C(=O)C2(C(C)CC)N([H])C(=O)C2CCCN2C(=O)C(C(O)C2=CC=CC=C2)N(C)C(=O)C1CC1=CC=CC=C1</t>
+        </is>
+      </c>
+      <c r="G1561" t="inlineStr"/>
+      <c r="H1561" t="inlineStr"/>
+      <c r="I1561" t="n">
+        <v>0.5830934947898146</v>
+      </c>
+      <c r="J1561" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1561" t="inlineStr"/>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="1" t="n">
+        <v>1560</v>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2249.png</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr"/>
+      <c r="D1562" t="inlineStr"/>
+      <c r="E1562" t="inlineStr"/>
+      <c r="F1562" t="inlineStr">
+        <is>
+          <t>[H]C1(C(=O)[CH]NC(=O)C(CC(C)O)NC(=O)C(COC(C)(C)C)NC2=O=C3(=O)N[CH]45(CNC6=CC=CC=6)C6(=O)=O=C478C4N67C45(=O)(N4C5(=O)N6[CH]4(COC(C)(C)C)[CH]5(CCNC(=O)NC(=O)C=C(C)OC=C)[CH]263)[CH]8(CNC2=CC=CC=C2)NC(=O)C(CC)NC(=O)C2C345C67C89C3%10C63O86C8%11C4%12C6(C85C27%10%12)O93%11)CCC2CC21[H]</t>
+        </is>
+      </c>
+      <c r="G1562" t="inlineStr"/>
+      <c r="H1562" t="inlineStr"/>
+      <c r="I1562" t="n">
+        <v>0.001837088407347106</v>
+      </c>
+      <c r="J1562" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1562" t="inlineStr"/>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="1" t="n">
+        <v>1561</v>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2253.png</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr"/>
+      <c r="D1563" t="inlineStr"/>
+      <c r="E1563" t="inlineStr"/>
+      <c r="F1563" t="inlineStr">
+        <is>
+          <t>CCCCCCCCCCCCNC(=O)CN(CCNC(=O)CCN(CCO)CCN(CCO)CCC(=O)NCC1CN1(CC(=O)NCCCCCCCCCCCC)CC(=O)NCCCCCCCCCCCC)CC(=O)NCCCCCCCCCCCC</t>
+        </is>
+      </c>
+      <c r="G1563" t="inlineStr"/>
+      <c r="H1563" t="inlineStr"/>
+      <c r="I1563" t="n">
+        <v>0.6936993558901191</v>
+      </c>
+      <c r="J1563" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1563" t="inlineStr"/>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="1" t="n">
+        <v>1562</v>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2261.png</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr"/>
+      <c r="D1564" t="inlineStr"/>
+      <c r="E1564" t="inlineStr"/>
+      <c r="F1564" t="inlineStr">
+        <is>
+          <t>CC(C)C.[H]C123C4C(O)CN1(C42)C3(=O)[CH]C(=O)N[CH]12CCN3(C)C4(=O)[CH]5(CC6=CC=C(O)C=C6)NC(=O)CSCC(C(=O)NCC(N)=O)NC(=O)C(CC(C)C)NC(=O)C(CCCC)N(C)C(=O)C(CCCC)N(C)C(=O)C(CC6=C78C9=C%10=C7=CC7=C%11C%10=C=7C%118=C96)NC1(=O)C2CCCC(N)C53(=O)N4(C)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1564" t="inlineStr"/>
+      <c r="H1564" t="inlineStr"/>
+      <c r="I1564" t="n">
+        <v>0.003680885213217047</v>
+      </c>
+      <c r="J1564" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1564" t="inlineStr"/>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="1" t="n">
+        <v>1563</v>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2265.png</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr"/>
+      <c r="D1565" t="inlineStr"/>
+      <c r="E1565" t="inlineStr"/>
+      <c r="F1565" t="inlineStr">
+        <is>
+          <t>C1=CC2=C3(C=C3C=C2)N1.CC=CC=CC=CC=O.NC(=O)[CH]C(=O)C(CC1=CNC2=C1C=CC=C2)N[CH]1(CCC(=O)N2CCN(C3=C(C(=O)O)C=CC=C3)CC2)C(=O)N1C(=O)C(CC1=CNC2=C1C=CC=C2)NC(=O)C(CC1=CNC2=C1C=CC=C2)NC(=O)C1C2C3C1C2N3C(=O)CCC(=O)N1CC2=CC=CC=C2C#CC2=C1C=CC=C2</t>
+        </is>
+      </c>
+      <c r="G1565" t="inlineStr"/>
+      <c r="H1565" t="inlineStr"/>
+      <c r="I1565" t="n">
+        <v>0.04544313316749088</v>
+      </c>
+      <c r="J1565" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1565" t="inlineStr"/>
+    </row>
+    <row r="1566">
+      <c r="A1566" s="1" t="n">
+        <v>1564</v>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2269.png</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr"/>
+      <c r="D1566" t="inlineStr"/>
+      <c r="E1566" t="inlineStr"/>
+      <c r="F1566" t="inlineStr">
+        <is>
+          <t>[H]CNCCCCCC(=O)N[CH]12C3(=O)[CH]4(CC(=CNC5=CC=CC=C5)N41C(=O)CCCCCNC(=O)CCC)C21(=O)N2[CH]456CCCNC7(=O)[CH]C(=O)NC(C(N)=O)=CC89=CC=CC=8=C98C(=C9N%10C(C=CC=C)=C9%108)CC8CC89=O=C(N9)C(CCCNC(N)=O)C(=O)NCCN[CH]8(CC[CH]79%10%11%12%13C7=CNC(=O)C%14=C9C%14%109=C%10=CC=9%11C%10%12=C7%13)C4(=O)[CH]2315C86=O</t>
+        </is>
+      </c>
+      <c r="G1566" t="inlineStr"/>
+      <c r="H1566" t="inlineStr"/>
+      <c r="I1566" t="n">
+        <v>1.170162756725826e-08</v>
+      </c>
+      <c r="J1566" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1566" t="inlineStr"/>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="1" t="n">
+        <v>1565</v>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2273.png</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr"/>
+      <c r="D1567" t="inlineStr"/>
+      <c r="E1567" t="inlineStr"/>
+      <c r="F1567" t="inlineStr">
+        <is>
+          <t>CNC1C2C3C12C31C2C(CC3C4C35C43C46C78C4(C5367)C834C56C378C5439C6745C8367C9438C5649%10C7356%11C8437%12C9548%13C%106359%14C%117436%10C%128547%11C%139358%12C%146439%13C%107546%14C%118357%10C%129438%11C%136549%12C%147356%13C%108437%14C%119548%10C%126359%11C%137436%12C%148547%13C%109358%14C%116439%10C%127546%11C%138357%12C%149438%13C%106549%14C%117356%10C%128437%11C%139548%12C%146359%13C%107436%14C%118547%10C%129358%11C%136439%12C%147546%13C%108357%14C%119438%10C%126549%11C%137356%12C%148437%13C%109548%14C%116359%10C%127436%11C%138547%12C%149358%13C%106439%14C%117546%10C%128357%11C%139438%12C%146549%13C%107356%14C%118437%10C%129548%11C%136359%12C%147436%13C%108547%14C%119358%10C%126439%11C%137546%12C%148357%13C%109438%14C%116549%10C%127356%11C%138437%12C%149548%13C%106359%14C%117436%10C%128547%11C%139358%12C%146439%13C%107546%14C%118357%10C%129438%11C%136549%12C%147356%13C%108437%14C%119548%10C%126359%11C%137436%12C%148547%13C%109358%14C%116439%10C%127546%11C%138357%12C%149438%13C%106549%14C%117356%10C%128437%11C%139548%12C%146359%13C%107436%14C%118547%10C%129358%11C%136439%12C%147546%13C%108357%14C%119438%10C%126549%11C%137356%12C%148437%13C%109548%14C%116359%10C%127436%11C%138547%12C%149358%13C%106439%14%15C%117546%10%16C%128357%11%17C%139438%12%18C%146549%13%19C%15%107356%14%20C%16%118437%10%15C%17%129548%11%16C%18%136359%12%17C%19%147436%13%18C%20%108547%14%19C%15%119358%10%20C39%11%15%21%22%23%24C%25%26%27%28%29%30%31%32C%33%34%35%36%37C%38%39%40C%33%41%42%43C%38%34%25%33%44%45C%39%41%35%26%25%34%38C%40%42%36%33%27%26%35%39C%43%37%44%25%28%27%33%36C%45%34%26%293%25%28%37C%38%35%27%3093%26%29C%39%33%31%25%119%27%30C%36%32%283%15%11%25%31C%16%12645%213%15C%37%2697%118%224C%17%13%27%14%25%10%233C%29%18%30%19%31%20%24%154)C21</t>
+        </is>
+      </c>
+      <c r="G1567" t="inlineStr"/>
+      <c r="H1567" t="inlineStr"/>
+      <c r="I1567" t="n">
+        <v>7.718355860784016e-163</v>
+      </c>
+      <c r="J1567" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1567" t="inlineStr"/>
+    </row>
+    <row r="1568">
+      <c r="A1568" s="1" t="n">
+        <v>1566</v>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2277.png</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr"/>
+      <c r="D1568" t="inlineStr"/>
+      <c r="E1568" t="inlineStr"/>
+      <c r="F1568" t="inlineStr">
+        <is>
+          <t>[H][C]NC(=O)[C@]1([H])CCSCCC(NC(=O)[C@H](CC(=O)O)NC(C)(C)C)C(=O)N[C@@H](C)C(=O)N[C@@H](Cc2c[nH]c3ccccc23)C(=O)N[C@@H](Cc2c[nH]cn2)C(=O)N[C@@H](CC(C)C)C(=O)NCC(=O)N[C@@H](CCC(=O)O)C(=O)N[C@@H](CC(C)C)C(=O)N[C@@H](C(C)C)C(=O)N[C@@H](Cc2c[nH]c3ccccc23)C(=O)N1 |^2:1|</t>
+        </is>
+      </c>
+      <c r="G1568" t="inlineStr"/>
+      <c r="H1568" t="inlineStr"/>
+      <c r="I1568" t="n">
+        <v>0.5728444734047116</v>
+      </c>
+      <c r="J1568" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1568" t="inlineStr"/>
+    </row>
+    <row r="1569">
+      <c r="A1569" s="1" t="n">
+        <v>1567</v>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2281.png</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr"/>
+      <c r="D1569" t="inlineStr"/>
+      <c r="E1569" t="inlineStr"/>
+      <c r="F1569" t="inlineStr">
+        <is>
+          <t>[H]C1CCCCC1([H])N([CH]C(=O)NC(C(=O)NC(CSC1(C2=CC=CC=C2)C2=CC=CC=C2C12=CC=CC=C2)C(=O)NC(C(=O)OC)C(C)CC)C(C)C)C(=O)C1CCCN1C(=O)C(CC(C)C)NC(=O)C(COC(C)(C)C)NC(=O)C(N)CCCNC(=N)NS(=O)(=O)C1=C(C)C(C)=C2OC(C)(C)CC2=C1C</t>
+        </is>
+      </c>
+      <c r="G1569" t="inlineStr"/>
+      <c r="H1569" t="inlineStr"/>
+      <c r="I1569" t="n">
+        <v>0.3491950597364938</v>
+      </c>
+      <c r="J1569" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1569" t="inlineStr"/>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="1" t="n">
+        <v>1568</v>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2285.png</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr"/>
+      <c r="D1570" t="inlineStr"/>
+      <c r="E1570" t="inlineStr"/>
+      <c r="F1570" t="inlineStr">
+        <is>
+          <t>CCC[C@@H]1NC(=O)[C@H](CCC(=O)O)NC(=O)CNC(=O)[C@H](CC(C)C)NC(=O)[C@H](Cc2c[nH]cn2)NC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](C)NC(=O)[C@@H](NC(=O)[C@@H](N)CC(=O)O)CCC(=O)N2CCC(C(=O)N[C@H](C(N)=O)[C@H](C)O)(CC2)NC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](C(C)C)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1570" t="inlineStr"/>
+      <c r="H1570" t="inlineStr"/>
+      <c r="I1570" t="n">
+        <v>0.7458168689307856</v>
+      </c>
+      <c r="J1570" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1570" t="inlineStr"/>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="1" t="n">
+        <v>1569</v>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2289.png</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr"/>
+      <c r="D1571" t="inlineStr"/>
+      <c r="E1571" t="inlineStr"/>
+      <c r="F1571" t="inlineStr">
+        <is>
+          <t>CC(C)C[CH]123C(C(C)C)[CH]45(C1(=O)N16[CH]789%10%11C%12%13CC7%14%15CC7CC(C)(C)[CH]%121%14%16%17%18N8(C24=O)[CH]%136%1512C9%164=O=C%101%1768=O=C%112%18(=O=6)N748)C1(=O)CN24CN6(C)(CC(=O)N135C)C21(=O)[CH]23C(C)[CH]15(CCC(C)(C)C)(NC1(=O)C(C789%10=O%11=C%12%13%14=O=7=C=%117%15(=O)[CH]%128%11C8%12CC%11%16(C)[CH]8%1397C(C)[CH]%12%16%14%10%15)[CH]17C1(C(C)CCCC(=O)NCCNC=CCNC=NC=CC(N)=O)=O=C7(=O=1)N25)C346=O</t>
+        </is>
+      </c>
+      <c r="G1571" t="inlineStr"/>
+      <c r="H1571" t="inlineStr"/>
+      <c r="I1571" t="n">
+        <v>3.671300545421354e-05</v>
+      </c>
+      <c r="J1571" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1571" t="inlineStr"/>
+    </row>
+    <row r="1572">
+      <c r="A1572" s="1" t="n">
+        <v>1570</v>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2293.png</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr"/>
+      <c r="D1572" t="inlineStr"/>
+      <c r="E1572" t="inlineStr"/>
+      <c r="F1572" t="inlineStr">
+        <is>
+          <t>[H]CNC(=O)C1([H])CSSCC23([H])(NC(C)(C)C)C(SSC1)C1([H])(NC(C)(C)C)C2(=O)N[CH]2(C)C4(=O)NC5CCC67=CN8(CCC[CH]9(NC(=O)C(CCC)NC(=O)C(CCC(=O)O)NC(=O)CNC(=O)C(CC(C)C)NC(=O)C(CC%10=CNC=N%10)NC5(=O)C(CC6)NC2(=O)[CH]4(C)NC13=O)C([CH]N9C=O)CC8)N=N7</t>
+        </is>
+      </c>
+      <c r="G1572" t="inlineStr"/>
+      <c r="H1572" t="inlineStr"/>
+      <c r="I1572" t="n">
+        <v>0.02614415308894088</v>
+      </c>
+      <c r="J1572" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1572" t="inlineStr"/>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="1" t="n">
+        <v>1571</v>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2297.png</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr"/>
+      <c r="D1573" t="inlineStr"/>
+      <c r="E1573" t="inlineStr"/>
+      <c r="F1573" t="inlineStr">
+        <is>
+          <t>Cc1c(F)cc2nc3c(c4c2c1C=C[C@@H]4NC(=O)COCNC(=O)CNC(=O)[C@H](Cc1ccccc1)NC(=O)CNC(=O)CNC(=O)COC1C#CCCCCC1)Cn1c-3cc2c(c1=O)COC(=O)[C@@]2(C)O</t>
+        </is>
+      </c>
+      <c r="G1573" t="inlineStr"/>
+      <c r="H1573" t="inlineStr"/>
+      <c r="I1573" t="n">
+        <v>0.7897859030571585</v>
+      </c>
+      <c r="J1573" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1573" t="inlineStr"/>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="1" t="n">
+        <v>1572</v>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2301.png</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr"/>
+      <c r="D1574" t="inlineStr"/>
+      <c r="E1574" t="inlineStr"/>
+      <c r="F1574" t="inlineStr">
+        <is>
+          <t>[H]C12345CCCN16C17(=O)[CH]89(CC(N)=O)N%10C%11%12(=O)N%13%14%15[CH]%16%17C%18C(N)(=O)C(C(N)=O)[CH]%18%13%19(N%13C%10%14%18%20=O=C%13%15%10(=O)[CH]%11%18%13%14N%11(C)C%13%15(=O)N%14(C(=O)C(CC%13=CC=C(O)C=C%13)NC(=O)CSCC(NC(=O)C(CC(C)C)NC(=O)C(CCC)N(C)C(=O)C(CCC)NC)C(=O)NCC(N)=O)[CH]%11%15%12%20%10O)C%168%10%11=O=C%179%19(=O)N1%102(CCC3)C(CC4)[CH]67%115.[H]CC=O</t>
+        </is>
+      </c>
+      <c r="G1574" t="inlineStr"/>
+      <c r="H1574" t="inlineStr"/>
+      <c r="I1574" t="n">
+        <v>1.888512877681452e-05</v>
+      </c>
+      <c r="J1574" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1574" t="inlineStr"/>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="1" t="n">
+        <v>1573</v>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2305.png</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr"/>
+      <c r="D1575" t="inlineStr"/>
+      <c r="E1575" t="inlineStr"/>
+      <c r="F1575" t="inlineStr">
+        <is>
+          <t>COC=CC=CCCC1OC(=O)[CH]23CCCCN2C(=O)C(=O)C2(C)(C)COC(=O)C=CCCN(C)C(=O)C(CC(C)C)N(C)C(=O)C4CCCN4C(=O)C(CC4=CC=CC=C4)N(C)C(=O)C(CC(=O)OC(C)(C)C)NC(=O)CCC(=O)NC=CC1C(CCC1=CC=C(OC)C(OC)=C1)OC3(=O)C1CCCCN1C(=O)C2(=O)C(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G1575" t="inlineStr"/>
+      <c r="H1575" t="inlineStr"/>
+      <c r="I1575" t="n">
+        <v>0.106345301335245</v>
+      </c>
+      <c r="J1575" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1575" t="inlineStr"/>
+    </row>
+    <row r="1576">
+      <c r="A1576" s="1" t="n">
+        <v>1574</v>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2309.png</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr"/>
+      <c r="D1576" t="inlineStr"/>
+      <c r="E1576" t="inlineStr"/>
+      <c r="F1576" t="inlineStr">
+        <is>
+          <t>CSC123SC4N5(C)C(=O)C(C)NC(=O)C(NC(=O)C6=NC7=CC=CC=C7N=C6)COC(=O)C(C(C)C)N(C)C(=O)C16N(C)C(=O)C(C)NC(=O)C17(NC(=O)C8=NC9=CC=CC=C9N=C8)COC(=O)C8(C(C)C)N9(C)C(=O)C5(S2)C49(=O)N8(C)C(C(C)C)C(=O)OC1C(NC(=O)C1=NC2=CC=CC=C2N=C1)C7(=O)NC(C)C(=O)N6(C)C3C(=O)N(C)C</t>
+        </is>
+      </c>
+      <c r="G1576" t="inlineStr"/>
+      <c r="H1576" t="inlineStr"/>
+      <c r="I1576" t="n">
+        <v>0.01712899355925279</v>
+      </c>
+      <c r="J1576" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1576" t="inlineStr"/>
+    </row>
+    <row r="1577">
+      <c r="A1577" s="1" t="n">
+        <v>1575</v>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2313.png</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr"/>
+      <c r="D1577" t="inlineStr"/>
+      <c r="E1577" t="inlineStr"/>
+      <c r="F1577" t="inlineStr">
+        <is>
+          <t>[H]C1(C(=O)(=O)NC(CN)CNC(CC(C)C)C(=O)N2(CCC)C34[H]C325([H])C(=O)NC(C(=O)C2=CNC3=C2C=CC=C3)NC45=O)CCN1C(=O)C(CC(N)=O)NC(=O)C(C)N(C)C(=O)C(CC1=CC=C(O)C=C1)NC(=O)CSCC(NC(=O)C(CC(C)C)NC(=O)C(CCCC)N(C)C([CH])=O)C(=O)NCC(N)=O</t>
+        </is>
+      </c>
+      <c r="G1577" t="inlineStr"/>
+      <c r="H1577" t="inlineStr"/>
+      <c r="I1577" t="n">
+        <v>0.1323869106779312</v>
+      </c>
+      <c r="J1577" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1577" t="inlineStr"/>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="1" t="n">
+        <v>1576</v>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2321.png</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr"/>
+      <c r="D1578" t="inlineStr"/>
+      <c r="E1578" t="inlineStr"/>
+      <c r="F1578" t="inlineStr">
+        <is>
+          <t>CC(C)C[C@@H]1NC(=O)[C@H](Cc2c[nH]cn2)NC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](C)NC(=O)[C@@H](NC(=O)[C@@H](N)CC(=O)O)CSSC[C@@H](C(=O)C(C)(C)C)NC(=O)[C@H](Cc2c[nH]c3ccccc23)NC(=O)[C@H](C(C)C)NC(=O)[C@H](CC(C)C)NC(=O)[C@H](CCC(=O)O)NC(=O)CNC1=O</t>
+        </is>
+      </c>
+      <c r="G1578" t="inlineStr"/>
+      <c r="H1578" t="inlineStr"/>
+      <c r="I1578" t="n">
+        <v>0.7853001756422912</v>
+      </c>
+      <c r="J1578" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1578" t="inlineStr"/>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="1" t="n">
+        <v>1577</v>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2325.png</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr"/>
+      <c r="D1579" t="inlineStr"/>
+      <c r="E1579" t="inlineStr"/>
+      <c r="F1579" t="inlineStr">
+        <is>
+          <t>CCC1NC(=O)[CH]23CCSSCC[CH]4(NC(=O)C(C)NC(=O)C(NC(C)(C)C)CCCCNC(=O)C(CC5=CC=C(C6=CC=CC=C6)C=C5)NC1=O)(C(=O)NC(CC1=CNC=N1)C(=O)NC(CC1CC1)C(=O)NCC(=O)NC(CCC(=O)O)C(=O)N2C)C([CH]N4C(=O)C(C)NC(=O)C(CCCCN)NC(C)(C)C)CSSCC3</t>
+        </is>
+      </c>
+      <c r="G1579" t="inlineStr"/>
+      <c r="H1579" t="inlineStr"/>
+      <c r="I1579" t="n">
+        <v>0.09686760751473954</v>
+      </c>
+      <c r="J1579" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1579" t="inlineStr"/>
+    </row>
+    <row r="1580">
+      <c r="A1580" s="1" t="n">
+        <v>1578</v>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2329.png</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr"/>
+      <c r="D1580" t="inlineStr"/>
+      <c r="E1580" t="inlineStr"/>
+      <c r="F1580" t="inlineStr">
+        <is>
+          <t>C[CH]C(=O)NC(CCCNC(C)=O)CC(=O)C[CH]CNCC1=O=C(=O)(CNC[CH]CNC(CCC)C(=O)N[CH]CCC[CH]CC2N[CH]345(CC67C2C2C68N69C27N82C678=O=C92(=N)(N7)N8)C26=O=C378(=O)NC(C(=O)NC(C)CNC(CC(C)C)C(=O)NC(CC(C)=O)C(CC(C)C)NC(C)=O)CC(C)(C)CC3(C)C9C(C)(C)C3[CH]74N28[CH]965)N1</t>
+        </is>
+      </c>
+      <c r="G1580" t="inlineStr"/>
+      <c r="H1580" t="inlineStr"/>
+      <c r="I1580" t="n">
+        <v>7.509874792271118e-09</v>
+      </c>
+      <c r="J1580" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1580" t="inlineStr"/>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="1" t="n">
+        <v>1579</v>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2333.png</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr"/>
+      <c r="D1581" t="inlineStr"/>
+      <c r="E1581" t="inlineStr"/>
+      <c r="F1581" t="inlineStr">
+        <is>
+          <t>CCCCC1C2(=O)N3C4C(C5=CC6=C(C=CC=C6)C=C5)[CH]356(CC3=CC7=C(C=CC=C7)C=C3)NC(=O)[CH]2(CCCC)N1(C)C(=O)COCC=CC(CCC1=CC(OC)=C(OC)C=C1OC)OC(=O)C1CCCCN1C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)CNC(=O)[CH]12(COC(C)(C)C)C(O)C3N17(C)C5(=O)N32(C)C476=O</t>
+        </is>
+      </c>
+      <c r="G1581" t="inlineStr"/>
+      <c r="H1581" t="inlineStr"/>
+      <c r="I1581" t="n">
+        <v>0.06735267694494634</v>
+      </c>
+      <c r="J1581" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1581" t="inlineStr"/>
+    </row>
+    <row r="1582">
+      <c r="A1582" s="1" t="n">
+        <v>1580</v>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2345.png</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr"/>
+      <c r="D1582" t="inlineStr"/>
+      <c r="E1582" t="inlineStr"/>
+      <c r="F1582" t="inlineStr">
+        <is>
+          <t>COC1=CC=C(CCC2O3C(=O)[CH]45CCCCN4C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)C(CC(C)C)N(C)C(=O)C4CCCN4C(=O)C(CC(=O)OC(C)(C)C)N(C)C(=O)C(C4=CC=CC=C4)NC(=O)CCC(=O)NC46=CC2(=CC=C4)[CH]3(CCC2=CC=C(OC)C(OC)=C2)(C=CC=C6)OC5=O)C=C1OC</t>
+        </is>
+      </c>
+      <c r="G1582" t="inlineStr"/>
+      <c r="H1582" t="inlineStr"/>
+      <c r="I1582" t="n">
+        <v>0.4144169858077055</v>
+      </c>
+      <c r="J1582" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1582" t="inlineStr"/>
+    </row>
+    <row r="1583">
+      <c r="A1583" s="1" t="n">
+        <v>1581</v>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_0/rb_2349.png</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr"/>
+      <c r="D1583" t="inlineStr"/>
+      <c r="E1583" t="inlineStr"/>
+      <c r="F1583" t="inlineStr">
+        <is>
+          <t>CCCCC1C2(=O)N3C4C(C5=CC6=C(C=CC=C6)C=C5)[CH]356(CC3=CC7=C(C=CC=C7)C=C3)NC(=O)[CH]2(CCCC)N1(C)C(=O)COCC=CC(CCC1=CC(OC)=C(OC)C=C1F)OC(=O)C1CCCCN1C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)CNC(=O)[CH]12(COC(C)(C)C)C(OC)C3N17(C)C5(=O)N32(C)C476=O</t>
+        </is>
+      </c>
+      <c r="G1583" t="inlineStr"/>
+      <c r="H1583" t="inlineStr"/>
+      <c r="I1583" t="n">
+        <v>0.08152160431686802</v>
+      </c>
+      <c r="J1583" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1583" t="inlineStr"/>
+    </row>
+    <row r="1584">
+      <c r="A1584" s="1" t="n">
+        <v>1582</v>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2106.png</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr"/>
+      <c r="D1584" t="inlineStr"/>
+      <c r="E1584" t="inlineStr"/>
+      <c r="F1584" t="inlineStr">
+        <is>
+          <t>CC=CC=CCC(NC(=O)CSC)N1C2C(C)(C)[CH]13(C(C)C)(NC(NC(=O)CSC)CC=CC=CCCNC3=O)C2(=O)N1CCCC1C(=O)N[CH]C(C)O.C[CH]C(=O)NC(CCC(=O)O)C(=O)NC(C)C(=O)N1CCCC1C(N)=O.NCCCC[CH]1(NC(=O)CNC=O)(C(N)=O)C(CCCN)C(NC(=O)CNC=O)C1(N)=O</t>
+        </is>
+      </c>
+      <c r="G1584" t="inlineStr"/>
+      <c r="H1584" t="inlineStr"/>
+      <c r="I1584" t="n">
+        <v>0.001737214049592349</v>
+      </c>
+      <c r="J1584" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1584" t="inlineStr"/>
+    </row>
+    <row r="1585">
+      <c r="A1585" s="1" t="n">
+        <v>1583</v>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2114.png</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr"/>
+      <c r="D1585" t="inlineStr"/>
+      <c r="E1585" t="inlineStr"/>
+      <c r="F1585" t="inlineStr">
+        <is>
+          <t>C[C@@H](O)[C@H]1C(=O)N[C@H](C(=O)N[C@H](Cc2ccc(O)cc2)C(N)=O)CSSC[C@@H](NC(=O)[C@@H](N)Cc2ccc(Cl)cc2)C(=O)N(C)[C@@H](Cc2ccc(O)cc2)C(=O)N[C@H](Cc2ccc(C(N)=O)cc2)C(=O)N[C@@H](CCCCN)C(=O)N1C</t>
+        </is>
+      </c>
+      <c r="G1585" t="inlineStr"/>
+      <c r="H1585" t="inlineStr"/>
+      <c r="I1585" t="n">
+        <v>0.4101574342635569</v>
+      </c>
+      <c r="J1585" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1585" t="inlineStr"/>
+    </row>
+    <row r="1586">
+      <c r="A1586" s="1" t="n">
+        <v>1584</v>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2118.png</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr"/>
+      <c r="D1586" t="inlineStr"/>
+      <c r="E1586" t="inlineStr"/>
+      <c r="F1586" t="inlineStr">
+        <is>
+          <t>CCOC1=CC=C23C(=C1)C21C3(=O)N12C(=O)C2NC(=O)C(CCNC(C)=O)NC(=O)C(NC(=O)C(NC(C)=O)C(C)C)C1C2=C34=C21=C312C3=C(N41)C21(C)=CC=C=13C.COC(=O)NCCCCNC(=O)C(=O)NC1234=O=C(=O=1)(N2)[CH]31(NC23=O=C(=O)(N2)[CH]34C(=O)NC(=O)[CH]234(CO)NC(=CC5=CC=CC=C5)C2C3(=O)N4C=CN)C2NC3=CC=CC=C321</t>
+        </is>
+      </c>
+      <c r="G1586" t="inlineStr"/>
+      <c r="H1586" t="inlineStr"/>
+      <c r="I1586" t="n">
+        <v>4.659556767132725e-10</v>
+      </c>
+      <c r="J1586" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1586" t="inlineStr"/>
+    </row>
+    <row r="1587">
+      <c r="A1587" s="1" t="n">
+        <v>1585</v>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2122.png</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr"/>
+      <c r="D1587" t="inlineStr"/>
+      <c r="E1587" t="inlineStr"/>
+      <c r="F1587" t="inlineStr">
+        <is>
+          <t>COC1=CC=C(CC[CH]23OC(=O)[CH]45CC6CC6N4C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)C(CC(C)C)N(C)C(=O)C4CCCN4C(=O)C(CC4=CC=C(CNC(=O)CN(C)C)C=C4)NC(=O)C(C4=CC=CC=C4)NC(=O)CCC(=O)NC46=CC278=C29=C3(=C=73C27=C4=C93=C=76)[CH]8(CCC2=CC=C(OC)C(OC)=C2)OC5=O)C=C1O</t>
+        </is>
+      </c>
+      <c r="G1587" t="inlineStr"/>
+      <c r="H1587" t="inlineStr"/>
+      <c r="I1587" t="n">
+        <v>0.1254758241402079</v>
+      </c>
+      <c r="J1587" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1587" t="inlineStr"/>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="1" t="n">
+        <v>1586</v>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2134.png</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr"/>
+      <c r="D1588" t="inlineStr"/>
+      <c r="E1588" t="inlineStr"/>
+      <c r="F1588" t="inlineStr">
+        <is>
+          <t>[H]C[CH]NC(=O)C(C)[CH]OCCCOCCNCCCN12CCC(=O)NCCOCC#CC(=O)CCCC1(=O)NC2CC(=O)NCCOCCOCC(=O)NC(=O)NC1C2CC3(=O)N456CN37(C)(C43=OC(C3)C2N1C(=O)C1CNC1C)[CH]512C3(C)CC4[CH]58C9(=O)N%10[CH]%11%12[CH]%13%14C[CH]%15(C)(C%13)C%13CC[CH]%13%11(OC)[CH]%10%14%15[CH]9%12(C)C(=O)N9C1%10(=O)N45C982(=O)[CH]3%1067C(C)C</t>
+        </is>
+      </c>
+      <c r="G1588" t="inlineStr"/>
+      <c r="H1588" t="inlineStr"/>
+      <c r="I1588" t="n">
+        <v>7.855807048440917e-07</v>
+      </c>
+      <c r="J1588" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1588" t="inlineStr"/>
+    </row>
+    <row r="1589">
+      <c r="A1589" s="1" t="n">
+        <v>1587</v>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2142.png</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr"/>
+      <c r="D1589" t="inlineStr"/>
+      <c r="E1589" t="inlineStr"/>
+      <c r="F1589" t="inlineStr">
+        <is>
+          <t>CC(C)[C@@H]1NC(=O)[C@H](CCCCN)NC(=O)[C@@H](Cc2ccc(C(N)=O)cc2)NC(=O)[C@H](Cc2ccc(O)cc2)NC(=O)[C@H](NC(=O)[C@@H](N)Cc2ccc(Cl)cc2)C/C=C/C[C@@H](C(=O)N[C@H](Cc2ccc(O)cc2)C(N)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1589" t="inlineStr"/>
+      <c r="H1589" t="inlineStr"/>
+      <c r="I1589" t="n">
+        <v>0.4610588872851759</v>
+      </c>
+      <c r="J1589" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1589" t="inlineStr"/>
+    </row>
+    <row r="1590">
+      <c r="A1590" s="1" t="n">
+        <v>1588</v>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2154.png</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr"/>
+      <c r="D1590" t="inlineStr"/>
+      <c r="E1590" t="inlineStr"/>
+      <c r="F1590" t="inlineStr">
+        <is>
+          <t>C[C@@H](O)[C@@H]1NC(=O)[C@H](CCCCN)NC(=O)[C@@H](CCCCNC(N)=O)NC(=O)[C@H](Cc2ccc(O)cc2)NC(=O)[C@H](NC(=O)[C@@H](N)Cc2ccc(Cl)cc2)CSSC[C@@H](C(=O)N[C@H](Cc2ccc(O)cc2)C(N)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1590" t="inlineStr"/>
+      <c r="H1590" t="inlineStr"/>
+      <c r="I1590" t="n">
+        <v>0.6816232664140597</v>
+      </c>
+      <c r="J1590" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1590" t="inlineStr"/>
+    </row>
+    <row r="1591">
+      <c r="A1591" s="1" t="n">
+        <v>1589</v>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2162.png</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr"/>
+      <c r="D1591" t="inlineStr"/>
+      <c r="E1591" t="inlineStr"/>
+      <c r="F1591" t="inlineStr">
+        <is>
+          <t>CCC(C)[CH]NC(=O)C(CCC(N)=O)NC(=O)[CH]12(CC(=O)O)NC(=O)[CH]345N6C(=O)C7(CCCC=CCCCC(C)(NC(=O)C(CCCCN)NC(=O)C(N)CC8=CC=C(O)C=C8)C(=O)NC(C(C)O)C(=O)NC(CCC(N)=O)C(=O)NC(CO)C(=O)N7)C6(=O)N3C(C4(=O)N1C(CC(=O)O)C2=O)[CH]5(C)CC</t>
+        </is>
+      </c>
+      <c r="G1591" t="inlineStr"/>
+      <c r="H1591" t="inlineStr"/>
+      <c r="I1591" t="n">
+        <v>0.04765954563470145</v>
+      </c>
+      <c r="J1591" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1591" t="inlineStr"/>
+    </row>
+    <row r="1592">
+      <c r="A1592" s="1" t="n">
+        <v>1590</v>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2166.png</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr"/>
+      <c r="D1592" t="inlineStr"/>
+      <c r="E1592" t="inlineStr"/>
+      <c r="F1592" t="inlineStr">
+        <is>
+          <t>CCCCCCC(=O)N[CH]123C4(=O)N5C(=O)(NC(C)C6(=O)[CH]N6C(=O)C6CCC6C(=O)[CH]N)[CH]56C5C7=CC=CC=C7C7(=CC=CC=C7)C7=CC=C(C[CH]418C21(=O)N249(C)C83(=O)N138(CCCC1=CC=CC=C1)[CH]21%10C2%11(=O)C(C%12[CH]%13(C=CC=C%13)[CH]%12%13%14(C)C=CC=CC%13=C%14)C1%12(=O)[CH]243(C)(C(=O)[CH]CCC1=CC=CC=C1)[CH]%11%12%1098C)C56=C7.CN</t>
+        </is>
+      </c>
+      <c r="G1592" t="inlineStr"/>
+      <c r="H1592" t="inlineStr"/>
+      <c r="I1592" t="n">
+        <v>2.45547257298343e-11</v>
+      </c>
+      <c r="J1592" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1592" t="inlineStr"/>
+    </row>
+    <row r="1593">
+      <c r="A1593" s="1" t="n">
+        <v>1591</v>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2174.png</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr"/>
+      <c r="D1593" t="inlineStr"/>
+      <c r="E1593" t="inlineStr"/>
+      <c r="F1593" t="inlineStr">
+        <is>
+          <t>[H]C12CSC(CCCCC(=O)NCCOCCOCCOCC3(=O)NC4CC=CN5CCCC[CH]6(C(N)=O)NC(=O)C7CCCN7C(=O)C(CC7=CNC8=C7C=CC=C8)NC(=O)CNC(=O)C(CC(C)C)NC(=O)C(CC(C)C)NC(=O)C(CC7=CN(CCCCCC6(N)=O)N5=N7)N4C(=O)C3OCCOCCOCCNC)C1([H])NC(=O)N2</t>
+        </is>
+      </c>
+      <c r="G1593" t="inlineStr"/>
+      <c r="H1593" t="inlineStr"/>
+      <c r="I1593" t="n">
+        <v>0.02858284301929712</v>
+      </c>
+      <c r="J1593" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1593" t="inlineStr"/>
+    </row>
+    <row r="1594">
+      <c r="A1594" s="1" t="n">
+        <v>1592</v>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2178.png</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr"/>
+      <c r="D1594" t="inlineStr"/>
+      <c r="E1594" t="inlineStr"/>
+      <c r="F1594" t="inlineStr">
+        <is>
+          <t>O.O.O.[1*]C1CN2C3(CN4CC4CNCCCN)=O4=C5N3C=452C2(C3C4CC432)N2345(CCN6C7C6N7CCCCCC=CCC6=C78=C(CC(C9=CC=C(N%10CCC%11(N)CC%10%11)C=C9)=C7C8)N6)(=O6=C2(CCNCCC2=O=C(C(=O)NC78=O9=C7%10=O7=C(N%11CC%11%12C%11=O%13=C(CCC%14=C%15=C%16(=C%17(=CC=C%18%19C%20C=CC(=O)(N%21%22%23CCC%21%24C%21C%22%25N%24C%21%25%23)C%18C%20%19)=C%16%18%19=N(=C%15%17%18)C%15C=C%15CN%19)N%14)C=%13N%11%12)C=7=98%10)N2)O=32=C4C=6=25CC)C1 |$;;;R1;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1594" t="inlineStr"/>
+      <c r="H1594" t="inlineStr"/>
+      <c r="I1594" t="n">
+        <v>5.060201491346404e-12</v>
+      </c>
+      <c r="J1594" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1594" t="inlineStr"/>
+    </row>
+    <row r="1595">
+      <c r="A1595" s="1" t="n">
+        <v>1593</v>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2182.png</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr"/>
+      <c r="D1595" t="inlineStr"/>
+      <c r="E1595" t="inlineStr"/>
+      <c r="F1595" t="inlineStr">
+        <is>
+          <t>CC(=O)N[CH]1234C(=O)N[CH]567(CC(N)=O)C(C(N)=O)C(N5C1(=O)[CH]1(N2C(C)=O)C3(O)(O)C2CC214(C)O)C6(=O)N1C7(=O)N[CH]2(C)[CH](C)(N)[CH]12CC1=CC2=CC34=C(C=CC=C21)(C3)C4.C[CH]NC12(=O)C3C(CCCN)[CH]14(CCCC(N)=O)N2[CH]12(N(C(C(=O)CCCCCCCCCC5=CC=CC=C5)C1(C)O)C34=O)C1345CC2(C1)(O3)(O4)O5</t>
+        </is>
+      </c>
+      <c r="G1595" t="inlineStr"/>
+      <c r="H1595" t="inlineStr"/>
+      <c r="I1595" t="n">
+        <v>1.073604465122897e-06</v>
+      </c>
+      <c r="J1595" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1595" t="inlineStr"/>
+    </row>
+    <row r="1596">
+      <c r="A1596" s="1" t="n">
+        <v>1594</v>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2186.png</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr"/>
+      <c r="D1596" t="inlineStr"/>
+      <c r="E1596" t="inlineStr"/>
+      <c r="F1596" t="inlineStr">
+        <is>
+          <t>CC(O)[C@@H]1NC(=O)[C@H](CCCCN)NC(=O)[C@@H](Cc2ccc(C(N)=O)cc2)NC(=O)[C@H](Cc2ccc(O)cc2)NC(=O)[C@H](NC(=O)[C@@H](N)Cc2ccc(Cl)cc2)Cc2cn(nn2)C[C@@H](C(=O)N[C@H](Cc2ccc(O)cc2)C(N)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1596" t="inlineStr"/>
+      <c r="H1596" t="inlineStr"/>
+      <c r="I1596" t="n">
+        <v>0.6269125088334075</v>
+      </c>
+      <c r="J1596" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1596" t="inlineStr"/>
+    </row>
+    <row r="1597">
+      <c r="A1597" s="1" t="n">
+        <v>1595</v>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2190.png</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr"/>
+      <c r="D1597" t="inlineStr"/>
+      <c r="E1597" t="inlineStr"/>
+      <c r="F1597" t="inlineStr">
+        <is>
+          <t>CCCOC1=CC=CC=C1.C[CH]N[CH]CC1[CH]N1C1CC1N12CC1CNC1C(CCC(NC3C4C(N)(=O)N34C[CH]C3=O=C3C(N)CC)CCNC2(=O)(=O)COCCOCCNCCOCCOCCNCC2C3CN234(C(CC(=O)CCCCCCCCCCC)C(=O)O)[CH]2356N7C(CCCCCCCCCCC)N2[CH]74289C347%10=O3=C52%11%12(=O=42=C845%13=O=C=3=269(=O=4)(O5)(O7%11)O%13%12)O%10)C2NC12.O</t>
+        </is>
+      </c>
+      <c r="G1597" t="inlineStr"/>
+      <c r="H1597" t="inlineStr"/>
+      <c r="I1597" t="n">
+        <v>8.687384418309655e-11</v>
+      </c>
+      <c r="J1597" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1597" t="inlineStr"/>
+    </row>
+    <row r="1598">
+      <c r="A1598" s="1" t="n">
+        <v>1596</v>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2194.png</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr"/>
+      <c r="D1598" t="inlineStr"/>
+      <c r="E1598" t="inlineStr"/>
+      <c r="F1598" t="inlineStr">
+        <is>
+          <t>CCC1(O)C(=O)OCC2=C1C=C134C=C1C31=NC3=CC(F)=C(C)C5=C3C(=C1CN4C2=O)C(NC(=O)COCNC(=O)CNC(=O)C(CC12=C3C4=C67=C3=C=43C64=C1=C73=C=42)NC(=O)CNC(=O)CNC(=O)CCC(=O)N1CC2=C(C=CC=C2)C=CC2=C1C=CC=C2)CC5</t>
+        </is>
+      </c>
+      <c r="G1598" t="inlineStr"/>
+      <c r="H1598" t="inlineStr"/>
+      <c r="I1598" t="n">
+        <v>0.1148205715876932</v>
+      </c>
+      <c r="J1598" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1598" t="inlineStr"/>
+    </row>
+    <row r="1599">
+      <c r="A1599" s="1" t="n">
+        <v>1597</v>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2202.png</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr"/>
+      <c r="D1599" t="inlineStr"/>
+      <c r="E1599" t="inlineStr"/>
+      <c r="F1599" t="inlineStr">
+        <is>
+          <t>CC1CC12CC2NC(=O)CCC1=C(NC(=O)NCCC[CH]23N4C(=O)N56[CH]789%10N%11%12C7%13%14=O=C87(=O=%13)N9([CH]25%118C(=O)N3825C3C89%11=C%13%15=C%16(=C=8%17C%138=C%13%18%19=C%15%17=C=8%15(=C%13=C3%1692C%155)C%1823=O=C%19(O)(=O=2)O3)C%11C4NC(=O)SCC(C=O)NCCCCC(NC2(=O)=O=C(CCC(NCCCCC3=CC=C(Cl)C=C3)C(=O)O)NC(C(=O)O)C2)C(N)=O)[CH]6%12%1472C34(C)CC%102(C3)C4)C=CC=C1</t>
+        </is>
+      </c>
+      <c r="G1599" t="inlineStr"/>
+      <c r="H1599" t="inlineStr"/>
+      <c r="I1599" t="n">
+        <v>6.648670889107789e-06</v>
+      </c>
+      <c r="J1599" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1599" t="inlineStr"/>
+    </row>
+    <row r="1600">
+      <c r="A1600" s="1" t="n">
+        <v>1598</v>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2214.png</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr"/>
+      <c r="D1600" t="inlineStr"/>
+      <c r="E1600" t="inlineStr"/>
+      <c r="F1600" t="inlineStr">
+        <is>
+          <t>CC[C@H](C)[C@@H]([C@@H](CC(=O)N1CCC[C@H]1[CH]OC(=O)N[C@H](C)[C@@H](O)c1ccccc1)OC)N(C)C(=O)C(NC(=O)[C@H](C(C)C)N(C)C(=O)OCc1ccc(NC(=O)[C@H](C)NC(=O)[C@@H](NC(=O)CCNC(=O)/C=C\C(=O)OC)C(C)C)cc1)C(C)C |^1:14|</t>
+        </is>
+      </c>
+      <c r="G1600" t="inlineStr"/>
+      <c r="H1600" t="inlineStr"/>
+      <c r="I1600" t="n">
+        <v>0.8013368428899509</v>
+      </c>
+      <c r="J1600" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1600" t="inlineStr"/>
+    </row>
+    <row r="1601">
+      <c r="A1601" s="1" t="n">
+        <v>1599</v>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2218.png</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr"/>
+      <c r="D1601" t="inlineStr"/>
+      <c r="E1601" t="inlineStr"/>
+      <c r="F1601" t="inlineStr">
+        <is>
+          <t>CCCCC1C2C13C21C324C135C216C4327C5134C6215C7326C4137C5214C6325C7136C4217C5324C6135C7216C4327C5134C6215C7326C4137C5214C6325C7136C4217C5324C6135C7216C4327C51348C62159C7326%10C4137%11C85214%12C963258C%1071369C%114217%10C%125324%11C86135%12C972168C%1043279C%115134%10C%126215%11C87326%12C941378C%1052149C%116325%10C%127136%11C84217%12C953248C%1061359C%117216%10C%124327%11C85134%12C962158C%1073269C%114137%10C%125214%11C86325%12C971368C%1042179C%115324%10C%126135%11C87216%12C943278C%1051349C%116215%10C%127326%11%13C84137%12%14C952148%15C%1063259%16C%117136%10%17C%13%124217%11%18C%1485324%12%13C%15961358%14C%16%1072169%15C%17%114327%10%16C%18%125134%11%17C%1386215%12%18C%14973268%13C%15%1041379%14C%16%115214%10%15C%17%126325%11%16C%1887136%12%17C%13942178%18C%14%1053249%13C%15%116135%10%14C%16%127216%11%15C%1784327%12%16C%18951348%17C%13%1062159%18C%14%117326%10%13C%15%124137%11%14C%1685214%12%15C%17963258%16C%18%1071369%17C%13%114217%10%18C%14%125324%11%13C%1586135%12%14C%16972168%15C%17%1043279%16C%18%115134%10%17C%13%126215%11%18C%1487326%12%13C%15941378%14C%16%1052149%15C%17%116325%10%16C%18%127136%11%17C%1384217%12%18C%14953248%13C%15%1061359%14C%16%117216%10%15C%17%124327%11%16C%1885134%12%17C%13962158%18C%14%1073269%13C%15%114137%10%14C%16%125214%11%15C%1786325%12%16C%18971368%17C%13%1042179%18C%14%115324%10%13C%15%126135%11%14C%1687216%12%15C%17943278%16C%18%1051349%17C%13%116215%10%18C%14%127326%11%13C%1584137%12%14C%16952148%15C%17%1063259%16C%18%117136%10%17C%13%124217%11%18C%1485324%12%13C%15961358%14C%16%1072169%15C%17%114327%10%16C%18%125134%11%17C%1386215%12%18C%14973268%13%19C379%14%20%21%22%23%24C%25%26%27%28%29C%30%31%32%33C%253%34%35%36%37C%30%2673%25%38%39C%31%27%3497%26%30%40C%32%28%353%149%27%31%34C%36%25172%203%14%28C%3845%2696%2112C%15%10%11%12%278%2234C%16%17%18%30%31%13%23%141C%33%29%37%39%40%34%19%24%2824</t>
+        </is>
+      </c>
+      <c r="G1601" t="inlineStr"/>
+      <c r="H1601" t="inlineStr"/>
+      <c r="I1601" t="n">
+        <v>1.36871712501066e-162</v>
+      </c>
+      <c r="J1601" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1601" t="inlineStr"/>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="1" t="n">
+        <v>1600</v>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2222.png</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr"/>
+      <c r="D1602" t="inlineStr"/>
+      <c r="E1602" t="inlineStr"/>
+      <c r="F1602" t="inlineStr">
+        <is>
+          <t>CC[CH][CH]NC1[CH]N1C1[CH]23(OC2O3)[CH]123456O[CH]21789O[CH]132(O74)[CH]134O[CH]1285(O3)[CH]49612O[CH]134O1C56C(CCCCO7C8C9C(O%10%11C%12C%10%13C(OCCCCCCCOCCCCOC%10C%14=C%10%15=O%14=C(COCCCCCC%10%14C%16O%10C(=O)O%16%14)O%15)C%12%13%11)C987)C5O63[CH]142.COCCCCC=CC=CCCCCCCOCC1C2C(O)O12.O=C(O)[CH]O[CH]O[CH]O1CC1</t>
+        </is>
+      </c>
+      <c r="G1602" t="inlineStr"/>
+      <c r="H1602" t="inlineStr"/>
+      <c r="I1602" t="n">
+        <v>6.342405036174278e-23</v>
+      </c>
+      <c r="J1602" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1602" t="inlineStr"/>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="1" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2226.png</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr"/>
+      <c r="D1603" t="inlineStr"/>
+      <c r="E1603" t="inlineStr"/>
+      <c r="F1603" t="inlineStr">
+        <is>
+          <t>C=CC=CC1[CH]NC(=O)C(C(C)C)C(=O)C(C(C)C)C(=O)NC(CO)C(=O)N2C34=C5N[CH]526CC(=O)[CH]25C7C8(=CC9=C(CO)C%10=C8%11=C8=CC7%11=C9C=C%108CO)C[CH]17(N([CH]C36=O)C7(=O)N2C=O)C5(=O)NC(CCCCN)C(=O)NC(CC(=CCCCN)C1=CC=CC(O)=C1)C(=O)NC(C)(C)NC(=O)[CH]CCC(=O)CCOC=C4</t>
+        </is>
+      </c>
+      <c r="G1603" t="inlineStr"/>
+      <c r="H1603" t="inlineStr"/>
+      <c r="I1603" t="n">
+        <v>1.316547212894752e-05</v>
+      </c>
+      <c r="J1603" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1603" t="inlineStr"/>
+    </row>
+    <row r="1604">
+      <c r="A1604" s="1" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2230.png</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr"/>
+      <c r="D1604" t="inlineStr"/>
+      <c r="E1604" t="inlineStr"/>
+      <c r="F1604" t="inlineStr">
+        <is>
+          <t>CCC1(O)C(=O)OCC2=C1C=C1N(CC3=C14=C15=C3C(NC(=O)OCC3=CC=C(CNC(=O)CNC(=O)C(CC6=CC=CC=C6)NC(=O)CNC(=O)CNC(=O)CCCCCN6C(=O)C=CC6=O)C=C3)CC=C1=C(C)=C(F)C=C5N4)C2=O</t>
+        </is>
+      </c>
+      <c r="G1604" t="inlineStr"/>
+      <c r="H1604" t="inlineStr"/>
+      <c r="I1604" t="n">
+        <v>0.2182458328325335</v>
+      </c>
+      <c r="J1604" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1604" t="inlineStr"/>
+    </row>
+    <row r="1605">
+      <c r="A1605" s="1" t="n">
+        <v>1603</v>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2234.png</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr"/>
+      <c r="D1605" t="inlineStr"/>
+      <c r="E1605" t="inlineStr"/>
+      <c r="F1605" t="inlineStr">
+        <is>
+          <t>[H]C12CCCCC1([H])N(C(=O)C1CCCN1C(=O)C(CC(C)C)NC(=O)C(COC(C)(C)C)NC1(=O)N([CH]COC)C3(=O)[CH]45C6CC4[CH]613N5C(=O)C(N)COC(C)(C)C)C(C(=O)NC(C(=O)NC(CSC(C1=CC=CC=C1)(C1=CC=CC=C1)C1=CC=CC=C1)C(=O)NC(C(=O)OC)C(C)CC)C(C)CC)C2</t>
+        </is>
+      </c>
+      <c r="G1605" t="inlineStr"/>
+      <c r="H1605" t="inlineStr"/>
+      <c r="I1605" t="n">
+        <v>0.07550828336620753</v>
+      </c>
+      <c r="J1605" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1605" t="inlineStr"/>
+    </row>
+    <row r="1606">
+      <c r="A1606" s="1" t="n">
+        <v>1604</v>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2238.png</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr"/>
+      <c r="D1606" t="inlineStr"/>
+      <c r="E1606" t="inlineStr"/>
+      <c r="F1606" t="inlineStr">
+        <is>
+          <t>[H]C12345(C(N)=O)C67(N)=O=C1(N)(=O)C6189%10[H]C76([CH]CC7=C(CNC(=O)CC(NC(=O)C(CC(=O)O)NC(C)(C)C)C(=O)NC(C)C(=O)NC(CC%11=CNC%12=C%11C=CC=C%12)C(=O)NC(CC%11=CNC=N%11)C(=O)NC(CC(C)C)C(=O)NCC(=O)N[CH]CCC=O)C=CC=C7)([H]1)[CH]82(C)(O)O1[CH]693(C)C2[CH]436C[CH]21%105(C3)O6</t>
+        </is>
+      </c>
+      <c r="G1606" t="inlineStr"/>
+      <c r="H1606" t="inlineStr"/>
+      <c r="I1606" t="n">
+        <v>0.006599966455568549</v>
+      </c>
+      <c r="J1606" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1606" t="inlineStr"/>
+    </row>
+    <row r="1607">
+      <c r="A1607" s="1" t="n">
+        <v>1605</v>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2242.png</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr"/>
+      <c r="D1607" t="inlineStr"/>
+      <c r="E1607" t="inlineStr"/>
+      <c r="F1607" t="inlineStr">
+        <is>
+          <t>[H]C12CSC(CCCCC(=O)NCCOCCOCCOCC3(=O)N4CN35[CH]36C7C8=CN9CCCC[CH]%10%11(C(N)=O)NC%12(=O)[CH]%13%14CCC%15N%16%17C%18%19CC[CH]%12%20%21C%13(=O)N%10C(C(N)=O)C%11CCCN%10C=C(N=N9%10)C83[CH]745C6(=O)NC(CCCCN)C(=O)NC(CC(C)C)C(=O)NCC(=O)NC3CC4=C%165(=N%18%20C3(=O)N%15%19%145%21)NC%173=C4C=CC=C3)C1([H])NC(=O)N2</t>
+        </is>
+      </c>
+      <c r="G1607" t="inlineStr"/>
+      <c r="H1607" t="inlineStr"/>
+      <c r="I1607" t="n">
+        <v>0.0004221844624619408</v>
+      </c>
+      <c r="J1607" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1607" t="inlineStr"/>
+    </row>
+    <row r="1608">
+      <c r="A1608" s="1" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2246.png</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr"/>
+      <c r="D1608" t="inlineStr"/>
+      <c r="E1608" t="inlineStr"/>
+      <c r="F1608" t="inlineStr">
+        <is>
+          <t>[H]N1C(=O)C(C(C)C)N(C)C(=O)C(C(C)CC)OC(=O)C(C(C)(C)O)N(C)C(=O)C(CC(C)C)N([H])C(=O)C(C(C)C)N2(C)C(=O)C2(C(C)CC)N([H])C(=O)C2CCCN2C(=O)C(CC2=CC=CC=C2)N(C)C(=O)C1CC1=CC=CC=C1</t>
+        </is>
+      </c>
+      <c r="G1608" t="inlineStr"/>
+      <c r="H1608" t="inlineStr"/>
+      <c r="I1608" t="n">
+        <v>0.6482002674137398</v>
+      </c>
+      <c r="J1608" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1608" t="inlineStr"/>
+    </row>
+    <row r="1609">
+      <c r="A1609" s="1" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2250.png</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr"/>
+      <c r="D1609" t="inlineStr"/>
+      <c r="E1609" t="inlineStr"/>
+      <c r="F1609" t="inlineStr">
+        <is>
+          <t>CC(=O)NCCCC[C@@H]1NC(=O)[C@@H](Cc2ccc(C(N)=O)cc2)NC(=O)[C@H](Cc2ccc(O)cc2)NC(=O)[C@H](NC(=O)[C@@H](N)Cc2ccc(Cl)cc2)CSSC[C@@H](C(=O)N[C@@H](Cc2ccc(O)cc2)C(N)=O)NC(=O)[C@H]([C@@H](C)O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1609" t="inlineStr"/>
+      <c r="H1609" t="inlineStr"/>
+      <c r="I1609" t="n">
+        <v>0.8031176731114633</v>
+      </c>
+      <c r="J1609" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1609" t="inlineStr"/>
+    </row>
+    <row r="1610">
+      <c r="A1610" s="1" t="n">
+        <v>1608</v>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2254.png</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr"/>
+      <c r="D1610" t="inlineStr"/>
+      <c r="E1610" t="inlineStr"/>
+      <c r="F1610" t="inlineStr">
+        <is>
+          <t>[H]C(=O)C12=C3C=CC(=C1)C2CC(CC)C(NC(=O)C(NC(=O)C(CCC(N)=O)NC(=O)C(CO)NC(=O)C(NC(=O)C(N)CC1=CC=C(C2=CC=C(C4=CC=CC=C4)C=C2)C=C1)C(C)CC)C(C)CC)C(=O)O3</t>
+        </is>
+      </c>
+      <c r="G1610" t="inlineStr"/>
+      <c r="H1610" t="inlineStr"/>
+      <c r="I1610" t="n">
+        <v>0.785148577142499</v>
+      </c>
+      <c r="J1610" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1610" t="inlineStr"/>
+    </row>
+    <row r="1611">
+      <c r="A1611" s="1" t="n">
+        <v>1609</v>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2258.png</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr"/>
+      <c r="D1611" t="inlineStr"/>
+      <c r="E1611" t="inlineStr"/>
+      <c r="F1611" t="inlineStr">
+        <is>
+          <t>CCCCCC12=O=C1(NC(=O)C(OC1C=CC3(=O)=C1=C3C1C=CC=CC=C1)C1OC1C1=O=C3(=O=C3NC(=O)CCCC(=O)C(N)C(C)O)N1)C2.CCCNC[CH]1(C2345=O6=C2789%10%11=O=3=C723%12(=O=C2(N)=O)N482C3947C3CC3C[CH]624%10N75%12%11)NC2(=O1)CN21C(CCNC)C1C(N)=O.CC[CH]NCCNCOCN(C)C[CH]N.O=C1C=CC=C2C34OC56(O)C7N89C1N27(C385)C496</t>
+        </is>
+      </c>
+      <c r="G1611" t="inlineStr"/>
+      <c r="H1611" t="inlineStr"/>
+      <c r="I1611" t="n">
+        <v>3.982628552531916e-12</v>
+      </c>
+      <c r="J1611" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1611" t="inlineStr"/>
+    </row>
+    <row r="1612">
+      <c r="A1612" s="1" t="n">
+        <v>1610</v>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2262.png</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr"/>
+      <c r="D1612" t="inlineStr"/>
+      <c r="E1612" t="inlineStr"/>
+      <c r="F1612" t="inlineStr">
+        <is>
+          <t>*CC(*)NC(=O)C(C)[CH]1(OC)[CH]23C4CC2[CH]413C(=O)N[CH]1(OC)O(C)[CH]23(C)CC(C2)[CH]13N(C)C(=O)[CH]1(N2CC2(=O)N234[CH]56C78C9%10=CC7%11%12%13(=C)C7C(=C)CNC(=O)C%14=CC(OC)=C%15%16(C=C%14N=CN=C[CH]7%14C5%11[CH]82N%146(C9%12)C%10%13)O2C(=C%15(C)OC)O%165C6C(C7C8CO9C=C%10=C3%11%12=C3(C=C(OC)COC89C76)C(=O)C%11=C%103%124)C25)C234C[CH]1(C2)(C3)C4 |$Ph;;;COO2Me;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1612" t="inlineStr"/>
+      <c r="H1612" t="inlineStr"/>
+      <c r="I1612" t="n">
+        <v>1.498750501559381e-08</v>
+      </c>
+      <c r="J1612" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1612" t="inlineStr"/>
+    </row>
+    <row r="1613">
+      <c r="A1613" s="1" t="n">
+        <v>1611</v>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2266.png</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr"/>
+      <c r="D1613" t="inlineStr"/>
+      <c r="E1613" t="inlineStr"/>
+      <c r="F1613" t="inlineStr">
+        <is>
+          <t>[H]C1(CCCCCCCC(=O)NCCC23[NH2+]C2[CH]3245C3N2[CH]3(CCCC(NC23=O=C2(N)C3(=O)NC(=O)NC2=O=C2NCCCCC2NC23(N)=O=C326(=O=C2(C)C)[CH]N6C236C[CH]2(C3)O6)C2367CC289%10%11C3C8(C)(C69)(C7%10)[CH]%1123NC6789=O=C6%10%11%12%13%14=O=7=C2%1067(=O=8=%11=C3N6%12)C(N)[CH]%13(C)N97%14)C42([NH2+])C(C3C4C3N4[CH]C)C25[NH2+])CC(NCC(=O)O)C(O)C(O)C1O</t>
+        </is>
+      </c>
+      <c r="G1613" t="inlineStr"/>
+      <c r="H1613" t="inlineStr"/>
+      <c r="I1613" t="n">
+        <v>6.727694403198388e-14</v>
+      </c>
+      <c r="J1613" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1613" t="inlineStr"/>
+    </row>
+    <row r="1614">
+      <c r="A1614" s="1" t="n">
+        <v>1612</v>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2270.png</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr"/>
+      <c r="D1614" t="inlineStr"/>
+      <c r="E1614" t="inlineStr"/>
+      <c r="F1614" t="inlineStr">
+        <is>
+          <t>CC(O)[CH]NC1(=O)[CH]2(CCCCN)NC3(=O)[CH]4(CC5=CC=C(C(N)=O)C=C5)NC5(=O)[CH]6(CC7=CC=C(O)C=C7)NC(=O)C7CC=CNC[CH]NC(=O)[CH]NC2(=O)[CH]1(CCCCN)NC4(=O)[CH]3(CC1=CC=C(C(N)=O)C=C1)NC6(=O)[CH]5(CC1=CC=C(O)C=C1)NC7(=O)C(N=N)NC(=O)C(N)CC1=CC=C(Cl)C=C1</t>
+        </is>
+      </c>
+      <c r="G1614" t="inlineStr"/>
+      <c r="H1614" t="inlineStr"/>
+      <c r="I1614" t="n">
+        <v>0.04533866498736919</v>
+      </c>
+      <c r="J1614" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1614" t="inlineStr"/>
+    </row>
+    <row r="1615">
+      <c r="A1615" s="1" t="n">
+        <v>1613</v>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2274.png</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr"/>
+      <c r="D1615" t="inlineStr"/>
+      <c r="E1615" t="inlineStr"/>
+      <c r="F1615" t="inlineStr">
+        <is>
+          <t>[H]C1OC(CCSSCC(NC(C)=O)C(=O)NCC(=O)NC(CC2=CC=CC=C2)C(=O)NC(CC2=CC=CC=C2)C(=O)NC(CC2=CC=CC=C2)C(=O)NCC(=O)NCC(=O)CNC23(=O)=O4=C5(NC(CCCCN)C(=O)NCC(N)=O)=O=C=4(C5C(C)C)N245CCC[CH]342CCC25)CCC1OC(=O)[CH]C(O)CC(C)C=CC=O</t>
+        </is>
+      </c>
+      <c r="G1615" t="inlineStr"/>
+      <c r="H1615" t="inlineStr"/>
+      <c r="I1615" t="n">
+        <v>0.01098208079725534</v>
+      </c>
+      <c r="J1615" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1615" t="inlineStr"/>
+    </row>
+    <row r="1616">
+      <c r="A1616" s="1" t="n">
+        <v>1614</v>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2278.png</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr"/>
+      <c r="D1616" t="inlineStr"/>
+      <c r="E1616" t="inlineStr"/>
+      <c r="F1616" t="inlineStr">
+        <is>
+          <t>CCC(C)C(NC(=O)C(NC(=O)C(NC(=O)OCC1=CC=C(NC(=O)C(CCCNC(N)=O)NC(=O)C(NC(=O)CC2C3CC2C3CN2C(=O)C=CC2=O)C(C)C)C=C1)C(C)C)C(C)C)C(CC(=O)[CH]12CCCC1[CH]2(OC)C(C)C(=O)NC(C)C(O)C1=CC=CC=C1)OC</t>
+        </is>
+      </c>
+      <c r="G1616" t="inlineStr"/>
+      <c r="H1616" t="inlineStr"/>
+      <c r="I1616" t="n">
+        <v>0.6359428758097035</v>
+      </c>
+      <c r="J1616" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1616" t="inlineStr"/>
+    </row>
+    <row r="1617">
+      <c r="A1617" s="1" t="n">
+        <v>1615</v>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2282.png</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr"/>
+      <c r="D1617" t="inlineStr"/>
+      <c r="E1617" t="inlineStr"/>
+      <c r="F1617" t="inlineStr">
+        <is>
+          <t>NCCCCC1C2N(C(=O)CCC3=CC=CC=C3)CC(=O)NC(CC3=CC=CC=C3)CN(CC(N)=O)C(=O)CCSCC=CC=CC(=O)NC(CC3=CC=CC=C3)CN34(C(=O)CC5CC5)CC(=O)NC(CC5=CNC6=C5C=CC=C6)CN56CC(=O)N[CH]2(CCCCN)N1C(=O)C5NC6C(CC1=CNC2=C1C=CC=C2)NC(=O)C3NC4(=O)CC1CC1</t>
+        </is>
+      </c>
+      <c r="G1617" t="inlineStr"/>
+      <c r="H1617" t="inlineStr"/>
+      <c r="I1617" t="n">
+        <v>0.1343497052262675</v>
+      </c>
+      <c r="J1617" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1617" t="inlineStr"/>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="1" t="n">
+        <v>1616</v>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2286.png</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr"/>
+      <c r="D1618" t="inlineStr"/>
+      <c r="E1618" t="inlineStr"/>
+      <c r="F1618" t="inlineStr">
+        <is>
+          <t>CC[CH]1(C)[CH]234[CH](CC(=O)N5CCCC5C(OC)C(C)C(=O)NC(C)C(O)C5=CC=CC=C5)(OC)[CH]156[CH]2(C)C1N352CN146(C)C2(=O)C(NC(=O)C(NC(=O)OCC1=CC=C(NC(=O)C(CCCNC(N)=O)NC(=O)C(NC(=O)CCCCCNC(=O)C=CC(=O)O)C(C)C)C=C1)C(C)C)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1618" t="inlineStr"/>
+      <c r="H1618" t="inlineStr"/>
+      <c r="I1618" t="n">
+        <v>0.08900906199006152</v>
+      </c>
+      <c r="J1618" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1618" t="inlineStr"/>
+    </row>
+    <row r="1619">
+      <c r="A1619" s="1" t="n">
+        <v>1617</v>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2290.png</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr"/>
+      <c r="D1619" t="inlineStr"/>
+      <c r="E1619" t="inlineStr"/>
+      <c r="F1619" t="inlineStr">
+        <is>
+          <t>COC=CC=C(C)CC[CH]12C=CC=CC34=CC1(=CC=C3)C(CCC1=CC=C(OC)C(OC)=C1)OC(=O)[CH]1(CCCCN1C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)C(CC(C)C)N(C)C(=O)C1CCCN1C(=O)C(CC1=CC=C(C(=O)NC3=CC=CC=C3)C=C1)NC(=O)C(C1=CC=CC=C1)NC(=O)CCC(=O)N4)C(=O)O2</t>
+        </is>
+      </c>
+      <c r="G1619" t="inlineStr"/>
+      <c r="H1619" t="inlineStr"/>
+      <c r="I1619" t="n">
+        <v>0.2060867265010994</v>
+      </c>
+      <c r="J1619" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1619" t="inlineStr"/>
+    </row>
+    <row r="1620">
+      <c r="A1620" s="1" t="n">
+        <v>1618</v>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2294.png</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr"/>
+      <c r="D1620" t="inlineStr"/>
+      <c r="E1620" t="inlineStr"/>
+      <c r="F1620" t="inlineStr">
+        <is>
+          <t>[H]C1CCCCC1([H])N([CH]C(=O)N[CH]C(=O)NC(C)CSC1(C2=CC=CC=C2)C=CC=CC2=C=C(=C)C2=CC=C1)C(=O)C1CCCN1C(=O)C(CC(C)C)NC(=O)C(COC(C)(C)C)NC(=O)C(CCCNC(=N)NS(=O)(=O)C1=C(C)C(C)=C2OC(C)(C)CC2=C1C)NC(=O)OCC1C2=C(C=CC=C2)C2=C1C=CC=C2</t>
+        </is>
+      </c>
+      <c r="G1620" t="inlineStr"/>
+      <c r="H1620" t="inlineStr"/>
+      <c r="I1620" t="n">
+        <v>0.1679005168574687</v>
+      </c>
+      <c r="J1620" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1620" t="inlineStr"/>
+    </row>
+    <row r="1621">
+      <c r="A1621" s="1" t="n">
+        <v>1619</v>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2298.png</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr"/>
+      <c r="D1621" t="inlineStr"/>
+      <c r="E1621" t="inlineStr"/>
+      <c r="F1621" t="inlineStr">
+        <is>
+          <t>C#CCCCC(=O)NCC1CN(CCCCCNC(=O)CN(CCN)C(=O)Cn2cnc3c(=O)[nH]c(N)nc32)CCN(CCCCCNC(=O)CN(CCN)C(=O)Cn2cnc3c(=O)[nH]c(N)nc32)CCN(CCCCCNC(=O)CN(CCN)C(=O)Cn2cnc3c(=O)[nH]c(N)nc32)CCN1CCCCCNC(=O)CN(CCN)C(=O)Cn1cnc2c(=O)[nH]c(N)cc21</t>
+        </is>
+      </c>
+      <c r="G1621" t="inlineStr"/>
+      <c r="H1621" t="inlineStr"/>
+      <c r="I1621" t="n">
+        <v>0.3562540847350699</v>
+      </c>
+      <c r="J1621" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1621" t="inlineStr"/>
+    </row>
+    <row r="1622">
+      <c r="A1622" s="1" t="n">
+        <v>1620</v>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2302.png</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr"/>
+      <c r="D1622" t="inlineStr"/>
+      <c r="E1622" t="inlineStr"/>
+      <c r="F1622" t="inlineStr">
+        <is>
+          <t>CC(C)CC[CH]1(C)CC(C)CC(CC(N)=O)C1.CCC(C)C.CCC(C)C123=O=C(=O=1)(N2)C3(CC(C)C)N[CH]123C45N6CC478(=O)N[CH]49(CCCNC(=N)N)C1(=O)N51C427CCC(NC2C(CCN)C(=O)(C4NC(C(=O)NC(CCCNC(=N)N)C(=O)NC(CCCNC(N)=O)CC5(=O)NC(CCC(=O)O)C5(CCN)C57(=O)=O=C(N5)O7)C4CN)C2(C)=O)C61938</t>
+        </is>
+      </c>
+      <c r="G1622" t="inlineStr"/>
+      <c r="H1622" t="inlineStr"/>
+      <c r="I1622" t="n">
+        <v>8.907307146623399e-05</v>
+      </c>
+      <c r="J1622" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1622" t="inlineStr"/>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="1" t="n">
+        <v>1621</v>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2306.png</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr"/>
+      <c r="D1623" t="inlineStr"/>
+      <c r="E1623" t="inlineStr"/>
+      <c r="F1623" t="inlineStr">
+        <is>
+          <t>CC(=O)CC(NC(C)=O)C(=O)N1CCCC1.CCC.CCCC1C2C(=O)(NC(CC)C(=O)NC(C)C(=O)NCC(=O)O)N12(C)CCC.CCCC[CH]N(C)C(CC12=CN(CC(=O)O)C13=C2C1=CC=C=13)NC(=O)C(CC)NC1(=O)[CH]2(CCC3=CC=CC=C3)NC3(=O)[CH]4567[H]C3489(CC(O)C5C8C6)C345=O=C796(=O=3)N4C23(=O)[CH]1(C)N356</t>
+        </is>
+      </c>
+      <c r="G1623" t="inlineStr"/>
+      <c r="H1623" t="inlineStr"/>
+      <c r="I1623" t="n">
+        <v>0.001266716476109386</v>
+      </c>
+      <c r="J1623" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1623" t="inlineStr"/>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="1" t="n">
+        <v>1622</v>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2310.png</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr"/>
+      <c r="D1624" t="inlineStr"/>
+      <c r="E1624" t="inlineStr"/>
+      <c r="F1624" t="inlineStr">
+        <is>
+          <t>CO.C[CH]NC[CH]NC1(=O)(=O)=O=C234N5C2(CNC(N)=O)C52[CH]35C[CH]241N5C12=O=C1(NC(=O)C1CCN3C45=O=C3(=O)(NCC[CH]3678C=C([NH2+])C=CC(=C(C)[NH2+])C=C39%10=C3%11%12C%13%14N%15[CH]%139%16%17C69%13O7C93%16([CH]%13%118N1)[CH]%15%14%12%10C%1713=O=C(NC6N7C(CN8C(NCCC9C%10%11%12=O=C9(=O)(C%10)(N%11)N%12)[CH]8(COCCC(C)C)CC8=O9%10=C%11%12C%13=O=C=9%13%11C=%108%12)C67=O)C1N3)(N4)N5)=O=2.O</t>
+        </is>
+      </c>
+      <c r="G1624" t="inlineStr"/>
+      <c r="H1624" t="inlineStr"/>
+      <c r="I1624" t="n">
+        <v>3.777116873155538e-17</v>
+      </c>
+      <c r="J1624" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1624" t="inlineStr"/>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="1" t="n">
+        <v>1623</v>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2314.png</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr"/>
+      <c r="D1625" t="inlineStr"/>
+      <c r="E1625" t="inlineStr"/>
+      <c r="F1625" t="inlineStr">
+        <is>
+          <t>CC(=O)[CH]123CC4C5N6C4(CC1[CH]1(C(=O)N12)C3(=O)NC(CC(N)=O)C1N2C3(NC4C7=C89%10NC%11%12%13=C74C=CC8%1147=C9%12(=CC4=C%10%13C)C7)=O=C123=O)N51C2=O=C61(N)(=O)N2.CCC1CC2C3C(CC4(=O)N5C(=O)(CCC1CCC1C6CC1C6C)N41[CH]46C78C(C[CH]571(C4(=O)O)C6(=O)O)C145=O=C1(=O=4)C85)C23.CCCCCCCC(=O)O.CCNCCO1CC12CN2C(=O)CNC(=O)C(C)O</t>
+        </is>
+      </c>
+      <c r="G1625" t="inlineStr"/>
+      <c r="H1625" t="inlineStr"/>
+      <c r="I1625" t="n">
+        <v>9.01531967896398e-08</v>
+      </c>
+      <c r="J1625" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1625" t="inlineStr"/>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="1" t="n">
+        <v>1624</v>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2318.png</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr"/>
+      <c r="D1626" t="inlineStr"/>
+      <c r="E1626" t="inlineStr"/>
+      <c r="F1626" t="inlineStr">
+        <is>
+          <t>CCCCC1C2(=O)N3C4C(C5=CC6=C(C=CC=C6)C=C5)[CH]356(CC3=CC7=C(C=CC=C7)C=C3)NC(=O)[CH]2(CCCC)N1(C)C(=O)COCC=CC(CCC1=CC(OC)=C(OC)C(F)=C1)OC(=O)C1CCCCN1C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)CNC(=O)[CH]12(COC(C)(C)C)C(O)C3N17(C)C5(=O)N32(C)C476=O</t>
+        </is>
+      </c>
+      <c r="G1626" t="inlineStr"/>
+      <c r="H1626" t="inlineStr"/>
+      <c r="I1626" t="n">
+        <v>0.04593159178966267</v>
+      </c>
+      <c r="J1626" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1626" t="inlineStr"/>
+    </row>
+    <row r="1627">
+      <c r="A1627" s="1" t="n">
+        <v>1625</v>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2326.png</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr"/>
+      <c r="D1627" t="inlineStr"/>
+      <c r="E1627" t="inlineStr"/>
+      <c r="F1627" t="inlineStr">
+        <is>
+          <t>C=CC=CCCC=CN1C(=O)C1(NC1=O=C1)C1N2C3(=O=C12=O)[CH]12(C)[CH]45CN6CCCC6N6(CCCC6(=O)NC(CNC6=O=C6)C(=O)NC(C)=O)C6C7(O)C[CH]6731(C)[CH]42C5(=O)O.CC(C)NC12C3NCC(=O)(O)=O=C(O)CN1C1(=O)[CH]32N12C1C[CH]12(C)NC1CN1C(C)(C)NC(=O)(=O)COC1=O=C1OC1=O=C12=CC=CC=C2.CO.O.O</t>
+        </is>
+      </c>
+      <c r="G1627" t="inlineStr"/>
+      <c r="H1627" t="inlineStr"/>
+      <c r="I1627" t="n">
+        <v>9.831823327540225e-11</v>
+      </c>
+      <c r="J1627" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1627" t="inlineStr"/>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="1" t="n">
+        <v>1626</v>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2330.png</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr"/>
+      <c r="D1628" t="inlineStr"/>
+      <c r="E1628" t="inlineStr"/>
+      <c r="F1628" t="inlineStr">
+        <is>
+          <t>CC(N)C1NC(=O)C(CCCCN)NC(=O)C(CC2=CC=C(NC(N)=O)C=C2)NC(=O)C(CC2=CC=C(O)C=C2)NC(=O)C(NC(=O)C(CC2=CC=C(Cl)C=C2)NC(=O)CCC(C(=O)O)N2345CCN67CCC289%10%11OC(=O)CN82(CC3)(O49)[CH]%10(OC(=O)C6)C752%11)CSSCC(C(=O)NC(CC2=CC=C(O)C=C2)C(N)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1628" t="inlineStr"/>
+      <c r="H1628" t="inlineStr"/>
+      <c r="I1628" t="n">
+        <v>0.001700625404755697</v>
+      </c>
+      <c r="J1628" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1628" t="inlineStr"/>
+    </row>
+    <row r="1629">
+      <c r="A1629" s="1" t="n">
+        <v>1627</v>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2334.png</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr"/>
+      <c r="D1629" t="inlineStr"/>
+      <c r="E1629" t="inlineStr"/>
+      <c r="F1629" t="inlineStr">
+        <is>
+          <t>CC[CH]NC(=O)[C@H](CO)NC(=O)[C@H](C)N(C)C(=O)[C@H](Cc1ccccc1)N(C)C(=O)[C@H](Cc1ccccc1)NC(=O)CSC[C@H](NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@@H](NC(=O)[C@H](CCCCN)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@H](CNc1ccccc1)N(C)C(=O)[CH]C/C=C/NC)C(=O)O)C(=O)NCC(N)=O |^1:2,96|</t>
+        </is>
+      </c>
+      <c r="G1629" t="inlineStr"/>
+      <c r="H1629" t="inlineStr"/>
+      <c r="I1629" t="n">
+        <v>0.4496678626336484</v>
+      </c>
+      <c r="J1629" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1629" t="inlineStr"/>
+    </row>
+    <row r="1630">
+      <c r="A1630" s="1" t="n">
+        <v>1628</v>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2338.png</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr"/>
+      <c r="D1630" t="inlineStr"/>
+      <c r="E1630" t="inlineStr"/>
+      <c r="F1630" t="inlineStr">
+        <is>
+          <t>CCCCCCCCCCCC1C2C13C21C32C13C1(NC(CC4=CNC567=C4C4=CN58C59=C486C=C5C=C97)C(=O)NC(=O)C(C)OC(=O)C(CC(=O)C4=CC=CC=C4N)NC45=O=C(NC(CO)C(=O)NC(=O)CNC(=O)C(CC(=O)O)NC(=O)C(C)NC(=O)C(CC(=O)O)NC(=O)[CH]CCCNC(=O)O[CH]C=CCCC(C)C)(=O=4)[CH]5)=O=C231</t>
+        </is>
+      </c>
+      <c r="G1630" t="inlineStr"/>
+      <c r="H1630" t="inlineStr"/>
+      <c r="I1630" t="n">
+        <v>0.001845312923298185</v>
+      </c>
+      <c r="J1630" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1630" t="inlineStr"/>
+    </row>
+    <row r="1631">
+      <c r="A1631" s="1" t="n">
+        <v>1629</v>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2342.png</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr"/>
+      <c r="D1631" t="inlineStr"/>
+      <c r="E1631" t="inlineStr"/>
+      <c r="F1631" t="inlineStr">
+        <is>
+          <t>CC[CH]1234C(C)[CH]56789C(=O)N%10C%11C(CNC(=O)CC%12%13=C%14%15%16%17%18C%19%20=C%21N%22C%23%24%25(=O)[CH]%26%27(CN)C(=O)NC%28(=O)=O=C%28N%28C%29%30%31=C%32C%28%14%33%34=C%12%15C%16%12=C%21%32%19%29%33%14(=C%20%15=C%17%16%19%20C%17=C(C%16C(=O)NCC%16C%21C%16N%21C(=O)[CH](C5C)(C16(=O)NC(=O)C(C)C)C27(=O)NC1(=O)C(C)(C)[CH]1(C)CNC(=O)NC38=O)C%17%13%19C%12%15%34%20%18%14=O)N%30C%31(=O)NC(=O)C[CH]%231(NC(CN)C(=O)NC49=O)[CH]%22%2423(CN)N4C2(=O)[CH]4%261%25(C)N%273)C%11%10</t>
+        </is>
+      </c>
+      <c r="G1631" t="inlineStr"/>
+      <c r="H1631" t="inlineStr"/>
+      <c r="I1631" t="n">
+        <v>2.026682876817744e-15</v>
+      </c>
+      <c r="J1631" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1631" t="inlineStr"/>
+    </row>
+    <row r="1632">
+      <c r="A1632" s="1" t="n">
+        <v>1630</v>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2346.png</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr"/>
+      <c r="D1632" t="inlineStr"/>
+      <c r="E1632" t="inlineStr"/>
+      <c r="F1632" t="inlineStr">
+        <is>
+          <t>Cc1c(F)cc2nc3c(c4c2c1C=C[C@@H]4NC(=O)CO[C@H]1CCCN1C(=O)CNC(=O)CNC(=O)CNC(=O)CNC(=O)COC1C#CCCCCC1)Cn1c-3cc2c(c1=O)COC(=O)[C@@]2(C)O</t>
+        </is>
+      </c>
+      <c r="G1632" t="inlineStr"/>
+      <c r="H1632" t="inlineStr"/>
+      <c r="I1632" t="n">
+        <v>0.8189183833148606</v>
+      </c>
+      <c r="J1632" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1632" t="inlineStr"/>
+    </row>
+    <row r="1633">
+      <c r="A1633" s="1" t="n">
+        <v>1631</v>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_1/rb_2350.png</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr"/>
+      <c r="D1633" t="inlineStr"/>
+      <c r="E1633" t="inlineStr"/>
+      <c r="F1633" t="inlineStr">
+        <is>
+          <t>C[C@@H](O)[C@@H]1NC(=O)[C@H](CCCCN)NC(=O)[C@@H](Cc2ccc(NC(=O)Nc3ccccc3)cc2)NC(=O)[C@H](Cc2ccc(O)cc2)NC(=O)[C@H](NC(=O)[C@@H](N)Cc2ccc(Cl)cc2)CNC(=O)C[C@@H](C(=O)N[C@H](Cc2ccc(O)cc2)C(N)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1633" t="inlineStr"/>
+      <c r="H1633" t="inlineStr"/>
+      <c r="I1633" t="n">
+        <v>0.7520093687665816</v>
+      </c>
+      <c r="J1633" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1633" t="inlineStr"/>
+    </row>
+    <row r="1634">
+      <c r="A1634" s="1" t="n">
+        <v>1632</v>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2103.png</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr"/>
+      <c r="D1634" t="inlineStr"/>
+      <c r="E1634" t="inlineStr"/>
+      <c r="F1634" t="inlineStr">
+        <is>
+          <t>CCC(C)C12(=O)=O=C(N1)C2(CC(C)C)NC[CH]12345C6N78C9%10=O=C71%11%12%13C17(=O)N(CC%14NCC%14(=O)NC(=O)CNCC(=O)NC(CCCNC(=N)N)NC(=O)NC)[CH]%14%15CCCC%11%16%17(=O)N2[CH]%122(CCCC(=N)N)(C3NC=O=C3NC3(=O)CC(O)CC(=O)NC3(=O)C(CCN)N3C(CC(C)=O)C%14NCC(=O)NC3=CC=CC=C3)N43C9(=O)C8125([CH]%103CCCC(=N)N)N6%16%13C%157%17</t>
+        </is>
+      </c>
+      <c r="G1634" t="inlineStr"/>
+      <c r="H1634" t="inlineStr"/>
+      <c r="I1634" t="n">
+        <v>2.456789531462609e-07</v>
+      </c>
+      <c r="J1634" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1634" t="inlineStr"/>
+    </row>
+    <row r="1635">
+      <c r="A1635" s="1" t="n">
+        <v>1633</v>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2107.png</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr"/>
+      <c r="D1635" t="inlineStr"/>
+      <c r="E1635" t="inlineStr"/>
+      <c r="F1635" t="inlineStr">
+        <is>
+          <t>*NC([H])(C(=O)NC1C(=O)N1C(C(=O)NC(CC1=CN(C)C23=C1C=CC2=C3)C(=O)NC(CCC(=O)O)C(=O)NC(CC(=O)O)C(=O)NC(CC1=CNC2=C1C=CC=C2)C(=O)NCC(=O)NC(C)C(=O)NC(CC12=C3N4=C56=N3=C=4(N15)N26)C(=O)NC(CCNC(=N)N)C(=O)N[CH]C(=O)NC[H])C(C)C)C(C)CC |$A2;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1635" t="inlineStr"/>
+      <c r="H1635" t="inlineStr"/>
+      <c r="I1635" t="n">
+        <v>0.2458337365914597</v>
+      </c>
+      <c r="J1635" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1635" t="inlineStr"/>
+    </row>
+    <row r="1636">
+      <c r="A1636" s="1" t="n">
+        <v>1634</v>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2115.png</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr"/>
+      <c r="D1636" t="inlineStr"/>
+      <c r="E1636" t="inlineStr"/>
+      <c r="F1636" t="inlineStr">
+        <is>
+          <t>[H]C123CCCC14([H])N1C(=O)[CH]5678N9CCC%10%11CC(C%10)[CH]%115%10[CH]5(NC(=O)[CH]14(C2)C3)C61234=O=C576%11(=O=1)N2[CH]C1(=O)N2[CH]57%12N[CH]2%13%14C52(C)C5%15CC2%16%17%18CC2(C5%16)[CH]7%13%175(C[CH]%152%12%14%18C5)C(C(C)CC)NC2(=O)=O=C5(N[CH]936C8(=O)[CH]%104%11CC)N(CC(=O)C(C)CC)[CH]152C*C(C=CC=CC=C)(C1=CC=CC=C1)C1(C2=CC=CC=C2)=CC=CC=C1 |$;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;R;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1636" t="inlineStr"/>
+      <c r="H1636" t="inlineStr"/>
+      <c r="I1636" t="n">
+        <v>3.127623369872342e-07</v>
+      </c>
+      <c r="J1636" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1636" t="inlineStr"/>
+    </row>
+    <row r="1637">
+      <c r="A1637" s="1" t="n">
+        <v>1635</v>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2119.png</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr"/>
+      <c r="D1637" t="inlineStr"/>
+      <c r="E1637" t="inlineStr"/>
+      <c r="F1637" t="inlineStr">
+        <is>
+          <t>CNCC(=O)NC(CCCNC(=N)N)C(=O)NC(CC(=O)O)C(=O)NC(CC1=CC=CC=C1)C(=O)NC(CC(N)=O)C(=O)N(C)C(CC1=CC=CC=C1)C(=O)NC(CSCC(=O)N[CH]123CC4(=CC=CC=C4)C4=CC=CC=C4CC(N1C)C21(=O)N(C3=O)[CH]234C(=O)[CH]5(C2C2C67C(C8N69C6%10%11=N=C9(=N)(N6)(N%10)N87%11)C253)N14)C(=O)NCC(N)=O</t>
+        </is>
+      </c>
+      <c r="G1637" t="inlineStr"/>
+      <c r="H1637" t="inlineStr"/>
+      <c r="I1637" t="n">
+        <v>0.007837795240503147</v>
+      </c>
+      <c r="J1637" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1637" t="inlineStr"/>
+    </row>
+    <row r="1638">
+      <c r="A1638" s="1" t="n">
+        <v>1636</v>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2123.png</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr"/>
+      <c r="D1638" t="inlineStr"/>
+      <c r="E1638" t="inlineStr"/>
+      <c r="F1638" t="inlineStr">
+        <is>
+          <t>[H]C12C3(=O)N[CH]C=NC13([H])[CH]2(O)C=CC(=COC=C(COC=C(Cl)C=CC(O)[CH]NC)OC1OC(CO)C(O)C(O)C1O[CH]12COC3C[CH]314(O)C2C4(C)NC(=S)NCCOCCOCCOCCC123=C4=C56(=C=1N5(C(O)=NC1=CN=C(OCCCC)N=C1N)C26)N3=NC4=NC1(=O)C(NC)C1C(C)C)CO</t>
+        </is>
+      </c>
+      <c r="G1638" t="inlineStr"/>
+      <c r="H1638" t="inlineStr"/>
+      <c r="I1638" t="n">
+        <v>0.0002573992482358107</v>
+      </c>
+      <c r="J1638" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1638" t="inlineStr"/>
+    </row>
+    <row r="1639">
+      <c r="A1639" s="1" t="n">
+        <v>1637</v>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2127.png</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr"/>
+      <c r="D1639" t="inlineStr"/>
+      <c r="E1639" t="inlineStr"/>
+      <c r="F1639" t="inlineStr">
+        <is>
+          <t>[H]C123[H]C(CSC1)(N2C(=O)CC(=O)O)C3(=O)NC(CC1=CNC2=CC=CC=C12)C(=O)NC(C(=O)NC(CC(=O)O)C1=O=C(=O)(NC(CC2=CNC3=CC=CC=C23)C(=O)NC(C(=O)N2CCCC2C(=O)NC(CSCC2=CC=CC(CSC[CH]NC(=O)CNCCN(CCNC)CC(=O)O)=C2)C(N)=O)C(C)C)CN1)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1639" t="inlineStr"/>
+      <c r="H1639" t="inlineStr"/>
+      <c r="I1639" t="n">
+        <v>0.1648737218662975</v>
+      </c>
+      <c r="J1639" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1639" t="inlineStr"/>
+    </row>
+    <row r="1640">
+      <c r="A1640" s="1" t="n">
+        <v>1638</v>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2131.png</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr"/>
+      <c r="D1640" t="inlineStr"/>
+      <c r="E1640" t="inlineStr"/>
+      <c r="F1640" t="inlineStr">
+        <is>
+          <t>CCCCCCCCCCCCCC(=O)NCCCC[CH]NC(=O)CN(C)C(N)C([CH]NC(=O)C(CCC(=O)O)NC(=O)[CH]CC[CH]CCCCN(CCN)CCC1(=O)C(C)C(=O)NC(=O)[CH]NC(=O)C2(C)(NC(=O)N2)C(=O)N(C(=O)CC(N)=O)C2(=O)C3[CH]45N[CH]3(O)(O4)[CH]25NC23=CC45=CC=C4C=C52N13)C1C2=CC=CC=C21</t>
+        </is>
+      </c>
+      <c r="G1640" t="inlineStr"/>
+      <c r="H1640" t="inlineStr"/>
+      <c r="I1640" t="n">
+        <v>1.920371690508818e-05</v>
+      </c>
+      <c r="J1640" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1640" t="inlineStr"/>
+    </row>
+    <row r="1641">
+      <c r="A1641" s="1" t="n">
+        <v>1639</v>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2135.png</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr"/>
+      <c r="D1641" t="inlineStr"/>
+      <c r="E1641" t="inlineStr"/>
+      <c r="F1641" t="inlineStr">
+        <is>
+          <t>CC1(O)[CH]234N5C(=O)C(CCCCN)NC(=O)C(CC6=CC=C(C(N)=O)C=C6)NC(=O)C(CC6=CC=C(O)C=C6)NC(=O)C(NC(=O)C(N)CC6=CC=C(Cl)C=C6)CSSC6[CH]789NC2(=O)[CH]512C3(=O)N[CH]613(C(SC71)[CH]42O)C8(=O)N[CH]124(C(N)=O)CC5(=CC=C(O)C=C5)C5=CC(O)=CC=C5C1C(N2C93=O)C4(N)=O</t>
+        </is>
+      </c>
+      <c r="G1641" t="inlineStr"/>
+      <c r="H1641" t="inlineStr"/>
+      <c r="I1641" t="n">
+        <v>0.005318282989567983</v>
+      </c>
+      <c r="J1641" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1641" t="inlineStr"/>
+    </row>
+    <row r="1642">
+      <c r="A1642" s="1" t="n">
+        <v>1640</v>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2139.png</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr"/>
+      <c r="D1642" t="inlineStr"/>
+      <c r="E1642" t="inlineStr"/>
+      <c r="F1642" t="inlineStr">
+        <is>
+          <t>C1CO12C13=O=C2(N1)O3.CC(O)C(O)[CH]C1O[CH]1(O)C(O)[CH]O[CH]C(O)C(O)C(O)C(O)C1OC1O.C[CH]12O[CH]13[CH]1(O)[CH]34(O)[CH]35(O)[CH]2(C2O[CH]2(O)C2OC2C2O[CH]26OC6O)[CH]3(O)[CH]145O.[CH]OCC(O)[CH]OCO1CC1NC12OC3(O1)C2O3C(O)[CH]OCO</t>
+        </is>
+      </c>
+      <c r="G1642" t="inlineStr"/>
+      <c r="H1642" t="inlineStr"/>
+      <c r="I1642" t="n">
+        <v>3.756790725613567e-25</v>
+      </c>
+      <c r="J1642" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1642" t="inlineStr"/>
+    </row>
+    <row r="1643">
+      <c r="A1643" s="1" t="n">
+        <v>1641</v>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2147.png</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr"/>
+      <c r="D1643" t="inlineStr"/>
+      <c r="E1643" t="inlineStr"/>
+      <c r="F1643" t="inlineStr">
+        <is>
+          <t>CC=CC=CCCOC(C12CC1O2)C(CNCCCCNC(=O)CCC(=O)NC1=O=C1C)(OCCC=CC=CC)(C1=CC2=CC=21)C1CO1.CCCOCCNCCOCCC(O)CCCCCNC[CH]1(CC(=O)O)C2C(OCCC3CC3CCCOCCCNC(=O)COCCC)C21.CO.O.O=CNCCC1NC(CCCC2CC(CCCCCCCCCC(=O)O)C2)=O=C1(=O)O</t>
+        </is>
+      </c>
+      <c r="G1643" t="inlineStr"/>
+      <c r="H1643" t="inlineStr"/>
+      <c r="I1643" t="n">
+        <v>1.240178575397199e-11</v>
+      </c>
+      <c r="J1643" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1643" t="inlineStr"/>
+    </row>
+    <row r="1644">
+      <c r="A1644" s="1" t="n">
+        <v>1642</v>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2151.png</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr"/>
+      <c r="D1644" t="inlineStr"/>
+      <c r="E1644" t="inlineStr"/>
+      <c r="F1644" t="inlineStr">
+        <is>
+          <t>CC[C@@]1(O)C(=O)OCc2c1cc1n(c2=O)Cc2c-1nc1cc(F)c(NC(=O)CNC(=O)[C@H](Cc3ccccc3)NC(=O)CNC(=O)CNC(=O)OC(C)(C)C)cc1c2CN1CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1644" t="inlineStr"/>
+      <c r="H1644" t="inlineStr"/>
+      <c r="I1644" t="n">
+        <v>0.8017438960655838</v>
+      </c>
+      <c r="J1644" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1644" t="inlineStr"/>
+    </row>
+    <row r="1645">
+      <c r="A1645" s="1" t="n">
+        <v>1643</v>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2155.png</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr"/>
+      <c r="D1645" t="inlineStr"/>
+      <c r="E1645" t="inlineStr"/>
+      <c r="F1645" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1645" t="inlineStr"/>
+      <c r="H1645" t="inlineStr"/>
+      <c r="I1645" t="n">
+        <v>1.263430249072084e-125</v>
+      </c>
+      <c r="J1645" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1645" t="inlineStr"/>
+    </row>
+    <row r="1646">
+      <c r="A1646" s="1" t="n">
+        <v>1644</v>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2159.png</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr"/>
+      <c r="D1646" t="inlineStr"/>
+      <c r="E1646" t="inlineStr"/>
+      <c r="F1646" t="inlineStr">
+        <is>
+          <t>C=C1=C2=C34=C2(=C3)(C=C1I)N41C2=C345=C=C26=C1=C3(C4N1C(CO)C1N=C=O)N5C(C(=O)NC(CC=CC=C(O)O)C(=O)NC(CCCCN)C(=O)C(CC1=CNC2=CC2=CC(O)=C1)NCC(=O)NC(C(=O)NC(CSCC(=O)NC(CC1=CC=C(C(=O)O)C=C1)C(=O)N(C)[CH]CCC1CCC1C=CC)C(N)=O)C(C)C)C6.CCC</t>
+        </is>
+      </c>
+      <c r="G1646" t="inlineStr"/>
+      <c r="H1646" t="inlineStr"/>
+      <c r="I1646" t="n">
+        <v>0.0007221111962311633</v>
+      </c>
+      <c r="J1646" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1646" t="inlineStr"/>
+    </row>
+    <row r="1647">
+      <c r="A1647" s="1" t="n">
+        <v>1645</v>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2163.png</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr"/>
+      <c r="D1647" t="inlineStr"/>
+      <c r="E1647" t="inlineStr"/>
+      <c r="F1647" t="inlineStr">
+        <is>
+          <t>CCCCCCCCCC1=O=C2(CC2CC(=O)NCCCCOCCOCCOCC2C3(O)C24OC34(O)[CH]234(CC(O)C56(O)CC5OC6CCOCCOCCCCCCOCCNCCCC5CC5CNCCNCCCCC5C6C57C5C(C8CC8C(N)CC(CCC(=O)O)N[CH][CH]N[CH]CN[CH]CN8[CH]C8NCC8CC8C)C657)(OC)O[CH]25[CH]3(O)[CH]54O)N1</t>
+        </is>
+      </c>
+      <c r="G1647" t="inlineStr"/>
+      <c r="H1647" t="inlineStr"/>
+      <c r="I1647" t="n">
+        <v>7.74803110242752e-17</v>
+      </c>
+      <c r="J1647" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1647" t="inlineStr"/>
+    </row>
+    <row r="1648">
+      <c r="A1648" s="1" t="n">
+        <v>1646</v>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2167.png</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr"/>
+      <c r="D1648" t="inlineStr"/>
+      <c r="E1648" t="inlineStr"/>
+      <c r="F1648" t="inlineStr">
+        <is>
+          <t>*N123=C45=C1(=CC=C4)C=521C3N1[CH]C[CH]N1C2C(O)[CH]21(O)C(C)N[CH]C(=O)NCC12C3C1[CH]32CCC.CC(=O)NCCCC(C=O)N[CH]1234C567C89%10C1%11%12%13N[CH]CCCC=C1%14%15C%16CC%17=C%18%19=C%171%20=C%181%17%21%22%23(=CC=CC=1)(=C1%18=C%17%24%25=C=%21%17%26=C%24(=C%17C%19)C=%26%25%22%17=C1%23%19=CC=C=%18=%19%171C%17C%14[CH]%16%201N%17%15)C=C[CH]NC=8521=C=69%1132N1(C%12C(=O)N1C3(=O=C(=O)(CCC(N)=O)N3)[CH]13CCCC3)C=%10=7%1342 |$Rb;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1648" t="inlineStr"/>
+      <c r="H1648" t="inlineStr"/>
+      <c r="I1648" t="n">
+        <v>1.869609775407658e-17</v>
+      </c>
+      <c r="J1648" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1648" t="inlineStr"/>
+    </row>
+    <row r="1649">
+      <c r="A1649" s="1" t="n">
+        <v>1647</v>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2171.png</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr"/>
+      <c r="D1649" t="inlineStr"/>
+      <c r="E1649" t="inlineStr"/>
+      <c r="F1649" t="inlineStr">
+        <is>
+          <t>C=CC=C/C=C\C[CH]NC(=O)[C@@H](CCCNC(=N)N)NC(=O)[C@H](CCCCNC(C)C)NC(=O)[C@H](Cc1ccc(O)cc1)NC(=O)[C@H](CCCCNC(=O)[C@H](CS(=O)(=O)O)NC(=O)CN1CCN(CC(=O)O)CCN(CC(=O)O)CCN(CC(=O)O)CC1)n1c(C)c2ccccc2c1SC[CH]C(=O)N[C@@H](CCCCNC(C)C)C(N)=O |^1:7,100|</t>
+        </is>
+      </c>
+      <c r="G1649" t="inlineStr"/>
+      <c r="H1649" t="inlineStr"/>
+      <c r="I1649" t="n">
+        <v>0.6830061548009632</v>
+      </c>
+      <c r="J1649" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1649" t="inlineStr"/>
+    </row>
+    <row r="1650">
+      <c r="A1650" s="1" t="n">
+        <v>1648</v>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2175.png</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr"/>
+      <c r="D1650" t="inlineStr"/>
+      <c r="E1650" t="inlineStr"/>
+      <c r="F1650" t="inlineStr">
+        <is>
+          <t>O.[H]C12CNCC(CNC(CC(C)C)C3(=O)N45CC(O)CN34C5(=O)N[CH]C(=O)N3C(CC3C(=O)NC3CC4=CN(CC(=O)O)C5=C4C=C(C=C5)C(C)CCC(C(=O)N(C)C(CCCC)C(=O)N[CH]CC(C)C)N(C)C3=O)NC(CC3=CC=C(O)C=C3)C(=O)N(C)C(C)C(=O)NC(CC(N)=O)CN1CC)NC2(=O)=O</t>
+        </is>
+      </c>
+      <c r="G1650" t="inlineStr"/>
+      <c r="H1650" t="inlineStr"/>
+      <c r="I1650" t="n">
+        <v>0.1526817833254441</v>
+      </c>
+      <c r="J1650" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1650" t="inlineStr"/>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="1" t="n">
+        <v>1649</v>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2179.png</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr"/>
+      <c r="D1651" t="inlineStr"/>
+      <c r="E1651" t="inlineStr"/>
+      <c r="F1651" t="inlineStr">
+        <is>
+          <t>[H]C1=CN1C(CNC1=C(OCC)C2(=O)=O=C12)C(=O)NC(C(=O)N1CC(O)CC1([H])NC(=O)[CH]CC=CC1=C2(N(C=CC34C56CC3(C5)C6[CH]4(NC)C(=O)N3(C)[CH]4(CC)C5=O=C4(=O)(N[CH]C(=O)NC(CSCC(=O)NC4=C(OCC)C(=O)C4=O)C(=O)NCC(N)=O)[CH]53CCC)CC(=O)CC)C=C3C2=C=C3=CC=C1)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1651" t="inlineStr"/>
+      <c r="H1651" t="inlineStr"/>
+      <c r="I1651" t="n">
+        <v>0.0006434096030940223</v>
+      </c>
+      <c r="J1651" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1651" t="inlineStr"/>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="1" t="n">
+        <v>1650</v>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2183.png</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr"/>
+      <c r="D1652" t="inlineStr"/>
+      <c r="E1652" t="inlineStr"/>
+      <c r="F1652" t="inlineStr">
+        <is>
+          <t>C1=CC=CC=C1.CC(C)(C)OCC(NC(=O)OCC1C2=C(C=CC=C2)C2=C1C=CC=C2)C(=O)N1[CH]234N5(C(=O)[CH]CO)C2678=O=C329%10%11=O=C43%12(=O=2)N69[CH]73%10N[CH]158%12%11.CCNC(=N)NS(=O)(=O)C1=C(C(F)(F)F)C(C)=C2OC(C)(C)CC2=C1C.[H]C1CCCCC1([H])C(=O)C1CCCN1C(=O)C(CC(C)C)NC(=O)[CH]COC(C)(C)C</t>
+        </is>
+      </c>
+      <c r="G1652" t="inlineStr"/>
+      <c r="H1652" t="inlineStr"/>
+      <c r="I1652" t="n">
+        <v>0.01206724897953146</v>
+      </c>
+      <c r="J1652" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1652" t="inlineStr"/>
+    </row>
+    <row r="1653">
+      <c r="A1653" s="1" t="n">
+        <v>1651</v>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2187.png</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr"/>
+      <c r="D1653" t="inlineStr"/>
+      <c r="E1653" t="inlineStr"/>
+      <c r="F1653" t="inlineStr">
+        <is>
+          <t>C=CCNC12(=O)N3[CH]4(CCCNC(=O)CCO5C6O7C(CCC(=O)O8CCOC8C8CN8C(=O)C(O)CC(=O)O)C657)C5(=O)[CH]1(CCCNC(=O)CCOC1C6C(CCC(=O)O7C(CNC(=O)[CH]8(O)OC8C(=O)O)O8CC87)O16)C34(=O)N52[CH]C(=O)C(CC(N)=O)NC(C(=O)NC(=O)C(CC123=CNC45=C16C=CC=CC4=C5C62=O3)NC(=O)[CH]C)C(C)O</t>
+        </is>
+      </c>
+      <c r="G1653" t="inlineStr"/>
+      <c r="H1653" t="inlineStr"/>
+      <c r="I1653" t="n">
+        <v>1.387812566109323e-07</v>
+      </c>
+      <c r="J1653" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1653" t="inlineStr"/>
+    </row>
+    <row r="1654">
+      <c r="A1654" s="1" t="n">
+        <v>1652</v>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2191.png</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr"/>
+      <c r="D1654" t="inlineStr"/>
+      <c r="E1654" t="inlineStr"/>
+      <c r="F1654" t="inlineStr">
+        <is>
+          <t>C[CH]C(O)[CH]OCCNC(=O)C123=O4=C56C(C(=O)NCCC7C8C79C7C%10(C%11C%10C%11(=O)NC(=O)C%10%11=O=C%12%13%14%15%16%17(=O)(C%18%19%20%21(=O)C%12%22%23%24%25(=O)O%12%26%27C%10%18%13%28%29%30(=O)C%22%14%10%13%18(=O)C%12%19%23%28%15%14(=O)C%26%20%24%10%29%16%12%15=O=C%27%21%25%13%30%14%17(=O=%12)O%18%15)N%11)C879)N5C=4615N2C351CN1C(=O)[CH]NCCNCCCNCC1CN1C(=O)CC1C2C13C1C(C4C56=O=C45N64CC4C(=O)NC4[CH]5(O)O[CH]56[CH]5(O)[CH]4(CO)[CH]56O)C213.[CH]C1=O=C23C4N(C=O)C42N13</t>
+        </is>
+      </c>
+      <c r="G1654" t="inlineStr"/>
+      <c r="H1654" t="inlineStr"/>
+      <c r="I1654" t="n">
+        <v>1.227530128368963e-19</v>
+      </c>
+      <c r="J1654" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1654" t="inlineStr"/>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="1" t="n">
+        <v>1653</v>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2195.png</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr"/>
+      <c r="D1655" t="inlineStr"/>
+      <c r="E1655" t="inlineStr"/>
+      <c r="F1655" t="inlineStr">
+        <is>
+          <t>CC(=O)C[CH]C(CC1=CC=CC=C1)NC(C)=O.CCC(C)C123=O=C(=O=1)(N2)C312456(=O)=O=C378(N1)N219C2%10%11%12=O=C1%13%14%15=O=C91%16(=O)(C9=O=C314(=O)N9)(N2%131C23=O=C14(C2(=O)NC1(=O)C2N9C(C(C)C%13=O=C(CC(C)C)N%13)[CH]2(CNC(=O)C(CC(C)C)NC=O)C91)C12=O=C4%107%14%165(=O=1)N32%11)N%128%156.CCCN1C2CCCC(=O)(O)OC(=O)CC[CH]21CC(=O)NC(C=O)CCCNC(C)=O</t>
+        </is>
+      </c>
+      <c r="G1655" t="inlineStr"/>
+      <c r="H1655" t="inlineStr"/>
+      <c r="I1655" t="n">
+        <v>4.435402096523396e-12</v>
+      </c>
+      <c r="J1655" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1655" t="inlineStr"/>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="1" t="n">
+        <v>1654</v>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2199.png</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr"/>
+      <c r="D1656" t="inlineStr"/>
+      <c r="E1656" t="inlineStr"/>
+      <c r="F1656" t="inlineStr">
+        <is>
+          <t>[CH]NC(CC(C)C)NC(=O)CNC(CC(C)C)C(=O)N[CH]CC(C)CC(NCCN)C(CC(C)C)[CH]123CCC4N56C(CC1C2N[CH]3(CC(C)C)C1CCC2N37C(CCC(NC(CC(C)C)N[CH]8(CC(C)C)C9CCCN8[CH]98(CC(C)C)NC8[CH]8(NCC9=CC=CC=C9)CC(C)C8)N1)N21C328=N=C71(=N)(N2)N8)N41C523=N=C61(=N)(N2)N3</t>
+        </is>
+      </c>
+      <c r="G1656" t="inlineStr"/>
+      <c r="H1656" t="inlineStr"/>
+      <c r="I1656" t="n">
+        <v>0.0001374931030430136</v>
+      </c>
+      <c r="J1656" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1656" t="inlineStr"/>
+    </row>
+    <row r="1657">
+      <c r="A1657" s="1" t="n">
+        <v>1655</v>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2207.png</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr"/>
+      <c r="D1657" t="inlineStr"/>
+      <c r="E1657" t="inlineStr"/>
+      <c r="F1657" t="inlineStr">
+        <is>
+          <t>CCC.CCCCCCCCCCCC(C(=O)N12C(=O)C13C1C3C12)[CH]1234(CCCNCCCOCCC(=O)NCCOCCCOC(=O)NCCCC5C(=O)C5NC(=O)CCC5NC6(C(=O)O)[CH]7(C8C9=CC=CC=C9867)C56=O=C(=O)([CH]NC(=O)[CH]CC(C)[CH]CCC=CC=CC=C(C)CCCCC)N6)C5(=O)N6C7(=O)C8C7C8(=O)C178(CCCCCCCC)=O=C72[CH]583C64=O</t>
+        </is>
+      </c>
+      <c r="G1657" t="inlineStr"/>
+      <c r="H1657" t="inlineStr"/>
+      <c r="I1657" t="n">
+        <v>1.680493496430868e-11</v>
+      </c>
+      <c r="J1657" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1657" t="inlineStr"/>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="1" t="n">
+        <v>1656</v>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2211.png</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr"/>
+      <c r="D1658" t="inlineStr"/>
+      <c r="E1658" t="inlineStr"/>
+      <c r="F1658" t="inlineStr">
+        <is>
+          <t>COC1=CC=C(CC[CH]23C=CC=C4=C5=CC46=CC2(=C5)C(CCC2=CC=C(OC)C(OC)=C2)OC(=O)[CH]2(CCCCN2C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)C(CC(C)C)N(C)C(=O)C2CCCN2C(=O)C(CC2=CC=C(CC(=O)OC(C)(C)C)C=C2)NC(=O)C(C2=CC=CC=C2)NC(=O)CCC(=O)N6)C(=O)O3)C=C1O</t>
+        </is>
+      </c>
+      <c r="G1658" t="inlineStr"/>
+      <c r="H1658" t="inlineStr"/>
+      <c r="I1658" t="n">
+        <v>0.1473881486467629</v>
+      </c>
+      <c r="J1658" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1658" t="inlineStr"/>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="1" t="n">
+        <v>1657</v>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2215.png</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr"/>
+      <c r="D1659" t="inlineStr"/>
+      <c r="E1659" t="inlineStr"/>
+      <c r="F1659" t="inlineStr">
+        <is>
+          <t>NCCCCC1NC2(=O)[CH]3(CC4=CC=C(NS(=O)(=O)C5=CC=CC=C5)C=C4)NC4(=O)[CH]56NC(=O)[CH]7(NC(=O)C(N)CC8=CC=C(Cl)C=C8)CSSC[CH]NC(=O)[CH]NC1(=O)C(CCCCN)NC3(=O)[CH]2(CC1=CC=C(NS(=O)(=O)C2=CC=CC=C2)C=C1)NC5(=O)[CH]4(CC1=CC=C(O)C=C1)(NC7=O)C6C1=CC=C(O)C=C1</t>
+        </is>
+      </c>
+      <c r="G1659" t="inlineStr"/>
+      <c r="H1659" t="inlineStr"/>
+      <c r="I1659" t="n">
+        <v>0.004737675350129884</v>
+      </c>
+      <c r="J1659" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1659" t="inlineStr"/>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="1" t="n">
+        <v>1658</v>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2223.png</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr"/>
+      <c r="D1660" t="inlineStr"/>
+      <c r="E1660" t="inlineStr"/>
+      <c r="F1660" t="inlineStr">
+        <is>
+          <t>C[CH]NC(=O)C(CSC1C234=C5C6=C2C512=C3C(=C=24)CSCC(C(N)=O)NC(=O)C(C(C)(C)C)NC(=O)C(CC)NC(=O)C(CC1=CC=C(O)C=C1)NC(=O)C(CC1=CC=CC=C1)NC(=O)C(CC(=O)O)NC(=O)C(CCC(=O)O)NC(=O)[CH]CSC6)NC(=O)CN1CCN(CC(=O)O)CCN(CC(=O)O)CCN2(CC(=O)O)CC12</t>
+        </is>
+      </c>
+      <c r="G1660" t="inlineStr"/>
+      <c r="H1660" t="inlineStr"/>
+      <c r="I1660" t="n">
+        <v>0.05776554101913565</v>
+      </c>
+      <c r="J1660" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1660" t="inlineStr"/>
+    </row>
+    <row r="1661">
+      <c r="A1661" s="1" t="n">
+        <v>1659</v>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2227.png</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr"/>
+      <c r="D1661" t="inlineStr"/>
+      <c r="E1661" t="inlineStr"/>
+      <c r="F1661" t="inlineStr">
+        <is>
+          <t>CNCCCC[C@@H]1NC(=O)[C@@H](Cc2ccc(NC(=O)Nc3ccccc3)cc2)NC(=O)[C@H](Cc2ccc(O)cc2)NC(=O)[C@H](NC(=O)[C@@H](N)Cc2ccc(Cl)cc2)CSCC[C@@H](C(=O)N[C@@H](Cc2ccc(O)cc2)C(N)=O)NC(=O)[C@H](C(C)(C)O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1661" t="inlineStr"/>
+      <c r="H1661" t="inlineStr"/>
+      <c r="I1661" t="n">
+        <v>0.7026599374404106</v>
+      </c>
+      <c r="J1661" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1661" t="inlineStr"/>
+    </row>
+    <row r="1662">
+      <c r="A1662" s="1" t="n">
+        <v>1660</v>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2231.png</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr"/>
+      <c r="D1662" t="inlineStr"/>
+      <c r="E1662" t="inlineStr"/>
+      <c r="F1662" t="inlineStr">
+        <is>
+          <t>NCCCCC1NC2(=O)[CH]34NC5(=O)[CH]6(CC7=CC=C(O)C=C7)NC(=O)C7CSSC[CH]8(C(=O)NC(CC9=CC=C(O)C=C9)C(N)=O)NC(=O)C(NC1(=O)C(CCCCN)NC3(=O)[CH]21(CC2=CC=C(C=C2)NC(=O)[CH](N)(CO)C(=O)(C(N)CO)NC2=CC=C(C=C2)C41)NC6(=O)[CH]5(CC1=CC=C(O)C=C1)NC7=O)C8O</t>
+        </is>
+      </c>
+      <c r="G1662" t="inlineStr"/>
+      <c r="H1662" t="inlineStr"/>
+      <c r="I1662" t="n">
+        <v>0.003975926955749906</v>
+      </c>
+      <c r="J1662" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1662" t="inlineStr"/>
+    </row>
+    <row r="1663">
+      <c r="A1663" s="1" t="n">
+        <v>1661</v>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2235.png</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr"/>
+      <c r="D1663" t="inlineStr"/>
+      <c r="E1663" t="inlineStr"/>
+      <c r="F1663" t="inlineStr">
+        <is>
+          <t>CC[C@H](C)[C@@H]([C@@H](C[C@H](OC)N1C(=O)C[C@H]1[C@H](OC)[C@@H](C)C(=O)N[C@H](C)[C@@H](O)c1ccccc1)OC)N(C)C(=O)[C@@H](NC(=O)[C@H](C(C)C)N(C)C(=O)OCc1ccc(NC(=O)[C@H](C)NC(=O)[C@@H](NC(=O)CCCCCNC(=O)/C=C/C(=O)OC)C(C)C)cc1)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1663" t="inlineStr"/>
+      <c r="H1663" t="inlineStr"/>
+      <c r="I1663" t="n">
+        <v>0.3033873086123886</v>
+      </c>
+      <c r="J1663" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1663" t="inlineStr"/>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="1" t="n">
+        <v>1662</v>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2239.png</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr"/>
+      <c r="D1664" t="inlineStr"/>
+      <c r="E1664" t="inlineStr"/>
+      <c r="F1664" t="inlineStr">
+        <is>
+          <t>CC[CH]NC(=O)C(CO)NC(=O)C(CC1=CC=CC=C1)N(C)C=O.[CH]C(=O)N(C)CC(=O)NC(CCCNC(=N)N)C(=O)NC(CCCCN)C(=O)N1CC2=C(C=CC=C2)CC1C(=O)NC(CC(N)=O)C(=O)N(C)C(=O)C(CC1=CC=CC=C1)C(CSCC(=O)N[CH]1(CC2=CC=CC=C2)C23=O=C1(=O=2)N3)C(=O)NCC(N)=O</t>
+        </is>
+      </c>
+      <c r="G1664" t="inlineStr"/>
+      <c r="H1664" t="inlineStr"/>
+      <c r="I1664" t="n">
+        <v>0.440787556871108</v>
+      </c>
+      <c r="J1664" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1664" t="inlineStr"/>
+    </row>
+    <row r="1665">
+      <c r="A1665" s="1" t="n">
+        <v>1663</v>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2243.png</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr"/>
+      <c r="D1665" t="inlineStr"/>
+      <c r="E1665" t="inlineStr"/>
+      <c r="F1665" t="inlineStr">
+        <is>
+          <t>[H]C12NC(=O)NC13([H])CS[CH]21CCCCC(=O)NCCOCCOCCOCC(=O)N2C(=O)(COCCOCCOCCNC(=O)CCCCC4SCC5([H])NC(=O)NC4513[H])N[CH]21CC2=CN3CCCCC4N5C6(=O)C7CCNC8(=CC=CC=C8)NCCC6C7(=O)N[CH]5(C(N)=O)(CCCCN56C=C(C1)(N=N5)N2=N36)C4(N)=O</t>
+        </is>
+      </c>
+      <c r="G1665" t="inlineStr"/>
+      <c r="H1665" t="inlineStr"/>
+      <c r="I1665" t="n">
+        <v>0.01631566757602801</v>
+      </c>
+      <c r="J1665" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1665" t="inlineStr"/>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="1" t="n">
+        <v>1664</v>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2247.png</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr"/>
+      <c r="D1666" t="inlineStr"/>
+      <c r="E1666" t="inlineStr"/>
+      <c r="F1666" t="inlineStr">
+        <is>
+          <t>CCC123=OC4(=O=1)C2(O)C12=C(CO413)C(=O)CC1=C(CCN(C(=O)OC3(CCN(C)C(=O)CNC(=O)COC(=O)CN(C)C(=O)CN(C)C(=O)C(=O)COC(=O)CCC(=O)CN(C)C(=O)CN(C)C(=O)COC(C)=O)C4=C5C(NC(=O)C(C)NC(=O)C(NC(=O)CCCCCN6C(=O)C=CC6=O)C(C)C)=CC=C543)C(C)C)C3=CC=CC=C3N=C1C=C2</t>
+        </is>
+      </c>
+      <c r="G1666" t="inlineStr"/>
+      <c r="H1666" t="inlineStr"/>
+      <c r="I1666" t="n">
+        <v>0.2063690527292111</v>
+      </c>
+      <c r="J1666" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1666" t="inlineStr"/>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="1" t="n">
+        <v>1665</v>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2255.png</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr"/>
+      <c r="D1667" t="inlineStr"/>
+      <c r="E1667" t="inlineStr"/>
+      <c r="F1667" t="inlineStr">
+        <is>
+          <t>CCOC1=CC=C(N2[CH]3(NC(=O)C(NC(C)C(=O)[CH]N[CH]456(C(C)C)N78C9C%10%11CC%10%12(=O)CC(C)[CH]%10(N%11%12)[CH]%11%12%13%14CC%15=CNC%16%17=C%15%18C=CC=C%16%15(C)CC%16=CC=CC%19=C%16%17%15NC=C%19%18C[CH]7%114%15[CH]8%125(O)[CH]9%10%136%15O%14)NC(CCCCC[CH]NC(C)=O)C(C)NC=O)C45=O=C3(=O)NC36(=O)C7(=CC8=CC=C=87)C37=CC3=C8C=C=37N8[CH]246C(=O)N5)C=C1</t>
+        </is>
+      </c>
+      <c r="G1667" t="inlineStr"/>
+      <c r="H1667" t="inlineStr"/>
+      <c r="I1667" t="n">
+        <v>6.211473658711633e-12</v>
+      </c>
+      <c r="J1667" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1667" t="inlineStr"/>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="1" t="n">
+        <v>1666</v>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2259.png</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr"/>
+      <c r="D1668" t="inlineStr"/>
+      <c r="E1668" t="inlineStr"/>
+      <c r="F1668" t="inlineStr">
+        <is>
+          <t>CCCCC1C2(=O)N3C4C(C5=CC6=C(C=CC=C6)C=C5)[CH]356(CC3=CC7=C(C=CC=C7)C=C3)NC(=O)[CH]2(CCCC)N1(C)C(=O)COCC=CC(CCC1=CC(OC)=C(OC)C(OC)=C1)OC(=O)C1CCCCN1C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)CNC(=O)[CH]12(COC(C)(C)C)CC3N17(C)C5(=O)N32(C)C476=O</t>
+        </is>
+      </c>
+      <c r="G1668" t="inlineStr"/>
+      <c r="H1668" t="inlineStr"/>
+      <c r="I1668" t="n">
+        <v>0.04448014166859854</v>
+      </c>
+      <c r="J1668" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1668" t="inlineStr"/>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="1" t="n">
+        <v>1667</v>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2263.png</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr"/>
+      <c r="D1669" t="inlineStr"/>
+      <c r="E1669" t="inlineStr"/>
+      <c r="F1669" t="inlineStr">
+        <is>
+          <t>CCC(C)C(C(CC(=O)N1CCCC1C(OC(C)=O)C(C)C(O)NC(CC1=CC=CC=C1)C(=O)O)OC)N(C)C(=O)C(NC(=O)C(C(C)C)N(C)C(=O)OCC1=CC=C(NC(=O)C(CCCNC(N)=O)NC(=O)C(NC(=O)CCCCCN2C(=O)C=C2=O)C(C)C)C=C1)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1669" t="inlineStr"/>
+      <c r="H1669" t="inlineStr"/>
+      <c r="I1669" t="n">
+        <v>0.5240427839390199</v>
+      </c>
+      <c r="J1669" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1669" t="inlineStr"/>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="1" t="n">
+        <v>1668</v>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2267.png</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr"/>
+      <c r="D1670" t="inlineStr"/>
+      <c r="E1670" t="inlineStr"/>
+      <c r="F1670" t="inlineStr">
+        <is>
+          <t>C=CC(=O)OCC(C)(C)C1(=O)C(=O)N2CCCCC2C2(=O)OC(CCC3=CC=C(OC)C(OC)=C3)C3C=CNC(=O)CCC(=O)N[CH]C(=O)NC(CC4=CC(NC(C)=O)=CC=C4)C(=O)N4CCCC4C(=O)N(C)C(CC(C)C)C(=O)N(C)CCC=CC(=O)OCC1(C)(C)C(=O)C(=O)N1CCCC[CH]12C(=O)OC3CCC=CC=COC</t>
+        </is>
+      </c>
+      <c r="G1670" t="inlineStr"/>
+      <c r="H1670" t="inlineStr"/>
+      <c r="I1670" t="n">
+        <v>0.2291293925937282</v>
+      </c>
+      <c r="J1670" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1670" t="inlineStr"/>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="1" t="n">
+        <v>1669</v>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2271.png</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr"/>
+      <c r="D1671" t="inlineStr"/>
+      <c r="E1671" t="inlineStr"/>
+      <c r="F1671" t="inlineStr">
+        <is>
+          <t>[H]C12345[H]C6(C7CC8=C(CNC(=O)CC(NC(C)(C)C)C(=O)NC(C)C(=O)NC(CC9=CNC%10=C9C=CC=C%10)C(=O)NC(CC9=CNC=N9)C(=O)NC(CC(C)C)C(=O)NCC(=O)NC(CCC(=O)O)C(=O)NC(CC(C)C)C(=O)NC(C=O)C(C)C)C=CC=C87)(C1(N)=O=C2(N)=O)[CH]31(C)O[CH]4237C[CH]65(C2)(O3)O17</t>
+        </is>
+      </c>
+      <c r="G1671" t="inlineStr"/>
+      <c r="H1671" t="inlineStr"/>
+      <c r="I1671" t="n">
+        <v>0.1066637538975981</v>
+      </c>
+      <c r="J1671" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1671" t="inlineStr"/>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="1" t="n">
+        <v>1670</v>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2275.png</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr"/>
+      <c r="D1672" t="inlineStr"/>
+      <c r="E1672" t="inlineStr"/>
+      <c r="F1672" t="inlineStr">
+        <is>
+          <t>C=CC(=O)NC=CCNC(=O)C=C(NC=CC=CC(=O)NCCNC(=O)CCCC(C)C(O)C1C2=ON1CCC(C)CC(C(=O)N[CH]C(=O)NC(C)C(=O)N1CCC(C)CC1C1(=O)N34C5C6C78(C)CC69(C7)C6[CH]37%10C(=O)[CH]64(C897)N51%10C)NCCC1CCC1NC(=O)C(CCC)N(C)C(=O)CN(C)C(=O)C(CC)N2)C(F)(F)F</t>
+        </is>
+      </c>
+      <c r="G1672" t="inlineStr"/>
+      <c r="H1672" t="inlineStr"/>
+      <c r="I1672" t="n">
+        <v>0.00843251284335933</v>
+      </c>
+      <c r="J1672" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1672" t="inlineStr"/>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="1" t="n">
+        <v>1671</v>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2279.png</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr"/>
+      <c r="D1673" t="inlineStr"/>
+      <c r="E1673" t="inlineStr"/>
+      <c r="F1673" t="inlineStr">
+        <is>
+          <t>CCCCCC(=O)NC(CCCNC(=N)N)C1=OC(C2=O[CH](CCC(N)=O)(C(=O)NC(C(=O)NC(CC34=CNC5=CC367C5=CC=C6C47)C(=O)NC(CCCN)C(=O)C(N)C3=O[CH](CC4=CC=C(OCCN)C=C4)(C(=O)NC(CC4=CC5=C(C=CC=C5)C=C4)C(=O)NC4(C(=O)N[CH]CCC(=O)O)CCOCC4)N3)C(C)O)N2)N1</t>
+        </is>
+      </c>
+      <c r="G1673" t="inlineStr"/>
+      <c r="H1673" t="inlineStr"/>
+      <c r="I1673" t="n">
+        <v>0.03945285451496375</v>
+      </c>
+      <c r="J1673" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1673" t="inlineStr"/>
+    </row>
+    <row r="1674">
+      <c r="A1674" s="1" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2307.png</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr"/>
+      <c r="D1674" t="inlineStr"/>
+      <c r="E1674" t="inlineStr"/>
+      <c r="F1674" t="inlineStr">
+        <is>
+          <t>[H][C@@]1(C(=O)N[C@]([H])(C(N)=O)[C@@H](C)O)CCSCC[C@H](NC(C)(C)C)C(=O)N[C@@H](C)C(=O)N[C@@H](Cc2c[nH]c3ccccc23)C(=O)N[C@@H](Cc2c[nH]cn2)C(=O)N[C@@H](CC(C)C)C(=O)NCC(=O)N[C@@H](CCC(=O)O)C(=O)N[C@@H](CC(C)C)C(=O)N[C@@H](C(C)C)C(=O)N[C@@H](Cc2c[nH]c3ccccc23)C(=O)N1</t>
+        </is>
+      </c>
+      <c r="G1674" t="inlineStr"/>
+      <c r="H1674" t="inlineStr"/>
+      <c r="I1674" t="n">
+        <v>0.7438573231083607</v>
+      </c>
+      <c r="J1674" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1674" t="inlineStr"/>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="1" t="n">
+        <v>1673</v>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2311.png</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr"/>
+      <c r="D1675" t="inlineStr"/>
+      <c r="E1675" t="inlineStr"/>
+      <c r="F1675" t="inlineStr">
+        <is>
+          <t>CC[C@@]1(O)C(=O)OCc2c1cc1n(c2=O)Cc2c-1nc1cc(F)c(C)cc1c2CNS(=O)(=O)CCOCNC(=O)CNC(=O)[C@H](Cc1ccccc1)NC(=O)CNC(=O)CNC(=O)CCOCCOCCOCCN1C(=O)C=CC1=O</t>
+        </is>
+      </c>
+      <c r="G1675" t="inlineStr"/>
+      <c r="H1675" t="inlineStr"/>
+      <c r="I1675" t="n">
+        <v>0.6636386662046982</v>
+      </c>
+      <c r="J1675" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1675" t="inlineStr"/>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="1" t="n">
+        <v>1674</v>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2315.png</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr"/>
+      <c r="D1676" t="inlineStr"/>
+      <c r="E1676" t="inlineStr"/>
+      <c r="F1676" t="inlineStr">
+        <is>
+          <t>CCC1(O)C(=O)OCC23=C1C=C14C56=NC=CC(F)=C(C)C7=C89%10[CH]%11%12O%13CC%14N8%15%16%17C8C%18%19%20=C5%21C5N1%22%23C(C6%18=C%211C%19%15N%14896%15CCO[CH]%13%108(C%119O%10%11%13C%14C%18C(=O)N%19C%10O%149(C%18%19%11)C%12%138)C7%166(OCCNC(=O)CNC(=O)C(CC6=CC=CC=C6)NC(=O)CNC(=O)CNC(=O)CCOCCOCCOCCN6C(=O)C=CC6=O)CC1%20%17%15)N54(C2%22=O)C3%23=O</t>
+        </is>
+      </c>
+      <c r="G1676" t="inlineStr"/>
+      <c r="H1676" t="inlineStr"/>
+      <c r="I1676" t="n">
+        <v>5.649838835849964e-05</v>
+      </c>
+      <c r="J1676" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1676" t="inlineStr"/>
+    </row>
+    <row r="1677">
+      <c r="A1677" s="1" t="n">
+        <v>1675</v>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2323.png</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr"/>
+      <c r="D1677" t="inlineStr"/>
+      <c r="E1677" t="inlineStr"/>
+      <c r="F1677" t="inlineStr">
+        <is>
+          <t>CC(=O)NCC(=O)NC1=CC=C(CC2NC(=O)C(CC3=CC=C(O)C=C3)NC(=O)C(NC(=O)C(N)CC3=CC=C(Cl)C=C3)CSSC[CH]3(C(=O)NC(CC4=CC=C(O)C=C4)C(N)=O)CC(O)C(NC(=O)C(CCCCN)NC2=O)C(=O)N3)C=C1</t>
+        </is>
+      </c>
+      <c r="G1677" t="inlineStr"/>
+      <c r="H1677" t="inlineStr"/>
+      <c r="I1677" t="n">
+        <v>0.5080226473558558</v>
+      </c>
+      <c r="J1677" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1677" t="inlineStr"/>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="1" t="n">
+        <v>1676</v>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2327.png</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr"/>
+      <c r="D1678" t="inlineStr"/>
+      <c r="E1678" t="inlineStr"/>
+      <c r="F1678" t="inlineStr">
+        <is>
+          <t>NC(=O)O.[H]C1(CC=CC=CC=CC=CC=CC(=O)[CH]2(CC)N3C45=O=C3(=O=4)N52)CCN1C(=O)NC(CNC1=C(OC(C)C)C(=O)C1=O)NC(=O)C1([H])CCCN1C(=O)NC(C)C(=O)N(C)C(=O)C(CC1=CC2=C(O)C=C=21)NC(=O)CSCC(NC1(=O)=O=C(C(CCC)N(C)C([CH])=O)NC1CC(C)C)C(=O)NCC(N)=O</t>
+        </is>
+      </c>
+      <c r="G1678" t="inlineStr"/>
+      <c r="H1678" t="inlineStr"/>
+      <c r="I1678" t="n">
+        <v>0.01744043259535703</v>
+      </c>
+      <c r="J1678" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1678" t="inlineStr"/>
+    </row>
+    <row r="1679">
+      <c r="A1679" s="1" t="n">
+        <v>1677</v>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2331.png</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr"/>
+      <c r="D1679" t="inlineStr"/>
+      <c r="E1679" t="inlineStr"/>
+      <c r="F1679" t="inlineStr">
+        <is>
+          <t>CCC=C(C)C=CCC1NC(=O)C(CC)NC(=O)[CH]C2(=O)N[CH]34C56=O=C3(=O)[CH]54NC(=O)[CH]CO[CH]34C(=O)N[CH]5789C%10OC5(O%10)[CH]75[CH]87[CH]8(N[CH]579%10[CH]57C9%11OC5%10(O9)[CH]%117[CH]35NC(=O)[CH]45OSC2CC23=C(C=CC=C(C=CC4=C=CC=4)C4=CC4)=C2C3=CC(OCCC)=CC=CCC6)[CH](C)(C)[CH]8(C)(C)NC1=O.CNC(C)=O</t>
+        </is>
+      </c>
+      <c r="G1679" t="inlineStr"/>
+      <c r="H1679" t="inlineStr"/>
+      <c r="I1679" t="n">
+        <v>9.686802599357973e-13</v>
+      </c>
+      <c r="J1679" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1679" t="inlineStr"/>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="1" t="n">
+        <v>1678</v>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2335.png</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr"/>
+      <c r="D1680" t="inlineStr"/>
+      <c r="E1680" t="inlineStr"/>
+      <c r="F1680" t="inlineStr">
+        <is>
+          <t>CCCC1NC2(=O)=O3=C(NC=3(=O)[CH](CC)(NC(=O)NC3(=O)C(CC)C3CCCC[CH]34NC(=O)[CH]3(CCN)[CH]3(CC(C)CN)C4C(C)C[CH]456(N)C3CC378=C(C=CC=C3)C3=CC=C7C79=C3C3=CC=C78C7(=C3)CNC43=O=C5(=O)(NC79)C36)C(=O)(NCC(=O)NC(=O)[CH]CCCCC3[CH]C(=O)N3)C(C(C)CC)NC1=O)C2CCCNC(=N)N</t>
+        </is>
+      </c>
+      <c r="G1680" t="inlineStr"/>
+      <c r="H1680" t="inlineStr"/>
+      <c r="I1680" t="n">
+        <v>3.026529231717879e-08</v>
+      </c>
+      <c r="J1680" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1680" t="inlineStr"/>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="1" t="n">
+        <v>1679</v>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2339.png</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr"/>
+      <c r="D1681" t="inlineStr"/>
+      <c r="E1681" t="inlineStr"/>
+      <c r="F1681" t="inlineStr">
+        <is>
+          <t>CC=CC[CH]C(=O)NC(CCCNC(C)CC1=CC=CC=C1)C(=O)N[CH]CCSC1=C2C=CC=C([N+](=O)[O-])C2=CN1C1CCCCNC2(=O)[CH]34C([N+](=O)[O-])[CH]25(C[N+](=O)[O-])(NC26(=O)CN7(CCN(CC(=O)O)CCN(CC(=O)O)CCN(CC(=O)O)CC7)C2C(=O)N365)C4(=O)NCCC=CCC(N[CH]CCCCNC(C)C)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1681" t="inlineStr"/>
+      <c r="H1681" t="inlineStr"/>
+      <c r="I1681" t="n">
+        <v>0.04169197578887034</v>
+      </c>
+      <c r="J1681" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1681" t="inlineStr"/>
+    </row>
+    <row r="1682">
+      <c r="A1682" s="1" t="n">
+        <v>1680</v>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_2/rb_2343.png</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr"/>
+      <c r="D1682" t="inlineStr"/>
+      <c r="E1682" t="inlineStr"/>
+      <c r="F1682" t="inlineStr">
+        <is>
+          <t>CC=CC1=CC=1CCCC1(=O)N23C(=O)(CCCC4=C(C=CC=CC5=CC67=C8C9=C=65C=798)=N4)N14C21=CC=C25(=C6(C(=O)(C(=O)OO)C(=O)OO)=C(C=CC34=C6)N23CCN2CC3N534CCN(CC(=O)NC(CC)C5(=O)N[CH]6(CNCCCC[CH]78CN7C(CCCCNC[CH]NCC7NC(=O)C72)N8CC27=C8(=C2=C8)C=C7)C2C78C56C25C72N67C85N25C6(N)=O=C75(N)=O)C2C(C3)C24)C=C1</t>
+        </is>
+      </c>
+      <c r="G1682" t="inlineStr"/>
+      <c r="H1682" t="inlineStr"/>
+      <c r="I1682" t="n">
+        <v>2.098336859806739e-09</v>
+      </c>
+      <c r="J1682" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1682" t="inlineStr"/>
+    </row>
+    <row r="1683">
+      <c r="A1683" s="1" t="n">
+        <v>1681</v>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2104.png</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr"/>
+      <c r="D1683" t="inlineStr"/>
+      <c r="E1683" t="inlineStr"/>
+      <c r="F1683" t="inlineStr">
+        <is>
+          <t>CC.CC(O)C(C)NC1C(=O)N[CH]2(CCC(=O)O)[CH]34CCC[CH]567O[CH]89[CH]5(C5%10=O%11=C5(O%10)OC=%1186=O)O937[CH]124CC(=O)O.CCCCCCCCCCC1C2C(C(=O)OCCCOCC(=O)NCCOCCOCC(=O)NCC(=O)NC345678(=O)N9%10C3%11%12%13=O3=C94%14%15%16=O=C=3%10549(O635%10C6%17%18%19C%20%21%22%23%24%25%26%27=C%28%29=C%20%30%31C%28=C%20%28=C(=C%29)C=C%20%306%21%29%32(=C=%17%28)C%226%17(=C=%23%20C%21%22%23NC%21(=O)C%20%31%1863%29%24(N%115%1474)(C%22(=O)N%19%10%329%25C3=O=C3)O%23%17%26)C=CC=C%27)(=O=%12=%15)N%13%168)C12</t>
+        </is>
+      </c>
+      <c r="G1683" t="inlineStr"/>
+      <c r="H1683" t="inlineStr"/>
+      <c r="I1683" t="n">
+        <v>3.233716170178916e-17</v>
+      </c>
+      <c r="J1683" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1683" t="inlineStr"/>
+    </row>
+    <row r="1684">
+      <c r="A1684" s="1" t="n">
+        <v>1682</v>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2116.png</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr"/>
+      <c r="D1684" t="inlineStr"/>
+      <c r="E1684" t="inlineStr"/>
+      <c r="F1684" t="inlineStr">
+        <is>
+          <t>CC(C)(C)CCCC(=O)CNC(=O)CCCCCCC1C2N3[CH]456C(C(C[CH]NC7(C(=O)NC(=O)NC89%10=O=C8%11(N8C%12=C(CCC%13=O=C%14%15(=O=C%14N%15CCCNC%14(=O)=O=C%14N)N%13)NC%13(C)=CC%13=C8C%12)=O=9=C%10%11)CC(=O)N7)NC(=O)(=O)CCCCCC(=O)CCC(=O)CCC(C)(C)C)C4[CH]123478CC54C7N68.CC(N)=CN(CC1C2C3C2C3[C]1(C)[Na])C(=O)CC123=C4=C1=C2(=C4)C3</t>
+        </is>
+      </c>
+      <c r="G1684" t="inlineStr"/>
+      <c r="H1684" t="inlineStr"/>
+      <c r="I1684" t="n">
+        <v>1.249709492615983e-10</v>
+      </c>
+      <c r="J1684" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1684" t="inlineStr"/>
+    </row>
+    <row r="1685">
+      <c r="A1685" s="1" t="n">
+        <v>1683</v>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2120.png</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr"/>
+      <c r="D1685" t="inlineStr"/>
+      <c r="E1685" t="inlineStr"/>
+      <c r="F1685" t="inlineStr">
+        <is>
+          <t>CCC1(O)C(=O)OCC2=C1C=C1C3=NC4=CC(F)=C(NC(=O)CNC(=O)C(CC5=CC=CC=C5)NC(=O)CNC(=O)CNC(=O)CCOCCOCCOCCN5C(=O)C=CC5=O)C=C4C4=C3C(=CCO3CCN56(C4)CC3OCC5C6)N1C2=O</t>
+        </is>
+      </c>
+      <c r="G1685" t="inlineStr"/>
+      <c r="H1685" t="inlineStr"/>
+      <c r="I1685" t="n">
+        <v>0.3033463023242628</v>
+      </c>
+      <c r="J1685" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1685" t="inlineStr"/>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="1" t="n">
+        <v>1684</v>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2124.png</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr"/>
+      <c r="D1686" t="inlineStr"/>
+      <c r="E1686" t="inlineStr"/>
+      <c r="F1686" t="inlineStr">
+        <is>
+          <t>[H]C1(C(=O)NC(CC2=C3C=CC=C32)C(=O)NC(CC)C(=O)N[CH]C)CC(O)CN1C(=O)[CH]NC(=O)C(CNC12=C3(N(C)C)C14=O=C23(=O)C4=O)NC(=O)C1([H])CCCN1C(=O)C(CC(N)=O)NC(C)N(C)C(=O)C(C)NC(=O)CSCC(NC(=O)C(CC(C)C)NC(=O)[CH]CCCC)C(=O)NCC(C)=O</t>
+        </is>
+      </c>
+      <c r="G1686" t="inlineStr"/>
+      <c r="H1686" t="inlineStr"/>
+      <c r="I1686" t="n">
+        <v>0.04163953253403384</v>
+      </c>
+      <c r="J1686" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1686" t="inlineStr"/>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="1" t="n">
+        <v>1685</v>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2132.png</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr"/>
+      <c r="D1687" t="inlineStr"/>
+      <c r="E1687" t="inlineStr"/>
+      <c r="F1687" t="inlineStr">
+        <is>
+          <t>Cc1ccccc1/C=C/C[CH]NC(=O)[C@@H](CCCNC(=N)N)NC(=O)[C@H](CCCCNC(C)C)NC(=O)[C@H](Cc1ccc(O)cc1)NC(=O)[C@H](CCCCNC(=O)[C@H](CS(=O)(=O)O)NC(=O)CN1CCN(CC(=O)O)CCN(CC(=O)O)CCN(CC(=O)O)CC1)n1cc2c(*(=O)O)cccc2c1SCC(=O)N[CH]CCCCNC(C)C |$;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;NC;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1687" t="inlineStr"/>
+      <c r="H1687" t="inlineStr"/>
+      <c r="I1687" t="n">
+        <v>0.7299699812255651</v>
+      </c>
+      <c r="J1687" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1687" t="inlineStr"/>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="1" t="n">
+        <v>1686</v>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2144.png</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr"/>
+      <c r="D1688" t="inlineStr"/>
+      <c r="E1688" t="inlineStr"/>
+      <c r="F1688" t="inlineStr">
+        <is>
+          <t>CC=C1CC1=CCC[CH]C(=O)CNC1CN1.CCCCCCCCCCCCNC(CCCN1C2C(OCCNC(=O)C3NC3C3CO3CCCNCC3CC3CCNC3456=O=C37(N4)C53(O)=CNC45=C8(C)=C49=C(=[CH]59376)C=C8)C21)C(=O)O.NCCOC1=C23=C(=C12)C(O1CC1O[CH]C(O)CNCCNC(=O)C(CCC(N)=O)C1(NCC(N)=O)C2C(CCC4C5=O=C4N5)C21)C=C3</t>
+        </is>
+      </c>
+      <c r="G1688" t="inlineStr"/>
+      <c r="H1688" t="inlineStr"/>
+      <c r="I1688" t="n">
+        <v>6.484866068647868e-11</v>
+      </c>
+      <c r="J1688" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1688" t="inlineStr"/>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="1" t="n">
+        <v>1687</v>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2148.png</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr"/>
+      <c r="D1689" t="inlineStr"/>
+      <c r="E1689" t="inlineStr"/>
+      <c r="F1689" t="inlineStr">
+        <is>
+          <t>CC(=O)OCC1234=C567(=O)(C8=CC9=C%10%11C=C=9%10(C)(C=CCN9%10C85%12=C9658%13%14=O1=C%10%12516=O=859=C(NC=58%10(=O)=O5=C%12(COCCO%15CC%15O%15CC%15%16=O=C(OCCOC%15CN%15C%15=O=C%15(O)CCC(O)C(C)O)N%16)N8C=5%12%10)C=91%13=C=6=%1427C12=C(C1)N2C(C)=O)C%11)N3C4=O.CCCNCC12CC1C(C1=O3=C1OC=31=O34=C1OC=31C(OCCO3C5C3O5CC)C=41(=O)O)N2.O.O.O=C(O)C(O)CCC1(O)=O=C1N1CC1OCCO</t>
+        </is>
+      </c>
+      <c r="G1689" t="inlineStr"/>
+      <c r="H1689" t="inlineStr"/>
+      <c r="I1689" t="n">
+        <v>3.507332098501673e-16</v>
+      </c>
+      <c r="J1689" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1689" t="inlineStr"/>
+    </row>
+    <row r="1690">
+      <c r="A1690" s="1" t="n">
+        <v>1688</v>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2152.png</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr"/>
+      <c r="D1690" t="inlineStr"/>
+      <c r="E1690" t="inlineStr"/>
+      <c r="F1690" t="inlineStr">
+        <is>
+          <t>COC1=CC=C(CCC2C=CC3=C4=C5=CC46=CC(=C35)C(CCC3=CC=C(OC)C(OC)=C3)OC(=O)[CH]3(CCCCN3C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)C(CC(C)C)N(C)C(=O)C3CCCN3C(=O)C3CC(NC(=O)OC(C)(C)C)CN3C(=O)C(C3=CC=CC=C3)NC(=O)CCC(=O)N6)C(=O)O2)C=C1OC</t>
+        </is>
+      </c>
+      <c r="G1690" t="inlineStr"/>
+      <c r="H1690" t="inlineStr"/>
+      <c r="I1690" t="n">
+        <v>0.1896930240400383</v>
+      </c>
+      <c r="J1690" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1690" t="inlineStr"/>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="1" t="n">
+        <v>1689</v>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2156.png</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr"/>
+      <c r="D1691" t="inlineStr"/>
+      <c r="E1691" t="inlineStr"/>
+      <c r="F1691" t="inlineStr">
+        <is>
+          <t>NCCCCC1NC(=O)C(CC2=CC=C(NC(=O)CN)C=C2)NC(=O)C(CC2=CC=C(O)C=C2)NC(=O)C(NC(=O)C(N)CC2=CC=C(Cl)C=C2)CSSC23[CH]45C67SC48[CH]6249C2(=O)N6C%10C%11C%12=CC=C(O)C=C%12C%12(=CC=C(O)C=C%12)C[CH]%116(C(N)=O)(NC(=O)[CH]3826%11N2C38(=O)N46C24(=O)[CH]326O3C1(=O)N[CH]3841[CH]2(O)C59%11C761O)C%10(N)=O</t>
+        </is>
+      </c>
+      <c r="G1691" t="inlineStr"/>
+      <c r="H1691" t="inlineStr"/>
+      <c r="I1691" t="n">
+        <v>4.233299279200333e-05</v>
+      </c>
+      <c r="J1691" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1691" t="inlineStr"/>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="1" t="n">
+        <v>1690</v>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2160.png</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr"/>
+      <c r="D1692" t="inlineStr"/>
+      <c r="E1692" t="inlineStr"/>
+      <c r="F1692" t="inlineStr">
+        <is>
+          <t>[N-]=[N+]=NCCCNC(=O)CN1CCN(CC(=O)NCCCN=[N+]=[N-])CCN(CC(=O)NCCCN=[N+]=[N-])CCN(CC(=O)NCCCN=[N+]=[N-])CC1</t>
+        </is>
+      </c>
+      <c r="G1692" t="inlineStr"/>
+      <c r="H1692" t="inlineStr"/>
+      <c r="I1692" t="n">
+        <v>0.7664225123912538</v>
+      </c>
+      <c r="J1692" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1692" t="inlineStr"/>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="1" t="n">
+        <v>1691</v>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2164.png</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr"/>
+      <c r="D1693" t="inlineStr"/>
+      <c r="E1693" t="inlineStr"/>
+      <c r="F1693" t="inlineStr">
+        <is>
+          <t>CCCCCCCCCCCCCC(=O)NC(CCC(=O)O)C(=O)NCCC1C(CC)CC1CN1(C)C23C45=C6C7=C8=C6=C6N9=C4=N68=C=95C(=C7)C4[CH]2567N[CH]4312[CH]5(C6C(N)=O)C721N2C1(=O)[CH]2(CC(N)=O)[CH]123NC4(=O)N56(C(=O)[CH]78(N1C72=O)N1C2C7(N[CH]C(=O)N[CH]CC9=CC=C=9C=C(C)CCCN)=O=C2183=O=7)C12C537OCC[CH]136[CH]2471CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1693" t="inlineStr"/>
+      <c r="H1693" t="inlineStr"/>
+      <c r="I1693" t="n">
+        <v>2.007666980387111e-10</v>
+      </c>
+      <c r="J1693" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1693" t="inlineStr"/>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="1" t="n">
+        <v>1692</v>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2168.png</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr"/>
+      <c r="D1694" t="inlineStr"/>
+      <c r="E1694" t="inlineStr"/>
+      <c r="F1694" t="inlineStr">
+        <is>
+          <t>CCCCC1N(C)C(=O)COCC=CC(CCC2=C(OC)C(OC)=CC=C2OC)OC(=O)C2CCCCN2C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)CNC(=O)[CH]23(COC(C)(C)C)C(O)[CH]N24(C)C25(=O)[CH]67C(C8=CC9=C(C=CC=C9)C=C8)[CH]28(CC2=CC9=C(C=CC=C9)C=C2)(NC2(=O)C(CCCC)C1(=O)N268)C74(=O)N53C</t>
+        </is>
+      </c>
+      <c r="G1694" t="inlineStr"/>
+      <c r="H1694" t="inlineStr"/>
+      <c r="I1694" t="n">
+        <v>0.01199537999230604</v>
+      </c>
+      <c r="J1694" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1694" t="inlineStr"/>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="1" t="n">
+        <v>1693</v>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2172.png</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr"/>
+      <c r="D1695" t="inlineStr"/>
+      <c r="E1695" t="inlineStr"/>
+      <c r="F1695" t="inlineStr">
+        <is>
+          <t>CC(=O)N[CH]12[CH]34567[CH]89%10(O%11CC%11CCNCCCN%11CC%11CC%11%12%13=O%14=C%11%15%16=O=%12=C=%14%15%11(=O)(=O=C(O%12C%14=O%15=C(OCCNCCOC%17[CH]%18(O[CH]C[O-])C%19%20(=O)=O=C%17%18%19(O)O%20)C=%15%14%12=O)N%11)N%13%16)(O%11C(C%12OC%12C(N)=O)O=C%11%12=O=C%12O)[CH]3%11%12%13O[CH]1%11843%14(O)O[CH]2%12953[CH]%13%106%14(OCC(N)=O)O7.CCCCO1C2C(OCCNCCC(OCCC=CC(=O)O)OC3CNC3OCCCCNCC)C21.O</t>
+        </is>
+      </c>
+      <c r="G1695" t="inlineStr"/>
+      <c r="H1695" t="inlineStr"/>
+      <c r="I1695" t="n">
+        <v>3.095453820133668e-16</v>
+      </c>
+      <c r="J1695" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1695" t="inlineStr"/>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="1" t="n">
+        <v>1694</v>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2176.png</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr"/>
+      <c r="D1696" t="inlineStr"/>
+      <c r="E1696" t="inlineStr"/>
+      <c r="F1696" t="inlineStr">
+        <is>
+          <t>C.CC=CC=CC(C=CC)=CC=CC1=C(C=CCC2=O=C345=O=C3(N24)N52CC2N[CH]2(C)CC(CN3[CH]C3NCCNCC)C3=O=C2(=O)N2C4C5C6C(C)C57[CH]58(N3)C3=O=C(N[CH]CNCCNC9=O%10%11=C(CNC[CH]N3)NC=%1093%12=O9=C3(C=CC=CC)C=9=%11%12)[CH]642753C(NC2CN2CCC2N(CC)[CH]45C(N24)C5(N)=O)C83)C12=CC=CC=C2.O.O</t>
+        </is>
+      </c>
+      <c r="G1696" t="inlineStr"/>
+      <c r="H1696" t="inlineStr"/>
+      <c r="I1696" t="n">
+        <v>2.043659840381105e-10</v>
+      </c>
+      <c r="J1696" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1696" t="inlineStr"/>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="1" t="n">
+        <v>1695</v>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2180.png</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr"/>
+      <c r="D1697" t="inlineStr"/>
+      <c r="E1697" t="inlineStr"/>
+      <c r="F1697" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1697" t="inlineStr"/>
+      <c r="H1697" t="inlineStr"/>
+      <c r="I1697" t="n">
+        <v>8.817894313255355e-28</v>
+      </c>
+      <c r="J1697" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1697" t="inlineStr"/>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="1" t="n">
+        <v>1696</v>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2188.png</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr"/>
+      <c r="D1698" t="inlineStr"/>
+      <c r="E1698" t="inlineStr"/>
+      <c r="F1698" t="inlineStr">
+        <is>
+          <t>CNC1(=O)C2C1[CH]2(O)C(C)(=O)O.C[CH]NC1CN1CNC1C2(C3N4C5N(CCN[CH]CNC(CCC=CC=CC)C(NCCN[CH]CNC[CH]NC6C(C(N)=O)CN6CC[CH]NCCCCCOCCC6OC6N6CO6)=O=CC6CC6)C4N532)C12=O=C1(=O3=C1NC=3145=O=C1(=O=4)N5C1C=CC=C(C3C=CC=CC=C3)C=C1)N2.O.[CH][CH]O</t>
+        </is>
+      </c>
+      <c r="G1698" t="inlineStr"/>
+      <c r="H1698" t="inlineStr"/>
+      <c r="I1698" t="n">
+        <v>1.003023748427233e-11</v>
+      </c>
+      <c r="J1698" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1698" t="inlineStr"/>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="1" t="n">
+        <v>1697</v>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2196.png</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr"/>
+      <c r="D1699" t="inlineStr"/>
+      <c r="E1699" t="inlineStr"/>
+      <c r="F1699" t="inlineStr">
+        <is>
+          <t>C/C=C\C=C\N[C@@H](CCCCNC(=O)[C@H](CS(=O)(=O)O)NC(=O)CN(C)CCN(CCN(CCN(CC)CC(=O)O)CC(=O)O)CC(=O)O)C(=O)N[C@@H](Cc1ccc(O)cc1)C(=O)N[C@@H](CCCCNC(C)C)C(=O)N[C@H](CCCNC(=N)N)C(=O)N[C@@H](Cc1ccc2ccccc2c1)C(=O)N[C@H](C)C(=O)NC(CCCNC(C)C)C(N)=O</t>
+        </is>
+      </c>
+      <c r="G1699" t="inlineStr"/>
+      <c r="H1699" t="inlineStr"/>
+      <c r="I1699" t="n">
+        <v>0.5779358433993874</v>
+      </c>
+      <c r="J1699" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1699" t="inlineStr"/>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="1" t="n">
+        <v>1698</v>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2200.png</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr"/>
+      <c r="D1700" t="inlineStr"/>
+      <c r="E1700" t="inlineStr"/>
+      <c r="F1700" t="inlineStr">
+        <is>
+          <t>CC(C)C[CH]NC(=O)C(CC1=CNC=N1)NC(=O)C(CC1=CNC2=C1C=CC=C2)NC(=O)C(C)NC(=O)C(CSSCC(NC(=O)C(CC12=CNC34567=C18C=CC319=C4=C53=C=164=CC8=C=72C=934)NC(=O)C(NC(=O)C(CC(C)C)NC(=O)[CH]CCC=O)C(C)C)C(=O)NC(C(=O)C(C)(C)C)C(C)O)NC(=O)C(N)CC(=O)O</t>
+        </is>
+      </c>
+      <c r="G1700" t="inlineStr"/>
+      <c r="H1700" t="inlineStr"/>
+      <c r="I1700" t="n">
+        <v>0.02065946710148077</v>
+      </c>
+      <c r="J1700" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1700" t="inlineStr"/>
+    </row>
+    <row r="1701">
+      <c r="A1701" s="1" t="n">
+        <v>1699</v>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2204.png</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr"/>
+      <c r="D1701" t="inlineStr"/>
+      <c r="E1701" t="inlineStr"/>
+      <c r="F1701" t="inlineStr">
+        <is>
+          <t>[CH]C(C)C(=O)NC(C(C)C)C(NC(=O)CCCNC(=O)CNC(=O)CCOCCOCCNC(=O)CCN(CC1C234=O=C156(=O=2=C1(=O)(NCCOCCCCC(=O)NC(C(=O)NC(C(=O)C(OC)C(C(=O)NC(CC)C(C)C(=O)NC(CC=CC=O)C(=O)O)C(CC)CC)C(C)C)C(C)C)C5CC136)C4)C(=O)CCCNC=C)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1701" t="inlineStr"/>
+      <c r="H1701" t="inlineStr"/>
+      <c r="I1701" t="n">
+        <v>0.002661791912257295</v>
+      </c>
+      <c r="J1701" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1701" t="inlineStr"/>
+    </row>
+    <row r="1702">
+      <c r="A1702" s="1" t="n">
+        <v>1700</v>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2212.png</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr"/>
+      <c r="D1702" t="inlineStr"/>
+      <c r="E1702" t="inlineStr"/>
+      <c r="F1702" t="inlineStr">
+        <is>
+          <t>CCC(C)C123=O=C(=O=1)(N2)C312456(CC(C)C)N37C89%10%11(=O)N1%12%13%14%15C31%16%17%18(=O)C23%19%20%21%22%23%24%25C%122%26%27%28%29(=O)N%12%30%31C%32%33%34%35%36%37%38N3C3%39%40%41%42%43(=O)(N%44%45C%46%47%48N%32%49%50%51%52%53%54%55C%46%32%56%57C%46%58C%59%60CC%46%61%62%63(C%59)CC%58%46%59(C)(CC%58%64%65(C)CC%66%67%68(C)CC%69%70%71(C)CC%72%73%74(C)CC%75%76%77(C)CC%78%79(C)(C)C%75C%12%13%49%193%75%80%81%82%83%84%85%86%87C%20(C%78%76%72)C%30%14%50%213%12%13%19=O=C%75%14%20%21%30%49=O=C8142%80%50(=O=%14)(N%20)C%261C%792C(C)(C)C(C2(C)C)C%162N9%175%27C7%10%15%50%22%39(CC(C)C)(C%33%283%8145789=O=C%823%10(=O)(=O=4)N%215%40C%5145%14%15C%16(C%66%58%46)C3%30%527%41%17%20%21(C%67%64%69)N4%34%12%83C%31%10%49%53%238%42347(C%77%73%70)(C%359C%68%74%71)C%44%8489%10%12N%475%36%13%173%85%22C%32%543(=O)C%56(C%60%61)C%483%14%37%204%865(=O=CN85)C%579%55%22%43(C%65%62%59)C%16%45%15%38%19%217%87(=O=%10)=O=%12)N21%11%186%29)C%63)(=O=%24)=O=%25.O</t>
+        </is>
+      </c>
+      <c r="G1702" t="inlineStr"/>
+      <c r="H1702" t="inlineStr"/>
+      <c r="I1702" t="n">
+        <v>5.106318632964852e-59</v>
+      </c>
+      <c r="J1702" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1702" t="inlineStr"/>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="1" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2216.png</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr"/>
+      <c r="D1703" t="inlineStr"/>
+      <c r="E1703" t="inlineStr"/>
+      <c r="F1703" t="inlineStr">
+        <is>
+          <t>C=CC(=O)NC=CCNC(=O)C=C(C)NC=CC=COCC(=O)NCCCC(=O)NCCC(C)C(O)C1C(=O)N2C(CC(C)C[CH]3(C=O)N456C7CC489C4C%10C8%11C4[CH]%104(NC8(=O)[CH]%10%12%13C(C(C)C)[CH]8%14(CC(C)C)(C%10(=O)N4)N%124CN%13%14C(=O)C8[CH]%10%12%13%14C%15%16%17CC%10%18(C%15)[CH]8%16%10%15C%128%16%19=O%12=C%13%10%20%21%22=O=C=%12%14%15(=O=8=%20)(N%16%21C)[CH]%17%18%19%22(CC)CC4=O)C5(=O)N739C%116)N13C(=O)C(C(C)C)C23</t>
+        </is>
+      </c>
+      <c r="G1703" t="inlineStr"/>
+      <c r="H1703" t="inlineStr"/>
+      <c r="I1703" t="n">
+        <v>2.275186715509269e-05</v>
+      </c>
+      <c r="J1703" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1703" t="inlineStr"/>
+    </row>
+    <row r="1704">
+      <c r="A1704" s="1" t="n">
+        <v>1702</v>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2224.png</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr"/>
+      <c r="D1704" t="inlineStr"/>
+      <c r="E1704" t="inlineStr"/>
+      <c r="F1704" t="inlineStr">
+        <is>
+          <t>C=CC(=O)NCCCC(=O)NCCC(=O)NCCOCCOCCC(=O)N(C)[CH]C(=O)NC(C)C(=O)NC(CCC)C(CC(=O)N1CCCC1C(OC)C(C)C(=O)NC(CO)C(=O)O)OC.C=CC(=O)NCCCC(=O)NCCC(=O)NCCOCCOCCC(=O)NC(C)C(=O)NCCCC(=O)NC(C(=O)NC1C2CC1(C)(C)C2)C(C)C</t>
+        </is>
+      </c>
+      <c r="G1704" t="inlineStr"/>
+      <c r="H1704" t="inlineStr"/>
+      <c r="I1704" t="n">
+        <v>0.2159909980585431</v>
+      </c>
+      <c r="J1704" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1704" t="inlineStr"/>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="1" t="n">
+        <v>1703</v>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2232.png</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr"/>
+      <c r="D1705" t="inlineStr"/>
+      <c r="E1705" t="inlineStr"/>
+      <c r="F1705" t="inlineStr">
+        <is>
+          <t>[H]C(CC(N)=O)C(=O)NC1([H])C=C(CO[CH]C(OC2CC(C)(NC(=S)NCCOCCOCCOCCN3C=C(CN4C(O)=NC5=C4N=C(OCCCC)N=C5N)N=N3)C(O)C(C)O2)C2O[CH]2(O)[CH]C)OC=C(CO)C=CC(O)C2([H])OC([H])(C=NC(=CO)C3=C([CH]NC2=O)C=C(O)C=C3O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1705" t="inlineStr"/>
+      <c r="H1705" t="inlineStr"/>
+      <c r="I1705" t="n">
+        <v>0.06552368514540385</v>
+      </c>
+      <c r="J1705" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1705" t="inlineStr"/>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="1" t="n">
+        <v>1704</v>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2236.png</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr"/>
+      <c r="D1706" t="inlineStr"/>
+      <c r="E1706" t="inlineStr"/>
+      <c r="F1706" t="inlineStr">
+        <is>
+          <t>CCCCC1C2(=O)N3C4C(C5=CC6=C(C=CC=C6)C=C5)[CH]356(CC3=CC7=C(C=CC=C7)C=C3)NC(=O)[CH]2(CCCC)N1(C)C(=O)COCC=CC(CCC1=C(OC)C(OC)=C(OC)C=C1)OC(=O)C1CCCCN1C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)CNC(=O)[CH]12(COC(C)(C)C)CC3N17(C)C5(=O)N32(C)C476=O</t>
+        </is>
+      </c>
+      <c r="G1706" t="inlineStr"/>
+      <c r="H1706" t="inlineStr"/>
+      <c r="I1706" t="n">
+        <v>0.05691586345357857</v>
+      </c>
+      <c r="J1706" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1706" t="inlineStr"/>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="1" t="n">
+        <v>1705</v>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2240.png</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr"/>
+      <c r="D1707" t="inlineStr"/>
+      <c r="E1707" t="inlineStr"/>
+      <c r="F1707" t="inlineStr">
+        <is>
+          <t>*C(=O)NCC(=O)NCC(=O)NC(CC1=CC=CC=C1)C(=O)NCC(=O)NCC1=CC=C(COC(=O)NC2CCC3=C(C)C(F)=CC4=NC56=C(CN7C(=O)C8=C(C=C75)C(O)(CC)C(=O)OC8)C2=C=643)C=C1 |$Y;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1707" t="inlineStr"/>
+      <c r="H1707" t="inlineStr"/>
+      <c r="I1707" t="n">
+        <v>0.6449203647037405</v>
+      </c>
+      <c r="J1707" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1707" t="inlineStr"/>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="1" t="n">
+        <v>1706</v>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2244.png</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr"/>
+      <c r="D1708" t="inlineStr"/>
+      <c r="E1708" t="inlineStr"/>
+      <c r="F1708" t="inlineStr">
+        <is>
+          <t>*C(=O)C(CCCNCCOCCOCCCO1CC1COC1CC1=CC12=C3C1C(NC(=O)CCC(CN)C1C4C15C1=C(C=CC)=C145)C32CC)NCCCCCCCCCCC.O.[CH]CCN[CH]123CC456=C78=C=49%10=C(C[CH]4(NC41=O=C21=O=C(N)(=O)N1)C31(=O)NC1CCC(CCNC(=O)C12(COCCCOCCC)COC1(O)C2)CNC(C)=O)C5=NC1=C79=C(=C=18%10)N=C6 |$HOCH3;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1708" t="inlineStr"/>
+      <c r="H1708" t="inlineStr"/>
+      <c r="I1708" t="n">
+        <v>3.172137913794772e-10</v>
+      </c>
+      <c r="J1708" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1708" t="inlineStr"/>
+    </row>
+    <row r="1709">
+      <c r="A1709" s="1" t="n">
+        <v>1707</v>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2248.png</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr"/>
+      <c r="D1709" t="inlineStr"/>
+      <c r="E1709" t="inlineStr"/>
+      <c r="F1709" t="inlineStr">
+        <is>
+          <t>CC1=CC=C(C(=O)NC2=CN3C=C(C(=O)N4C5[CH]67C(Cl)[CH]58(CCl)C659=C46C=C(OC(=O)N(C)CCN(C)C(=O)OCC4=CC=C(NC(=O)C(CCCNC(N)=O)NC(=O)C(NC(=O)C(CCCCN)NC(=O)CNC(=O)CNC(=O)CN)C(C)C)C=C4)C4=CC=CC=45=C6798)N=C3C=C2)C=C1</t>
+        </is>
+      </c>
+      <c r="G1709" t="inlineStr"/>
+      <c r="H1709" t="inlineStr"/>
+      <c r="I1709" t="n">
+        <v>0.1523224382102992</v>
+      </c>
+      <c r="J1709" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1709" t="inlineStr"/>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="1" t="n">
+        <v>1708</v>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2256.png</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr"/>
+      <c r="D1710" t="inlineStr"/>
+      <c r="E1710" t="inlineStr"/>
+      <c r="F1710" t="inlineStr">
+        <is>
+          <t>CCC(C)C123=O=C(=O=1)(N2)C31245678(CC(C)C)N3C19%10%11%12%13C21%14(CCCNC(=N)N)C2%15%16%17%18%19=O%20=C(C(=O)NC(=O)CNC(CC(C)C)C(=O)NC(CC(C)=O)C%21(NCC(C)=O)N%22C%23(C%24=C%25C=CC%25=C%24)=O=C%22%21%23)N2%21%22C%152%23%24(CC(C)C)N94%15%25C=%20%21%164=O9=C42%175(CCCNC(N)=O)C%22%1524(CC(C)C)=O=%10=C31%25%11(=O=%14)(N2%126)C%234%18%13712=O=C=9%24%198(=O=1)N2.CCCNC12(=O)=O=C(C1)N2C(CCCNC(N)=O)C(=O)NCC(=O)NC(=O)NC(C)=O</t>
+        </is>
+      </c>
+      <c r="G1710" t="inlineStr"/>
+      <c r="H1710" t="inlineStr"/>
+      <c r="I1710" t="n">
+        <v>2.21397202161274e-14</v>
+      </c>
+      <c r="J1710" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1710" t="inlineStr"/>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="1" t="n">
+        <v>1709</v>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2260.png</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr"/>
+      <c r="D1711" t="inlineStr"/>
+      <c r="E1711" t="inlineStr"/>
+      <c r="F1711" t="inlineStr">
+        <is>
+          <t>[H][C@@]12CCCC[C@]1([H])N(C(=O)[C@@H]1CCCN1C(=O)[C@H](CC(C)C)NC(=O)[C@H](CO)NC(=O)[C@H](CCCNC(=N)N)NC(=O)[C@H](CO)NC(=O)[C@H](CS)NC(=O)[C@@H](NC(=O)[C@@H](N)C1CCOCC1)C(C)CO)[C](C(=O)N[C@H](C(=O)N[C@@H](CO)C(=O)N[C@H](C(=O)O)C(C)CC)C(C)CC)C2 |^1:71|</t>
+        </is>
+      </c>
+      <c r="G1711" t="inlineStr"/>
+      <c r="H1711" t="inlineStr"/>
+      <c r="I1711" t="n">
+        <v>0.5978899268350858</v>
+      </c>
+      <c r="J1711" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1711" t="inlineStr"/>
+    </row>
+    <row r="1712">
+      <c r="A1712" s="1" t="n">
+        <v>1710</v>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2264.png</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr"/>
+      <c r="D1712" t="inlineStr"/>
+      <c r="E1712" t="inlineStr"/>
+      <c r="F1712" t="inlineStr">
+        <is>
+          <t>CC(C)C1=CC=C(C(C)C)C=C1.CC(C)C1=CNC(C(C)C)=C1.CCC[CH]12NC(=O)CNC(=O)[CH]34([NH][Pr])CC(=O)NCCCC[CH]NC5(=O)N([CH]CCCCNC(=O)C3C([CH2][Pr])C4(=O)NC(CC(=O)[NH][Pr])CN1C(CC)C2(N)=O)C1(=O)C2C(=O)N[CH]513CC14=C[N]5([Ac])C678=CC=CC9%10=C16%11%12=C1=C=9476C%11(=C[N]8([Ac])C5%126=CC=C1%10)C23.O</t>
+        </is>
+      </c>
+      <c r="G1712" t="inlineStr"/>
+      <c r="H1712" t="inlineStr"/>
+      <c r="I1712" t="n">
+        <v>6.523575809584198e-05</v>
+      </c>
+      <c r="J1712" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1712" t="inlineStr"/>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="1" t="n">
+        <v>1711</v>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2268.png</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr"/>
+      <c r="D1713" t="inlineStr"/>
+      <c r="E1713" t="inlineStr"/>
+      <c r="F1713" t="inlineStr">
+        <is>
+          <t>CCC(C)C(NC(=O)CCCCCN1C(=O)C=CC1=O)C(=O)NC(CCCNC(N)=O)C(=O)NC1=CC=C2C3=O=C2(O)(OCC[CH]245NC6C2789%10=C2%11%12CN%13%14C%15(=O)C%16%17=C%18%19C=C%13%20%21%22N%13%23CC7%24%25%26=C247%27%28C24%29%30=C%31%32%33C=C(C)C=C2%34%35%36%37%38%39%40=C2%41=C%42%43(C)=C%44(C)=CC%31%45(=C87%34%31%46C=24%3578=C=%36%42=C%41%29%3172(=C%44%37)(=N%38=C%11%20%244C%21%25(=N2%39)C%14%13%224=CC2=C%15%18(C%16OC(=O)C2%19(O)CC)C%17%23=O)C%32%45%439%278%40=C6%125%30%26%10%46%28)C%33)OC2=O=C2(C)COC(=O)CNCC=C13</t>
+        </is>
+      </c>
+      <c r="G1713" t="inlineStr"/>
+      <c r="H1713" t="inlineStr"/>
+      <c r="I1713" t="n">
+        <v>2.29457256418061e-10</v>
+      </c>
+      <c r="J1713" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1713" t="inlineStr"/>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="1" t="n">
+        <v>1712</v>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2272.png</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr"/>
+      <c r="D1714" t="inlineStr"/>
+      <c r="E1714" t="inlineStr"/>
+      <c r="F1714" t="inlineStr">
+        <is>
+          <t>CC(O)C(O)[CH]O.CCO[CH]12C(CO[CH]3456C7C3C7438C5(O)C3457C86C43(O)[CH]54(CC)NC5C6N(C8C9C8%10C98%11%12=C9%13%14(C=O)=C%15(CO%15%16C%15C%16%17[CH]%16(C%18C%19C%18%16N%19347)N%15%173CCC3)C9(=C3CO3[CH]347C[CH]9%15%16(C3C4CN%13)C3[CH]4(O79)C%157OC4%169[CH]7(O)O[CH]39(C)O)=C=%14%108347=C8=C9%10%13(=C8%14%15=C8%16N%17C%18%19%20=C%21%22=C%18%23C=%19=%14%21%18%24=C%14O(CC(=O)CO)C=%20=%11=9=3%14%22%18=C=%15%17%238%104C=%24%16%13)O%127)C56OC(C)=O)O3CC314=O=C241=O=CO1.O.O</t>
+        </is>
+      </c>
+      <c r="G1714" t="inlineStr"/>
+      <c r="H1714" t="inlineStr"/>
+      <c r="I1714" t="n">
+        <v>1.544760348398359e-20</v>
+      </c>
+      <c r="J1714" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1714" t="inlineStr"/>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="1" t="n">
+        <v>1713</v>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2276.png</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr"/>
+      <c r="D1715" t="inlineStr"/>
+      <c r="E1715" t="inlineStr"/>
+      <c r="F1715" t="inlineStr">
+        <is>
+          <t>CCCCCCCCCCCCCC(=O)NCCCC(=O)NCCCCCCCCNCCCOCCC(O)C1C(OC(C)=O)C2O[CH]2(O)C(C(C)O)C2=O=C(=O)(N2)C(CCCNC(C)=O)C[CH]OC2C3=CC(OCCN)=CC(=O)[CH]32[CH]OC(C)(C)CSC1C(O)COCCO1C2=O=C21OCCCNC(=O)CCC1=O=C(=O)(CCCCCCCC)N1</t>
+        </is>
+      </c>
+      <c r="G1715" t="inlineStr"/>
+      <c r="H1715" t="inlineStr"/>
+      <c r="I1715" t="n">
+        <v>8.677377131171291e-08</v>
+      </c>
+      <c r="J1715" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1715" t="inlineStr"/>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="1" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2284.png</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr"/>
+      <c r="D1716" t="inlineStr"/>
+      <c r="E1716" t="inlineStr"/>
+      <c r="F1716" t="inlineStr">
+        <is>
+          <t>C=CCC12N3(C(=O)CN45C67=O=C489%10%11(=O4=C8%12%13=O=9=C=45%12(N6%10)N%13%11)C7N4C(=O)C4NC(=O)C[CH]C(CCC(=O)O)N4C5=O=CC(C[CH]NC(=O)[CH]N6C7=O=C76NC(=O)N6C7=O=C768(C)=O=C6C(C(=O)NC[CH]C(=O)NC(=O)C=CC(=CC=CC)C7=CC=CC=C7)N68)NC54)C4(C)CN4[CH]134NC13(=O)C(NC(=O)NC5(=O)C678C[CH]56(O)(O7)O8)C1(=O)N234</t>
+        </is>
+      </c>
+      <c r="G1716" t="inlineStr"/>
+      <c r="H1716" t="inlineStr"/>
+      <c r="I1716" t="n">
+        <v>1.183474522951222e-10</v>
+      </c>
+      <c r="J1716" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1716" t="inlineStr"/>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="1" t="n">
+        <v>1715</v>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2288.png</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr"/>
+      <c r="D1717" t="inlineStr"/>
+      <c r="E1717" t="inlineStr"/>
+      <c r="F1717" t="inlineStr">
+        <is>
+          <t>CC[CH]1(C)C(CN2CCCC2C(OC)C(C)C(=O)NC(C)C(O)C2=CC=CC=C2)OC1[CH]1(OC)C(O)C(=O)(NCC(=O)OCC2=CC=C(NC(=O)C(C)NCC(NC(=O)CCNC3(=O)CC4C(C)(C)C43(=O)OC)C(C)C)C=C2)C23(C)CC1(C2)C3</t>
+        </is>
+      </c>
+      <c r="G1717" t="inlineStr"/>
+      <c r="H1717" t="inlineStr"/>
+      <c r="I1717" t="n">
+        <v>0.02257684202250967</v>
+      </c>
+      <c r="J1717" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1717" t="inlineStr"/>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="1" t="n">
+        <v>1716</v>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2292.png</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr"/>
+      <c r="D1718" t="inlineStr"/>
+      <c r="E1718" t="inlineStr"/>
+      <c r="F1718" t="inlineStr">
+        <is>
+          <t>[H]C12345CCCC16789%10([H])[H]C261%11%12C7CCCC1382([H])C4(=O)OC1(=O)[CH]346C7CC8N73%13%14C(=O)(C(C=O)CC(C)C)N8437%15CCC3[CH]%137C6347=O=C5(=O=3)(N43[CH]4568C(=O)N[CH]%13%16C(=O)N[CH]%17%18(CSCC%19=CC=CC=C%19)C%19%20=O=C%17(C(=O)OC)(=O=%19)(N%20)N%17C%19(C(C)CC)=O=C%17%18(=O=%19)C(CSC%17=CC=CC=C%17)NC%13(=O)C(NC4(=O)[CH]352(C6%119)C8%12%10)[CH]%16(C)CC)[CH]17%14%15</t>
+        </is>
+      </c>
+      <c r="G1718" t="inlineStr"/>
+      <c r="H1718" t="inlineStr"/>
+      <c r="I1718" t="n">
+        <v>6.316323739774905e-08</v>
+      </c>
+      <c r="J1718" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1718" t="inlineStr"/>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="1" t="n">
+        <v>1717</v>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2300.png</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr"/>
+      <c r="D1719" t="inlineStr"/>
+      <c r="E1719" t="inlineStr"/>
+      <c r="F1719" t="inlineStr">
+        <is>
+          <t>CC(C)=O.CCCCCCCCCCC1=O=C2(=O=C(C(CC)N3C4C3C435=O4=C3C=45CCCCNC(=O)CC3C4C(CC(=O)N5CC5CCCCCCCCC)C34)N2)C1.C[CH]COC[CH]12(C(=O)NC34=C5=C3(CC36=CC3=CC=C6)=O=45)C3OC(=O)[CH]1(NC(=O)[CH]CCCNC)[CH]32COCC(=O)[CH]1(C)C(=O)N12CC2=O.C[CH]NC(=O)C([CH]CC(C)=O)C(N)=O.O</t>
+        </is>
+      </c>
+      <c r="G1719" t="inlineStr"/>
+      <c r="H1719" t="inlineStr"/>
+      <c r="I1719" t="n">
+        <v>1.613604706078868e-11</v>
+      </c>
+      <c r="J1719" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1719" t="inlineStr"/>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="1" t="n">
+        <v>1718</v>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2304.png</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr"/>
+      <c r="D1720" t="inlineStr"/>
+      <c r="E1720" t="inlineStr"/>
+      <c r="F1720" t="inlineStr">
+        <is>
+          <t>[H]C(NC(=O)C1CCCNC=CCCC(NC(C)(C)C)C(=O)NC(C)C(=O)NC(CC2=CNC3=C2C=CC=C3)C(=O)NC(CC2=CNC=N2)C(=O)NC(CC(C)C)C(=O)NCC(=O)NC(CCC(=O)O)C(=O)NC(CC(C)C)C(=O)NC(C(C)C)C(=O)N2[CH]345C67C89=CN%10C%11=C8C6(=C%10N%11)C93[CH]273C426=O=C53(=O=2)N16)C(N)=O</t>
+        </is>
+      </c>
+      <c r="G1720" t="inlineStr"/>
+      <c r="H1720" t="inlineStr"/>
+      <c r="I1720" t="n">
+        <v>0.06873066558445885</v>
+      </c>
+      <c r="J1720" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1720" t="inlineStr"/>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="1" t="n">
+        <v>1719</v>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2308.png</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr"/>
+      <c r="D1721" t="inlineStr"/>
+      <c r="E1721" t="inlineStr"/>
+      <c r="F1721" t="inlineStr">
+        <is>
+          <t>CC(O)[CH]12NC(=O)C(CCCCN)NC(=O)C(CC3=CC=C(NC(=O)C(N)CCC(N)=O)C=C3)NC(=O)C(CC3=CC=C(O)C=C3)NC(=O)C(NC(=O)C(N)CC3=CC=C(Cl)C=C3)CSC[CH]34C5SC3[CH]5(C(=O)NC(CC3=CC=C(O)C=C3)C(N)=O)(NC1=O)N4C2=O</t>
+        </is>
+      </c>
+      <c r="G1721" t="inlineStr"/>
+      <c r="H1721" t="inlineStr"/>
+      <c r="I1721" t="n">
+        <v>0.2666155469904701</v>
+      </c>
+      <c r="J1721" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1721" t="inlineStr"/>
+    </row>
+    <row r="1722">
+      <c r="A1722" s="1" t="n">
+        <v>1720</v>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2312.png</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr"/>
+      <c r="D1722" t="inlineStr"/>
+      <c r="E1722" t="inlineStr"/>
+      <c r="F1722" t="inlineStr">
+        <is>
+          <t>CC[C@H](C)[C@H](N)C(=O)N[C@H](C(=O)N[C@@H](CC(N)=O)C(=O)N[C@@](C)(CCC/C=C\CCC[C](C)NC(=O)[C@H](CC(=O)O)NC(=O)[C@@H](NC(=O)[C@H](C)NC(=O)[C@H](CC(N)=O)NC(=O)[C@H](CCC(N)=O)NC(=O)[C@@H](N)[C@@H](C)O)[C@@H](C)CC)C(=O)N[C@H](C(=O)N[C@@H](CC(N)=O)C(=O)C(C)(C)C)C(C)C)[C@@H](C)O |^1:31|</t>
+        </is>
+      </c>
+      <c r="G1722" t="inlineStr"/>
+      <c r="H1722" t="inlineStr"/>
+      <c r="I1722" t="n">
+        <v>0.521861753979287</v>
+      </c>
+      <c r="J1722" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1722" t="inlineStr"/>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="1" t="n">
+        <v>1721</v>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2320.png</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr"/>
+      <c r="D1723" t="inlineStr"/>
+      <c r="E1723" t="inlineStr"/>
+      <c r="F1723" t="inlineStr">
+        <is>
+          <t>C=C1C2C(N[CH]C3C4C(NC[CH]OC5C(CO[CH]C6C7C[CH]67OC(=O)CC(O)C(CCNC67(=CCC)=O=C6O7)NC6(=O)OC6C(C(N)=O)C(C(N)=O)C6C(NCC)O6C(C)=O)C56=CC=CC=6)N34)C12.CCCCCCCCCCCC(=O)NCCN1C2C(CCOCCCCC=O)C21=O.CCCCOCC(=O)CO1CC1C(=O)(=O)O.O</t>
+        </is>
+      </c>
+      <c r="G1723" t="inlineStr"/>
+      <c r="H1723" t="inlineStr"/>
+      <c r="I1723" t="n">
+        <v>3.835961981135984e-12</v>
+      </c>
+      <c r="J1723" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1723" t="inlineStr"/>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="1" t="n">
+        <v>1722</v>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2324.png</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr"/>
+      <c r="D1724" t="inlineStr"/>
+      <c r="E1724" t="inlineStr"/>
+      <c r="F1724" t="inlineStr">
+        <is>
+          <t>CCCC(NC(=O)C(CC(C)=O)N(CC(C)C)CC12N(C(C)=O)C13(C1C4=CC=CC=C41)N(C1=CC=CC=C1)C23C(C)=O)C(=O)N[CH]12CC(CNC(=O)[CH]34(CC(C)C)C(C(C)C)C3N4CCCNC(=N)N)C13[CH]C2N3C(=O)C(CCC(C)C)NC(=O)[CH]1234NC56(C(C)=O)C17CC18=C9C%10=C%11=C9=CC(=C1)=C8(=C%11)C(=C%10)C[CH]218CC12(N53C(CC)N284)C76(C)=O</t>
+        </is>
+      </c>
+      <c r="G1724" t="inlineStr"/>
+      <c r="H1724" t="inlineStr"/>
+      <c r="I1724" t="n">
+        <v>2.139129758066569e-11</v>
+      </c>
+      <c r="J1724" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1724" t="inlineStr"/>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="1" t="n">
+        <v>1723</v>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2328.png</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr"/>
+      <c r="D1725" t="inlineStr"/>
+      <c r="E1725" t="inlineStr"/>
+      <c r="F1725" t="inlineStr">
+        <is>
+          <t>CC(O)[CH]12NC(=O)C(CCCCN)NC(=O)C(CC3=CC=C(NC(=O)C(N)CCCNC(N)=O)C=C3)NC(=O)C(CC3=CC=C(O)C=C3)NC(=O)C(NC(=O)C(N)CC3=CC=C(Cl)C=C3)CSSC(C(=O)NC(CC3=CC=C(O)C=C3)C(N)=O)[CH]1(O)NC2=O</t>
+        </is>
+      </c>
+      <c r="G1725" t="inlineStr"/>
+      <c r="H1725" t="inlineStr"/>
+      <c r="I1725" t="n">
+        <v>0.1567620404789463</v>
+      </c>
+      <c r="J1725" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1725" t="inlineStr"/>
+    </row>
+    <row r="1726">
+      <c r="A1726" s="1" t="n">
+        <v>1724</v>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2332.png</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr"/>
+      <c r="D1726" t="inlineStr"/>
+      <c r="E1726" t="inlineStr"/>
+      <c r="F1726" t="inlineStr">
+        <is>
+          <t>CCC1(O)C(=O)OCC2=C1C=C1C(N=C34C(=CCCCNCC5=CC=C(NC(=O)C(CC6CC6NC(=O)CNC(=O)CNC(=O)CNC(=O)CN(C)C(=O)CN(C)C(=O)COC(=O)CNC(=O)CN(C)C(=O)C(=O)N(C)C(=O)CNC(C)=O)NC(=O)C(NC(=O)CCCCCN6C(=O)C=CC6=O)C(C)C)C=C5)C5=C3C(C)=C54)=CCN1C2=O</t>
+        </is>
+      </c>
+      <c r="G1726" t="inlineStr"/>
+      <c r="H1726" t="inlineStr"/>
+      <c r="I1726" t="n">
+        <v>0.01778187016379393</v>
+      </c>
+      <c r="J1726" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1726" t="inlineStr"/>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="1" t="n">
+        <v>1725</v>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2340.png</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr"/>
+      <c r="D1727" t="inlineStr"/>
+      <c r="E1727" t="inlineStr"/>
+      <c r="F1727" t="inlineStr">
+        <is>
+          <t>[H]C1CCCN1C(=O)C(CC(N)=O)NC(=O)C1CN1(C)C(=O)C(CC=O)NC(=O)CNCC(NC(=O)C(CC(C)C)NC(=O)C(CCC)N(C)C(=O)C(CCCC)N(C)[CH]CC12=C(C=CC=C)N(CC(=O)O)C1=C2NC(=O)NC(CC1=C(C=CC=C)N1)C(=O)NC12([H])[H]C13C1[CH]([Li])CN132)C(=O)NCC(N)=O</t>
+        </is>
+      </c>
+      <c r="G1727" t="inlineStr"/>
+      <c r="H1727" t="inlineStr"/>
+      <c r="I1727" t="n">
+        <v>0.02786304593807742</v>
+      </c>
+      <c r="J1727" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1727" t="inlineStr"/>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="1" t="n">
+        <v>1726</v>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2344.png</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr"/>
+      <c r="D1728" t="inlineStr"/>
+      <c r="E1728" t="inlineStr"/>
+      <c r="F1728" t="inlineStr">
+        <is>
+          <t>CC(O)C1NC(=O)C(CCCCN)NC(=O)C(CC2=CC=C(NCCN3CCOCC3)C=C2)NC(=O)C(CC2=CC=C(O)C=C2)NC(=O)C(NC(=O)C(N)CC2=CC=C(Cl)C=C2)CSSCC(C(=O)NC2CC3=CC=C(O)C=C3NC2(N)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1728" t="inlineStr"/>
+      <c r="H1728" t="inlineStr"/>
+      <c r="I1728" t="n">
+        <v>0.7489322536899075</v>
+      </c>
+      <c r="J1728" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1728" t="inlineStr"/>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="1" t="n">
+        <v>1727</v>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261010T220456_3/rb_2348.png</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr"/>
+      <c r="D1729" t="inlineStr"/>
+      <c r="E1729" t="inlineStr"/>
+      <c r="F1729" t="inlineStr">
+        <is>
+          <t>CC(C)CNC(C)CC(=O)NC(=O)C1CC(N)(=O)=O=C(N)CC(C(=O)NC(C(=O)N[CH]C(=O)NC(=O)[CH]CCCCCCOCCOCC23=O=C(N2)C3OCCOCC=O)C(C)O)N1.CCCCCCCCCC(NCC(=O)NCCOCCOCC(=O)NCCCCOCC(=O)NCCCC1C2COCCC12C1=C=C(NC(=O)NC2(=O)=O=C2N)C=1)C(=O)O</t>
+        </is>
+      </c>
+      <c r="G1729" t="inlineStr"/>
+      <c r="H1729" t="inlineStr"/>
+      <c r="I1729" t="n">
+        <v>0.0009220530976184253</v>
+      </c>
+      <c r="J1729" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1729" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
+++ b/benchmarks/published_runs/sonnet55_api_superatoms/cxmolscribe/Completed_LowConfidence_CMAGE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1729"/>
+  <dimension ref="A1:K1857"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50592,6 +50592,3718 @@
       </c>
       <c r="K1729" t="inlineStr"/>
     </row>
+    <row r="1730">
+      <c r="A1730" s="1" t="n">
+        <v>1728</v>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2351.png</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr"/>
+      <c r="D1730" t="inlineStr"/>
+      <c r="E1730" t="inlineStr"/>
+      <c r="F1730" t="inlineStr">
+        <is>
+          <t>CCn1c(-c2cccnc2[C@H](C)OC)c2c3cc(ccc31)-c1csc(n1)C[C@H](NC(=O)[C@H]1C[C@@H]1C)C(=O)N1CCC[C@H](N1)C(=O)OCC(C)(C)C2.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1730" t="inlineStr"/>
+      <c r="H1730" t="inlineStr"/>
+      <c r="I1730" t="n">
+        <v>0.8368413219234653</v>
+      </c>
+      <c r="J1730" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1730" t="inlineStr"/>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="1" t="n">
+        <v>1729</v>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2355.png</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr"/>
+      <c r="D1731" t="inlineStr"/>
+      <c r="E1731" t="inlineStr"/>
+      <c r="F1731" t="inlineStr">
+        <is>
+          <t>COC=CC=CCCC1NC(=O)[CH]23CCCCN2C(=O)C(=O)C2(C)(C)COC(=O)C=CCCN4(C)C(=O)[CH]5(CC(C)C)C4N(C)CCC=CC(=O)OCC(C)(C)C2(=O)C(=O)N2CCCCC2C3(=O)NC(CCC2=CC=C(OC)C(OC)=C2)C1C=CNC(=O)CCC(=O)NCC(=O)N(C)C(CC1=CC=CC=C1)C(=O)N1CCCC1C(=O)N5C</t>
+        </is>
+      </c>
+      <c r="G1731" t="inlineStr"/>
+      <c r="H1731" t="inlineStr"/>
+      <c r="I1731" t="n">
+        <v>0.02135713964825246</v>
+      </c>
+      <c r="J1731" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1731" t="inlineStr"/>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="1" t="n">
+        <v>1730</v>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2371.png</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr"/>
+      <c r="D1732" t="inlineStr"/>
+      <c r="E1732" t="inlineStr"/>
+      <c r="F1732" t="inlineStr">
+        <is>
+          <t>CCN12C34=C56C=C(C=C3)C3=CSC(=N3)CC(NC(=O)C3CCCCC3)C(=O)N3CCCC(N3)C(=O)OCC(C)(C)CC53=C15=C6=C=32(N4)C12=C3N4=CC=C1C51=C45(N=CC=C21)[CH](C)(OC)C[CH]35OC.S.S</t>
+        </is>
+      </c>
+      <c r="G1732" t="inlineStr"/>
+      <c r="H1732" t="inlineStr"/>
+      <c r="I1732" t="n">
+        <v>0.01145046907967703</v>
+      </c>
+      <c r="J1732" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1732" t="inlineStr"/>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="1" t="n">
+        <v>1731</v>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2375.png</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr"/>
+      <c r="D1733" t="inlineStr"/>
+      <c r="E1733" t="inlineStr"/>
+      <c r="F1733" t="inlineStr">
+        <is>
+          <t>[H]C1(C2=CC(C34=C5C=C3CC(C)(C)COC3(=O)[CH]678CCC9N%10%11N6%12%13[CH]36%14(CCC3N%12%15%16%17N6N93%136%12(CCC7%14)C%15(=O)[CH]379%13NC%14(=O)[CH]%15(C(=O)N3[CH]3([CH]7(OCC)C7=COC(=N7)C7=CC=C(C=C7)N4CC)C%109%166=O=C3%11%13%17%12=O)C(C)[CH]%15(C)[CH]%143C(C)C3C)C8(=O)OCC(C)(C)C5)=C(C(C)OC)N=C2)CCN2CCOCC2C1</t>
+        </is>
+      </c>
+      <c r="G1733" t="inlineStr"/>
+      <c r="H1733" t="inlineStr"/>
+      <c r="I1733" t="n">
+        <v>0.0004523750554595651</v>
+      </c>
+      <c r="J1733" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1733" t="inlineStr"/>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="1" t="n">
+        <v>1732</v>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2391.png</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr"/>
+      <c r="D1734" t="inlineStr"/>
+      <c r="E1734" t="inlineStr"/>
+      <c r="F1734" t="inlineStr">
+        <is>
+          <t>C#Cc1cccc(Nc2ncnc3cc(OCCOC)c(OCCN4CCN(C(=O)CCC[C@@H]5/C=C(\C)C[C@H](C)C[C@H](OC)[C@H]6O[C@@](O)(C(=O)C(=O)N7CCCC[C@H]7C(=O)O[C@H](C(C)C[C@@H]7CC[C@@H](O)[C@H](OC)C7)[C@H](C)[C@@H](O)CC5=O)[C@H](C)C[C@@H]6OC)CC4)cc23)c1</t>
+        </is>
+      </c>
+      <c r="G1734" t="inlineStr"/>
+      <c r="H1734" t="inlineStr"/>
+      <c r="I1734" t="n">
+        <v>0.7049683384558627</v>
+      </c>
+      <c r="J1734" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1734" t="inlineStr"/>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="1" t="n">
+        <v>1733</v>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2403.png</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr"/>
+      <c r="D1735" t="inlineStr"/>
+      <c r="E1735" t="inlineStr"/>
+      <c r="F1735" t="inlineStr">
+        <is>
+          <t>C[C@@H](Cc1cccc(C2(C)CCCC(C)(C)CS(=O)(=O)CCc3c(c(F)cc4[nH]ccc34)Oc3ccc(F)c(c3)-c3nc2nn3C)c1)C(=O)OCCN1CCOCC1</t>
+        </is>
+      </c>
+      <c r="G1735" t="inlineStr"/>
+      <c r="H1735" t="inlineStr"/>
+      <c r="I1735" t="n">
+        <v>0.4643986960330215</v>
+      </c>
+      <c r="J1735" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1735" t="inlineStr"/>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="1" t="n">
+        <v>1734</v>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2407.png</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr"/>
+      <c r="D1736" t="inlineStr"/>
+      <c r="E1736" t="inlineStr"/>
+      <c r="F1736" t="inlineStr">
+        <is>
+          <t>CCN1/C(c2cc(N3CCN(C)CC3)cnc2[C@H](C)OC)=C/CC(C)(C)COC(=O)[C@H]2NN(C(=O)[C@@H](NC(=O)[C@H]3C[C@@H]3C)Cc3nc(cs3)-c3ccc1cc3)C1CC2C1</t>
+        </is>
+      </c>
+      <c r="G1736" t="inlineStr"/>
+      <c r="H1736" t="inlineStr"/>
+      <c r="I1736" t="n">
+        <v>0.4367614435820963</v>
+      </c>
+      <c r="J1736" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1736" t="inlineStr"/>
+    </row>
+    <row r="1737">
+      <c r="A1737" s="1" t="n">
+        <v>1735</v>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2411.png</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr"/>
+      <c r="D1737" t="inlineStr"/>
+      <c r="E1737" t="inlineStr"/>
+      <c r="F1737" t="inlineStr">
+        <is>
+          <t>CCN12C(C3=C(C(C)OC)N=CC=C3)=C34CC(C)(C)COC(=O)C5CCCN(N5)C(=O)C(NS(=O)(=O)C5=CN(C)C(C)=N5)CC5=CC6(=CC(O)=C5)C5=C7C38=C1C=C5C761=CC4=C=82C=C1</t>
+        </is>
+      </c>
+      <c r="G1737" t="inlineStr"/>
+      <c r="H1737" t="inlineStr"/>
+      <c r="I1737" t="n">
+        <v>0.2329005495534057</v>
+      </c>
+      <c r="J1737" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1737" t="inlineStr"/>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="1" t="n">
+        <v>1736</v>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2415.png</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr"/>
+      <c r="D1738" t="inlineStr"/>
+      <c r="E1738" t="inlineStr"/>
+      <c r="F1738" t="inlineStr">
+        <is>
+          <t>CN1N=C23N=C1C1=CC(=CC=C1F)C(O)C1=C(F)C=C4NC=CC4=C14CCS(=O)(=O)CC(C)(C)CCCC215(C)CC3(C1CCC(C)(C)CS(=O)(=O)CC4)C51=CC(CCC(=O)O)=CC=C1</t>
+        </is>
+      </c>
+      <c r="G1738" t="inlineStr"/>
+      <c r="H1738" t="inlineStr"/>
+      <c r="I1738" t="n">
+        <v>0.2837567910718328</v>
+      </c>
+      <c r="J1738" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1738" t="inlineStr"/>
+    </row>
+    <row r="1739">
+      <c r="A1739" s="1" t="n">
+        <v>1737</v>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2423.png</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr"/>
+      <c r="D1739" t="inlineStr"/>
+      <c r="E1739" t="inlineStr"/>
+      <c r="F1739" t="inlineStr">
+        <is>
+          <t>CCN12C(C3=C(C(C)OC)N=CC=C3)=C3=C1(C1=C(C(C)OC)N=CC=C1)=C1CC(C)(C)COC(=O)C4CCCN(N4)C(=O)C(NC(=O)C4CC4C)CC4=CC(=CC(O)=C4)C4=CC13=C2C=C4</t>
+        </is>
+      </c>
+      <c r="G1739" t="inlineStr"/>
+      <c r="H1739" t="inlineStr"/>
+      <c r="I1739" t="n">
+        <v>0.2775531123007234</v>
+      </c>
+      <c r="J1739" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1739" t="inlineStr"/>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="1" t="n">
+        <v>1738</v>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2435.png</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr"/>
+      <c r="D1740" t="inlineStr"/>
+      <c r="E1740" t="inlineStr"/>
+      <c r="F1740" t="inlineStr">
+        <is>
+          <t>CCN12C3=C4C=C(C=C3)C3=CN=C(CC(NC(=O)C(C(C)C)N(C)C(=O)C5(C)CCN(C(=O)C#CC(C)(C)N6CCC6)C5)C(=O)N5CCCC(N5)C(=O)OCC(C)(C)CC45=C14(C1=C(C(C)OC)N=CC=C1)=C2(C1=C(C(C)OC)N=CC=C1)=C54)O3</t>
+        </is>
+      </c>
+      <c r="G1740" t="inlineStr"/>
+      <c r="H1740" t="inlineStr"/>
+      <c r="I1740" t="n">
+        <v>0.2546527301191379</v>
+      </c>
+      <c r="J1740" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1740" t="inlineStr"/>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="1" t="n">
+        <v>1739</v>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2439.png</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr"/>
+      <c r="D1741" t="inlineStr"/>
+      <c r="E1741" t="inlineStr"/>
+      <c r="F1741" t="inlineStr">
+        <is>
+          <t>CCOC(=O)C(C)CC1=CC=CC(C2(NC(=O)OCC3=CC=CC=C3)CCCC(C)(C)CS(=O)(=O)CCC3=C4C=CNC4=CC(F)=C3OC3=CC=C(F)C(=C3)C34=NC2=N=3N4C)=C1</t>
+        </is>
+      </c>
+      <c r="G1741" t="inlineStr"/>
+      <c r="H1741" t="inlineStr"/>
+      <c r="I1741" t="n">
+        <v>0.4154080736354795</v>
+      </c>
+      <c r="J1741" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1741" t="inlineStr"/>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="1" t="n">
+        <v>1740</v>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2443.png</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr"/>
+      <c r="D1742" t="inlineStr"/>
+      <c r="E1742" t="inlineStr"/>
+      <c r="F1742" t="inlineStr">
+        <is>
+          <t>C=CC(=O)NCCNC=NCNCCC(=O)N123CCN4C5(=O)CC6C789C(CC4(=O)N54(CC1)C1C2C4C13)C612C7C34=C(C)C[CH]5(C)C[CH]6(OC)C7OC(O)C(=O)C(=O)N%10CCCCC%10C(=O)O[CH]%10([CH]CC%11CCC(O)C%12OCO(C)C%11%12)C(C)[CH]%11(O)C%12C%13(=O)[CH]381C(=O)(C%11[CH]%12(O)C%10C)[CH]%13492C=C(C)C5C(C)C6C7OC</t>
+        </is>
+      </c>
+      <c r="G1742" t="inlineStr"/>
+      <c r="H1742" t="inlineStr"/>
+      <c r="I1742" t="n">
+        <v>0.0001999911692722091</v>
+      </c>
+      <c r="J1742" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1742" t="inlineStr"/>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="1" t="n">
+        <v>1741</v>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2455.png</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr"/>
+      <c r="D1743" t="inlineStr"/>
+      <c r="E1743" t="inlineStr"/>
+      <c r="F1743" t="inlineStr">
+        <is>
+          <t>C=CC(=O)NCCC1C23=O=C14(=O)N2(C)[CH]1256C(=O)NC(CC7=CC(C8=CC9=C(C=C8)N(CC)C(C8=CC(COC)=C(CN(C)C)C=C8)=C9CC(C)(C)C)=CC(O)=C7)NC1(=O)[CH](C2(C)C)(C5(C)C)N346C.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1743" t="inlineStr"/>
+      <c r="H1743" t="inlineStr"/>
+      <c r="I1743" t="n">
+        <v>0.08101359497783914</v>
+      </c>
+      <c r="J1743" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1743" t="inlineStr"/>
+    </row>
+    <row r="1744">
+      <c r="A1744" s="1" t="n">
+        <v>1742</v>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2459.png</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr"/>
+      <c r="D1744" t="inlineStr"/>
+      <c r="E1744" t="inlineStr"/>
+      <c r="F1744" t="inlineStr">
+        <is>
+          <t>[H]N1C(=O)C(C(C)C)N(C)C(=O)C(C(C)CC)OC(=O)C(C(C)C)N(C)C(=O)C(CC(C)C)N([H])C(=O)C(C(C)C)N2(C)C(=O)C2(C(C)CC)N([H])C(=O)C2CCCN2C(=O)C(CC2=CC=CC=C2)N(C)C(=O)C1CC1=CC=CC=C1</t>
+        </is>
+      </c>
+      <c r="G1744" t="inlineStr"/>
+      <c r="H1744" t="inlineStr"/>
+      <c r="I1744" t="n">
+        <v>0.6185282215034793</v>
+      </c>
+      <c r="J1744" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1744" t="inlineStr"/>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="1" t="n">
+        <v>1743</v>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2463.png</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr"/>
+      <c r="D1745" t="inlineStr"/>
+      <c r="E1745" t="inlineStr"/>
+      <c r="F1745" t="inlineStr">
+        <is>
+          <t>CCCCCNC=CC=CC[CH]12NC3(=O)[CH]4(CC5=CC=C(O)C=C5)NC(=O)[CH]56(NC(=O)C(N)CC7=CC=C(Cl)C=C7)C7SSC[CH]89NC(=O)[CH]NC(=O)C(CCCCN)NC1(=O)C(NC4(=O)[CH]3(CC1=CC=C(O)C=C1)NC5(=O)C7C6SSC8[CH]C9(=O)NC(CC1=CC=C(O)C=C1)C(N)=O)C2C1=CC=C(NCCCCC)C=C1</t>
+        </is>
+      </c>
+      <c r="G1745" t="inlineStr"/>
+      <c r="H1745" t="inlineStr"/>
+      <c r="I1745" t="n">
+        <v>0.03084890073441612</v>
+      </c>
+      <c r="J1745" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1745" t="inlineStr"/>
+    </row>
+    <row r="1746">
+      <c r="A1746" s="1" t="n">
+        <v>1744</v>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2467.png</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr"/>
+      <c r="D1746" t="inlineStr"/>
+      <c r="E1746" t="inlineStr"/>
+      <c r="F1746" t="inlineStr">
+        <is>
+          <t>CCCCC1C2(=O)N3C4C(C5=CC6=C(C=CC=C6)C=C5)[CH]356(CC3=CC7=C(C=CC=C7)C=C3)NC(=O)[CH]2(CCCC)N1(C)C(=O)COCC=CC(CCC1=CC(OC)=C(OC)C(O)=C1)OC(=O)C1CCCCN1C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)CNC(=O)[CH]12(COC(C)(C)C)C(O)C3N17(C)C5(=O)N32(C)C476=O</t>
+        </is>
+      </c>
+      <c r="G1746" t="inlineStr"/>
+      <c r="H1746" t="inlineStr"/>
+      <c r="I1746" t="n">
+        <v>0.04441107242907606</v>
+      </c>
+      <c r="J1746" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1746" t="inlineStr"/>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="1" t="n">
+        <v>1745</v>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2479.png</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr"/>
+      <c r="D1747" t="inlineStr"/>
+      <c r="E1747" t="inlineStr"/>
+      <c r="F1747" t="inlineStr">
+        <is>
+          <t>Cc1c(CCOc2c(-c3ccc4ncc(CN(C)C(=O)CNC(=O)[C@H](Cc5ccccc5)NC(=O)CNC(=O)CNC(=O)CCCCCN5C(=O)C=CC5=O)n4c3)ccc(F)c2F)c(C(O)C(C)(C)C)nn1C</t>
+        </is>
+      </c>
+      <c r="G1747" t="inlineStr"/>
+      <c r="H1747" t="inlineStr"/>
+      <c r="I1747" t="n">
+        <v>0.7485156989727315</v>
+      </c>
+      <c r="J1747" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1747" t="inlineStr"/>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="1" t="n">
+        <v>1746</v>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2487.png</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr"/>
+      <c r="D1748" t="inlineStr"/>
+      <c r="E1748" t="inlineStr"/>
+      <c r="F1748" t="inlineStr">
+        <is>
+          <t>CCN1C23=C4=C5(=C6CC(C)(C)COC(=O)C7CCCN(N7)C(=O)C(NC(=O)C7CCCC7C(F)F)CC7=NC(=CS7)C7=CC64=C1(C=C7)N25CC)C1=C245N6=C(=N2=CC=C1)C=CC3=C6[CH]41C[CH]5(C)(OC)O1C.S.S</t>
+        </is>
+      </c>
+      <c r="G1748" t="inlineStr"/>
+      <c r="H1748" t="inlineStr"/>
+      <c r="I1748" t="n">
+        <v>0.006256662700782688</v>
+      </c>
+      <c r="J1748" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1748" t="inlineStr"/>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="1" t="n">
+        <v>1747</v>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2491.png</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr"/>
+      <c r="D1749" t="inlineStr"/>
+      <c r="E1749" t="inlineStr"/>
+      <c r="F1749" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC12=NC345=C67C(=CC(C(N)=O)=C3)OCC3COC8=CC(C(=O)NC9CCC(C(=O)O)CC9)=CC9%10=C8%11N(CC=CCN16C1=C(N4)C5=C(C(N)=O)C=C1OCC(N1CC4CCC(C1)O4)N31CC3CCC(C1)O3)C13(=N9)=N%10=C(NC(=O)C4=CC(C)=NN4(CC)C4(=CC(C)=NN4CC)C(=O)N1)N%113CC=CCN27</t>
+        </is>
+      </c>
+      <c r="G1749" t="inlineStr"/>
+      <c r="H1749" t="inlineStr"/>
+      <c r="I1749" t="n">
+        <v>0.0315070505519489</v>
+      </c>
+      <c r="J1749" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1749" t="inlineStr"/>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="1" t="n">
+        <v>1748</v>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2503.png</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr"/>
+      <c r="D1750" t="inlineStr"/>
+      <c r="E1750" t="inlineStr"/>
+      <c r="F1750" t="inlineStr">
+        <is>
+          <t>CC(C)C1NC2(=O)[CH]3(CCCCN)NC4(=O)[CH]5(CC6=CC=C(C(N)=O)C=C6)NC6(=O)[CH]7(CC8=CC=C(O)C=C8)NC8(=O)C9C%10C=CC[CH]NC1(=O)C(C(C)C)NC3(=O)[CH]2(CCCCN)NC5(=O)[CH]4(CC1=CC=C(C(N)=O)C=C1)NC7(=O)[CH]6(CC1=CC=C(O)C=C1)NC9(=O)[CH]%108NC(=O)C(N)CC1=CC=C(Cl)C=C1</t>
+        </is>
+      </c>
+      <c r="G1750" t="inlineStr"/>
+      <c r="H1750" t="inlineStr"/>
+      <c r="I1750" t="n">
+        <v>0.003213209531069947</v>
+      </c>
+      <c r="J1750" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1750" t="inlineStr"/>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="1" t="n">
+        <v>1749</v>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2527.png</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr"/>
+      <c r="D1751" t="inlineStr"/>
+      <c r="E1751" t="inlineStr"/>
+      <c r="F1751" t="inlineStr">
+        <is>
+          <t>CCN12C3=C45C=C(C=C3)C3=CSC(=N3)CC(NC(=O)N3CCN(C)CC3C)C(=O)N36CCC[CH]C(=O)OCC(C)(C)C7C4=C14=C75(=C2C12=C57(C(C)OC)N=CC89=C1C41=C(N5=CC(=C=812)N1CCN(C)CC1N91CCN(C)CC1)[CH]7(C)OC)CC(C)(C)COC(=O)C(CCC3)N6.S.S</t>
+        </is>
+      </c>
+      <c r="G1751" t="inlineStr"/>
+      <c r="H1751" t="inlineStr"/>
+      <c r="I1751" t="n">
+        <v>0.0364698402461902</v>
+      </c>
+      <c r="J1751" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1751" t="inlineStr"/>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2539.png</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr"/>
+      <c r="D1752" t="inlineStr"/>
+      <c r="E1752" t="inlineStr"/>
+      <c r="F1752" t="inlineStr">
+        <is>
+          <t>CCn1c(-c2cc(N3CCN(C)CC3)cnc2[C@H](C)OC)c2c3cc(ccc31)-c1csc(n1)C[C@H](NC(=O)[C@H](C(C)C)N(C)C(=O)N1CCC3(CCN(C(=O)/C=C/CF)C3)CC1)C(=O)N1CCC[C@H](N1)C(=O)OCC(C)(C)C2.S.S</t>
+        </is>
+      </c>
+      <c r="G1752" t="inlineStr"/>
+      <c r="H1752" t="inlineStr"/>
+      <c r="I1752" t="n">
+        <v>0.7596000857024107</v>
+      </c>
+      <c r="J1752" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1752" t="inlineStr"/>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="1" t="n">
+        <v>1751</v>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2543.png</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr"/>
+      <c r="D1753" t="inlineStr"/>
+      <c r="E1753" t="inlineStr"/>
+      <c r="F1753" t="inlineStr">
+        <is>
+          <t>[2H]C([2H])([2H])C(COCC(CS(=O)(=O)CC(C([2H])([2H])[2H])(C([2H])([2H])[2H])C([2H])([2H])[2H])(C([2H])([2H])[2H])C([2H])([2H])[2H])(C1=CC(CC(C)C(=O)O)=CC=C1)C1=NN(C)C2(=N1)C13=CC=C(F)C12=C3</t>
+        </is>
+      </c>
+      <c r="G1753" t="inlineStr"/>
+      <c r="H1753" t="inlineStr"/>
+      <c r="I1753" t="n">
+        <v>0.1278137094053041</v>
+      </c>
+      <c r="J1753" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1753" t="inlineStr"/>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="1" t="n">
+        <v>1752</v>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2547.png</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr"/>
+      <c r="D1754" t="inlineStr"/>
+      <c r="E1754" t="inlineStr"/>
+      <c r="F1754" t="inlineStr">
+        <is>
+          <t>CCN1CC(C(=O)NC2CC3=NC(=CS3)C3=CC45=C(C=C3)N3(CC)C(C6=C(C(C)OC)N=CC=C6)=C4C4C5(=C3C3=C(C(C)OC)N=CC=C3)CC4(C)(C)COC(=O)C3CCCN(N3)C2=O)CC1=O.S.S</t>
+        </is>
+      </c>
+      <c r="G1754" t="inlineStr"/>
+      <c r="H1754" t="inlineStr"/>
+      <c r="I1754" t="n">
+        <v>0.09868856462271502</v>
+      </c>
+      <c r="J1754" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1754" t="inlineStr"/>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="1" t="n">
+        <v>1753</v>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2555.png</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr"/>
+      <c r="D1755" t="inlineStr"/>
+      <c r="E1755" t="inlineStr"/>
+      <c r="F1755" t="inlineStr">
+        <is>
+          <t>CCN1C(C2=C(C(C)OC)N=CC=C2)=C2CC(C)(C)COC(=O)C3CCCN(N3)C(=O)C(NS(=O)(=O)N3CCN(C)CC3)CC3=CC(=CC(O)=C3)C34=CC25=C1(C=C3)C=C45</t>
+        </is>
+      </c>
+      <c r="G1755" t="inlineStr"/>
+      <c r="H1755" t="inlineStr"/>
+      <c r="I1755" t="n">
+        <v>0.7432083234156498</v>
+      </c>
+      <c r="J1755" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1755" t="inlineStr"/>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="1" t="n">
+        <v>1754</v>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2591.png</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr"/>
+      <c r="D1756" t="inlineStr"/>
+      <c r="E1756" t="inlineStr"/>
+      <c r="F1756" t="inlineStr">
+        <is>
+          <t>C=CC=C[CH]1(CCC2=CC=C(OC)C=C2)OC(=O)[CH]23CC4CC4N2C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)C(CC(C)C)N(C)C(=O)C2CCC45=CC(C(=O)NC6=CN=CC=C6)=CC=C4CC(NC(=O)C(C4=CC=CC=C4)NC(=O)CCC(=O)NC4=CC1(=CC=C4)C(CCC1=CC=C(OC)C(OC)=C1)OC3=O)C(=O)N25</t>
+        </is>
+      </c>
+      <c r="G1756" t="inlineStr"/>
+      <c r="H1756" t="inlineStr"/>
+      <c r="I1756" t="n">
+        <v>0.2887743799015174</v>
+      </c>
+      <c r="J1756" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1756" t="inlineStr"/>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="1" t="n">
+        <v>1755</v>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_0/rb_2595.png</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr"/>
+      <c r="D1757" t="inlineStr"/>
+      <c r="E1757" t="inlineStr"/>
+      <c r="F1757" t="inlineStr">
+        <is>
+          <t>CC(C)SC=CSC=CS.CC1SC23=C[SH]2C13C.CC1SC=C(C2=CSC=C(C(=O)C=CSC=C3SC=C(C(=O)C=CSC=CSC4567=C89%10%11%12%13%14%15%16%17=C%18%19%20%21%22%23%24=C%25%26%27%28%29%30%31%32[SH]8C8%33%34%35%36%37=C%38%39%40(S%18)C%18%41%42=C8%43%44[SH]%38%198C%259%19%38=C%209%25%45%46%47=C8%26%10(=C%19%218%10(S%33%27%11)([SH]%349%28%12)([SH]%35%25%29%13)C%45%30%149=O%11=C%468%31%15%12(=O)=O=9=C%11%47%10%32%16C4%12%22=C5(S6)C7%23=O)S%43%39%38%24C%18%36=C%44%4045S%416C789=C%10%11C%12%13%14=C74%15%16S%125C%106%15(=C8%13%37%17)S%119%42%14%16)SC34=C35C6=C437SC(C)(C(C)S6)[SH]57)S2)SC1C.O=C1C2=C3456=C1(=C=31(S4)C5=OC16=O)S2</t>
+        </is>
+      </c>
+      <c r="G1757" t="inlineStr"/>
+      <c r="H1757" t="inlineStr"/>
+      <c r="I1757" t="n">
+        <v>1.123351519850123e-09</v>
+      </c>
+      <c r="J1757" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1757" t="inlineStr"/>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="1" t="n">
+        <v>1756</v>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2352.png</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr"/>
+      <c r="D1758" t="inlineStr"/>
+      <c r="E1758" t="inlineStr"/>
+      <c r="F1758" t="inlineStr">
+        <is>
+          <t>CCN12C34=C5=C1(=C1CC(C)(C)COC(=O)C6CCCN(N6)C(=O)C(NC(=O)C6OCCOC6C)CC6=NC(=CS6)C6=CC15=C2(C=C6)N3)C12=C356N7=C8=N3=CC=C1C4(=C7[CH]51C[CH]6(C)(OC)O1C)C2=C8.S.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1758" t="inlineStr"/>
+      <c r="H1758" t="inlineStr"/>
+      <c r="I1758" t="n">
+        <v>0.005379766522242448</v>
+      </c>
+      <c r="J1758" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1758" t="inlineStr"/>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="1" t="n">
+        <v>1757</v>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2360.png</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr"/>
+      <c r="D1759" t="inlineStr"/>
+      <c r="E1759" t="inlineStr"/>
+      <c r="F1759" t="inlineStr">
+        <is>
+          <t>CCN1C2=C3C=C(C=C2)C24=CS[CH]567C89=N2C52(=N4)[CH]845OCC8CCOCC8C8(CCOCC8)CO[CH]928[CH]462C(=O)N4(CCCC(N4)C(=O)OCC(C)(C)CC3=C1C1=C(C(C)OC)N=CC=C1)C(=O)[CH]5871NC(=O)[CH]3(CC3C)[CH]3(C)CC3C(=O)N21.S.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1759" t="inlineStr"/>
+      <c r="H1759" t="inlineStr"/>
+      <c r="I1759" t="n">
+        <v>0.04792684308190849</v>
+      </c>
+      <c r="J1759" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1759" t="inlineStr"/>
+    </row>
+    <row r="1760">
+      <c r="A1760" s="1" t="n">
+        <v>1758</v>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2376.png</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr"/>
+      <c r="D1760" t="inlineStr"/>
+      <c r="E1760" t="inlineStr"/>
+      <c r="F1760" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CC[C@H](C(=O)N(C)[C@H](C(=O)N[C@H]2Cc3cccc(c3)-c3ccc4c(c3)c(c(-c3cccnc3[C@H](C)OC)n4CC)CC(C)(C)COC(=O)[C@@H]3CCCN(N3)C2=O)[C@H](C)C(F)(F)F)C1</t>
+        </is>
+      </c>
+      <c r="G1760" t="inlineStr"/>
+      <c r="H1760" t="inlineStr"/>
+      <c r="I1760" t="n">
+        <v>0.7150401026796303</v>
+      </c>
+      <c r="J1760" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1760" t="inlineStr"/>
+    </row>
+    <row r="1761">
+      <c r="A1761" s="1" t="n">
+        <v>1759</v>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2392.png</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr"/>
+      <c r="D1761" t="inlineStr"/>
+      <c r="E1761" t="inlineStr"/>
+      <c r="F1761" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CCCN(C(=O)N(C)[C@H](C(=O)N[C@H]2Cc3cc(O)cc(c3)-c3ccc4c(c3)c(c(-c3cccnc3[C@H](C)OC)n4CC)CC(C)(C)COC(=O)[C@@H]3CCCN(N3)C2=O)C(C)C)CC1.S.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1761" t="inlineStr"/>
+      <c r="H1761" t="inlineStr"/>
+      <c r="I1761" t="n">
+        <v>0.8147550889813523</v>
+      </c>
+      <c r="J1761" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1761" t="inlineStr"/>
+    </row>
+    <row r="1762">
+      <c r="A1762" s="1" t="n">
+        <v>1760</v>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2396.png</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr"/>
+      <c r="D1762" t="inlineStr"/>
+      <c r="E1762" t="inlineStr"/>
+      <c r="F1762" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CC[C@H]2[C@@H]1CN2C(=O)N(C)[C@H](C(=O)N[C@H]1Cc2nc(cs2)-c2ccc3c(c2)c(c(-c2cccnc2[C@H](C)OC)n3CC)CC(C)(C)COC(=O)[C@@H]2CCCN(N2)C1=O)C(C)C.S.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1762" t="inlineStr"/>
+      <c r="H1762" t="inlineStr"/>
+      <c r="I1762" t="n">
+        <v>0.8356805970855435</v>
+      </c>
+      <c r="J1762" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1762" t="inlineStr"/>
+    </row>
+    <row r="1763">
+      <c r="A1763" s="1" t="n">
+        <v>1761</v>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2404.png</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr"/>
+      <c r="D1763" t="inlineStr"/>
+      <c r="E1763" t="inlineStr"/>
+      <c r="F1763" t="inlineStr">
+        <is>
+          <t>CN[CH]12C(O)C(O)[CH]3(CO)OC1O3C2CCC(=O)NCCNC(=O)CCCOCCCCCCCCC(=O)CCCCCN1C2C(=O)NCC3(=O)C45C6SC4C634(CS)=NC2C(=O)N2(CC12)C(=O)CCCN1(C)C(C)(C)[CH]2(O)N3C6=O=C3(=O)(NC3CC321)C1[CH]2378C6[CH]126(C3N12(C=CC39C=C%10C3=C1=C%109=C2)C76)N8(C12C3C167=C18=C9%10=CC1=C=9C=C%106C=8327)C54.O</t>
+        </is>
+      </c>
+      <c r="G1763" t="inlineStr"/>
+      <c r="H1763" t="inlineStr"/>
+      <c r="I1763" t="n">
+        <v>6.837184805252751e-10</v>
+      </c>
+      <c r="J1763" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1763" t="inlineStr"/>
+    </row>
+    <row r="1764">
+      <c r="A1764" s="1" t="n">
+        <v>1762</v>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2408.png</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr"/>
+      <c r="D1764" t="inlineStr"/>
+      <c r="E1764" t="inlineStr"/>
+      <c r="F1764" t="inlineStr">
+        <is>
+          <t>N=C(N)NCCCC1NC(=O)C(CC2=CC=C(O)C=C2)NC(=O)C(CC(=O)O)NC(=O)CNC1=O.N=C(N)NCCC[CH]NC(=O)[CH]CCCCNC(=O)C1CC2(=O)CC3C(C(=O)C12)C1[CH]245C678=O=C29(=O=6)O26C%10(=O)O[CH]24%11%12(CN24%13%14%15C%16%17%18%19N2%20%21%22%23C%114C%16%13%2024(CN%17%21%11%13%16%20CC%17(=O)=O=C%21%24%25(=O=C%26%27C%28N%18%14%222%11%29%30CN%28%19%234%132%11(O%21C%2924(CN6%12(C4%16)C31%10795)O%26%24%11)C%27%25%20%30)O%17)OC(=O)C%15)O8</t>
+        </is>
+      </c>
+      <c r="G1764" t="inlineStr"/>
+      <c r="H1764" t="inlineStr"/>
+      <c r="I1764" t="n">
+        <v>2.735494460201476e-13</v>
+      </c>
+      <c r="J1764" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1764" t="inlineStr"/>
+    </row>
+    <row r="1765">
+      <c r="A1765" s="1" t="n">
+        <v>1763</v>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2412.png</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr"/>
+      <c r="D1765" t="inlineStr"/>
+      <c r="E1765" t="inlineStr"/>
+      <c r="F1765" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1COC2(CCN(C(=O)N(C)[C@H](C(=O)N[C@H]3CN4CCC=C(C4)c4ccc5c(c4)c(c(-c4cccnc4[C@H](C)OC)n5CC)CC(C)(C)COC(=O)[C@@H]4CCCN(N4)C3=O)C(C)C)CC2)[C@@H]1C.S.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1765" t="inlineStr"/>
+      <c r="H1765" t="inlineStr"/>
+      <c r="I1765" t="n">
+        <v>0.7804513698209291</v>
+      </c>
+      <c r="J1765" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1765" t="inlineStr"/>
+    </row>
+    <row r="1766">
+      <c r="A1766" s="1" t="n">
+        <v>1764</v>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2416.png</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr"/>
+      <c r="D1766" t="inlineStr"/>
+      <c r="E1766" t="inlineStr"/>
+      <c r="F1766" t="inlineStr">
+        <is>
+          <t>CCN12C=C3CC(C)(C)COC(=O)C4CCC5N67N4N5489CCCC(C(=O)OCC(C)(C)CC(=C1C1=C(C(C)OC)N=CC(N5CCN%10CCOCC%10C5)=C1)C31=C2C=CC(=C1)C1=CC=CC(=C1)C[CH](NC(=O)N1CCN(C)CC1C)(C4=O)C68=O)N79.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1766" t="inlineStr"/>
+      <c r="H1766" t="inlineStr"/>
+      <c r="I1766" t="n">
+        <v>0.09113824643262261</v>
+      </c>
+      <c r="J1766" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1766" t="inlineStr"/>
+    </row>
+    <row r="1767">
+      <c r="A1767" s="1" t="n">
+        <v>1765</v>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2420.png</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr"/>
+      <c r="D1767" t="inlineStr"/>
+      <c r="E1767" t="inlineStr"/>
+      <c r="F1767" t="inlineStr">
+        <is>
+          <t>CCN1C(C2=C(C(C)OC)N=CC(N3CCN(C)CC3)=C2)=C2CC(C)(C)COC(=O)C3CCCN(N3)C(=O)C(NC(=O)C3CCC3C#N)CC3=NC4(=CS3)C3=C5C26=C12C=CC54(=C6)C3=C2</t>
+        </is>
+      </c>
+      <c r="G1767" t="inlineStr"/>
+      <c r="H1767" t="inlineStr"/>
+      <c r="I1767" t="n">
+        <v>0.5659510590530604</v>
+      </c>
+      <c r="J1767" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1767" t="inlineStr"/>
+    </row>
+    <row r="1768">
+      <c r="A1768" s="1" t="n">
+        <v>1766</v>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2428.png</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr"/>
+      <c r="D1768" t="inlineStr"/>
+      <c r="E1768" t="inlineStr"/>
+      <c r="F1768" t="inlineStr">
+        <is>
+          <t>CC(C)CC1N2C(=O)CNCC(CC3=CC=CC=C3)NC(=O)C=CC=CCSCCC3(=O)N4(CC(N)=O)CN35(CC(N)=O)C[CH]367(CC8=CC=CC=C8)NC8(=O)CN9%10(C(=O)CCCN)C[CH]%11(CCCCN)NC(=O)CN%12%13%14C[CH]2(CC(C)C)C1%12N(C%13C(=O)N%11C(CCCCN)C9N(C(=O)CCCN)C%10C(=O)N83C(C6C1=CC=CC=C1)C457)C%14(=O)CC1CC1</t>
+        </is>
+      </c>
+      <c r="G1768" t="inlineStr"/>
+      <c r="H1768" t="inlineStr"/>
+      <c r="I1768" t="n">
+        <v>0.0126858574560048</v>
+      </c>
+      <c r="J1768" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1768" t="inlineStr"/>
+    </row>
+    <row r="1769">
+      <c r="A1769" s="1" t="n">
+        <v>1767</v>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2436.png</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr"/>
+      <c r="D1769" t="inlineStr"/>
+      <c r="E1769" t="inlineStr"/>
+      <c r="F1769" t="inlineStr">
+        <is>
+          <t>CCC1(O)C(=O)OCC2=C1C=C1C3=NC4=CC(F)=C(C)C=C4C(CNC(=O)NCCOCC4C567=O=C4(=O=5)(N6)C7NC(=O)C(CC4=CC=CC=C4)NC(=O)CNC(=O)CNC(=O)CCOCCOCCOCCN4C(=O)C=CC4=O)=C3CN1C2=O</t>
+        </is>
+      </c>
+      <c r="G1769" t="inlineStr"/>
+      <c r="H1769" t="inlineStr"/>
+      <c r="I1769" t="n">
+        <v>0.4687174569077772</v>
+      </c>
+      <c r="J1769" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1769" t="inlineStr"/>
+    </row>
+    <row r="1770">
+      <c r="A1770" s="1" t="n">
+        <v>1768</v>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2444.png</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr"/>
+      <c r="D1770" t="inlineStr"/>
+      <c r="E1770" t="inlineStr"/>
+      <c r="F1770" t="inlineStr">
+        <is>
+          <t>CCC1CN12C1C2[CH]1(CNC[CH][CH]NC[CH]N[CH]1(C234=O=C56789C%10C%11%12%13%14%15%16CC%10(C2%11)(C5%12)(C6%13)(C7%14)(C8%15)[CH]39%16(C2N[CH]23(CC)CC3C)N4)C2C(CCCC3C4N5C34C534C5C36C537C58C9%10%11C%12(C9%13C%12%109C%13%10%12=O%13%14=C%15%16%17C%18C%15C=%13%18%16%10C=%149%17%12)C53%11C6847)N21)C12(CC1)CO2.O.O.O=C12C345O[CH]36789%10(O)[CH]3%11(O)[CH]6%12%13%14(O)[CH]14376%15O[CH]256(OCCC12N3C4C315C13C6N1C64235)C81234O[CH]15(O2)[CH]3%1212O[CH]51%139(O2)[CH]%114%14%15%10O</t>
+        </is>
+      </c>
+      <c r="G1770" t="inlineStr"/>
+      <c r="H1770" t="inlineStr"/>
+      <c r="I1770" t="n">
+        <v>5.13142619801191e-24</v>
+      </c>
+      <c r="J1770" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1770" t="inlineStr"/>
+    </row>
+    <row r="1771">
+      <c r="A1771" s="1" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2448.png</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr"/>
+      <c r="D1771" t="inlineStr"/>
+      <c r="E1771" t="inlineStr"/>
+      <c r="F1771" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CCO[C@@]2(CCN(C(=O)N(C)[C@H](C(=O)N[C@H]3Cc4nc(cs4)-c4ccc5c(c4)c(c(-c4cccnc4[C@H](C)OC)n5CC(F)(F)F)CC(C)(C)COC(=O)[C@@H]4CCCN(N4)C3=O)C(C)C)C2)C1.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1771" t="inlineStr"/>
+      <c r="H1771" t="inlineStr"/>
+      <c r="I1771" t="n">
+        <v>0.8370848593982799</v>
+      </c>
+      <c r="J1771" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1771" t="inlineStr"/>
+    </row>
+    <row r="1772">
+      <c r="A1772" s="1" t="n">
+        <v>1770</v>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2452.png</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr"/>
+      <c r="D1772" t="inlineStr"/>
+      <c r="E1772" t="inlineStr"/>
+      <c r="F1772" t="inlineStr">
+        <is>
+          <t>C[C@@H](O)[C@@H]1NC(=O)[C@H](CCCCN)NC(=O)[C@@H](Cc2ccc(NC(=O)[C@@H](N)CCCCN)cc2)NC(=O)[C@H](Cc2ccc(O)cc2)NC(=O)[C@H](NC(=O)[C@@H](N)Cc2ccc(Cl)cc2)CSSC[C@@H](C(=O)N[C@H](Cc2ccc(O)cc2)C(N)=O)NC1=O</t>
+        </is>
+      </c>
+      <c r="G1772" t="inlineStr"/>
+      <c r="H1772" t="inlineStr"/>
+      <c r="I1772" t="n">
+        <v>0.8073189925395687</v>
+      </c>
+      <c r="J1772" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1772" t="inlineStr"/>
+    </row>
+    <row r="1773">
+      <c r="A1773" s="1" t="n">
+        <v>1771</v>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2456.png</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr"/>
+      <c r="D1773" t="inlineStr"/>
+      <c r="E1773" t="inlineStr"/>
+      <c r="F1773" t="inlineStr">
+        <is>
+          <t>*C1C(=O)OCCOCCOCCOCCOCCOC23C(COCCOCCOCCOCCOCCOCC(=O)OCC45([H])C6[CH]7(OC(=O)C8([H])CCCCN8C(=O)C(=O)COCC[CH]OC(O)CC=CCC(C)CC(C)C(O)C(O)C(O)C=CC8(*)C9[CH]7(O)[CH]968O)[CH]46(O)O[CH]156)C1C245=C2C6C=N=C=NC64CCN2135 |$OMe;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;Me;;;;;;;;;;;;;;;;;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1773" t="inlineStr"/>
+      <c r="H1773" t="inlineStr"/>
+      <c r="I1773" t="n">
+        <v>9.286061716085153e-07</v>
+      </c>
+      <c r="J1773" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1773" t="inlineStr"/>
+    </row>
+    <row r="1774">
+      <c r="A1774" s="1" t="n">
+        <v>1772</v>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2460.png</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr"/>
+      <c r="D1774" t="inlineStr"/>
+      <c r="E1774" t="inlineStr"/>
+      <c r="F1774" t="inlineStr">
+        <is>
+          <t>CCN1C=C2C=C3C=C45=C36=C3[SH]4C(=N6)(CC(NC(=O)N4CCOCC4C)C(=O)N4CCCC(N4)C(=O)OCC(C)(C)CC2=C1C1=C(C(C)OC)N=CC(N2CCN(C)CC2)=C1)[SH]35.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1774" t="inlineStr"/>
+      <c r="H1774" t="inlineStr"/>
+      <c r="I1774" t="n">
+        <v>0.4674008562642531</v>
+      </c>
+      <c r="J1774" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1774" t="inlineStr"/>
+    </row>
+    <row r="1775">
+      <c r="A1775" s="1" t="n">
+        <v>1773</v>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2464.png</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr"/>
+      <c r="D1775" t="inlineStr"/>
+      <c r="E1775" t="inlineStr"/>
+      <c r="F1775" t="inlineStr">
+        <is>
+          <t>C=CC=C1NC=C1N[CH]N1=O=C1[CH]CCCNCC(CC1CCC1N)C12345=O=C67(=O=1)(N1CN2[CH]163CC)[CH]412368C4C9CC(C)C91[CH]47519%10%11N(C4(=O)CC5CC(=O)N7CC%12(C%13C%14%15%16%17=C%18%19%20=C%14%21%22=CC=CN%14C=CC=CC%23=C%14N(=C%23)C=CC=C%21%18C%19%15%14%18=C%16C=C%15C=CC=CC%15%16=C%20%14N%13%12%16%22%18%17)N(C%12=C(C)C%13(N%14%15C=CC=CC%14=C%15)=CC=C=%13%12)CCC%12NC7(=O)C5CCC(=O)(N21)C%124C)C39=O=C6%10(=O)N8%11</t>
+        </is>
+      </c>
+      <c r="G1775" t="inlineStr"/>
+      <c r="H1775" t="inlineStr"/>
+      <c r="I1775" t="n">
+        <v>3.235967036140597e-10</v>
+      </c>
+      <c r="J1775" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1775" t="inlineStr"/>
+    </row>
+    <row r="1776">
+      <c r="A1776" s="1" t="n">
+        <v>1774</v>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2472.png</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr"/>
+      <c r="D1776" t="inlineStr"/>
+      <c r="E1776" t="inlineStr"/>
+      <c r="F1776" t="inlineStr">
+        <is>
+          <t>CCn1c(-c2cccnc2[C@H](C)OC)c2c3cc(ccc31)-c1csc(n1)C[C@H](NC(=O)[C@H](C(C)C)N(C)C(=O)N1CCC13CN(C(=O)/C=C/CN(C)C)C3)C(=O)N1CCC[C@H](N1)C(=O)OCC(C)(C)C2.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1776" t="inlineStr"/>
+      <c r="H1776" t="inlineStr"/>
+      <c r="I1776" t="n">
+        <v>0.811419524464953</v>
+      </c>
+      <c r="J1776" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1776" t="inlineStr"/>
+    </row>
+    <row r="1777">
+      <c r="A1777" s="1" t="n">
+        <v>1775</v>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2484.png</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr"/>
+      <c r="D1777" t="inlineStr"/>
+      <c r="E1777" t="inlineStr"/>
+      <c r="F1777" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CCC(C(=O)N(C)C(C(=O)NC2CC3=CC=CC(=C3)C3=CC4=C5(C=C3)N(CC#CC)C(C3=C(C(C)OC)N=CC=C3)(=C4CC(C)(C)COC(=O)C3CCCN(N3)C2=O)N5CC#CC)C(C)C)C1.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1777" t="inlineStr"/>
+      <c r="H1777" t="inlineStr"/>
+      <c r="I1777" t="n">
+        <v>0.3416046976002618</v>
+      </c>
+      <c r="J1777" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1777" t="inlineStr"/>
+    </row>
+    <row r="1778">
+      <c r="A1778" s="1" t="n">
+        <v>1776</v>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2496.png</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr"/>
+      <c r="D1778" t="inlineStr"/>
+      <c r="E1778" t="inlineStr"/>
+      <c r="F1778" t="inlineStr">
+        <is>
+          <t>C[SiH]1O[SiH]2O[SiH2]3O[SiH2]4O[Si](C)(O[SiH2](O)O[SiH2]O[SiH2]O[Si]5(O[SiH2]O[SiH2]O[SiH2](O)O[Si](C)(O)O[SiH2](O1)O5)O4)O[Si](C)(O[SiH2](C)O[Si](C)(O)O2)O3</t>
+        </is>
+      </c>
+      <c r="G1778" t="inlineStr"/>
+      <c r="H1778" t="inlineStr"/>
+      <c r="I1778" t="n">
+        <v>0.7371115637594295</v>
+      </c>
+      <c r="J1778" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1778" t="inlineStr"/>
+    </row>
+    <row r="1779">
+      <c r="A1779" s="1" t="n">
+        <v>1777</v>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2500.png</t>
+        </is>
+      </c>
+      <c r="C1779" t="inlineStr"/>
+      <c r="D1779" t="inlineStr"/>
+      <c r="E1779" t="inlineStr"/>
+      <c r="F1779" t="inlineStr">
+        <is>
+          <t>CCO[C@@H]1c2nc(cs2)-c2ccc3c(c2)c(c(-c2cccnc2[C@H](C)OC)n3CC)CC(C)(C)COC(=O)[C@@H]2CCCN(N2)C(=O)[C@H]1NC(=O)[C@H]1[C@H](C)[C@@H]1C(=O)N(C)C.S.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1779" t="inlineStr"/>
+      <c r="H1779" t="inlineStr"/>
+      <c r="I1779" t="n">
+        <v>0.8323271969756373</v>
+      </c>
+      <c r="J1779" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1779" t="inlineStr"/>
+    </row>
+    <row r="1780">
+      <c r="A1780" s="1" t="n">
+        <v>1778</v>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2516.png</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr"/>
+      <c r="D1780" t="inlineStr"/>
+      <c r="E1780" t="inlineStr"/>
+      <c r="F1780" t="inlineStr">
+        <is>
+          <t>C1=CC2=NC(=C1)C1=CN=C(C=C1)OCCOCCOCCOC1=CC=C(C=C1)OCCOCCOCCOC1=CC=C(C=C1)C13=N4C5678=C9%10C(=C1)C51%11(=C=6495C746=C79%12=C85%13=C=45(C7=CC(=N6%13)C4=CC=C(C=C4)OCCOCC4OCC4OC4=CC=C(C=C4)OCCccCOC4=CC=C2C=N4)C9=C%101=C%125=C%11)C=C3</t>
+        </is>
+      </c>
+      <c r="G1780" t="inlineStr"/>
+      <c r="H1780" t="inlineStr"/>
+      <c r="I1780" t="n">
+        <v>0.01048852188572887</v>
+      </c>
+      <c r="J1780" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1780" t="inlineStr"/>
+    </row>
+    <row r="1781">
+      <c r="A1781" s="1" t="n">
+        <v>1779</v>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2520.png</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr"/>
+      <c r="D1781" t="inlineStr"/>
+      <c r="E1781" t="inlineStr"/>
+      <c r="F1781" t="inlineStr">
+        <is>
+          <t>CCN12C=C34C=C1C=C=C1=CC(=CC3=C12)C1=CC(O)=CC(=C1)CC(NC(=O)C(C(C)C)N(C)C(=O)C1CCN(C(=O)C#CC(C)(C)N(C)C)C1)C(=O)N1CCCC(N1)C(=O)OCC(C)(C)C4.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1781" t="inlineStr"/>
+      <c r="H1781" t="inlineStr"/>
+      <c r="I1781" t="n">
+        <v>0.1190851848833307</v>
+      </c>
+      <c r="J1781" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1781" t="inlineStr"/>
+    </row>
+    <row r="1782">
+      <c r="A1782" s="1" t="n">
+        <v>1780</v>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2528.png</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr"/>
+      <c r="D1782" t="inlineStr"/>
+      <c r="E1782" t="inlineStr"/>
+      <c r="F1782" t="inlineStr">
+        <is>
+          <t>[CH]CSSC[C@H](NC(=O)C(NC(=O)[C@@H]1CSSC[CH]C(=O)N[C@@H](C)C(=O)N[C@@H](Cc2c[nH]c3ccccc23)C(=O)N[C@@H](Cc2c[nH]cn2)C(=O)N[C@@H](CC(C)C)C(=O)NCC(=O)N[C@@H](CCC(=O)O)C(=O)N[C@@H](CC(C)C)C(=O)N[C@@H](C(C)C)C(=O)N[C@@H](Cc2c[nH]c3ccccc23)C(=O)N1)[C@@H](C)O)C(=O)C(C)(C)C |^1:18,^2:0|</t>
+        </is>
+      </c>
+      <c r="G1782" t="inlineStr"/>
+      <c r="H1782" t="inlineStr"/>
+      <c r="I1782" t="n">
+        <v>0.830028715348326</v>
+      </c>
+      <c r="J1782" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1782" t="inlineStr"/>
+    </row>
+    <row r="1783">
+      <c r="A1783" s="1" t="n">
+        <v>1781</v>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2540.png</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr"/>
+      <c r="D1783" t="inlineStr"/>
+      <c r="E1783" t="inlineStr"/>
+      <c r="F1783" t="inlineStr">
+        <is>
+          <t>CCN1C(C2=C(C(C)OC)N=CC=C2)=C2CC(C)(C)COC(=O)C3CCCN(N3)C(=O)C(NC(=O)C3(F)CCC3)CC3=NC(=CS3)C34=CC25=C1(C=C3)C=C45.S.S</t>
+        </is>
+      </c>
+      <c r="G1783" t="inlineStr"/>
+      <c r="H1783" t="inlineStr"/>
+      <c r="I1783" t="n">
+        <v>0.6809121284070303</v>
+      </c>
+      <c r="J1783" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1783" t="inlineStr"/>
+    </row>
+    <row r="1784">
+      <c r="A1784" s="1" t="n">
+        <v>1782</v>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2544.png</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr"/>
+      <c r="D1784" t="inlineStr"/>
+      <c r="E1784" t="inlineStr"/>
+      <c r="F1784" t="inlineStr">
+        <is>
+          <t>C[C@H](Cc1cccc(C2(C)CCCC(C)(C)CS(=O)(=O)CCc3c(c(F)cc4[nH]ccc34)Cc3ccc(F)c(c3)-c3nc2nn3C)c1)C(=O)O</t>
+        </is>
+      </c>
+      <c r="G1784" t="inlineStr"/>
+      <c r="H1784" t="inlineStr"/>
+      <c r="I1784" t="n">
+        <v>0.8170731137256627</v>
+      </c>
+      <c r="J1784" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1784" t="inlineStr"/>
+    </row>
+    <row r="1785">
+      <c r="A1785" s="1" t="n">
+        <v>1783</v>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2548.png</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr"/>
+      <c r="D1785" t="inlineStr"/>
+      <c r="E1785" t="inlineStr"/>
+      <c r="F1785" t="inlineStr">
+        <is>
+          <t>CCN12C34=C5C=C(C=C3)C3=CSC(=N3)CC(NC(=O)N3CCC3COC)C(=O)N3CCCC(N3)C(=O)OCC(C)(C)CC5=C1(C1=C(C(C)OC)N=CC(N3CCN(C)CC3)=C1)N42CC.S.S</t>
+        </is>
+      </c>
+      <c r="G1785" t="inlineStr"/>
+      <c r="H1785" t="inlineStr"/>
+      <c r="I1785" t="n">
+        <v>0.4611432792040294</v>
+      </c>
+      <c r="J1785" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1785" t="inlineStr"/>
+    </row>
+    <row r="1786">
+      <c r="A1786" s="1" t="n">
+        <v>1784</v>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2556.png</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr"/>
+      <c r="D1786" t="inlineStr"/>
+      <c r="E1786" t="inlineStr"/>
+      <c r="F1786" t="inlineStr">
+        <is>
+          <t>CC=CC=C1C=CC(F)=C[SH]2(=O)C3=CC=C4(F)C5=C3C436=CC(=CC=C3F)S(=O)C23=C(F)C=C2C(=C3CCS(=O)(=O)CCCC(C)(C3=CC(CC4COC(C)(C)O4)=CC=C3)C3=NN(C)C56=N3)C=CN2S1(=O)=O</t>
+        </is>
+      </c>
+      <c r="G1786" t="inlineStr"/>
+      <c r="H1786" t="inlineStr"/>
+      <c r="I1786" t="n">
+        <v>0.2168690314445248</v>
+      </c>
+      <c r="J1786" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1786" t="inlineStr"/>
+    </row>
+    <row r="1787">
+      <c r="A1787" s="1" t="n">
+        <v>1785</v>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2564.png</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr"/>
+      <c r="D1787" t="inlineStr"/>
+      <c r="E1787" t="inlineStr"/>
+      <c r="F1787" t="inlineStr">
+        <is>
+          <t>CCn1c(-c2cccnc2[C@H](C)OC)c2c3cc(ccc31)-c1csc(n1)C[C@H](NC(=O)[C@H]1CC[C@@H]1C#N)C(=O)N1CCC[C@H](N1)C(=O)OCC(C)(C)C2.S.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1787" t="inlineStr"/>
+      <c r="H1787" t="inlineStr"/>
+      <c r="I1787" t="n">
+        <v>0.8195305597968415</v>
+      </c>
+      <c r="J1787" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1787" t="inlineStr"/>
+    </row>
+    <row r="1788">
+      <c r="A1788" s="1" t="n">
+        <v>1786</v>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2572.png</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr"/>
+      <c r="D1788" t="inlineStr"/>
+      <c r="E1788" t="inlineStr"/>
+      <c r="F1788" t="inlineStr">
+        <is>
+          <t>[H][C@@]1(C[C@@H](C)[C@@H]2C[C@@H](OC)[C@H](C)/C=C(\C)[C@@H](O)[C@@H](OC)C(=O)[C@H](C)C[C@H](C)CC/C=C/CC(C)[C@@H](OC)C[C@]3([H])CC[C@@H](C)[C@@](O)(O3)C(=O)C(=O)N3CCCC[C@@]3(F)C(=O)O2)CC[C@@H](OC(=S)Oc2ccc([N+](=O)[O-])cc2)[C@H](OC)C1</t>
+        </is>
+      </c>
+      <c r="G1788" t="inlineStr"/>
+      <c r="H1788" t="inlineStr"/>
+      <c r="I1788" t="n">
+        <v>0.7388767990868536</v>
+      </c>
+      <c r="J1788" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1788" t="inlineStr"/>
+    </row>
+    <row r="1789">
+      <c r="A1789" s="1" t="n">
+        <v>1787</v>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2588.png</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr"/>
+      <c r="D1789" t="inlineStr"/>
+      <c r="E1789" t="inlineStr"/>
+      <c r="F1789" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1C[C@@H](C(=O)N(C)[C@H](C(=O)N[C@H]2Cc3cccc(c3)-c3ccc4c(c3)c(c(-c3cccnc3[C@H](C)OC)n4CC)CC(C)(C)COC(=O)[C@@H]3CCCN(N3)C2=O)C(C)C)C(C)(C)C1.S.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1789" t="inlineStr"/>
+      <c r="H1789" t="inlineStr"/>
+      <c r="I1789" t="n">
+        <v>0.5222433600104546</v>
+      </c>
+      <c r="J1789" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1789" t="inlineStr"/>
+    </row>
+    <row r="1790">
+      <c r="A1790" s="1" t="n">
+        <v>1788</v>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2592.png</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr"/>
+      <c r="D1790" t="inlineStr"/>
+      <c r="E1790" t="inlineStr"/>
+      <c r="F1790" t="inlineStr">
+        <is>
+          <t>CC#CC(=O)N1CC[C@H](C(=O)N(C)[C@H](C(=O)N[C@H]2Cc3nc(ns3)-c3ccc4c(c3)c(c(-c3cccnc3[C@H](C)OC)n4CC)CC(C)(C)COC(=O)[C@@H]3CCCN(N3)C2=O)C(C)C)C1</t>
+        </is>
+      </c>
+      <c r="G1790" t="inlineStr"/>
+      <c r="H1790" t="inlineStr"/>
+      <c r="I1790" t="n">
+        <v>0.7574502036350426</v>
+      </c>
+      <c r="J1790" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1790" t="inlineStr"/>
+    </row>
+    <row r="1791">
+      <c r="A1791" s="1" t="n">
+        <v>1789</v>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_1/rb_2600.png</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr"/>
+      <c r="D1791" t="inlineStr"/>
+      <c r="E1791" t="inlineStr"/>
+      <c r="F1791" t="inlineStr">
+        <is>
+          <t>CCN12C(C3=C(C(C)OC)N=CC=C3)=CC34=C1C=CC(=C3)C1=CC(=CC(O)=C1)CC(NC(=O)C1CC(=O)N(C)C1C)C(=O)N1CCCC(N1)C(=O)OCC(C)(C)CC4=C2C1=C(C(C)OC)N=CC=C1</t>
+        </is>
+      </c>
+      <c r="G1791" t="inlineStr"/>
+      <c r="H1791" t="inlineStr"/>
+      <c r="I1791" t="n">
+        <v>0.4222008455044047</v>
+      </c>
+      <c r="J1791" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1791" t="inlineStr"/>
+    </row>
+    <row r="1792">
+      <c r="A1792" s="1" t="n">
+        <v>1790</v>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2353.png</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr"/>
+      <c r="D1792" t="inlineStr"/>
+      <c r="E1792" t="inlineStr"/>
+      <c r="F1792" t="inlineStr">
+        <is>
+          <t>CCN12C3=C(C)C45=C1C=CC(=C4)C1=CSC(=N1)CC(NC(=O)C1CC1CO)C(=O)N1CCCC(N1)C(=O)OCC(C)(C)CC5(C)=C2C12=C(C(C)OC)N=CC(N4CCN(C)CC4)=C1C31=C(C(C)OC)N=CC(N3CCN(C)CC3)=C12.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1792" t="inlineStr"/>
+      <c r="H1792" t="inlineStr"/>
+      <c r="I1792" t="n">
+        <v>0.2118688944693231</v>
+      </c>
+      <c r="J1792" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1792" t="inlineStr"/>
+    </row>
+    <row r="1793">
+      <c r="A1793" s="1" t="n">
+        <v>1791</v>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2357.png</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr"/>
+      <c r="D1793" t="inlineStr"/>
+      <c r="E1793" t="inlineStr"/>
+      <c r="F1793" t="inlineStr">
+        <is>
+          <t>CC(C)[C@@H]1NC(=O)[C@@H]2CCCCn3cc(nn3)CC[C@H](NC(=O)[C@H](C)NC(=O)[C@@H](NC(=O)[C@H](CCC(=O)O)NC(C)(C)C)CSC[C@@H](C(=O)N[C@H](C(=O)O)[C@H](C)O)NC(=O)[C@H](Cc3cc4ccccc4cn3)NC1=O)C(=O)N[C@@H](Cc1c[nH]cn1)C(=O)N[C@@H](CC1CC1)C(=O)NCC(=O)N[C@@H](CCC(=O)O)C(=O)N2</t>
+        </is>
+      </c>
+      <c r="G1793" t="inlineStr"/>
+      <c r="H1793" t="inlineStr"/>
+      <c r="I1793" t="n">
+        <v>0.7040299935828741</v>
+      </c>
+      <c r="J1793" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1793" t="inlineStr"/>
+    </row>
+    <row r="1794">
+      <c r="A1794" s="1" t="n">
+        <v>1792</v>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2361.png</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr"/>
+      <c r="D1794" t="inlineStr"/>
+      <c r="E1794" t="inlineStr"/>
+      <c r="F1794" t="inlineStr">
+        <is>
+          <t>CCN1C23=C4=C5(=C6CC(C)(C)COC(=O)C7CCCN(N7)C(=O)C(NC(=O)N7CC(C)C7)CC7=NC(=CS7)C7=CC64=C1(C=C7)N25CC)C12=C45(C(C)OC)N=CC=C1C31=C(N4=CC=C12)[CH]5(C)OC.S</t>
+        </is>
+      </c>
+      <c r="G1794" t="inlineStr"/>
+      <c r="H1794" t="inlineStr"/>
+      <c r="I1794" t="n">
+        <v>0.03022538552958453</v>
+      </c>
+      <c r="J1794" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1794" t="inlineStr"/>
+    </row>
+    <row r="1795">
+      <c r="A1795" s="1" t="n">
+        <v>1793</v>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2373.png</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr"/>
+      <c r="D1795" t="inlineStr"/>
+      <c r="E1795" t="inlineStr"/>
+      <c r="F1795" t="inlineStr">
+        <is>
+          <t>*[CH][CH]1(O)[CH]OC=CCCCC(*)C(O)CC2CCC(*)C(=O2)C2(=O)=O=C234=C25C6CCCC27([H])C328C(CCC3C29%10[H]C3982([H])C%103(O[CH]C([H])CC[CH]OCCOCCOCCOCC8OCC8OCCOCCOCCOCCCNCC8CCN8N=CCC=CCOC(=N)N)=O=C28(=O)O[CH]38CC(=O)C(*)C(=O)C1O)N6574 |$Me;;;;;;;;;;;;Me;;;;;;;;Me;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;;Me;;;;;$|</t>
+        </is>
+      </c>
+      <c r="G1795" t="inlineStr"/>
+      <c r="H1795" t="inlineStr"/>
+      <c r="I1795" t="n">
+        <v>1.149433521235862e-05</v>
+      </c>
+      <c r="J1795" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1795" t="inlineStr"/>
+    </row>
+    <row r="1796">
+      <c r="A1796" s="1" t="n">
+        <v>1794</v>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2377.png</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr"/>
+      <c r="D1796" t="inlineStr"/>
+      <c r="E1796" t="inlineStr"/>
+      <c r="F1796" t="inlineStr">
+        <is>
+          <t>CCN12C3=C456(C)=C78=C9C%10(=CC94(=C71C=C%10)C8(C)=C251C2=C(C(C)OC)N=CC4=C2C312=C(C(C)OC)N=CC(=C2)N1(CCN(C)CC1)C1CN(C)CCN41)CCCCC(NC(=O)C1CC1C)C(=O)N1CCCC(N1)C(=O)OCC(C)(C)C6</t>
+        </is>
+      </c>
+      <c r="G1796" t="inlineStr"/>
+      <c r="H1796" t="inlineStr"/>
+      <c r="I1796" t="n">
+        <v>0.05621666624541153</v>
+      </c>
+      <c r="J1796" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1796" t="inlineStr"/>
+    </row>
+    <row r="1797">
+      <c r="A1797" s="1" t="n">
+        <v>1795</v>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2385.png</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr"/>
+      <c r="D1797" t="inlineStr"/>
+      <c r="E1797" t="inlineStr"/>
+      <c r="F1797" t="inlineStr">
+        <is>
+          <t>CCCCOC=NC1=CN=C(O)N1CC=CNCCOCCOCCOCCNC(=O)CCN1C(=O)CC(SCC(NC(=O)CNC(=O)C(CO)NC(=O)C(CO)NC(=O)C(CC2=CNC=N2)NC(=O)C(N)CCCCN)C(=O)NC(C)C(=O)N[CH]2(CC34=CC=CC=3=C4)C(=O)N[CH]3(CC(C)C)[CH]4(O)N5C(C2C2=CC=CC=2)C534=O)C1=O</t>
+        </is>
+      </c>
+      <c r="G1797" t="inlineStr"/>
+      <c r="H1797" t="inlineStr"/>
+      <c r="I1797" t="n">
+        <v>0.01944656074589383</v>
+      </c>
+      <c r="J1797" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1797" t="inlineStr"/>
+    </row>
+    <row r="1798">
+      <c r="A1798" s="1" t="n">
+        <v>1796</v>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2397.png</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr"/>
+      <c r="D1798" t="inlineStr"/>
+      <c r="E1798" t="inlineStr"/>
+      <c r="F1798" t="inlineStr">
+        <is>
+          <t>C=C1C=C1NC(C(N)=O)C(=O)[CH]NC(=O)C(NC(=O)[CH]1(NC(=O)C(CC2=CNC3=C2C=CC=C3)NC(=O)CCCCCNC(=O)CCC(=O)N2CC3=CC=CC=C3C#CC3=C2C=CC=C3)CC23=C45C6=C7C=CC89=C62%10(N48)C5(=C39%10C=CC7=C)C1)C1CC(=O)N1C(CC)C(=O)N1C2C3CCN4C5CC(=O)NC4C5C2[CH]31C(=O)NCCNC=CC</t>
+        </is>
+      </c>
+      <c r="G1798" t="inlineStr"/>
+      <c r="H1798" t="inlineStr"/>
+      <c r="I1798" t="n">
+        <v>3.305520101924631e-05</v>
+      </c>
+      <c r="J1798" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1798" t="inlineStr"/>
+    </row>
+    <row r="1799">
+      <c r="A1799" s="1" t="n">
+        <v>1797</v>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2401.png</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr"/>
+      <c r="D1799" t="inlineStr"/>
+      <c r="E1799" t="inlineStr"/>
+      <c r="F1799" t="inlineStr">
+        <is>
+          <t>CCC(C)C(NC(=O)C1(CCCC=CCCCC(C)(NC(=O)C(CCCCN)NC(=O)C(N)CC2=CC=C(O)C=C2)C(=O)C(C)C)N2C3456CC2(C3)(C4)(C5)N16)C(=O)NC(CC(=O)O)C(=O)NC(CCC(N)=O)C(=O)NC(C(=O)C(C)C)C(C)CC</t>
+        </is>
+      </c>
+      <c r="G1799" t="inlineStr"/>
+      <c r="H1799" t="inlineStr"/>
+      <c r="I1799" t="n">
+        <v>0.7364318485896774</v>
+      </c>
+      <c r="J1799" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1799" t="inlineStr"/>
+    </row>
+    <row r="1800">
+      <c r="A1800" s="1" t="n">
+        <v>1798</v>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2405.png</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr"/>
+      <c r="D1800" t="inlineStr"/>
+      <c r="E1800" t="inlineStr"/>
+      <c r="F1800" t="inlineStr">
+        <is>
+          <t>CCCCC1C2(=O)[CH]3(CCCC)C4(=O)N[CH]5678CC9=CC%10(=C(C=CC=C%10)C=C9)C9=CC=CC%10=C9C=C(C=C%10)C5[CH]5(N426)C72(=O)N4(C)C58(=O)N25(C)[CH]C[CH]45(COC(C)(C)C)C(=O)NCC(=O)N(C)CCC=CC(=O)OCC(C)(C)C(=O)C(=O)N2CCCCC2C(=O)OC(CCC2=C(OC)C(OC)=CC(OC)=C2)C=CCOCC(=O)N13C</t>
+        </is>
+      </c>
+      <c r="G1800" t="inlineStr"/>
+      <c r="H1800" t="inlineStr"/>
+      <c r="I1800" t="n">
+        <v>0.009712927714728025</v>
+      </c>
+      <c r="J1800" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1800" t="inlineStr"/>
+    </row>
+    <row r="1801">
+      <c r="A1801" s="1" t="n">
+        <v>1799</v>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2417.png</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr"/>
+      <c r="D1801" t="inlineStr"/>
+      <c r="E1801" t="inlineStr"/>
+      <c r="F1801" t="inlineStr">
+        <is>
+          <t>CNN=CC1234(C)CCS(=O)(=O)CC(C)(C)C567=CN(CC8=C9C=CNC9=CC(F)=C8OC8=CC=C(F)C(=C8)C89=NC1(=N=8N9C)C(C)(C2=CC1(CC(C)C(=O)O)=CC=CC3=C1)C4CS(=O)(=O)CC5(C)C)C6=N7</t>
+        </is>
+      </c>
+      <c r="G1801" t="inlineStr"/>
+      <c r="H1801" t="inlineStr"/>
+      <c r="I1801" t="n">
+        <v>0.1045213378791923</v>
+      </c>
+      <c r="J1801" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1801" t="inlineStr"/>
+    </row>
+    <row r="1802">
+      <c r="A1802" s="1" t="n">
+        <v>1800</v>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2421.png</t>
+        </is>
+      </c>
+      <c r="C1802" t="inlineStr"/>
+      <c r="D1802" t="inlineStr"/>
+      <c r="E1802" t="inlineStr"/>
+      <c r="F1802" t="inlineStr">
+        <is>
+          <t>COC=CC=CCCC1OC2(=O)[CH]345CCCCN36C(=O)C(=O)C3(C)(C)COC(=O)C=CCCN(C)C(=O)C(CC(C)C)N(C)C(=O)[CH]CCC7=CC(CNC(=O)CC8=CC=CC=C8)=CC=C7C[CH]NC(=O)[CH]NC(=O)CCC(=O)NC=CC1C(CCC1=CC=C(OC)C(OC)=C1)OC4(=O)[CH]261CCCCN51C(=O)C3(=O)C(C)(C)COC=O</t>
+        </is>
+      </c>
+      <c r="G1802" t="inlineStr"/>
+      <c r="H1802" t="inlineStr"/>
+      <c r="I1802" t="n">
+        <v>0.05758746573929202</v>
+      </c>
+      <c r="J1802" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1802" t="inlineStr"/>
+    </row>
+    <row r="1803">
+      <c r="A1803" s="1" t="n">
+        <v>1801</v>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2425.png</t>
+        </is>
+      </c>
+      <c r="C1803" t="inlineStr"/>
+      <c r="D1803" t="inlineStr"/>
+      <c r="E1803" t="inlineStr"/>
+      <c r="F1803" t="inlineStr">
+        <is>
+          <t>[C-]#[N+]C12=CNC3456=C(F)C(F)=C789%10OC%11%12=CC=C(F)C(=C%11)C%11=NC(=NN%11C)C(C)(C%11=CC(CC(C)C(=O)O)=CC=C%11)CCCC(C)(C)CS(=O)(=O)CCC7%11%13=C13C41(N)=C5C8(F)=C%11(C9=C=%13216)O%12%10</t>
+        </is>
+      </c>
+      <c r="G1803" t="inlineStr"/>
+      <c r="H1803" t="inlineStr"/>
+      <c r="I1803" t="n">
+        <v>0.02468059354332396</v>
+      </c>
+      <c r="J1803" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1803" t="inlineStr"/>
+    </row>
+    <row r="1804">
+      <c r="A1804" s="1" t="n">
+        <v>1802</v>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2433.png</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr"/>
+      <c r="D1804" t="inlineStr"/>
+      <c r="E1804" t="inlineStr"/>
+      <c r="F1804" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1804" t="inlineStr"/>
+      <c r="H1804" t="inlineStr"/>
+      <c r="I1804" t="n">
+        <v>2.606617571182441e-21</v>
+      </c>
+      <c r="J1804" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1804" t="inlineStr"/>
+    </row>
+    <row r="1805">
+      <c r="A1805" s="1" t="n">
+        <v>1803</v>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2441.png</t>
+        </is>
+      </c>
+      <c r="C1805" t="inlineStr"/>
+      <c r="D1805" t="inlineStr"/>
+      <c r="E1805" t="inlineStr"/>
+      <c r="F1805" t="inlineStr">
+        <is>
+          <t>CCN12C(C3=C(C(C)OC)N=CC=C3)=C3=C1(C1=C(C(C)OC)N=CC=C1)=C1CC(C)(C)COC(=O)C4CCCN(N4)C(=O)C(NC(=O)N4CCOCC4)CC4=CC(=CC(O)=C4)C4=CC13=C2C=C4</t>
+        </is>
+      </c>
+      <c r="G1805" t="inlineStr"/>
+      <c r="H1805" t="inlineStr"/>
+      <c r="I1805" t="n">
+        <v>0.5627198608879065</v>
+      </c>
+      <c r="J1805" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1805" t="inlineStr"/>
+    </row>
+    <row r="1806">
+      <c r="A1806" s="1" t="n">
+        <v>1804</v>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2445.png</t>
+        </is>
+      </c>
+      <c r="C1806" t="inlineStr"/>
+      <c r="D1806" t="inlineStr"/>
+      <c r="E1806" t="inlineStr"/>
+      <c r="F1806" t="inlineStr">
+        <is>
+          <t>CCN12C(C3=C(C(C)OC)N=CC(N4CCN5CCOCC5C4)=C3)=C(C)C34=C1C=CC(=C3)C1=CSC(=N1)CC(NC(=O)N1CCC1COC)C(=O)N1CCCC(N1)C(=O)OCC(C)(C)CC4=C2C1=C(C(C)OC)N=CC(N2CCN3CCOCC3C2)=C1.S.S</t>
+        </is>
+      </c>
+      <c r="G1806" t="inlineStr"/>
+      <c r="H1806" t="inlineStr"/>
+      <c r="I1806" t="n">
+        <v>0.7338405575099866</v>
+      </c>
+      <c r="J1806" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1806" t="inlineStr"/>
+    </row>
+    <row r="1807">
+      <c r="A1807" s="1" t="n">
+        <v>1805</v>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2449.png</t>
+        </is>
+      </c>
+      <c r="C1807" t="inlineStr"/>
+      <c r="D1807" t="inlineStr"/>
+      <c r="E1807" t="inlineStr"/>
+      <c r="F1807" t="inlineStr">
+        <is>
+          <t>C=CC(=O)NCCN(C)C(=O)N(C)[C@H](C(=O)N[C@H]1Cc2nc(cs2)-c2ccc3c(c2)c(c(-c2cccnc2[C@H](C)OCC)n3CC)CC(C)(C)COC(=O)[C@@H]2CCCN(N2)C1=O)C(C)C.S.S</t>
+        </is>
+      </c>
+      <c r="G1807" t="inlineStr"/>
+      <c r="H1807" t="inlineStr"/>
+      <c r="I1807" t="n">
+        <v>0.7043849563206362</v>
+      </c>
+      <c r="J1807" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1807" t="inlineStr"/>
+    </row>
+    <row r="1808">
+      <c r="A1808" s="1" t="n">
+        <v>1806</v>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2453.png</t>
+        </is>
+      </c>
+      <c r="C1808" t="inlineStr"/>
+      <c r="D1808" t="inlineStr"/>
+      <c r="E1808" t="inlineStr"/>
+      <c r="F1808" t="inlineStr">
+        <is>
+          <t>CCN12C=C34CC(C)(C)COC(=O)C5CCCN(N5)C(=O)C(NC(=O)C(C(C)C)N(C)C(=O)N5CC6C5CCN6C(=O)C=CCF)CC56=CC(CF)=C7C89%10%11=C5C75%12(=C68)C967=C8C39%13=C13C1=C6C8%1056%14%15=C795C4(=C=%132C=13=C6)C%14=C5%11%12%15.S.S.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1808" t="inlineStr"/>
+      <c r="H1808" t="inlineStr"/>
+      <c r="I1808" t="n">
+        <v>0.007993838954618008</v>
+      </c>
+      <c r="J1808" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1808" t="inlineStr"/>
+    </row>
+    <row r="1809">
+      <c r="A1809" s="1" t="n">
+        <v>1807</v>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2457.png</t>
+        </is>
+      </c>
+      <c r="C1809" t="inlineStr"/>
+      <c r="D1809" t="inlineStr"/>
+      <c r="E1809" t="inlineStr"/>
+      <c r="F1809" t="inlineStr">
+        <is>
+          <t>[H]C1CC(O)CN1C(=O)C(CC(C)C)NC(=O)NC(=O)C1([H])CCCN1C(=O)C(CC(N)=O)NC(=O)C(CNCCC1NC23(=O)=O=C(C2CC=C2C=CC=C2)N13)N(C)C(=O)C(CC1=CC=C(O)C=C1)NC(=O)CSCC(NC(=O)C(CC(C)C)NC(=O)C(CCCC)N(C)C(=O)C(N)CCCC)C(=O)NCC(N)=O</t>
+        </is>
+      </c>
+      <c r="G1809" t="inlineStr"/>
+      <c r="H1809" t="inlineStr"/>
+      <c r="I1809" t="n">
+        <v>0.2094861283692591</v>
+      </c>
+      <c r="J1809" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1809" t="inlineStr"/>
+    </row>
+    <row r="1810">
+      <c r="A1810" s="1" t="n">
+        <v>1808</v>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2481.png</t>
+        </is>
+      </c>
+      <c r="C1810" t="inlineStr"/>
+      <c r="D1810" t="inlineStr"/>
+      <c r="E1810" t="inlineStr"/>
+      <c r="F1810" t="inlineStr">
+        <is>
+          <t>CCCNC(=O)[CH]CC(O)C[CH]C(=O)N[CH]C(=O)[CH]C(=O)N[CH]1(C(=O)N[CH]CC(C)C)CC2=NC=C3(O)C=C(O)C3=C21.O=CN1[CH]CC1=O.[H]CCCNCCCC[CH]NC(=O)C1NC1(=O)[CH]NCCC1(=O)OC(=O)(CCC(C=O)CC(=O)NC(=O)[CH]NC(=O)C(CO)NC(=O)C(C)(CC)NC=O)O1</t>
+        </is>
+      </c>
+      <c r="G1810" t="inlineStr"/>
+      <c r="H1810" t="inlineStr"/>
+      <c r="I1810" t="n">
+        <v>1.944839858861861e-06</v>
+      </c>
+      <c r="J1810" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1810" t="inlineStr"/>
+    </row>
+    <row r="1811">
+      <c r="A1811" s="1" t="n">
+        <v>1809</v>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2485.png</t>
+        </is>
+      </c>
+      <c r="C1811" t="inlineStr"/>
+      <c r="D1811" t="inlineStr"/>
+      <c r="E1811" t="inlineStr"/>
+      <c r="F1811" t="inlineStr">
+        <is>
+          <t>CC1C[CH]23(C)CCCC4C(CC2C3)C[CH]2(O)[CH]3(O)O[CH]56[CH]7(O)CC8[CH]9%10%11O%12C(=O)[CH]%13%14C%15CCC[CH]%13%16%17O%13%18C(=O)O%16%19%20C(=O)(O[CH]%16(C(C)C=CC(O)C(O)C(O)C1O)[CH]%131%21CC%13[CH]%22%23OC(CC[CH]%13(O)[CH]%16%181%19C%21O)CC%22C%23O)O[CH]%14%17%201CCCC[CH]%151C(=O)O[CH]8%1291%13%14%15C8C9%12(O[CH]82(O)[CH]43N)C12(O)CC59%13C2%10%14C76%12%11%15</t>
+        </is>
+      </c>
+      <c r="G1811" t="inlineStr"/>
+      <c r="H1811" t="inlineStr"/>
+      <c r="I1811" t="n">
+        <v>5.908140657096492e-12</v>
+      </c>
+      <c r="J1811" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1811" t="inlineStr"/>
+    </row>
+    <row r="1812">
+      <c r="A1812" s="1" t="n">
+        <v>1810</v>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2489.png</t>
+        </is>
+      </c>
+      <c r="C1812" t="inlineStr"/>
+      <c r="D1812" t="inlineStr"/>
+      <c r="E1812" t="inlineStr"/>
+      <c r="F1812" t="inlineStr">
+        <is>
+          <t>C=CC(=O)NCC12CCN3(C(C(=O)NC4CC5=CC(=CC(O)=C5)C5=CC6=C(C=C5)N(CC)C(C5=C(C(C)OC)N=CC=C5)=C6CC(C)(C)COC(=O)C5CCCN(N5)C4=O)C(C)C)C14=O=C23=O=4.S.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1812" t="inlineStr"/>
+      <c r="H1812" t="inlineStr"/>
+      <c r="I1812" t="n">
+        <v>0.782309172877888</v>
+      </c>
+      <c r="J1812" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1812" t="inlineStr"/>
+    </row>
+    <row r="1813">
+      <c r="A1813" s="1" t="n">
+        <v>1811</v>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2505.png</t>
+        </is>
+      </c>
+      <c r="C1813" t="inlineStr"/>
+      <c r="D1813" t="inlineStr"/>
+      <c r="E1813" t="inlineStr"/>
+      <c r="F1813" t="inlineStr">
+        <is>
+          <t>CCCCC1C2(=O)N3C4C(C5=CC6=C(C=CC=C6)C=C5)[CH]356(CC3=CC7=C(C=CC=C7)C=C3)NC(=O)[CH]2(CCCC)N1(C)C(=O)COCC=CC(CCC1=C(F)C(OC)=C(OC)C=C1)OC(=O)C1CCCCN1C(=O)C(=O)C(C)(C)COC(=O)C=CCCN(C)C(=O)CNC(=O)[CH]12(COC(C)(C)C)C(O)C3N17(C)C5(=O)N32(C)C476=O</t>
+        </is>
+      </c>
+      <c r="G1813" t="inlineStr"/>
+      <c r="H1813" t="inlineStr"/>
+      <c r="I1813" t="n">
+        <v>0.06250325159290214</v>
+      </c>
+      <c r="J1813" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1813" t="inlineStr"/>
+    </row>
+    <row r="1814">
+      <c r="A1814" s="1" t="n">
+        <v>1812</v>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2513.png</t>
+        </is>
+      </c>
+      <c r="C1814" t="inlineStr"/>
+      <c r="D1814" t="inlineStr"/>
+      <c r="E1814" t="inlineStr"/>
+      <c r="F1814" t="inlineStr">
+        <is>
+          <t>CCN12C(C3=C(C(C)OC)N=CC(N4CCN(C)CC4)=C3)=C(C)C345=C16C=CC(=C3)C1=CSC(=N1)CC(NC(=O)C1CC1C)C(=O)N1CCCC(N1)C(=O)OCC(C)(C)CC4(=C2C1=C(C(C)OC)N=CC(N2CCN(C)CC2)=C1)C6=C5</t>
+        </is>
+      </c>
+      <c r="G1814" t="inlineStr"/>
+      <c r="H1814" t="inlineStr"/>
+      <c r="I1814" t="n">
+        <v>0.5389912106493131</v>
+      </c>
+      <c r="J1814" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1814" t="inlineStr"/>
+    </row>
+    <row r="1815">
+      <c r="A1815" s="1" t="n">
+        <v>1813</v>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2517.png</t>
+        </is>
+      </c>
+      <c r="C1815" t="inlineStr"/>
+      <c r="D1815" t="inlineStr"/>
+      <c r="E1815" t="inlineStr"/>
+      <c r="F1815" t="inlineStr">
+        <is>
+          <t>CCN12C(C3=CC(N4CCN(C)CC4)=CN=C3C(C)OC)=C34CC(C)(C)COC(=O)C5CCCN(N5)C(=O)C(NC(=O)C5CC5C)CC5=NC6(=CS5)C5=CC378=C1(=C471=C28C=CC6=C1)C=C5</t>
+        </is>
+      </c>
+      <c r="G1815" t="inlineStr"/>
+      <c r="H1815" t="inlineStr"/>
+      <c r="I1815" t="n">
+        <v>0.07237376940257639</v>
+      </c>
+      <c r="J1815" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1815" t="inlineStr"/>
+    </row>
+    <row r="1816">
+      <c r="A1816" s="1" t="n">
+        <v>1814</v>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2525.png</t>
+        </is>
+      </c>
+      <c r="C1816" t="inlineStr"/>
+      <c r="D1816" t="inlineStr"/>
+      <c r="E1816" t="inlineStr"/>
+      <c r="F1816" t="inlineStr">
+        <is>
+          <t>CCn1c(-c2cccnc2[C@H](C)OC)c2c3cc(ccc31)-c1cccc(c1)C[C@H](NC(=O)[C@H](C(C)C)N(C)C(=O)C1(F)CCN(C(=O)/C=C/CN(C)C)CC1)C(=O)N1CCC[C@H](N1)C(=O)OCC(C)(C)C2.S.S</t>
+        </is>
+      </c>
+      <c r="G1816" t="inlineStr"/>
+      <c r="H1816" t="inlineStr"/>
+      <c r="I1816" t="n">
+        <v>0.8175937964796871</v>
+      </c>
+      <c r="J1816" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1816" t="inlineStr"/>
+    </row>
+    <row r="1817">
+      <c r="A1817" s="1" t="n">
+        <v>1815</v>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2529.png</t>
+        </is>
+      </c>
+      <c r="C1817" t="inlineStr"/>
+      <c r="D1817" t="inlineStr"/>
+      <c r="E1817" t="inlineStr"/>
+      <c r="F1817" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CC[C@H](C(=O)N(C)[C@H](C(=O)N[C@H]2Cc3csc(n3)-c3cc4c(c(-c5cccnc5[C@H](C)OC)n(CC)c4cn3)CC(C)(C)COC(=O)[C@@H]3CCCN(N3)C2=O)C(C)C)C1</t>
+        </is>
+      </c>
+      <c r="G1817" t="inlineStr"/>
+      <c r="H1817" t="inlineStr"/>
+      <c r="I1817" t="n">
+        <v>0.7920780637041067</v>
+      </c>
+      <c r="J1817" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1817" t="inlineStr"/>
+    </row>
+    <row r="1818">
+      <c r="A1818" s="1" t="n">
+        <v>1816</v>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2533.png</t>
+        </is>
+      </c>
+      <c r="C1818" t="inlineStr"/>
+      <c r="D1818" t="inlineStr"/>
+      <c r="E1818" t="inlineStr"/>
+      <c r="F1818" t="inlineStr">
+        <is>
+          <t>&lt;invalid&gt;</t>
+        </is>
+      </c>
+      <c r="G1818" t="inlineStr"/>
+      <c r="H1818" t="inlineStr"/>
+      <c r="I1818" t="n">
+        <v>1.710481894903708e-40</v>
+      </c>
+      <c r="J1818" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1818" t="inlineStr"/>
+    </row>
+    <row r="1819">
+      <c r="A1819" s="1" t="n">
+        <v>1817</v>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2537.png</t>
+        </is>
+      </c>
+      <c r="C1819" t="inlineStr"/>
+      <c r="D1819" t="inlineStr"/>
+      <c r="E1819" t="inlineStr"/>
+      <c r="F1819" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CC[C@](F)(C(=O)N(C)[C@H](C(=O)N[C@H]2Cc3cc(cc(C(F)F)c3)-c3ccc4c(c3)c(c(-c3cc(N5CCNCC5)cnc3[C@H](C)OC)n4CC)CC(C)(C)COC(=O)[C@@H]3CCCN(N3)C2=O)C(C)C)C1</t>
+        </is>
+      </c>
+      <c r="G1819" t="inlineStr"/>
+      <c r="H1819" t="inlineStr"/>
+      <c r="I1819" t="n">
+        <v>0.7742552336740756</v>
+      </c>
+      <c r="J1819" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1819" t="inlineStr"/>
+    </row>
+    <row r="1820">
+      <c r="A1820" s="1" t="n">
+        <v>1818</v>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2541.png</t>
+        </is>
+      </c>
+      <c r="C1820" t="inlineStr"/>
+      <c r="D1820" t="inlineStr"/>
+      <c r="E1820" t="inlineStr"/>
+      <c r="F1820" t="inlineStr">
+        <is>
+          <t>[CH]CN[CH]CN1C2N3C(CN[CH]CNCCN[CH]CNCCNCC(C)O)[CH]2134C12356789%10%11O%12%13C1%14%15%16%17%18O1C%12%142%19%20%21%22N2C3%12%14N3C%12%23N%12%24C%25%26N%27CC%28(N)=O=C%28C%28C%29%30%31%32=O=C%28%29%33%34(=O=%30%28=C%29%30%35(OC%29%15%195%36%37C65%15%19%29%38O6(C%33)C57%33%39%40%41N57C%33%42(N[CH]%33%43C(NCCN[CH]CN%44C%45N[CH]%46%47C%48C%46(NC(CN[CH]C%46CN%46)C%45%44)[CH]%48%47N%44C%45%46%47C[CH]%44%45(C%46)O%47)[CH]%25%33%12C%273%23%26%43%24)[CH]5%1583%12O%39%19[CH]76%423%40%29%16%36%209[CH]21%13%144%12%41%38%17%37%21%10O%18%22%11)C123C45C16(O)O42%30%31C=%28=%34563%35)O%32</t>
+        </is>
+      </c>
+      <c r="G1820" t="inlineStr"/>
+      <c r="H1820" t="inlineStr"/>
+      <c r="I1820" t="n">
+        <v>2.586979751327969e-39</v>
+      </c>
+      <c r="J1820" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1820" t="inlineStr"/>
+    </row>
+    <row r="1821">
+      <c r="A1821" s="1" t="n">
+        <v>1819</v>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2553.png</t>
+        </is>
+      </c>
+      <c r="C1821" t="inlineStr"/>
+      <c r="D1821" t="inlineStr"/>
+      <c r="E1821" t="inlineStr"/>
+      <c r="F1821" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC1=NC2=C3C(=CC(C(=O)NC4CCC(C5=NN=NN5)CC4)=C2)OCC(N2CC4CCC(C2)O4)COC2=CC(C(N)=O)=CC45=C26N(CC=CCN2C=C(C=C(C)C(=O)NC7CCC(C8=NN=NN8)CC7)N=C2NC)C(NC(=O)C2=CC(C)=NN2CC)(=N4)N6(CC=CCN13)C(NC(=O)C1=CC(C)=NN1CC)=N5</t>
+        </is>
+      </c>
+      <c r="G1821" t="inlineStr"/>
+      <c r="H1821" t="inlineStr"/>
+      <c r="I1821" t="n">
+        <v>0.2396116576547006</v>
+      </c>
+      <c r="J1821" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1821" t="inlineStr"/>
+    </row>
+    <row r="1822">
+      <c r="A1822" s="1" t="n">
+        <v>1820</v>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2557.png</t>
+        </is>
+      </c>
+      <c r="C1822" t="inlineStr"/>
+      <c r="D1822" t="inlineStr"/>
+      <c r="E1822" t="inlineStr"/>
+      <c r="F1822" t="inlineStr">
+        <is>
+          <t>CCN1C(C2=C(C(C)OC)N=CC=C2)=C2CC(C)(C)COC(=O)[CH]345CCCN67(N3)C(=O)[CH]3(NC(=O)C8CCCN(C(C)=O)C8)CC8=NC(=CS8)C8=CC2(=C1C=C8)C=CC(C)(C)COC4(=O)C1CCCN(C36=O)N157.S.S</t>
+        </is>
+      </c>
+      <c r="G1822" t="inlineStr"/>
+      <c r="H1822" t="inlineStr"/>
+      <c r="I1822" t="n">
+        <v>0.1727098386586325</v>
+      </c>
+      <c r="J1822" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1822" t="inlineStr"/>
+    </row>
+    <row r="1823">
+      <c r="A1823" s="1" t="n">
+        <v>1821</v>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2565.png</t>
+        </is>
+      </c>
+      <c r="C1823" t="inlineStr"/>
+      <c r="D1823" t="inlineStr"/>
+      <c r="E1823" t="inlineStr"/>
+      <c r="F1823" t="inlineStr">
+        <is>
+          <t>CCN1N=C(C)C=C1C(=O)NC1=NC23=C4C(=CC(C(N)=O)=C2)OCC(N2C5CCC2COC5)COC256=C7=C8(=C=29C72%10=C7=C9%11(=C=2C729=C85N5(CC=CCN14)C(NC(=O)C1=CC(C)=NN1CC)=N2C5(NC(=O)C1=CC(C)=NN1CC)=N9)C%101=O=C%11(=O)(O)O1)O6C[CH]COC=CC(C(N)=O)=C3</t>
+        </is>
+      </c>
+      <c r="G1823" t="inlineStr"/>
+      <c r="H1823" t="inlineStr"/>
+      <c r="I1823" t="n">
+        <v>0.02974922628171159</v>
+      </c>
+      <c r="J1823" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1823" t="inlineStr"/>
+    </row>
+    <row r="1824">
+      <c r="A1824" s="1" t="n">
+        <v>1822</v>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2569.png</t>
+        </is>
+      </c>
+      <c r="C1824" t="inlineStr"/>
+      <c r="D1824" t="inlineStr"/>
+      <c r="E1824" t="inlineStr"/>
+      <c r="F1824" t="inlineStr">
+        <is>
+          <t>C[C@H](Cc1cccc([C@@]2(C)CCCC(C)(C)CS(=O)(=O)CCc3c(c(F)cc4[nH]ccc34)S(=O)c3ccc(F)c(c3)-c3nc2nn3C)c1)C(=O)O</t>
+        </is>
+      </c>
+      <c r="G1824" t="inlineStr"/>
+      <c r="H1824" t="inlineStr"/>
+      <c r="I1824" t="n">
+        <v>0.7382782019201566</v>
+      </c>
+      <c r="J1824" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1824" t="inlineStr"/>
+    </row>
+    <row r="1825">
+      <c r="A1825" s="1" t="n">
+        <v>1823</v>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2573.png</t>
+        </is>
+      </c>
+      <c r="C1825" t="inlineStr"/>
+      <c r="D1825" t="inlineStr"/>
+      <c r="E1825" t="inlineStr"/>
+      <c r="F1825" t="inlineStr">
+        <is>
+          <t>CCN12C3=C4CC(C)(C)COC(=O)C5CCCN(N5)C(=O)N56CCCC(N5)C(=O)OCC(C)(C)CC(=C1C15=C7(C(C)OC)N=CC89=C1C31=C(N=CC(=C=815)N1CCN(C)CC1N91CCN(C)CC1)[CH]7(C)OC)C41=C2C=CC(=C1)C1=CSC(=N1)CC(NC(=O)C1CC1CF)C6=O</t>
+        </is>
+      </c>
+      <c r="G1825" t="inlineStr"/>
+      <c r="H1825" t="inlineStr"/>
+      <c r="I1825" t="n">
+        <v>0.0221064739060076</v>
+      </c>
+      <c r="J1825" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1825" t="inlineStr"/>
+    </row>
+    <row r="1826">
+      <c r="A1826" s="1" t="n">
+        <v>1824</v>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2585.png</t>
+        </is>
+      </c>
+      <c r="C1826" t="inlineStr"/>
+      <c r="D1826" t="inlineStr"/>
+      <c r="E1826" t="inlineStr"/>
+      <c r="F1826" t="inlineStr">
+        <is>
+          <t>CCN1C23=C4=C5(=C6CC(C)(C)COC(=O)C7CCCN(N7)C(=O)C(NC(=O)N7CCCC7C)CC7=NC(=CS7)C7=CC64=C1(C=C7)N25CC)C1=C2(C(C)OC)(N=CC=C1)N1=CC=CC3=C1[CH]2(C)OC.S.S</t>
+        </is>
+      </c>
+      <c r="G1826" t="inlineStr"/>
+      <c r="H1826" t="inlineStr"/>
+      <c r="I1826" t="n">
+        <v>0.0102621920809496</v>
+      </c>
+      <c r="J1826" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1826" t="inlineStr"/>
+    </row>
+    <row r="1827">
+      <c r="A1827" s="1" t="n">
+        <v>1825</v>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_2/rb_2593.png</t>
+        </is>
+      </c>
+      <c r="C1827" t="inlineStr"/>
+      <c r="D1827" t="inlineStr"/>
+      <c r="E1827" t="inlineStr"/>
+      <c r="F1827" t="inlineStr">
+        <is>
+          <t>COCCN12C(C3=CN=CC(N4CCN(C)CC4)=C3)=C3CC(C)(C)COC4(=O)C5CCCN6N5N578CCC[CH]4(N5)C(=O)OCC(C)(C)CC4(=C1C1=CN=CC59=C1%10=C1%11(=C5C4%10=CN=C1)N91C4CN(C)CC15C1CN45%11CCN1C)C31=C2C=CC(=C1)C1=CSC(=N1)C[CH](NC(=O)C1CC1C)(C7=O)C68=O</t>
+        </is>
+      </c>
+      <c r="G1827" t="inlineStr"/>
+      <c r="H1827" t="inlineStr"/>
+      <c r="I1827" t="n">
+        <v>0.001073380030597701</v>
+      </c>
+      <c r="J1827" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1827" t="inlineStr"/>
+    </row>
+    <row r="1828">
+      <c r="A1828" s="1" t="n">
+        <v>1826</v>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2362.png</t>
+        </is>
+      </c>
+      <c r="C1828" t="inlineStr"/>
+      <c r="D1828" t="inlineStr"/>
+      <c r="E1828" t="inlineStr"/>
+      <c r="F1828" t="inlineStr">
+        <is>
+          <t>C[C@H](Cc1cccc(C2(C)CCCC(C)(C)CS(=O)(=O)CCc3c(c(F)cc4[nH]ccc34)Oc3ccc(F)c(c3)-c3nc2nn3C)c1)C(=O)OCCN1CCN(C)CC1</t>
+        </is>
+      </c>
+      <c r="G1828" t="inlineStr"/>
+      <c r="H1828" t="inlineStr"/>
+      <c r="I1828" t="n">
+        <v>0.4486229310337874</v>
+      </c>
+      <c r="J1828" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1828" t="inlineStr"/>
+    </row>
+    <row r="1829">
+      <c r="A1829" s="1" t="n">
+        <v>1827</v>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2370.png</t>
+        </is>
+      </c>
+      <c r="C1829" t="inlineStr"/>
+      <c r="D1829" t="inlineStr"/>
+      <c r="E1829" t="inlineStr"/>
+      <c r="F1829" t="inlineStr">
+        <is>
+          <t>C=CC[C@H]1/C=C(\C)C[C@H](C)C[C@H](OC)[C@H]2O[C@@](O)(C(=O)C(=O)N3CCCC[C@H]3C(=O)O[C@H](C(C)=C[C@@H]3CC[C@@H](O)[C@H](OC)C3)[C@H](C)[C@@H](O)CC1=O)[C@H](C)C[C@@H]2OC</t>
+        </is>
+      </c>
+      <c r="G1829" t="inlineStr"/>
+      <c r="H1829" t="inlineStr"/>
+      <c r="I1829" t="n">
+        <v>0.7463870293669022</v>
+      </c>
+      <c r="J1829" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1829" t="inlineStr"/>
+    </row>
+    <row r="1830">
+      <c r="A1830" s="1" t="n">
+        <v>1828</v>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2374.png</t>
+        </is>
+      </c>
+      <c r="C1830" t="inlineStr"/>
+      <c r="D1830" t="inlineStr"/>
+      <c r="E1830" t="inlineStr"/>
+      <c r="F1830" t="inlineStr">
+        <is>
+          <t>[H]CCC(C)[CH]CC(OC(=O)OC1=CC=C([N+](=O)[O-])C=C1)C(C)C=C(C)C(O)[CH]1(OC)C(=O)C(C)CC(C)C=CC=CC=C(C)C(OC)CC2([H])CCC(C)C(O)(O2)C(=O)C(=O)N2CCCCC2([H])C(=O)O[CH]CC(OC(=O)OC2=CC=C([N+](=O)[O-])C=C2)C(C)C=C(C)C1O</t>
+        </is>
+      </c>
+      <c r="G1830" t="inlineStr"/>
+      <c r="H1830" t="inlineStr"/>
+      <c r="I1830" t="n">
+        <v>0.06976157432425004</v>
+      </c>
+      <c r="J1830" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1830" t="inlineStr"/>
+    </row>
+    <row r="1831">
+      <c r="A1831" s="1" t="n">
+        <v>1829</v>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2378.png</t>
+        </is>
+      </c>
+      <c r="C1831" t="inlineStr"/>
+      <c r="D1831" t="inlineStr"/>
+      <c r="E1831" t="inlineStr"/>
+      <c r="F1831" t="inlineStr">
+        <is>
+          <t>CCN12C(C3=C(C(C)OC)N=CC=C3)=CC34=C1C=CC(=C3)C1=CC(O)=CC(=C1)CC(NS(=O)(=O)C1=CC=C(OC)C=C1OC)C(=O)N1CCCC(N1)C(=O)OCC(C)(C)CC4=C2C1=C(C(C)OC)N=CC=C1</t>
+        </is>
+      </c>
+      <c r="G1831" t="inlineStr"/>
+      <c r="H1831" t="inlineStr"/>
+      <c r="I1831" t="n">
+        <v>0.1973532153788057</v>
+      </c>
+      <c r="J1831" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1831" t="inlineStr"/>
+    </row>
+    <row r="1832">
+      <c r="A1832" s="1" t="n">
+        <v>1830</v>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2382.png</t>
+        </is>
+      </c>
+      <c r="C1832" t="inlineStr"/>
+      <c r="D1832" t="inlineStr"/>
+      <c r="E1832" t="inlineStr"/>
+      <c r="F1832" t="inlineStr">
+        <is>
+          <t>CCO[C@@H]1c2nc(cs2)-c2ccc3c(c2)c(c(-c2cccnc2[C@H](C)OC)n3CC)CC(C)(C)COC(=O)[C@@H]2CCCN(N2)C(=O)[C@H]1NC(=O)[C@H]1C[C@@H]1c1ccccn1.S.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1832" t="inlineStr"/>
+      <c r="H1832" t="inlineStr"/>
+      <c r="I1832" t="n">
+        <v>0.8315549093356119</v>
+      </c>
+      <c r="J1832" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1832" t="inlineStr"/>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="1" t="n">
+        <v>1831</v>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2386.png</t>
+        </is>
+      </c>
+      <c r="C1833" t="inlineStr"/>
+      <c r="D1833" t="inlineStr"/>
+      <c r="E1833" t="inlineStr"/>
+      <c r="F1833" t="inlineStr">
+        <is>
+          <t>COC1CC(C=C(C)[CH]2(C(C)C(O)CC(=O)C(C=C(C)CC(C)CC(OC)C3OC(O)C(C)CC3OC)CCOC(=O)NCCNC3=CC=C4SC(C5=CC=C(N(C)C)C=C5)=NC4=C3)OC34(=O)O2C2(=O)[CH]3567C3CC8C9CC%10N5%11%12%13C8N%1065(C%116=O=C%125(=O)C6=O)[CH]3247%13C9)CCC1O</t>
+        </is>
+      </c>
+      <c r="G1833" t="inlineStr"/>
+      <c r="H1833" t="inlineStr"/>
+      <c r="I1833" t="n">
+        <v>0.1142313503196454</v>
+      </c>
+      <c r="J1833" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1833" t="inlineStr"/>
+    </row>
+    <row r="1834">
+      <c r="A1834" s="1" t="n">
+        <v>1832</v>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2398.png</t>
+        </is>
+      </c>
+      <c r="C1834" t="inlineStr"/>
+      <c r="D1834" t="inlineStr"/>
+      <c r="E1834" t="inlineStr"/>
+      <c r="F1834" t="inlineStr">
+        <is>
+          <t>CCN12C3=CC=C4C(=C3)C3(=CC(=C1C=C3)C1=C2C2=C(N=CC(C3CCN(C)CC3)=C2)C(OC)C1)C4C=CC[CH]NC(=O)C1CC1C.S.S.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1834" t="inlineStr"/>
+      <c r="H1834" t="inlineStr"/>
+      <c r="I1834" t="n">
+        <v>0.2952288599000598</v>
+      </c>
+      <c r="J1834" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1834" t="inlineStr"/>
+    </row>
+    <row r="1835">
+      <c r="A1835" s="1" t="n">
+        <v>1833</v>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2410.png</t>
+        </is>
+      </c>
+      <c r="C1835" t="inlineStr"/>
+      <c r="D1835" t="inlineStr"/>
+      <c r="E1835" t="inlineStr"/>
+      <c r="F1835" t="inlineStr">
+        <is>
+          <t>CNC(=O)C(C)CC1=CC=CC(C2(C)CCCC(C)(C)CS(=O)(=O)CC(NC)C3456=C789C=CNC7%10=C(F)C(F)=C37OC3(=CC=C(F)C(=C3)C3=NC2=NN3C)OC42=C(F)C(F)=C83NC=CC3%105=C279C6NC)=C1</t>
+        </is>
+      </c>
+      <c r="G1835" t="inlineStr"/>
+      <c r="H1835" t="inlineStr"/>
+      <c r="I1835" t="n">
+        <v>0.1282542346090332</v>
+      </c>
+      <c r="J1835" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1835" t="inlineStr"/>
+    </row>
+    <row r="1836">
+      <c r="A1836" s="1" t="n">
+        <v>1834</v>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2414.png</t>
+        </is>
+      </c>
+      <c r="C1836" t="inlineStr"/>
+      <c r="D1836" t="inlineStr"/>
+      <c r="E1836" t="inlineStr"/>
+      <c r="F1836" t="inlineStr">
+        <is>
+          <t>CCn1c(-c2cccnc2[C@H](C)OC)cc2cc(-c3cscn3)ccc21.S.S.S.S.S.S.S.S.S.S.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1836" t="inlineStr"/>
+      <c r="H1836" t="inlineStr"/>
+      <c r="I1836" t="n">
+        <v>0.6982324825893863</v>
+      </c>
+      <c r="J1836" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1836" t="inlineStr"/>
+    </row>
+    <row r="1837">
+      <c r="A1837" s="1" t="n">
+        <v>1835</v>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2418.png</t>
+        </is>
+      </c>
+      <c r="C1837" t="inlineStr"/>
+      <c r="D1837" t="inlineStr"/>
+      <c r="E1837" t="inlineStr"/>
+      <c r="F1837" t="inlineStr">
+        <is>
+          <t>CCN12C3=CC=C(C=C3)C3=C[SH](C4=NC(=CS4)C4=CC(=C1C=C4)C=C2C1=C(C(C)OC)N=CC=C1)C1(=N3)C2[CH]345C[CH]2(C3=O)(C14)N5C(=O)CC1CCOCC1OC</t>
+        </is>
+      </c>
+      <c r="G1837" t="inlineStr"/>
+      <c r="H1837" t="inlineStr"/>
+      <c r="I1837" t="n">
+        <v>0.1282571098972689</v>
+      </c>
+      <c r="J1837" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1837" t="inlineStr"/>
+    </row>
+    <row r="1838">
+      <c r="A1838" s="1" t="n">
+        <v>1836</v>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2426.png</t>
+        </is>
+      </c>
+      <c r="C1838" t="inlineStr"/>
+      <c r="D1838" t="inlineStr"/>
+      <c r="E1838" t="inlineStr"/>
+      <c r="F1838" t="inlineStr">
+        <is>
+          <t>CC(CC1=CC=CC(C2(C)CCCC(C)(C)CS(=O)(=O)CCC3456=C78=C9%10=C=3%11%12%13C3(C)=CNC%11%14%15=C%11C%16(F)=C94O4C9(=CC=C(F)C(=C9)C9=NC2=NN9C)OC4%16%105=C(F)C(F)=C%117%14%122NC=C8%13(C)C=63%152)=C1)C(=O)O</t>
+        </is>
+      </c>
+      <c r="G1838" t="inlineStr"/>
+      <c r="H1838" t="inlineStr"/>
+      <c r="I1838" t="n">
+        <v>0.003544108256151042</v>
+      </c>
+      <c r="J1838" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1838" t="inlineStr"/>
+    </row>
+    <row r="1839">
+      <c r="A1839" s="1" t="n">
+        <v>1837</v>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2430.png</t>
+        </is>
+      </c>
+      <c r="C1839" t="inlineStr"/>
+      <c r="D1839" t="inlineStr"/>
+      <c r="E1839" t="inlineStr"/>
+      <c r="F1839" t="inlineStr">
+        <is>
+          <t>CCn1c(-c2cccnc2[C@H](C)OC)cc2ccccc21.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1839" t="inlineStr"/>
+      <c r="H1839" t="inlineStr"/>
+      <c r="I1839" t="n">
+        <v>0.5064543631449593</v>
+      </c>
+      <c r="J1839" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1839" t="inlineStr"/>
+    </row>
+    <row r="1840">
+      <c r="A1840" s="1" t="n">
+        <v>1838</v>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2438.png</t>
+        </is>
+      </c>
+      <c r="C1840" t="inlineStr"/>
+      <c r="D1840" t="inlineStr"/>
+      <c r="E1840" t="inlineStr"/>
+      <c r="F1840" t="inlineStr">
+        <is>
+          <t>CCN12C(C3=C(C(C)OC)N=CC(N4CCN(C)CC4C)=C3)=C(C)C34=C1C=CC(=C3)C1=CSC(=N1)CC(NC(=O)C1CC1C)C(=O)N1CCCC(N1)C(=O)OCC(C)(C)CC41=C2C23=C(C(C)OC)N=CC4=C2C12=C(C(C)OC)N=CC(=C32)N1(CCN(C)CC1C)[CH]1(C)CN(C)CCN41.S.S</t>
+        </is>
+      </c>
+      <c r="G1840" t="inlineStr"/>
+      <c r="H1840" t="inlineStr"/>
+      <c r="I1840" t="n">
+        <v>0.0377917551542149</v>
+      </c>
+      <c r="J1840" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1840" t="inlineStr"/>
+    </row>
+    <row r="1841">
+      <c r="A1841" s="1" t="n">
+        <v>1839</v>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2442.png</t>
+        </is>
+      </c>
+      <c r="C1841" t="inlineStr"/>
+      <c r="D1841" t="inlineStr"/>
+      <c r="E1841" t="inlineStr"/>
+      <c r="F1841" t="inlineStr">
+        <is>
+          <t>CCN12C(C3=C(C(C)OC)N=CC=C3)=C3=C1(C1=C(C(C)OC)N=CC=C1)=C1CC(C)(C)COC(=O)C4CCCN(N4)C(=O)C(NC(=O)C(C(C)C)N(C)C(=O)C4CCN(C(=O)C#CC5CCCN5C)C4)CC4=CC(=CC(O)=C4)C4=CC13=C2C=C4</t>
+        </is>
+      </c>
+      <c r="G1841" t="inlineStr"/>
+      <c r="H1841" t="inlineStr"/>
+      <c r="I1841" t="n">
+        <v>0.1100295212720272</v>
+      </c>
+      <c r="J1841" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1841" t="inlineStr"/>
+    </row>
+    <row r="1842">
+      <c r="A1842" s="1" t="n">
+        <v>1840</v>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2466.png</t>
+        </is>
+      </c>
+      <c r="C1842" t="inlineStr"/>
+      <c r="D1842" t="inlineStr"/>
+      <c r="E1842" t="inlineStr"/>
+      <c r="F1842" t="inlineStr">
+        <is>
+          <t>COC1(C)(C)C(OC2OC(C)CC(N(C)C)C2O)C(C)C(=O)C(C)(C)C(=O)OCC(CC2CCN(CCC(C)CCC=C(C)C)CC2)N(C)CC(C)O1C</t>
+        </is>
+      </c>
+      <c r="G1842" t="inlineStr"/>
+      <c r="H1842" t="inlineStr"/>
+      <c r="I1842" t="n">
+        <v>0.4340182131014485</v>
+      </c>
+      <c r="J1842" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1842" t="inlineStr"/>
+    </row>
+    <row r="1843">
+      <c r="A1843" s="1" t="n">
+        <v>1841</v>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2470.png</t>
+        </is>
+      </c>
+      <c r="C1843" t="inlineStr"/>
+      <c r="D1843" t="inlineStr"/>
+      <c r="E1843" t="inlineStr"/>
+      <c r="F1843" t="inlineStr">
+        <is>
+          <t>CCN1C(C2=C(C(C)OC)N=CC(N3CCN(C)CC3)=C2)=C2CC(C)(C)COC(=O)C3CCCN(N3)C(=O)C(NC(=O)C3CC3C)CC3=CC(=CC=C3)C34=CC25=C1(C=C3)C=C45.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1843" t="inlineStr"/>
+      <c r="H1843" t="inlineStr"/>
+      <c r="I1843" t="n">
+        <v>0.4457987319163595</v>
+      </c>
+      <c r="J1843" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1843" t="inlineStr"/>
+    </row>
+    <row r="1844">
+      <c r="A1844" s="1" t="n">
+        <v>1842</v>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2474.png</t>
+        </is>
+      </c>
+      <c r="C1844" t="inlineStr"/>
+      <c r="D1844" t="inlineStr"/>
+      <c r="E1844" t="inlineStr"/>
+      <c r="F1844" t="inlineStr">
+        <is>
+          <t>CC(CC(=O)O)c1cccc([C@@]2(C)CCCC(C)(C)CS(=O)(=O)CCc3c(c(F)cc4[nH]ccc34)S(=O)c3ccc(F)c(c3)-c3nc2nn3C)c1</t>
+        </is>
+      </c>
+      <c r="G1844" t="inlineStr"/>
+      <c r="H1844" t="inlineStr"/>
+      <c r="I1844" t="n">
+        <v>0.7766541257635429</v>
+      </c>
+      <c r="J1844" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1844" t="inlineStr"/>
+    </row>
+    <row r="1845">
+      <c r="A1845" s="1" t="n">
+        <v>1843</v>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2478.png</t>
+        </is>
+      </c>
+      <c r="C1845" t="inlineStr"/>
+      <c r="D1845" t="inlineStr"/>
+      <c r="E1845" t="inlineStr"/>
+      <c r="F1845" t="inlineStr">
+        <is>
+          <t>CCN12C3=C4C=C(C=C3)C3=CSC(=N3)C[CH]3(NC(=O)C5CCCN(C(C)=O)C5)C(=O)N5678CCC[CH]9%10(N5)C(=O)OCC(C)(C)CC(C5=C(C(C)OC)N=CC(N%11CCN%12CCOCC%12C%11)=C5)=C1=C4(=C2C1=C(C(C)OC)N=CC(N2CCN4CCOCC4C2)=C1)CC(C)(C)COC9(=O)C1CCC6N(C37=O)N1%108.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1845" t="inlineStr"/>
+      <c r="H1845" t="inlineStr"/>
+      <c r="I1845" t="n">
+        <v>0.08213418505482188</v>
+      </c>
+      <c r="J1845" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1845" t="inlineStr"/>
+    </row>
+    <row r="1846">
+      <c r="A1846" s="1" t="n">
+        <v>1844</v>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2482.png</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr"/>
+      <c r="D1846" t="inlineStr"/>
+      <c r="E1846" t="inlineStr"/>
+      <c r="F1846" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1C[C@H](C(=O)N(C)[C@H](C(=O)N[C@H]2Cc3cccc(c3)-c3ccc4c(c3)c(c(-c3cccnc3[C@H](C)OC)n4CC)CC(C)(C)COC(=O)[C@@H]3CCCN(N3)C2=O)C(C)C)[C@@H]1C</t>
+        </is>
+      </c>
+      <c r="G1846" t="inlineStr"/>
+      <c r="H1846" t="inlineStr"/>
+      <c r="I1846" t="n">
+        <v>0.8076092181430293</v>
+      </c>
+      <c r="J1846" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1846" t="inlineStr"/>
+    </row>
+    <row r="1847">
+      <c r="A1847" s="1" t="n">
+        <v>1845</v>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2490.png</t>
+        </is>
+      </c>
+      <c r="C1847" t="inlineStr"/>
+      <c r="D1847" t="inlineStr"/>
+      <c r="E1847" t="inlineStr"/>
+      <c r="F1847" t="inlineStr">
+        <is>
+          <t>C=CC(=O)N1CC[C@H](C(=O)N(C2COC2)[C@H](C(=O)N[C@H]2Cc3cccc(c3)-c3ccc4c(c3)c(c(-c3cccnc3[C@H](C)OC)n4CC)CC(C)(C)COC(=O)[C@@H]3CCCN(N3)C2=O)C(C)C)C1</t>
+        </is>
+      </c>
+      <c r="G1847" t="inlineStr"/>
+      <c r="H1847" t="inlineStr"/>
+      <c r="I1847" t="n">
+        <v>0.7931231682292662</v>
+      </c>
+      <c r="J1847" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1847" t="inlineStr"/>
+    </row>
+    <row r="1848">
+      <c r="A1848" s="1" t="n">
+        <v>1846</v>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2494.png</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr"/>
+      <c r="D1848" t="inlineStr"/>
+      <c r="E1848" t="inlineStr"/>
+      <c r="F1848" t="inlineStr">
+        <is>
+          <t>NCCCCC1NC2(=O)[CH]34NC[CH]5(CC6=CC=C(O)C=C6)NC(=O)C(NC(=O)C(N)CC6=CC=C(Cl)C=C6)CSSCC(C(=O)NC(CC6=CC=C(O)C=C6)C(N)=O)NC(=O)[CH]NC1(=O)C(CCCCN)NC3(=O)[CH]2(CC1=CC=C(NC(=O)NC2=CC=CC=C2)C=C1)(NC5=O)C4C1=CC=C(NC(=O)NC2=CC=CC=C2)C=C1</t>
+        </is>
+      </c>
+      <c r="G1848" t="inlineStr"/>
+      <c r="H1848" t="inlineStr"/>
+      <c r="I1848" t="n">
+        <v>0.2471672306144385</v>
+      </c>
+      <c r="J1848" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1848" t="inlineStr"/>
+    </row>
+    <row r="1849">
+      <c r="A1849" s="1" t="n">
+        <v>1847</v>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2502.png</t>
+        </is>
+      </c>
+      <c r="C1849" t="inlineStr"/>
+      <c r="D1849" t="inlineStr"/>
+      <c r="E1849" t="inlineStr"/>
+      <c r="F1849" t="inlineStr">
+        <is>
+          <t>C=CC=COCC(O)C(O)C(O)CC(O)C(CO[CH]123456CC[CH]7(OCC89%10(O)CC%11%12(O8)C(N%11C8C%11C8C%118%13%14%15=C%11O8=C=%138(=C%11%14%13C(OC)[CH]%11%14(CO%13%11)O[CH]%11(C[CH](C)(O)C%11O)C%14C)=C%11%13%14%16(=C(COC%17C%18OC%17%18=O)=C(=O)(C%11)O%15)=C%11(O8)C%138C%13%15%17%18C%19[CH]%13%20C%15(N%20%17%14)C%198%11%18%16)C%129NC%10CC)O(C1C2(O)[CH]3(OC)C41C5C16)[CH]123OCO14C21C(C)C1743)OCC.CCN12(C)C(CN)C13C1OC132.O</t>
+        </is>
+      </c>
+      <c r="G1849" t="inlineStr"/>
+      <c r="H1849" t="inlineStr"/>
+      <c r="I1849" t="n">
+        <v>1.585624388286356e-20</v>
+      </c>
+      <c r="J1849" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1849" t="inlineStr"/>
+    </row>
+    <row r="1850">
+      <c r="A1850" s="1" t="n">
+        <v>1848</v>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2510.png</t>
+        </is>
+      </c>
+      <c r="C1850" t="inlineStr"/>
+      <c r="D1850" t="inlineStr"/>
+      <c r="E1850" t="inlineStr"/>
+      <c r="F1850" t="inlineStr">
+        <is>
+          <t>CCn1c(-c2cccnc2[C@H](C)OC)c2c3cc(ccc31)-c1csc(n1)C[C@H](NC(=O)CCO[C@H]1CCN(C(=O)C#CC(C)(C)N3CCC3)C1)C(=O)N1CCC[C@H](N1)C(=O)OCC(C)(C)C2.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1850" t="inlineStr"/>
+      <c r="H1850" t="inlineStr"/>
+      <c r="I1850" t="n">
+        <v>0.7769459203241242</v>
+      </c>
+      <c r="J1850" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1850" t="inlineStr"/>
+    </row>
+    <row r="1851">
+      <c r="A1851" s="1" t="n">
+        <v>1849</v>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2514.png</t>
+        </is>
+      </c>
+      <c r="C1851" t="inlineStr"/>
+      <c r="D1851" t="inlineStr"/>
+      <c r="E1851" t="inlineStr"/>
+      <c r="F1851" t="inlineStr">
+        <is>
+          <t>CC(C)CC1CN(C(=O)CC2CC2)CC(=O)NC(CCCCN)CN(C(=O)CC2=CC=CC=C2)CC(=O)NC(CC2=CC=CC=C2)CN(CC(N)=O)C(=O)CCSCC2=CC=C(C=C2)C(=O)N[CH]2(CC3=CC=CC=C3)CN(CC(=O)N1)C2C(=O)CC1CC1</t>
+        </is>
+      </c>
+      <c r="G1851" t="inlineStr"/>
+      <c r="H1851" t="inlineStr"/>
+      <c r="I1851" t="n">
+        <v>0.7885169215899096</v>
+      </c>
+      <c r="J1851" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1851" t="inlineStr"/>
+    </row>
+    <row r="1852">
+      <c r="A1852" s="1" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2522.png</t>
+        </is>
+      </c>
+      <c r="C1852" t="inlineStr"/>
+      <c r="D1852" t="inlineStr"/>
+      <c r="E1852" t="inlineStr"/>
+      <c r="F1852" t="inlineStr">
+        <is>
+          <t>CC(O)C1NC(=O)C(CCCCN)NC(=O)C(CC2=CC=C(NC(=O)C(N)CC(N)=O)C=C2)NC(=O)C(CC2=CC=C(O)C=C2)NC(=O)[CH]2(NC(=O)C(N)CC3=CC=C(Cl)C=C3)CSSC[CH]34C(SSC2C(C)NC(=O)C(N)CC2=CC=C(Cl)C=C2)C(N3C1=O)C4(=O)NC(CC1=CC=C(O)C=C1)C(N)=O.N.N.N</t>
+        </is>
+      </c>
+      <c r="G1852" t="inlineStr"/>
+      <c r="H1852" t="inlineStr"/>
+      <c r="I1852" t="n">
+        <v>0.09787428881527049</v>
+      </c>
+      <c r="J1852" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1852" t="inlineStr"/>
+    </row>
+    <row r="1853">
+      <c r="A1853" s="1" t="n">
+        <v>1851</v>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2526.png</t>
+        </is>
+      </c>
+      <c r="C1853" t="inlineStr"/>
+      <c r="D1853" t="inlineStr"/>
+      <c r="E1853" t="inlineStr"/>
+      <c r="F1853" t="inlineStr">
+        <is>
+          <t>COC(=O)C=CC(=O)NCCCCCC(=O)N[CH]C(=O)NC(CCCNC(N)=O)C(=O)NC=CC=CCOC1N(C)[CH]23(CC4C256=O=C453(=O)N[CH]623C4(=O)[CH]56(C7=O=C58N459CN784(C)[CH]57[CH]5(C)CCC8C(=O)(N%10CCCC%10C(OC)C(C)C(=O)NC(C)C(O)C%10=CC=CC=C%10)[CH]594[CH]87OC)C245CC63(C)(C4)C5)C(C)CC1(C)C</t>
+        </is>
+      </c>
+      <c r="G1853" t="inlineStr"/>
+      <c r="H1853" t="inlineStr"/>
+      <c r="I1853" t="n">
+        <v>0.0002830261033874716</v>
+      </c>
+      <c r="J1853" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1853" t="inlineStr"/>
+    </row>
+    <row r="1854">
+      <c r="A1854" s="1" t="n">
+        <v>1852</v>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2534.png</t>
+        </is>
+      </c>
+      <c r="C1854" t="inlineStr"/>
+      <c r="D1854" t="inlineStr"/>
+      <c r="E1854" t="inlineStr"/>
+      <c r="F1854" t="inlineStr">
+        <is>
+          <t>CO[C@H]1C/C(C)=C/[C@@H](CCCSC[C@H](N)C(=O)O)C(=O)C[C@H](O)[C@@H](C)[C@@H](C(C)=C[C@@H]2CC[C@@H](O)[C@H](OC)C2)OC(=O)[C@@H]2CCCCN2C(=O)C(=O)[C@]2(O)O[C@H]([C@@H](OC)C1)[C@@H](OC)C[C@H]2C</t>
+        </is>
+      </c>
+      <c r="G1854" t="inlineStr"/>
+      <c r="H1854" t="inlineStr"/>
+      <c r="I1854" t="n">
+        <v>0.8250563720899429</v>
+      </c>
+      <c r="J1854" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1854" t="inlineStr"/>
+    </row>
+    <row r="1855">
+      <c r="A1855" s="1" t="n">
+        <v>1853</v>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2538.png</t>
+        </is>
+      </c>
+      <c r="C1855" t="inlineStr"/>
+      <c r="D1855" t="inlineStr"/>
+      <c r="E1855" t="inlineStr"/>
+      <c r="F1855" t="inlineStr">
+        <is>
+          <t>CCN1C(C2=C(C(C)OC)N=CC(N3CCCN(C)CC3)=C2)=C2CC(C)(C)COC(=O)C3CCCN(N3)C(=O)C(NC(=O)C3CC3C)CC3=NC(=CS3)C34=CC2=C1(C=C3)C=C4.S.S.S</t>
+        </is>
+      </c>
+      <c r="G1855" t="inlineStr"/>
+      <c r="H1855" t="inlineStr"/>
+      <c r="I1855" t="n">
+        <v>0.5037645452641982</v>
+      </c>
+      <c r="J1855" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1855" t="inlineStr"/>
+    </row>
+    <row r="1856">
+      <c r="A1856" s="1" t="n">
+        <v>1854</v>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2562.png</t>
+        </is>
+      </c>
+      <c r="C1856" t="inlineStr"/>
+      <c r="D1856" t="inlineStr"/>
+      <c r="E1856" t="inlineStr"/>
+      <c r="F1856" t="inlineStr">
+        <is>
+          <t>CCN1C(C2=C(C(C)OC)N=CC=C2)=C2CC(C)(C)COC(=O)[CH]345CCCN67(N3)C(=O)[CH]3(NC(=O)C8CCN(C(C)=O)CC8)CC8=NC(=CS8)C8=CC2(=C1C=C8)C=CC(C)(C)COC4(=O)C1CCCN(C36=O)N157.S</t>
+        </is>
+      </c>
+      <c r="G1856" t="inlineStr"/>
+      <c r="H1856" t="inlineStr"/>
+      <c r="I1856" t="n">
+        <v>0.174634108297536</v>
+      </c>
+      <c r="J1856" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1856" t="inlineStr"/>
+    </row>
+    <row r="1857">
+      <c r="A1857" s="1" t="n">
+        <v>1855</v>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>/root/cmage-work/bigsa/cx_in_20261011T030441_3/rb_2566.png</t>
+        </is>
+      </c>
+      <c r="C1857" t="inlineStr"/>
+      <c r="D1857" t="inlineStr"/>
+      <c r="E1857" t="inlineStr"/>
+      <c r="F1857" t="inlineStr">
+        <is>
+          <t>COc1ccc(C2(c3ccc(OCCO)cc3)C=Cc3c4c(c5ccccc5c3O2)-c2ccccc2C42CCCCCCCCCCC2)cc1</t>
+        </is>
+      </c>
+      <c r="G1857" t="inlineStr"/>
+      <c r="H1857" t="inlineStr"/>
+      <c r="I1857" t="n">
+        <v>0.7018883136748434</v>
+      </c>
+      <c r="J1857" t="inlineStr">
+        <is>
+          <t>Discard this SMILES prediction</t>
+        </is>
+      </c>
+      <c r="K1857" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
